--- a/NFL_Edge_Model.xlsx
+++ b/NFL_Edge_Model.xlsx
@@ -365,8 +365,8 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="tblWeather" displayName="tblWeather" ref="A4:J38" headerRowCount="1">
-  <autoFilter ref="A4:J38"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="tblWeather" displayName="tblWeather" ref="A4:J37" headerRowCount="1">
+  <autoFilter ref="A4:J37"/>
   <tableColumns count="10">
     <tableColumn id="1" name="Game id"/>
     <tableColumn id="2" name="Venue"/>
@@ -689,7 +689,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Snapshot of the live model, generated 2026-08-23T04:20:20+00:00. Read-only: the model runs in the pipeline, not in this file.</t>
+          <t>Snapshot of the live model, generated 2026-08-23T06:00:13+00:00. Read-only: the model runs in the pipeline, not in this file.</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23T04:20:20+00:00</t>
+          <t>2026-08-23T06:00:13+00:00</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>DAL @ NYG</t>
+          <t>ATL @ PIT</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -3638,23 +3638,23 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>DAL -2.5</t>
+          <t>PIT -3</t>
         </is>
       </c>
       <c r="E31" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>0.5101</v>
+        <v>0.5097</v>
       </c>
       <c r="G31" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>-0.0134</v>
+        <v>-0.0138</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>-0.02613350288850708</v>
+        <v>-0.0250340463292979</v>
       </c>
       <c r="J31" s="10" t="n">
         <v>0.5</v>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>ATL @ PIT</t>
+          <t>DAL @ NYG</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -3679,23 +3679,23 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>PIT -3</t>
+          <t>DAL -2.5</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.5097</v>
+        <v>0.5094</v>
       </c>
       <c r="G32" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H32" s="13" t="n">
-        <v>-0.0138</v>
+        <v>-0.0141</v>
       </c>
       <c r="I32" s="13" t="n">
-        <v>-0.0250340463292979</v>
+        <v>-0.0275104067761156</v>
       </c>
       <c r="J32" s="14" t="n">
         <v>0.5</v>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>ATL @ PIT</t>
+          <t>DAL @ NYG</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -4212,23 +4212,23 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>ATL +3</t>
+          <t>NYG +2.5</t>
         </is>
       </c>
       <c r="E45" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>0.4903</v>
+        <v>0.4906</v>
       </c>
       <c r="G45" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H45" s="8" t="n">
-        <v>-0.0299</v>
+        <v>-0.0297</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>-0.05931477362409254</v>
+        <v>-0.06339868413297528</v>
       </c>
       <c r="J45" s="10" t="n">
         <v>0.5</v>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>DAL @ NYG</t>
+          <t>ATL @ PIT</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -4253,23 +4253,23 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>NYG +2.5</t>
+          <t>ATL +3</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.4899</v>
+        <v>0.4903</v>
       </c>
       <c r="G46" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H46" s="13" t="n">
-        <v>-0.0302</v>
+        <v>-0.0299</v>
       </c>
       <c r="I46" s="13" t="n">
-        <v>-0.06477558802058375</v>
+        <v>-0.05931477362409254</v>
       </c>
       <c r="J46" s="14" t="n">
         <v>0.5</v>
@@ -6036,7 +6036,7 @@
         </is>
       </c>
       <c r="D9" s="22" t="n">
-        <v>-2.43</v>
+        <v>-2.39</v>
       </c>
       <c r="E9" s="22" t="n">
         <v>2.5</v>
@@ -7238,7 +7238,7 @@
         </is>
       </c>
       <c r="C22" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D22" s="18" t="n">
         <v>-0.07000000000000001</v>
@@ -7270,7 +7270,7 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D23" s="16" t="n">
         <v>-0.34</v>
@@ -7302,7 +7302,7 @@
         </is>
       </c>
       <c r="C24" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D24" s="18" t="n">
         <v>-0.47</v>
@@ -7334,7 +7334,7 @@
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D25" s="16" t="n">
         <v>-0.65</v>
@@ -7366,7 +7366,7 @@
         </is>
       </c>
       <c r="C26" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D26" s="18" t="n">
         <v>-0.8100000000000001</v>
@@ -7398,7 +7398,7 @@
         </is>
       </c>
       <c r="C27" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D27" s="16" t="n">
         <v>-1.39</v>
@@ -7430,7 +7430,7 @@
         </is>
       </c>
       <c r="C28" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D28" s="18" t="n">
         <v>-1.86</v>
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="C29" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D29" s="16" t="n">
         <v>-2</v>
@@ -7494,7 +7494,7 @@
         </is>
       </c>
       <c r="C30" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D30" s="18" t="n">
         <v>-2.32</v>
@@ -7526,7 +7526,7 @@
         </is>
       </c>
       <c r="C31" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D31" s="16" t="n">
         <v>-2.63</v>
@@ -7558,7 +7558,7 @@
         </is>
       </c>
       <c r="C32" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D32" s="18" t="n">
         <v>-3.17</v>
@@ -7590,7 +7590,7 @@
         </is>
       </c>
       <c r="C33" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D33" s="16" t="n">
         <v>-3.24</v>
@@ -7622,7 +7622,7 @@
         </is>
       </c>
       <c r="C34" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D34" s="18" t="n">
         <v>-3.76</v>
@@ -7654,7 +7654,7 @@
         </is>
       </c>
       <c r="C35" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D35" s="16" t="n">
         <v>-4.7</v>
@@ -7686,7 +7686,7 @@
         </is>
       </c>
       <c r="C36" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D36" s="18" t="n">
         <v>-5.61</v>
@@ -9250,14 +9250,14 @@
       <c r="I36" s="12" t="n"/>
       <c r="J36" s="12" t="n"/>
       <c r="K36" s="17" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="L36" s="17" t="n">
         <v>13</v>
       </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>13:59 - 4th</t>
+          <t>Final</t>
         </is>
       </c>
     </row>
@@ -27924,12 +27924,12 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>Rome Odunze</t>
+          <t>Cairo Santos</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>Odunze brought in one of two targets for 18 yards in the Bears' 27-9 preseason loss to the Bengals on Saturday.</t>
+          <t>Santos connected on field-goal attempts of 45, 26 and 44 yards and missed wide right from 53 yards in the Bears' 27-9 preseason loss to the Bengals on Saturday.</t>
         </is>
       </c>
     </row>
@@ -27956,7 +27956,7 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Colston Loveland</t>
+          <t>Sam Roush</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
@@ -27976,7 +27976,7 @@
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>Loveland brought in one of three targets for 10 yards in the Bears' 27-9 preseason loss to the Bengals on Saturday.</t>
+          <t>Roush brought in two of three targets for 30 yards in the Bears' 27-9 preseason loss to the Bengals on Saturday.</t>
         </is>
       </c>
     </row>
@@ -27988,12 +27988,12 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>Caleb Williams</t>
+          <t>Rome Odunze</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
@@ -28008,7 +28008,7 @@
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>Williams completed two of five passes for 28 yards with no touchdowns or interceptions in the Bears' 27-9 preseason loss to the Bengals on Saturday.</t>
+          <t>Odunze brought in one of two targets for 18 yards in the Bears' 27-9 preseason loss to the Bengals on Saturday.</t>
         </is>
       </c>
     </row>
@@ -28020,27 +28020,27 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Tyrique Stevenson</t>
+          <t>Colston Loveland</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>Stevenson (undisclosed) returned to practice Thursday following a week-long absence, Brad Biggs of the Chicago Tribune reports.</t>
+          <t>Loveland brought in one of three targets for 10 yards in the Bears' 27-9 preseason loss to the Bengals on Saturday.</t>
         </is>
       </c>
     </row>
@@ -28052,7 +28052,7 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>Tyson Bagent</t>
+          <t>Caleb Williams</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
@@ -28062,17 +28062,17 @@
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>Bagent is still dealing with a hamstring injury and did not join the team on its trip to Cincinnati for a preseason game this Saturday, Courtney Cronin of ESPN.com reports.</t>
+          <t>Williams completed two of five passes for 28 yards with no touchdowns or interceptions in the Bears' 27-9 preseason loss to the Bengals on Saturday.</t>
         </is>
       </c>
     </row>
@@ -28084,12 +28084,12 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Xavier Woods</t>
+          <t>Tyrique Stevenson</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
@@ -28104,7 +28104,7 @@
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>Stevenson (undisclosed) returned to practice Thursday following a week-long absence, Brad Biggs of the Chicago Tribune reports.</t>
         </is>
       </c>
     </row>
@@ -28116,12 +28116,12 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>Nephi Sewell</t>
+          <t>Tyson Bagent</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
@@ -28131,12 +28131,12 @@
       </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>Concussion</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>Bagent is still dealing with a hamstring injury and did not join the team on its trip to Cincinnati for a preseason game this Saturday, Courtney Cronin of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -28148,12 +28148,12 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Ruben Hyppolite II</t>
+          <t>Xavier Woods</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
@@ -28180,27 +28180,27 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>Nikola Kalinic</t>
+          <t>Nephi Sewell</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Concussion</t>
         </is>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>ir</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -28212,27 +28212,27 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Coby Bryant</t>
+          <t>Ruben Hyppolite II</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Out</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>Surgery</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>out</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -28244,17 +28244,17 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>Nikola Kalinic</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
@@ -28264,7 +28264,7 @@
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>ir</t>
         </is>
       </c>
     </row>
@@ -28276,27 +28276,27 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Dallis Flowers</t>
+          <t>Coby Bryant</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Surgery</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>ir</t>
+          <t>out</t>
         </is>
       </c>
     </row>
@@ -28308,17 +28308,17 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>Jonathan Garvin</t>
+          <t>Luther Burden III</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
@@ -28328,7 +28328,7 @@
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>ir</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -28340,25 +28340,29 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Ozzy Trapilo</t>
+          <t>Dallis Flowers</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>OT</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="F143" s="4" t="inlineStr"/>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F143" s="4" t="inlineStr">
+        <is>
+          <t>ir</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
@@ -28368,7 +28372,7 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>Dayo Odeyingbo</t>
+          <t>Jonathan Garvin</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
@@ -28378,15 +28382,19 @@
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="F144" s="5" t="inlineStr"/>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F144" s="5" t="inlineStr">
+        <is>
+          <t>ir</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
@@ -28396,12 +28404,12 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Zavion Thomas</t>
+          <t>Ozzy Trapilo</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>OT</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
@@ -28414,11 +28422,7 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F145" s="4" t="inlineStr">
-        <is>
-          <t>Thomas (knee) was a full participant in Tuesday's practice, Brad Biggs of the Chicago Tribune reports.</t>
-        </is>
-      </c>
+      <c r="F145" s="4" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
@@ -28428,29 +28432,25 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>Kyle Monangai</t>
+          <t>Dayo Odeyingbo</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="F146" s="5" t="inlineStr">
-        <is>
-          <t>Monangai (knee) is considered week-to-week, Adam Jahns of AllCHGO.com reports.</t>
-        </is>
-      </c>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F146" s="5" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
@@ -28460,12 +28460,12 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>Marcus Davenport</t>
+          <t>Zavion Thomas</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
@@ -28480,7 +28480,7 @@
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>The Bears signed Davenport to a contract Monday, NFL reporter Jordan Schultz reports.</t>
+          <t>Thomas (knee) was a full participant in Tuesday's practice, Brad Biggs of the Chicago Tribune reports.</t>
         </is>
       </c>
     </row>
@@ -28492,7 +28492,7 @@
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>Salvon Ahmed</t>
+          <t>Kyle Monangai</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
@@ -28502,17 +28502,17 @@
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F148" s="5" t="inlineStr">
         <is>
-          <t>Ahmed was among the Bears' top performers in Saturday's 34-10 preseason win over the Browns, which was highlighted by his 49-yard touchdown catch, Courtney Cronin of ESPN.com reports.</t>
+          <t>Monangai (knee) is considered week-to-week, Adam Jahns of AllCHGO.com reports.</t>
         </is>
       </c>
     </row>
@@ -28524,12 +28524,12 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>Braxton Jones</t>
+          <t>Marcus Davenport</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>OT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
@@ -28544,7 +28544,7 @@
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>Jones (knee) returned to practice Sunday, Adam Hoge of AllCHGO.com reports.</t>
+          <t>The Bears signed Davenport to a contract Monday, NFL reporter Jordan Schultz reports.</t>
         </is>
       </c>
     </row>
@@ -28556,12 +28556,12 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>Cam Lewis</t>
+          <t>Salvon Ahmed</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
@@ -28576,7 +28576,7 @@
       </c>
       <c r="F150" s="5" t="inlineStr">
         <is>
-          <t>Lewis made one tackle assist during Saturday's preseason opener against the Browns.</t>
+          <t>Ahmed was among the Bears' top performers in Saturday's 34-10 preseason win over the Browns, which was highlighted by his 49-yard touchdown catch, Courtney Cronin of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -28588,12 +28588,12 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>Montez Sweat</t>
+          <t>Braxton Jones</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>OT</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
@@ -28608,7 +28608,7 @@
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>Sweat (undisclosed) was a full participant in Sunday's practice, Adam Hoge of AllCHGO.com reports.</t>
+          <t>Jones (knee) returned to practice Sunday, Adam Hoge of AllCHGO.com reports.</t>
         </is>
       </c>
     </row>
@@ -28620,7 +28620,7 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>Kyler Gordon</t>
+          <t>Cam Lewis</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
@@ -28630,17 +28630,17 @@
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>Out</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F152" s="5" t="inlineStr">
         <is>
-          <t>Bears coach Ben Johnson said Saturday that Gordon's timeline to return to practice from his calf injury is "unknown," Courtney Cronin of ESPN.com reports.</t>
+          <t>Lewis made one tackle assist during Saturday's preseason opener against the Browns.</t>
         </is>
       </c>
     </row>
@@ -28652,12 +28652,12 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>Montez Sweat</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
@@ -28672,7 +28672,7 @@
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>Swift has been one of the brightest stars of training camp for the Bears, Courtney Cronin of ESPN.com reports.</t>
+          <t>Sweat (undisclosed) was a full participant in Sunday's practice, Adam Hoge of AllCHGO.com reports.</t>
         </is>
       </c>
     </row>
@@ -28684,27 +28684,27 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>Jahdae Walker</t>
+          <t>Kyler Gordon</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F154" s="5" t="inlineStr">
         <is>
-          <t>Walker was listed as a second-string wide receiver on the Bears' first unofficial depth chart that was released Tuesday, Kevin Fishbain of The Athletic reports.</t>
+          <t>Bears coach Ben Johnson said Saturday that Gordon's timeline to return to practice from his calf injury is "unknown," Courtney Cronin of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -28716,12 +28716,12 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>Joe Burrow</t>
+          <t>Evan McPherson</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
@@ -28736,7 +28736,7 @@
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>Bengals head coach Zac Taylor said that Burrow and other key starters are in line to be rested for Saturday's preseason game against the Bears, Jay Morrison of SI.com reports.</t>
+          <t>McPherson connected on field-goal attempts of 25 and 58 yards while also knocking home all three PATs in the Bengals' 27-9 preseason win over the Bears on Saturday.</t>
         </is>
       </c>
     </row>
@@ -28748,27 +28748,27 @@
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>Myles Murphy</t>
+          <t>Colbie Young</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F156" s="5" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>Young brought in three of eight targets for 48 yards and a touchdown in the Bengals' 27-9 preseason win over the Bears on Saturday.</t>
         </is>
       </c>
     </row>
@@ -28780,27 +28780,27 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>Dax Hill</t>
+          <t>Joe Burrow</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>Soreness</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>Bengals head coach Zac Taylor said that Burrow and other key starters are in line to be rested for Saturday's preseason game against the Bears, Jay Morrison of SI.com reports.</t>
         </is>
       </c>
     </row>
@@ -28812,12 +28812,12 @@
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>McKinnley Jackson</t>
+          <t>Myles Murphy</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
@@ -28844,25 +28844,29 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>Josh Kattus</t>
+          <t>Dax Hill</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="F159" s="4" t="inlineStr"/>
+          <t>Soreness</t>
+        </is>
+      </c>
+      <c r="F159" s="4" t="inlineStr">
+        <is>
+          <t>questionable</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
@@ -28872,12 +28876,12 @@
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>Bryan Cook</t>
+          <t>McKinnley Jackson</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
@@ -28904,12 +28908,12 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>Kris Jenkins Jr.</t>
+          <t>Josh Kattus</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
@@ -28932,25 +28936,29 @@
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>Cam Grandy</t>
+          <t>Bryan Cook</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="F162" s="5" t="inlineStr"/>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F162" s="5" t="inlineStr">
+        <is>
+          <t>questionable</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
@@ -28960,12 +28968,12 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>Jack Endries</t>
+          <t>Kris Jenkins Jr.</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
@@ -28978,11 +28986,7 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F163" s="4" t="inlineStr">
-        <is>
-          <t>Endries caught a 17-yard touchdown reception from Joe Flacco in Thursday's preseason opener against the Lions. He's competing with veteran Tanner Hudson for a roster spot, Geoff Hobson of Bengals.com reports.</t>
-        </is>
-      </c>
+      <c r="F163" s="4" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
@@ -28992,12 +28996,12 @@
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>B.J. Hill</t>
+          <t>Cam Grandy</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
@@ -29010,11 +29014,7 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F164" s="5" t="inlineStr">
-        <is>
-          <t>The Bengals activated Hill (undisclosed) from the active/PUP list Saturday after he passed a physical.</t>
-        </is>
-      </c>
+      <c r="F164" s="5" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
@@ -29024,12 +29024,12 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Colbie Young</t>
+          <t>Jack Endries</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
@@ -29044,7 +29044,7 @@
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>Young caught two of four targets for 28 yards in Thursday's 16-14 preseason win over the Lions.</t>
+          <t>Endries caught a 17-yard touchdown reception from Joe Flacco in Thursday's preseason opener against the Lions. He's competing with veteran Tanner Hudson for a roster spot, Geoff Hobson of Bengals.com reports.</t>
         </is>
       </c>
     </row>
@@ -29056,12 +29056,12 @@
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>Mike Gesicki</t>
+          <t>B.J. Hill</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
@@ -29076,7 +29076,7 @@
       </c>
       <c r="F166" s="5" t="inlineStr">
         <is>
-          <t>Gesicki didn't catch his only target in Thursday's 16-14 preseason win over the Lions.</t>
+          <t>The Bengals activated Hill (undisclosed) from the active/PUP list Saturday after he passed a physical.</t>
         </is>
       </c>
     </row>
@@ -29088,12 +29088,12 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Tee Higgins</t>
+          <t>Mike Gesicki</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
@@ -29108,7 +29108,7 @@
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>Higgins and quarterback Joe Burrow have had no trouble connecting at practice, Dan Hoard of the Bengals' official website reports.</t>
+          <t>Gesicki didn't catch his only target in Thursday's 16-14 preseason win over the Lions.</t>
         </is>
       </c>
     </row>
@@ -29120,12 +29120,12 @@
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>Chase Brown</t>
+          <t>Tee Higgins</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
@@ -29140,7 +29140,7 @@
       </c>
       <c r="F168" s="5" t="inlineStr">
         <is>
-          <t>Brown rushed five times for 16 yards in Thursday's preseason-opening 16-14 win over the Lions.</t>
+          <t>Higgins and quarterback Joe Burrow have had no trouble connecting at practice, Dan Hoard of the Bengals' official website reports.</t>
         </is>
       </c>
     </row>
@@ -29152,12 +29152,12 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
@@ -29172,7 +29172,7 @@
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>Chase caught his only target for 16 yards in Thursday's preseason-opening 16-14 win over the Lions.</t>
+          <t>Brown rushed five times for 16 yards in Thursday's preseason-opening 16-14 win over the Lions.</t>
         </is>
       </c>
     </row>
@@ -29184,12 +29184,12 @@
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>Cashius Howell</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
@@ -29204,7 +29204,7 @@
       </c>
       <c r="F170" s="5" t="inlineStr">
         <is>
-          <t>Howell has "been a monster in camp," particularly surprising the Bengals' coaching staff with his strength, Sports Illustrated's Albert Breer reports.</t>
+          <t>Chase caught his only target for 16 yards in Thursday's preseason-opening 16-14 win over the Lions.</t>
         </is>
       </c>
     </row>
@@ -29216,12 +29216,12 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>Erick All Jr.</t>
+          <t>Cashius Howell</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
@@ -29236,7 +29236,7 @@
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>All (knee) passed his conditioning test and is all set to participate in training camp, Dan Hoard of the Bengals' official site reports.</t>
+          <t>Howell has "been a monster in camp," particularly surprising the Bengals' coaching staff with his strength, Sports Illustrated's Albert Breer reports.</t>
         </is>
       </c>
     </row>
@@ -29248,12 +29248,12 @@
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
-          <t>Jonathan Allen</t>
+          <t>Erick All Jr.</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D172" s="5" t="inlineStr">
@@ -29266,7 +29266,11 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F172" s="5" t="inlineStr"/>
+      <c r="F172" s="5" t="inlineStr">
+        <is>
+          <t>All (knee) passed his conditioning test and is all set to participate in training camp, Dan Hoard of the Bengals' official site reports.</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
@@ -29276,29 +29280,25 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>Shemar Stewart</t>
+          <t>Jonathan Allen</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E173" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="F173" s="4" t="inlineStr">
-        <is>
-          <t>Stewart will miss several weeks due to a hyperextended knee, head coach Zac Taylor revealed Thursday, Charlie Goldsmith of FOX19 Cincinnati reports.</t>
-        </is>
-      </c>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F173" s="4" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
@@ -29308,27 +29308,27 @@
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>Josh Newton</t>
+          <t>Shemar Stewart</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F174" s="5" t="inlineStr">
         <is>
-          <t>Newton (hamstring) is expected to compete for the Bengals' starting cornerback role, Chris Roling of USA Today reports.</t>
+          <t>Stewart will miss several weeks due to a hyperextended knee, head coach Zac Taylor revealed Thursday, Charlie Goldsmith of FOX19 Cincinnati reports.</t>
         </is>
       </c>
     </row>
@@ -29340,12 +29340,12 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Connor Lew</t>
+          <t>Josh Newton</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
@@ -29360,7 +29360,7 @@
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>Lew (knee) participated in Cincinnati's training camp Wednesday, Dan Hoard of the team's official site reports.</t>
+          <t>Newton (hamstring) is expected to compete for the Bengals' starting cornerback role, Chris Roling of USA Today reports.</t>
         </is>
       </c>
     </row>
@@ -29372,12 +29372,12 @@
       </c>
       <c r="B176" s="5" t="inlineStr">
         <is>
-          <t>DJ Turner II</t>
+          <t>Connor Lew</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D176" s="5" t="inlineStr">
@@ -29392,7 +29392,7 @@
       </c>
       <c r="F176" s="5" t="inlineStr">
         <is>
-          <t>Turner (calf) was active in Wednesday's training camp practice, mixing it up with Ja'Marr Chase during 7-on-7 and 11-on-11 drills, Geoff Hobson of the Bengals' official site reports.</t>
+          <t>Lew (knee) participated in Cincinnati's training camp Wednesday, Dan Hoard of the team's official site reports.</t>
         </is>
       </c>
     </row>
@@ -29404,12 +29404,12 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>Charlie Jones</t>
+          <t>DJ Turner II</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
@@ -29424,7 +29424,7 @@
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>Jones (ankle) is participating at the Bengals' training camp, Sam Greene and Jacob Sebastian of The Cincinnati Enquirer report.</t>
+          <t>Turner (calf) was active in Wednesday's training camp practice, mixing it up with Ja'Marr Chase during 7-on-7 and 11-on-11 drills, Geoff Hobson of the Bengals' official site reports.</t>
         </is>
       </c>
     </row>
@@ -29436,12 +29436,12 @@
       </c>
       <c r="B178" s="5" t="inlineStr">
         <is>
-          <t>Tahj Brooks</t>
+          <t>Charlie Jones</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D178" s="5" t="inlineStr">
@@ -29456,7 +29456,7 @@
       </c>
       <c r="F178" s="5" t="inlineStr">
         <is>
-          <t>Brooks will compete against Samaje Perine in training camp for the No. 2 running back role behind Chase Brown, Michael Hull of the Bengals' official site reports.</t>
+          <t>Jones (ankle) is participating at the Bengals' training camp, Sam Greene and Jacob Sebastian of The Cincinnati Enquirer report.</t>
         </is>
       </c>
     </row>
@@ -29468,12 +29468,12 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>Evan McPherson</t>
+          <t>Tahj Brooks</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
@@ -29488,7 +29488,7 @@
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>McPherson will again work as Cincinnati's primary kicker during the upcoming season following a bounce-back performance last year, John Sheeran of A to Z Sports reports.</t>
+          <t>Brooks will compete against Samaje Perine in training camp for the No. 2 running back role behind Chase Brown, Michael Hull of the Bengals' official site reports.</t>
         </is>
       </c>
     </row>
@@ -30288,12 +30288,12 @@
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Jaydon Blue</t>
+          <t>Joe Milton III</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D205" s="4" t="inlineStr">
@@ -30306,7 +30306,11 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F205" s="4" t="inlineStr"/>
+      <c r="F205" s="4" t="inlineStr">
+        <is>
+          <t>Milton completed nine of 13 passes for 179 yards with two touchdowns and no interceptions and rushed three times for two yards and another score in the Cowboys' 34-13 preseason win over the Cardinals on Saturday.</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="5" t="inlineStr">
@@ -30316,27 +30320,27 @@
       </c>
       <c r="B206" s="5" t="inlineStr">
         <is>
-          <t>Zion Childress</t>
+          <t>Jaydon Blue</t>
         </is>
       </c>
       <c r="C206" s="5" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D206" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E206" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F206" s="5" t="inlineStr">
         <is>
-          <t>Childress (hamstring) returned to practice as a limited participant Thursday, Calvin Watkins of The Dallas Morning News reports.</t>
+          <t>Blue (shoulder) rushed 15 times for 75 yards in the Cowboys' 34-13 preseason win over the Cardinals on Saturday. He also returned one kickoff for 26 yards.</t>
         </is>
       </c>
     </row>
@@ -30348,27 +30352,27 @@
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>Michael Trigg</t>
+          <t>Malik Davis</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D207" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E207" s="4" t="inlineStr">
         <is>
-          <t>Toe</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>Trigg (toe) did not practice Thursday, Tommy Yarrish of the Cowboys' official site reports.</t>
+          <t>Davis rushed five times for 29 yards and brought in his only target for an eight-yard touchdown in the Cowboys' 34-13 preseason win over the Cardinals on Saturday. He also committed a fumble but recovered and ran back one kickoff for 31 yards.</t>
         </is>
       </c>
     </row>
@@ -30380,12 +30384,12 @@
       </c>
       <c r="B208" s="5" t="inlineStr">
         <is>
-          <t>Tyler Guyton</t>
+          <t>Julius Wood</t>
         </is>
       </c>
       <c r="C208" s="5" t="inlineStr">
         <is>
-          <t>OT</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D208" s="5" t="inlineStr">
@@ -30395,12 +30399,12 @@
       </c>
       <c r="E208" s="5" t="inlineStr">
         <is>
-          <t>Soreness</t>
+          <t>Concussion</t>
         </is>
       </c>
       <c r="F208" s="5" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>Wood has entered the league's concussion protocol and has been ruled out for the rest of Saturday's preseason game against the Cardinals, Patrik Walker of the Cowboys' official site reports.</t>
         </is>
       </c>
     </row>
@@ -30412,12 +30416,12 @@
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>Phil Mafah</t>
+          <t>Zion Childress</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D209" s="4" t="inlineStr">
@@ -30432,7 +30436,7 @@
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>Childress (hamstring) returned to practice as a limited participant Thursday, Calvin Watkins of The Dallas Morning News reports.</t>
         </is>
       </c>
     </row>
@@ -30444,25 +30448,29 @@
       </c>
       <c r="B210" s="5" t="inlineStr">
         <is>
-          <t>Jalen Thompson</t>
+          <t>Michael Trigg</t>
         </is>
       </c>
       <c r="C210" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D210" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E210" s="5" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="F210" s="5" t="inlineStr"/>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F210" s="5" t="inlineStr">
+        <is>
+          <t>Trigg (toe) did not practice Thursday, Tommy Yarrish of the Cowboys' official site reports.</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
@@ -30472,12 +30480,12 @@
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>Jonathan Bullard</t>
+          <t>Tyler Guyton</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>OT</t>
         </is>
       </c>
       <c r="D211" s="4" t="inlineStr">
@@ -30504,27 +30512,27 @@
       </c>
       <c r="B212" s="5" t="inlineStr">
         <is>
-          <t>Princeton Fant</t>
+          <t>Phil Mafah</t>
         </is>
       </c>
       <c r="C212" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D212" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E212" s="5" t="inlineStr">
         <is>
-          <t>Surgery</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F212" s="5" t="inlineStr">
         <is>
-          <t>ir</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -30536,12 +30544,12 @@
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>Ajani Cornelius</t>
+          <t>Jalen Thompson</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>OT</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D213" s="4" t="inlineStr">
@@ -30564,25 +30572,29 @@
       </c>
       <c r="B214" s="5" t="inlineStr">
         <is>
-          <t>P.J. Locke</t>
+          <t>Jonathan Bullard</t>
         </is>
       </c>
       <c r="C214" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="D214" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E214" s="5" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="F214" s="5" t="inlineStr"/>
+          <t>Soreness</t>
+        </is>
+      </c>
+      <c r="F214" s="5" t="inlineStr">
+        <is>
+          <t>questionable</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
@@ -30592,25 +30604,29 @@
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>James Houston</t>
+          <t>Princeton Fant</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D215" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E215" s="4" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="F215" s="4" t="inlineStr"/>
+          <t>Surgery</t>
+        </is>
+      </c>
+      <c r="F215" s="4" t="inlineStr">
+        <is>
+          <t>ir</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="5" t="inlineStr">
@@ -30620,12 +30636,12 @@
       </c>
       <c r="B216" s="5" t="inlineStr">
         <is>
-          <t>DeMarvion Overshown</t>
+          <t>Ajani Cornelius</t>
         </is>
       </c>
       <c r="C216" s="5" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>OT</t>
         </is>
       </c>
       <c r="D216" s="5" t="inlineStr">
@@ -30638,11 +30654,7 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F216" s="5" t="inlineStr">
-        <is>
-          <t>Overshown (lower body) participated at the Cowboys' training camp practice Monday, Todd Archer of ESPN.com reports.</t>
-        </is>
-      </c>
+      <c r="F216" s="5" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
@@ -30652,12 +30664,12 @@
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>Jaishawn Barham</t>
+          <t>P.J. Locke</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D217" s="4" t="inlineStr">
@@ -30670,11 +30682,7 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F217" s="4" t="inlineStr">
-        <is>
-          <t>Barham (groin) returned to practice Monday, Todd Archer of ESPN.com reports.</t>
-        </is>
-      </c>
+      <c r="F217" s="4" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="5" t="inlineStr">
@@ -30684,7 +30692,7 @@
       </c>
       <c r="B218" s="5" t="inlineStr">
         <is>
-          <t>Von Miller</t>
+          <t>James Houston</t>
         </is>
       </c>
       <c r="C218" s="5" t="inlineStr">
@@ -30702,11 +30710,7 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F218" s="5" t="inlineStr">
-        <is>
-          <t>Miller is not expected to practice with the Cowboys this week, Calvin Watkins of The Dallas Morning News reports.</t>
-        </is>
-      </c>
+      <c r="F218" s="5" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
@@ -30716,12 +30720,12 @@
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>Alijah Clark</t>
+          <t>DeMarvion Overshown</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D219" s="4" t="inlineStr">
@@ -30736,7 +30740,7 @@
       </c>
       <c r="F219" s="4" t="inlineStr">
         <is>
-          <t>Clark (ankle) recorded one tackle in the Cowboys' 17-7 preseason win over the Seahawks on Saturday.</t>
+          <t>Overshown (lower body) participated at the Cowboys' training camp practice Monday, Todd Archer of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -30748,12 +30752,12 @@
       </c>
       <c r="B220" s="5" t="inlineStr">
         <is>
-          <t>Camden Brown</t>
+          <t>Jaishawn Barham</t>
         </is>
       </c>
       <c r="C220" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D220" s="5" t="inlineStr">
@@ -30768,7 +30772,7 @@
       </c>
       <c r="F220" s="5" t="inlineStr">
         <is>
-          <t>Brown caught all three of his targets for 62 yards and two touchdowns during Saturday night's preseason game against the Seahawks.</t>
+          <t>Barham (groin) returned to practice Monday, Todd Archer of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -30780,12 +30784,12 @@
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>Anthony Smith</t>
+          <t>Von Miller</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D221" s="4" t="inlineStr">
@@ -30800,7 +30804,7 @@
       </c>
       <c r="F221" s="4" t="inlineStr">
         <is>
-          <t>Smith brought in two of five targets for 28 yards and rushed once for nine yards in the Cowboys' 17-7 preseason win over the Seahawks on Saturday.</t>
+          <t>Miller is not expected to practice with the Cowboys this week, Calvin Watkins of The Dallas Morning News reports.</t>
         </is>
       </c>
     </row>
@@ -30812,12 +30816,12 @@
       </c>
       <c r="B222" s="5" t="inlineStr">
         <is>
-          <t>Marquez Valdes-Scantling</t>
+          <t>Alijah Clark</t>
         </is>
       </c>
       <c r="C222" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D222" s="5" t="inlineStr">
@@ -30832,7 +30836,7 @@
       </c>
       <c r="F222" s="5" t="inlineStr">
         <is>
-          <t>Valdes-Scantling failed to bring in his only target in the Cowboys' 17-7 preseason win over the Seahawks on Saturday.</t>
+          <t>Clark (ankle) recorded one tackle in the Cowboys' 17-7 preseason win over the Seahawks on Saturday.</t>
         </is>
       </c>
     </row>
@@ -30844,12 +30848,12 @@
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>Brandon Aubrey</t>
+          <t>Camden Brown</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D223" s="4" t="inlineStr">
@@ -30864,7 +30868,7 @@
       </c>
       <c r="F223" s="4" t="inlineStr">
         <is>
-          <t>Aubrey made his only field-goal attempt from 29 yards and knocked home both extra-point tries in the Cowboys' 17-7 preseason win over the Seahawks on Saturday.</t>
+          <t>Brown caught all three of his targets for 62 yards and two touchdowns during Saturday night's preseason game against the Seahawks.</t>
         </is>
       </c>
     </row>
@@ -30876,7 +30880,7 @@
       </c>
       <c r="B224" s="5" t="inlineStr">
         <is>
-          <t>Ryan Flournoy</t>
+          <t>Anthony Smith</t>
         </is>
       </c>
       <c r="C224" s="5" t="inlineStr">
@@ -30896,7 +30900,7 @@
       </c>
       <c r="F224" s="5" t="inlineStr">
         <is>
-          <t>Flournoy isn't suited up ahead of Saturday's preseason opener versus Seattle, Nick Harris of the Fort Worth Star-Telegram reports.</t>
+          <t>Smith brought in two of five targets for 28 yards and rushed once for nine yards in the Cowboys' 17-7 preseason win over the Seahawks on Saturday.</t>
         </is>
       </c>
     </row>
@@ -30908,12 +30912,12 @@
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>Jake Ferguson</t>
+          <t>Marquez Valdes-Scantling</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D225" s="4" t="inlineStr">
@@ -30928,7 +30932,7 @@
       </c>
       <c r="F225" s="4" t="inlineStr">
         <is>
-          <t>Ferguson isn't suited up for Saturday's preseason contest against the Seahawks, Nick Harris of the Fort Worth Star-Telegram reports.</t>
+          <t>Valdes-Scantling failed to bring in his only target in the Cowboys' 17-7 preseason win over the Seahawks on Saturday.</t>
         </is>
       </c>
     </row>
@@ -30940,12 +30944,12 @@
       </c>
       <c r="B226" s="5" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>Brandon Aubrey</t>
         </is>
       </c>
       <c r="C226" s="5" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="D226" s="5" t="inlineStr">
@@ -30960,7 +30964,7 @@
       </c>
       <c r="F226" s="5" t="inlineStr">
         <is>
-          <t>Prescott isn't slated to play in Saturday's preseason matchup versus Seattle, Nick Harris of the Fort Worth Star-Telegram reports.</t>
+          <t>Aubrey made his only field-goal attempt from 29 yards and knocked home both extra-point tries in the Cowboys' 17-7 preseason win over the Seahawks on Saturday.</t>
         </is>
       </c>
     </row>
@@ -30972,12 +30976,12 @@
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>Devin Moore</t>
+          <t>Ryan Flournoy</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D227" s="4" t="inlineStr">
@@ -30992,7 +30996,7 @@
       </c>
       <c r="F227" s="4" t="inlineStr">
         <is>
-          <t>Moore (groin) was an active participant at the Cowboys' training camp practice Thursday, Tommy Yarrish of the team's official site reports.</t>
+          <t>Flournoy isn't suited up ahead of Saturday's preseason opener versus Seattle, Nick Harris of the Fort Worth Star-Telegram reports.</t>
         </is>
       </c>
     </row>
@@ -31004,12 +31008,12 @@
       </c>
       <c r="B228" s="5" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>Jake Ferguson</t>
         </is>
       </c>
       <c r="C228" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D228" s="5" t="inlineStr">
@@ -31024,7 +31028,7 @@
       </c>
       <c r="F228" s="5" t="inlineStr">
         <is>
-          <t>Pickens has impressed throughout the Cowboys' training camp, Dan Rogers of SB Nation reports.</t>
+          <t>Ferguson isn't suited up for Saturday's preseason contest against the Seahawks, Nick Harris of the Fort Worth Star-Telegram reports.</t>
         </is>
       </c>
     </row>
@@ -31036,12 +31040,12 @@
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>CeeDee Lamb</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D229" s="4" t="inlineStr">
@@ -31056,7 +31060,7 @@
       </c>
       <c r="F229" s="4" t="inlineStr">
         <is>
-          <t>Lamb recently told reporters that he and QB Dak Prescott are "hitting on all cylinders" at training camp, Tommy Yarish of DallasCowboys.com reports.</t>
+          <t>Prescott isn't slated to play in Saturday's preseason matchup versus Seattle, Nick Harris of the Fort Worth Star-Telegram reports.</t>
         </is>
       </c>
     </row>
@@ -35964,7 +35968,7 @@
       </c>
       <c r="F384" s="5" t="inlineStr">
         <is>
-          <t>Walker rushed twice for four yards in the Chiefs' 16-15 preseason loss to the Bengals on Saturday.</t>
+          <t>Walker rushed twice for four yards in the Chiefs' 16-15 preseason loss to the Buccaneers on Saturday.</t>
         </is>
       </c>
     </row>
@@ -38340,7 +38344,7 @@
       </c>
       <c r="F459" s="4" t="inlineStr">
         <is>
-          <t>Rickert (knee) won't return to the Ram's preseason matchup versus the Saints on Saturday.</t>
+          <t>Rickert (knee) won't return to the Rams' preseason matchup versus the Saints on Saturday.</t>
         </is>
       </c>
     </row>
@@ -46940,27 +46944,27 @@
       </c>
       <c r="B730" s="5" t="inlineStr">
         <is>
-          <t>Chris Braswell</t>
+          <t>Ted Hurst III</t>
         </is>
       </c>
       <c r="C730" s="5" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D730" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E730" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F730" s="5" t="inlineStr">
         <is>
-          <t>Braswell (undisclosed) did not play in the Buccaneers' 16-15 preseason win over the Chiefs on Saturday, Greg Auman of Fox Sports reports.</t>
+          <t>Hurst failed to bring in his only target in the Buccaneers' 16-15 preseason win over the Chiefs on Saturday.</t>
         </is>
       </c>
     </row>
@@ -46972,27 +46976,27 @@
       </c>
       <c r="B731" s="4" t="inlineStr">
         <is>
-          <t>Baker Mayfield</t>
+          <t>Chris Braswell</t>
         </is>
       </c>
       <c r="C731" s="4" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D731" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E731" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F731" s="4" t="inlineStr">
         <is>
-          <t>Mayfield completed two of four passes for 10 yards with no touchdowns or interceptions in the Buccaneers' 16-15 preseason win over the Chiefs on Saturday.</t>
+          <t>Braswell (undisclosed) did not play in the Buccaneers' 16-15 preseason win over the Chiefs on Saturday, Greg Auman of Fox Sports reports.</t>
         </is>
       </c>
     </row>
@@ -47004,12 +47008,12 @@
       </c>
       <c r="B732" s="5" t="inlineStr">
         <is>
-          <t>Kenny Gainwell</t>
+          <t>Baker Mayfield</t>
         </is>
       </c>
       <c r="C732" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D732" s="5" t="inlineStr">
@@ -47024,7 +47028,7 @@
       </c>
       <c r="F732" s="5" t="inlineStr">
         <is>
-          <t>Gainwell rushed once for no gain in the Buccaneers' 16-15 preseason win over the Chiefs on Saturday.</t>
+          <t>Mayfield completed two of four passes for 10 yards with no touchdowns or interceptions in the Buccaneers' 16-15 preseason win over the Chiefs on Saturday.</t>
         </is>
       </c>
     </row>
@@ -47036,7 +47040,7 @@
       </c>
       <c r="B733" s="4" t="inlineStr">
         <is>
-          <t>Bucky Irving</t>
+          <t>Kenny Gainwell</t>
         </is>
       </c>
       <c r="C733" s="4" t="inlineStr">
@@ -47056,7 +47060,7 @@
       </c>
       <c r="F733" s="4" t="inlineStr">
         <is>
-          <t>Irving rushed three times for 14 yards in the Buccaneers' 16-15 preseason win over the Chiefs on Saturday.</t>
+          <t>Gainwell rushed once for no gain in the Buccaneers' 16-15 preseason win over the Chiefs on Saturday.</t>
         </is>
       </c>
     </row>
@@ -47068,27 +47072,27 @@
       </c>
       <c r="B734" s="5" t="inlineStr">
         <is>
-          <t>Dennis Houston</t>
+          <t>Bucky Irving</t>
         </is>
       </c>
       <c r="C734" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D734" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E734" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F734" s="5" t="inlineStr">
         <is>
-          <t>Houston has been ruled out for the rest of Saturday's preseason game against the Chiefs due to a groin injury.</t>
+          <t>Irving rushed three times for 14 yards in the Buccaneers' 16-15 preseason win over the Chiefs on Saturday.</t>
         </is>
       </c>
     </row>
@@ -47100,27 +47104,27 @@
       </c>
       <c r="B735" s="4" t="inlineStr">
         <is>
-          <t>Zyon McCollum</t>
+          <t>Dennis Houston</t>
         </is>
       </c>
       <c r="C735" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D735" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E735" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F735" s="4" t="inlineStr">
         <is>
-          <t>McCollum (groin) practiced Thursday and might even see some snaps in Saturday's preseason game against the Chiefs, Scott Smith of the Buccaneers' official site reports.</t>
+          <t>Houston has been ruled out for the rest of Saturday's preseason game against the Chiefs due to a groin injury.</t>
         </is>
       </c>
     </row>
@@ -47132,12 +47136,12 @@
       </c>
       <c r="B736" s="5" t="inlineStr">
         <is>
-          <t>Vita Vea</t>
+          <t>Zyon McCollum</t>
         </is>
       </c>
       <c r="C736" s="5" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D736" s="5" t="inlineStr">
@@ -47152,7 +47156,7 @@
       </c>
       <c r="F736" s="5" t="inlineStr">
         <is>
-          <t>Vea (back) and the Buccaneers reached an agreement on a one-year, $30 million extension Wednesday, Adam Schefter of ESPN reports.</t>
+          <t>McCollum (groin) practiced Thursday and might even see some snaps in Saturday's preseason game against the Chiefs, Scott Smith of the Buccaneers' official site reports.</t>
         </is>
       </c>
     </row>
@@ -47164,27 +47168,27 @@
       </c>
       <c r="B737" s="4" t="inlineStr">
         <is>
-          <t>Cade Otton</t>
+          <t>Vita Vea</t>
         </is>
       </c>
       <c r="C737" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="D737" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E737" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F737" s="4" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>Vea (back) and the Buccaneers reached an agreement on a one-year, $30 million extension Wednesday, Adam Schefter of ESPN reports.</t>
         </is>
       </c>
     </row>
@@ -47196,12 +47200,12 @@
       </c>
       <c r="B738" s="5" t="inlineStr">
         <is>
-          <t>Tez Johnson</t>
+          <t>Cade Otton</t>
         </is>
       </c>
       <c r="C738" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D738" s="5" t="inlineStr">
@@ -47211,7 +47215,7 @@
       </c>
       <c r="E738" s="5" t="inlineStr">
         <is>
-          <t>Strain</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F738" s="5" t="inlineStr">
@@ -47228,7 +47232,7 @@
       </c>
       <c r="B739" s="4" t="inlineStr">
         <is>
-          <t>Jalen McMillan</t>
+          <t>Tez Johnson</t>
         </is>
       </c>
       <c r="C739" s="4" t="inlineStr">
@@ -47243,7 +47247,7 @@
       </c>
       <c r="E739" s="4" t="inlineStr">
         <is>
-          <t>Soreness</t>
+          <t>Strain</t>
         </is>
       </c>
       <c r="F739" s="4" t="inlineStr">
@@ -47260,27 +47264,27 @@
       </c>
       <c r="B740" s="5" t="inlineStr">
         <is>
-          <t>Kadarius Calloway</t>
+          <t>Jalen McMillan</t>
         </is>
       </c>
       <c r="C740" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D740" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E740" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Soreness</t>
         </is>
       </c>
       <c r="F740" s="5" t="inlineStr">
         <is>
-          <t>ir</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -47292,27 +47296,27 @@
       </c>
       <c r="B741" s="4" t="inlineStr">
         <is>
-          <t>Emeka Egbuka</t>
+          <t>Kadarius Calloway</t>
         </is>
       </c>
       <c r="C741" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D741" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E741" s="4" t="inlineStr">
         <is>
-          <t>Sprain</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F741" s="4" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>ir</t>
         </is>
       </c>
     </row>
@@ -47324,25 +47328,29 @@
       </c>
       <c r="B742" s="5" t="inlineStr">
         <is>
-          <t>JJ Roberts</t>
+          <t>Emeka Egbuka</t>
         </is>
       </c>
       <c r="C742" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D742" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E742" s="5" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="F742" s="5" t="inlineStr"/>
+          <t>Sprain</t>
+        </is>
+      </c>
+      <c r="F742" s="5" t="inlineStr">
+        <is>
+          <t>questionable</t>
+        </is>
+      </c>
     </row>
     <row r="743">
       <c r="A743" s="4" t="inlineStr">
@@ -47352,12 +47360,12 @@
       </c>
       <c r="B743" s="4" t="inlineStr">
         <is>
-          <t>Tristan Wirfs</t>
+          <t>JJ Roberts</t>
         </is>
       </c>
       <c r="C743" s="4" t="inlineStr">
         <is>
-          <t>OT</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D743" s="4" t="inlineStr">
@@ -47380,29 +47388,25 @@
       </c>
       <c r="B744" s="5" t="inlineStr">
         <is>
-          <t>Billy Schrauth</t>
+          <t>Tristan Wirfs</t>
         </is>
       </c>
       <c r="C744" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>OT</t>
         </is>
       </c>
       <c r="D744" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E744" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="F744" s="5" t="inlineStr">
-        <is>
-          <t>Schrauth (knee) did not participate in Tuesday's practice, Greg Auman of Fox Sports reports.</t>
-        </is>
-      </c>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F744" s="5" t="inlineStr"/>
     </row>
     <row r="745">
       <c r="A745" s="4" t="inlineStr">
@@ -47412,27 +47416,27 @@
       </c>
       <c r="B745" s="4" t="inlineStr">
         <is>
-          <t>Jake Browning</t>
+          <t>Billy Schrauth</t>
         </is>
       </c>
       <c r="C745" s="4" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D745" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E745" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F745" s="4" t="inlineStr">
         <is>
-          <t>Browning (back) practiced Monday after missing Friday's preseason game against the Jets, Rick Stroud of the Tampa Bay Times reports.</t>
+          <t>Schrauth (knee) did not participate in Tuesday's practice, Greg Auman of Fox Sports reports.</t>
         </is>
       </c>
     </row>
@@ -47444,12 +47448,12 @@
       </c>
       <c r="B746" s="5" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr.</t>
+          <t>Jake Browning</t>
         </is>
       </c>
       <c r="C746" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D746" s="5" t="inlineStr">
@@ -47464,7 +47468,7 @@
       </c>
       <c r="F746" s="5" t="inlineStr">
         <is>
-          <t>Godwin didn't play in Friday's 24-16 preseason victory over the Jets.</t>
+          <t>Browning (back) practiced Monday after missing Friday's preseason game against the Jets, Rick Stroud of the Tampa Bay Times reports.</t>
         </is>
       </c>
     </row>
@@ -47476,7 +47480,7 @@
       </c>
       <c r="B747" s="4" t="inlineStr">
         <is>
-          <t>Ted Hurst III</t>
+          <t>Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="C747" s="4" t="inlineStr">
@@ -47496,7 +47500,7 @@
       </c>
       <c r="F747" s="4" t="inlineStr">
         <is>
-          <t>Hurst brought in two of six targets for 19 yards in the Buccaneers' 24-16 preseason win over the Jets on Friday.</t>
+          <t>Godwin didn't play in Friday's 24-16 preseason victory over the Jets.</t>
         </is>
       </c>
     </row>
@@ -49322,7 +49326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -49406,54 +49410,50 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>401874101</t>
+          <t>401873297</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>State Farm Stadium</t>
+          <t>Nissan Stadium</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>retractable</t>
+          <t>open</t>
         </is>
       </c>
       <c r="D5" s="15" t="n">
-        <v>108.1</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>7.6</v>
+        <v>5.6</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>11</v>
+        <v>12.3</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Partly cloudy</t>
         </is>
       </c>
       <c r="I5" s="9" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>108°F · retractable roof — effect halved</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>401873297</t>
+          <t>401873298</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Nissan Stadium</t>
+          <t>Highmark Stadium</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -49462,20 +49462,20 @@
         </is>
       </c>
       <c r="D6" s="17" t="n">
-        <v>82.90000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="E6" s="17" t="n">
         <v>5.6</v>
       </c>
       <c r="F6" s="17" t="n">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>Partly cloudy</t>
+          <t>Light drizzle</t>
         </is>
       </c>
       <c r="I6" s="22" t="n">
@@ -49486,12 +49486,12 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>401873298</t>
+          <t>401873299</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Highmark Stadium</t>
+          <t>Huntington Bank Field</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -49500,142 +49500,142 @@
         </is>
       </c>
       <c r="D7" s="15" t="n">
-        <v>74.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>6.7</v>
+        <v>5.1</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>12.1</v>
+        <v>21.7</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Partly cloudy</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="I7" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr"/>
+        <v>-0.8</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>Wind 5 mph (gusts 22)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>401873299</t>
+          <t>401873641</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Huntington Bank Field</t>
+          <t>Allegiant Stadium</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>dome</t>
         </is>
       </c>
       <c r="D8" s="17" t="n">
-        <v>72.3</v>
+        <v>108.5</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>9.800000000000001</v>
+        <v>18.8</v>
       </c>
       <c r="F8" s="17" t="n">
-        <v>21.7</v>
+        <v>16.1</v>
       </c>
       <c r="G8" s="17" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>Light drizzle</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="I8" s="22" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>Wind 10 mph (gusts 22)</t>
+          <t>Indoors — weather ignored</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>401873641</t>
+          <t>401873300</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Allegiant Stadium</t>
+          <t>SoFi Stadium</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>dome</t>
+          <t>canopy</t>
         </is>
       </c>
       <c r="D9" s="15" t="n">
-        <v>108.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>18</v>
+        <v>8.1</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>16.1</v>
+        <v>6.9</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Overcast</t>
         </is>
       </c>
       <c r="I9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>Indoors — weather ignored</t>
-        </is>
-      </c>
+      <c r="J9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>401873300</t>
+          <t>401873302</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>SoFi Stadium</t>
+          <t>M&amp;T Bank Stadium</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>canopy</t>
+          <t>open</t>
         </is>
       </c>
       <c r="D10" s="17" t="n">
-        <v>78.40000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>8.300000000000001</v>
+        <v>2.7</v>
       </c>
       <c r="F10" s="17" t="n">
-        <v>6.9</v>
+        <v>8.1</v>
       </c>
       <c r="G10" s="17" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>Partly cloudy</t>
+          <t>Light drizzle</t>
         </is>
       </c>
       <c r="I10" s="22" t="n">
@@ -49646,34 +49646,34 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>401873302</t>
+          <t>401873304</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>M&amp;T Bank Stadium</t>
+          <t>Hard Rock Stadium</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>canopy</t>
         </is>
       </c>
       <c r="D11" s="15" t="n">
-        <v>86.2</v>
+        <v>89.5</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>2</v>
+        <v>10.5</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>8.1</v>
+        <v>11.6</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Mainly clear</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="I11" s="9" t="n">
@@ -49684,30 +49684,30 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>401873304</t>
+          <t>401873307</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Hard Rock Stadium</t>
+          <t>Bank of America Stadium</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>canopy</t>
+          <t>open</t>
         </is>
       </c>
       <c r="D12" s="17" t="n">
-        <v>89.09999999999999</v>
+        <v>82</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>12.1</v>
+        <v>4</v>
       </c>
       <c r="F12" s="17" t="n">
-        <v>11.6</v>
+        <v>4.7</v>
       </c>
       <c r="G12" s="17" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
@@ -49715,23 +49715,19 @@
         </is>
       </c>
       <c r="I12" s="22" t="n">
-        <v>-0.68</v>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>Wind 12 mph (gusts 12) · canopy — wind damped</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>401873307</t>
+          <t>401873303</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Bank of America Stadium</t>
+          <t>MetLife Stadium</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -49740,20 +49736,20 @@
         </is>
       </c>
       <c r="D13" s="15" t="n">
-        <v>85.90000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>4.7</v>
+        <v>10.1</v>
       </c>
       <c r="G13" s="15" t="n">
         <v>25</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Overcast</t>
+          <t>Drizzle</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
@@ -49764,12 +49760,12 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>401873303</t>
+          <t>401873306</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>MetLife Stadium</t>
+          <t>EverBank Stadium</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -49778,36 +49774,40 @@
         </is>
       </c>
       <c r="D14" s="17" t="n">
-        <v>79.2</v>
+        <v>91.5</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>7.6</v>
+        <v>11.2</v>
       </c>
       <c r="F14" s="17" t="n">
-        <v>10.1</v>
+        <v>11.2</v>
       </c>
       <c r="G14" s="17" t="n">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>Light drizzle</t>
+          <t>Overcast</t>
         </is>
       </c>
       <c r="I14" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="5" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>67% chance of rain</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>401873306</t>
+          <t>401873301</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>EverBank Stadium</t>
+          <t>Lincoln Financial Field</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -49816,16 +49816,16 @@
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>94.8</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>11.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
@@ -49833,23 +49833,19 @@
         </is>
       </c>
       <c r="I15" s="9" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>67% chance of rain · 95°F</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>401873301</t>
+          <t>401873305</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Lincoln Financial Field</t>
+          <t>Arrowhead Stadium</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -49858,20 +49854,20 @@
         </is>
       </c>
       <c r="D16" s="17" t="n">
-        <v>79.59999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>4.1</v>
+        <v>10.6</v>
       </c>
       <c r="F16" s="17" t="n">
-        <v>9.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="G16" s="17" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>Light drizzle</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="I16" s="22" t="n">
@@ -49882,92 +49878,96 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>401873305</t>
+          <t>401874048</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Arrowhead Stadium</t>
+          <t>AT&amp;T Stadium</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>retractable</t>
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>84.40000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>8.800000000000001</v>
+        <v>10.7</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>14.5</v>
+        <v>6</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Mainly clear</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr"/>
+        <v>-0.25</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>93°F · retractable roof — effect halved</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>401874048</t>
+          <t>401874102</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>AT&amp;T Stadium</t>
+          <t>Lambeau Field</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>retractable</t>
+          <t>open</t>
         </is>
       </c>
       <c r="D18" s="17" t="n">
-        <v>98.3</v>
+        <v>63.7</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>8.4</v>
+        <v>12.6</v>
       </c>
       <c r="F18" s="17" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="G18" s="17" t="n">
         <v>2</v>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Mainly clear</t>
         </is>
       </c>
       <c r="I18" s="22" t="n">
-        <v>-0.25</v>
+        <v>-0.8</v>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>98°F · retractable roof — effect halved</t>
+          <t>Wind 13 mph (gusts 19)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>401874102</t>
+          <t>401873614</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Lambeau Field</t>
+          <t>Empower Field at Mile High</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -49976,62 +49976,58 @@
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>63.5</v>
+        <v>82.2</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>13.8</v>
+        <v>7.7</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>19</v>
+        <v>7.4</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Partly cloudy</t>
+          <t>Light drizzle</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>Wind 14 mph (gusts 19)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>401873614</t>
+          <t>401873308</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Empower Field at Mile High</t>
+          <t>Lucas Oil Stadium</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>retractable</t>
         </is>
       </c>
       <c r="D20" s="17" t="n">
-        <v>74.59999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>9.699999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="F20" s="17" t="n">
-        <v>7.4</v>
+        <v>2.2</v>
       </c>
       <c r="G20" s="17" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>Partly cloudy</t>
+          <t>Overcast</t>
         </is>
       </c>
       <c r="I20" s="22" t="n">
@@ -50042,34 +50038,34 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>401873308</t>
+          <t>401874394</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Lucas Oil Stadium</t>
+          <t>Nissan Stadium</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>retractable</t>
+          <t>open</t>
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>79.59999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>2.2</v>
+        <v>5.6</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="G21" s="15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>Light drizzle</t>
+          <t>Mainly clear</t>
         </is>
       </c>
       <c r="I21" s="9" t="n">
@@ -50080,36 +50076,24 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>401874394</t>
+          <t>401872656</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Nissan Stadium</t>
+          <t>Lumen Field</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="E22" s="17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="F22" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="G22" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>Partly cloudy</t>
-        </is>
-      </c>
+          <t>canopy</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="n"/>
+      <c r="E22" s="17" t="n"/>
+      <c r="F22" s="17" t="n"/>
+      <c r="G22" s="17" t="n"/>
+      <c r="H22" s="5" t="n"/>
       <c r="I22" s="22" t="n">
         <v>0</v>
       </c>
@@ -50118,17 +50102,17 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>401872656</t>
+          <t>401872657</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Lumen Field</t>
+          <t>Melbourne Cricket Ground</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>canopy</t>
+          <t>open</t>
         </is>
       </c>
       <c r="D23" s="15" t="n"/>
@@ -50144,12 +50128,12 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>401872657</t>
+          <t>401872658</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Melbourne Cricket Ground</t>
+          <t>Acrisure Stadium</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -50170,17 +50154,17 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>401872658</t>
+          <t>401872659</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Acrisure Stadium</t>
+          <t>Lucas Oil Stadium</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>retractable</t>
         </is>
       </c>
       <c r="D25" s="15" t="n"/>
@@ -50196,12 +50180,12 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>401872659</t>
+          <t>401872660</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Lucas Oil Stadium</t>
+          <t>Reliant Stadium</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -50222,17 +50206,17 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>401872660</t>
+          <t>401872661</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Reliant Stadium</t>
+          <t>Bank of America Stadium</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>retractable</t>
+          <t>open</t>
         </is>
       </c>
       <c r="D27" s="15" t="n"/>
@@ -50248,12 +50232,12 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>401872661</t>
+          <t>401872922</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Bank of America Stadium</t>
+          <t>EverBank Stadium</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -50274,17 +50258,17 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>401872922</t>
+          <t>401872923</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>EverBank Stadium</t>
+          <t>Ford Field</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>dome</t>
         </is>
       </c>
       <c r="D29" s="15" t="n"/>
@@ -50300,17 +50284,17 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>401872923</t>
+          <t>401872924</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Ford Field</t>
+          <t>Nissan Stadium</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>dome</t>
+          <t>open</t>
         </is>
       </c>
       <c r="D30" s="17" t="n"/>
@@ -50326,12 +50310,12 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>401872924</t>
+          <t>401872925</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Nissan Stadium</t>
+          <t>Paycor Stadium</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -50352,17 +50336,17 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>401872925</t>
+          <t>401872926</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Paycor Stadium</t>
+          <t>SoFi Stadium</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>canopy</t>
         </is>
       </c>
       <c r="D32" s="17" t="n"/>
@@ -50378,17 +50362,17 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>401872926</t>
+          <t>401872927</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>SoFi Stadium</t>
+          <t>U.S. Bank Stadium</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>canopy</t>
+          <t>dome</t>
         </is>
       </c>
       <c r="D33" s="15" t="n"/>
@@ -50404,12 +50388,12 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>401872927</t>
+          <t>401872928</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>U.S. Bank Stadium</t>
+          <t>Allegiant Stadium</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -50430,17 +50414,17 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>401872928</t>
+          <t>401872929</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Allegiant Stadium</t>
+          <t>Lincoln Financial Field</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>dome</t>
+          <t>open</t>
         </is>
       </c>
       <c r="D35" s="15" t="n"/>
@@ -50456,12 +50440,12 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>401872929</t>
+          <t>401872930</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Lincoln Financial Field</t>
+          <t>MetLife Stadium</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -50482,12 +50466,12 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>401872930</t>
+          <t>401872931</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>MetLife Stadium</t>
+          <t>Arrowhead Stadium</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -50504,32 +50488,6 @@
         <v>0</v>
       </c>
       <c r="J37" s="4" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>401872931</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>Arrowhead Stadium</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="D38" s="17" t="n"/>
-      <c r="E38" s="17" t="n"/>
-      <c r="F38" s="17" t="n"/>
-      <c r="G38" s="17" t="n"/>
-      <c r="H38" s="5" t="n"/>
-      <c r="I38" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/NFL_Edge_Model.xlsx
+++ b/NFL_Edge_Model.xlsx
@@ -689,7 +689,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Snapshot of the live model, generated 2026-08-23T06:00:13+00:00. Read-only: the model runs in the pipeline, not in this file.</t>
+          <t>Snapshot of the live model, generated 2026-08-23T13:45:14+00:00. Read-only: the model runs in the pipeline, not in this file.</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23T06:00:13+00:00</t>
+          <t>2026-08-23T13:45:14+00:00</t>
         </is>
       </c>
     </row>
@@ -23972,27 +23972,27 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Dadrion Taylor-Demerson</t>
+          <t>Chad Ryland</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Taylor-Demerson is questionable to return to Saturday's preseason game against the Cowboys due to a rib injury.</t>
+          <t>Ryland made field goals of 38 and 31 yards, missed a 62-yarder wide right and knocked through his only extra-point try in the Cardinals' 34-13 preseason loss to the Cowboys on Saturday.</t>
         </is>
       </c>
     </row>
@@ -24004,12 +24004,12 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Blake Gillikin</t>
+          <t>Dadrion Taylor-Demerson</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -24024,7 +24024,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Gillikin sustained a groin injury during pregame warmups and is questionable to play in Saturday's preseason game against the Cowboys, Darren Urban of the Cardinals' official site reports.</t>
+          <t>Taylor-Demerson is questionable to return to Saturday's preseason game against the Cowboys due to a rib injury.</t>
         </is>
       </c>
     </row>
@@ -24036,12 +24036,12 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Trey Benson</t>
+          <t>Blake Gillikin</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -24056,7 +24056,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Benson (knee) has not been present for any portion of the Cardinals' previous two full-squad practices this week, Theo Mackie of The Arizona Republic reports.</t>
+          <t>Gillikin sustained a groin injury during pregame warmups and is questionable to play in Saturday's preseason game against the Cowboys, Darren Urban of the Cardinals' official site reports.</t>
         </is>
       </c>
     </row>
@@ -24068,17 +24068,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Tip Reiman</t>
+          <t>Trey Benson</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Out</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -24088,7 +24088,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Reiman (ankle) will not be back for the start of the regular season, Darren Urban of the Cardinals' official site reports.</t>
+          <t>Benson (knee) has not been present for any portion of the Cardinals' previous two full-squad practices this week, Theo Mackie of The Arizona Republic reports.</t>
         </is>
       </c>
     </row>
@@ -24100,12 +24100,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Josh Sweat</t>
+          <t>Tip Reiman</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -24120,7 +24120,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Sweat (knee) is almost ready to be activated off the PUP list, Darren Urban of the Cardinals' official site reports.</t>
+          <t>Reiman (ankle) will not be back for the start of the regular season, Darren Urban of the Cardinals' official site reports.</t>
         </is>
       </c>
     </row>
@@ -24132,27 +24132,27 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Garrett Williams</t>
+          <t>Josh Sweat</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Williams (Achilles) was activated from the PUP list by the Cardinals on Thursday, Darren Urban of the Cardinals' official site reports.</t>
+          <t>Sweat (knee) is almost ready to be activated off the PUP list, Darren Urban of the Cardinals' official site reports.</t>
         </is>
       </c>
     </row>
@@ -24164,27 +24164,27 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Carson Beck</t>
+          <t>Garrett Williams</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Coach Mike LaFleur said Beck (ribs) "most likely" won't suit up for Saturday's preseason contest against the Cowboys, Josh Weinfuss of ESPN.com reports.</t>
+          <t>Williams (Achilles) was activated from the PUP list by the Cardinals on Thursday, Darren Urban of the Cardinals' official site reports.</t>
         </is>
       </c>
     </row>
@@ -24196,7 +24196,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Jacoby Brissett</t>
+          <t>Carson Beck</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -24206,17 +24206,17 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Coach Mike LaFleur said Thursday that Brissett won't suit up for Saturday's preseason game against the Cowboys, Josh Weinfuss of ESPN.com reports.</t>
+          <t>Coach Mike LaFleur said Beck (ribs) "most likely" won't suit up for Saturday's preseason contest against the Cowboys, Josh Weinfuss of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -24228,27 +24228,27 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Xavier Weaver</t>
+          <t>Jacoby Brissett</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Concussion</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>Coach Mike LaFleur said Thursday that Brissett won't suit up for Saturday's preseason game against the Cowboys, Josh Weinfuss of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -24260,12 +24260,12 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Elijah Higgins</t>
+          <t>Xavier Weaver</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -24292,27 +24292,27 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Austin Keys</t>
+          <t>Elijah Higgins</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Concussion</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>ir</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -24324,25 +24324,29 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Valentin Senn</t>
+          <t>Austin Keys</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>OT</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr"/>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>ir</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -24352,29 +24356,25 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Chase Bisontis</t>
+          <t>Valentin Senn</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>OT</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Surgery</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>ir</t>
-        </is>
-      </c>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -24384,12 +24384,12 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Joey Blount</t>
+          <t>Chase Bisontis</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -24399,7 +24399,7 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Stinger</t>
+          <t>Surgery</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -24416,27 +24416,27 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Zachary Carter</t>
+          <t>Joey Blount</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Stinger</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>ir</t>
         </is>
       </c>
     </row>
@@ -24448,17 +24448,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Jameson Geers</t>
+          <t>Zachary Carter</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -24468,7 +24468,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>ir</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -24480,27 +24480,27 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>Jameson Geers</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Sprain</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Coach Mike LaFleur confirmed Tuesday that Love does not need surgery to address his ankle injury, Tyler Drake of ArizonaSports.com reports.</t>
+          <t>ir</t>
         </is>
       </c>
     </row>
@@ -24512,7 +24512,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Tyler Allgeier</t>
+          <t>Jeremiyah Love</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -24522,17 +24522,17 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Sprain</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Allgeier could open the regular season as the Cardinals' primary running back, as Adam Schefter of ESPN reports that Jeremiyah Love sustained a high-ankle sprain in Thursday's preseason win over the Raiders.</t>
+          <t>Coach Mike LaFleur confirmed Tuesday that Love does not need surgery to address his ankle injury, Tyler Drake of ArizonaSports.com reports.</t>
         </is>
       </c>
     </row>
@@ -24544,7 +24544,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Tre Stewart</t>
+          <t>Tyler Allgeier</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -24564,7 +24564,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>The Cardinals signed Stewart to a contract Saturday.</t>
+          <t>Allgeier could open the regular season as the Cardinals' primary running back, as Adam Schefter of ESPN reports that Jeremiyah Love sustained a high-ankle sprain in Thursday's preseason win over the Raiders.</t>
         </is>
       </c>
     </row>
@@ -24576,12 +24576,12 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Baylor Cupp</t>
+          <t>Tre Stewart</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -24596,7 +24596,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>The Cardinals signed Cupp to a contract Saturday.</t>
+          <t>The Cardinals signed Stewart to a contract Saturday.</t>
         </is>
       </c>
     </row>
@@ -24608,27 +24608,27 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>James Conner</t>
+          <t>Baylor Cupp</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Head coach Mike LaFleur said Saturday that there is no timeline for Conner (foot) to participate in 11-on-11 drills in training camp practice, Darren Urban of the Cardinals' official site reports.</t>
+          <t>The Cardinals signed Cupp to a contract Saturday.</t>
         </is>
       </c>
     </row>
@@ -24640,27 +24640,27 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Trey McBride</t>
+          <t>James Conner</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>McBride played one snap in Thursday's 27-14 preseason win over the Raiders.</t>
+          <t>Head coach Mike LaFleur said Saturday that there is no timeline for Conner (foot) to participate in 11-on-11 drills in training camp practice, Darren Urban of the Cardinals' official site reports.</t>
         </is>
       </c>
     </row>
@@ -24672,12 +24672,12 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr.</t>
+          <t>Trey McBride</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -24692,7 +24692,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Harrison brought in his only target for seven yards and a touchdown and also drew a 20-yard pass interference penalty in the Cardinals' 27-14 preseason win over the Raiders on Thursday.</t>
+          <t>McBride played one snap in Thursday's 27-14 preseason win over the Raiders.</t>
         </is>
       </c>
     </row>
@@ -24704,7 +24704,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Wilson brought in both targets for 23 yards in the Cardinals' 27-14 preseason win over the Raiders on Thursday.</t>
+          <t>Harrison brought in his only target for seven yards and a touchdown and also drew a 20-yard pass interference penalty in the Cardinals' 27-14 preseason win over the Raiders on Thursday.</t>
         </is>
       </c>
     </row>
@@ -24736,12 +24736,12 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Shawn Bowman</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -24756,7 +24756,7 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>The Cardinals signed Bowman to a contract Sunday, Zach Gershman of the team's official site reports.</t>
+          <t>Wilson brought in both targets for 23 yards in the Cardinals' 27-14 preseason win over the Raiders on Thursday.</t>
         </is>
       </c>
     </row>
@@ -35024,27 +35024,27 @@
       </c>
       <c r="B355" s="4" t="inlineStr">
         <is>
-          <t>Tanner Koziol</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="C355" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D355" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E355" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F355" s="4" t="inlineStr">
         <is>
-          <t>Koziol played 18 snaps (13 on offense, five on special teams) but didn't show up in the box score otherwise during the Jaguars' 34-17 preseason loss to the Panthers on Friday.</t>
+          <t>Washington (undisclosed) was spotted at Sunday's walkthrough, Ryan O'Halloran of The Florida Times-Union reports.</t>
         </is>
       </c>
     </row>
@@ -35056,7 +35056,7 @@
       </c>
       <c r="B356" s="5" t="inlineStr">
         <is>
-          <t>Nate Boerkircher</t>
+          <t>Tanner Koziol</t>
         </is>
       </c>
       <c r="C356" s="5" t="inlineStr">
@@ -35076,7 +35076,7 @@
       </c>
       <c r="F356" s="5" t="inlineStr">
         <is>
-          <t>Boerkircher did not participate in Friday's 34-17 preseason loss to Carolina.</t>
+          <t>Koziol played 18 snaps (13 on offense, five on special teams) but didn't show up in the box score otherwise during the Jaguars' 34-17 preseason loss to the Panthers on Friday.</t>
         </is>
       </c>
     </row>
@@ -35088,7 +35088,7 @@
       </c>
       <c r="B357" s="4" t="inlineStr">
         <is>
-          <t>Brenton Strange</t>
+          <t>Nate Boerkircher</t>
         </is>
       </c>
       <c r="C357" s="4" t="inlineStr">
@@ -35108,7 +35108,7 @@
       </c>
       <c r="F357" s="4" t="inlineStr">
         <is>
-          <t>Strange did not play in the Jaguars' 34-17 preseason loss to the Panthers on Friday.</t>
+          <t>Boerkircher did not participate in Friday's 34-17 preseason loss to Carolina.</t>
         </is>
       </c>
     </row>
@@ -35120,12 +35120,12 @@
       </c>
       <c r="B358" s="5" t="inlineStr">
         <is>
-          <t>Travis Hunter</t>
+          <t>Brenton Strange</t>
         </is>
       </c>
       <c r="C358" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D358" s="5" t="inlineStr">
@@ -35140,7 +35140,7 @@
       </c>
       <c r="F358" s="5" t="inlineStr">
         <is>
-          <t>Hunter did not play in the Jaguars' 34-17 preseason loss to the Panthers on Friday.</t>
+          <t>Strange did not play in the Jaguars' 34-17 preseason loss to the Panthers on Friday.</t>
         </is>
       </c>
     </row>
@@ -35152,12 +35152,12 @@
       </c>
       <c r="B359" s="4" t="inlineStr">
         <is>
-          <t>Ameer Abdullah</t>
+          <t>Travis Hunter</t>
         </is>
       </c>
       <c r="C359" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D359" s="4" t="inlineStr">
@@ -35172,7 +35172,7 @@
       </c>
       <c r="F359" s="4" t="inlineStr">
         <is>
-          <t>Abdullah carried the ball six times for 45 yards and caught three of four targets for 37 yards in Friday's 34-17 preseason loss to the Panthers.</t>
+          <t>Hunter did not play in the Jaguars' 34-17 preseason loss to the Panthers on Friday.</t>
         </is>
       </c>
     </row>
@@ -35184,12 +35184,12 @@
       </c>
       <c r="B360" s="5" t="inlineStr">
         <is>
-          <t>CJ Williams</t>
+          <t>Ameer Abdullah</t>
         </is>
       </c>
       <c r="C360" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D360" s="5" t="inlineStr">
@@ -35204,7 +35204,7 @@
       </c>
       <c r="F360" s="5" t="inlineStr">
         <is>
-          <t>Williams caught all four of his targets for 22 yards and gained two rushing yards on his lone carry during Friday's 34-17 preseason loss to the Panthers.</t>
+          <t>Abdullah carried the ball six times for 45 yards and caught three of four targets for 37 yards in Friday's 34-17 preseason loss to the Panthers.</t>
         </is>
       </c>
     </row>
@@ -35216,7 +35216,7 @@
       </c>
       <c r="B361" s="4" t="inlineStr">
         <is>
-          <t>Josh Cameron</t>
+          <t>CJ Williams</t>
         </is>
       </c>
       <c r="C361" s="4" t="inlineStr">
@@ -35236,7 +35236,7 @@
       </c>
       <c r="F361" s="4" t="inlineStr">
         <is>
-          <t>Cameron caught both his targets for 41 yards in Friday's 34-17 preseason loss to the Panthers.</t>
+          <t>Williams caught all four of his targets for 22 yards and gained two rushing yards on his lone carry during Friday's 34-17 preseason loss to the Panthers.</t>
         </is>
       </c>
     </row>
@@ -35248,12 +35248,12 @@
       </c>
       <c r="B362" s="5" t="inlineStr">
         <is>
-          <t>Nick Mullens</t>
+          <t>Josh Cameron</t>
         </is>
       </c>
       <c r="C362" s="5" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D362" s="5" t="inlineStr">
@@ -35268,7 +35268,7 @@
       </c>
       <c r="F362" s="5" t="inlineStr">
         <is>
-          <t>Mullens completed six of seven passes for 65 yards in Friday's 34-17 preseason loss to the Panthers.</t>
+          <t>Cameron caught both his targets for 41 yards in Friday's 34-17 preseason loss to the Panthers.</t>
         </is>
       </c>
     </row>
@@ -35280,27 +35280,27 @@
       </c>
       <c r="B363" s="4" t="inlineStr">
         <is>
-          <t>Jakobi Meyers</t>
+          <t>Nick Mullens</t>
         </is>
       </c>
       <c r="C363" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D363" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E363" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F363" s="4" t="inlineStr">
         <is>
-          <t>Head coach Liam Coen said after Friday's 34-17 preseason loss to the Panthers that Meyers jammed his right hand during Wednesday's joint practice with Carolina, Juston Lewis of The Florida Times-Union reports.</t>
+          <t>Mullens completed six of seven passes for 65 yards in Friday's 34-17 preseason loss to the Panthers.</t>
         </is>
       </c>
     </row>
@@ -35312,27 +35312,27 @@
       </c>
       <c r="B364" s="5" t="inlineStr">
         <is>
-          <t>Trevor Lawrence</t>
+          <t>Jakobi Meyers</t>
         </is>
       </c>
       <c r="C364" s="5" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D364" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E364" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F364" s="5" t="inlineStr">
         <is>
-          <t>Lawrence won't play in Friday's preseason game against the Panthers, John Shipley of SI.com reports.</t>
+          <t>Head coach Liam Coen said after Friday's 34-17 preseason loss to the Panthers that Meyers jammed his right hand during Wednesday's joint practice with Carolina, Juston Lewis of The Florida Times-Union reports.</t>
         </is>
       </c>
     </row>
@@ -35344,27 +35344,27 @@
       </c>
       <c r="B365" s="4" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>Trevor Lawrence</t>
         </is>
       </c>
       <c r="C365" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D365" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E365" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F365" s="4" t="inlineStr">
         <is>
-          <t>Washington (undisclosed) is expected to return to practice next week, ESPN's Adam Schefter reports.</t>
+          <t>Lawrence won't play in Friday's preseason game against the Panthers, John Shipley of SI.com reports.</t>
         </is>
       </c>
     </row>
@@ -49424,20 +49424,20 @@
         </is>
       </c>
       <c r="D5" s="15" t="n">
-        <v>82.90000000000001</v>
+        <v>82.7</v>
       </c>
       <c r="E5" s="15" t="n">
         <v>5.6</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Partly cloudy</t>
+          <t>Overcast</t>
         </is>
       </c>
       <c r="I5" s="9" t="n">
@@ -49465,13 +49465,13 @@
         <v>70.5</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="F6" s="17" t="n">
-        <v>12.1</v>
+        <v>20.6</v>
       </c>
       <c r="G6" s="17" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
@@ -49479,9 +49479,13 @@
         </is>
       </c>
       <c r="I6" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5" t="inlineStr"/>
+        <v>-0.8</v>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Wind 7 mph (gusts 21)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -49500,16 +49504,16 @@
         </is>
       </c>
       <c r="D7" s="15" t="n">
-        <v>73</v>
+        <v>73.3</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>21.7</v>
+        <v>9.4</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
@@ -49517,13 +49521,9 @@
         </is>
       </c>
       <c r="I7" s="9" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>Wind 5 mph (gusts 22)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -49542,16 +49542,16 @@
         </is>
       </c>
       <c r="D8" s="17" t="n">
-        <v>108.5</v>
+        <v>107.4</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>18.8</v>
+        <v>20</v>
       </c>
       <c r="F8" s="17" t="n">
-        <v>16.1</v>
+        <v>20.4</v>
       </c>
       <c r="G8" s="17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
@@ -49584,10 +49584,10 @@
         </is>
       </c>
       <c r="D9" s="15" t="n">
-        <v>78.59999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="F9" s="15" t="n">
         <v>6.9</v>
@@ -49597,7 +49597,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Overcast</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="I9" s="9" t="n">
@@ -49622,20 +49622,20 @@
         </is>
       </c>
       <c r="D10" s="17" t="n">
-        <v>83.7</v>
+        <v>86.7</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="F10" s="17" t="n">
-        <v>8.1</v>
+        <v>6.9</v>
       </c>
       <c r="G10" s="17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>Light drizzle</t>
+          <t>Overcast</t>
         </is>
       </c>
       <c r="I10" s="22" t="n">
@@ -49660,26 +49660,30 @@
         </is>
       </c>
       <c r="D11" s="15" t="n">
-        <v>89.5</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>10.5</v>
+        <v>13.9</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>11.6</v>
+        <v>14.3</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Mainly clear</t>
         </is>
       </c>
       <c r="I11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr"/>
+        <v>-0.68</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>Wind 14 mph (gusts 14) · canopy — wind damped</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -49698,16 +49702,16 @@
         </is>
       </c>
       <c r="D12" s="17" t="n">
-        <v>82</v>
+        <v>85.3</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="F12" s="17" t="n">
-        <v>4.7</v>
+        <v>13.2</v>
       </c>
       <c r="G12" s="17" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
@@ -49736,20 +49740,20 @@
         </is>
       </c>
       <c r="D13" s="15" t="n">
-        <v>80.5</v>
+        <v>84.7</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>10.1</v>
+        <v>12.3</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Drizzle</t>
+          <t>Mainly clear</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
@@ -49774,16 +49778,16 @@
         </is>
       </c>
       <c r="D14" s="17" t="n">
-        <v>91.5</v>
+        <v>93.2</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>11.2</v>
+        <v>8.9</v>
       </c>
       <c r="F14" s="17" t="n">
-        <v>11.2</v>
+        <v>12.8</v>
       </c>
       <c r="G14" s="17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
@@ -49791,11 +49795,11 @@
         </is>
       </c>
       <c r="I14" s="22" t="n">
-        <v>-1</v>
+        <v>-1.5</v>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>67% chance of rain</t>
+          <t>61% chance of rain · 93°F</t>
         </is>
       </c>
     </row>
@@ -49816,16 +49820,16 @@
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>81.59999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>7.4</v>
+        <v>4.7</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
@@ -49854,26 +49858,30 @@
         </is>
       </c>
       <c r="D16" s="17" t="n">
-        <v>89.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>10.6</v>
+        <v>11.4</v>
       </c>
       <c r="F16" s="17" t="n">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="G16" s="17" t="n">
         <v>7</v>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Overcast</t>
         </is>
       </c>
       <c r="I16" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="5" t="inlineStr"/>
+        <v>-0.8</v>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>Wind 11 mph (gusts 19)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -49892,20 +49900,20 @@
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>93.3</v>
+        <v>101.9</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>10.7</v>
+        <v>8</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Partly cloudy</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
@@ -49913,7 +49921,7 @@
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>93°F · retractable roof — effect halved</t>
+          <t>102°F · retractable roof — effect halved</t>
         </is>
       </c>
     </row>
@@ -49934,30 +49942,26 @@
         </is>
       </c>
       <c r="D18" s="17" t="n">
-        <v>63.7</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>12.6</v>
+        <v>7.8</v>
       </c>
       <c r="F18" s="17" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G18" s="17" t="n">
         <v>2</v>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>Mainly clear</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="I18" s="22" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>Wind 13 mph (gusts 19)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -49976,26 +49980,30 @@
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>82.2</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>7.7</v>
+        <v>13.2</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>7.4</v>
+        <v>21</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Light drizzle</t>
+          <t>Overcast</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr"/>
+        <v>-0.8</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>Wind 13 mph (gusts 21)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -50014,20 +50022,20 @@
         </is>
       </c>
       <c r="D20" s="17" t="n">
-        <v>78.7</v>
+        <v>76.2</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>0.7</v>
+        <v>6.1</v>
       </c>
       <c r="F20" s="17" t="n">
-        <v>2.2</v>
+        <v>7.2</v>
       </c>
       <c r="G20" s="17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>Overcast</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="I20" s="22" t="n">
@@ -50052,16 +50060,16 @@
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>88.8</v>
+        <v>88.3</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="G21" s="15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>

--- a/NFL_Edge_Model.xlsx
+++ b/NFL_Edge_Model.xlsx
@@ -689,7 +689,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Snapshot of the live model, generated 2026-08-23T13:45:14+00:00. Read-only: the model runs in the pipeline, not in this file.</t>
+          <t>Snapshot of the live model, generated 2026-08-23T16:56:41+00:00. Read-only: the model runs in the pipeline, not in this file.</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23T13:45:14+00:00</t>
+          <t>2026-08-23T16:56:41+00:00</t>
         </is>
       </c>
     </row>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>CLE @ JAX</t>
+          <t>NE @ SEA</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -3023,23 +3023,23 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>CLE +7.5</t>
+          <t>NE +3.5</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5356</v>
+        <v>0.5327</v>
       </c>
       <c r="G16" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H16" s="13" t="n">
-        <v>0.0117</v>
+        <v>0.0089</v>
       </c>
       <c r="I16" s="13" t="n">
-        <v>0.02260161108580988</v>
+        <v>0.01706011721804213</v>
       </c>
       <c r="J16" s="14" t="n">
         <v>0.5</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>NE @ SEA</t>
+          <t>NO @ DET</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -3064,23 +3064,23 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>NE +3.5</t>
+          <t>NO +7</t>
         </is>
       </c>
       <c r="E17" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>0.5327</v>
+        <v>0.5323</v>
       </c>
       <c r="G17" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>0.0089</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>0.01706011721804213</v>
+        <v>0.01531241952910156</v>
       </c>
       <c r="J17" s="10" t="n">
         <v>0.5</v>
@@ -3095,7 +3095,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>NO @ DET</t>
+          <t>CLE @ JAX</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -3105,23 +3105,23 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>NO +7</t>
+          <t>CLE +7.5</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5323</v>
+        <v>0.5313</v>
       </c>
       <c r="G18" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H18" s="13" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0074</v>
       </c>
       <c r="I18" s="13" t="n">
-        <v>0.01531241952910156</v>
+        <v>0.01421344402886232</v>
       </c>
       <c r="J18" s="14" t="n">
         <v>0.5</v>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>MIA @ LV</t>
+          <t>GB @ MIN</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -3720,23 +3720,23 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>MIA +3.5</t>
+          <t>MIN -1.5</t>
         </is>
       </c>
       <c r="E33" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>0.5048</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="G33" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>-0.0183</v>
+        <v>-0.0185</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>-0.03638401763136451</v>
+        <v>-0.03680188589386885</v>
       </c>
       <c r="J33" s="10" t="n">
         <v>0.5</v>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>GB @ MIN</t>
+          <t>MIA @ LV</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -3761,23 +3761,23 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>MIN -1.5</t>
+          <t>MIA +3.5</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.5044999999999999</v>
+        <v>0.5034999999999999</v>
       </c>
       <c r="G34" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H34" s="13" t="n">
-        <v>-0.0185</v>
+        <v>-0.0194</v>
       </c>
       <c r="I34" s="13" t="n">
-        <v>-0.03680188589386885</v>
+        <v>-0.03879346990146776</v>
       </c>
       <c r="J34" s="14" t="n">
         <v>0.5</v>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>GB @ MIN</t>
+          <t>MIA @ LV</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -4130,23 +4130,23 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>GB +1.5</t>
+          <t>LV -3.5</t>
         </is>
       </c>
       <c r="E43" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>0.4955</v>
+        <v>0.4965</v>
       </c>
       <c r="G43" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>-0.0261</v>
+        <v>-0.0253</v>
       </c>
       <c r="I43" s="8" t="n">
-        <v>-0.05410720501522198</v>
+        <v>-0.05211562100762307</v>
       </c>
       <c r="J43" s="10" t="n">
         <v>0.5</v>
@@ -4161,7 +4161,7 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>MIA @ LV</t>
+          <t>GB @ MIN</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -4171,23 +4171,23 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>LV -3.5</t>
+          <t>GB +1.5</t>
         </is>
       </c>
       <c r="E44" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.4952</v>
+        <v>0.4955</v>
       </c>
       <c r="G44" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H44" s="13" t="n">
-        <v>-0.0262</v>
+        <v>-0.0261</v>
       </c>
       <c r="I44" s="13" t="n">
-        <v>-0.05452507327772632</v>
+        <v>-0.05410720501522198</v>
       </c>
       <c r="J44" s="14" t="n">
         <v>0.5</v>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>NO @ DET</t>
+          <t>CLE @ JAX</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -4786,23 +4786,23 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>DET -7</t>
+          <t>JAX -7.5</t>
         </is>
       </c>
       <c r="E59" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>0.4677</v>
+        <v>0.4687</v>
       </c>
       <c r="G59" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H59" s="8" t="n">
-        <v>-0.0423</v>
+        <v>-0.0419</v>
       </c>
       <c r="I59" s="8" t="n">
-        <v>-0.101227913867188</v>
+        <v>-0.1051225349379531</v>
       </c>
       <c r="J59" s="10" t="n">
         <v>0.5</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>NE @ SEA</t>
+          <t>NO @ DET</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -4827,23 +4827,23 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>SEA -3.5</t>
+          <t>DET -7</t>
         </is>
       </c>
       <c r="E60" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.4673</v>
+        <v>0.4677</v>
       </c>
       <c r="G60" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H60" s="13" t="n">
-        <v>-0.0425</v>
+        <v>-0.0423</v>
       </c>
       <c r="I60" s="13" t="n">
-        <v>-0.1079692081271329</v>
+        <v>-0.101227913867188</v>
       </c>
       <c r="J60" s="14" t="n">
         <v>0.5</v>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>CLE @ JAX</t>
+          <t>NE @ SEA</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -4868,23 +4868,23 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>JAX -7.5</t>
+          <t>SEA -3.5</t>
         </is>
       </c>
       <c r="E61" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>0.4644</v>
+        <v>0.4673</v>
       </c>
       <c r="G61" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H61" s="8" t="n">
-        <v>-0.0436</v>
+        <v>-0.0425</v>
       </c>
       <c r="I61" s="8" t="n">
-        <v>-0.1135107019949007</v>
+        <v>-0.1079692081271329</v>
       </c>
       <c r="J61" s="10" t="n">
         <v>0.5</v>
@@ -6138,7 +6138,7 @@
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>4.21</v>
+        <v>4.28</v>
       </c>
       <c r="E12" s="9" t="n">
         <v>-3.5</v>
@@ -6342,7 +6342,7 @@
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>7.73</v>
+        <v>7.97</v>
       </c>
       <c r="E18" s="9" t="n">
         <v>-7.5</v>
@@ -24768,7 +24768,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Michael Penix Jr.</t>
+          <t>Tua Tagovailoa</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -24778,17 +24778,17 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>Surgery</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Penix (knee) has been cleared to participate in 11-on-11 drills, Marc Raimondi of ESPN.com reports.</t>
+          <t>Tagovailoa's teammate, Michael Penix (knee), is in line to return to 11-on-11 drills in Monday's practice, Will McFadden of the Falcons' official site reports.</t>
         </is>
       </c>
     </row>
@@ -24800,27 +24800,27 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Nick Folk</t>
+          <t>Michael Penix Jr.</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Surgery</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Folk made both of his field-goal attempts and all four PAT tries in Saturday's 34-6 preseason win over the Colts.</t>
+          <t>Penix (knee) has been cleared to participate in 11-on-11 drills, Marc Raimondi of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -24832,12 +24832,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Zachariah Branch</t>
+          <t>Nick Folk</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -24852,7 +24852,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Branch caught two of three targets for 15 yards and added a five-yard punt return in Saturday's 34-6 preseason win over the Colts.</t>
+          <t>Folk made both of his field-goal attempts and all four PAT tries in Saturday's 34-6 preseason win over the Colts.</t>
         </is>
       </c>
     </row>
@@ -24864,12 +24864,12 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Tua Tagovailoa</t>
+          <t>Zachariah Branch</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -24884,7 +24884,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Tagovailoa didn't play in Saturday's 34-6 preseason win over the Colts.</t>
+          <t>Branch caught two of three targets for 15 yards and added a five-yard punt return in Saturday's 34-6 preseason win over the Colts.</t>
         </is>
       </c>
     </row>
@@ -29500,27 +29500,27 @@
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>Dillon Gabriel</t>
+          <t>Alex Wright</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F180" s="5" t="inlineStr">
         <is>
-          <t>Gabriel didn't complete his only pass attempt in Saturday's 31-7 preseason loss to the Bills.</t>
+          <t>ir</t>
         </is>
       </c>
     </row>
@@ -29532,7 +29532,7 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>Deshaun Watson</t>
+          <t>Dillon Gabriel</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
@@ -29552,7 +29552,7 @@
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>Watson completed five of 12 passes for 36 yards, no touchdowns and one interception in Saturday's 31-7 preseason loss to the Bills. He also rushed twice for 13 yards.</t>
+          <t>Gabriel didn't complete his only pass attempt in Saturday's 31-7 preseason loss to the Bills.</t>
         </is>
       </c>
     </row>
@@ -29564,7 +29564,7 @@
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>Shedeur Sanders</t>
+          <t>Deshaun Watson</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
@@ -29584,7 +29584,7 @@
       </c>
       <c r="F182" s="5" t="inlineStr">
         <is>
-          <t>Sanders completed nine of 11 passes for 74 yards, one touchdown and one interception in Saturday's 31-7 preseason loss to the Bills. He also rushed once for two yards.</t>
+          <t>Watson completed five of 12 passes for 36 yards, no touchdowns and one interception in Saturday's 31-7 preseason loss to the Bills. He also rushed twice for 13 yards.</t>
         </is>
       </c>
     </row>
@@ -29596,12 +29596,12 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Isaiah Bond</t>
+          <t>Shedeur Sanders</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr">
@@ -29616,7 +29616,7 @@
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>Bond cleared concussion protocol during Saturday's preseason game against the Bills.</t>
+          <t>Sanders completed nine of 11 passes for 74 yards, one touchdown and one interception in Saturday's 31-7 preseason loss to the Bills. He also rushed once for two yards.</t>
         </is>
       </c>
     </row>
@@ -29628,7 +29628,7 @@
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>Jerry Jeudy</t>
+          <t>Isaiah Bond</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
@@ -29648,7 +29648,7 @@
       </c>
       <c r="F184" s="5" t="inlineStr">
         <is>
-          <t>Jeudy will not play in the Browns' preseason game against the Bills on Saturday, Daniel Oyefusi of ESPN.com reports.</t>
+          <t>Bond cleared concussion protocol during Saturday's preseason game against the Bills.</t>
         </is>
       </c>
     </row>
@@ -29660,27 +29660,27 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>Alex Wright</t>
+          <t>Jerry Jeudy</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E185" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>Wright (lower leg) is not expected to play in Saturday's preseason game against the Bills, Mary Kay Cabot of The Cleveland Plain Dealer reports.</t>
+          <t>Jeudy will not play in the Browns' preseason game against the Bills on Saturday, Daniel Oyefusi of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -33455,7 +33455,7 @@
       </c>
       <c r="E305" s="4" t="inlineStr">
         <is>
-          <t>Fracture</t>
+          <t>Surgery</t>
         </is>
       </c>
       <c r="F305" s="4" t="inlineStr">
@@ -34155,7 +34155,7 @@
       </c>
       <c r="E327" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Surgery</t>
         </is>
       </c>
       <c r="F327" s="4" t="inlineStr">
@@ -38996,12 +38996,12 @@
       </c>
       <c r="B480" s="5" t="inlineStr">
         <is>
-          <t>Chris Bell</t>
+          <t>Ronnie Harrison Jr.</t>
         </is>
       </c>
       <c r="C480" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D480" s="5" t="inlineStr">
@@ -39011,12 +39011,12 @@
       </c>
       <c r="E480" s="5" t="inlineStr">
         <is>
-          <t>Surgery</t>
+          <t>Hamstring</t>
         </is>
       </c>
       <c r="F480" s="5" t="inlineStr">
         <is>
-          <t>Head coach Jeff Hafley told reporters Saturday that Bell (knee) is "close" to being cleared to fully participate in practice, C. Isaiah Smalls II of the Miami Herald reports.</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -39028,27 +39028,27 @@
       </c>
       <c r="B481" s="4" t="inlineStr">
         <is>
-          <t>Kevin Coleman Jr.</t>
+          <t>Trey Moore</t>
         </is>
       </c>
       <c r="C481" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D481" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E481" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Ankle</t>
         </is>
       </c>
       <c r="F481" s="4" t="inlineStr">
         <is>
-          <t>Coleman (undisclosed) caught two of five targets for 32 yards in Saturday's 26-3 preseason loss to the Giants.</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -39060,27 +39060,27 @@
       </c>
       <c r="B482" s="5" t="inlineStr">
         <is>
-          <t>James Ester</t>
+          <t>Chris Bell</t>
         </is>
       </c>
       <c r="C482" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D482" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E482" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Surgery</t>
         </is>
       </c>
       <c r="F482" s="5" t="inlineStr">
         <is>
-          <t>Ester (undisclosed) reverted to Miami's injured reserve Saturday, Aaron Wilson of KPRC 2 Houston reports.</t>
+          <t>Head coach Jeff Hafley told reporters Saturday that Bell (knee) is "close" to being cleared to fully participate in practice, C. Isaiah Smalls II of the Miami Herald reports.</t>
         </is>
       </c>
     </row>
@@ -39092,27 +39092,27 @@
       </c>
       <c r="B483" s="4" t="inlineStr">
         <is>
-          <t>Ollie Gordon II</t>
+          <t>Kevin Coleman Jr.</t>
         </is>
       </c>
       <c r="C483" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D483" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E483" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F483" s="4" t="inlineStr">
         <is>
-          <t>Gordon exited Miami's preseason game versus the Giants on Sunday with an undisclosed injury, Chris Perkins of the South Florida Sun Sentinel reports.</t>
+          <t>Coleman (undisclosed) caught two of five targets for 32 yards in Saturday's 26-3 preseason loss to the Giants.</t>
         </is>
       </c>
     </row>
@@ -39124,27 +39124,27 @@
       </c>
       <c r="B484" s="5" t="inlineStr">
         <is>
-          <t>Malik Washington</t>
+          <t>James Ester</t>
         </is>
       </c>
       <c r="C484" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D484" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E484" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F484" s="5" t="inlineStr">
         <is>
-          <t>Washington is not playing in Saturday's preseason game against the Giants, C. Isaiah Smalls II of the Miami Herald reports.</t>
+          <t>Ester (undisclosed) reverted to Miami's injured reserve Saturday, Aaron Wilson of KPRC 2 Houston reports.</t>
         </is>
       </c>
     </row>
@@ -39156,27 +39156,27 @@
       </c>
       <c r="B485" s="4" t="inlineStr">
         <is>
-          <t>Malik Willis</t>
+          <t>Ollie Gordon II</t>
         </is>
       </c>
       <c r="C485" s="4" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D485" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E485" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F485" s="4" t="inlineStr">
         <is>
-          <t>Willis is not in uniform for Saturday's preseason game against the Giants, David Furones of the South Florida Sun Sentinel reports.</t>
+          <t>Gordon exited Miami's preseason game versus the Giants on Sunday with an undisclosed injury, Chris Perkins of the South Florida Sun Sentinel reports.</t>
         </is>
       </c>
     </row>
@@ -39188,12 +39188,12 @@
       </c>
       <c r="B486" s="5" t="inlineStr">
         <is>
-          <t>De'Von Achane</t>
+          <t>Malik Washington</t>
         </is>
       </c>
       <c r="C486" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D486" s="5" t="inlineStr">
@@ -39208,7 +39208,7 @@
       </c>
       <c r="F486" s="5" t="inlineStr">
         <is>
-          <t>Achane is not in uniform for Saturday's preseason game against the Giants, David Furones of the South Florida Sun Sentinel reports.</t>
+          <t>Washington is not playing in Saturday's preseason game against the Giants, C. Isaiah Smalls II of the Miami Herald reports.</t>
         </is>
       </c>
     </row>
@@ -39220,27 +39220,27 @@
       </c>
       <c r="B487" s="4" t="inlineStr">
         <is>
-          <t>JuJu Brents</t>
+          <t>Malik Willis</t>
         </is>
       </c>
       <c r="C487" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D487" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E487" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F487" s="4" t="inlineStr">
         <is>
-          <t>Brents (undisclosed) is trending in the right direction but did not participate in full-team drills against the Giants on Thursday, Alain Poupart of SI.com reports.</t>
+          <t>Willis is not in uniform for Saturday's preseason game against the Giants, David Furones of the South Florida Sun Sentinel reports.</t>
         </is>
       </c>
     </row>
@@ -39252,27 +39252,27 @@
       </c>
       <c r="B488" s="5" t="inlineStr">
         <is>
-          <t>Ethan Robinson</t>
+          <t>De'Von Achane</t>
         </is>
       </c>
       <c r="C488" s="5" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D488" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E488" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F488" s="5" t="inlineStr">
         <is>
-          <t>ir</t>
+          <t>Achane is not in uniform for Saturday's preseason game against the Giants, David Furones of the South Florida Sun Sentinel reports.</t>
         </is>
       </c>
     </row>
@@ -39284,17 +39284,17 @@
       </c>
       <c r="B489" s="4" t="inlineStr">
         <is>
-          <t>Jamaree Salyer</t>
+          <t>JuJu Brents</t>
         </is>
       </c>
       <c r="C489" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D489" s="4" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E489" s="4" t="inlineStr">
@@ -39304,7 +39304,7 @@
       </c>
       <c r="F489" s="4" t="inlineStr">
         <is>
-          <t>ir</t>
+          <t>Brents (undisclosed) is trending in the right direction but did not participate in full-team drills against the Giants on Thursday, Alain Poupart of SI.com reports.</t>
         </is>
       </c>
     </row>
@@ -39316,17 +39316,17 @@
       </c>
       <c r="B490" s="5" t="inlineStr">
         <is>
-          <t>Zach Sieler</t>
+          <t>Ethan Robinson</t>
         </is>
       </c>
       <c r="C490" s="5" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D490" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E490" s="5" t="inlineStr">
@@ -39336,7 +39336,7 @@
       </c>
       <c r="F490" s="5" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>ir</t>
         </is>
       </c>
     </row>
@@ -39348,17 +39348,17 @@
       </c>
       <c r="B491" s="4" t="inlineStr">
         <is>
-          <t>Ben Sims</t>
+          <t>Jamaree Salyer</t>
         </is>
       </c>
       <c r="C491" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D491" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E491" s="4" t="inlineStr">
@@ -39368,7 +39368,7 @@
       </c>
       <c r="F491" s="4" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>ir</t>
         </is>
       </c>
     </row>
@@ -39380,7 +39380,7 @@
       </c>
       <c r="B492" s="5" t="inlineStr">
         <is>
-          <t>Kenneth Grant</t>
+          <t>Zach Sieler</t>
         </is>
       </c>
       <c r="C492" s="5" t="inlineStr">
@@ -39412,12 +39412,12 @@
       </c>
       <c r="B493" s="4" t="inlineStr">
         <is>
-          <t>Lonnie Johnson Jr.</t>
+          <t>Ben Sims</t>
         </is>
       </c>
       <c r="C493" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D493" s="4" t="inlineStr">
@@ -39444,7 +39444,7 @@
       </c>
       <c r="B494" s="5" t="inlineStr">
         <is>
-          <t>Rene Konga</t>
+          <t>Kenneth Grant</t>
         </is>
       </c>
       <c r="C494" s="5" t="inlineStr">
@@ -39454,7 +39454,7 @@
       </c>
       <c r="D494" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E494" s="5" t="inlineStr">
@@ -39464,7 +39464,7 @@
       </c>
       <c r="F494" s="5" t="inlineStr">
         <is>
-          <t>ir</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -39476,12 +39476,12 @@
       </c>
       <c r="B495" s="4" t="inlineStr">
         <is>
-          <t>Jordyn Brooks</t>
+          <t>Lonnie Johnson Jr.</t>
         </is>
       </c>
       <c r="C495" s="4" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D495" s="4" t="inlineStr">
@@ -39508,17 +39508,17 @@
       </c>
       <c r="B496" s="5" t="inlineStr">
         <is>
-          <t>Quinn Ewers</t>
+          <t>Rene Konga</t>
         </is>
       </c>
       <c r="C496" s="5" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="D496" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E496" s="5" t="inlineStr">
@@ -39528,7 +39528,7 @@
       </c>
       <c r="F496" s="5" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>ir</t>
         </is>
       </c>
     </row>
@@ -39540,12 +39540,12 @@
       </c>
       <c r="B497" s="4" t="inlineStr">
         <is>
-          <t>Clelin Ferrell</t>
+          <t>Jordyn Brooks</t>
         </is>
       </c>
       <c r="C497" s="4" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D497" s="4" t="inlineStr">
@@ -39572,27 +39572,27 @@
       </c>
       <c r="B498" s="5" t="inlineStr">
         <is>
-          <t>Caleb Douglas</t>
+          <t>Quinn Ewers</t>
         </is>
       </c>
       <c r="C498" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D498" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E498" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F498" s="5" t="inlineStr">
         <is>
-          <t>Douglas (lower body) returned to practice Tuesday, David Furones of the South Florida Sun Sentinel reports.</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -39604,27 +39604,27 @@
       </c>
       <c r="B499" s="4" t="inlineStr">
         <is>
-          <t>Mark Gronowski</t>
+          <t>Clelin Ferrell</t>
         </is>
       </c>
       <c r="C499" s="4" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D499" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E499" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F499" s="4" t="inlineStr">
         <is>
-          <t>The Dolphins signed Gronowski to a contract Sunday.</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -39636,12 +39636,12 @@
       </c>
       <c r="B500" s="5" t="inlineStr">
         <is>
-          <t>Greg Dulcich</t>
+          <t>Caleb Douglas</t>
         </is>
       </c>
       <c r="C500" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D500" s="5" t="inlineStr">
@@ -39656,7 +39656,7 @@
       </c>
       <c r="F500" s="5" t="inlineStr">
         <is>
-          <t>Dulcich played 13 snaps on offense but didn't show up in the box score otherwise during the Dolphins' 20-7 preseason loss to the Commanders on Friday.</t>
+          <t>Douglas (lower body) returned to practice Tuesday, David Furones of the South Florida Sun Sentinel reports.</t>
         </is>
       </c>
     </row>
@@ -39668,12 +39668,12 @@
       </c>
       <c r="B501" s="4" t="inlineStr">
         <is>
-          <t>Jaylen Wright</t>
+          <t>Mark Gronowski</t>
         </is>
       </c>
       <c r="C501" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D501" s="4" t="inlineStr">
@@ -39688,7 +39688,7 @@
       </c>
       <c r="F501" s="4" t="inlineStr">
         <is>
-          <t>Wright rushed six times for 22 yards and failed to bring in his only target in the Dolphins' 20-7 preseason loss to the Commanders on Friday. He also returned one kickoff for no gain.</t>
+          <t>The Dolphins signed Gronowski to a contract Sunday.</t>
         </is>
       </c>
     </row>
@@ -39700,12 +39700,12 @@
       </c>
       <c r="B502" s="5" t="inlineStr">
         <is>
-          <t>Jalen Tolbert</t>
+          <t>Greg Dulcich</t>
         </is>
       </c>
       <c r="C502" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D502" s="5" t="inlineStr">
@@ -39720,7 +39720,7 @@
       </c>
       <c r="F502" s="5" t="inlineStr">
         <is>
-          <t>Tolbert secured one of three targets for 27 yards in the Dolphins' 20-7 preseason loss to the Commanders on Friday.</t>
+          <t>Dulcich played 13 snaps on offense but didn't show up in the box score otherwise during the Dolphins' 20-7 preseason loss to the Commanders on Friday.</t>
         </is>
       </c>
     </row>
@@ -39732,12 +39732,12 @@
       </c>
       <c r="B503" s="4" t="inlineStr">
         <is>
-          <t>Tutu Atwell</t>
+          <t>Jaylen Wright</t>
         </is>
       </c>
       <c r="C503" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D503" s="4" t="inlineStr">
@@ -39752,7 +39752,7 @@
       </c>
       <c r="F503" s="4" t="inlineStr">
         <is>
-          <t>Atwell is listed with the second-team offense on the Dolphins' first unofficial depth chart of training camp, David Furones of the South Florida Sun Sentinel reports.</t>
+          <t>Wright rushed six times for 22 yards and failed to bring in his only target in the Dolphins' 20-7 preseason loss to the Commanders on Friday. He also returned one kickoff for no gain.</t>
         </is>
       </c>
     </row>
@@ -39764,12 +39764,12 @@
       </c>
       <c r="B504" s="5" t="inlineStr">
         <is>
-          <t>Caedan Wallace</t>
+          <t>Jalen Tolbert</t>
         </is>
       </c>
       <c r="C504" s="5" t="inlineStr">
         <is>
-          <t>OT</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D504" s="5" t="inlineStr">
@@ -39784,7 +39784,7 @@
       </c>
       <c r="F504" s="5" t="inlineStr">
         <is>
-          <t>The Dolphins acquired Wallace from the Patriots on Monday.</t>
+          <t>Tolbert secured one of three targets for 27 yards in the Dolphins' 20-7 preseason loss to the Commanders on Friday.</t>
         </is>
       </c>
     </row>
@@ -40600,7 +40600,7 @@
       </c>
       <c r="F530" s="5" t="inlineStr">
         <is>
-          <t>Morton completed 13 of 17 passes for 129 yards with one touchdown and no interceptions while rushing once for minus-1 yard in the Patriot's 24-21 preseason win over the Eagles on Saturday.</t>
+          <t>Morton completed 13 of 17 passes for 129 yards with one touchdown and no interceptions while rushing once for minus-1 yard in the Patriots' 24-21 preseason win over the Eagles on Saturday.</t>
         </is>
       </c>
     </row>
@@ -46148,12 +46148,12 @@
       </c>
       <c r="B705" s="4" t="inlineStr">
         <is>
-          <t>Julian Hicks</t>
+          <t>Jadarian Price</t>
         </is>
       </c>
       <c r="C705" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D705" s="4" t="inlineStr">
@@ -46168,7 +46168,7 @@
       </c>
       <c r="F705" s="4" t="inlineStr">
         <is>
-          <t>The Seahawks signed Hicks to a contract Saturday, John Boyle of the team's official site reports.</t>
+          <t>Price will not play in Sunday's preseason game against the Titans, Gregg Bell of The Tacoma News Tribune reports.</t>
         </is>
       </c>
     </row>
@@ -46180,7 +46180,7 @@
       </c>
       <c r="B706" s="5" t="inlineStr">
         <is>
-          <t>Jake Bobo</t>
+          <t>Julian Hicks</t>
         </is>
       </c>
       <c r="C706" s="5" t="inlineStr">
@@ -46190,17 +46190,17 @@
       </c>
       <c r="D706" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E706" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F706" s="5" t="inlineStr">
         <is>
-          <t>The Seahawks placed Bobo (knee) on injured reserve Saturday, John Boyle of the team's official site reports.</t>
+          <t>The Seahawks signed Hicks to a contract Saturday, John Boyle of the team's official site reports.</t>
         </is>
       </c>
     </row>
@@ -46212,27 +46212,27 @@
       </c>
       <c r="B707" s="4" t="inlineStr">
         <is>
-          <t>Trevon Diggs</t>
+          <t>Jake Bobo</t>
         </is>
       </c>
       <c r="C707" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D707" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E707" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F707" s="4" t="inlineStr">
         <is>
-          <t>The Seahawks are slated to sign Diggs to a one-year deal, Adam Schefter of ESPN reports.</t>
+          <t>The Seahawks placed Bobo (knee) on injured reserve Saturday, John Boyle of the team's official site reports.</t>
         </is>
       </c>
     </row>
@@ -46244,27 +46244,27 @@
       </c>
       <c r="B708" s="5" t="inlineStr">
         <is>
-          <t>Joseph Vaughn</t>
+          <t>Trevon Diggs</t>
         </is>
       </c>
       <c r="C708" s="5" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D708" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E708" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F708" s="5" t="inlineStr">
         <is>
-          <t>ir</t>
+          <t>The Seahawks are slated to sign Diggs to a one-year deal, Adam Schefter of ESPN reports.</t>
         </is>
       </c>
     </row>
@@ -46276,17 +46276,17 @@
       </c>
       <c r="B709" s="4" t="inlineStr">
         <is>
-          <t>Emanuel Wilson</t>
+          <t>Joseph Vaughn</t>
         </is>
       </c>
       <c r="C709" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D709" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E709" s="4" t="inlineStr">
@@ -46296,7 +46296,7 @@
       </c>
       <c r="F709" s="4" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>ir</t>
         </is>
       </c>
     </row>
@@ -46308,17 +46308,17 @@
       </c>
       <c r="B710" s="5" t="inlineStr">
         <is>
-          <t>Robbie Ouzts</t>
+          <t>Emanuel Wilson</t>
         </is>
       </c>
       <c r="C710" s="5" t="inlineStr">
         <is>
-          <t>FB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D710" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E710" s="5" t="inlineStr">
@@ -46328,7 +46328,7 @@
       </c>
       <c r="F710" s="5" t="inlineStr">
         <is>
-          <t>ir</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -46340,27 +46340,27 @@
       </c>
       <c r="B711" s="4" t="inlineStr">
         <is>
-          <t>Tory Horton</t>
+          <t>Robbie Ouzts</t>
         </is>
       </c>
       <c r="C711" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="D711" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E711" s="4" t="inlineStr">
         <is>
-          <t>Undisclosed</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F711" s="4" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>ir</t>
         </is>
       </c>
     </row>
@@ -46372,27 +46372,27 @@
       </c>
       <c r="B712" s="5" t="inlineStr">
         <is>
-          <t>Shemar Jean-Charles</t>
+          <t>Tory Horton</t>
         </is>
       </c>
       <c r="C712" s="5" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D712" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E712" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Undisclosed</t>
         </is>
       </c>
       <c r="F712" s="5" t="inlineStr">
         <is>
-          <t>ir</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -46404,27 +46404,27 @@
       </c>
       <c r="B713" s="4" t="inlineStr">
         <is>
-          <t>Nick Emmanwori</t>
+          <t>Shemar Jean-Charles</t>
         </is>
       </c>
       <c r="C713" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D713" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E713" s="4" t="inlineStr">
         <is>
-          <t>Surgery</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F713" s="4" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>ir</t>
         </is>
       </c>
     </row>
@@ -46436,27 +46436,27 @@
       </c>
       <c r="B714" s="5" t="inlineStr">
         <is>
-          <t>Anthony Hankerson</t>
+          <t>Nick Emmanwori</t>
         </is>
       </c>
       <c r="C714" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D714" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E714" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Surgery</t>
         </is>
       </c>
       <c r="F714" s="5" t="inlineStr">
         <is>
-          <t>Hankerson and the Seahawks agreed on a contract Monday, John Boyle of the team's official website reports.</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -46468,7 +46468,7 @@
       </c>
       <c r="B715" s="4" t="inlineStr">
         <is>
-          <t>Jadarian Price</t>
+          <t>Anthony Hankerson</t>
         </is>
       </c>
       <c r="C715" s="4" t="inlineStr">
@@ -46488,7 +46488,7 @@
       </c>
       <c r="F715" s="4" t="inlineStr">
         <is>
-          <t>Price (lower body) participated fully in Monday's practice, Bob Condotta of The Seattle Times reports.</t>
+          <t>Hankerson and the Seahawks agreed on a contract Monday, John Boyle of the team's official website reports.</t>
         </is>
       </c>
     </row>
@@ -49424,13 +49424,13 @@
         </is>
       </c>
       <c r="D5" s="15" t="n">
-        <v>82.7</v>
+        <v>83.2</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>5.6</v>
+        <v>6.7</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>12.1</v>
+        <v>13.2</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>0</v>
@@ -49471,7 +49471,7 @@
         <v>20.6</v>
       </c>
       <c r="G6" s="17" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
@@ -49513,7 +49513,7 @@
         <v>9.4</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
@@ -49631,7 +49631,7 @@
         <v>6.9</v>
       </c>
       <c r="G10" s="17" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
@@ -49669,7 +49669,7 @@
         <v>14.3</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
@@ -49711,7 +49711,7 @@
         <v>13.2</v>
       </c>
       <c r="G12" s="17" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
@@ -49749,7 +49749,7 @@
         <v>12.3</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
@@ -49787,7 +49787,7 @@
         <v>12.8</v>
       </c>
       <c r="G14" s="17" t="n">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
@@ -49795,11 +49795,11 @@
         </is>
       </c>
       <c r="I14" s="22" t="n">
-        <v>-1.5</v>
+        <v>-0.5</v>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>61% chance of rain · 93°F</t>
+          <t>93°F</t>
         </is>
       </c>
     </row>
@@ -49829,7 +49829,7 @@
         <v>9.4</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
@@ -49867,7 +49867,7 @@
         <v>19</v>
       </c>
       <c r="G16" s="17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
@@ -49909,7 +49909,7 @@
         <v>10.5</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
@@ -49989,7 +49989,7 @@
         <v>21</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
@@ -50031,7 +50031,7 @@
         <v>7.2</v>
       </c>
       <c r="G20" s="17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>

--- a/NFL_Edge_Model.xlsx
+++ b/NFL_Edge_Model.xlsx
@@ -689,7 +689,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Snapshot of the live model, generated 2026-08-23T19:56:25+00:00. Read-only: the model runs in the pipeline, not in this file.</t>
+          <t>Snapshot of the live model, generated 2026-08-23T19:57:37+00:00. Read-only: the model runs in the pipeline, not in this file.</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23T19:56:25+00:00</t>
+          <t>2026-08-23T19:57:37+00:00</t>
         </is>
       </c>
     </row>
@@ -2609,19 +2609,19 @@
         </is>
       </c>
       <c r="E6" s="12" t="n">
-        <v>-112</v>
+        <v>-108</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5888</v>
+        <v>0.5858</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>0.5283</v>
+        <v>0.5192</v>
       </c>
       <c r="H6" s="13" t="n">
-        <v>0.044</v>
+        <v>0.046</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>0.1145574022904216</v>
+        <v>0.1281919050894967</v>
       </c>
       <c r="J6" s="14" t="n">
         <v>0.15</v>
@@ -2727,28 +2727,28 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>SEA ML</t>
+          <t>SEA +3.5</t>
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>164</v>
+        <v>-105</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>0.4136</v>
+        <v>0.5502</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>0.3788</v>
+        <v>0.5122</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>0.0308</v>
+        <v>0.0329</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>0.09120300354675681</v>
+        <v>0.07419026293050812</v>
       </c>
       <c r="J9" s="10" t="n">
         <v>0.15</v>
@@ -2772,28 +2772,28 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>SEA +4.5</t>
+          <t>SEA ML</t>
         </is>
       </c>
       <c r="E10" s="12" t="n">
-        <v>-115</v>
+        <v>154</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5668</v>
+        <v>0.4307</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.3937</v>
       </c>
       <c r="H10" s="13" t="n">
-        <v>0.0288</v>
+        <v>0.0323</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>0.05970271346067979</v>
+        <v>0.0930713376416743</v>
       </c>
       <c r="J10" s="14" t="n">
         <v>0.15</v>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>CHI @ CAR</t>
+          <t>NE @ SEA</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -3109,23 +3109,23 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>CAR ML</t>
+          <t>NE ML</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.4611</v>
+        <v>0.4102</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>0.4464</v>
+        <v>0.3937</v>
       </c>
       <c r="H18" s="13" t="n">
-        <v>0.0143</v>
+        <v>0.016</v>
       </c>
       <c r="I18" s="13" t="n">
-        <v>0.0325138851490685</v>
+        <v>0.04157344040829225</v>
       </c>
       <c r="J18" s="14" t="n">
         <v>0.5</v>
@@ -3140,33 +3140,33 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>ATL @ PIT</t>
+          <t>CHI @ CAR</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Over 42.5</t>
+          <t>CAR ML</t>
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>-105</v>
+        <v>124</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>0.5266999999999999</v>
+        <v>0.4611</v>
       </c>
       <c r="G19" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.4464</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>0.0141</v>
+        <v>0.0143</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>0.02824070440763249</v>
+        <v>0.0325138851490685</v>
       </c>
       <c r="J19" s="10" t="n">
         <v>0.5</v>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>MIA @ LV</t>
+          <t>ATL @ PIT</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -3191,23 +3191,23 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Over 40.5</t>
+          <t>Over 42.5</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.538</v>
+        <v>0.5266999999999999</v>
       </c>
       <c r="G20" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5122</v>
       </c>
       <c r="H20" s="13" t="n">
-        <v>0.0139</v>
+        <v>0.0141</v>
       </c>
       <c r="I20" s="13" t="n">
-        <v>0.02712503029680507</v>
+        <v>0.02824070440763249</v>
       </c>
       <c r="J20" s="14" t="n">
         <v>0.5</v>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>CHI @ CAR</t>
+          <t>MIA @ LV</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -3232,23 +3232,23 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Under 47.5</t>
+          <t>Over 40.5</t>
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>0.5241</v>
+        <v>0.538</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.5238</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>0.0118</v>
+        <v>0.0139</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>0.02330043912717339</v>
+        <v>0.02712503029680507</v>
       </c>
       <c r="J21" s="10" t="n">
         <v>0.5</v>
@@ -3263,33 +3263,33 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>CLE @ JAX</t>
+          <t>CHI @ CAR</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>CLE +7.5</t>
+          <t>Under 47.5</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5353</v>
+        <v>0.5241</v>
       </c>
       <c r="G22" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5122</v>
       </c>
       <c r="H22" s="13" t="n">
-        <v>0.0113</v>
+        <v>0.0118</v>
       </c>
       <c r="I22" s="13" t="n">
-        <v>0.02190365162224267</v>
+        <v>0.02330043912717339</v>
       </c>
       <c r="J22" s="14" t="n">
         <v>0.5</v>
@@ -3304,33 +3304,33 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>NO @ DET</t>
+          <t>CLE @ JAX</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>NO ML</t>
+          <t>CLE +7.5</t>
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>250</v>
+        <v>-110</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>0.2972</v>
+        <v>0.5353</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>0.2857</v>
+        <v>0.5238</v>
       </c>
       <c r="H23" s="8" t="n">
         <v>0.0113</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>0.03991163697142053</v>
+        <v>0.02190365162224267</v>
       </c>
       <c r="J23" s="10" t="n">
         <v>0.5</v>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>NE @ SEA</t>
+          <t>NO @ DET</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -3355,23 +3355,23 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>NE ML</t>
+          <t>NO ML</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4111</v>
+        <v>0.2972</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>0.4</v>
+        <v>0.2857</v>
       </c>
       <c r="H24" s="13" t="n">
-        <v>0.0109</v>
+        <v>0.0113</v>
       </c>
       <c r="I24" s="13" t="n">
-        <v>0.02741697578924818</v>
+        <v>0.03991163697142053</v>
       </c>
       <c r="J24" s="14" t="n">
         <v>0.5</v>
@@ -3386,33 +3386,33 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>CHI @ CAR</t>
+          <t>SF @ LAR</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>CAR +2.5</t>
+          <t>SF ML</t>
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>-102</v>
+        <v>160</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>0.5141</v>
+        <v>0.3952</v>
       </c>
       <c r="G25" s="8" t="n">
-        <v>0.505</v>
+        <v>0.3846</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0105</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>0.0180591736369381</v>
+        <v>0.02738011685610797</v>
       </c>
       <c r="J25" s="10" t="n">
         <v>0.5</v>
@@ -3444,16 +3444,16 @@
         <v>-110</v>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5327</v>
+        <v>0.534</v>
       </c>
       <c r="G26" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H26" s="13" t="n">
-        <v>0.0089</v>
+        <v>0.0101</v>
       </c>
       <c r="I26" s="13" t="n">
-        <v>0.01706011721804213</v>
+        <v>0.01944210719035699</v>
       </c>
       <c r="J26" s="14" t="n">
         <v>0.5</v>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>NO @ DET</t>
+          <t>CHI @ CAR</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -3478,23 +3478,23 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>NO +7</t>
+          <t>CAR +2.5</t>
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>-110</v>
+        <v>-102</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>0.5323</v>
+        <v>0.5141</v>
       </c>
       <c r="G27" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.505</v>
       </c>
       <c r="H27" s="8" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="I27" s="8" t="n">
-        <v>0.01531241952910156</v>
+        <v>0.0180591736369381</v>
       </c>
       <c r="J27" s="10" t="n">
         <v>0.5</v>
@@ -3509,33 +3509,33 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>BAL @ IND</t>
+          <t>NO @ DET</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>IND ML</t>
+          <t>NO +7</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>150</v>
+        <v>-110</v>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.4077</v>
+        <v>0.5323</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>0.4</v>
+        <v>0.5238</v>
       </c>
       <c r="H28" s="13" t="n">
-        <v>0.0076</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="I28" s="13" t="n">
-        <v>0.0189591996912486</v>
+        <v>0.01531241952910156</v>
       </c>
       <c r="J28" s="14" t="n">
         <v>0.5</v>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>SF @ LAR</t>
+          <t>BAL @ IND</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -3560,23 +3560,23 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>SF ML</t>
+          <t>IND ML</t>
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>0.3966</v>
+        <v>0.4077</v>
       </c>
       <c r="G29" s="8" t="n">
-        <v>0.3937</v>
+        <v>0.4</v>
       </c>
       <c r="H29" s="8" t="n">
-        <v>0.0029</v>
+        <v>0.0076</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>0.007300801423401726</v>
+        <v>0.0189591996912486</v>
       </c>
       <c r="J29" s="10" t="n">
         <v>0.5</v>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>WSH @ PHI</t>
+          <t>SF @ LAR</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -3765,23 +3765,23 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>WSH +4.5</t>
+          <t>SF +3.5</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.5209</v>
+        <v>0.522</v>
       </c>
       <c r="G34" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H34" s="13" t="n">
-        <v>-0.0029</v>
+        <v>-0.0018</v>
       </c>
       <c r="I34" s="13" t="n">
-        <v>-0.00557688940705281</v>
+        <v>-0.003423344769942216</v>
       </c>
       <c r="J34" s="14" t="n">
         <v>0.5</v>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>SF @ LAR</t>
+          <t>WSH @ PHI</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -3806,23 +3806,23 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>SF +3.5</t>
+          <t>WSH +4.5</t>
         </is>
       </c>
       <c r="E35" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>0.5204</v>
+        <v>0.5209</v>
       </c>
       <c r="G35" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>-0.0034</v>
+        <v>-0.0029</v>
       </c>
       <c r="I35" s="8" t="n">
-        <v>-0.006504965748980907</v>
+        <v>-0.00557688940705281</v>
       </c>
       <c r="J35" s="10" t="n">
         <v>0.5</v>
@@ -4387,16 +4387,16 @@
         <v>130</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>0.4165</v>
+        <v>0.4163</v>
       </c>
       <c r="G49" s="8" t="n">
         <v>0.4348</v>
       </c>
       <c r="H49" s="8" t="n">
-        <v>-0.0176</v>
+        <v>-0.0178</v>
       </c>
       <c r="I49" s="8" t="n">
-        <v>-0.04170524916936713</v>
+        <v>-0.04211347125206366</v>
       </c>
       <c r="J49" s="10" t="n">
         <v>0.5</v>
@@ -4428,16 +4428,16 @@
         <v>-105</v>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.4929</v>
+        <v>0.4931</v>
       </c>
       <c r="G50" s="13" t="n">
         <v>0.5122</v>
       </c>
       <c r="H50" s="13" t="n">
-        <v>-0.0185</v>
+        <v>-0.0184</v>
       </c>
       <c r="I50" s="13" t="n">
-        <v>-0.03491941307422497</v>
+        <v>-0.03456897245401863</v>
       </c>
       <c r="J50" s="14" t="n">
         <v>0.5</v>
@@ -4674,16 +4674,16 @@
         <v>-155</v>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.5835</v>
+        <v>0.5837</v>
       </c>
       <c r="G56" s="13" t="n">
         <v>0.6078</v>
       </c>
       <c r="H56" s="13" t="n">
-        <v>-0.0229</v>
+        <v>-0.0227</v>
       </c>
       <c r="I56" s="13" t="n">
-        <v>-0.03967882301045061</v>
+        <v>-0.0393869186590014</v>
       </c>
       <c r="J56" s="14" t="n">
         <v>0.5</v>
@@ -5002,16 +5002,16 @@
         <v>-115</v>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.5071</v>
+        <v>0.5069</v>
       </c>
       <c r="G64" s="13" t="n">
         <v>0.5349</v>
       </c>
       <c r="H64" s="13" t="n">
-        <v>-0.0257</v>
+        <v>-0.0258</v>
       </c>
       <c r="I64" s="13" t="n">
-        <v>-0.04823004570995831</v>
+        <v>-0.04856547434225605</v>
       </c>
       <c r="J64" s="14" t="n">
         <v>0.5</v>
@@ -5518,33 +5518,33 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>SF @ LAR</t>
+          <t>MIA @ LV</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>LAR -3.5</t>
+          <t>LV ML</t>
         </is>
       </c>
       <c r="E77" s="7" t="n">
-        <v>-110</v>
+        <v>-205</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>0.4796</v>
+        <v>0.6278</v>
       </c>
       <c r="G77" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.6721</v>
       </c>
       <c r="H77" s="8" t="n">
-        <v>-0.0366</v>
+        <v>-0.0367</v>
       </c>
       <c r="I77" s="8" t="n">
-        <v>-0.08440412516010987</v>
+        <v>-0.06538038662822776</v>
       </c>
       <c r="J77" s="10" t="n">
         <v>0.5</v>
@@ -5559,33 +5559,33 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>MIA @ LV</t>
+          <t>WSH @ PHI</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>LV ML</t>
+          <t>PHI -4.5</t>
         </is>
       </c>
       <c r="E78" s="12" t="n">
-        <v>-205</v>
+        <v>-110</v>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.6278</v>
+        <v>0.4791</v>
       </c>
       <c r="G78" s="13" t="n">
-        <v>0.6721</v>
+        <v>0.5238</v>
       </c>
       <c r="H78" s="13" t="n">
-        <v>-0.0367</v>
+        <v>-0.0369</v>
       </c>
       <c r="I78" s="13" t="n">
-        <v>-0.06538038662822776</v>
+        <v>-0.08533220150203796</v>
       </c>
       <c r="J78" s="14" t="n">
         <v>0.5</v>
@@ -5600,7 +5600,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>WSH @ PHI</t>
+          <t>SF @ LAR</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -5610,23 +5610,23 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>PHI -4.5</t>
+          <t>LAR -3.5</t>
         </is>
       </c>
       <c r="E79" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>0.4791</v>
+        <v>0.478</v>
       </c>
       <c r="G79" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H79" s="8" t="n">
-        <v>-0.0369</v>
+        <v>-0.0375</v>
       </c>
       <c r="I79" s="8" t="n">
-        <v>-0.08533220150203796</v>
+        <v>-0.08748574613914867</v>
       </c>
       <c r="J79" s="10" t="n">
         <v>0.5</v>
@@ -5641,33 +5641,33 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>SF @ LAR</t>
+          <t>DEN @ KC</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>LAR ML</t>
+          <t>Over 42.5</t>
         </is>
       </c>
       <c r="E80" s="12" t="n">
-        <v>-185</v>
+        <v>-110</v>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.6034</v>
+        <v>0.4771</v>
       </c>
       <c r="G80" s="13" t="n">
-        <v>0.6491</v>
+        <v>0.5238</v>
       </c>
       <c r="H80" s="13" t="n">
-        <v>-0.0375</v>
+        <v>-0.038</v>
       </c>
       <c r="I80" s="13" t="n">
-        <v>-0.06982294310384429</v>
+        <v>-0.08908584867374703</v>
       </c>
       <c r="J80" s="14" t="n">
         <v>0.5</v>
@@ -5682,33 +5682,33 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>DEN @ KC</t>
+          <t>BAL @ IND</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Over 42.5</t>
+          <t>BAL -3.5</t>
         </is>
       </c>
       <c r="E81" s="7" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>0.4771</v>
+        <v>0.4691</v>
       </c>
       <c r="G81" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5192</v>
       </c>
       <c r="H81" s="8" t="n">
-        <v>-0.038</v>
+        <v>-0.0397</v>
       </c>
       <c r="I81" s="8" t="n">
-        <v>-0.08908584867374703</v>
+        <v>-0.09649040432769079</v>
       </c>
       <c r="J81" s="10" t="n">
         <v>0.5</v>
@@ -5728,28 +5728,28 @@
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>BAL -3.5</t>
+          <t>BAL ML</t>
         </is>
       </c>
       <c r="E82" s="12" t="n">
-        <v>-108</v>
+        <v>-180</v>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.4691</v>
+        <v>0.5923</v>
       </c>
       <c r="G82" s="13" t="n">
-        <v>0.5192</v>
+        <v>0.6429</v>
       </c>
       <c r="H82" s="13" t="n">
-        <v>-0.0397</v>
+        <v>-0.0399</v>
       </c>
       <c r="I82" s="13" t="n">
-        <v>-0.09649040432769079</v>
+        <v>-0.07787638073675418</v>
       </c>
       <c r="J82" s="14" t="n">
         <v>0.5</v>
@@ -5764,7 +5764,7 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>BAL @ IND</t>
+          <t>SF @ LAR</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -5774,23 +5774,23 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>BAL ML</t>
+          <t>LAR ML</t>
         </is>
       </c>
       <c r="E83" s="7" t="n">
-        <v>-180</v>
+        <v>-192</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>0.5923</v>
+        <v>0.6048</v>
       </c>
       <c r="G83" s="8" t="n">
-        <v>0.6429</v>
+        <v>0.6575</v>
       </c>
       <c r="H83" s="8" t="n">
-        <v>-0.0399</v>
+        <v>-0.0409</v>
       </c>
       <c r="I83" s="8" t="n">
-        <v>-0.07787638073675418</v>
+        <v>-0.07955712205271259</v>
       </c>
       <c r="J83" s="10" t="n">
         <v>0.5</v>
@@ -5846,33 +5846,33 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>NE @ SEA</t>
+          <t>CHI @ CAR</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>SEA ML</t>
+          <t>CHI -2.5</t>
         </is>
       </c>
       <c r="E85" s="7" t="n">
-        <v>-180</v>
+        <v>-118</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>0.5889</v>
+        <v>0.4859</v>
       </c>
       <c r="G85" s="8" t="n">
-        <v>0.6429</v>
+        <v>0.5413</v>
       </c>
       <c r="H85" s="8" t="n">
-        <v>-0.0414</v>
+        <v>-0.042</v>
       </c>
       <c r="I85" s="8" t="n">
-        <v>-0.08313747713867009</v>
+        <v>-0.1022639614444939</v>
       </c>
       <c r="J85" s="10" t="n">
         <v>0.5</v>
@@ -5887,7 +5887,7 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>CHI @ CAR</t>
+          <t>NO @ DET</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
@@ -5897,23 +5897,23 @@
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>CHI -2.5</t>
+          <t>DET -7</t>
         </is>
       </c>
       <c r="E86" s="12" t="n">
-        <v>-118</v>
+        <v>-110</v>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.4859</v>
+        <v>0.4677</v>
       </c>
       <c r="G86" s="13" t="n">
-        <v>0.5413</v>
+        <v>0.5238</v>
       </c>
       <c r="H86" s="13" t="n">
-        <v>-0.042</v>
+        <v>-0.0423</v>
       </c>
       <c r="I86" s="13" t="n">
-        <v>-0.1022639614444939</v>
+        <v>-0.101227913867188</v>
       </c>
       <c r="J86" s="14" t="n">
         <v>0.5</v>
@@ -5928,7 +5928,7 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>NO @ DET</t>
+          <t>NE @ SEA</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -5938,23 +5938,23 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>DET -7</t>
+          <t>SEA -3.5</t>
         </is>
       </c>
       <c r="E87" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>0.4677</v>
+        <v>0.466</v>
       </c>
       <c r="G87" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H87" s="8" t="n">
-        <v>-0.0423</v>
+        <v>-0.043</v>
       </c>
       <c r="I87" s="8" t="n">
-        <v>-0.101227913867188</v>
+        <v>-0.1103511980994479</v>
       </c>
       <c r="J87" s="10" t="n">
         <v>0.5</v>
@@ -5969,33 +5969,33 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>NE @ SEA</t>
+          <t>CHI @ CAR</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>SEA -3.5</t>
+          <t>CHI ML</t>
         </is>
       </c>
       <c r="E88" s="12" t="n">
-        <v>-110</v>
+        <v>-148</v>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.4673</v>
+        <v>0.5389</v>
       </c>
       <c r="G88" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5968</v>
       </c>
       <c r="H88" s="13" t="n">
-        <v>-0.0425</v>
+        <v>-0.043</v>
       </c>
       <c r="I88" s="13" t="n">
-        <v>-0.1079692081271329</v>
+        <v>-0.09606695185565578</v>
       </c>
       <c r="J88" s="14" t="n">
         <v>0.5</v>
@@ -6015,28 +6015,28 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>CHI ML</t>
+          <t>Over 47.5</t>
         </is>
       </c>
       <c r="E89" s="7" t="n">
-        <v>-148</v>
+        <v>-115</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>0.5389</v>
+        <v>0.4759</v>
       </c>
       <c r="G89" s="8" t="n">
-        <v>0.5968</v>
+        <v>0.5349</v>
       </c>
       <c r="H89" s="8" t="n">
-        <v>-0.043</v>
+        <v>-0.0435</v>
       </c>
       <c r="I89" s="8" t="n">
-        <v>-0.09606695185565578</v>
+        <v>-0.1103290525258087</v>
       </c>
       <c r="J89" s="10" t="n">
         <v>0.5</v>
@@ -6051,33 +6051,33 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>CHI @ CAR</t>
+          <t>CLE @ JAX</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>Over 47.5</t>
+          <t>JAX -7.5</t>
         </is>
       </c>
       <c r="E90" s="12" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.4759</v>
+        <v>0.4647</v>
       </c>
       <c r="G90" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.5238</v>
       </c>
       <c r="H90" s="13" t="n">
         <v>-0.0435</v>
       </c>
       <c r="I90" s="13" t="n">
-        <v>-0.1103290525258087</v>
+        <v>-0.1128127425313334</v>
       </c>
       <c r="J90" s="14" t="n">
         <v>0.5</v>
@@ -6092,33 +6092,33 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>CLE @ JAX</t>
+          <t>NE @ SEA</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>JAX -7.5</t>
+          <t>SEA ML</t>
         </is>
       </c>
       <c r="E91" s="7" t="n">
-        <v>-110</v>
+        <v>-185</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>0.4647</v>
+        <v>0.5898</v>
       </c>
       <c r="G91" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.6491</v>
       </c>
       <c r="H91" s="8" t="n">
-        <v>-0.0435</v>
+        <v>-0.0436</v>
       </c>
       <c r="I91" s="8" t="n">
-        <v>-0.1128127425313334</v>
+        <v>-0.09060324316118262</v>
       </c>
       <c r="J91" s="10" t="n">
         <v>0.5</v>
@@ -6469,42 +6469,38 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>SEA @ TEN</t>
+          <t>TB @ CIN</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>TEN ML</t>
+          <t>Over 51.5</t>
         </is>
       </c>
       <c r="E100" s="12" t="n">
-        <v>-198</v>
+        <v>-110</v>
       </c>
       <c r="F100" s="13" t="n">
-        <v>0.5864</v>
+        <v>0.4445</v>
       </c>
       <c r="G100" s="13" t="n">
-        <v>0.6644</v>
+        <v>0.5238</v>
       </c>
       <c r="H100" s="13" t="n">
-        <v>-0.0489</v>
+        <v>-0.0492</v>
       </c>
       <c r="I100" s="13" t="n">
-        <v>-0.1164607636337045</v>
+        <v>-0.1514496874157239</v>
       </c>
       <c r="J100" s="14" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K100" s="5" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K100" s="5" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
@@ -6519,28 +6515,28 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>TEN -4.5</t>
+          <t>TEN ML</t>
         </is>
       </c>
       <c r="E101" s="7" t="n">
-        <v>-105</v>
+        <v>-185</v>
       </c>
       <c r="F101" s="8" t="n">
-        <v>0.4332</v>
+        <v>0.5693</v>
       </c>
       <c r="G101" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.6491</v>
       </c>
       <c r="H101" s="8" t="n">
-        <v>-0.0491</v>
+        <v>-0.0493</v>
       </c>
       <c r="I101" s="8" t="n">
-        <v>-0.1542631880325815</v>
+        <v>-0.1218307247308589</v>
       </c>
       <c r="J101" s="10" t="n">
         <v>0.15</v>
@@ -6559,38 +6555,42 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>TB @ CIN</t>
+          <t>SEA @ TEN</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>Over 51.5</t>
+          <t>TEN -3.5</t>
         </is>
       </c>
       <c r="E102" s="12" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="F102" s="13" t="n">
-        <v>0.4445</v>
+        <v>0.4498</v>
       </c>
       <c r="G102" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5349</v>
       </c>
       <c r="H102" s="13" t="n">
-        <v>-0.0492</v>
+        <v>-0.0502</v>
       </c>
       <c r="I102" s="13" t="n">
-        <v>-0.1514496874157239</v>
+        <v>-0.1590602411731166</v>
       </c>
       <c r="J102" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K102" s="5" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K102" s="5" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>SEA @ TEN</t>
+          <t>NYJ @ TEN</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
@@ -6692,32 +6692,28 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Under 37.5</t>
+          <t>Under 38.5</t>
         </is>
       </c>
       <c r="E105" s="7" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="F105" s="8" t="n">
-        <v>0.4112</v>
+        <v>0.4041</v>
       </c>
       <c r="G105" s="8" t="n">
-        <v>0.5192</v>
+        <v>0.5122</v>
       </c>
       <c r="H105" s="8" t="n">
         <v>-0.0529</v>
       </c>
       <c r="I105" s="8" t="n">
-        <v>-0.2081031290949362</v>
+        <v>-0.2109934210059127</v>
       </c>
       <c r="J105" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K105" s="4" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K105" s="4" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
@@ -6727,7 +6723,7 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>NYJ @ TEN</t>
+          <t>SEA @ TEN</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
@@ -6737,28 +6733,32 @@
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>Under 38.5</t>
+          <t>Under 37.5</t>
         </is>
       </c>
       <c r="E106" s="12" t="n">
-        <v>-105</v>
+        <v>-112</v>
       </c>
       <c r="F106" s="13" t="n">
-        <v>0.4041</v>
+        <v>0.4142</v>
       </c>
       <c r="G106" s="13" t="n">
-        <v>0.5122</v>
+        <v>0.5283</v>
       </c>
       <c r="H106" s="13" t="n">
-        <v>-0.0529</v>
+        <v>-0.0533</v>
       </c>
       <c r="I106" s="13" t="n">
-        <v>-0.2109934210059127</v>
+        <v>-0.2159633352905699</v>
       </c>
       <c r="J106" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K106" s="5" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K106" s="5" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7437,7 +7437,7 @@
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="E8" s="9" t="n">
         <v>-3</v>
@@ -7913,7 +7913,7 @@
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="E22" s="9" t="n">
         <v>-3.5</v>
@@ -7947,7 +7947,7 @@
         </is>
       </c>
       <c r="D23" s="22" t="n">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="E23" s="22" t="n">
         <v>-3.5</v>
@@ -7981,10 +7981,10 @@
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>2.11</v>
+        <v>1.45</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>-4.5</v>
+        <v>-3.5</v>
       </c>
       <c r="F24" s="11" t="n">
         <v>41</v>
@@ -8132,7 +8132,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="E5" s="16" t="n">
         <v>2.9</v>
@@ -8164,7 +8164,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="18" t="n">
-        <v>3.07</v>
+        <v>2.93</v>
       </c>
       <c r="E6" s="18" t="n">
         <v>2.35</v>
@@ -8260,7 +8260,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="E9" s="16" t="n">
         <v>-1.33</v>
@@ -8445,20 +8445,20 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="F15" s="16" t="n">
-        <v>-1.14</v>
+        <v>-0.01</v>
       </c>
       <c r="G15" s="4" t="n"/>
       <c r="H15" s="11" t="n"/>
@@ -8477,20 +8477,20 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="F16" s="18" t="n">
-        <v>-0.01</v>
+        <v>-1.14</v>
       </c>
       <c r="G16" s="5" t="n"/>
       <c r="H16" s="23" t="n"/>
@@ -8548,7 +8548,7 @@
         <v>0</v>
       </c>
       <c r="D18" s="18" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="E18" s="18" t="n">
         <v>-0.24</v>
@@ -8644,7 +8644,7 @@
         <v>0</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="E21" s="16" t="n">
         <v>1.87</v>
@@ -8868,7 +8868,7 @@
         <v>0</v>
       </c>
       <c r="D28" s="18" t="n">
-        <v>-1.86</v>
+        <v>-1.87</v>
       </c>
       <c r="E28" s="18" t="n">
         <v>-1.28</v>
@@ -8932,7 +8932,7 @@
         <v>0</v>
       </c>
       <c r="D30" s="18" t="n">
-        <v>-2.32</v>
+        <v>-2.31</v>
       </c>
       <c r="E30" s="18" t="n">
         <v>-0.52</v>
@@ -9028,7 +9028,7 @@
         <v>0</v>
       </c>
       <c r="D33" s="16" t="n">
-        <v>-3.24</v>
+        <v>-3.23</v>
       </c>
       <c r="E33" s="16" t="n">
         <v>-2.1</v>
@@ -9092,7 +9092,7 @@
         <v>0</v>
       </c>
       <c r="D35" s="16" t="n">
-        <v>-4.7</v>
+        <v>-4.69</v>
       </c>
       <c r="E35" s="16" t="n">
         <v>-1.02</v>
@@ -10726,16 +10726,16 @@
         </is>
       </c>
       <c r="G37" s="9" t="n">
-        <v>-4.5</v>
+        <v>-3.5</v>
       </c>
       <c r="H37" s="11" t="n">
         <v>37.5</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="J37" s="7" t="n">
-        <v>-198</v>
+        <v>-185</v>
       </c>
       <c r="K37" s="15" t="n">
         <v>0</v>
@@ -11505,10 +11505,10 @@
         <v>44.5</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>-180</v>
+        <v>-185</v>
       </c>
       <c r="K54" s="17" t="n">
         <v>0</v>
@@ -11558,10 +11558,10 @@
         <v>48.5</v>
       </c>
       <c r="I55" s="7" t="n">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="J55" s="7" t="n">
-        <v>-185</v>
+        <v>-192</v>
       </c>
       <c r="K55" s="15" t="n">
         <v>0</v>
@@ -12936,10 +12936,10 @@
         <v>46.5</v>
       </c>
       <c r="I81" s="7" t="n">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="J81" s="7" t="n">
-        <v>-700</v>
+        <v>-675</v>
       </c>
       <c r="K81" s="15" t="n">
         <v>0</v>
@@ -18446,10 +18446,10 @@
         <v>46.5</v>
       </c>
       <c r="I185" s="7" t="n">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="J185" s="7" t="n">
-        <v>-440</v>
+        <v>-425</v>
       </c>
       <c r="K185" s="15" t="n">
         <v>0</v>
@@ -20772,7 +20772,7 @@
         </is>
       </c>
       <c r="G229" s="9" t="n">
-        <v>1.5</v>
+        <v>-1.5</v>
       </c>
       <c r="H229" s="11" t="n">
         <v>46.5</v>
@@ -21043,10 +21043,10 @@
         <v>47.5</v>
       </c>
       <c r="I234" s="12" t="n">
-        <v>-166</v>
+        <v>-162</v>
       </c>
       <c r="J234" s="12" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="K234" s="17" t="n">
         <v>0</v>
@@ -25707,10 +25707,10 @@
         <v>44.5</v>
       </c>
       <c r="I322" s="12" t="n">
-        <v>-425</v>
+        <v>-410</v>
       </c>
       <c r="J322" s="12" t="n">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="K322" s="17" t="n">
         <v>0</v>
@@ -51958,10 +51958,10 @@
         <v>83</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>13.2</v>
+        <v>11.6</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>0</v>

--- a/NFL_Edge_Model.xlsx
+++ b/NFL_Edge_Model.xlsx
@@ -689,7 +689,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Snapshot of the live model, generated 2026-08-23T19:57:37+00:00. Read-only: the model runs in the pipeline, not in this file.</t>
+          <t>Snapshot of the live model, generated 2026-08-23T20:52:05+00:00. Read-only: the model runs in the pipeline, not in this file.</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23T19:57:37+00:00</t>
+          <t>2026-08-23T20:52:05+00:00</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" s="16" t="n">
         <v>1.81</v>
@@ -8481,7 +8481,7 @@
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D16" s="18" t="n">
         <v>1.79</v>
@@ -32027,27 +32027,27 @@
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>Alex Wright</t>
+          <t>Shedeur Sanders</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F180" s="5" t="inlineStr">
         <is>
-          <t>The Browns placed Wright on injured reserve Sunday due to a ruptured Achilles, Adam Schefter of ESPN reports.</t>
+          <t>Sanders will learn Monday if he or Deshaun Watson will start at quarterback for the Browns, Jeremy Fowler of ESPN reports.</t>
         </is>
       </c>
     </row>
@@ -32059,12 +32059,12 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>Derek Barnett</t>
+          <t>Deshaun Watson</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
@@ -32079,7 +32079,7 @@
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>Barnett and the Browns agreed to a one-year contract worth up to $5.5 million Sunday, Jeremy Fowler of ESPN.com reports.</t>
+          <t>Watson will learn Monday if he or Shedeur Sanders will be named starting quarterback for the Browns, Jeremy Fowler of ESPN reports.</t>
         </is>
       </c>
     </row>
@@ -32091,27 +32091,27 @@
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>Dillon Gabriel</t>
+          <t>Alex Wright</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F182" s="5" t="inlineStr">
         <is>
-          <t>Gabriel didn't complete his only pass attempt in Saturday's 31-7 preseason loss to the Bills.</t>
+          <t>The Browns placed Wright on injured reserve Sunday due to a ruptured Achilles, Adam Schefter of ESPN reports.</t>
         </is>
       </c>
     </row>
@@ -32123,12 +32123,12 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Deshaun Watson</t>
+          <t>Derek Barnett</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr">
@@ -32143,7 +32143,7 @@
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>Watson completed five of 12 passes for 36 yards, no touchdowns and one interception in Saturday's 31-7 preseason loss to the Bills. He also rushed twice for 13 yards.</t>
+          <t>Barnett and the Browns agreed to a one-year contract worth up to $5.5 million Sunday, Jeremy Fowler of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -32155,7 +32155,7 @@
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>Shedeur Sanders</t>
+          <t>Dillon Gabriel</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
@@ -32175,7 +32175,7 @@
       </c>
       <c r="F184" s="5" t="inlineStr">
         <is>
-          <t>Sanders completed nine of 11 passes for 74 yards, one touchdown and one interception in Saturday's 31-7 preseason loss to the Bills. He also rushed once for two yards.</t>
+          <t>Gabriel didn't complete his only pass attempt in Saturday's 31-7 preseason loss to the Bills.</t>
         </is>
       </c>
     </row>
@@ -44703,12 +44703,12 @@
       </c>
       <c r="B580" s="5" t="inlineStr">
         <is>
-          <t>Joshua Ezeudu</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="C580" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D580" s="5" t="inlineStr">
@@ -44718,12 +44718,12 @@
       </c>
       <c r="E580" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Surgery</t>
         </is>
       </c>
       <c r="F580" s="5" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>Giants coach John Harbaugh said Sunday that Nabers (knee) could be out of his red non-contact jersey at some point this week, Evan Barnes of Newsday reports.</t>
         </is>
       </c>
     </row>
@@ -44735,12 +44735,12 @@
       </c>
       <c r="B581" s="4" t="inlineStr">
         <is>
-          <t>Braxton Berrios</t>
+          <t>Joshua Ezeudu</t>
         </is>
       </c>
       <c r="C581" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D581" s="4" t="inlineStr">
@@ -44755,7 +44755,7 @@
       </c>
       <c r="F581" s="4" t="inlineStr">
         <is>
-          <t>Head coach John Harbaugh told reporters that Berrios did not play in Saturday's 26-3 preseason win over the Dolphins due to a soft-tissue issue, Paul Schwartz of the New York Post reports.</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -44767,27 +44767,27 @@
       </c>
       <c r="B582" s="5" t="inlineStr">
         <is>
-          <t>Theo Johnson</t>
+          <t>Braxton Berrios</t>
         </is>
       </c>
       <c r="C582" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D582" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E582" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F582" s="5" t="inlineStr">
         <is>
-          <t>Johnson caught his only target for 12 yards in Saturday's 26-3 preseason win over the Dolphins.</t>
+          <t>Head coach John Harbaugh told reporters that Berrios did not play in Saturday's 26-3 preseason win over the Dolphins due to a soft-tissue issue, Paul Schwartz of the New York Post reports.</t>
         </is>
       </c>
     </row>
@@ -44799,12 +44799,12 @@
       </c>
       <c r="B583" s="4" t="inlineStr">
         <is>
-          <t>Darius Slayton</t>
+          <t>Theo Johnson</t>
         </is>
       </c>
       <c r="C583" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D583" s="4" t="inlineStr">
@@ -44819,7 +44819,7 @@
       </c>
       <c r="F583" s="4" t="inlineStr">
         <is>
-          <t>Slayton caught four of six targets for 58 yards in Saturday's 26-3 preseason win over the Dolphins.</t>
+          <t>Johnson caught his only target for 12 yards in Saturday's 26-3 preseason win over the Dolphins.</t>
         </is>
       </c>
     </row>
@@ -44831,12 +44831,12 @@
       </c>
       <c r="B584" s="5" t="inlineStr">
         <is>
-          <t>Tyrone Tracy Jr.</t>
+          <t>Darius Slayton</t>
         </is>
       </c>
       <c r="C584" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D584" s="5" t="inlineStr">
@@ -44851,7 +44851,7 @@
       </c>
       <c r="F584" s="5" t="inlineStr">
         <is>
-          <t>Tracy rushed six times for 26 yards, caught all three of his targets for 22 yards and lost a fumble in Saturday's 26-3 preseason win over the Dolphins.</t>
+          <t>Slayton caught four of six targets for 58 yards in Saturday's 26-3 preseason win over the Dolphins.</t>
         </is>
       </c>
     </row>
@@ -44863,7 +44863,7 @@
       </c>
       <c r="B585" s="4" t="inlineStr">
         <is>
-          <t>Devin Singletary</t>
+          <t>Tyrone Tracy Jr.</t>
         </is>
       </c>
       <c r="C585" s="4" t="inlineStr">
@@ -44883,7 +44883,7 @@
       </c>
       <c r="F585" s="4" t="inlineStr">
         <is>
-          <t>Singletary rushed eight times for 40 yards and a touchdown while catching his only target for four yards in Saturday's 26-3 preseason win over the Dolphins.</t>
+          <t>Tracy rushed six times for 26 yards, caught all three of his targets for 22 yards and lost a fumble in Saturday's 26-3 preseason win over the Dolphins.</t>
         </is>
       </c>
     </row>
@@ -44895,12 +44895,12 @@
       </c>
       <c r="B586" s="5" t="inlineStr">
         <is>
-          <t>Jaxson Dart</t>
+          <t>Devin Singletary</t>
         </is>
       </c>
       <c r="C586" s="5" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D586" s="5" t="inlineStr">
@@ -44915,7 +44915,7 @@
       </c>
       <c r="F586" s="5" t="inlineStr">
         <is>
-          <t>Dart didn't suit up for Saturday's 26-3 preseason win over the Dolphins.</t>
+          <t>Singletary rushed eight times for 40 yards and a touchdown while catching his only target for four yards in Saturday's 26-3 preseason win over the Dolphins.</t>
         </is>
       </c>
     </row>
@@ -44927,27 +44927,27 @@
       </c>
       <c r="B587" s="4" t="inlineStr">
         <is>
-          <t>Francis Mauigoa</t>
+          <t>Jaxson Dart</t>
         </is>
       </c>
       <c r="C587" s="4" t="inlineStr">
         <is>
-          <t>OT</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D587" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E587" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F587" s="4" t="inlineStr">
         <is>
-          <t>Mauigoa (upper body) had to leave Thursday's joint practice with the Dolphins due to a stinger, Dan Benton of USA Today reports.</t>
+          <t>Dart didn't suit up for Saturday's 26-3 preseason win over the Dolphins.</t>
         </is>
       </c>
     </row>
@@ -44959,27 +44959,27 @@
       </c>
       <c r="B588" s="5" t="inlineStr">
         <is>
-          <t>Najee Harris</t>
+          <t>Francis Mauigoa</t>
         </is>
       </c>
       <c r="C588" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>OT</t>
         </is>
       </c>
       <c r="D588" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E588" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F588" s="5" t="inlineStr">
         <is>
-          <t>Harris (Achilles) is participating in live drills Thursday, Jordan Raanan of ESPN.com reports.</t>
+          <t>Mauigoa (upper body) had to leave Thursday's joint practice with the Dolphins due to a stinger, Dan Benton of USA Today reports.</t>
         </is>
       </c>
     </row>
@@ -44991,27 +44991,27 @@
       </c>
       <c r="B589" s="4" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Najee Harris</t>
         </is>
       </c>
       <c r="C589" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D589" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E589" s="4" t="inlineStr">
         <is>
-          <t>Surgery</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F589" s="4" t="inlineStr">
         <is>
-          <t>Head coach John Harbaugh said that Nabers (knee) won't participate in the Giants' joint practices with the Dolphins this week, Jordan Raanan of ESPN.com reports.</t>
+          <t>Harris (Achilles) is participating in live drills Thursday, Jordan Raanan of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -51955,20 +51955,20 @@
         </is>
       </c>
       <c r="D5" s="15" t="n">
-        <v>83</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>11.6</v>
+        <v>12.3</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Overcast</t>
+          <t>Mainly clear</t>
         </is>
       </c>
       <c r="I5" s="9" t="n">
@@ -52002,7 +52002,7 @@
         <v>22.4</v>
       </c>
       <c r="G6" s="17" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
@@ -52044,7 +52044,7 @@
         <v>13</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
@@ -52082,7 +52082,7 @@
         <v>19.5</v>
       </c>
       <c r="G8" s="17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
@@ -52162,7 +52162,7 @@
         <v>7.4</v>
       </c>
       <c r="G10" s="17" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
@@ -52200,7 +52200,7 @@
         <v>13.4</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
@@ -52242,7 +52242,7 @@
         <v>2.9</v>
       </c>
       <c r="G12" s="17" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
@@ -52280,7 +52280,7 @@
         <v>6.5</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
@@ -52318,7 +52318,7 @@
         <v>10.1</v>
       </c>
       <c r="G14" s="17" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
@@ -52326,9 +52326,13 @@
         </is>
       </c>
       <c r="I14" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="5" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>56% chance of rain</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -52356,7 +52360,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
@@ -52394,7 +52398,7 @@
         <v>13.6</v>
       </c>
       <c r="G16" s="17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
@@ -52432,7 +52436,7 @@
         <v>7.8</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
@@ -52474,7 +52478,7 @@
         <v>16.3</v>
       </c>
       <c r="G18" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
@@ -52512,7 +52516,7 @@
         <v>10.5</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
@@ -52588,7 +52592,7 @@
         <v>7.2</v>
       </c>
       <c r="G21" s="15" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>

--- a/NFL_Edge_Model.xlsx
+++ b/NFL_Edge_Model.xlsx
@@ -692,7 +692,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Snapshot of the live model, generated 2026-08-24T03:34:11+00:00. Read-only: the model runs in the pipeline, not in this file.</t>
+          <t>Snapshot of the live model, generated 2026-08-24T08:03:54+00:00. Read-only: the model runs in the pipeline, not in this file.</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>2026-08-24T03:34:11+00:00</t>
+          <t>2026-08-24T08:03:54+00:00</t>
         </is>
       </c>
     </row>
@@ -3951,33 +3951,33 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>NYJ @ TEN</t>
+          <t>BUF @ HOU</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>TEN -3</t>
+          <t>Over 44.5</t>
         </is>
       </c>
       <c r="E39" s="7" t="n">
-        <v>100</v>
+        <v>-110</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>0.4897</v>
+        <v>0.5127</v>
       </c>
       <c r="G39" s="8" t="n">
-        <v>0.5</v>
+        <v>0.5238</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>-0.0102</v>
+        <v>-0.0109</v>
       </c>
       <c r="I39" s="8" t="n">
-        <v>-0.01914606343509778</v>
+        <v>-0.02118472397290833</v>
       </c>
       <c r="J39" s="10" t="n">
         <v>0.5</v>
@@ -3992,33 +3992,33 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>BUF @ HOU</t>
+          <t>NYJ @ TEN</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Over 44.5</t>
+          <t>TEN -3</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>-110</v>
+        <v>100</v>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.5127</v>
+        <v>0.4887</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5</v>
       </c>
       <c r="H40" s="13" t="n">
-        <v>-0.0109</v>
+        <v>-0.0111</v>
       </c>
       <c r="I40" s="13" t="n">
-        <v>-0.02118472397290833</v>
+        <v>-0.0209408624219064</v>
       </c>
       <c r="J40" s="14" t="n">
         <v>0.5</v>
@@ -4156,33 +4156,33 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>NYJ @ TEN</t>
+          <t>ATL @ PIT</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>TEN ML</t>
+          <t>ATL +3</t>
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>-148</v>
+        <v>100</v>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.5802</v>
+        <v>0.4827</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>0.5968</v>
+        <v>0.5</v>
       </c>
       <c r="H44" s="13" t="n">
-        <v>-0.0161</v>
+        <v>-0.0167</v>
       </c>
       <c r="I44" s="13" t="n">
-        <v>-0.0274936344486636</v>
+        <v>-0.03207583043232859</v>
       </c>
       <c r="J44" s="14" t="n">
         <v>0.5</v>
@@ -4197,33 +4197,33 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>ATL @ PIT</t>
+          <t>NYJ @ TEN</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>ATL +3</t>
+          <t>TEN ML</t>
         </is>
       </c>
       <c r="E45" s="7" t="n">
-        <v>100</v>
+        <v>-148</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>0.4827</v>
+        <v>0.5793</v>
       </c>
       <c r="G45" s="8" t="n">
-        <v>0.5</v>
+        <v>0.5968</v>
       </c>
       <c r="H45" s="8" t="n">
-        <v>-0.0167</v>
+        <v>-0.0169</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>-0.03207583043232859</v>
+        <v>-0.02898030615415753</v>
       </c>
       <c r="J45" s="10" t="n">
         <v>0.5</v>
@@ -4607,33 +4607,33 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>BUF @ HOU</t>
+          <t>NYJ @ TEN</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>BUF -1.5</t>
+          <t>NYJ ML</t>
         </is>
       </c>
       <c r="E55" s="7" t="n">
-        <v>-105</v>
+        <v>124</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>0.4861</v>
+        <v>0.4207</v>
       </c>
       <c r="G55" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.4464</v>
       </c>
       <c r="H55" s="8" t="n">
-        <v>-0.0243</v>
+        <v>-0.024</v>
       </c>
       <c r="I55" s="8" t="n">
-        <v>-0.05094536914808651</v>
+        <v>-0.05718351511097874</v>
       </c>
       <c r="J55" s="10" t="n">
         <v>0.5</v>
@@ -4648,7 +4648,7 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>DAL @ NYG</t>
+          <t>BUF @ HOU</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -4658,23 +4658,23 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>NYG +2.5</t>
+          <t>BUF -1.5</t>
         </is>
       </c>
       <c r="E56" s="12" t="n">
         <v>-105</v>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.4859</v>
+        <v>0.4861</v>
       </c>
       <c r="G56" s="13" t="n">
         <v>0.5122</v>
       </c>
       <c r="H56" s="13" t="n">
-        <v>-0.0245</v>
+        <v>-0.0243</v>
       </c>
       <c r="I56" s="13" t="n">
-        <v>-0.0513240982517143</v>
+        <v>-0.05094536914808651</v>
       </c>
       <c r="J56" s="14" t="n">
         <v>0.5</v>
@@ -4694,28 +4694,28 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Under 48.5</t>
+          <t>NYG +2.5</t>
         </is>
       </c>
       <c r="E57" s="7" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>0.4975</v>
+        <v>0.4859</v>
       </c>
       <c r="G57" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5122</v>
       </c>
       <c r="H57" s="8" t="n">
         <v>-0.0245</v>
       </c>
       <c r="I57" s="8" t="n">
-        <v>-0.05031031389922158</v>
+        <v>-0.0513240982517143</v>
       </c>
       <c r="J57" s="10" t="n">
         <v>0.5</v>
@@ -4730,33 +4730,33 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>NYJ @ TEN</t>
+          <t>DAL @ NYG</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>NYJ ML</t>
+          <t>Under 48.5</t>
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>124</v>
+        <v>-110</v>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.4198</v>
+        <v>0.4975</v>
       </c>
       <c r="G58" s="13" t="n">
-        <v>0.4464</v>
+        <v>0.5238</v>
       </c>
       <c r="H58" s="13" t="n">
-        <v>-0.0247</v>
+        <v>-0.0245</v>
       </c>
       <c r="I58" s="13" t="n">
-        <v>-0.05917149296025048</v>
+        <v>-0.05031031389922158</v>
       </c>
       <c r="J58" s="14" t="n">
         <v>0.5</v>
@@ -5034,16 +5034,16 @@
         <v>-120</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>0.5103</v>
+        <v>0.5113</v>
       </c>
       <c r="G65" s="8" t="n">
         <v>0.5455</v>
       </c>
       <c r="H65" s="8" t="n">
-        <v>-0.031</v>
+        <v>-0.0304</v>
       </c>
       <c r="I65" s="8" t="n">
-        <v>-0.0597714860381045</v>
+        <v>-0.05812694981548389</v>
       </c>
       <c r="J65" s="10" t="n">
         <v>0.5</v>
@@ -7702,7 +7702,7 @@
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>3.03</v>
+        <v>2.98</v>
       </c>
       <c r="E20" s="9" t="n">
         <v>-3</v>
@@ -8230,7 +8230,7 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" s="18" t="n">
         <v>1.9</v>
@@ -8262,7 +8262,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D13" s="16" t="n">
         <v>1.88</v>
@@ -8326,7 +8326,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" s="16" t="n">
         <v>1.79</v>
@@ -8358,7 +8358,7 @@
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D16" s="18" t="n">
         <v>1.76</v>
@@ -32020,7 +32020,7 @@
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>Watson will learn Monday if he or Shedeur Sanders will be named starting quarterback for the Browns, Jeremy Fowler of ESPN reports.</t>
+          <t>Watson will learn Monday if he or Shedeur Sanders will be named the starting quarterback for the Browns, Jeremy Fowler of ESPN reports.</t>
         </is>
       </c>
     </row>
@@ -39880,27 +39880,27 @@
       </c>
       <c r="B432" s="5" t="inlineStr">
         <is>
-          <t>Tyler Biadasz</t>
+          <t>Gary Jennings</t>
         </is>
       </c>
       <c r="C432" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D432" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E432" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F432" s="5" t="inlineStr">
         <is>
-          <t>The Chargers placed Biadasz (knee) on injured reserve Sunday.</t>
+          <t>The Chargers signed Jennings to a contract Sunday.</t>
         </is>
       </c>
     </row>
@@ -39912,27 +39912,27 @@
       </c>
       <c r="B433" s="4" t="inlineStr">
         <is>
-          <t>Tre' Harris</t>
+          <t>Tyler Biadasz</t>
         </is>
       </c>
       <c r="C433" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D433" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E433" s="4" t="inlineStr">
         <is>
-          <t>Undisclosed</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F433" s="4" t="inlineStr">
         <is>
-          <t>Harris (undisclosed) will participate in Saturday's training camp practice, Alex Insdorf of BoltBeat.com reports.</t>
+          <t>The Chargers placed Biadasz (knee) on injured reserve Sunday.</t>
         </is>
       </c>
     </row>
@@ -39944,12 +39944,12 @@
       </c>
       <c r="B434" s="5" t="inlineStr">
         <is>
-          <t>Rashawn Slater</t>
+          <t>Tre' Harris</t>
         </is>
       </c>
       <c r="C434" s="5" t="inlineStr">
         <is>
-          <t>OT</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D434" s="5" t="inlineStr">
@@ -39959,12 +39959,12 @@
       </c>
       <c r="E434" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Undisclosed</t>
         </is>
       </c>
       <c r="F434" s="5" t="inlineStr">
         <is>
-          <t>Slater (undisclosed) was a limited participant in Saturday's practice, Alex Insdorf of BoltBeat.com reports.</t>
+          <t>Harris (undisclosed) will participate in Saturday's training camp practice, Alex Insdorf of BoltBeat.com reports.</t>
         </is>
       </c>
     </row>
@@ -39976,12 +39976,12 @@
       </c>
       <c r="B435" s="4" t="inlineStr">
         <is>
-          <t>Quentin Johnston</t>
+          <t>Rashawn Slater</t>
         </is>
       </c>
       <c r="C435" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>OT</t>
         </is>
       </c>
       <c r="D435" s="4" t="inlineStr">
@@ -39996,7 +39996,7 @@
       </c>
       <c r="F435" s="4" t="inlineStr">
         <is>
-          <t>Johnston (lower body) will not participate in Saturday's training camp practice, Alex Insdorf of BoltBeat.com reports.</t>
+          <t>Slater (undisclosed) was a limited participant in Saturday's practice, Alex Insdorf of BoltBeat.com reports.</t>
         </is>
       </c>
     </row>
@@ -40008,27 +40008,27 @@
       </c>
       <c r="B436" s="5" t="inlineStr">
         <is>
-          <t>Kimani Vidal</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="C436" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D436" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E436" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F436" s="5" t="inlineStr">
         <is>
-          <t>Vidal turned four carries into six yards while catching both targets for 10 yards during the Chargers' 41-17 preseason loss to the 49ers on Thursday. He also returned one kickoff for 27 yards.</t>
+          <t>Johnston (lower body) will not participate in Saturday's training camp practice, Alex Insdorf of BoltBeat.com reports.</t>
         </is>
       </c>
     </row>
@@ -40040,12 +40040,12 @@
       </c>
       <c r="B437" s="4" t="inlineStr">
         <is>
-          <t>KeAndre Lambert-Smith</t>
+          <t>Kimani Vidal</t>
         </is>
       </c>
       <c r="C437" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D437" s="4" t="inlineStr">
@@ -40060,7 +40060,7 @@
       </c>
       <c r="F437" s="4" t="inlineStr">
         <is>
-          <t>Lambert-Smith caught two of four targets for 14 yards in Thursday night's 41-17 preseason loss to the 49ers.</t>
+          <t>Vidal turned four carries into six yards while catching both targets for 10 yards during the Chargers' 41-17 preseason loss to the 49ers on Thursday. He also returned one kickoff for 27 yards.</t>
         </is>
       </c>
     </row>
@@ -40072,12 +40072,12 @@
       </c>
       <c r="B438" s="5" t="inlineStr">
         <is>
-          <t>Trey Lance</t>
+          <t>KeAndre Lambert-Smith</t>
         </is>
       </c>
       <c r="C438" s="5" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D438" s="5" t="inlineStr">
@@ -40092,7 +40092,7 @@
       </c>
       <c r="F438" s="5" t="inlineStr">
         <is>
-          <t>Lance completed 10 of 16 passes for 73 yards while rushing twice for 42 yards in Thursday's 41-17 preseason loss to the 49ers.</t>
+          <t>Lambert-Smith caught two of four targets for 14 yards in Thursday night's 41-17 preseason loss to the 49ers.</t>
         </is>
       </c>
     </row>
@@ -40104,12 +40104,12 @@
       </c>
       <c r="B439" s="4" t="inlineStr">
         <is>
-          <t>Cameron Dicker</t>
+          <t>Trey Lance</t>
         </is>
       </c>
       <c r="C439" s="4" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D439" s="4" t="inlineStr">
@@ -40124,7 +40124,7 @@
       </c>
       <c r="F439" s="4" t="inlineStr">
         <is>
-          <t>Dicker made his sole field-goal attempt but missed a PAT try in Thursday night's 41-17 preseason loss to the 49ers.</t>
+          <t>Lance completed 10 of 16 passes for 73 yards while rushing twice for 42 yards in Thursday's 41-17 preseason loss to the 49ers.</t>
         </is>
       </c>
     </row>
@@ -40136,12 +40136,12 @@
       </c>
       <c r="B440" s="5" t="inlineStr">
         <is>
-          <t>Charlie Kolar</t>
+          <t>Cameron Dicker</t>
         </is>
       </c>
       <c r="C440" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="D440" s="5" t="inlineStr">
@@ -40156,7 +40156,7 @@
       </c>
       <c r="F440" s="5" t="inlineStr">
         <is>
-          <t>Kolar and David Njoku both started Thursday's preseason game against San Francisco. Kolar finished with one catch for nine yards on eight snaps.</t>
+          <t>Dicker made his sole field-goal attempt but missed a PAT try in Thursday night's 41-17 preseason loss to the 49ers.</t>
         </is>
       </c>
     </row>
@@ -40168,7 +40168,7 @@
       </c>
       <c r="B441" s="4" t="inlineStr">
         <is>
-          <t>David Njoku</t>
+          <t>Charlie Kolar</t>
         </is>
       </c>
       <c r="C441" s="4" t="inlineStr">
@@ -40188,7 +40188,7 @@
       </c>
       <c r="F441" s="4" t="inlineStr">
         <is>
-          <t>Njoku and Charlie Kolar both started Thursday's preseason game against San Francisco. Njoku finished with no targets on five snaps.</t>
+          <t>Kolar and David Njoku both started Thursday's preseason game against San Francisco. Kolar finished with one catch for nine yards on eight snaps.</t>
         </is>
       </c>
     </row>
@@ -40200,12 +40200,12 @@
       </c>
       <c r="B442" s="5" t="inlineStr">
         <is>
-          <t>Keaton Mitchell</t>
+          <t>David Njoku</t>
         </is>
       </c>
       <c r="C442" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D442" s="5" t="inlineStr">
@@ -40220,7 +40220,7 @@
       </c>
       <c r="F442" s="5" t="inlineStr">
         <is>
-          <t>Mitchell rushed three times for minus-1 yard and brought in his only target for 11 yards in the Chargers' 41-17 preseason loss to the 49ers on Thursday night.</t>
+          <t>Njoku and Charlie Kolar both started Thursday's preseason game against San Francisco. Njoku finished with no targets on five snaps.</t>
         </is>
       </c>
     </row>
@@ -40232,12 +40232,12 @@
       </c>
       <c r="B443" s="4" t="inlineStr">
         <is>
-          <t>Ladd McConkey</t>
+          <t>Keaton Mitchell</t>
         </is>
       </c>
       <c r="C443" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D443" s="4" t="inlineStr">
@@ -40252,7 +40252,7 @@
       </c>
       <c r="F443" s="4" t="inlineStr">
         <is>
-          <t>McConkey failed to bring in his only target in the Chargers' 41-17 preseason loss to the 49ers on Thursday night.</t>
+          <t>Mitchell rushed three times for minus-1 yard and brought in his only target for 11 yards in the Chargers' 41-17 preseason loss to the 49ers on Thursday night.</t>
         </is>
       </c>
     </row>
@@ -40264,12 +40264,12 @@
       </c>
       <c r="B444" s="5" t="inlineStr">
         <is>
-          <t>Justin Herbert</t>
+          <t>Ladd McConkey</t>
         </is>
       </c>
       <c r="C444" s="5" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D444" s="5" t="inlineStr">
@@ -40284,7 +40284,7 @@
       </c>
       <c r="F444" s="5" t="inlineStr">
         <is>
-          <t>Herbert completed one of two passes for nine yards with no touchdowns or interceptions in the Chargers' 41-17 preseason loss to the 49ers on Thursday night.</t>
+          <t>McConkey failed to bring in his only target in the Chargers' 41-17 preseason loss to the 49ers on Thursday night.</t>
         </is>
       </c>
     </row>
@@ -40296,12 +40296,12 @@
       </c>
       <c r="B445" s="4" t="inlineStr">
         <is>
-          <t>Omarion Hampton</t>
+          <t>Justin Herbert</t>
         </is>
       </c>
       <c r="C445" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D445" s="4" t="inlineStr">
@@ -40316,7 +40316,7 @@
       </c>
       <c r="F445" s="4" t="inlineStr">
         <is>
-          <t>Hampton rushed once for minus-1 yard and wasn't targeted in the Chargers' 41-17 preseason loss to the 49ers on Thursday night.</t>
+          <t>Herbert completed one of two passes for nine yards with no touchdowns or interceptions in the Chargers' 41-17 preseason loss to the 49ers on Thursday night.</t>
         </is>
       </c>
     </row>
@@ -40328,27 +40328,27 @@
       </c>
       <c r="B446" s="5" t="inlineStr">
         <is>
-          <t>Luke Grimm</t>
+          <t>Omarion Hampton</t>
         </is>
       </c>
       <c r="C446" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D446" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E446" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F446" s="5" t="inlineStr">
         <is>
-          <t>Grimm (undisclosed) reverted to the Chargers' injured-reserve list Thursday, per the NFL's transaction log.</t>
+          <t>Hampton rushed once for minus-1 yard and wasn't targeted in the Chargers' 41-17 preseason loss to the 49ers on Thursday night.</t>
         </is>
       </c>
     </row>
@@ -40360,7 +40360,7 @@
       </c>
       <c r="B447" s="4" t="inlineStr">
         <is>
-          <t>Liam Clifford</t>
+          <t>Luke Grimm</t>
         </is>
       </c>
       <c r="C447" s="4" t="inlineStr">
@@ -40370,17 +40370,17 @@
       </c>
       <c r="D447" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E447" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F447" s="4" t="inlineStr">
         <is>
-          <t>The Chargers signed Clifford on Wednesday.</t>
+          <t>Grimm (undisclosed) reverted to the Chargers' injured-reserve list Thursday, per the NFL's transaction log.</t>
         </is>
       </c>
     </row>
@@ -40392,12 +40392,12 @@
       </c>
       <c r="B448" s="5" t="inlineStr">
         <is>
-          <t>Junior Colson</t>
+          <t>Liam Clifford</t>
         </is>
       </c>
       <c r="C448" s="5" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D448" s="5" t="inlineStr">
@@ -40410,7 +40410,11 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F448" s="5" t="inlineStr"/>
+      <c r="F448" s="5" t="inlineStr">
+        <is>
+          <t>The Chargers signed Clifford on Wednesday.</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" s="4" t="inlineStr">
@@ -40420,12 +40424,12 @@
       </c>
       <c r="B449" s="4" t="inlineStr">
         <is>
-          <t>Nikko Reed</t>
+          <t>Junior Colson</t>
         </is>
       </c>
       <c r="C449" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D449" s="4" t="inlineStr">
@@ -40448,7 +40452,7 @@
       </c>
       <c r="B450" s="5" t="inlineStr">
         <is>
-          <t>Eric Rogers</t>
+          <t>Nikko Reed</t>
         </is>
       </c>
       <c r="C450" s="5" t="inlineStr">
@@ -40476,12 +40480,12 @@
       </c>
       <c r="B451" s="4" t="inlineStr">
         <is>
-          <t>Oronde Gadsden</t>
+          <t>Eric Rogers</t>
         </is>
       </c>
       <c r="C451" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D451" s="4" t="inlineStr">
@@ -40494,11 +40498,7 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F451" s="4" t="inlineStr">
-        <is>
-          <t>Gadsden caught two of three targets for 21 yards in Thursday's 21-7 preseason win over the Texans.</t>
-        </is>
-      </c>
+      <c r="F451" s="4" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" s="5" t="inlineStr">
@@ -40508,12 +40508,12 @@
       </c>
       <c r="B452" s="5" t="inlineStr">
         <is>
-          <t>Andre Carter II</t>
+          <t>Oronde Gadsden</t>
         </is>
       </c>
       <c r="C452" s="5" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D452" s="5" t="inlineStr">
@@ -40528,7 +40528,7 @@
       </c>
       <c r="F452" s="5" t="inlineStr">
         <is>
-          <t>The Chargers signed Carter on Monday, Aaron Wilson of KPRC 2 Houston reports.</t>
+          <t>Gadsden caught two of three targets for 21 yards in Thursday's 21-7 preseason win over the Texans.</t>
         </is>
       </c>
     </row>
@@ -40540,12 +40540,12 @@
       </c>
       <c r="B453" s="4" t="inlineStr">
         <is>
-          <t>Kendall Williamson</t>
+          <t>Andre Carter II</t>
         </is>
       </c>
       <c r="C453" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D453" s="4" t="inlineStr">
@@ -40560,7 +40560,7 @@
       </c>
       <c r="F453" s="4" t="inlineStr">
         <is>
-          <t>Williamson (ankle) participated in the Chargers' training camp Wednesday, Eric Smith of the team's official site reports.</t>
+          <t>The Chargers signed Carter on Monday, Aaron Wilson of KPRC 2 Houston reports.</t>
         </is>
       </c>
     </row>
@@ -40572,12 +40572,12 @@
       </c>
       <c r="B454" s="5" t="inlineStr">
         <is>
-          <t>Tuli Tuipulotu</t>
+          <t>Kendall Williamson</t>
         </is>
       </c>
       <c r="C454" s="5" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D454" s="5" t="inlineStr">
@@ -40592,7 +40592,7 @@
       </c>
       <c r="F454" s="5" t="inlineStr">
         <is>
-          <t>Tuipulotu did not participate in team drills Monday due his ongoing negotiations on an extension, Kris Rhim of ESPN.com reports.</t>
+          <t>Williamson (ankle) participated in the Chargers' training camp Wednesday, Eric Smith of the team's official site reports.</t>
         </is>
       </c>
     </row>
@@ -45376,12 +45376,12 @@
       </c>
       <c r="B605" s="4" t="inlineStr">
         <is>
-          <t>Cade York</t>
+          <t>Dominic Richardson</t>
         </is>
       </c>
       <c r="C605" s="4" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D605" s="4" t="inlineStr">
@@ -45396,7 +45396,7 @@
       </c>
       <c r="F605" s="4" t="inlineStr">
         <is>
-          <t>York missed his sole field-goal attempt, but converted a PAT in Friday night's preseason game against the Steelers.</t>
+          <t>The Jets signed Richardson to a contract Sunday.</t>
         </is>
       </c>
     </row>
@@ -45408,12 +45408,12 @@
       </c>
       <c r="B606" s="5" t="inlineStr">
         <is>
-          <t>Cade Klubnik</t>
+          <t>Cade York</t>
         </is>
       </c>
       <c r="C606" s="5" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="D606" s="5" t="inlineStr">
@@ -45428,7 +45428,7 @@
       </c>
       <c r="F606" s="5" t="inlineStr">
         <is>
-          <t>Klubnik completed 10 of 14 passes for 75 yards and recorded a 16-yard carry during the Jets' 17-0 preseason win over the Steelers on Friday.</t>
+          <t>York missed his sole field-goal attempt, but converted a PAT in Friday night's preseason game against the Steelers.</t>
         </is>
       </c>
     </row>
@@ -45440,12 +45440,12 @@
       </c>
       <c r="B607" s="4" t="inlineStr">
         <is>
-          <t>Jason Sanders</t>
+          <t>Cade Klubnik</t>
         </is>
       </c>
       <c r="C607" s="4" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D607" s="4" t="inlineStr">
@@ -45460,7 +45460,7 @@
       </c>
       <c r="F607" s="4" t="inlineStr">
         <is>
-          <t>Sanders converted his sole field-goal attempt and only PAT in Friday night's preseason game against the Steelers.</t>
+          <t>Klubnik completed 10 of 14 passes for 75 yards and recorded a 16-yard carry during the Jets' 17-0 preseason win over the Steelers on Friday.</t>
         </is>
       </c>
     </row>
@@ -45472,27 +45472,27 @@
       </c>
       <c r="B608" s="5" t="inlineStr">
         <is>
-          <t>Isaiah Davis</t>
+          <t>Jason Sanders</t>
         </is>
       </c>
       <c r="C608" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="D608" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E608" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F608" s="5" t="inlineStr">
         <is>
-          <t>Davis (knee) did not play in the Jets' 17-0 preseason win over the Steelers on Friday.</t>
+          <t>Sanders converted his sole field-goal attempt and only PAT in Friday night's preseason game against the Steelers.</t>
         </is>
       </c>
     </row>
@@ -45504,27 +45504,27 @@
       </c>
       <c r="B609" s="4" t="inlineStr">
         <is>
-          <t>Mason Taylor</t>
+          <t>Isaiah Davis</t>
         </is>
       </c>
       <c r="C609" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D609" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E609" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F609" s="4" t="inlineStr">
         <is>
-          <t>Taylor caught his only target for 10 yards in Friday's 17-0 preseason win over the Steelers.</t>
+          <t>Davis (knee) did not play in the Jets' 17-0 preseason win over the Steelers on Friday.</t>
         </is>
       </c>
     </row>
@@ -45536,12 +45536,12 @@
       </c>
       <c r="B610" s="5" t="inlineStr">
         <is>
-          <t>Adonai Mitchell</t>
+          <t>Mason Taylor</t>
         </is>
       </c>
       <c r="C610" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D610" s="5" t="inlineStr">
@@ -45556,7 +45556,7 @@
       </c>
       <c r="F610" s="5" t="inlineStr">
         <is>
-          <t>Mitchell caught both of his targets for 29 yards in Friday's 17-0 preseason win over the Steelers.</t>
+          <t>Taylor caught his only target for 10 yards in Friday's 17-0 preseason win over the Steelers.</t>
         </is>
       </c>
     </row>
@@ -45568,12 +45568,12 @@
       </c>
       <c r="B611" s="4" t="inlineStr">
         <is>
-          <t>Braelon Allen</t>
+          <t>Adonai Mitchell</t>
         </is>
       </c>
       <c r="C611" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D611" s="4" t="inlineStr">
@@ -45588,7 +45588,7 @@
       </c>
       <c r="F611" s="4" t="inlineStr">
         <is>
-          <t>Allen rushed three times for four yards and caught his lone target for five yards in Friday's 17-0 preseason win over the Steelers.</t>
+          <t>Mitchell caught both of his targets for 29 yards in Friday's 17-0 preseason win over the Steelers.</t>
         </is>
       </c>
     </row>
@@ -45600,12 +45600,12 @@
       </c>
       <c r="B612" s="5" t="inlineStr">
         <is>
-          <t>Omar Cooper Jr.</t>
+          <t>Braelon Allen</t>
         </is>
       </c>
       <c r="C612" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D612" s="5" t="inlineStr">
@@ -45620,7 +45620,7 @@
       </c>
       <c r="F612" s="5" t="inlineStr">
         <is>
-          <t>Cooper caught his only target for nine yards in Friday's 17-0 preseason win over the Steelers.</t>
+          <t>Allen rushed three times for four yards and caught his lone target for five yards in Friday's 17-0 preseason win over the Steelers.</t>
         </is>
       </c>
     </row>
@@ -45632,12 +45632,12 @@
       </c>
       <c r="B613" s="4" t="inlineStr">
         <is>
-          <t>Geno Smith</t>
+          <t>Omar Cooper Jr.</t>
         </is>
       </c>
       <c r="C613" s="4" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D613" s="4" t="inlineStr">
@@ -45652,7 +45652,7 @@
       </c>
       <c r="F613" s="4" t="inlineStr">
         <is>
-          <t>Smith completed all seven of his pass attempts for 65 yards and a touchdown in Friday's 17-0 preseason win over the Steelers.</t>
+          <t>Cooper caught his only target for nine yards in Friday's 17-0 preseason win over the Steelers.</t>
         </is>
       </c>
     </row>
@@ -45664,12 +45664,12 @@
       </c>
       <c r="B614" s="5" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>Geno Smith</t>
         </is>
       </c>
       <c r="C614" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D614" s="5" t="inlineStr">
@@ -45684,7 +45684,7 @@
       </c>
       <c r="F614" s="5" t="inlineStr">
         <is>
-          <t>Wilson caught his only target for 10 yards in Friday's 17-0 preseason win over the Steelers.</t>
+          <t>Smith completed all seven of his pass attempts for 65 yards and a touchdown in Friday's 17-0 preseason win over the Steelers.</t>
         </is>
       </c>
     </row>
@@ -45696,27 +45696,27 @@
       </c>
       <c r="B615" s="4" t="inlineStr">
         <is>
-          <t>Chase Curtis</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="C615" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D615" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E615" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F615" s="4" t="inlineStr">
         <is>
-          <t>Curtis (knee) is out for the remainder of Friday's preseason contest at Pittsburgh.</t>
+          <t>Wilson caught his only target for 10 yards in Friday's 17-0 preseason win over the Steelers.</t>
         </is>
       </c>
     </row>
@@ -45728,27 +45728,27 @@
       </c>
       <c r="B616" s="5" t="inlineStr">
         <is>
-          <t>Kingsley Jonathan</t>
+          <t>Chase Curtis</t>
         </is>
       </c>
       <c r="C616" s="5" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D616" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E616" s="5" t="inlineStr">
         <is>
-          <t>Bruise</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F616" s="5" t="inlineStr">
         <is>
-          <t>Jonathan (thigh) reverted to the Jets' injured reserve Wednesday, Aaron Wilson of KPRC 2 Houston reports.</t>
+          <t>Curtis (knee) is out for the remainder of Friday's preseason contest at Pittsburgh.</t>
         </is>
       </c>
     </row>
@@ -45760,27 +45760,27 @@
       </c>
       <c r="B617" s="4" t="inlineStr">
         <is>
-          <t>Qwan'tez Stiggers</t>
+          <t>Kingsley Jonathan</t>
         </is>
       </c>
       <c r="C617" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D617" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E617" s="4" t="inlineStr">
         <is>
-          <t>Concussion</t>
+          <t>Bruise</t>
         </is>
       </c>
       <c r="F617" s="4" t="inlineStr">
         <is>
-          <t>Stiggers (concussion) was a limited participant in Wednesday's practice, Rich Cimini of ESPN.com reports.</t>
+          <t>Jonathan (thigh) reverted to the Jets' injured reserve Wednesday, Aaron Wilson of KPRC 2 Houston reports.</t>
         </is>
       </c>
     </row>
@@ -45792,27 +45792,27 @@
       </c>
       <c r="B618" s="5" t="inlineStr">
         <is>
-          <t>Junior Bergen</t>
+          <t>Qwan'tez Stiggers</t>
         </is>
       </c>
       <c r="C618" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D618" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E618" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Concussion</t>
         </is>
       </c>
       <c r="F618" s="5" t="inlineStr">
         <is>
-          <t>The Jets signed Bergen to a contract Wednesday, Eric Allen of the team's official site reports.</t>
+          <t>Stiggers (concussion) was a limited participant in Wednesday's practice, Rich Cimini of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -45824,27 +45824,27 @@
       </c>
       <c r="B619" s="4" t="inlineStr">
         <is>
-          <t>Nahshon Wright</t>
+          <t>Junior Bergen</t>
         </is>
       </c>
       <c r="C619" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D619" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E619" s="4" t="inlineStr">
         <is>
-          <t>Strain</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F619" s="4" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>The Jets signed Bergen to a contract Wednesday, Eric Allen of the team's official site reports.</t>
         </is>
       </c>
     </row>
@@ -45856,12 +45856,12 @@
       </c>
       <c r="B620" s="5" t="inlineStr">
         <is>
-          <t>VJ Payne</t>
+          <t>Nahshon Wright</t>
         </is>
       </c>
       <c r="C620" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D620" s="5" t="inlineStr">
@@ -45871,7 +45871,7 @@
       </c>
       <c r="E620" s="5" t="inlineStr">
         <is>
-          <t>Bruise</t>
+          <t>Strain</t>
         </is>
       </c>
       <c r="F620" s="5" t="inlineStr">
@@ -45888,12 +45888,12 @@
       </c>
       <c r="B621" s="4" t="inlineStr">
         <is>
-          <t>Kenyon Sadiq</t>
+          <t>VJ Payne</t>
         </is>
       </c>
       <c r="C621" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D621" s="4" t="inlineStr">
@@ -45903,7 +45903,7 @@
       </c>
       <c r="E621" s="4" t="inlineStr">
         <is>
-          <t>Surgery</t>
+          <t>Bruise</t>
         </is>
       </c>
       <c r="F621" s="4" t="inlineStr">
@@ -45920,12 +45920,12 @@
       </c>
       <c r="B622" s="5" t="inlineStr">
         <is>
-          <t>Breece Hall</t>
+          <t>Kenyon Sadiq</t>
         </is>
       </c>
       <c r="C622" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D622" s="5" t="inlineStr">
@@ -45935,7 +45935,7 @@
       </c>
       <c r="E622" s="5" t="inlineStr">
         <is>
-          <t>Strain</t>
+          <t>Surgery</t>
         </is>
       </c>
       <c r="F622" s="5" t="inlineStr">
@@ -45952,12 +45952,12 @@
       </c>
       <c r="B623" s="4" t="inlineStr">
         <is>
-          <t>Mory Bamba</t>
+          <t>Breece Hall</t>
         </is>
       </c>
       <c r="C623" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D623" s="4" t="inlineStr">
@@ -45967,7 +45967,7 @@
       </c>
       <c r="E623" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Strain</t>
         </is>
       </c>
       <c r="F623" s="4" t="inlineStr">
@@ -45984,25 +45984,29 @@
       </c>
       <c r="B624" s="5" t="inlineStr">
         <is>
-          <t>Joseph Ossai</t>
+          <t>Mory Bamba</t>
         </is>
       </c>
       <c r="C624" s="5" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D624" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E624" s="5" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="F624" s="5" t="inlineStr"/>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F624" s="5" t="inlineStr">
+        <is>
+          <t>questionable</t>
+        </is>
+      </c>
     </row>
     <row r="625">
       <c r="A625" s="4" t="inlineStr">
@@ -46012,12 +46016,12 @@
       </c>
       <c r="B625" s="4" t="inlineStr">
         <is>
-          <t>Kiko Mauigoa</t>
+          <t>Joseph Ossai</t>
         </is>
       </c>
       <c r="C625" s="4" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D625" s="4" t="inlineStr">
@@ -46040,12 +46044,12 @@
       </c>
       <c r="B626" s="5" t="inlineStr">
         <is>
-          <t>T'Vondre Sweat</t>
+          <t>Kiko Mauigoa</t>
         </is>
       </c>
       <c r="C626" s="5" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D626" s="5" t="inlineStr">
@@ -46068,12 +46072,12 @@
       </c>
       <c r="B627" s="4" t="inlineStr">
         <is>
-          <t>Andre Cisco</t>
+          <t>T'Vondre Sweat</t>
         </is>
       </c>
       <c r="C627" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="D627" s="4" t="inlineStr">
@@ -46096,12 +46100,12 @@
       </c>
       <c r="B628" s="5" t="inlineStr">
         <is>
-          <t>Kingsley Enagbare</t>
+          <t>Andre Cisco</t>
         </is>
       </c>
       <c r="C628" s="5" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D628" s="5" t="inlineStr">
@@ -46114,11 +46118,7 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F628" s="5" t="inlineStr">
-        <is>
-          <t>Enagbare (undisclosed) was a full participant in Tuesday's practice, Brian Costello of the New York Post reports.</t>
-        </is>
-      </c>
+      <c r="F628" s="5" t="inlineStr"/>
     </row>
     <row r="629">
       <c r="A629" s="4" t="inlineStr">
@@ -46128,27 +46128,27 @@
       </c>
       <c r="B629" s="4" t="inlineStr">
         <is>
-          <t>D'Angelo Ponds</t>
+          <t>Kingsley Enagbare</t>
         </is>
       </c>
       <c r="C629" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D629" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E629" s="4" t="inlineStr">
         <is>
-          <t>Strain</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F629" s="4" t="inlineStr">
         <is>
-          <t>Ponds (calf) is nearing a return to the field according to head coach Aaron Glenn, Eric Allen of the Jets' official site reports.</t>
+          <t>Enagbare (undisclosed) was a full participant in Tuesday's practice, Brian Costello of the New York Post reports.</t>
         </is>
       </c>
     </row>
@@ -47904,7 +47904,7 @@
       </c>
       <c r="F684" s="5" t="inlineStr">
         <is>
-          <t>Kittle (Achilles) was activated from the Active/PUP list Sunday.</t>
+          <t>Kittle (Achilles) was activated from the active/PUP list Sunday.</t>
         </is>
       </c>
     </row>
@@ -48556,27 +48556,27 @@
       </c>
       <c r="B705" s="4" t="inlineStr">
         <is>
-          <t>Bud Clark</t>
+          <t>Drew Lock</t>
         </is>
       </c>
       <c r="C705" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D705" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E705" s="4" t="inlineStr">
         <is>
-          <t>Leg</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F705" s="4" t="inlineStr">
         <is>
-          <t>Clark was carted off the field with a right leg injury during Sunday's preseason matchup with the Titans, Brady Henderson of ESPN.com reports.</t>
+          <t>Lock completed 12 of 14 passes for 103 yards and a touchdown while rushing twice for eight yards in Sunday's 19-16 preseason loss to the Titans.</t>
         </is>
       </c>
     </row>
@@ -48588,12 +48588,12 @@
       </c>
       <c r="B706" s="5" t="inlineStr">
         <is>
-          <t>Drew Lock</t>
+          <t>Emmanuel Henderson Jr.</t>
         </is>
       </c>
       <c r="C706" s="5" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D706" s="5" t="inlineStr">
@@ -48608,7 +48608,7 @@
       </c>
       <c r="F706" s="5" t="inlineStr">
         <is>
-          <t>Lock will start Sunday's preseason game against the Titans, Bob Condotta of The Seattle Times reports.</t>
+          <t>Henderson caught one of two targets for seven yards in Sunday's 19-16 preseason loss to the Titans. He also returned two kickoffs for 47 yards and notched two solo tackles on special teams.</t>
         </is>
       </c>
     </row>
@@ -48620,12 +48620,12 @@
       </c>
       <c r="B707" s="4" t="inlineStr">
         <is>
-          <t>Jadarian Price</t>
+          <t>Elijah Arroyo</t>
         </is>
       </c>
       <c r="C707" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D707" s="4" t="inlineStr">
@@ -48640,7 +48640,7 @@
       </c>
       <c r="F707" s="4" t="inlineStr">
         <is>
-          <t>Price will not play in Sunday's preseason game against the Titans, Gregg Bell of The Tacoma News Tribune reports.</t>
+          <t>Arroyo caught two of four targets for 50 yards and a touchdown in Sunday's 19-16 preseason loss to the Titans.</t>
         </is>
       </c>
     </row>
@@ -48652,27 +48652,27 @@
       </c>
       <c r="B708" s="5" t="inlineStr">
         <is>
-          <t>Julian Hicks</t>
+          <t>Bud Clark</t>
         </is>
       </c>
       <c r="C708" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D708" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E708" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Leg</t>
         </is>
       </c>
       <c r="F708" s="5" t="inlineStr">
         <is>
-          <t>The Seahawks signed Hicks to a contract Saturday, John Boyle of the team's official site reports.</t>
+          <t>Clark was carted off the field with a right leg injury during Sunday's preseason matchup with the Titans, Brady Henderson of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -48684,27 +48684,27 @@
       </c>
       <c r="B709" s="4" t="inlineStr">
         <is>
-          <t>Jake Bobo</t>
+          <t>Jadarian Price</t>
         </is>
       </c>
       <c r="C709" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D709" s="4" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E709" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F709" s="4" t="inlineStr">
         <is>
-          <t>The Seahawks placed Bobo (knee) on injured reserve Saturday, John Boyle of the team's official site reports.</t>
+          <t>Price will not play in Sunday's preseason game against the Titans, Gregg Bell of The Tacoma News Tribune reports.</t>
         </is>
       </c>
     </row>
@@ -48716,12 +48716,12 @@
       </c>
       <c r="B710" s="5" t="inlineStr">
         <is>
-          <t>Trevon Diggs</t>
+          <t>Julian Hicks</t>
         </is>
       </c>
       <c r="C710" s="5" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D710" s="5" t="inlineStr">
@@ -48736,7 +48736,7 @@
       </c>
       <c r="F710" s="5" t="inlineStr">
         <is>
-          <t>The Seahawks are slated to sign Diggs to a one-year deal, Adam Schefter of ESPN reports.</t>
+          <t>The Seahawks signed Hicks to a contract Saturday, John Boyle of the team's official site reports.</t>
         </is>
       </c>
     </row>
@@ -48748,12 +48748,12 @@
       </c>
       <c r="B711" s="4" t="inlineStr">
         <is>
-          <t>Joseph Vaughn</t>
+          <t>Jake Bobo</t>
         </is>
       </c>
       <c r="C711" s="4" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D711" s="4" t="inlineStr">
@@ -48768,7 +48768,7 @@
       </c>
       <c r="F711" s="4" t="inlineStr">
         <is>
-          <t>ir</t>
+          <t>The Seahawks placed Bobo (knee) on injured reserve Saturday, John Boyle of the team's official site reports.</t>
         </is>
       </c>
     </row>
@@ -48780,27 +48780,27 @@
       </c>
       <c r="B712" s="5" t="inlineStr">
         <is>
-          <t>Emanuel Wilson</t>
+          <t>Trevon Diggs</t>
         </is>
       </c>
       <c r="C712" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D712" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E712" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F712" s="5" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>The Seahawks are slated to sign Diggs to a one-year deal, Adam Schefter of ESPN reports.</t>
         </is>
       </c>
     </row>
@@ -48812,12 +48812,12 @@
       </c>
       <c r="B713" s="4" t="inlineStr">
         <is>
-          <t>Robbie Ouzts</t>
+          <t>Joseph Vaughn</t>
         </is>
       </c>
       <c r="C713" s="4" t="inlineStr">
         <is>
-          <t>FB</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D713" s="4" t="inlineStr">
@@ -48844,12 +48844,12 @@
       </c>
       <c r="B714" s="5" t="inlineStr">
         <is>
-          <t>Tory Horton</t>
+          <t>Emanuel Wilson</t>
         </is>
       </c>
       <c r="C714" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D714" s="5" t="inlineStr">
@@ -48859,7 +48859,7 @@
       </c>
       <c r="E714" s="5" t="inlineStr">
         <is>
-          <t>Undisclosed</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F714" s="5" t="inlineStr">
@@ -48876,12 +48876,12 @@
       </c>
       <c r="B715" s="4" t="inlineStr">
         <is>
-          <t>Shemar Jean-Charles</t>
+          <t>Robbie Ouzts</t>
         </is>
       </c>
       <c r="C715" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="D715" s="4" t="inlineStr">
@@ -48908,12 +48908,12 @@
       </c>
       <c r="B716" s="5" t="inlineStr">
         <is>
-          <t>Nick Emmanwori</t>
+          <t>Tory Horton</t>
         </is>
       </c>
       <c r="C716" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D716" s="5" t="inlineStr">
@@ -48923,7 +48923,7 @@
       </c>
       <c r="E716" s="5" t="inlineStr">
         <is>
-          <t>Surgery</t>
+          <t>Undisclosed</t>
         </is>
       </c>
       <c r="F716" s="5" t="inlineStr">
@@ -48940,27 +48940,27 @@
       </c>
       <c r="B717" s="4" t="inlineStr">
         <is>
-          <t>Anthony Hankerson</t>
+          <t>Shemar Jean-Charles</t>
         </is>
       </c>
       <c r="C717" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D717" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E717" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F717" s="4" t="inlineStr">
         <is>
-          <t>Hankerson and the Seahawks agreed on a contract Monday, John Boyle of the team's official website reports.</t>
+          <t>ir</t>
         </is>
       </c>
     </row>
@@ -48972,27 +48972,27 @@
       </c>
       <c r="B718" s="5" t="inlineStr">
         <is>
-          <t>Montorie Foster Jr.</t>
+          <t>Nick Emmanwori</t>
         </is>
       </c>
       <c r="C718" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D718" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E718" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Surgery</t>
         </is>
       </c>
       <c r="F718" s="5" t="inlineStr">
         <is>
-          <t>Foster caught five of seven targets for 36 yards and a touchdown in Saturday's 17-7 preseason loss to the Cowboys, building on what has been a strong performance in training camp, John Boyle of the Seahawks' official site reports.</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -49004,12 +49004,12 @@
       </c>
       <c r="B719" s="4" t="inlineStr">
         <is>
-          <t>Rashid Shaheed</t>
+          <t>Anthony Hankerson</t>
         </is>
       </c>
       <c r="C719" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D719" s="4" t="inlineStr">
@@ -49024,7 +49024,7 @@
       </c>
       <c r="F719" s="4" t="inlineStr">
         <is>
-          <t>Shaheed didn't suit up for Saturday's 17-7 preseason loss to the Cowboys.</t>
+          <t>Hankerson and the Seahawks agreed on a contract Monday, John Boyle of the team's official website reports.</t>
         </is>
       </c>
     </row>
@@ -49036,12 +49036,12 @@
       </c>
       <c r="B720" s="5" t="inlineStr">
         <is>
-          <t>AJ Barner</t>
+          <t>Montorie Foster Jr.</t>
         </is>
       </c>
       <c r="C720" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D720" s="5" t="inlineStr">
@@ -49056,7 +49056,7 @@
       </c>
       <c r="F720" s="5" t="inlineStr">
         <is>
-          <t>Barner was rested for Seattle's 17-7 preseason loss to the Cowboys on Saturday.</t>
+          <t>Foster caught five of seven targets for 36 yards and a touchdown in Saturday's 17-7 preseason loss to the Cowboys, building on what has been a strong performance in training camp, John Boyle of the Seahawks' official site reports.</t>
         </is>
       </c>
     </row>
@@ -49068,27 +49068,27 @@
       </c>
       <c r="B721" s="4" t="inlineStr">
         <is>
-          <t>Zach Charbonnet</t>
+          <t>Rashid Shaheed</t>
         </is>
       </c>
       <c r="C721" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D721" s="4" t="inlineStr">
         <is>
-          <t>Out</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E721" s="4" t="inlineStr">
         <is>
-          <t>Surgery</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F721" s="4" t="inlineStr">
         <is>
-          <t>Charbonnet (knee) remains on the active/PUP list as the Seahawks' second preseason contest (Sunday, Aug. 23 versus the Titans) approaches.</t>
+          <t>Shaheed didn't suit up for Saturday's 17-7 preseason loss to the Cowboys.</t>
         </is>
       </c>
     </row>
@@ -49100,12 +49100,12 @@
       </c>
       <c r="B722" s="5" t="inlineStr">
         <is>
-          <t>Jason Myers</t>
+          <t>AJ Barner</t>
         </is>
       </c>
       <c r="C722" s="5" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D722" s="5" t="inlineStr">
@@ -49120,7 +49120,7 @@
       </c>
       <c r="F722" s="5" t="inlineStr">
         <is>
-          <t>Myers missed his only field-goal attempt from 45 yards out and made his only extra-point try in the Seahawks' 17-7 preseason loss to the Cowboys on Saturday.</t>
+          <t>Barner was rested for Seattle's 17-7 preseason loss to the Cowboys on Saturday.</t>
         </is>
       </c>
     </row>
@@ -49132,7 +49132,7 @@
       </c>
       <c r="B723" s="4" t="inlineStr">
         <is>
-          <t>George Holani</t>
+          <t>Zach Charbonnet</t>
         </is>
       </c>
       <c r="C723" s="4" t="inlineStr">
@@ -49142,17 +49142,17 @@
       </c>
       <c r="D723" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="E723" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Surgery</t>
         </is>
       </c>
       <c r="F723" s="4" t="inlineStr">
         <is>
-          <t>Holani rushed 12 times for 42 yards in the Seahawks' 17-7 preseason loss to the Cowboys on Saturday.</t>
+          <t>Charbonnet (knee) remains on the active/PUP list as the Seahawks' second preseason contest (Sunday, Aug. 23 versus the Titans) approaches.</t>
         </is>
       </c>
     </row>
@@ -49164,12 +49164,12 @@
       </c>
       <c r="B724" s="5" t="inlineStr">
         <is>
-          <t>Devon Witherspoon</t>
+          <t>Jason Myers</t>
         </is>
       </c>
       <c r="C724" s="5" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="D724" s="5" t="inlineStr">
@@ -49184,7 +49184,7 @@
       </c>
       <c r="F724" s="5" t="inlineStr">
         <is>
-          <t>Witherspoon and the Seahawks agreed to a four-year, $132 million contract extension Saturday, Adam Schefter of ESPN reports.</t>
+          <t>Myers missed his only field-goal attempt from 45 yards out and made his only extra-point try in the Seahawks' 17-7 preseason loss to the Cowboys on Saturday.</t>
         </is>
       </c>
     </row>
@@ -49196,12 +49196,12 @@
       </c>
       <c r="B725" s="4" t="inlineStr">
         <is>
-          <t>DeMarcus Lawrence</t>
+          <t>George Holani</t>
         </is>
       </c>
       <c r="C725" s="4" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D725" s="4" t="inlineStr">
@@ -49216,7 +49216,7 @@
       </c>
       <c r="F725" s="4" t="inlineStr">
         <is>
-          <t>Lawrence has declared that he will retire after the 2026 season, Jori Epstein of Yahoo Sports reports.</t>
+          <t>Holani rushed 12 times for 42 yards in the Seahawks' 17-7 preseason loss to the Cowboys on Saturday.</t>
         </is>
       </c>
     </row>
@@ -49228,12 +49228,12 @@
       </c>
       <c r="B726" s="5" t="inlineStr">
         <is>
-          <t>Sam Darnold</t>
+          <t>Devon Witherspoon</t>
         </is>
       </c>
       <c r="C726" s="5" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D726" s="5" t="inlineStr">
@@ -49248,7 +49248,7 @@
       </c>
       <c r="F726" s="5" t="inlineStr">
         <is>
-          <t>Coach Mike Macdonald said Friday that Darnold won't suit up for Saturday's preseason game versus the Cowboys, Curtis Crabtree of Fox 13 Seattle reports.</t>
+          <t>Witherspoon and the Seahawks agreed to a four-year, $132 million contract extension Saturday, Adam Schefter of ESPN reports.</t>
         </is>
       </c>
     </row>
@@ -49260,12 +49260,12 @@
       </c>
       <c r="B727" s="4" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba</t>
+          <t>DeMarcus Lawrence</t>
         </is>
       </c>
       <c r="C727" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D727" s="4" t="inlineStr">
@@ -49280,7 +49280,7 @@
       </c>
       <c r="F727" s="4" t="inlineStr">
         <is>
-          <t>Smith-Njigba is always willing to be coached up in an attempt to be a better player, Anthony Moeglin of Roundtable Sports reports.</t>
+          <t>Lawrence has declared that he will retire after the 2026 season, Jori Epstein of Yahoo Sports reports.</t>
         </is>
       </c>
     </row>
@@ -49292,12 +49292,12 @@
       </c>
       <c r="B728" s="5" t="inlineStr">
         <is>
-          <t>AJ Finley</t>
+          <t>Sam Darnold</t>
         </is>
       </c>
       <c r="C728" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D728" s="5" t="inlineStr">
@@ -49310,7 +49310,11 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F728" s="5" t="inlineStr"/>
+      <c r="F728" s="5" t="inlineStr">
+        <is>
+          <t>Coach Mike Macdonald said Friday that Darnold won't suit up for Saturday's preseason game versus the Cowboys, Curtis Crabtree of Fox 13 Seattle reports.</t>
+        </is>
+      </c>
     </row>
     <row r="729">
       <c r="A729" s="4" t="inlineStr">
@@ -49320,12 +49324,12 @@
       </c>
       <c r="B729" s="4" t="inlineStr">
         <is>
-          <t>Brock Lampe</t>
+          <t>Jaxon Smith-Njigba</t>
         </is>
       </c>
       <c r="C729" s="4" t="inlineStr">
         <is>
-          <t>FB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D729" s="4" t="inlineStr">
@@ -49340,7 +49344,7 @@
       </c>
       <c r="F729" s="4" t="inlineStr">
         <is>
-          <t>Seattle signed Lampe on Thursday, John Boyle of the Seahawks' official site reports.</t>
+          <t>Smith-Njigba is always willing to be coached up in an attempt to be a better player, Anthony Moeglin of Roundtable Sports reports.</t>
         </is>
       </c>
     </row>
@@ -50144,12 +50148,12 @@
       </c>
       <c r="B755" s="4" t="inlineStr">
         <is>
-          <t>Carnell Tate</t>
+          <t>Joey Slye</t>
         </is>
       </c>
       <c r="C755" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="D755" s="4" t="inlineStr">
@@ -50164,7 +50168,7 @@
       </c>
       <c r="F755" s="4" t="inlineStr">
         <is>
-          <t>Tate (undisclosed) is in uniform for Sunday's preseason game against the Seahawks.</t>
+          <t>Slye converted all four of his field-goal attempts and made his only PAT try in Sunday's 19-16 preseason win over the Seahawks.</t>
         </is>
       </c>
     </row>
@@ -50176,27 +50180,27 @@
       </c>
       <c r="B756" s="5" t="inlineStr">
         <is>
-          <t>Nazeeh Johnson</t>
+          <t>Tyjae Spears</t>
         </is>
       </c>
       <c r="C756" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D756" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E756" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F756" s="5" t="inlineStr">
         <is>
-          <t>The Titans placed Johnson (ankle) on injured reserve Friday, Jim Wyatt of the team's official site reports.</t>
+          <t>Spears rushed twice for two yards and caught all three of his targets for 14 yards in Sunday's 19-16 preseason win over the Seahawks.</t>
         </is>
       </c>
     </row>
@@ -50208,7 +50212,7 @@
       </c>
       <c r="B757" s="4" t="inlineStr">
         <is>
-          <t>Mitchell Trubisky</t>
+          <t>Cam Ward</t>
         </is>
       </c>
       <c r="C757" s="4" t="inlineStr">
@@ -50218,17 +50222,17 @@
       </c>
       <c r="D757" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E757" s="4" t="inlineStr">
         <is>
-          <t>Biceps</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F757" s="4" t="inlineStr">
         <is>
-          <t>Trubisky (biceps) did not participate in Wednesday's practice, Terry McCormick of TitanInsider.com reports.</t>
+          <t>Ward completed eight of 12 passes for 69 yards, no touchdowns and no interceptions in Sunday's 19-16 preseason win over the Seahawks.</t>
         </is>
       </c>
     </row>
@@ -50260,7 +50264,7 @@
       </c>
       <c r="F758" s="5" t="inlineStr">
         <is>
-          <t>Pollard (undisclosed) returned to practice Wednesday, Turron Davenport of ESPN.com reports.</t>
+          <t>Pollard rushed twice for 12 yards and caught his only target for 33 yards in Sunday's 19-16 preseason win over the Seahawks.</t>
         </is>
       </c>
     </row>
@@ -50272,12 +50276,12 @@
       </c>
       <c r="B759" s="4" t="inlineStr">
         <is>
-          <t>D'Ernest Johnson</t>
+          <t>Carnell Tate</t>
         </is>
       </c>
       <c r="C759" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D759" s="4" t="inlineStr">
@@ -50292,7 +50296,7 @@
       </c>
       <c r="F759" s="4" t="inlineStr">
         <is>
-          <t>Johnson agreed to a one-year contract with the Titans on Wednesday, NFL reporter Jordan Schultz reports.</t>
+          <t>Tate didn't catch either of his two targets in Sunday's 19-16 preseason win over the Seahawks.</t>
         </is>
       </c>
     </row>
@@ -50304,17 +50308,17 @@
       </c>
       <c r="B760" s="5" t="inlineStr">
         <is>
-          <t>Kalel Mullings</t>
+          <t>Nazeeh Johnson</t>
         </is>
       </c>
       <c r="C760" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D760" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E760" s="5" t="inlineStr">
@@ -50324,7 +50328,7 @@
       </c>
       <c r="F760" s="5" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>The Titans placed Johnson (ankle) on injured reserve Friday, Jim Wyatt of the team's official site reports.</t>
         </is>
       </c>
     </row>
@@ -50336,27 +50340,27 @@
       </c>
       <c r="B761" s="4" t="inlineStr">
         <is>
-          <t>Jaylen Harrell</t>
+          <t>Mitchell Trubisky</t>
         </is>
       </c>
       <c r="C761" s="4" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D761" s="4" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E761" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Biceps</t>
         </is>
       </c>
       <c r="F761" s="4" t="inlineStr">
         <is>
-          <t>ir</t>
+          <t>Trubisky (biceps) did not participate in Wednesday's practice, Terry McCormick of TitanInsider.com reports.</t>
         </is>
       </c>
     </row>
@@ -50368,27 +50372,27 @@
       </c>
       <c r="B762" s="5" t="inlineStr">
         <is>
-          <t>Jaren Kanak</t>
+          <t>D'Ernest Johnson</t>
         </is>
       </c>
       <c r="C762" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D762" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E762" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F762" s="5" t="inlineStr">
         <is>
-          <t>ir</t>
+          <t>Johnson agreed to a one-year contract with the Titans on Wednesday, NFL reporter Jordan Schultz reports.</t>
         </is>
       </c>
     </row>
@@ -50400,27 +50404,27 @@
       </c>
       <c r="B763" s="4" t="inlineStr">
         <is>
-          <t>Calvin Ridley</t>
+          <t>Kalel Mullings</t>
         </is>
       </c>
       <c r="C763" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D763" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E763" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F763" s="4" t="inlineStr">
         <is>
-          <t>Ridley caught his only target for 18 yards in Thursday's preseason win over San Francisco.</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -50432,27 +50436,27 @@
       </c>
       <c r="B764" s="5" t="inlineStr">
         <is>
-          <t>Nicholas Singleton</t>
+          <t>Jaylen Harrell</t>
         </is>
       </c>
       <c r="C764" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D764" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E764" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F764" s="5" t="inlineStr">
         <is>
-          <t>Singleton rushed eight times for 31 yards in the Titans' 19-13 preseason win over the 49ers on Thursday.</t>
+          <t>ir</t>
         </is>
       </c>
     </row>
@@ -50464,27 +50468,27 @@
       </c>
       <c r="B765" s="4" t="inlineStr">
         <is>
-          <t>Tyjae Spears</t>
+          <t>Jaren Kanak</t>
         </is>
       </c>
       <c r="C765" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D765" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E765" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F765" s="4" t="inlineStr">
         <is>
-          <t>Spears rushed four times for 35 yards and brought in his only target for four yards in the Titans' 19-13 preseason win over the 49ers on Thursday.</t>
+          <t>ir</t>
         </is>
       </c>
     </row>
@@ -50496,7 +50500,7 @@
       </c>
       <c r="B766" s="5" t="inlineStr">
         <is>
-          <t>Wan'Dale Robinson</t>
+          <t>Calvin Ridley</t>
         </is>
       </c>
       <c r="C766" s="5" t="inlineStr">
@@ -50516,7 +50520,7 @@
       </c>
       <c r="F766" s="5" t="inlineStr">
         <is>
-          <t>Robinson brought in two of four targets for 19 yards in the Titans' 19-13 preseason win over the 49ers on Thursday.</t>
+          <t>Ridley caught his only target for 18 yards in Thursday's preseason win over San Francisco.</t>
         </is>
       </c>
     </row>
@@ -50528,12 +50532,12 @@
       </c>
       <c r="B767" s="4" t="inlineStr">
         <is>
-          <t>Gunnar Helm</t>
+          <t>Nicholas Singleton</t>
         </is>
       </c>
       <c r="C767" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D767" s="4" t="inlineStr">
@@ -50548,7 +50552,7 @@
       </c>
       <c r="F767" s="4" t="inlineStr">
         <is>
-          <t>Helm brought in his only target for 16 yards in the Titans' 19-13 preseason win over the 49ers on Thursday.</t>
+          <t>Singleton rushed eight times for 31 yards in the Titans' 19-13 preseason win over the 49ers on Thursday.</t>
         </is>
       </c>
     </row>
@@ -50560,12 +50564,12 @@
       </c>
       <c r="B768" s="5" t="inlineStr">
         <is>
-          <t>Cam Ward</t>
+          <t>Wan'Dale Robinson</t>
         </is>
       </c>
       <c r="C768" s="5" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D768" s="5" t="inlineStr">
@@ -50580,7 +50584,7 @@
       </c>
       <c r="F768" s="5" t="inlineStr">
         <is>
-          <t>Ward completed five of 12 targets for 57 yards with no touchdowns or interceptions and rushed once for two yards in the Titans' 19-13 preseason win over the 49ers on Thursday.</t>
+          <t>Robinson brought in two of four targets for 19 yards in the Titans' 19-13 preseason win over the 49ers on Thursday.</t>
         </is>
       </c>
     </row>
@@ -50592,12 +50596,12 @@
       </c>
       <c r="B769" s="4" t="inlineStr">
         <is>
-          <t>Elic Ayomanor</t>
+          <t>Gunnar Helm</t>
         </is>
       </c>
       <c r="C769" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D769" s="4" t="inlineStr">
@@ -50612,7 +50616,7 @@
       </c>
       <c r="F769" s="4" t="inlineStr">
         <is>
-          <t>Ayomanor (shoulder) is practicing Friday, Turron Davenport of ESPN.com reports.</t>
+          <t>Helm brought in his only target for 16 yards in the Titans' 19-13 preseason win over the 49ers on Thursday.</t>
         </is>
       </c>
     </row>
@@ -50624,12 +50628,12 @@
       </c>
       <c r="B770" s="5" t="inlineStr">
         <is>
-          <t>Mario Goodrich III</t>
+          <t>Elic Ayomanor</t>
         </is>
       </c>
       <c r="C770" s="5" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D770" s="5" t="inlineStr">
@@ -50644,7 +50648,7 @@
       </c>
       <c r="F770" s="5" t="inlineStr">
         <is>
-          <t>The Titans signed Goodrich to a contract Saturday, Jim Wyatt of the team's official site reports.</t>
+          <t>Ayomanor (shoulder) is practicing Friday, Turron Davenport of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -50656,27 +50660,27 @@
       </c>
       <c r="B771" s="4" t="inlineStr">
         <is>
-          <t>Sanoussi Kane</t>
+          <t>Mario Goodrich III</t>
         </is>
       </c>
       <c r="C771" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D771" s="4" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E771" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F771" s="4" t="inlineStr">
         <is>
-          <t>Kane (undisclosed) reverted to the Titans' injured reserve Friday, per the NFL's transaction log.</t>
+          <t>The Titans signed Goodrich to a contract Saturday, Jim Wyatt of the team's official site reports.</t>
         </is>
       </c>
     </row>
@@ -50688,27 +50692,27 @@
       </c>
       <c r="B772" s="5" t="inlineStr">
         <is>
-          <t>Marcus Harris</t>
+          <t>Sanoussi Kane</t>
         </is>
       </c>
       <c r="C772" s="5" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D772" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E772" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F772" s="5" t="inlineStr">
         <is>
-          <t>Harris (knee) has been participating fully in training camp practices, Jim Wyatt of the Titans' official site reports.</t>
+          <t>Kane (undisclosed) reverted to the Titans' injured reserve Friday, per the NFL's transaction log.</t>
         </is>
       </c>
     </row>
@@ -50720,12 +50724,12 @@
       </c>
       <c r="B773" s="4" t="inlineStr">
         <is>
-          <t>Jeffery Simmons</t>
+          <t>Marcus Harris</t>
         </is>
       </c>
       <c r="C773" s="4" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D773" s="4" t="inlineStr">
@@ -50740,7 +50744,7 @@
       </c>
       <c r="F773" s="4" t="inlineStr">
         <is>
-          <t>Simmons (elbow) is participating at the Titans' training camp, George Walker of the Kingsport Times News reports.</t>
+          <t>Harris (knee) has been participating fully in training camp practices, Jim Wyatt of the Titans' official site reports.</t>
         </is>
       </c>
     </row>
@@ -50752,12 +50756,12 @@
       </c>
       <c r="B774" s="5" t="inlineStr">
         <is>
-          <t>JC Latham</t>
+          <t>Jeffery Simmons</t>
         </is>
       </c>
       <c r="C774" s="5" t="inlineStr">
         <is>
-          <t>OT</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="D774" s="5" t="inlineStr">
@@ -50772,7 +50776,7 @@
       </c>
       <c r="F774" s="5" t="inlineStr">
         <is>
-          <t>Tennessee took Latham (undisclosed) off its active/PUP list Thursday, Buck Reising of WGFX-FM reports.</t>
+          <t>Simmons (elbow) is participating at the Titans' training camp, George Walker of the Kingsport Times News reports.</t>
         </is>
       </c>
     </row>
@@ -50784,12 +50788,12 @@
       </c>
       <c r="B775" s="4" t="inlineStr">
         <is>
-          <t>Oluwafemi Oladejo</t>
+          <t>JC Latham</t>
         </is>
       </c>
       <c r="C775" s="4" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>OT</t>
         </is>
       </c>
       <c r="D775" s="4" t="inlineStr">
@@ -50804,7 +50808,7 @@
       </c>
       <c r="F775" s="4" t="inlineStr">
         <is>
-          <t>Oladejo (hamstring) passed his conditioning test and is participating in the Titans' training camp activities, Jim Wyatt of the team's official site reports.</t>
+          <t>Tennessee took Latham (undisclosed) off its active/PUP list Thursday, Buck Reising of WGFX-FM reports.</t>
         </is>
       </c>
     </row>
@@ -50816,12 +50820,12 @@
       </c>
       <c r="B776" s="5" t="inlineStr">
         <is>
-          <t>Will Levis</t>
+          <t>Oluwafemi Oladejo</t>
         </is>
       </c>
       <c r="C776" s="5" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D776" s="5" t="inlineStr">
@@ -50836,7 +50840,7 @@
       </c>
       <c r="F776" s="5" t="inlineStr">
         <is>
-          <t>Levis is set to compete with Mitchell Trubisky for the backup quarterback role, Turron Davenport of ESPN.com reports.</t>
+          <t>Oladejo (hamstring) passed his conditioning test and is participating in the Titans' training camp activities, Jim Wyatt of the team's official site reports.</t>
         </is>
       </c>
     </row>
@@ -50848,12 +50852,12 @@
       </c>
       <c r="B777" s="4" t="inlineStr">
         <is>
-          <t>Amani Hooker</t>
+          <t>Will Levis</t>
         </is>
       </c>
       <c r="C777" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D777" s="4" t="inlineStr">
@@ -50868,7 +50872,7 @@
       </c>
       <c r="F777" s="4" t="inlineStr">
         <is>
-          <t>The Titans activated Hooker (undisclosed) from the active/PUP list Tuesday, Jim Wyatt of the team's official site reports.</t>
+          <t>Levis is set to compete with Mitchell Trubisky for the backup quarterback role, Turron Davenport of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -50880,12 +50884,12 @@
       </c>
       <c r="B778" s="5" t="inlineStr">
         <is>
-          <t>Michael Carter</t>
+          <t>Amani Hooker</t>
         </is>
       </c>
       <c r="C778" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D778" s="5" t="inlineStr">
@@ -50900,7 +50904,7 @@
       </c>
       <c r="F778" s="5" t="inlineStr">
         <is>
-          <t>Carter will enter training camp competing for a depth role in Tennessee's backfield, Mark Mihalko of USA Today reports.</t>
+          <t>The Titans activated Hooker (undisclosed) from the active/PUP list Tuesday, Jim Wyatt of the team's official site reports.</t>
         </is>
       </c>
     </row>
@@ -50912,12 +50916,12 @@
       </c>
       <c r="B779" s="4" t="inlineStr">
         <is>
-          <t>Chimere Dike</t>
+          <t>Michael Carter</t>
         </is>
       </c>
       <c r="C779" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D779" s="4" t="inlineStr">
@@ -50932,7 +50936,7 @@
       </c>
       <c r="F779" s="4" t="inlineStr">
         <is>
-          <t>As the coming season approaches, Nick Suss of the Nashville Tennessean projects that Dike is in line to compete for a rotational role in the Titans' re-tooled WR corps.</t>
+          <t>Carter will enter training camp competing for a depth role in Tennessee's backfield, Mark Mihalko of USA Today reports.</t>
         </is>
       </c>
     </row>
@@ -51832,26 +51836,30 @@
         </is>
       </c>
       <c r="D5" s="15" t="n">
-        <v>71.8</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>5.8</v>
+        <v>7.1</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>10.1</v>
+        <v>19.7</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>31</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Overcast</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="I5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr"/>
+        <v>-0.8</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>Wind 7 mph (gusts 20)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -51870,20 +51878,20 @@
         </is>
       </c>
       <c r="D6" s="17" t="n">
-        <v>75.09999999999999</v>
+        <v>70.3</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>2.6</v>
+        <v>11.3</v>
       </c>
       <c r="F6" s="17" t="n">
-        <v>2.7</v>
+        <v>13.2</v>
       </c>
       <c r="G6" s="17" t="n">
         <v>16</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>Mainly clear</t>
+          <t>Drizzle</t>
         </is>
       </c>
       <c r="I6" s="24" t="n">
@@ -51908,13 +51916,13 @@
         </is>
       </c>
       <c r="D7" s="15" t="n">
-        <v>108.3</v>
+        <v>107.6</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>16.9</v>
+        <v>22</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>15.4</v>
+        <v>21.7</v>
       </c>
       <c r="G7" s="15" t="n">
         <v>0</v>
@@ -51950,10 +51958,10 @@
         </is>
       </c>
       <c r="D8" s="17" t="n">
-        <v>79</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>8.6</v>
+        <v>7.5</v>
       </c>
       <c r="F8" s="17" t="n">
         <v>6.7</v>
@@ -51963,7 +51971,7 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>Partly cloudy</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="I8" s="24" t="n">
@@ -51988,20 +51996,20 @@
         </is>
       </c>
       <c r="D9" s="15" t="n">
-        <v>82</v>
+        <v>86.3</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>9.800000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="G9" s="15" t="n">
         <v>22</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Thunderstorm</t>
+          <t>Overcast</t>
         </is>
       </c>
       <c r="I9" s="9" t="n">
@@ -52026,13 +52034,13 @@
         </is>
       </c>
       <c r="D10" s="17" t="n">
-        <v>88.8</v>
+        <v>89.2</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>11.6</v>
+        <v>5.7</v>
       </c>
       <c r="F10" s="17" t="n">
-        <v>12.3</v>
+        <v>5.8</v>
       </c>
       <c r="G10" s="17" t="n">
         <v>33</v>
@@ -52064,13 +52072,13 @@
         </is>
       </c>
       <c r="D11" s="15" t="n">
-        <v>83.09999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>5.9</v>
+        <v>4</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>11.9</v>
+        <v>13</v>
       </c>
       <c r="G11" s="15" t="n">
         <v>50</v>
@@ -52102,10 +52110,10 @@
         </is>
       </c>
       <c r="D12" s="17" t="n">
-        <v>83.2</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="F12" s="17" t="n">
         <v>9.4</v>
@@ -52115,7 +52123,7 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>Mainly clear</t>
+          <t>Overcast</t>
         </is>
       </c>
       <c r="I12" s="24" t="n">
@@ -52140,30 +52148,26 @@
         </is>
       </c>
       <c r="D13" s="15" t="n">
-        <v>88.5</v>
+        <v>87.8</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>12.4</v>
+        <v>10.2</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>17</v>
+        <v>14.3</v>
       </c>
       <c r="G13" s="15" t="n">
         <v>52</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Partly cloudy</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>Wind 12 mph (gusts 17)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -52182,20 +52186,20 @@
         </is>
       </c>
       <c r="D14" s="17" t="n">
-        <v>82</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="F14" s="17" t="n">
-        <v>6.9</v>
+        <v>11</v>
       </c>
       <c r="G14" s="17" t="n">
         <v>30</v>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Overcast</t>
         </is>
       </c>
       <c r="I14" s="24" t="n">
@@ -52220,20 +52224,20 @@
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>92.5</v>
+        <v>93.2</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>11.3</v>
+        <v>9.4</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>19</v>
+        <v>18.3</v>
       </c>
       <c r="G15" s="15" t="n">
         <v>4</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Mainly clear</t>
+          <t>Overcast</t>
         </is>
       </c>
       <c r="I15" s="9" t="n">
@@ -52241,7 +52245,7 @@
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>Wind 11 mph (gusts 19) · 92°F</t>
+          <t>Wind 9 mph (gusts 18) · 93°F</t>
         </is>
       </c>
     </row>
@@ -52262,20 +52266,20 @@
         </is>
       </c>
       <c r="D16" s="17" t="n">
-        <v>105.9</v>
+        <v>102.3</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>6</v>
+        <v>10.2</v>
       </c>
       <c r="F16" s="17" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="G16" s="17" t="n">
         <v>2</v>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Mainly clear</t>
         </is>
       </c>
       <c r="I16" s="24" t="n">
@@ -52283,7 +52287,7 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>106°F · retractable roof — effect halved</t>
+          <t>102°F · retractable roof — effect halved</t>
         </is>
       </c>
     </row>
@@ -52304,13 +52308,13 @@
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>64.59999999999999</v>
+        <v>68</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>13</v>
+        <v>12.1</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>20.1</v>
+        <v>18.3</v>
       </c>
       <c r="G17" s="15" t="n">
         <v>2</v>
@@ -52325,7 +52329,7 @@
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>Wind 13 mph (gusts 20)</t>
+          <t>Wind 12 mph (gusts 18)</t>
         </is>
       </c>
     </row>
@@ -52346,26 +52350,30 @@
         </is>
       </c>
       <c r="D18" s="17" t="n">
-        <v>81.3</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>10.9</v>
+        <v>14.3</v>
       </c>
       <c r="F18" s="17" t="n">
-        <v>12.8</v>
+        <v>17.7</v>
       </c>
       <c r="G18" s="17" t="n">
         <v>18</v>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>Partly cloudy</t>
+          <t>Overcast</t>
         </is>
       </c>
       <c r="I18" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="5" t="inlineStr"/>
+        <v>-0.8</v>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>Wind 14 mph (gusts 18)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -52384,13 +52392,13 @@
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>79.59999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>3.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>6.5</v>
+        <v>12.3</v>
       </c>
       <c r="G19" s="15" t="n">
         <v>2</v>
@@ -52422,26 +52430,30 @@
         </is>
       </c>
       <c r="D20" s="17" t="n">
-        <v>91.3</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F20" s="17" t="n">
-        <v>7.2</v>
+        <v>3.6</v>
       </c>
       <c r="G20" s="17" t="n">
         <v>1</v>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>Mainly clear</t>
+          <t>Partly cloudy</t>
         </is>
       </c>
       <c r="I20" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="5" t="inlineStr"/>
+        <v>-0.5</v>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>94°F</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">

--- a/NFL_Edge_Model.xlsx
+++ b/NFL_Edge_Model.xlsx
@@ -692,7 +692,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Snapshot of the live model, generated 2026-08-24T08:03:54+00:00. Read-only: the model runs in the pipeline, not in this file.</t>
+          <t>Snapshot of the live model, generated 2026-08-24T14:25:16+00:00. Read-only: the model runs in the pipeline, not in this file.</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>2026-08-24T08:03:54+00:00</t>
+          <t>2026-08-24T14:25:16+00:00</t>
         </is>
       </c>
     </row>
@@ -2779,16 +2779,16 @@
         <v>154</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.4133</v>
+        <v>0.4178</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>0.3937</v>
       </c>
       <c r="H10" s="13" t="n">
-        <v>0.0188</v>
+        <v>0.0227</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>0.04928467578930995</v>
+        <v>0.06065052683172301</v>
       </c>
       <c r="J10" s="14" t="n">
         <v>0.5</v>
@@ -2967,33 +2967,33 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>CLE @ JAX</t>
+          <t>NE @ SEA</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Over 40.5</t>
+          <t>NE +3.5</t>
         </is>
       </c>
       <c r="E15" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>0.5405</v>
+        <v>0.5415</v>
       </c>
       <c r="G15" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>0.0162</v>
+        <v>0.0171</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>0.03192423886530243</v>
+        <v>0.0336946163134072</v>
       </c>
       <c r="J15" s="10" t="n">
         <v>0.5</v>
@@ -3008,33 +3008,33 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>CHI @ CAR</t>
+          <t>CLE @ JAX</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>CAR ML</t>
+          <t>Over 40.5</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>124</v>
+        <v>-110</v>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.4611</v>
+        <v>0.5405</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>0.4464</v>
+        <v>0.5238</v>
       </c>
       <c r="H16" s="13" t="n">
-        <v>0.0143</v>
+        <v>0.0162</v>
       </c>
       <c r="I16" s="13" t="n">
-        <v>0.0325138851490685</v>
+        <v>0.03192423886530243</v>
       </c>
       <c r="J16" s="14" t="n">
         <v>0.5</v>
@@ -3049,33 +3049,33 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>ATL @ PIT</t>
+          <t>CHI @ CAR</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Over 42.5</t>
+          <t>CAR ML</t>
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>-105</v>
+        <v>124</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>0.5266999999999999</v>
+        <v>0.4611</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.4464</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>0.0141</v>
+        <v>0.0143</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>0.02824070440763249</v>
+        <v>0.0325138851490685</v>
       </c>
       <c r="J17" s="10" t="n">
         <v>0.5</v>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>MIA @ LV</t>
+          <t>ATL @ PIT</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -3100,23 +3100,23 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Over 40.5</t>
+          <t>Over 42.5</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.538</v>
+        <v>0.5266999999999999</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5122</v>
       </c>
       <c r="H18" s="13" t="n">
-        <v>0.0139</v>
+        <v>0.0141</v>
       </c>
       <c r="I18" s="13" t="n">
-        <v>0.02712503029680507</v>
+        <v>0.02824070440763249</v>
       </c>
       <c r="J18" s="14" t="n">
         <v>0.5</v>
@@ -3131,33 +3131,33 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>NE @ SEA</t>
+          <t>MIA @ LV</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>NE +3.5</t>
+          <t>Over 40.5</t>
         </is>
       </c>
       <c r="E19" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>0.537</v>
+        <v>0.538</v>
       </c>
       <c r="G19" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>0.013</v>
+        <v>0.0139</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>0.0252193678819661</v>
+        <v>0.02712503029680507</v>
       </c>
       <c r="J19" s="10" t="n">
         <v>0.5</v>
@@ -3476,16 +3476,16 @@
         <v>170</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>0.3741</v>
+        <v>0.3738</v>
       </c>
       <c r="G27" s="8" t="n">
         <v>0.3704</v>
       </c>
       <c r="H27" s="8" t="n">
-        <v>0.0037</v>
+        <v>0.0034</v>
       </c>
       <c r="I27" s="8" t="n">
-        <v>0.01004562953541044</v>
+        <v>0.009105696963362275</v>
       </c>
       <c r="J27" s="10" t="n">
         <v>0.5</v>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>WSH @ PHI</t>
+          <t>BAL @ IND</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -3551,23 +3551,23 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>WSH +4.5</t>
+          <t>IND +3.5</t>
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>0.5265</v>
+        <v>0.5309</v>
       </c>
       <c r="G29" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5283</v>
       </c>
       <c r="H29" s="8" t="n">
-        <v>0.0027</v>
+        <v>0.0026</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>0.005078033170534846</v>
+        <v>0.004861104802833471</v>
       </c>
       <c r="J29" s="10" t="n">
         <v>0.5</v>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>BAL @ IND</t>
+          <t>WSH @ PHI</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -3592,23 +3592,23 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>IND +3.5</t>
+          <t>WSH +4.5</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.5309</v>
+        <v>0.5261</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>0.5283</v>
+        <v>0.5238</v>
       </c>
       <c r="H30" s="13" t="n">
-        <v>0.0026</v>
+        <v>0.0023</v>
       </c>
       <c r="I30" s="13" t="n">
-        <v>0.004861104802833471</v>
+        <v>0.004391528631370045</v>
       </c>
       <c r="J30" s="14" t="n">
         <v>0.5</v>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>DEN @ KC</t>
+          <t>NE @ SEA</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Under 42.5</t>
+          <t>Under 44.5</t>
         </is>
       </c>
       <c r="E31" s="7" t="n">
@@ -3649,7 +3649,7 @@
         <v>-0.001</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>-0.001823242235343747</v>
+        <v>-0.001817132797922338</v>
       </c>
       <c r="J31" s="10" t="n">
         <v>0.5</v>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>NE @ SEA</t>
+          <t>DEN @ KC</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -3674,23 +3674,23 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Under 44.5</t>
+          <t>Under 42.5</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.5203</v>
+        <v>0.5229</v>
       </c>
       <c r="G32" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H32" s="13" t="n">
-        <v>-0.0035</v>
+        <v>-0.001</v>
       </c>
       <c r="I32" s="13" t="n">
-        <v>-0.00665550171248247</v>
+        <v>-0.001823242235343747</v>
       </c>
       <c r="J32" s="14" t="n">
         <v>0.5</v>
@@ -4132,16 +4132,16 @@
         <v>124</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>0.4304</v>
+        <v>0.4306</v>
       </c>
       <c r="G43" s="8" t="n">
         <v>0.4464</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>-0.0156</v>
+        <v>-0.0154</v>
       </c>
       <c r="I43" s="8" t="n">
-        <v>-0.03563281766189008</v>
+        <v>-0.03523243596438208</v>
       </c>
       <c r="J43" s="10" t="n">
         <v>0.5</v>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>DAL @ NYG</t>
+          <t>BUF @ HOU</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -4371,23 +4371,23 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>DAL -2.5</t>
+          <t>HOU +1.5</t>
         </is>
       </c>
       <c r="E49" s="7" t="n">
         <v>-115</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>0.5141</v>
+        <v>0.5139</v>
       </c>
       <c r="G49" s="8" t="n">
         <v>0.5349</v>
       </c>
       <c r="H49" s="8" t="n">
-        <v>-0.0199</v>
+        <v>-0.02</v>
       </c>
       <c r="I49" s="8" t="n">
-        <v>-0.03886992500392589</v>
+        <v>-0.03923258924631812</v>
       </c>
       <c r="J49" s="10" t="n">
         <v>0.5</v>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>BUF @ HOU</t>
+          <t>DAL @ NYG</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>HOU +1.5</t>
+          <t>DAL -2.5</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
@@ -4428,7 +4428,7 @@
         <v>-0.02</v>
       </c>
       <c r="I50" s="13" t="n">
-        <v>-0.03923258924631812</v>
+        <v>-0.0392070114276778</v>
       </c>
       <c r="J50" s="14" t="n">
         <v>0.5</v>
@@ -4706,16 +4706,16 @@
         <v>-105</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>0.4859</v>
+        <v>0.4861</v>
       </c>
       <c r="G57" s="8" t="n">
         <v>0.5122</v>
       </c>
       <c r="H57" s="8" t="n">
-        <v>-0.0245</v>
+        <v>-0.0243</v>
       </c>
       <c r="I57" s="8" t="n">
-        <v>-0.0513240982517143</v>
+        <v>-0.05097207998194903</v>
       </c>
       <c r="J57" s="10" t="n">
         <v>0.5</v>
@@ -4788,16 +4788,16 @@
         <v>-148</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>0.5696</v>
+        <v>0.5694</v>
       </c>
       <c r="G59" s="8" t="n">
         <v>0.5968</v>
       </c>
       <c r="H59" s="8" t="n">
-        <v>-0.0251</v>
+        <v>-0.0253</v>
       </c>
       <c r="I59" s="8" t="n">
-        <v>-0.04509709345712926</v>
+        <v>-0.04539652946240208</v>
       </c>
       <c r="J59" s="10" t="n">
         <v>0.5</v>
@@ -5345,33 +5345,33 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>NE @ SEA</t>
+          <t>MIA @ LV</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Over 44.5</t>
+          <t>LV ML</t>
         </is>
       </c>
       <c r="E73" s="7" t="n">
-        <v>-110</v>
+        <v>-205</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>0.4797</v>
+        <v>0.6269</v>
       </c>
       <c r="G73" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.6721</v>
       </c>
       <c r="H73" s="8" t="n">
-        <v>-0.0366</v>
+        <v>-0.0372</v>
       </c>
       <c r="I73" s="8" t="n">
-        <v>-0.08425358919660841</v>
+        <v>-0.06667280051647667</v>
       </c>
       <c r="J73" s="10" t="n">
         <v>0.5</v>
@@ -5386,7 +5386,7 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>MIA @ LV</t>
+          <t>WSH @ PHI</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
@@ -5396,23 +5396,23 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>LV ML</t>
+          <t>PHI ML</t>
         </is>
       </c>
       <c r="E74" s="12" t="n">
         <v>-205</v>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.6269</v>
+        <v>0.6262</v>
       </c>
       <c r="G74" s="13" t="n">
         <v>0.6721</v>
       </c>
       <c r="H74" s="13" t="n">
-        <v>-0.0372</v>
+        <v>-0.0376</v>
       </c>
       <c r="I74" s="13" t="n">
-        <v>-0.06667280051647667</v>
+        <v>-0.06770763182517281</v>
       </c>
       <c r="J74" s="14" t="n">
         <v>0.5</v>
@@ -5427,33 +5427,33 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>WSH @ PHI</t>
+          <t>NE @ SEA</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>PHI ML</t>
+          <t>Over 44.5</t>
         </is>
       </c>
       <c r="E75" s="7" t="n">
-        <v>-205</v>
+        <v>-110</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>0.6259</v>
+        <v>0.4771</v>
       </c>
       <c r="G75" s="8" t="n">
-        <v>0.6721</v>
+        <v>0.5238</v>
       </c>
       <c r="H75" s="8" t="n">
-        <v>-0.0377</v>
+        <v>-0.038</v>
       </c>
       <c r="I75" s="8" t="n">
-        <v>-0.06822534515899709</v>
+        <v>-0.08909195811116855</v>
       </c>
       <c r="J75" s="10" t="n">
         <v>0.5</v>
@@ -5509,7 +5509,7 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>BAL @ IND</t>
+          <t>WSH @ PHI</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -5519,23 +5519,23 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>BAL -3.5</t>
+          <t>PHI -4.5</t>
         </is>
       </c>
       <c r="E77" s="7" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>0.4691</v>
+        <v>0.4739</v>
       </c>
       <c r="G77" s="8" t="n">
-        <v>0.5192</v>
+        <v>0.5238</v>
       </c>
       <c r="H77" s="8" t="n">
-        <v>-0.0397</v>
+        <v>-0.0396</v>
       </c>
       <c r="I77" s="8" t="n">
-        <v>-0.09649040432769079</v>
+        <v>-0.09530061954046082</v>
       </c>
       <c r="J77" s="10" t="n">
         <v>0.5</v>
@@ -5550,33 +5550,33 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>SF @ LAR</t>
+          <t>BAL @ IND</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>LAR ML</t>
+          <t>BAL -3.5</t>
         </is>
       </c>
       <c r="E78" s="12" t="n">
-        <v>-192</v>
+        <v>-108</v>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.6073</v>
+        <v>0.4691</v>
       </c>
       <c r="G78" s="13" t="n">
-        <v>0.6575</v>
+        <v>0.5192</v>
       </c>
       <c r="H78" s="13" t="n">
-        <v>-0.0398</v>
+        <v>-0.0397</v>
       </c>
       <c r="I78" s="13" t="n">
-        <v>-0.07579738296532001</v>
+        <v>-0.09649040432769079</v>
       </c>
       <c r="J78" s="14" t="n">
         <v>0.5</v>
@@ -5591,33 +5591,33 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>WSH @ PHI</t>
+          <t>SF @ LAR</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>PHI -4.5</t>
+          <t>LAR ML</t>
         </is>
       </c>
       <c r="E79" s="7" t="n">
-        <v>-110</v>
+        <v>-192</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>0.4735</v>
+        <v>0.6073</v>
       </c>
       <c r="G79" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.6575</v>
       </c>
       <c r="H79" s="8" t="n">
         <v>-0.0398</v>
       </c>
       <c r="I79" s="8" t="n">
-        <v>-0.09598712407962567</v>
+        <v>-0.07579738296532001</v>
       </c>
       <c r="J79" s="10" t="n">
         <v>0.5</v>
@@ -5919,33 +5919,33 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>NE @ SEA</t>
+          <t>ATL @ PIT</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>SEA -3.5</t>
+          <t>Under 42.5</t>
         </is>
       </c>
       <c r="E87" s="7" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>0.463</v>
+        <v>0.4733</v>
       </c>
       <c r="G87" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5349</v>
       </c>
       <c r="H87" s="8" t="n">
-        <v>-0.0441</v>
+        <v>-0.0444</v>
       </c>
       <c r="I87" s="8" t="n">
-        <v>-0.1161284587910569</v>
+        <v>-0.1150597625451667</v>
       </c>
       <c r="J87" s="10" t="n">
         <v>0.5</v>
@@ -5960,38 +5960,42 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>ATL @ PIT</t>
+          <t>ARI @ LAC</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>Under 42.5</t>
+          <t>LAC ML</t>
         </is>
       </c>
       <c r="E88" s="12" t="n">
-        <v>-115</v>
+        <v>-575</v>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.4733</v>
+        <v>0.7902</v>
       </c>
       <c r="G88" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.8519</v>
       </c>
       <c r="H88" s="13" t="n">
-        <v>-0.0444</v>
+        <v>-0.0445</v>
       </c>
       <c r="I88" s="13" t="n">
-        <v>-0.1150597625451667</v>
+        <v>-0.07194112640748435</v>
       </c>
       <c r="J88" s="14" t="n">
         <v>0.5</v>
       </c>
-      <c r="K88" s="5" t="inlineStr"/>
+      <c r="K88" s="5" t="inlineStr">
+        <is>
+          <t>price -575 outside the allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
@@ -6001,42 +6005,38 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>ARI @ LAC</t>
+          <t>MIA @ LV</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>LAC ML</t>
+          <t>Under 40.5</t>
         </is>
       </c>
       <c r="E89" s="7" t="n">
-        <v>-575</v>
+        <v>-110</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>0.7902</v>
+        <v>0.462</v>
       </c>
       <c r="G89" s="8" t="n">
-        <v>0.8519</v>
+        <v>0.5238</v>
       </c>
       <c r="H89" s="8" t="n">
         <v>-0.0445</v>
       </c>
       <c r="I89" s="8" t="n">
-        <v>-0.07194112640748435</v>
+        <v>-0.1180341212058959</v>
       </c>
       <c r="J89" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="K89" s="4" t="inlineStr">
-        <is>
-          <t>price -575 outside the allowed range</t>
-        </is>
-      </c>
+      <c r="K89" s="4" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>MIA @ LV</t>
+          <t>CLE @ JAX</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
@@ -6063,16 +6063,16 @@
         <v>-110</v>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.462</v>
+        <v>0.4595</v>
       </c>
       <c r="G90" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H90" s="13" t="n">
-        <v>-0.0445</v>
+        <v>-0.0453</v>
       </c>
       <c r="I90" s="13" t="n">
-        <v>-0.1180341212058959</v>
+        <v>-0.1228333297743933</v>
       </c>
       <c r="J90" s="14" t="n">
         <v>0.5</v>
@@ -6092,28 +6092,28 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>SEA ML</t>
+          <t>SEA -3.5</t>
         </is>
       </c>
       <c r="E91" s="7" t="n">
-        <v>-185</v>
+        <v>-110</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>0.5867</v>
+        <v>0.4585</v>
       </c>
       <c r="G91" s="8" t="n">
-        <v>0.6491</v>
+        <v>0.5238</v>
       </c>
       <c r="H91" s="8" t="n">
-        <v>-0.0447</v>
+        <v>-0.0456</v>
       </c>
       <c r="I91" s="8" t="n">
-        <v>-0.09527897345482961</v>
+        <v>-0.1246037072224981</v>
       </c>
       <c r="J91" s="10" t="n">
         <v>0.5</v>
@@ -6128,33 +6128,33 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>CLE @ JAX</t>
+          <t>ARI @ LAC</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>Under 40.5</t>
+          <t>LAC -10.5</t>
         </is>
       </c>
       <c r="E92" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.4595</v>
+        <v>0.4576</v>
       </c>
       <c r="G92" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H92" s="13" t="n">
-        <v>-0.0453</v>
+        <v>-0.0459</v>
       </c>
       <c r="I92" s="13" t="n">
-        <v>-0.1228333297743933</v>
+        <v>-0.1263306720701867</v>
       </c>
       <c r="J92" s="14" t="n">
         <v>0.5</v>
@@ -6169,33 +6169,33 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>ARI @ LAC</t>
+          <t>NE @ SEA</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>LAC -10.5</t>
+          <t>SEA ML</t>
         </is>
       </c>
       <c r="E93" s="7" t="n">
-        <v>-110</v>
+        <v>-185</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>0.4576</v>
+        <v>0.5822000000000001</v>
       </c>
       <c r="G93" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.6491</v>
       </c>
       <c r="H93" s="8" t="n">
-        <v>-0.0459</v>
+        <v>-0.0461</v>
       </c>
       <c r="I93" s="8" t="n">
-        <v>-0.1263306720701867</v>
+        <v>-0.1021708430092774</v>
       </c>
       <c r="J93" s="10" t="n">
         <v>0.5</v>
@@ -7328,7 +7328,7 @@
         </is>
       </c>
       <c r="D9" s="24" t="n">
-        <v>-2.44</v>
+        <v>-2.43</v>
       </c>
       <c r="E9" s="24" t="n">
         <v>2.5</v>
@@ -7464,7 +7464,7 @@
         </is>
       </c>
       <c r="D13" s="24" t="n">
-        <v>4.17</v>
+        <v>4.19</v>
       </c>
       <c r="E13" s="24" t="n">
         <v>-4.5</v>
@@ -7804,13 +7804,13 @@
         </is>
       </c>
       <c r="D23" s="24" t="n">
-        <v>2.41</v>
+        <v>2.16</v>
       </c>
       <c r="E23" s="24" t="n">
         <v>-3.5</v>
       </c>
       <c r="F23" s="25" t="n">
-        <v>43.7</v>
+        <v>43.6</v>
       </c>
       <c r="G23" s="25" t="n">
         <v>44.5</v>
@@ -8681,7 +8681,7 @@
         <v>0</v>
       </c>
       <c r="D26" s="18" t="n">
-        <v>-0.8</v>
+        <v>-0.83</v>
       </c>
       <c r="E26" s="18" t="n">
         <v>-0.8100000000000001</v>
@@ -8713,7 +8713,7 @@
         <v>0</v>
       </c>
       <c r="D27" s="16" t="n">
-        <v>-1.39</v>
+        <v>-1.36</v>
       </c>
       <c r="E27" s="16" t="n">
         <v>0.02</v>
@@ -8809,7 +8809,7 @@
         <v>0</v>
       </c>
       <c r="D30" s="18" t="n">
-        <v>-2.31</v>
+        <v>-2.32</v>
       </c>
       <c r="E30" s="18" t="n">
         <v>-0.52</v>
@@ -8905,7 +8905,7 @@
         <v>0</v>
       </c>
       <c r="D33" s="16" t="n">
-        <v>-3.24</v>
+        <v>-3.23</v>
       </c>
       <c r="E33" s="16" t="n">
         <v>-2.1</v>
@@ -14030,10 +14030,10 @@
         <v>45.5</v>
       </c>
       <c r="I104" s="12" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="J104" s="12" t="n">
-        <v>-325</v>
+        <v>-310</v>
       </c>
       <c r="K104" s="17" t="n">
         <v>0</v>
@@ -15190,7 +15190,7 @@
         </is>
       </c>
       <c r="G126" s="24" t="n">
-        <v>-2.5</v>
+        <v>-1.5</v>
       </c>
       <c r="H126" s="25" t="n">
         <v>48.5</v>
@@ -15832,10 +15832,10 @@
         <v>44.5</v>
       </c>
       <c r="I138" s="12" t="n">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="J138" s="12" t="n">
-        <v>-142</v>
+        <v>-135</v>
       </c>
       <c r="K138" s="17" t="n">
         <v>0</v>
@@ -18588,10 +18588,10 @@
         <v>47.5</v>
       </c>
       <c r="I190" s="12" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="J190" s="12" t="n">
-        <v>-125</v>
+        <v>-122</v>
       </c>
       <c r="K190" s="17" t="n">
         <v>0</v>
@@ -24047,10 +24047,10 @@
         <v>49.5</v>
       </c>
       <c r="I293" s="7" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="J293" s="7" t="n">
-        <v>-218</v>
+        <v>-205</v>
       </c>
       <c r="K293" s="15" t="n">
         <v>0</v>
@@ -25478,10 +25478,10 @@
         <v>41.5</v>
       </c>
       <c r="I320" s="12" t="n">
-        <v>-162</v>
+        <v>-155</v>
       </c>
       <c r="J320" s="12" t="n">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="K320" s="17" t="n">
         <v>0</v>
@@ -31904,7 +31904,7 @@
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>Taylen Green</t>
+          <t>Shedeur Sanders</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
@@ -31924,7 +31924,7 @@
       </c>
       <c r="F180" s="5" t="inlineStr">
         <is>
-          <t>Green is set to play in Thursday night's preseason finale against the Patriots, Mary Kay Cabot of The Cleveland Plain Dealer reports.</t>
+          <t>Sanders will open the season as the Browns' backup quarterback after the team named Deshaun Watson its starter Monday, multiple sources tell NFL reporter Jordan Schultz.</t>
         </is>
       </c>
     </row>
@@ -31936,7 +31936,7 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>Dillon Gabriel</t>
+          <t>Deshaun Watson</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
@@ -31956,7 +31956,7 @@
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>Gabriel will start at quarterback in Thursday's preseason finale against the Patriots, Mary Kay Cabot of The Cleveland Plain Dealer reports.</t>
+          <t>The Browns named Watson their starting quarterback Monday, multiple sources tell NFL reporter Jordan Schultz.</t>
         </is>
       </c>
     </row>
@@ -31968,12 +31968,12 @@
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>Shedeur Sanders</t>
+          <t>Denzel Boston</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D182" s="5" t="inlineStr">
@@ -31988,7 +31988,7 @@
       </c>
       <c r="F182" s="5" t="inlineStr">
         <is>
-          <t>Sanders will learn Monday if he or Deshaun Watson will start at quarterback for the Browns, Jeremy Fowler of ESPN reports.</t>
+          <t>Boston went without a target while playing 11 snaps on offense Saturday in the Browns' 31-7 preseason loss to the Bills.</t>
         </is>
       </c>
     </row>
@@ -32000,7 +32000,7 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Deshaun Watson</t>
+          <t>Taylen Green</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
@@ -32020,7 +32020,7 @@
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>Watson will learn Monday if he or Shedeur Sanders will be named the starting quarterback for the Browns, Jeremy Fowler of ESPN reports.</t>
+          <t>Green is set to play in Thursday night's preseason finale against the Patriots, Mary Kay Cabot of The Cleveland Plain Dealer reports.</t>
         </is>
       </c>
     </row>
@@ -32032,27 +32032,27 @@
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>Alex Wright</t>
+          <t>Dillon Gabriel</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F184" s="5" t="inlineStr">
         <is>
-          <t>The Browns placed Wright on injured reserve Sunday due to a ruptured Achilles, Adam Schefter of ESPN reports.</t>
+          <t>Gabriel will start at quarterback in Thursday's preseason finale against the Patriots, Mary Kay Cabot of The Cleveland Plain Dealer reports.</t>
         </is>
       </c>
     </row>
@@ -32064,7 +32064,7 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>Derek Barnett</t>
+          <t>Alex Wright</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
@@ -32074,17 +32074,17 @@
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E185" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>Barnett and the Browns agreed to a one-year contract worth up to $5.5 million Sunday, Jeremy Fowler of ESPN.com reports.</t>
+          <t>The Browns placed Wright on injured reserve Sunday due to a ruptured Achilles, Adam Schefter of ESPN reports.</t>
         </is>
       </c>
     </row>
@@ -32096,12 +32096,12 @@
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>Isaiah Bond</t>
+          <t>Derek Barnett</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D186" s="5" t="inlineStr">
@@ -32116,7 +32116,7 @@
       </c>
       <c r="F186" s="5" t="inlineStr">
         <is>
-          <t>Bond cleared concussion protocol during Saturday's preseason game against the Bills.</t>
+          <t>Barnett and the Browns agreed to a one-year contract worth up to $5.5 million Sunday, Jeremy Fowler of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -32128,7 +32128,7 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>Jerry Jeudy</t>
+          <t>Isaiah Bond</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
@@ -32148,7 +32148,7 @@
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>Jeudy will not play in the Browns' preseason game against the Bills on Saturday, Daniel Oyefusi of ESPN.com reports.</t>
+          <t>Bond cleared concussion protocol during Saturday's preseason game against the Bills.</t>
         </is>
       </c>
     </row>
@@ -32160,27 +32160,27 @@
       </c>
       <c r="B188" s="5" t="inlineStr">
         <is>
-          <t>Carson Schwesinger</t>
+          <t>Jerry Jeudy</t>
         </is>
       </c>
       <c r="C188" s="5" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D188" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E188" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F188" s="5" t="inlineStr">
         <is>
-          <t>Schwesinger (undisclosed) is not expected to play in Saturday's preseason game against the Bills, Mary Kay Cabot of The Cleveland Plain Dealer reports.</t>
+          <t>Jeudy will not play in the Browns' preseason game against the Bills on Saturday, Daniel Oyefusi of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -32192,12 +32192,12 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>Cedric Tillman</t>
+          <t>Carson Schwesinger</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr">
@@ -32212,7 +32212,7 @@
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>Tillman (undisclosed) is not expected to play in Saturday's preseason game against the Bills, Mary Kay Cabot of The Cleveland Plain Dealer reports.</t>
+          <t>Schwesinger (undisclosed) is not expected to play in Saturday's preseason game against the Bills, Mary Kay Cabot of The Cleveland Plain Dealer reports.</t>
         </is>
       </c>
     </row>
@@ -32224,12 +32224,12 @@
       </c>
       <c r="B190" s="5" t="inlineStr">
         <is>
-          <t>Quinshon Judkins</t>
+          <t>Cedric Tillman</t>
         </is>
       </c>
       <c r="C190" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D190" s="5" t="inlineStr">
@@ -32244,7 +32244,7 @@
       </c>
       <c r="F190" s="5" t="inlineStr">
         <is>
-          <t>Judkins (undisclosed) is not expected to play in Saturday's preseason game against the Bills, Kelsey Russo of the Browns' official site reports.</t>
+          <t>Tillman (undisclosed) is not expected to play in Saturday's preseason game against the Bills, Mary Kay Cabot of The Cleveland Plain Dealer reports.</t>
         </is>
       </c>
     </row>
@@ -32256,17 +32256,17 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>Jack Stoll</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E191" s="4" t="inlineStr">
@@ -32276,7 +32276,7 @@
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>The Browns placed Stoll (undisclosed) on injured reserve Thursday.</t>
+          <t>Judkins (undisclosed) is not expected to play in Saturday's preseason game against the Bills, Kelsey Russo of the Browns' official site reports.</t>
         </is>
       </c>
     </row>
@@ -32288,7 +32288,7 @@
       </c>
       <c r="B192" s="5" t="inlineStr">
         <is>
-          <t>Drew Biber</t>
+          <t>Jack Stoll</t>
         </is>
       </c>
       <c r="C192" s="5" t="inlineStr">
@@ -32298,17 +32298,17 @@
       </c>
       <c r="D192" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E192" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F192" s="5" t="inlineStr">
         <is>
-          <t>The Browns signed Biber on Thursday.</t>
+          <t>The Browns placed Stoll (undisclosed) on injured reserve Thursday.</t>
         </is>
       </c>
     </row>
@@ -32320,27 +32320,27 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>Jamari Thrash</t>
+          <t>Drew Biber</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E193" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>ir</t>
+          <t>The Browns signed Biber on Thursday.</t>
         </is>
       </c>
     </row>
@@ -32352,17 +32352,17 @@
       </c>
       <c r="B194" s="5" t="inlineStr">
         <is>
-          <t>Joe Royer</t>
+          <t>Jamari Thrash</t>
         </is>
       </c>
       <c r="C194" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D194" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E194" s="5" t="inlineStr">
@@ -32372,7 +32372,7 @@
       </c>
       <c r="F194" s="5" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>ir</t>
         </is>
       </c>
     </row>
@@ -32384,7 +32384,7 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>Carsen Ryan</t>
+          <t>Joe Royer</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
@@ -32416,17 +32416,17 @@
       </c>
       <c r="B196" s="5" t="inlineStr">
         <is>
-          <t>Kendrick Green</t>
+          <t>Carsen Ryan</t>
         </is>
       </c>
       <c r="C196" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D196" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E196" s="5" t="inlineStr">
@@ -32436,7 +32436,7 @@
       </c>
       <c r="F196" s="5" t="inlineStr">
         <is>
-          <t>ir</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -32448,12 +32448,12 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>Tyron Herring</t>
+          <t>Kendrick Green</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D197" s="4" t="inlineStr">
@@ -32480,7 +32480,7 @@
       </c>
       <c r="B198" s="5" t="inlineStr">
         <is>
-          <t>Damarri Mathis</t>
+          <t>Tyron Herring</t>
         </is>
       </c>
       <c r="C198" s="5" t="inlineStr">
@@ -32512,25 +32512,29 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>Nathaniel Watson</t>
+          <t>Damarri Mathis</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E199" s="4" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="F199" s="4" t="inlineStr"/>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F199" s="4" t="inlineStr">
+        <is>
+          <t>ir</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="5" t="inlineStr">
@@ -32540,12 +32544,12 @@
       </c>
       <c r="B200" s="5" t="inlineStr">
         <is>
-          <t>Kingsley Eguakun</t>
+          <t>Nathaniel Watson</t>
         </is>
       </c>
       <c r="C200" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D200" s="5" t="inlineStr">
@@ -32568,7 +32572,7 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>Parker Brailsford</t>
+          <t>Kingsley Eguakun</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
@@ -32578,19 +32582,15 @@
       </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E201" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="F201" s="4" t="inlineStr">
-        <is>
-          <t>questionable</t>
-        </is>
-      </c>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F201" s="4" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="5" t="inlineStr">
@@ -32600,12 +32600,12 @@
       </c>
       <c r="B202" s="5" t="inlineStr">
         <is>
-          <t>Michael Coats Jr.</t>
+          <t>Parker Brailsford</t>
         </is>
       </c>
       <c r="C202" s="5" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D202" s="5" t="inlineStr">
@@ -32632,7 +32632,7 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>Nate Evans</t>
+          <t>Michael Coats Jr.</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
@@ -32664,25 +32664,29 @@
       </c>
       <c r="B204" s="5" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Nate Evans</t>
         </is>
       </c>
       <c r="C204" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D204" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E204" s="5" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="F204" s="5" t="inlineStr"/>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F204" s="5" t="inlineStr">
+        <is>
+          <t>questionable</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
@@ -39071,7 +39075,7 @@
       </c>
       <c r="E406" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Sprain</t>
         </is>
       </c>
       <c r="F406" s="5" t="inlineStr">
@@ -42988,27 +42992,27 @@
       </c>
       <c r="B530" s="5" t="inlineStr">
         <is>
-          <t>Behren Morton</t>
+          <t>Bryce Baringer</t>
         </is>
       </c>
       <c r="C530" s="5" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D530" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E530" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F530" s="5" t="inlineStr">
         <is>
-          <t>Morton completed 13 of 17 passes for 129 yards with one touchdown and no interceptions while rushing once for minus-1 yard in the Patriots' 24-21 preseason win over the Eagles on Saturday.</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -43020,12 +43024,12 @@
       </c>
       <c r="B531" s="4" t="inlineStr">
         <is>
-          <t>Andy Borregales</t>
+          <t>Behren Morton</t>
         </is>
       </c>
       <c r="C531" s="4" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D531" s="4" t="inlineStr">
@@ -43040,7 +43044,7 @@
       </c>
       <c r="F531" s="4" t="inlineStr">
         <is>
-          <t>Borregales made his only field-goal attempt, from 41 yards out, and connected on all three extra-point tries in the Patriots' 24-21 preseason win over the Eagles on Saturday.</t>
+          <t>Morton completed 13 of 17 passes for 129 yards with one touchdown and no interceptions while rushing once for minus-1 yard in the Patriots' 24-21 preseason win over the Eagles on Saturday.</t>
         </is>
       </c>
     </row>
@@ -43052,12 +43056,12 @@
       </c>
       <c r="B532" s="5" t="inlineStr">
         <is>
-          <t>Kyle Williams</t>
+          <t>Andy Borregales</t>
         </is>
       </c>
       <c r="C532" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="D532" s="5" t="inlineStr">
@@ -43072,7 +43076,7 @@
       </c>
       <c r="F532" s="5" t="inlineStr">
         <is>
-          <t>Williams brought in two of six targets for 74 yards and a touchdown in the Patriots' 24-21 preseason win over the Eagles on Saturday.</t>
+          <t>Borregales made his only field-goal attempt, from 41 yards out, and connected on all three extra-point tries in the Patriots' 24-21 preseason win over the Eagles on Saturday.</t>
         </is>
       </c>
     </row>
@@ -43084,27 +43088,27 @@
       </c>
       <c r="B533" s="4" t="inlineStr">
         <is>
-          <t>Marcus Bryant</t>
+          <t>Kyle Williams</t>
         </is>
       </c>
       <c r="C533" s="4" t="inlineStr">
         <is>
-          <t>OT</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D533" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E533" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F533" s="4" t="inlineStr">
         <is>
-          <t>Bryant has been ruled out for the rest of Saturday's preseason game against the Eagles due to an ankle injury, Evan Lazar of the Patriots' official site reports.</t>
+          <t>Williams brought in two of six targets for 74 yards and a touchdown in the Patriots' 24-21 preseason win over the Eagles on Saturday.</t>
         </is>
       </c>
     </row>
@@ -43116,12 +43120,12 @@
       </c>
       <c r="B534" s="5" t="inlineStr">
         <is>
-          <t>Christian Gonzalez</t>
+          <t>Marcus Bryant</t>
         </is>
       </c>
       <c r="C534" s="5" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>OT</t>
         </is>
       </c>
       <c r="D534" s="5" t="inlineStr">
@@ -43136,7 +43140,7 @@
       </c>
       <c r="F534" s="5" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>Bryant has been ruled out for the rest of Saturday's preseason game against the Eagles due to an ankle injury, Evan Lazar of the Patriots' official site reports.</t>
         </is>
       </c>
     </row>
@@ -43148,17 +43152,17 @@
       </c>
       <c r="B535" s="4" t="inlineStr">
         <is>
-          <t>Myles Montgomery</t>
+          <t>Christian Gonzalez</t>
         </is>
       </c>
       <c r="C535" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D535" s="4" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E535" s="4" t="inlineStr">
@@ -43168,7 +43172,7 @@
       </c>
       <c r="F535" s="4" t="inlineStr">
         <is>
-          <t>ir</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -43180,17 +43184,17 @@
       </c>
       <c r="B536" s="5" t="inlineStr">
         <is>
-          <t>Ben Brown</t>
+          <t>Myles Montgomery</t>
         </is>
       </c>
       <c r="C536" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D536" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E536" s="5" t="inlineStr">
@@ -43200,7 +43204,7 @@
       </c>
       <c r="F536" s="5" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>ir</t>
         </is>
       </c>
     </row>
@@ -43212,25 +43216,29 @@
       </c>
       <c r="B537" s="4" t="inlineStr">
         <is>
-          <t>Carlton Davis III</t>
+          <t>Ben Brown</t>
         </is>
       </c>
       <c r="C537" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D537" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E537" s="4" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="F537" s="4" t="inlineStr"/>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F537" s="4" t="inlineStr">
+        <is>
+          <t>questionable</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" s="5" t="inlineStr">
@@ -43240,12 +43248,12 @@
       </c>
       <c r="B538" s="5" t="inlineStr">
         <is>
-          <t>Quintayvious Hutchins</t>
+          <t>Carlton Davis III</t>
         </is>
       </c>
       <c r="C538" s="5" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D538" s="5" t="inlineStr">
@@ -43268,12 +43276,12 @@
       </c>
       <c r="B539" s="4" t="inlineStr">
         <is>
-          <t>Greg Van Roten</t>
+          <t>Quintayvious Hutchins</t>
         </is>
       </c>
       <c r="C539" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D539" s="4" t="inlineStr">
@@ -43286,11 +43294,7 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F539" s="4" t="inlineStr">
-        <is>
-          <t>The Patriots signed Van Roten on Tuesday.</t>
-        </is>
-      </c>
+      <c r="F539" s="4" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" s="5" t="inlineStr">
@@ -43300,12 +43304,12 @@
       </c>
       <c r="B540" s="5" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>Greg Van Roten</t>
         </is>
       </c>
       <c r="C540" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D540" s="5" t="inlineStr">
@@ -43320,7 +43324,7 @@
       </c>
       <c r="F540" s="5" t="inlineStr">
         <is>
-          <t>Chad Graff of The Athletic predicts that Rhamondre Stevenson and Henderson seem likely to share New England's backfield work pretty evenly this coming season.</t>
+          <t>The Patriots signed Van Roten on Tuesday.</t>
         </is>
       </c>
     </row>
@@ -43332,7 +43336,7 @@
       </c>
       <c r="B541" s="4" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C541" s="4" t="inlineStr">
@@ -43352,7 +43356,7 @@
       </c>
       <c r="F541" s="4" t="inlineStr">
         <is>
-          <t>Chad Graff of The Athletic predicts that Stevenson and TreVeyon Henderson are likely to share New England's backfield work pretty evenly this coming season.</t>
+          <t>Chad Graff of The Athletic predicts that Rhamondre Stevenson and Henderson seem likely to share New England's backfield work pretty evenly this coming season.</t>
         </is>
       </c>
     </row>
@@ -43364,12 +43368,12 @@
       </c>
       <c r="B542" s="5" t="inlineStr">
         <is>
-          <t>Drake Maye</t>
+          <t>Rhamondre Stevenson</t>
         </is>
       </c>
       <c r="C542" s="5" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D542" s="5" t="inlineStr">
@@ -43384,7 +43388,7 @@
       </c>
       <c r="F542" s="5" t="inlineStr">
         <is>
-          <t>Maye completed every pass during the first two periods of practice Monday, including a deep ball to A.J. Brown, Taylor Kyles of CLNSMedia.com reports.</t>
+          <t>Chad Graff of The Athletic predicts that Stevenson and TreVeyon Henderson are likely to share New England's backfield work pretty evenly this coming season.</t>
         </is>
       </c>
     </row>
@@ -43396,12 +43400,12 @@
       </c>
       <c r="B543" s="4" t="inlineStr">
         <is>
-          <t>Romeo Doubs</t>
+          <t>Drake Maye</t>
         </is>
       </c>
       <c r="C543" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D543" s="4" t="inlineStr">
@@ -43416,7 +43420,7 @@
       </c>
       <c r="F543" s="4" t="inlineStr">
         <is>
-          <t>Doubs was the standout wide receiver during the Patriots' training camp practice Saturday, Taylor Kyles of CLNSMedia.com reports.</t>
+          <t>Maye completed every pass during the first two periods of practice Monday, including a deep ball to A.J. Brown, Taylor Kyles of CLNSMedia.com reports.</t>
         </is>
       </c>
     </row>
@@ -43428,7 +43432,7 @@
       </c>
       <c r="B544" s="5" t="inlineStr">
         <is>
-          <t>Kayshon Boutte</t>
+          <t>Romeo Doubs</t>
         </is>
       </c>
       <c r="C544" s="5" t="inlineStr">
@@ -43448,7 +43452,7 @@
       </c>
       <c r="F544" s="5" t="inlineStr">
         <is>
-          <t>Boutte logged 16 snaps in Thursday's preseason opener against the Colts.</t>
+          <t>Doubs was the standout wide receiver during the Patriots' training camp practice Saturday, Taylor Kyles of CLNSMedia.com reports.</t>
         </is>
       </c>
     </row>
@@ -43460,7 +43464,7 @@
       </c>
       <c r="B545" s="4" t="inlineStr">
         <is>
-          <t>DeMario Douglas</t>
+          <t>Kayshon Boutte</t>
         </is>
       </c>
       <c r="C545" s="4" t="inlineStr">
@@ -43480,7 +43484,7 @@
       </c>
       <c r="F545" s="4" t="inlineStr">
         <is>
-          <t>Douglas was among the Patriots' key skill players who didn't play in Thursday's preseason opener against the Colts,  Mark Daniels of masslive.com reports.</t>
+          <t>Boutte logged 16 snaps in Thursday's preseason opener against the Colts.</t>
         </is>
       </c>
     </row>
@@ -43492,7 +43496,7 @@
       </c>
       <c r="B546" s="5" t="inlineStr">
         <is>
-          <t>A.J. Brown</t>
+          <t>DeMario Douglas</t>
         </is>
       </c>
       <c r="C546" s="5" t="inlineStr">
@@ -43512,7 +43516,7 @@
       </c>
       <c r="F546" s="5" t="inlineStr">
         <is>
-          <t>Brown was among the Patriots' key skill players who didn't see action in Thursday's preseason opener against the Colts, Evan Lazar of the team's official site reports.</t>
+          <t>Douglas was among the Patriots' key skill players who didn't play in Thursday's preseason opener against the Colts,  Mark Daniels of masslive.com reports.</t>
         </is>
       </c>
     </row>
@@ -43524,12 +43528,12 @@
       </c>
       <c r="B547" s="4" t="inlineStr">
         <is>
-          <t>Jam Miller</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="C547" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D547" s="4" t="inlineStr">
@@ -43544,7 +43548,7 @@
       </c>
       <c r="F547" s="4" t="inlineStr">
         <is>
-          <t>Miller carried the ball 14 times for 55 yards and failed to catch his only target in Thursday's 13-13 preseason tie with the Colts.</t>
+          <t>Brown was among the Patriots' key skill players who didn't see action in Thursday's preseason opener against the Colts, Evan Lazar of the team's official site reports.</t>
         </is>
       </c>
     </row>
@@ -43556,7 +43560,7 @@
       </c>
       <c r="B548" s="5" t="inlineStr">
         <is>
-          <t>Lan Larison</t>
+          <t>Jam Miller</t>
         </is>
       </c>
       <c r="C548" s="5" t="inlineStr">
@@ -43576,7 +43580,7 @@
       </c>
       <c r="F548" s="5" t="inlineStr">
         <is>
-          <t>Larison gained just one yard on seven carries in Thursday's 13-13 preseason tie with the Colts, but he caught six of eight targets for 38 yards.</t>
+          <t>Miller carried the ball 14 times for 55 yards and failed to catch his only target in Thursday's 13-13 preseason tie with the Colts.</t>
         </is>
       </c>
     </row>
@@ -43588,12 +43592,12 @@
       </c>
       <c r="B549" s="4" t="inlineStr">
         <is>
-          <t>Mack Hollins</t>
+          <t>Lan Larison</t>
         </is>
       </c>
       <c r="C549" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D549" s="4" t="inlineStr">
@@ -43608,7 +43612,7 @@
       </c>
       <c r="F549" s="4" t="inlineStr">
         <is>
-          <t>Hollins caught two of four targets for 24 yards in Thursday's 13-13 preseason tie with the Colts.</t>
+          <t>Larison gained just one yard on seven carries in Thursday's 13-13 preseason tie with the Colts, but he caught six of eight targets for 38 yards.</t>
         </is>
       </c>
     </row>
@@ -43620,12 +43624,12 @@
       </c>
       <c r="B550" s="5" t="inlineStr">
         <is>
-          <t>Jared Wilson</t>
+          <t>Mack Hollins</t>
         </is>
       </c>
       <c r="C550" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D550" s="5" t="inlineStr">
@@ -43640,7 +43644,7 @@
       </c>
       <c r="F550" s="5" t="inlineStr">
         <is>
-          <t>Wilson (knee) was a full participant in Thursday's practice, Brooks Kubena of The Athletic reports.</t>
+          <t>Hollins caught two of four targets for 24 yards in Thursday's 13-13 preseason tie with the Colts.</t>
         </is>
       </c>
     </row>
@@ -43652,12 +43656,12 @@
       </c>
       <c r="B551" s="4" t="inlineStr">
         <is>
-          <t>JaMycal Hasty</t>
+          <t>Jared Wilson</t>
         </is>
       </c>
       <c r="C551" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D551" s="4" t="inlineStr">
@@ -43672,7 +43676,7 @@
       </c>
       <c r="F551" s="4" t="inlineStr">
         <is>
-          <t>Hasty and the Patriots agreed on a one-year contract Wednesday, Aaron Wilson of KPRC 2 Houston reports.</t>
+          <t>Wilson (knee) was a full participant in Thursday's practice, Brooks Kubena of The Athletic reports.</t>
         </is>
       </c>
     </row>
@@ -43684,7 +43688,7 @@
       </c>
       <c r="B552" s="5" t="inlineStr">
         <is>
-          <t>Hassan Haskins</t>
+          <t>JaMycal Hasty</t>
         </is>
       </c>
       <c r="C552" s="5" t="inlineStr">
@@ -43704,7 +43708,7 @@
       </c>
       <c r="F552" s="5" t="inlineStr">
         <is>
-          <t>New England signed Haskins on Wednesday.</t>
+          <t>Hasty and the Patriots agreed on a one-year contract Wednesday, Aaron Wilson of KPRC 2 Houston reports.</t>
         </is>
       </c>
     </row>
@@ -43716,12 +43720,12 @@
       </c>
       <c r="B553" s="4" t="inlineStr">
         <is>
-          <t>Hunter Henry</t>
+          <t>Hassan Haskins</t>
         </is>
       </c>
       <c r="C553" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D553" s="4" t="inlineStr">
@@ -43736,7 +43740,7 @@
       </c>
       <c r="F553" s="4" t="inlineStr">
         <is>
-          <t>Henry agreed to a two-year, $16 million contract extension with the Patriots on Monday, Adam Schefter of ESPN reports.</t>
+          <t>New England signed Haskins on Wednesday.</t>
         </is>
       </c>
     </row>
@@ -43748,7 +43752,7 @@
       </c>
       <c r="B554" s="5" t="inlineStr">
         <is>
-          <t>CJ Dippre</t>
+          <t>Hunter Henry</t>
         </is>
       </c>
       <c r="C554" s="5" t="inlineStr">
@@ -43768,7 +43772,7 @@
       </c>
       <c r="F554" s="5" t="inlineStr">
         <is>
-          <t>The Patriots activated Dippre (undisclosed) off the active/PUP list Wednesday, Mike Reiss of ESPN.com reports.</t>
+          <t>Henry agreed to a two-year, $16 million contract extension with the Patriots on Monday, Adam Schefter of ESPN reports.</t>
         </is>
       </c>
     </row>
@@ -48556,27 +48560,27 @@
       </c>
       <c r="B705" s="4" t="inlineStr">
         <is>
-          <t>Drew Lock</t>
+          <t>Rodney Thomas II</t>
         </is>
       </c>
       <c r="C705" s="4" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D705" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E705" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Surgery</t>
         </is>
       </c>
       <c r="F705" s="4" t="inlineStr">
         <is>
-          <t>Lock completed 12 of 14 passes for 103 yards and a touchdown while rushing twice for eight yards in Sunday's 19-16 preseason loss to the Titans.</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -48588,27 +48592,27 @@
       </c>
       <c r="B706" s="5" t="inlineStr">
         <is>
-          <t>Emmanuel Henderson Jr.</t>
+          <t>Mason Richman</t>
         </is>
       </c>
       <c r="C706" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D706" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Doubtful</t>
         </is>
       </c>
       <c r="E706" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F706" s="5" t="inlineStr">
         <is>
-          <t>Henderson caught one of two targets for seven yards in Sunday's 19-16 preseason loss to the Titans. He also returned two kickoffs for 47 yards and notched two solo tackles on special teams.</t>
+          <t>doubtful</t>
         </is>
       </c>
     </row>
@@ -48620,27 +48624,27 @@
       </c>
       <c r="B707" s="4" t="inlineStr">
         <is>
-          <t>Elijah Arroyo</t>
+          <t>Bud Clark</t>
         </is>
       </c>
       <c r="C707" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D707" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="E707" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Fracture</t>
         </is>
       </c>
       <c r="F707" s="4" t="inlineStr">
         <is>
-          <t>Arroyo caught two of four targets for 50 yards and a touchdown in Sunday's 19-16 preseason loss to the Titans.</t>
+          <t>Seahawks head coach Mike Macdonald said that Clark will be out for "multiple months" after fracturing his right ankle in Sunday's 19-16 preseason loss to Tennessee, Brady Henderson of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -48652,27 +48656,27 @@
       </c>
       <c r="B708" s="5" t="inlineStr">
         <is>
-          <t>Bud Clark</t>
+          <t>Drew Lock</t>
         </is>
       </c>
       <c r="C708" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D708" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E708" s="5" t="inlineStr">
         <is>
-          <t>Leg</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F708" s="5" t="inlineStr">
         <is>
-          <t>Clark was carted off the field with a right leg injury during Sunday's preseason matchup with the Titans, Brady Henderson of ESPN.com reports.</t>
+          <t>Lock completed 12 of 14 passes for 103 yards and a touchdown while rushing twice for eight yards in Sunday's 19-16 preseason loss to the Titans.</t>
         </is>
       </c>
     </row>
@@ -48684,12 +48688,12 @@
       </c>
       <c r="B709" s="4" t="inlineStr">
         <is>
-          <t>Jadarian Price</t>
+          <t>Emmanuel Henderson Jr.</t>
         </is>
       </c>
       <c r="C709" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D709" s="4" t="inlineStr">
@@ -48704,7 +48708,7 @@
       </c>
       <c r="F709" s="4" t="inlineStr">
         <is>
-          <t>Price will not play in Sunday's preseason game against the Titans, Gregg Bell of The Tacoma News Tribune reports.</t>
+          <t>Henderson caught one of two targets for seven yards in Sunday's 19-16 preseason loss to the Titans. He also returned two kickoffs for 47 yards and notched two solo tackles on special teams.</t>
         </is>
       </c>
     </row>
@@ -48716,12 +48720,12 @@
       </c>
       <c r="B710" s="5" t="inlineStr">
         <is>
-          <t>Julian Hicks</t>
+          <t>Elijah Arroyo</t>
         </is>
       </c>
       <c r="C710" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D710" s="5" t="inlineStr">
@@ -48736,7 +48740,7 @@
       </c>
       <c r="F710" s="5" t="inlineStr">
         <is>
-          <t>The Seahawks signed Hicks to a contract Saturday, John Boyle of the team's official site reports.</t>
+          <t>Arroyo caught two of four targets for 50 yards and a touchdown in Sunday's 19-16 preseason loss to the Titans.</t>
         </is>
       </c>
     </row>
@@ -48748,27 +48752,27 @@
       </c>
       <c r="B711" s="4" t="inlineStr">
         <is>
-          <t>Jake Bobo</t>
+          <t>Jadarian Price</t>
         </is>
       </c>
       <c r="C711" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D711" s="4" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E711" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F711" s="4" t="inlineStr">
         <is>
-          <t>The Seahawks placed Bobo (knee) on injured reserve Saturday, John Boyle of the team's official site reports.</t>
+          <t>Price will not play in Sunday's preseason game against the Titans, Gregg Bell of The Tacoma News Tribune reports.</t>
         </is>
       </c>
     </row>
@@ -48780,12 +48784,12 @@
       </c>
       <c r="B712" s="5" t="inlineStr">
         <is>
-          <t>Trevon Diggs</t>
+          <t>Julian Hicks</t>
         </is>
       </c>
       <c r="C712" s="5" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D712" s="5" t="inlineStr">
@@ -48800,7 +48804,7 @@
       </c>
       <c r="F712" s="5" t="inlineStr">
         <is>
-          <t>The Seahawks are slated to sign Diggs to a one-year deal, Adam Schefter of ESPN reports.</t>
+          <t>The Seahawks signed Hicks to a contract Saturday, John Boyle of the team's official site reports.</t>
         </is>
       </c>
     </row>
@@ -48812,12 +48816,12 @@
       </c>
       <c r="B713" s="4" t="inlineStr">
         <is>
-          <t>Joseph Vaughn</t>
+          <t>Jake Bobo</t>
         </is>
       </c>
       <c r="C713" s="4" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D713" s="4" t="inlineStr">
@@ -48832,7 +48836,7 @@
       </c>
       <c r="F713" s="4" t="inlineStr">
         <is>
-          <t>ir</t>
+          <t>The Seahawks placed Bobo (knee) on injured reserve Saturday, John Boyle of the team's official site reports.</t>
         </is>
       </c>
     </row>
@@ -48844,27 +48848,27 @@
       </c>
       <c r="B714" s="5" t="inlineStr">
         <is>
-          <t>Emanuel Wilson</t>
+          <t>Trevon Diggs</t>
         </is>
       </c>
       <c r="C714" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D714" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E714" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F714" s="5" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>The Seahawks are slated to sign Diggs to a one-year deal, Adam Schefter of ESPN reports.</t>
         </is>
       </c>
     </row>
@@ -48876,12 +48880,12 @@
       </c>
       <c r="B715" s="4" t="inlineStr">
         <is>
-          <t>Robbie Ouzts</t>
+          <t>Joseph Vaughn</t>
         </is>
       </c>
       <c r="C715" s="4" t="inlineStr">
         <is>
-          <t>FB</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D715" s="4" t="inlineStr">
@@ -48908,12 +48912,12 @@
       </c>
       <c r="B716" s="5" t="inlineStr">
         <is>
-          <t>Tory Horton</t>
+          <t>Emanuel Wilson</t>
         </is>
       </c>
       <c r="C716" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D716" s="5" t="inlineStr">
@@ -48923,7 +48927,7 @@
       </c>
       <c r="E716" s="5" t="inlineStr">
         <is>
-          <t>Undisclosed</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F716" s="5" t="inlineStr">
@@ -48940,12 +48944,12 @@
       </c>
       <c r="B717" s="4" t="inlineStr">
         <is>
-          <t>Shemar Jean-Charles</t>
+          <t>Robbie Ouzts</t>
         </is>
       </c>
       <c r="C717" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="D717" s="4" t="inlineStr">
@@ -48972,12 +48976,12 @@
       </c>
       <c r="B718" s="5" t="inlineStr">
         <is>
-          <t>Nick Emmanwori</t>
+          <t>Tory Horton</t>
         </is>
       </c>
       <c r="C718" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D718" s="5" t="inlineStr">
@@ -48987,7 +48991,7 @@
       </c>
       <c r="E718" s="5" t="inlineStr">
         <is>
-          <t>Surgery</t>
+          <t>Undisclosed</t>
         </is>
       </c>
       <c r="F718" s="5" t="inlineStr">
@@ -49004,27 +49008,27 @@
       </c>
       <c r="B719" s="4" t="inlineStr">
         <is>
-          <t>Anthony Hankerson</t>
+          <t>Shemar Jean-Charles</t>
         </is>
       </c>
       <c r="C719" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D719" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E719" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F719" s="4" t="inlineStr">
         <is>
-          <t>Hankerson and the Seahawks agreed on a contract Monday, John Boyle of the team's official website reports.</t>
+          <t>ir</t>
         </is>
       </c>
     </row>
@@ -49036,27 +49040,27 @@
       </c>
       <c r="B720" s="5" t="inlineStr">
         <is>
-          <t>Montorie Foster Jr.</t>
+          <t>Nick Emmanwori</t>
         </is>
       </c>
       <c r="C720" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D720" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E720" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Surgery</t>
         </is>
       </c>
       <c r="F720" s="5" t="inlineStr">
         <is>
-          <t>Foster caught five of seven targets for 36 yards and a touchdown in Saturday's 17-7 preseason loss to the Cowboys, building on what has been a strong performance in training camp, John Boyle of the Seahawks' official site reports.</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -49068,12 +49072,12 @@
       </c>
       <c r="B721" s="4" t="inlineStr">
         <is>
-          <t>Rashid Shaheed</t>
+          <t>Anthony Hankerson</t>
         </is>
       </c>
       <c r="C721" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D721" s="4" t="inlineStr">
@@ -49088,7 +49092,7 @@
       </c>
       <c r="F721" s="4" t="inlineStr">
         <is>
-          <t>Shaheed didn't suit up for Saturday's 17-7 preseason loss to the Cowboys.</t>
+          <t>Hankerson and the Seahawks agreed on a contract Monday, John Boyle of the team's official website reports.</t>
         </is>
       </c>
     </row>
@@ -49100,12 +49104,12 @@
       </c>
       <c r="B722" s="5" t="inlineStr">
         <is>
-          <t>AJ Barner</t>
+          <t>Montorie Foster Jr.</t>
         </is>
       </c>
       <c r="C722" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D722" s="5" t="inlineStr">
@@ -49120,7 +49124,7 @@
       </c>
       <c r="F722" s="5" t="inlineStr">
         <is>
-          <t>Barner was rested for Seattle's 17-7 preseason loss to the Cowboys on Saturday.</t>
+          <t>Foster caught five of seven targets for 36 yards and a touchdown in Saturday's 17-7 preseason loss to the Cowboys, building on what has been a strong performance in training camp, John Boyle of the Seahawks' official site reports.</t>
         </is>
       </c>
     </row>
@@ -49132,27 +49136,27 @@
       </c>
       <c r="B723" s="4" t="inlineStr">
         <is>
-          <t>Zach Charbonnet</t>
+          <t>Rashid Shaheed</t>
         </is>
       </c>
       <c r="C723" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D723" s="4" t="inlineStr">
         <is>
-          <t>Out</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E723" s="4" t="inlineStr">
         <is>
-          <t>Surgery</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F723" s="4" t="inlineStr">
         <is>
-          <t>Charbonnet (knee) remains on the active/PUP list as the Seahawks' second preseason contest (Sunday, Aug. 23 versus the Titans) approaches.</t>
+          <t>Shaheed didn't suit up for Saturday's 17-7 preseason loss to the Cowboys.</t>
         </is>
       </c>
     </row>
@@ -49164,12 +49168,12 @@
       </c>
       <c r="B724" s="5" t="inlineStr">
         <is>
-          <t>Jason Myers</t>
+          <t>AJ Barner</t>
         </is>
       </c>
       <c r="C724" s="5" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D724" s="5" t="inlineStr">
@@ -49184,7 +49188,7 @@
       </c>
       <c r="F724" s="5" t="inlineStr">
         <is>
-          <t>Myers missed his only field-goal attempt from 45 yards out and made his only extra-point try in the Seahawks' 17-7 preseason loss to the Cowboys on Saturday.</t>
+          <t>Barner was rested for Seattle's 17-7 preseason loss to the Cowboys on Saturday.</t>
         </is>
       </c>
     </row>
@@ -49196,7 +49200,7 @@
       </c>
       <c r="B725" s="4" t="inlineStr">
         <is>
-          <t>George Holani</t>
+          <t>Zach Charbonnet</t>
         </is>
       </c>
       <c r="C725" s="4" t="inlineStr">
@@ -49206,17 +49210,17 @@
       </c>
       <c r="D725" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="E725" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Surgery</t>
         </is>
       </c>
       <c r="F725" s="4" t="inlineStr">
         <is>
-          <t>Holani rushed 12 times for 42 yards in the Seahawks' 17-7 preseason loss to the Cowboys on Saturday.</t>
+          <t>Charbonnet (knee) remains on the active/PUP list as the Seahawks' second preseason contest (Sunday, Aug. 23 versus the Titans) approaches.</t>
         </is>
       </c>
     </row>
@@ -49228,12 +49232,12 @@
       </c>
       <c r="B726" s="5" t="inlineStr">
         <is>
-          <t>Devon Witherspoon</t>
+          <t>Jason Myers</t>
         </is>
       </c>
       <c r="C726" s="5" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="D726" s="5" t="inlineStr">
@@ -49248,7 +49252,7 @@
       </c>
       <c r="F726" s="5" t="inlineStr">
         <is>
-          <t>Witherspoon and the Seahawks agreed to a four-year, $132 million contract extension Saturday, Adam Schefter of ESPN reports.</t>
+          <t>Myers missed his only field-goal attempt from 45 yards out and made his only extra-point try in the Seahawks' 17-7 preseason loss to the Cowboys on Saturday.</t>
         </is>
       </c>
     </row>
@@ -49260,12 +49264,12 @@
       </c>
       <c r="B727" s="4" t="inlineStr">
         <is>
-          <t>DeMarcus Lawrence</t>
+          <t>George Holani</t>
         </is>
       </c>
       <c r="C727" s="4" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D727" s="4" t="inlineStr">
@@ -49280,7 +49284,7 @@
       </c>
       <c r="F727" s="4" t="inlineStr">
         <is>
-          <t>Lawrence has declared that he will retire after the 2026 season, Jori Epstein of Yahoo Sports reports.</t>
+          <t>Holani rushed 12 times for 42 yards in the Seahawks' 17-7 preseason loss to the Cowboys on Saturday.</t>
         </is>
       </c>
     </row>
@@ -49292,12 +49296,12 @@
       </c>
       <c r="B728" s="5" t="inlineStr">
         <is>
-          <t>Sam Darnold</t>
+          <t>Devon Witherspoon</t>
         </is>
       </c>
       <c r="C728" s="5" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D728" s="5" t="inlineStr">
@@ -49312,7 +49316,7 @@
       </c>
       <c r="F728" s="5" t="inlineStr">
         <is>
-          <t>Coach Mike Macdonald said Friday that Darnold won't suit up for Saturday's preseason game versus the Cowboys, Curtis Crabtree of Fox 13 Seattle reports.</t>
+          <t>Witherspoon and the Seahawks agreed to a four-year, $132 million contract extension Saturday, Adam Schefter of ESPN reports.</t>
         </is>
       </c>
     </row>
@@ -49324,12 +49328,12 @@
       </c>
       <c r="B729" s="4" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba</t>
+          <t>DeMarcus Lawrence</t>
         </is>
       </c>
       <c r="C729" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D729" s="4" t="inlineStr">
@@ -49344,7 +49348,7 @@
       </c>
       <c r="F729" s="4" t="inlineStr">
         <is>
-          <t>Smith-Njigba is always willing to be coached up in an attempt to be a better player, Anthony Moeglin of Roundtable Sports reports.</t>
+          <t>Lawrence has declared that he will retire after the 2026 season, Jori Epstein of Yahoo Sports reports.</t>
         </is>
       </c>
     </row>
@@ -51836,16 +51840,16 @@
         </is>
       </c>
       <c r="D5" s="15" t="n">
-        <v>71.40000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>19.7</v>
+        <v>15.7</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
@@ -51853,13 +51857,9 @@
         </is>
       </c>
       <c r="I5" s="9" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>Wind 7 mph (gusts 20)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -51878,20 +51878,20 @@
         </is>
       </c>
       <c r="D6" s="17" t="n">
-        <v>70.3</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>11.3</v>
+        <v>4.3</v>
       </c>
       <c r="F6" s="17" t="n">
-        <v>13.2</v>
+        <v>4.5</v>
       </c>
       <c r="G6" s="17" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>Drizzle</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="I6" s="24" t="n">
@@ -51916,20 +51916,20 @@
         </is>
       </c>
       <c r="D7" s="15" t="n">
-        <v>107.6</v>
+        <v>107.4</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>21.7</v>
+        <v>20.6</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Partly cloudy</t>
+          <t>Overcast</t>
         </is>
       </c>
       <c r="I7" s="9" t="n">
@@ -51958,20 +51958,20 @@
         </is>
       </c>
       <c r="D8" s="17" t="n">
-        <v>79.59999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>7.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F8" s="17" t="n">
-        <v>6.7</v>
+        <v>7.2</v>
       </c>
       <c r="G8" s="17" t="n">
         <v>0</v>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Overcast</t>
         </is>
       </c>
       <c r="I8" s="24" t="n">
@@ -51996,16 +51996,16 @@
         </is>
       </c>
       <c r="D9" s="15" t="n">
-        <v>86.3</v>
+        <v>86.2</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>3.4</v>
+        <v>4.9</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>8.1</v>
+        <v>6</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
@@ -52034,26 +52034,30 @@
         </is>
       </c>
       <c r="D10" s="17" t="n">
-        <v>89.2</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>5.7</v>
+        <v>13.1</v>
       </c>
       <c r="F10" s="17" t="n">
-        <v>5.8</v>
+        <v>13</v>
       </c>
       <c r="G10" s="17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>Overcast</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="I10" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="5" t="inlineStr"/>
+        <v>-0.68</v>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Wind 13 mph (gusts 13) · canopy — wind damped</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -52072,16 +52076,16 @@
         </is>
       </c>
       <c r="D11" s="15" t="n">
-        <v>82.2</v>
+        <v>84.2</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>13</v>
+        <v>2.9</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
@@ -52110,13 +52114,13 @@
         </is>
       </c>
       <c r="D12" s="17" t="n">
-        <v>82.90000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="F12" s="17" t="n">
-        <v>9.4</v>
+        <v>5.8</v>
       </c>
       <c r="G12" s="17" t="n">
         <v>23</v>
@@ -52148,26 +52152,30 @@
         </is>
       </c>
       <c r="D13" s="15" t="n">
-        <v>87.8</v>
+        <v>78.3</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>10.2</v>
+        <v>8.9</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>14.3</v>
+        <v>10.7</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Violent showers</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>55% chance of rain</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -52186,16 +52194,16 @@
         </is>
       </c>
       <c r="D14" s="17" t="n">
-        <v>82.90000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="F14" s="17" t="n">
-        <v>11</v>
+        <v>12.3</v>
       </c>
       <c r="G14" s="17" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
@@ -52224,30 +52232,26 @@
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>93.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>18.3</v>
+        <v>15.2</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Overcast</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="I15" s="9" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>Wind 9 mph (gusts 18) · 93°F</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -52266,20 +52270,20 @@
         </is>
       </c>
       <c r="D16" s="17" t="n">
-        <v>102.3</v>
+        <v>104.1</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>10.2</v>
+        <v>6</v>
       </c>
       <c r="F16" s="17" t="n">
-        <v>7.2</v>
+        <v>10.1</v>
       </c>
       <c r="G16" s="17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>Mainly clear</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="I16" s="24" t="n">
@@ -52287,7 +52291,7 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>102°F · retractable roof — effect halved</t>
+          <t>104°F · retractable roof — effect halved</t>
         </is>
       </c>
     </row>
@@ -52308,16 +52312,16 @@
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>68</v>
+        <v>65.7</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>12.1</v>
+        <v>11.4</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>18.3</v>
+        <v>18.6</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
@@ -52329,7 +52333,7 @@
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>Wind 12 mph (gusts 18)</t>
+          <t>Wind 11 mph (gusts 19)</t>
         </is>
       </c>
     </row>
@@ -52350,30 +52354,26 @@
         </is>
       </c>
       <c r="D18" s="17" t="n">
-        <v>80.90000000000001</v>
+        <v>80.7</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>14.3</v>
+        <v>9.6</v>
       </c>
       <c r="F18" s="17" t="n">
-        <v>17.7</v>
+        <v>12.5</v>
       </c>
       <c r="G18" s="17" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>Overcast</t>
+          <t>Mainly clear</t>
         </is>
       </c>
       <c r="I18" s="24" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>Wind 14 mph (gusts 18)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -52392,20 +52392,20 @@
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>81.59999999999999</v>
+        <v>81</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>8.300000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>12.3</v>
+        <v>5.4</v>
       </c>
       <c r="G19" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Overcast</t>
+          <t>Mainly clear</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
@@ -52430,20 +52430,20 @@
         </is>
       </c>
       <c r="D20" s="17" t="n">
-        <v>94.40000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="F20" s="17" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="G20" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>Partly cloudy</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="I20" s="24" t="n">
@@ -52451,7 +52451,7 @@
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>94°F</t>
+          <t>92°F</t>
         </is>
       </c>
     </row>

--- a/NFL_Edge_Model.xlsx
+++ b/NFL_Edge_Model.xlsx
@@ -692,7 +692,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Snapshot of the live model, generated 2026-08-25T03:16:42+00:00. Read-only: the model runs in the pipeline, not in this file.</t>
+          <t>Snapshot of the live model, generated 2026-08-25T06:03:38+00:00. Read-only: the model runs in the pipeline, not in this file.</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>2026-08-25T03:16:42+00:00</t>
+          <t>2026-08-25T06:03:38+00:00</t>
         </is>
       </c>
     </row>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>CHI @ TEN</t>
+          <t>ATL @ MIA</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -2927,19 +2927,19 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>0.61</v>
+        <v>0.5968</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>0.5349</v>
+        <v>0.5238</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>0.0483</v>
+        <v>0.0478</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0.1404490184348804</v>
+        <v>0.1394118943956764</v>
       </c>
       <c r="J13" s="10" t="n">
         <v>0.15</v>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>ATL @ MIA</t>
+          <t>CHI @ TEN</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -2972,19 +2972,19 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5968</v>
+        <v>0.6077</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5349</v>
       </c>
       <c r="H14" s="13" t="n">
-        <v>0.0478</v>
+        <v>0.0477</v>
       </c>
       <c r="I14" s="13" t="n">
-        <v>0.1394118943956764</v>
+        <v>0.1360905800626417</v>
       </c>
       <c r="J14" s="14" t="n">
         <v>0.15</v>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>NO @ DET</t>
+          <t>HOU @ CAR</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -3193,28 +3193,32 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Under 48.5</t>
+          <t>Over 35.5</t>
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>-102</v>
+        <v>-118</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>0.5544</v>
+        <v>0.591</v>
       </c>
       <c r="G19" s="8" t="n">
-        <v>0.505</v>
+        <v>0.5413</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>0.0394</v>
+        <v>0.0395</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>0.09793347314860723</v>
+        <v>0.09184040173237618</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K19" s="4" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -3224,7 +3228,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>SEA @ KC</t>
+          <t>NO @ DET</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -3234,32 +3238,28 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Over 36.5</t>
+          <t>Under 48.5</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>-110</v>
+        <v>-102</v>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5728</v>
+        <v>0.5544</v>
       </c>
       <c r="G20" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.505</v>
       </c>
       <c r="H20" s="13" t="n">
-        <v>0.0391</v>
+        <v>0.0394</v>
       </c>
       <c r="I20" s="13" t="n">
-        <v>0.09351056060470653</v>
+        <v>0.09793347314860723</v>
       </c>
       <c r="J20" s="14" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>HOU @ CAR</t>
+          <t>SEA @ KC</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -3279,23 +3279,23 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Over 35.5</t>
+          <t>Over 36.5</t>
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>-118</v>
+        <v>-110</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>0.5886</v>
+        <v>0.5728</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>0.5413</v>
+        <v>0.5238</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>0.0383</v>
+        <v>0.0391</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>0.08739014554814406</v>
+        <v>0.09351056060470653</v>
       </c>
       <c r="J21" s="10" t="n">
         <v>0.15</v>
@@ -3748,33 +3748,33 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>NO @ DAL</t>
+          <t>ATL @ MIA</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>DAL -1.5</t>
+          <t>MIA ML</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>-112</v>
+        <v>164</v>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.5533</v>
+        <v>0.4032</v>
       </c>
       <c r="G32" s="13" t="n">
-        <v>0.5283</v>
+        <v>0.3788</v>
       </c>
       <c r="H32" s="13" t="n">
-        <v>0.0234</v>
+        <v>0.0229</v>
       </c>
       <c r="I32" s="13" t="n">
-        <v>0.04734461804003537</v>
+        <v>0.06383255020986645</v>
       </c>
       <c r="J32" s="14" t="n">
         <v>0.15</v>
@@ -3793,33 +3793,33 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>ATL @ MIA</t>
+          <t>NO @ DAL</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>MIA ML</t>
+          <t>DAL -1.5</t>
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>164</v>
+        <v>-112</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>0.4032</v>
+        <v>0.5524</v>
       </c>
       <c r="G33" s="8" t="n">
-        <v>0.3788</v>
+        <v>0.5283</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>0.0229</v>
+        <v>0.0227</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>0.06383255020986645</v>
+        <v>0.04566188352606299</v>
       </c>
       <c r="J33" s="10" t="n">
         <v>0.15</v>
@@ -3883,42 +3883,38 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>NO @ DAL</t>
+          <t>ARI @ LAC</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>DAL ML</t>
+          <t>Under 46.5</t>
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>-130</v>
+        <v>-110</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>0.5874</v>
+        <v>0.5455</v>
       </c>
       <c r="G35" s="8" t="n">
-        <v>0.5652</v>
+        <v>0.5238</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>0.021</v>
+        <v>0.0207</v>
       </c>
       <c r="I35" s="8" t="n">
-        <v>0.0388506216300466</v>
+        <v>0.04148808649207303</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K35" s="4" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -3933,28 +3929,28 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Under 46.5</t>
+          <t>ARI +10.5</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.5455</v>
+        <v>0.5454</v>
       </c>
       <c r="G36" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H36" s="13" t="n">
-        <v>0.0207</v>
+        <v>0.0205</v>
       </c>
       <c r="I36" s="13" t="n">
-        <v>0.04148808649207303</v>
+        <v>0.0411405841524814</v>
       </c>
       <c r="J36" s="14" t="n">
         <v>0.5</v>
@@ -3969,38 +3965,42 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>ARI @ LAC</t>
+          <t>NO @ DAL</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>ARI +10.5</t>
+          <t>DAL ML</t>
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>-110</v>
+        <v>-130</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>0.5454</v>
+        <v>0.5865</v>
       </c>
       <c r="G37" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5652</v>
       </c>
       <c r="H37" s="8" t="n">
-        <v>0.0205</v>
+        <v>0.0203</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>0.0411405841524814</v>
+        <v>0.03730483326311795</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K37" s="4" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -4522,7 +4522,7 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>CHI @ TEN</t>
+          <t>NO @ DET</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -4532,32 +4532,28 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>CHI +3</t>
+          <t>NO +7</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.5486</v>
+        <v>0.5377</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.5238</v>
       </c>
       <c r="H50" s="13" t="n">
-        <v>0.0134</v>
+        <v>0.0136</v>
       </c>
       <c r="I50" s="13" t="n">
-        <v>0.02374157070022298</v>
+        <v>0.02500105918643447</v>
       </c>
       <c r="J50" s="14" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K50" s="5" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K50" s="5" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -4567,7 +4563,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>PIT @ BUF</t>
+          <t>CHI @ TEN</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -4577,23 +4573,23 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>BUF -1.5</t>
+          <t>CHI +3</t>
         </is>
       </c>
       <c r="E51" s="7" t="n">
-        <v>-112</v>
+        <v>-115</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>0.5414</v>
+        <v>0.5486</v>
       </c>
       <c r="G51" s="8" t="n">
-        <v>0.5283</v>
+        <v>0.5349</v>
       </c>
       <c r="H51" s="8" t="n">
-        <v>0.0128</v>
+        <v>0.0134</v>
       </c>
       <c r="I51" s="8" t="n">
-        <v>0.02471707908597648</v>
+        <v>0.02374157070022298</v>
       </c>
       <c r="J51" s="10" t="n">
         <v>0.15</v>
@@ -4612,42 +4608,38 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>NYG @ NYJ</t>
+          <t>NO @ DET</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>NYJ +3</t>
+          <t>NO ML</t>
         </is>
       </c>
       <c r="E52" s="12" t="n">
-        <v>-108</v>
+        <v>245</v>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.532</v>
+        <v>0.3031</v>
       </c>
       <c r="G52" s="13" t="n">
-        <v>0.5192</v>
+        <v>0.2899</v>
       </c>
       <c r="H52" s="13" t="n">
-        <v>0.0125</v>
+        <v>0.013</v>
       </c>
       <c r="I52" s="13" t="n">
-        <v>0.02284129340967922</v>
+        <v>0.04525769555304948</v>
       </c>
       <c r="J52" s="14" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K52" s="5" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K52" s="5" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -4657,38 +4649,42 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>SF @ LAR</t>
+          <t>PIT @ BUF</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>SF ML</t>
+          <t>BUF -1.5</t>
         </is>
       </c>
       <c r="E53" s="7" t="n">
-        <v>160</v>
+        <v>-112</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>0.3967</v>
+        <v>0.5414</v>
       </c>
       <c r="G53" s="8" t="n">
-        <v>0.3846</v>
+        <v>0.5283</v>
       </c>
       <c r="H53" s="8" t="n">
-        <v>0.0119</v>
+        <v>0.0128</v>
       </c>
       <c r="I53" s="8" t="n">
-        <v>0.03106029847990965</v>
+        <v>0.02471707908597648</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K53" s="4" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K53" s="4" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -4698,38 +4694,42 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>CHI @ CAR</t>
+          <t>NYG @ NYJ</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Under 47.5</t>
+          <t>NYJ +3</t>
         </is>
       </c>
       <c r="E54" s="12" t="n">
-        <v>-105</v>
+        <v>-108</v>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.5241</v>
+        <v>0.532</v>
       </c>
       <c r="G54" s="13" t="n">
-        <v>0.5122</v>
+        <v>0.5192</v>
       </c>
       <c r="H54" s="13" t="n">
-        <v>0.0118</v>
+        <v>0.0125</v>
       </c>
       <c r="I54" s="13" t="n">
-        <v>0.02330043912717339</v>
+        <v>0.02284129340967922</v>
       </c>
       <c r="J54" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K54" s="5" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K54" s="5" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -4739,33 +4739,33 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>NO @ DET</t>
+          <t>SF @ LAR</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>NO +7</t>
+          <t>SF ML</t>
         </is>
       </c>
       <c r="E55" s="7" t="n">
-        <v>-110</v>
+        <v>160</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>0.5354</v>
+        <v>0.3967</v>
       </c>
       <c r="G55" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.3846</v>
       </c>
       <c r="H55" s="8" t="n">
-        <v>0.0114</v>
+        <v>0.0119</v>
       </c>
       <c r="I55" s="8" t="n">
-        <v>0.02085323522306032</v>
+        <v>0.03106029847990965</v>
       </c>
       <c r="J55" s="10" t="n">
         <v>0.5</v>
@@ -4780,33 +4780,33 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>NO @ DET</t>
+          <t>CHI @ CAR</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>NO ML</t>
+          <t>Under 47.5</t>
         </is>
       </c>
       <c r="E56" s="12" t="n">
-        <v>245</v>
+        <v>-105</v>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.3011</v>
+        <v>0.5241</v>
       </c>
       <c r="G56" s="13" t="n">
-        <v>0.2899</v>
+        <v>0.5122</v>
       </c>
       <c r="H56" s="13" t="n">
-        <v>0.0111</v>
+        <v>0.0118</v>
       </c>
       <c r="I56" s="13" t="n">
-        <v>0.03851713007639801</v>
+        <v>0.02330043912717339</v>
       </c>
       <c r="J56" s="14" t="n">
         <v>0.5</v>
@@ -4821,33 +4821,33 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>CIN @ PHI</t>
+          <t>WSH @ BAL</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>CIN ML</t>
+          <t>BAL -2.5</t>
         </is>
       </c>
       <c r="E57" s="7" t="n">
-        <v>130</v>
+        <v>-118</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>0.4438</v>
+        <v>0.5503</v>
       </c>
       <c r="G57" s="8" t="n">
-        <v>0.4348</v>
+        <v>0.5413</v>
       </c>
       <c r="H57" s="8" t="n">
         <v>0.0089</v>
       </c>
       <c r="I57" s="8" t="n">
-        <v>0.02046761093596383</v>
+        <v>0.01668150236672911</v>
       </c>
       <c r="J57" s="10" t="n">
         <v>0.15</v>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>NE @ CLE</t>
+          <t>CIN @ PHI</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -4962,23 +4962,23 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>NE ML</t>
+          <t>CIN ML</t>
         </is>
       </c>
       <c r="E60" s="12" t="n">
-        <v>-142</v>
+        <v>130</v>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.5943000000000001</v>
+        <v>0.4427</v>
       </c>
       <c r="G60" s="13" t="n">
-        <v>0.5868</v>
+        <v>0.4348</v>
       </c>
       <c r="H60" s="13" t="n">
-        <v>0.0075</v>
+        <v>0.0078</v>
       </c>
       <c r="I60" s="13" t="n">
-        <v>0.01267203952571916</v>
+        <v>0.0179808503866109</v>
       </c>
       <c r="J60" s="14" t="n">
         <v>0.15</v>
@@ -4997,7 +4997,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>BAL @ IND</t>
+          <t>NE @ CLE</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -5007,28 +5007,32 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>IND ML</t>
+          <t>NE ML</t>
         </is>
       </c>
       <c r="E61" s="7" t="n">
-        <v>150</v>
+        <v>-142</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>0.4075</v>
+        <v>0.5943000000000001</v>
       </c>
       <c r="G61" s="8" t="n">
-        <v>0.4</v>
+        <v>0.5868</v>
       </c>
       <c r="H61" s="8" t="n">
-        <v>0.0074</v>
+        <v>0.0075</v>
       </c>
       <c r="I61" s="8" t="n">
-        <v>0.01851461403901522</v>
+        <v>0.01267203952571916</v>
       </c>
       <c r="J61" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K61" s="4" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
@@ -5038,7 +5042,7 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>WSH @ PHI</t>
+          <t>BAL @ IND</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -5048,23 +5052,23 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>WSH ML</t>
+          <t>IND ML</t>
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.3644</v>
+        <v>0.4075</v>
       </c>
       <c r="G62" s="13" t="n">
-        <v>0.3571</v>
+        <v>0.4</v>
       </c>
       <c r="H62" s="13" t="n">
-        <v>0.0072</v>
+        <v>0.0074</v>
       </c>
       <c r="I62" s="13" t="n">
-        <v>0.02017226062420963</v>
+        <v>0.01851461403901522</v>
       </c>
       <c r="J62" s="14" t="n">
         <v>0.5</v>
@@ -5124,7 +5128,7 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>CHI @ CAR</t>
+          <t>WSH @ BAL</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
@@ -5134,28 +5138,32 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>CAR ML</t>
+          <t>BAL ML</t>
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>120</v>
+        <v>-148</v>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.4602</v>
+        <v>0.6032</v>
       </c>
       <c r="G64" s="13" t="n">
-        <v>0.4545</v>
+        <v>0.5968</v>
       </c>
       <c r="H64" s="13" t="n">
-        <v>0.0057</v>
+        <v>0.0064</v>
       </c>
       <c r="I64" s="13" t="n">
-        <v>0.01241887614461901</v>
+        <v>0.01075463493612738</v>
       </c>
       <c r="J64" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K64" s="5" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -5165,42 +5173,38 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>CIN @ PHI</t>
+          <t>WSH @ PHI</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>CIN +3</t>
+          <t>WSH ML</t>
         </is>
       </c>
       <c r="E65" s="7" t="n">
-        <v>-112</v>
+        <v>180</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>0.5339</v>
+        <v>0.363</v>
       </c>
       <c r="G65" s="8" t="n">
-        <v>0.5283</v>
+        <v>0.3571</v>
       </c>
       <c r="H65" s="8" t="n">
-        <v>0.0056</v>
+        <v>0.0058</v>
       </c>
       <c r="I65" s="8" t="n">
-        <v>0.009814316337750095</v>
+        <v>0.01629898461556178</v>
       </c>
       <c r="J65" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K65" s="4" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K65" s="4" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -5215,28 +5219,28 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>CAR +2.5</t>
+          <t>CAR ML</t>
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>-102</v>
+        <v>120</v>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.5103</v>
+        <v>0.4602</v>
       </c>
       <c r="G66" s="13" t="n">
-        <v>0.505</v>
+        <v>0.4545</v>
       </c>
       <c r="H66" s="13" t="n">
-        <v>0.0053</v>
+        <v>0.0057</v>
       </c>
       <c r="I66" s="13" t="n">
-        <v>0.01058349168961248</v>
+        <v>0.01241887614461901</v>
       </c>
       <c r="J66" s="14" t="n">
         <v>0.5</v>
@@ -5251,42 +5255,38 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>TB @ JAX</t>
+          <t>CHI @ CAR</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>JAX ML</t>
+          <t>CAR +2.5</t>
         </is>
       </c>
       <c r="E67" s="7" t="n">
-        <v>105</v>
+        <v>-102</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>0.4928</v>
+        <v>0.5103</v>
       </c>
       <c r="G67" s="8" t="n">
-        <v>0.4878</v>
+        <v>0.505</v>
       </c>
       <c r="H67" s="8" t="n">
-        <v>0.005</v>
+        <v>0.0053</v>
       </c>
       <c r="I67" s="8" t="n">
-        <v>0.01023043510877542</v>
+        <v>0.01058349168961248</v>
       </c>
       <c r="J67" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K67" s="4" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K67" s="4" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>MIA @ LV</t>
+          <t>TB @ JAX</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
@@ -5306,28 +5306,32 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>MIA ML</t>
+          <t>JAX ML</t>
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>170</v>
+        <v>105</v>
       </c>
       <c r="F68" s="13" t="n">
-        <v>0.3747</v>
+        <v>0.4928</v>
       </c>
       <c r="G68" s="13" t="n">
-        <v>0.3704</v>
+        <v>0.4878</v>
       </c>
       <c r="H68" s="13" t="n">
-        <v>0.0043</v>
+        <v>0.005</v>
       </c>
       <c r="I68" s="13" t="n">
-        <v>0.01145619582939239</v>
+        <v>0.01023043510877542</v>
       </c>
       <c r="J68" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K68" s="5" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K68" s="5" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
@@ -5337,33 +5341,33 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>PIT @ BUF</t>
+          <t>CIN @ PHI</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>BUF ML</t>
+          <t>CIN +3</t>
         </is>
       </c>
       <c r="E69" s="7" t="n">
-        <v>-135</v>
+        <v>-112</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>0.5785</v>
+        <v>0.5327</v>
       </c>
       <c r="G69" s="8" t="n">
-        <v>0.5745</v>
+        <v>0.5283</v>
       </c>
       <c r="H69" s="8" t="n">
-        <v>0.0041</v>
+        <v>0.0044</v>
       </c>
       <c r="I69" s="8" t="n">
-        <v>0.007027298660423897</v>
+        <v>0.007795131746541006</v>
       </c>
       <c r="J69" s="10" t="n">
         <v>0.15</v>
@@ -5382,33 +5386,33 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>BAL @ IND</t>
+          <t>MIA @ LV</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>IND +3.5</t>
+          <t>MIA ML</t>
         </is>
       </c>
       <c r="E70" s="12" t="n">
-        <v>-112</v>
+        <v>170</v>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.5306999999999999</v>
+        <v>0.3747</v>
       </c>
       <c r="G70" s="13" t="n">
-        <v>0.5283</v>
+        <v>0.3704</v>
       </c>
       <c r="H70" s="13" t="n">
-        <v>0.0024</v>
+        <v>0.0043</v>
       </c>
       <c r="I70" s="13" t="n">
-        <v>0.004522928097008994</v>
+        <v>0.01145619582939239</v>
       </c>
       <c r="J70" s="14" t="n">
         <v>0.5</v>
@@ -5423,33 +5427,33 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>TB @ JAX</t>
+          <t>PIT @ BUF</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>JAX +1.5</t>
+          <t>BUF ML</t>
         </is>
       </c>
       <c r="E71" s="7" t="n">
-        <v>-110</v>
+        <v>-135</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>0.5245</v>
+        <v>0.5785</v>
       </c>
       <c r="G71" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5745</v>
       </c>
       <c r="H71" s="8" t="n">
-        <v>0.0007</v>
+        <v>0.0041</v>
       </c>
       <c r="I71" s="8" t="n">
-        <v>0.001375866034897644</v>
+        <v>0.007027298660423897</v>
       </c>
       <c r="J71" s="10" t="n">
         <v>0.15</v>
@@ -5468,7 +5472,7 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>SF @ LAR</t>
+          <t>BAL @ IND</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
@@ -5478,23 +5482,23 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>SF +3.5</t>
+          <t>IND +3.5</t>
         </is>
       </c>
       <c r="E72" s="12" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.5235</v>
+        <v>0.5306999999999999</v>
       </c>
       <c r="G72" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5283</v>
       </c>
       <c r="H72" s="13" t="n">
-        <v>-0.0004</v>
+        <v>0.0024</v>
       </c>
       <c r="I72" s="13" t="n">
-        <v>-0.0006859452100267949</v>
+        <v>0.004522928097008994</v>
       </c>
       <c r="J72" s="14" t="n">
         <v>0.5</v>
@@ -5509,7 +5513,7 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>SF @ LV</t>
+          <t>TB @ JAX</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -5519,23 +5523,23 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>SF +2.5</t>
+          <t>JAX +1.5</t>
         </is>
       </c>
       <c r="E73" s="7" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>0.5343</v>
+        <v>0.5245</v>
       </c>
       <c r="G73" s="8" t="n">
-        <v>0.5349</v>
+        <v>0.5238</v>
       </c>
       <c r="H73" s="8" t="n">
-        <v>-0.0005</v>
+        <v>0.0007</v>
       </c>
       <c r="I73" s="8" t="n">
-        <v>-0.001019663556231232</v>
+        <v>0.001375866034897644</v>
       </c>
       <c r="J73" s="10" t="n">
         <v>0.15</v>
@@ -5554,42 +5558,38 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>HOU @ CAR</t>
+          <t>SF @ LAR</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>CAR ML</t>
+          <t>SF +3.5</t>
         </is>
       </c>
       <c r="E74" s="12" t="n">
-        <v>114</v>
+        <v>-110</v>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.4668</v>
+        <v>0.5235</v>
       </c>
       <c r="G74" s="13" t="n">
-        <v>0.4673</v>
+        <v>0.5238</v>
       </c>
       <c r="H74" s="13" t="n">
-        <v>-0.0005</v>
+        <v>-0.0004</v>
       </c>
       <c r="I74" s="13" t="n">
-        <v>-0.0009722273621682875</v>
+        <v>-0.0006859452100267949</v>
       </c>
       <c r="J74" s="14" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K74" s="5" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K74" s="5" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>NYJ @ TEN</t>
+          <t>SF @ LV</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -5609,28 +5609,32 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>TEN -3</t>
+          <t>SF +2.5</t>
         </is>
       </c>
       <c r="E75" s="7" t="n">
-        <v>100</v>
+        <v>-115</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>0.4992</v>
+        <v>0.5343</v>
       </c>
       <c r="G75" s="8" t="n">
-        <v>0.5</v>
+        <v>0.5349</v>
       </c>
       <c r="H75" s="8" t="n">
-        <v>-0.0008</v>
+        <v>-0.0005</v>
       </c>
       <c r="I75" s="8" t="n">
-        <v>-0.00155002925296932</v>
+        <v>-0.001019663556231232</v>
       </c>
       <c r="J75" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K75" s="4" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K75" s="4" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
@@ -5640,33 +5644,33 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>NE @ SEA</t>
+          <t>NYJ @ TEN</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Under 44.5</t>
+          <t>TEN -3</t>
         </is>
       </c>
       <c r="E76" s="12" t="n">
-        <v>-110</v>
+        <v>100</v>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.5229</v>
+        <v>0.4992</v>
       </c>
       <c r="G76" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5</v>
       </c>
       <c r="H76" s="13" t="n">
-        <v>-0.001</v>
+        <v>-0.0008</v>
       </c>
       <c r="I76" s="13" t="n">
-        <v>-0.001817132797922338</v>
+        <v>-0.00155002925296932</v>
       </c>
       <c r="J76" s="14" t="n">
         <v>0.5</v>
@@ -5681,42 +5685,38 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>WSH @ BAL</t>
+          <t>BUF @ HOU</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>BAL ML</t>
+          <t>Over 44.5</t>
         </is>
       </c>
       <c r="E77" s="7" t="n">
-        <v>-166</v>
+        <v>-110</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>0.623</v>
+        <v>0.5229</v>
       </c>
       <c r="G77" s="8" t="n">
-        <v>0.6241</v>
+        <v>0.5238</v>
       </c>
       <c r="H77" s="8" t="n">
-        <v>-0.0011</v>
+        <v>-0.0009</v>
       </c>
       <c r="I77" s="8" t="n">
-        <v>-0.001696228641810238</v>
+        <v>-0.001810501477686022</v>
       </c>
       <c r="J77" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K77" s="4" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K77" s="4" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
@@ -5726,42 +5726,38 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>SF @ LV</t>
+          <t>NE @ SEA</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>SF ML</t>
+          <t>Under 44.5</t>
         </is>
       </c>
       <c r="E78" s="12" t="n">
-        <v>105</v>
+        <v>-110</v>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.4855</v>
+        <v>0.5229</v>
       </c>
       <c r="G78" s="13" t="n">
-        <v>0.4878</v>
+        <v>0.5238</v>
       </c>
       <c r="H78" s="13" t="n">
-        <v>-0.0023</v>
+        <v>-0.001</v>
       </c>
       <c r="I78" s="13" t="n">
-        <v>-0.004623943048392753</v>
+        <v>-0.001817132797922338</v>
       </c>
       <c r="J78" s="14" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K78" s="5" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K78" s="5" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -5771,38 +5767,42 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>WSH @ PHI</t>
+          <t>SF @ LV</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>WSH +4.5</t>
+          <t>SF ML</t>
         </is>
       </c>
       <c r="E79" s="7" t="n">
-        <v>-110</v>
+        <v>105</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>0.5211</v>
+        <v>0.4855</v>
       </c>
       <c r="G79" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.4878</v>
       </c>
       <c r="H79" s="8" t="n">
-        <v>-0.0027</v>
+        <v>-0.0023</v>
       </c>
       <c r="I79" s="8" t="n">
-        <v>-0.005232732731691669</v>
+        <v>-0.004623943048392753</v>
       </c>
       <c r="J79" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K79" s="4" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K79" s="4" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>BUF @ HOU</t>
+          <t>DEN @ KC</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Over 44.5</t>
+          <t>Under 42.5</t>
         </is>
       </c>
       <c r="E80" s="12" t="n">
@@ -5838,7 +5838,7 @@
         <v>-0.0035</v>
       </c>
       <c r="I80" s="13" t="n">
-        <v>-0.006648938044830577</v>
+        <v>-0.006661412687633483</v>
       </c>
       <c r="J80" s="14" t="n">
         <v>0.5</v>
@@ -5853,38 +5853,42 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>DEN @ KC</t>
+          <t>HOU @ CAR</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Under 42.5</t>
+          <t>CAR ML</t>
         </is>
       </c>
       <c r="E81" s="7" t="n">
-        <v>-110</v>
+        <v>114</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>0.5203</v>
+        <v>0.4637</v>
       </c>
       <c r="G81" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.4673</v>
       </c>
       <c r="H81" s="8" t="n">
-        <v>-0.0035</v>
+        <v>-0.0036</v>
       </c>
       <c r="I81" s="8" t="n">
-        <v>-0.006661412687633483</v>
+        <v>-0.007550149574790499</v>
       </c>
       <c r="J81" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K81" s="4" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K81" s="4" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
@@ -5894,7 +5898,7 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>GB @ MIN</t>
+          <t>WSH @ PHI</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
@@ -5904,23 +5908,23 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>MIN -1.5</t>
+          <t>WSH +4.5</t>
         </is>
       </c>
       <c r="E82" s="12" t="n">
-        <v>-102</v>
+        <v>-110</v>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.5004</v>
+        <v>0.5196</v>
       </c>
       <c r="G82" s="13" t="n">
-        <v>0.505</v>
+        <v>0.5238</v>
       </c>
       <c r="H82" s="13" t="n">
-        <v>-0.0045</v>
+        <v>-0.0042</v>
       </c>
       <c r="I82" s="13" t="n">
-        <v>-0.008925859351553045</v>
+        <v>-0.007986771548511018</v>
       </c>
       <c r="J82" s="14" t="n">
         <v>0.5</v>
@@ -5935,33 +5939,33 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>TB @ CIN</t>
+          <t>GB @ MIN</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>TB ML</t>
+          <t>MIN -1.5</t>
         </is>
       </c>
       <c r="E83" s="7" t="n">
-        <v>164</v>
+        <v>-102</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>0.3734</v>
+        <v>0.5004</v>
       </c>
       <c r="G83" s="8" t="n">
-        <v>0.3788</v>
+        <v>0.505</v>
       </c>
       <c r="H83" s="8" t="n">
-        <v>-0.0054</v>
+        <v>-0.0045</v>
       </c>
       <c r="I83" s="8" t="n">
-        <v>-0.0142155900834755</v>
+        <v>-0.008925859351553045</v>
       </c>
       <c r="J83" s="10" t="n">
         <v>0.5</v>
@@ -5976,7 +5980,7 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>NYJ @ TEN</t>
+          <t>TB @ CIN</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
@@ -5986,23 +5990,23 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>TEN ML</t>
+          <t>TB ML</t>
         </is>
       </c>
       <c r="E84" s="12" t="n">
-        <v>-148</v>
+        <v>164</v>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.589</v>
+        <v>0.3734</v>
       </c>
       <c r="G84" s="13" t="n">
-        <v>0.5968</v>
+        <v>0.3788</v>
       </c>
       <c r="H84" s="13" t="n">
-        <v>-0.0078</v>
+        <v>-0.0054</v>
       </c>
       <c r="I84" s="13" t="n">
-        <v>-0.01298082351031937</v>
+        <v>-0.0142155900834755</v>
       </c>
       <c r="J84" s="14" t="n">
         <v>0.5</v>
@@ -6017,42 +6021,38 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>WSH @ BAL</t>
+          <t>NYJ @ TEN</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>BAL -3.5</t>
+          <t>TEN ML</t>
         </is>
       </c>
       <c r="E85" s="7" t="n">
-        <v>-105</v>
+        <v>-148</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>0.5041</v>
+        <v>0.589</v>
       </c>
       <c r="G85" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.5968</v>
       </c>
       <c r="H85" s="8" t="n">
-        <v>-0.008</v>
+        <v>-0.0078</v>
       </c>
       <c r="I85" s="8" t="n">
-        <v>-0.01582927786255423</v>
+        <v>-0.01298082351031937</v>
       </c>
       <c r="J85" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K85" s="4" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K85" s="4" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
@@ -6185,42 +6185,38 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>HOU @ CAR</t>
+          <t>ATL @ PIT</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>CAR +2.5</t>
+          <t>ATL ML</t>
         </is>
       </c>
       <c r="E89" s="7" t="n">
-        <v>-115</v>
+        <v>145</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>0.5225</v>
+        <v>0.3952</v>
       </c>
       <c r="G89" s="8" t="n">
-        <v>0.5349</v>
+        <v>0.4082</v>
       </c>
       <c r="H89" s="8" t="n">
-        <v>-0.0122</v>
+        <v>-0.0127</v>
       </c>
       <c r="I89" s="8" t="n">
-        <v>-0.02314959152635626</v>
+        <v>-0.03150835492349835</v>
       </c>
       <c r="J89" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K89" s="4" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K89" s="4" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
@@ -6230,33 +6226,33 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>ATL @ PIT</t>
+          <t>TB @ CIN</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>ATL ML</t>
+          <t>TB +3.5</t>
         </is>
       </c>
       <c r="E90" s="12" t="n">
-        <v>145</v>
+        <v>-105</v>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.3952</v>
+        <v>0.4981</v>
       </c>
       <c r="G90" s="13" t="n">
-        <v>0.4082</v>
+        <v>0.5122</v>
       </c>
       <c r="H90" s="13" t="n">
-        <v>-0.0127</v>
+        <v>-0.0138</v>
       </c>
       <c r="I90" s="13" t="n">
-        <v>-0.03150835492349835</v>
+        <v>-0.0275697342050793</v>
       </c>
       <c r="J90" s="14" t="n">
         <v>0.5</v>
@@ -6271,7 +6267,7 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>TB @ CIN</t>
+          <t>HOU @ CAR</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -6281,28 +6277,32 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>TB +3.5</t>
+          <t>CAR +2.5</t>
         </is>
       </c>
       <c r="E91" s="7" t="n">
-        <v>-105</v>
+        <v>-115</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>0.4981</v>
+        <v>0.5194</v>
       </c>
       <c r="G91" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.5349</v>
       </c>
       <c r="H91" s="8" t="n">
-        <v>-0.0138</v>
+        <v>-0.015</v>
       </c>
       <c r="I91" s="8" t="n">
-        <v>-0.0275697342050793</v>
+        <v>-0.02886448961825583</v>
       </c>
       <c r="J91" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K91" s="4" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K91" s="4" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
@@ -6517,33 +6517,33 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>BUF @ HOU</t>
+          <t>DAL @ NYG</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>BUF ML</t>
+          <t>DAL -2.5</t>
         </is>
       </c>
       <c r="E97" s="7" t="n">
-        <v>-118</v>
+        <v>-115</v>
       </c>
       <c r="F97" s="8" t="n">
-        <v>0.5211</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="G97" s="8" t="n">
-        <v>0.5413</v>
+        <v>0.5349</v>
       </c>
       <c r="H97" s="8" t="n">
         <v>-0.0194</v>
       </c>
       <c r="I97" s="8" t="n">
-        <v>-0.03702997621180176</v>
+        <v>-0.0378586986429581</v>
       </c>
       <c r="J97" s="10" t="n">
         <v>0.5</v>
@@ -6558,33 +6558,33 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>DAL @ NYG</t>
+          <t>DET @ BUF</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>DAL -2.5</t>
+          <t>BUF ML</t>
         </is>
       </c>
       <c r="E98" s="12" t="n">
-        <v>-115</v>
+        <v>-162</v>
       </c>
       <c r="F98" s="13" t="n">
-        <v>0.5145999999999999</v>
+        <v>0.5975</v>
       </c>
       <c r="G98" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.6183</v>
       </c>
       <c r="H98" s="13" t="n">
-        <v>-0.0194</v>
+        <v>-0.0199</v>
       </c>
       <c r="I98" s="13" t="n">
-        <v>-0.0378586986429581</v>
+        <v>-0.03340633720581493</v>
       </c>
       <c r="J98" s="14" t="n">
         <v>0.5</v>
@@ -6609,23 +6609,23 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>BUF ML</t>
+          <t>DET ML</t>
         </is>
       </c>
       <c r="E99" s="7" t="n">
-        <v>-162</v>
+        <v>136</v>
       </c>
       <c r="F99" s="8" t="n">
-        <v>0.5975</v>
+        <v>0.4025</v>
       </c>
       <c r="G99" s="8" t="n">
-        <v>0.6183</v>
+        <v>0.4237</v>
       </c>
       <c r="H99" s="8" t="n">
-        <v>-0.0199</v>
+        <v>-0.0202</v>
       </c>
       <c r="I99" s="8" t="n">
-        <v>-0.03340633720581493</v>
+        <v>-0.04962516856208898</v>
       </c>
       <c r="J99" s="10" t="n">
         <v>0.5</v>
@@ -6640,33 +6640,33 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>DET @ BUF</t>
+          <t>BUF @ HOU</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>DET ML</t>
+          <t>HOU +1.5</t>
         </is>
       </c>
       <c r="E100" s="12" t="n">
-        <v>136</v>
+        <v>-115</v>
       </c>
       <c r="F100" s="13" t="n">
-        <v>0.4025</v>
+        <v>0.5134</v>
       </c>
       <c r="G100" s="13" t="n">
-        <v>0.4237</v>
+        <v>0.5349</v>
       </c>
       <c r="H100" s="13" t="n">
-        <v>-0.0202</v>
+        <v>-0.0205</v>
       </c>
       <c r="I100" s="13" t="n">
-        <v>-0.04962516856208898</v>
+        <v>-0.04024554521808849</v>
       </c>
       <c r="J100" s="14" t="n">
         <v>0.5</v>
@@ -6686,28 +6686,28 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>BUF -1.5</t>
+          <t>HOU ML</t>
         </is>
       </c>
       <c r="E101" s="7" t="n">
-        <v>-105</v>
+        <v>-102</v>
       </c>
       <c r="F101" s="8" t="n">
-        <v>0.4906</v>
+        <v>0.483</v>
       </c>
       <c r="G101" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.505</v>
       </c>
       <c r="H101" s="8" t="n">
-        <v>-0.0205</v>
+        <v>-0.0209</v>
       </c>
       <c r="I101" s="8" t="n">
-        <v>-0.04212760260498499</v>
+        <v>-0.04316351477081548</v>
       </c>
       <c r="J101" s="10" t="n">
         <v>0.5</v>
@@ -6809,28 +6809,28 @@
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>HOU +1.5</t>
+          <t>BUF ML</t>
         </is>
       </c>
       <c r="E104" s="12" t="n">
-        <v>-115</v>
+        <v>-118</v>
       </c>
       <c r="F104" s="13" t="n">
-        <v>0.5094</v>
+        <v>0.517</v>
       </c>
       <c r="G104" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.5413</v>
       </c>
       <c r="H104" s="13" t="n">
-        <v>-0.0238</v>
+        <v>-0.0228</v>
       </c>
       <c r="I104" s="13" t="n">
-        <v>-0.04767632539522654</v>
+        <v>-0.04438412363015121</v>
       </c>
       <c r="J104" s="14" t="n">
         <v>0.5</v>
@@ -6850,28 +6850,28 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>HOU ML</t>
+          <t>BUF -1.5</t>
         </is>
       </c>
       <c r="E105" s="7" t="n">
-        <v>-102</v>
+        <v>-105</v>
       </c>
       <c r="F105" s="8" t="n">
-        <v>0.4789</v>
+        <v>0.4866</v>
       </c>
       <c r="G105" s="8" t="n">
-        <v>0.505</v>
+        <v>0.5122</v>
       </c>
       <c r="H105" s="8" t="n">
-        <v>-0.0242</v>
+        <v>-0.0239</v>
       </c>
       <c r="I105" s="8" t="n">
-        <v>-0.05104746769846191</v>
+        <v>-0.04988754247989219</v>
       </c>
       <c r="J105" s="10" t="n">
         <v>0.5</v>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>DET @ BUF</t>
+          <t>HOU @ CAR</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
@@ -7224,28 +7224,32 @@
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>DET +3</t>
+          <t>HOU -2.5</t>
         </is>
       </c>
       <c r="E114" s="12" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="F114" s="13" t="n">
-        <v>0.4921</v>
+        <v>0.4806</v>
       </c>
       <c r="G114" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5122</v>
       </c>
       <c r="H114" s="13" t="n">
         <v>-0.0286</v>
       </c>
       <c r="I114" s="13" t="n">
-        <v>-0.05622902500539134</v>
+        <v>-0.06177274229234198</v>
       </c>
       <c r="J114" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K114" s="5" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K114" s="5" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
@@ -7255,7 +7259,7 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>TB @ CIN</t>
+          <t>DET @ BUF</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
@@ -7265,23 +7269,23 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>CIN -3.5</t>
+          <t>DET +3</t>
         </is>
       </c>
       <c r="E115" s="7" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="F115" s="8" t="n">
-        <v>0.5019</v>
+        <v>0.4921</v>
       </c>
       <c r="G115" s="8" t="n">
-        <v>0.5349</v>
+        <v>0.5238</v>
       </c>
       <c r="H115" s="8" t="n">
-        <v>-0.0295</v>
+        <v>-0.0286</v>
       </c>
       <c r="I115" s="8" t="n">
-        <v>-0.06161668081952648</v>
+        <v>-0.05622902500539134</v>
       </c>
       <c r="J115" s="10" t="n">
         <v>0.5</v>
@@ -7296,7 +7300,7 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>HOU @ CAR</t>
+          <t>TB @ CIN</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
@@ -7306,32 +7310,28 @@
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>HOU -2.5</t>
+          <t>CIN -3.5</t>
         </is>
       </c>
       <c r="E116" s="12" t="n">
-        <v>-105</v>
+        <v>-115</v>
       </c>
       <c r="F116" s="13" t="n">
-        <v>0.4775</v>
+        <v>0.5019</v>
       </c>
       <c r="G116" s="13" t="n">
-        <v>0.5122</v>
+        <v>0.5349</v>
       </c>
       <c r="H116" s="13" t="n">
-        <v>-0.0307</v>
+        <v>-0.0295</v>
       </c>
       <c r="I116" s="13" t="n">
-        <v>-0.06774079201621941</v>
+        <v>-0.06161668081952648</v>
       </c>
       <c r="J116" s="14" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K116" s="5" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K116" s="5" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>GB @ MIN</t>
+          <t>HOU @ CAR</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
@@ -7474,28 +7474,32 @@
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>GB ML</t>
+          <t>HOU ML</t>
         </is>
       </c>
       <c r="E120" s="12" t="n">
-        <v>-102</v>
+        <v>-135</v>
       </c>
       <c r="F120" s="13" t="n">
-        <v>0.4667</v>
+        <v>0.5363</v>
       </c>
       <c r="G120" s="13" t="n">
-        <v>0.505</v>
+        <v>0.5745</v>
       </c>
       <c r="H120" s="13" t="n">
-        <v>-0.0331</v>
+        <v>-0.033</v>
       </c>
       <c r="I120" s="13" t="n">
-        <v>-0.07501174777919262</v>
+        <v>-0.06589652820444242</v>
       </c>
       <c r="J120" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K120" s="5" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K120" s="5" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
@@ -7505,42 +7509,38 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>WSH @ BAL</t>
+          <t>GB @ MIN</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>WSH +3.5</t>
+          <t>GB ML</t>
         </is>
       </c>
       <c r="E121" s="7" t="n">
-        <v>-115</v>
+        <v>-102</v>
       </c>
       <c r="F121" s="8" t="n">
-        <v>0.4959</v>
+        <v>0.4667</v>
       </c>
       <c r="G121" s="8" t="n">
-        <v>0.5349</v>
+        <v>0.505</v>
       </c>
       <c r="H121" s="8" t="n">
-        <v>-0.0335</v>
+        <v>-0.0331</v>
       </c>
       <c r="I121" s="8" t="n">
-        <v>-0.07285913265123395</v>
+        <v>-0.07501174777919262</v>
       </c>
       <c r="J121" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K121" s="4" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K121" s="4" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>WSH @ BAL</t>
+          <t>SF @ LV</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
@@ -7601,23 +7601,23 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>WSH ML</t>
+          <t>LV ML</t>
         </is>
       </c>
       <c r="E123" s="7" t="n">
-        <v>140</v>
+        <v>-125</v>
       </c>
       <c r="F123" s="8" t="n">
-        <v>0.377</v>
+        <v>0.5145</v>
       </c>
       <c r="G123" s="8" t="n">
-        <v>0.4167</v>
+        <v>0.5556</v>
       </c>
       <c r="H123" s="8" t="n">
-        <v>-0.034</v>
+        <v>-0.0348</v>
       </c>
       <c r="I123" s="8" t="n">
-        <v>-0.09437665434752285</v>
+        <v>-0.07328755549361393</v>
       </c>
       <c r="J123" s="10" t="n">
         <v>0.15</v>
@@ -7636,42 +7636,38 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>SF @ LV</t>
+          <t>GB @ MIN</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>LV ML</t>
+          <t>GB +1.5</t>
         </is>
       </c>
       <c r="E124" s="12" t="n">
-        <v>-125</v>
+        <v>-118</v>
       </c>
       <c r="F124" s="13" t="n">
-        <v>0.5145</v>
+        <v>0.4996</v>
       </c>
       <c r="G124" s="13" t="n">
-        <v>0.5556</v>
+        <v>0.5413</v>
       </c>
       <c r="H124" s="13" t="n">
-        <v>-0.0348</v>
+        <v>-0.0352</v>
       </c>
       <c r="I124" s="13" t="n">
-        <v>-0.07328755549361393</v>
+        <v>-0.07709030841831122</v>
       </c>
       <c r="J124" s="14" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K124" s="5" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K124" s="5" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
@@ -7681,42 +7677,38 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>HOU @ CAR</t>
+          <t>WSH @ PHI</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>HOU ML</t>
+          <t>PHI -4.5</t>
         </is>
       </c>
       <c r="E125" s="7" t="n">
-        <v>-135</v>
+        <v>-110</v>
       </c>
       <c r="F125" s="8" t="n">
-        <v>0.5332</v>
+        <v>0.4804</v>
       </c>
       <c r="G125" s="8" t="n">
-        <v>0.5745</v>
+        <v>0.5238</v>
       </c>
       <c r="H125" s="8" t="n">
-        <v>-0.035</v>
+        <v>-0.0362</v>
       </c>
       <c r="I125" s="8" t="n">
-        <v>-0.07124670750056644</v>
+        <v>-0.08292231936057987</v>
       </c>
       <c r="J125" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K125" s="4" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K125" s="4" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
@@ -7726,33 +7718,33 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>GB @ MIN</t>
+          <t>DEN @ KC</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>GB +1.5</t>
+          <t>Over 42.5</t>
         </is>
       </c>
       <c r="E126" s="12" t="n">
-        <v>-118</v>
+        <v>-110</v>
       </c>
       <c r="F126" s="13" t="n">
-        <v>0.4996</v>
+        <v>0.4797</v>
       </c>
       <c r="G126" s="13" t="n">
-        <v>0.5413</v>
+        <v>0.5238</v>
       </c>
       <c r="H126" s="13" t="n">
-        <v>-0.0352</v>
+        <v>-0.0366</v>
       </c>
       <c r="I126" s="13" t="n">
-        <v>-0.07709030841831122</v>
+        <v>-0.08424767822145734</v>
       </c>
       <c r="J126" s="14" t="n">
         <v>0.5</v>
@@ -7767,33 +7759,33 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>BUF @ HOU</t>
+          <t>NYJ @ TEN</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Under 44.5</t>
+          <t>NYJ +3</t>
         </is>
       </c>
       <c r="E127" s="7" t="n">
-        <v>-110</v>
+        <v>-120</v>
       </c>
       <c r="F127" s="8" t="n">
-        <v>0.4797</v>
+        <v>0.5008</v>
       </c>
       <c r="G127" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5455</v>
       </c>
       <c r="H127" s="8" t="n">
-        <v>-0.0366</v>
+        <v>-0.0369</v>
       </c>
       <c r="I127" s="8" t="n">
-        <v>-0.08426015286426025</v>
+        <v>-0.07589832569976962</v>
       </c>
       <c r="J127" s="10" t="n">
         <v>0.5</v>
@@ -7808,38 +7800,42 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>DEN @ KC</t>
+          <t>PIT @ BUF</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>Over 42.5</t>
+          <t>PIT ML</t>
         </is>
       </c>
       <c r="E128" s="12" t="n">
-        <v>-110</v>
+        <v>114</v>
       </c>
       <c r="F128" s="13" t="n">
-        <v>0.4797</v>
+        <v>0.4215</v>
       </c>
       <c r="G128" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.4673</v>
       </c>
       <c r="H128" s="13" t="n">
-        <v>-0.0366</v>
+        <v>-0.0375</v>
       </c>
       <c r="I128" s="13" t="n">
-        <v>-0.08424767822145734</v>
+        <v>-0.09721980889612331</v>
       </c>
       <c r="J128" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K128" s="5" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K128" s="5" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
@@ -7849,7 +7845,7 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>NYJ @ TEN</t>
+          <t>SF @ LV</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
@@ -7859,28 +7855,32 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>NYJ +3</t>
+          <t>LV -2.5</t>
         </is>
       </c>
       <c r="E129" s="7" t="n">
-        <v>-120</v>
+        <v>-105</v>
       </c>
       <c r="F129" s="8" t="n">
-        <v>0.5008</v>
+        <v>0.4657</v>
       </c>
       <c r="G129" s="8" t="n">
-        <v>0.5455</v>
+        <v>0.5122</v>
       </c>
       <c r="H129" s="8" t="n">
-        <v>-0.0369</v>
+        <v>-0.0379</v>
       </c>
       <c r="I129" s="8" t="n">
-        <v>-0.07589832569976962</v>
+        <v>-0.09085100472477742</v>
       </c>
       <c r="J129" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K129" s="4" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K129" s="4" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
@@ -7890,33 +7890,33 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>WSH @ PHI</t>
+          <t>NE @ SEA</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>PHI -4.5</t>
+          <t>Over 44.5</t>
         </is>
       </c>
       <c r="E130" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F130" s="13" t="n">
-        <v>0.4789</v>
+        <v>0.4771</v>
       </c>
       <c r="G130" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H130" s="13" t="n">
-        <v>-0.037</v>
+        <v>-0.038</v>
       </c>
       <c r="I130" s="13" t="n">
-        <v>-0.08567635817739921</v>
+        <v>-0.08909195811116855</v>
       </c>
       <c r="J130" s="14" t="n">
         <v>0.5</v>
@@ -7931,42 +7931,38 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>PIT @ BUF</t>
+          <t>BUF @ HOU</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>PIT ML</t>
+          <t>Under 44.5</t>
         </is>
       </c>
       <c r="E131" s="7" t="n">
-        <v>114</v>
+        <v>-110</v>
       </c>
       <c r="F131" s="8" t="n">
-        <v>0.4215</v>
+        <v>0.4771</v>
       </c>
       <c r="G131" s="8" t="n">
-        <v>0.4673</v>
+        <v>0.5238</v>
       </c>
       <c r="H131" s="8" t="n">
-        <v>-0.0375</v>
+        <v>-0.038</v>
       </c>
       <c r="I131" s="8" t="n">
-        <v>-0.09721980889612331</v>
+        <v>-0.08909858943140481</v>
       </c>
       <c r="J131" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K131" s="4" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K131" s="4" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
@@ -7976,42 +7972,38 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>SF @ LV</t>
+          <t>MIA @ LV</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>LV -2.5</t>
+          <t>LV ML</t>
         </is>
       </c>
       <c r="E132" s="12" t="n">
-        <v>-105</v>
+        <v>-205</v>
       </c>
       <c r="F132" s="13" t="n">
-        <v>0.4657</v>
+        <v>0.6253</v>
       </c>
       <c r="G132" s="13" t="n">
-        <v>0.5122</v>
+        <v>0.6721</v>
       </c>
       <c r="H132" s="13" t="n">
-        <v>-0.0379</v>
+        <v>-0.038</v>
       </c>
       <c r="I132" s="13" t="n">
-        <v>-0.09085100472477742</v>
+        <v>-0.06900228481403581</v>
       </c>
       <c r="J132" s="14" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K132" s="5" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K132" s="5" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
@@ -8021,33 +8013,33 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>NE @ SEA</t>
+          <t>CHI @ CAR</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Over 44.5</t>
+          <t>CHI ML</t>
         </is>
       </c>
       <c r="E133" s="7" t="n">
-        <v>-110</v>
+        <v>-142</v>
       </c>
       <c r="F133" s="8" t="n">
-        <v>0.4771</v>
+        <v>0.5397999999999999</v>
       </c>
       <c r="G133" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5868</v>
       </c>
       <c r="H133" s="8" t="n">
-        <v>-0.038</v>
+        <v>-0.0381</v>
       </c>
       <c r="I133" s="8" t="n">
-        <v>-0.08909195811116855</v>
+        <v>-0.07941152255424772</v>
       </c>
       <c r="J133" s="10" t="n">
         <v>0.5</v>
@@ -8062,33 +8054,33 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>MIA @ LV</t>
+          <t>SF @ LAR</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>LV ML</t>
+          <t>LAR -3.5</t>
         </is>
       </c>
       <c r="E134" s="12" t="n">
-        <v>-205</v>
+        <v>-110</v>
       </c>
       <c r="F134" s="13" t="n">
-        <v>0.6253</v>
+        <v>0.4765</v>
       </c>
       <c r="G134" s="13" t="n">
-        <v>0.6721</v>
+        <v>0.5238</v>
       </c>
       <c r="H134" s="13" t="n">
-        <v>-0.038</v>
+        <v>-0.0383</v>
       </c>
       <c r="I134" s="13" t="n">
-        <v>-0.06900228481403581</v>
+        <v>-0.09022314569906403</v>
       </c>
       <c r="J134" s="14" t="n">
         <v>0.5</v>
@@ -8103,38 +8095,42 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>CHI @ CAR</t>
+          <t>TB @ JAX</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>CHI ML</t>
+          <t>TB -1.5</t>
         </is>
       </c>
       <c r="E135" s="7" t="n">
-        <v>-142</v>
+        <v>-110</v>
       </c>
       <c r="F135" s="8" t="n">
-        <v>0.5397999999999999</v>
+        <v>0.4755</v>
       </c>
       <c r="G135" s="8" t="n">
-        <v>0.5868</v>
+        <v>0.5238</v>
       </c>
       <c r="H135" s="8" t="n">
-        <v>-0.0381</v>
+        <v>-0.0388</v>
       </c>
       <c r="I135" s="8" t="n">
-        <v>-0.07941152255424772</v>
+        <v>-0.09228495694398847</v>
       </c>
       <c r="J135" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K135" s="4" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K135" s="4" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
@@ -8144,38 +8140,42 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>SF @ LAR</t>
+          <t>TB @ JAX</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>LAR -3.5</t>
+          <t>TB ML</t>
         </is>
       </c>
       <c r="E136" s="12" t="n">
-        <v>-110</v>
+        <v>-125</v>
       </c>
       <c r="F136" s="13" t="n">
-        <v>0.4765</v>
+        <v>0.5072</v>
       </c>
       <c r="G136" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5556</v>
       </c>
       <c r="H136" s="13" t="n">
-        <v>-0.0383</v>
+        <v>-0.0389</v>
       </c>
       <c r="I136" s="13" t="n">
-        <v>-0.09022314569906403</v>
+        <v>-0.08633046574523462</v>
       </c>
       <c r="J136" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K136" s="5" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K136" s="5" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
@@ -8185,42 +8185,38 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>TB @ JAX</t>
+          <t>WSH @ PHI</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>TB -1.5</t>
+          <t>PHI ML</t>
         </is>
       </c>
       <c r="E137" s="7" t="n">
-        <v>-110</v>
+        <v>-218</v>
       </c>
       <c r="F137" s="8" t="n">
-        <v>0.4755</v>
+        <v>0.637</v>
       </c>
       <c r="G137" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.6855</v>
       </c>
       <c r="H137" s="8" t="n">
-        <v>-0.0388</v>
+        <v>-0.0389</v>
       </c>
       <c r="I137" s="8" t="n">
-        <v>-0.09228495694398847</v>
+        <v>-0.07021421185805221</v>
       </c>
       <c r="J137" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K137" s="4" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K137" s="4" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
@@ -8230,7 +8226,7 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>TB @ JAX</t>
+          <t>NE @ CLE</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
@@ -8240,23 +8236,23 @@
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>TB ML</t>
+          <t>CLE ML</t>
         </is>
       </c>
       <c r="E138" s="12" t="n">
-        <v>-125</v>
+        <v>120</v>
       </c>
       <c r="F138" s="13" t="n">
-        <v>0.5072</v>
+        <v>0.4057</v>
       </c>
       <c r="G138" s="13" t="n">
-        <v>0.5556</v>
+        <v>0.4545</v>
       </c>
       <c r="H138" s="13" t="n">
-        <v>-0.0389</v>
+        <v>-0.0391</v>
       </c>
       <c r="I138" s="13" t="n">
-        <v>-0.08633046574523462</v>
+        <v>-0.1064823744763364</v>
       </c>
       <c r="J138" s="14" t="n">
         <v>0.15</v>
@@ -8275,7 +8271,7 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>NE @ CLE</t>
+          <t>WSH @ BAL</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
@@ -8285,23 +8281,23 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>CLE ML</t>
+          <t>WSH ML</t>
         </is>
       </c>
       <c r="E139" s="7" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F139" s="8" t="n">
-        <v>0.4057</v>
+        <v>0.3968</v>
       </c>
       <c r="G139" s="8" t="n">
-        <v>0.4545</v>
+        <v>0.4464</v>
       </c>
       <c r="H139" s="8" t="n">
-        <v>-0.0391</v>
+        <v>-0.0395</v>
       </c>
       <c r="I139" s="8" t="n">
-        <v>-0.1064823744763364</v>
+        <v>-0.1103207427170217</v>
       </c>
       <c r="J139" s="10" t="n">
         <v>0.15</v>
@@ -8361,7 +8357,7 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>WSH @ PHI</t>
+          <t>BAL @ IND</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
@@ -8371,23 +8367,23 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>PHI ML</t>
+          <t>BAL ML</t>
         </is>
       </c>
       <c r="E141" s="7" t="n">
-        <v>-218</v>
+        <v>-180</v>
       </c>
       <c r="F141" s="8" t="n">
-        <v>0.6356000000000001</v>
+        <v>0.5925</v>
       </c>
       <c r="G141" s="8" t="n">
-        <v>0.6855</v>
+        <v>0.6429</v>
       </c>
       <c r="H141" s="8" t="n">
-        <v>-0.0396</v>
+        <v>-0.0398</v>
       </c>
       <c r="I141" s="8" t="n">
-        <v>-0.07223111767257701</v>
+        <v>-0.07759983246853486</v>
       </c>
       <c r="J141" s="10" t="n">
         <v>0.5</v>
@@ -8402,7 +8398,7 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>BAL @ IND</t>
+          <t>CIN @ PHI</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
@@ -8412,28 +8408,32 @@
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>BAL ML</t>
+          <t>PHI ML</t>
         </is>
       </c>
       <c r="E142" s="12" t="n">
-        <v>-180</v>
+        <v>-155</v>
       </c>
       <c r="F142" s="13" t="n">
-        <v>0.5925</v>
+        <v>0.5573</v>
       </c>
       <c r="G142" s="13" t="n">
-        <v>0.6429</v>
+        <v>0.6078</v>
       </c>
       <c r="H142" s="13" t="n">
-        <v>-0.0398</v>
+        <v>-0.0399</v>
       </c>
       <c r="I142" s="13" t="n">
-        <v>-0.07759983246853486</v>
+        <v>-0.08236139182819086</v>
       </c>
       <c r="J142" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K142" s="5" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K142" s="5" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
@@ -8488,42 +8488,38 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>CIN @ PHI</t>
+          <t>CHI @ CAR</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>PHI ML</t>
+          <t>CHI -2.5</t>
         </is>
       </c>
       <c r="E144" s="12" t="n">
-        <v>-155</v>
+        <v>-118</v>
       </c>
       <c r="F144" s="13" t="n">
-        <v>0.5562</v>
+        <v>0.4897</v>
       </c>
       <c r="G144" s="13" t="n">
-        <v>0.6078</v>
+        <v>0.5413</v>
       </c>
       <c r="H144" s="13" t="n">
         <v>-0.0404</v>
       </c>
       <c r="I144" s="13" t="n">
-        <v>-0.08413985778991712</v>
+        <v>-0.0952900873137365</v>
       </c>
       <c r="J144" s="14" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K144" s="5" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K144" s="5" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
@@ -8533,7 +8529,7 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>CHI @ CAR</t>
+          <t>CIN @ PHI</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
@@ -8543,28 +8539,32 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>CHI -2.5</t>
+          <t>PHI -3</t>
         </is>
       </c>
       <c r="E145" s="7" t="n">
-        <v>-118</v>
+        <v>-108</v>
       </c>
       <c r="F145" s="8" t="n">
-        <v>0.4897</v>
+        <v>0.4673</v>
       </c>
       <c r="G145" s="8" t="n">
-        <v>0.5413</v>
+        <v>0.5192</v>
       </c>
       <c r="H145" s="8" t="n">
-        <v>-0.0404</v>
+        <v>-0.0406</v>
       </c>
       <c r="I145" s="8" t="n">
-        <v>-0.0952900873137365</v>
+        <v>-0.09292922796816361</v>
       </c>
       <c r="J145" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K145" s="4" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K145" s="4" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>CIN @ PHI</t>
+          <t>NE @ CLE</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
@@ -8584,23 +8584,23 @@
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>PHI -3</t>
+          <t>CLE +2.5</t>
         </is>
       </c>
       <c r="E146" s="12" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="F146" s="13" t="n">
-        <v>0.4661</v>
+        <v>0.458</v>
       </c>
       <c r="G146" s="13" t="n">
-        <v>0.5192</v>
+        <v>0.5122</v>
       </c>
       <c r="H146" s="13" t="n">
-        <v>-0.0411</v>
+        <v>-0.0415</v>
       </c>
       <c r="I146" s="13" t="n">
-        <v>-0.09498749463121131</v>
+        <v>-0.1057221641419687</v>
       </c>
       <c r="J146" s="14" t="n">
         <v>0.15</v>
@@ -8619,42 +8619,38 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>NE @ CLE</t>
+          <t>SF @ LAR</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>CLE +2.5</t>
+          <t>LAR ML</t>
         </is>
       </c>
       <c r="E147" s="7" t="n">
-        <v>-105</v>
+        <v>-192</v>
       </c>
       <c r="F147" s="8" t="n">
-        <v>0.458</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="G147" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.6575</v>
       </c>
       <c r="H147" s="8" t="n">
         <v>-0.0415</v>
       </c>
       <c r="I147" s="8" t="n">
-        <v>-0.1057221641419687</v>
+        <v>-0.08170907724210463</v>
       </c>
       <c r="J147" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K147" s="4" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K147" s="4" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
@@ -8664,38 +8660,42 @@
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>SF @ LAR</t>
+          <t>WSH @ BAL</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>LAR ML</t>
+          <t>WSH +2.5</t>
         </is>
       </c>
       <c r="E148" s="12" t="n">
-        <v>-192</v>
+        <v>-102</v>
       </c>
       <c r="F148" s="13" t="n">
-        <v>0.6032999999999999</v>
+        <v>0.4497</v>
       </c>
       <c r="G148" s="13" t="n">
-        <v>0.6575</v>
+        <v>0.505</v>
       </c>
       <c r="H148" s="13" t="n">
-        <v>-0.0415</v>
+        <v>-0.042</v>
       </c>
       <c r="I148" s="13" t="n">
-        <v>-0.08170907724210463</v>
+        <v>-0.1094450571331784</v>
       </c>
       <c r="J148" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K148" s="5" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K148" s="5" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
@@ -8705,33 +8705,33 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>NO @ DET</t>
+          <t>NE @ SEA</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>DET ML</t>
+          <t>SEA -3.5</t>
         </is>
       </c>
       <c r="E149" s="7" t="n">
-        <v>-305</v>
+        <v>-105</v>
       </c>
       <c r="F149" s="8" t="n">
-        <v>0.6989</v>
+        <v>0.4569</v>
       </c>
       <c r="G149" s="8" t="n">
-        <v>0.7531</v>
+        <v>0.5122</v>
       </c>
       <c r="H149" s="8" t="n">
-        <v>-0.0415</v>
+        <v>-0.042</v>
       </c>
       <c r="I149" s="8" t="n">
-        <v>-0.07138998096726146</v>
+        <v>-0.1079997422600398</v>
       </c>
       <c r="J149" s="10" t="n">
         <v>0.5</v>
@@ -8746,33 +8746,33 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>NE @ SEA</t>
+          <t>NO @ DET</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>SEA -3.5</t>
+          <t>DET ML</t>
         </is>
       </c>
       <c r="E150" s="12" t="n">
-        <v>-105</v>
+        <v>-305</v>
       </c>
       <c r="F150" s="13" t="n">
-        <v>0.4569</v>
+        <v>0.6969</v>
       </c>
       <c r="G150" s="13" t="n">
-        <v>0.5122</v>
+        <v>0.7531</v>
       </c>
       <c r="H150" s="13" t="n">
-        <v>-0.042</v>
+        <v>-0.0424</v>
       </c>
       <c r="I150" s="13" t="n">
-        <v>-0.1079997422600398</v>
+        <v>-0.07398248680679584</v>
       </c>
       <c r="J150" s="14" t="n">
         <v>0.5</v>
@@ -8873,38 +8873,42 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>NO @ DET</t>
+          <t>NYG @ NYJ</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>DET -7</t>
+          <t>NYG ML</t>
         </is>
       </c>
       <c r="E153" s="7" t="n">
-        <v>-110</v>
+        <v>-162</v>
       </c>
       <c r="F153" s="8" t="n">
-        <v>0.4646</v>
+        <v>0.5588</v>
       </c>
       <c r="G153" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.6183</v>
       </c>
       <c r="H153" s="8" t="n">
-        <v>-0.0435</v>
+        <v>-0.0437</v>
       </c>
       <c r="I153" s="8" t="n">
-        <v>-0.1067730175746041</v>
+        <v>-0.09543527747745123</v>
       </c>
       <c r="J153" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K153" s="4" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K153" s="4" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
@@ -8919,28 +8923,28 @@
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>NYG ML</t>
+          <t>NYG -3</t>
         </is>
       </c>
       <c r="E154" s="12" t="n">
-        <v>-162</v>
+        <v>-112</v>
       </c>
       <c r="F154" s="13" t="n">
-        <v>0.5588</v>
+        <v>0.468</v>
       </c>
       <c r="G154" s="13" t="n">
-        <v>0.6183</v>
+        <v>0.5283</v>
       </c>
       <c r="H154" s="13" t="n">
-        <v>-0.0437</v>
+        <v>-0.044</v>
       </c>
       <c r="I154" s="13" t="n">
-        <v>-0.09543527747745123</v>
+        <v>-0.105995166002205</v>
       </c>
       <c r="J154" s="14" t="n">
         <v>0.15</v>
@@ -8959,7 +8963,7 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>NYG @ NYJ</t>
+          <t>PIT @ BUF</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
@@ -8969,23 +8973,23 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>NYG -3</t>
+          <t>PIT +1.5</t>
         </is>
       </c>
       <c r="E155" s="7" t="n">
-        <v>-112</v>
+        <v>-108</v>
       </c>
       <c r="F155" s="8" t="n">
-        <v>0.468</v>
+        <v>0.4586</v>
       </c>
       <c r="G155" s="8" t="n">
-        <v>0.5283</v>
+        <v>0.5192</v>
       </c>
       <c r="H155" s="8" t="n">
-        <v>-0.044</v>
+        <v>-0.0441</v>
       </c>
       <c r="I155" s="8" t="n">
-        <v>-0.105995166002205</v>
+        <v>-0.1166932684480655</v>
       </c>
       <c r="J155" s="10" t="n">
         <v>0.15</v>
@@ -9004,7 +9008,7 @@
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>PIT @ BUF</t>
+          <t>CHI @ TEN</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
@@ -9014,23 +9018,23 @@
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>PIT +1.5</t>
+          <t>TEN -3</t>
         </is>
       </c>
       <c r="E156" s="12" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="F156" s="13" t="n">
-        <v>0.4586</v>
+        <v>0.4514</v>
       </c>
       <c r="G156" s="13" t="n">
-        <v>0.5192</v>
+        <v>0.5122</v>
       </c>
       <c r="H156" s="13" t="n">
         <v>-0.0441</v>
       </c>
       <c r="I156" s="13" t="n">
-        <v>-0.1166932684480655</v>
+        <v>-0.1101885964729252</v>
       </c>
       <c r="J156" s="14" t="n">
         <v>0.15</v>
@@ -9049,42 +9053,38 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>CHI @ TEN</t>
+          <t>NE @ SEA</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>TEN -3</t>
+          <t>SEA ML</t>
         </is>
       </c>
       <c r="E157" s="7" t="n">
-        <v>-105</v>
+        <v>-180</v>
       </c>
       <c r="F157" s="8" t="n">
-        <v>0.4514</v>
+        <v>0.5823</v>
       </c>
       <c r="G157" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.6429</v>
       </c>
       <c r="H157" s="8" t="n">
         <v>-0.0441</v>
       </c>
       <c r="I157" s="8" t="n">
-        <v>-0.1101885964729252</v>
+        <v>-0.09341681268792873</v>
       </c>
       <c r="J157" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K157" s="4" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K157" s="4" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
@@ -9094,33 +9094,33 @@
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>NE @ SEA</t>
+          <t>ATL @ PIT</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>SEA ML</t>
+          <t>Under 41.5</t>
         </is>
       </c>
       <c r="E158" s="12" t="n">
-        <v>-180</v>
+        <v>-105</v>
       </c>
       <c r="F158" s="13" t="n">
-        <v>0.5823</v>
+        <v>0.4507</v>
       </c>
       <c r="G158" s="13" t="n">
-        <v>0.6429</v>
+        <v>0.5122</v>
       </c>
       <c r="H158" s="13" t="n">
-        <v>-0.0441</v>
+        <v>-0.0444</v>
       </c>
       <c r="I158" s="13" t="n">
-        <v>-0.09341681268792873</v>
+        <v>-0.1201358675073684</v>
       </c>
       <c r="J158" s="14" t="n">
         <v>0.5</v>
@@ -9135,33 +9135,33 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>ATL @ PIT</t>
+          <t>NO @ DET</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>Under 41.5</t>
+          <t>DET -7</t>
         </is>
       </c>
       <c r="E159" s="7" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="F159" s="8" t="n">
-        <v>0.4507</v>
+        <v>0.4623</v>
       </c>
       <c r="G159" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.5238</v>
       </c>
       <c r="H159" s="8" t="n">
         <v>-0.0444</v>
       </c>
       <c r="I159" s="8" t="n">
-        <v>-0.1201358675073684</v>
+        <v>-0.110924484243574</v>
       </c>
       <c r="J159" s="10" t="n">
         <v>0.5</v>
@@ -9221,7 +9221,7 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>CHI @ TEN</t>
+          <t>NO @ DAL</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
@@ -9231,23 +9231,23 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>TEN ML</t>
+          <t>NO ML</t>
         </is>
       </c>
       <c r="E161" s="7" t="n">
-        <v>-155</v>
+        <v>110</v>
       </c>
       <c r="F161" s="8" t="n">
-        <v>0.5444</v>
+        <v>0.4135</v>
       </c>
       <c r="G161" s="8" t="n">
-        <v>0.6078</v>
+        <v>0.4762</v>
       </c>
       <c r="H161" s="8" t="n">
-        <v>-0.045</v>
+        <v>-0.0448</v>
       </c>
       <c r="I161" s="8" t="n">
-        <v>-0.1034474654159895</v>
+        <v>-0.1304842621149513</v>
       </c>
       <c r="J161" s="10" t="n">
         <v>0.15</v>
@@ -9266,7 +9266,7 @@
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>NO @ DAL</t>
+          <t>CHI @ TEN</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
@@ -9276,23 +9276,23 @@
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>NO ML</t>
+          <t>TEN ML</t>
         </is>
       </c>
       <c r="E162" s="12" t="n">
-        <v>110</v>
+        <v>-155</v>
       </c>
       <c r="F162" s="13" t="n">
-        <v>0.4126</v>
+        <v>0.5444</v>
       </c>
       <c r="G162" s="13" t="n">
-        <v>0.4762</v>
+        <v>0.6078</v>
       </c>
       <c r="H162" s="13" t="n">
-        <v>-0.0451</v>
+        <v>-0.045</v>
       </c>
       <c r="I162" s="13" t="n">
-        <v>-0.1323197891264711</v>
+        <v>-0.1034474654159895</v>
       </c>
       <c r="J162" s="14" t="n">
         <v>0.15</v>
@@ -9754,16 +9754,16 @@
         <v>-108</v>
       </c>
       <c r="F173" s="8" t="n">
-        <v>0.4467</v>
+        <v>0.4476</v>
       </c>
       <c r="G173" s="8" t="n">
         <v>0.5192</v>
       </c>
       <c r="H173" s="8" t="n">
-        <v>-0.0477</v>
+        <v>-0.0474</v>
       </c>
       <c r="I173" s="8" t="n">
-        <v>-0.1397161173069821</v>
+        <v>-0.1380039849154072</v>
       </c>
       <c r="J173" s="10" t="n">
         <v>0.15</v>
@@ -10237,16 +10237,16 @@
         <v>-102</v>
       </c>
       <c r="F184" s="13" t="n">
-        <v>0.4114</v>
+        <v>0.409</v>
       </c>
       <c r="G184" s="13" t="n">
         <v>0.505</v>
       </c>
       <c r="H184" s="13" t="n">
-        <v>-0.0515</v>
+        <v>-0.0517</v>
       </c>
       <c r="I184" s="13" t="n">
-        <v>-0.1852415681456001</v>
+        <v>-0.1900120442387533</v>
       </c>
       <c r="J184" s="14" t="n">
         <v>0.15</v>
@@ -10617,7 +10617,7 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>DET @ IND</t>
+          <t>CHI @ TEN</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
@@ -10627,23 +10627,23 @@
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>Under 35.5</t>
+          <t>Under 36.5</t>
         </is>
       </c>
       <c r="E193" s="7" t="n">
-        <v>100</v>
+        <v>-105</v>
       </c>
       <c r="F193" s="8" t="n">
-        <v>0.3792</v>
+        <v>0.3923</v>
       </c>
       <c r="G193" s="8" t="n">
-        <v>0.5</v>
+        <v>0.5122</v>
       </c>
       <c r="H193" s="8" t="n">
-        <v>-0.0537</v>
+        <v>-0.0536</v>
       </c>
       <c r="I193" s="8" t="n">
-        <v>-0.2415296221740544</v>
+        <v>-0.2340347918040657</v>
       </c>
       <c r="J193" s="10" t="n">
         <v>0.15</v>
@@ -10662,7 +10662,7 @@
       </c>
       <c r="B194" s="5" t="inlineStr">
         <is>
-          <t>CHI @ TEN</t>
+          <t>DET @ IND</t>
         </is>
       </c>
       <c r="C194" s="5" t="inlineStr">
@@ -10672,23 +10672,23 @@
       </c>
       <c r="D194" s="5" t="inlineStr">
         <is>
-          <t>Under 36.5</t>
+          <t>Under 35.5</t>
         </is>
       </c>
       <c r="E194" s="12" t="n">
-        <v>-105</v>
+        <v>100</v>
       </c>
       <c r="F194" s="13" t="n">
-        <v>0.39</v>
+        <v>0.3792</v>
       </c>
       <c r="G194" s="13" t="n">
-        <v>0.5122</v>
+        <v>0.5</v>
       </c>
       <c r="H194" s="13" t="n">
         <v>-0.0537</v>
       </c>
       <c r="I194" s="13" t="n">
-        <v>-0.2385862949989949</v>
+        <v>-0.2415296221740544</v>
       </c>
       <c r="J194" s="14" t="n">
         <v>0.15</v>
@@ -11974,7 +11974,7 @@
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>4.47</v>
+        <v>4.55</v>
       </c>
       <c r="E14" s="9" t="n">
         <v>-4.5</v>
@@ -12076,13 +12076,13 @@
         </is>
       </c>
       <c r="D17" s="24" t="n">
-        <v>-0.82</v>
+        <v>-0.6</v>
       </c>
       <c r="E17" s="24" t="n">
         <v>1.5</v>
       </c>
       <c r="F17" s="25" t="n">
-        <v>45.3</v>
+        <v>45.4</v>
       </c>
       <c r="G17" s="25" t="n">
         <v>44.5</v>
@@ -12178,7 +12178,7 @@
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>6.87</v>
+        <v>6.75</v>
       </c>
       <c r="E20" s="9" t="n">
         <v>-7</v>
@@ -12354,7 +12354,7 @@
         <v>-3</v>
       </c>
       <c r="F25" s="25" t="n">
-        <v>40.8</v>
+        <v>40.7</v>
       </c>
       <c r="G25" s="25" t="n">
         <v>36.5</v>
@@ -12450,7 +12450,7 @@
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="E28" s="9" t="n">
         <v>-3</v>
@@ -12518,7 +12518,7 @@
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>4.01</v>
+        <v>3.96</v>
       </c>
       <c r="E30" s="9" t="n">
         <v>-1.5</v>
@@ -12688,13 +12688,13 @@
         </is>
       </c>
       <c r="D35" s="24" t="n">
-        <v>-0.83</v>
+        <v>-1</v>
       </c>
       <c r="E35" s="24" t="n">
         <v>2.5</v>
       </c>
       <c r="F35" s="25" t="n">
-        <v>38.8</v>
+        <v>38.9</v>
       </c>
       <c r="G35" s="25" t="n">
         <v>35.5</v>
@@ -12722,10 +12722,10 @@
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>4.91</v>
+        <v>4.33</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>-3.5</v>
+        <v>-2.5</v>
       </c>
       <c r="F36" s="11" t="n">
         <v>39.8</v>
@@ -13252,7 +13252,7 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" s="16" t="n">
         <v>1.92</v>
@@ -13284,7 +13284,7 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D12" s="18" t="n">
         <v>1.91</v>
@@ -13316,7 +13316,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" s="16" t="n">
         <v>1.87</v>
@@ -13348,7 +13348,7 @@
         </is>
       </c>
       <c r="C14" s="12" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D14" s="18" t="n">
         <v>1.86</v>
@@ -15922,16 +15922,16 @@
         </is>
       </c>
       <c r="G42" s="24" t="n">
-        <v>-3.5</v>
+        <v>-2.5</v>
       </c>
       <c r="H42" s="25" t="n">
         <v>35.5</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>-166</v>
+        <v>-148</v>
       </c>
       <c r="K42" s="17" t="n">
         <v>0</v>
@@ -37878,12 +37878,12 @@
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Joe Milton III</t>
+          <t>Mitch Van Vooren</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D205" s="4" t="inlineStr">
@@ -37898,7 +37898,7 @@
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>Milton completed nine of 13 passes for 179 yards with two touchdowns and no interceptions and rushed three times for two yards and another score in the Cowboys' 34-13 preseason win over the Cardinals on Saturday.</t>
+          <t>Van Vooren signed with the Cowboys on Monday, Nick Harris of the Fort Worth Star-Telegram reports.</t>
         </is>
       </c>
     </row>
@@ -37910,12 +37910,12 @@
       </c>
       <c r="B206" s="5" t="inlineStr">
         <is>
-          <t>Jaydon Blue</t>
+          <t>Joe Milton III</t>
         </is>
       </c>
       <c r="C206" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D206" s="5" t="inlineStr">
@@ -37930,7 +37930,7 @@
       </c>
       <c r="F206" s="5" t="inlineStr">
         <is>
-          <t>Blue (shoulder) rushed 15 times for 75 yards in the Cowboys' 34-13 preseason win over the Cardinals on Saturday. He also returned one kickoff for 26 yards.</t>
+          <t>Milton completed nine of 13 passes for 179 yards with two touchdowns and no interceptions and rushed three times for two yards and another score in the Cowboys' 34-13 preseason win over the Cardinals on Saturday.</t>
         </is>
       </c>
     </row>
@@ -37942,7 +37942,7 @@
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>Malik Davis</t>
+          <t>Jaydon Blue</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
@@ -37962,7 +37962,7 @@
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>Davis rushed five times for 29 yards and brought in his only target for an eight-yard touchdown in the Cowboys' 34-13 preseason win over the Cardinals on Saturday. He also committed a fumble but recovered and ran back one kickoff for 31 yards.</t>
+          <t>Blue (shoulder) rushed 15 times for 75 yards in the Cowboys' 34-13 preseason win over the Cardinals on Saturday. He also returned one kickoff for 26 yards.</t>
         </is>
       </c>
     </row>
@@ -37974,27 +37974,27 @@
       </c>
       <c r="B208" s="5" t="inlineStr">
         <is>
-          <t>Julius Wood</t>
+          <t>Malik Davis</t>
         </is>
       </c>
       <c r="C208" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D208" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E208" s="5" t="inlineStr">
         <is>
-          <t>Concussion</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F208" s="5" t="inlineStr">
         <is>
-          <t>Wood has entered the league's concussion protocol and has been ruled out for the rest of Saturday's preseason game against the Cardinals, Patrik Walker of the Cowboys' official site reports.</t>
+          <t>Davis rushed five times for 29 yards and brought in his only target for an eight-yard touchdown in the Cowboys' 34-13 preseason win over the Cardinals on Saturday. He also committed a fumble but recovered and ran back one kickoff for 31 yards.</t>
         </is>
       </c>
     </row>
@@ -38006,12 +38006,12 @@
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>Zion Childress</t>
+          <t>Julius Wood</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D209" s="4" t="inlineStr">
@@ -38021,12 +38021,12 @@
       </c>
       <c r="E209" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Concussion</t>
         </is>
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>Childress (hamstring) returned to practice as a limited participant Thursday, Calvin Watkins of The Dallas Morning News reports.</t>
+          <t>Wood has entered the league's concussion protocol and has been ruled out for the rest of Saturday's preseason game against the Cardinals, Patrik Walker of the Cowboys' official site reports.</t>
         </is>
       </c>
     </row>
@@ -38038,12 +38038,12 @@
       </c>
       <c r="B210" s="5" t="inlineStr">
         <is>
-          <t>Michael Trigg</t>
+          <t>Zion Childress</t>
         </is>
       </c>
       <c r="C210" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D210" s="5" t="inlineStr">
@@ -38058,7 +38058,7 @@
       </c>
       <c r="F210" s="5" t="inlineStr">
         <is>
-          <t>Trigg (toe) did not practice Thursday, Tommy Yarrish of the Cowboys' official site reports.</t>
+          <t>Childress (hamstring) returned to practice as a limited participant Thursday, Calvin Watkins of The Dallas Morning News reports.</t>
         </is>
       </c>
     </row>
@@ -38070,12 +38070,12 @@
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>Tyler Guyton</t>
+          <t>Michael Trigg</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>OT</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D211" s="4" t="inlineStr">
@@ -38085,12 +38085,12 @@
       </c>
       <c r="E211" s="4" t="inlineStr">
         <is>
-          <t>Soreness</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F211" s="4" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>Trigg (toe) did not practice Thursday, Tommy Yarrish of the Cowboys' official site reports.</t>
         </is>
       </c>
     </row>
@@ -38102,12 +38102,12 @@
       </c>
       <c r="B212" s="5" t="inlineStr">
         <is>
-          <t>Phil Mafah</t>
+          <t>Tyler Guyton</t>
         </is>
       </c>
       <c r="C212" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>OT</t>
         </is>
       </c>
       <c r="D212" s="5" t="inlineStr">
@@ -38117,7 +38117,7 @@
       </c>
       <c r="E212" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Soreness</t>
         </is>
       </c>
       <c r="F212" s="5" t="inlineStr">
@@ -38134,25 +38134,29 @@
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>Jalen Thompson</t>
+          <t>Phil Mafah</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D213" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E213" s="4" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="F213" s="4" t="inlineStr"/>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F213" s="4" t="inlineStr">
+        <is>
+          <t>questionable</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="5" t="inlineStr">
@@ -38162,29 +38166,25 @@
       </c>
       <c r="B214" s="5" t="inlineStr">
         <is>
-          <t>Jonathan Bullard</t>
+          <t>Jalen Thompson</t>
         </is>
       </c>
       <c r="C214" s="5" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D214" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E214" s="5" t="inlineStr">
         <is>
-          <t>Soreness</t>
-        </is>
-      </c>
-      <c r="F214" s="5" t="inlineStr">
-        <is>
-          <t>questionable</t>
-        </is>
-      </c>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F214" s="5" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
@@ -38194,27 +38194,27 @@
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>Princeton Fant</t>
+          <t>Jonathan Bullard</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="D215" s="4" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E215" s="4" t="inlineStr">
         <is>
-          <t>Surgery</t>
+          <t>Soreness</t>
         </is>
       </c>
       <c r="F215" s="4" t="inlineStr">
         <is>
-          <t>ir</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -38226,25 +38226,29 @@
       </c>
       <c r="B216" s="5" t="inlineStr">
         <is>
-          <t>Ajani Cornelius</t>
+          <t>Princeton Fant</t>
         </is>
       </c>
       <c r="C216" s="5" t="inlineStr">
         <is>
-          <t>OT</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D216" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E216" s="5" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="F216" s="5" t="inlineStr"/>
+          <t>Surgery</t>
+        </is>
+      </c>
+      <c r="F216" s="5" t="inlineStr">
+        <is>
+          <t>ir</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
@@ -38254,12 +38258,12 @@
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>P.J. Locke</t>
+          <t>Ajani Cornelius</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>OT</t>
         </is>
       </c>
       <c r="D217" s="4" t="inlineStr">
@@ -38282,12 +38286,12 @@
       </c>
       <c r="B218" s="5" t="inlineStr">
         <is>
-          <t>James Houston</t>
+          <t>P.J. Locke</t>
         </is>
       </c>
       <c r="C218" s="5" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D218" s="5" t="inlineStr">
@@ -38310,7 +38314,7 @@
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>DeMarvion Overshown</t>
+          <t>James Houston</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
@@ -38328,11 +38332,7 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F219" s="4" t="inlineStr">
-        <is>
-          <t>Overshown (lower body) participated at the Cowboys' training camp practice Monday, Todd Archer of ESPN.com reports.</t>
-        </is>
-      </c>
+      <c r="F219" s="4" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="5" t="inlineStr">
@@ -38342,7 +38342,7 @@
       </c>
       <c r="B220" s="5" t="inlineStr">
         <is>
-          <t>Jaishawn Barham</t>
+          <t>DeMarvion Overshown</t>
         </is>
       </c>
       <c r="C220" s="5" t="inlineStr">
@@ -38362,7 +38362,7 @@
       </c>
       <c r="F220" s="5" t="inlineStr">
         <is>
-          <t>Barham (groin) returned to practice Monday, Todd Archer of ESPN.com reports.</t>
+          <t>Overshown (lower body) participated at the Cowboys' training camp practice Monday, Todd Archer of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -38374,7 +38374,7 @@
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>Von Miller</t>
+          <t>Jaishawn Barham</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
@@ -38394,7 +38394,7 @@
       </c>
       <c r="F221" s="4" t="inlineStr">
         <is>
-          <t>Miller is not expected to practice with the Cowboys this week, Calvin Watkins of The Dallas Morning News reports.</t>
+          <t>Barham (groin) returned to practice Monday, Todd Archer of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -38406,12 +38406,12 @@
       </c>
       <c r="B222" s="5" t="inlineStr">
         <is>
-          <t>Alijah Clark</t>
+          <t>Von Miller</t>
         </is>
       </c>
       <c r="C222" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D222" s="5" t="inlineStr">
@@ -38426,7 +38426,7 @@
       </c>
       <c r="F222" s="5" t="inlineStr">
         <is>
-          <t>Clark (ankle) recorded one tackle in the Cowboys' 17-7 preseason win over the Seahawks on Saturday.</t>
+          <t>Miller is not expected to practice with the Cowboys this week, Calvin Watkins of The Dallas Morning News reports.</t>
         </is>
       </c>
     </row>
@@ -38438,12 +38438,12 @@
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>Camden Brown</t>
+          <t>Alijah Clark</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D223" s="4" t="inlineStr">
@@ -38458,7 +38458,7 @@
       </c>
       <c r="F223" s="4" t="inlineStr">
         <is>
-          <t>Brown caught all three of his targets for 62 yards and two touchdowns during Saturday night's preseason game against the Seahawks.</t>
+          <t>Clark (ankle) recorded one tackle in the Cowboys' 17-7 preseason win over the Seahawks on Saturday.</t>
         </is>
       </c>
     </row>
@@ -38470,7 +38470,7 @@
       </c>
       <c r="B224" s="5" t="inlineStr">
         <is>
-          <t>Anthony Smith</t>
+          <t>Camden Brown</t>
         </is>
       </c>
       <c r="C224" s="5" t="inlineStr">
@@ -38490,7 +38490,7 @@
       </c>
       <c r="F224" s="5" t="inlineStr">
         <is>
-          <t>Smith brought in two of five targets for 28 yards and rushed once for nine yards in the Cowboys' 17-7 preseason win over the Seahawks on Saturday.</t>
+          <t>Brown caught all three of his targets for 62 yards and two touchdowns during Saturday night's preseason game against the Seahawks.</t>
         </is>
       </c>
     </row>
@@ -38502,7 +38502,7 @@
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>Marquez Valdes-Scantling</t>
+          <t>Anthony Smith</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr">
@@ -38522,7 +38522,7 @@
       </c>
       <c r="F225" s="4" t="inlineStr">
         <is>
-          <t>Valdes-Scantling failed to bring in his only target in the Cowboys' 17-7 preseason win over the Seahawks on Saturday.</t>
+          <t>Smith brought in two of five targets for 28 yards and rushed once for nine yards in the Cowboys' 17-7 preseason win over the Seahawks on Saturday.</t>
         </is>
       </c>
     </row>
@@ -38534,12 +38534,12 @@
       </c>
       <c r="B226" s="5" t="inlineStr">
         <is>
-          <t>Brandon Aubrey</t>
+          <t>Marquez Valdes-Scantling</t>
         </is>
       </c>
       <c r="C226" s="5" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D226" s="5" t="inlineStr">
@@ -38554,7 +38554,7 @@
       </c>
       <c r="F226" s="5" t="inlineStr">
         <is>
-          <t>Aubrey made his only field-goal attempt from 29 yards and knocked home both extra-point tries in the Cowboys' 17-7 preseason win over the Seahawks on Saturday.</t>
+          <t>Valdes-Scantling failed to bring in his only target in the Cowboys' 17-7 preseason win over the Seahawks on Saturday.</t>
         </is>
       </c>
     </row>
@@ -38566,12 +38566,12 @@
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>Ryan Flournoy</t>
+          <t>Brandon Aubrey</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="D227" s="4" t="inlineStr">
@@ -38586,7 +38586,7 @@
       </c>
       <c r="F227" s="4" t="inlineStr">
         <is>
-          <t>Flournoy isn't suited up ahead of Saturday's preseason opener versus Seattle, Nick Harris of the Fort Worth Star-Telegram reports.</t>
+          <t>Aubrey made his only field-goal attempt from 29 yards and knocked home both extra-point tries in the Cowboys' 17-7 preseason win over the Seahawks on Saturday.</t>
         </is>
       </c>
     </row>
@@ -38598,12 +38598,12 @@
       </c>
       <c r="B228" s="5" t="inlineStr">
         <is>
-          <t>Jake Ferguson</t>
+          <t>Ryan Flournoy</t>
         </is>
       </c>
       <c r="C228" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D228" s="5" t="inlineStr">
@@ -38618,7 +38618,7 @@
       </c>
       <c r="F228" s="5" t="inlineStr">
         <is>
-          <t>Ferguson isn't suited up for Saturday's preseason contest against the Seahawks, Nick Harris of the Fort Worth Star-Telegram reports.</t>
+          <t>Flournoy isn't suited up ahead of Saturday's preseason opener versus Seattle, Nick Harris of the Fort Worth Star-Telegram reports.</t>
         </is>
       </c>
     </row>
@@ -38630,12 +38630,12 @@
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>Jake Ferguson</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D229" s="4" t="inlineStr">
@@ -38650,7 +38650,7 @@
       </c>
       <c r="F229" s="4" t="inlineStr">
         <is>
-          <t>Prescott isn't slated to play in Saturday's preseason matchup versus Seattle, Nick Harris of the Fort Worth Star-Telegram reports.</t>
+          <t>Ferguson isn't suited up for Saturday's preseason contest against the Seahawks, Nick Harris of the Fort Worth Star-Telegram reports.</t>
         </is>
       </c>
     </row>
@@ -39486,7 +39486,7 @@
       </c>
       <c r="B256" s="5" t="inlineStr">
         <is>
-          <t>Raheem Blackshear</t>
+          <t>Roydell Williams</t>
         </is>
       </c>
       <c r="C256" s="5" t="inlineStr">
@@ -39496,17 +39496,17 @@
       </c>
       <c r="D256" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E256" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F256" s="5" t="inlineStr">
         <is>
-          <t>The Lions placed Blackshear (undisclosed) on injured reserve Monday.</t>
+          <t>Williams signed with the Lions on Monday.</t>
         </is>
       </c>
     </row>
@@ -39518,17 +39518,17 @@
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>Michael Niese</t>
+          <t>Raheem Blackshear</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D257" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E257" s="4" t="inlineStr">
@@ -39538,7 +39538,7 @@
       </c>
       <c r="F257" s="4" t="inlineStr">
         <is>
-          <t>Niese (leg) was spotted leaving the Lions' locker room in crutches after sustaining an injury in Saturday's preseason game against the Commanders, Eric Woodyard of ESPN.com reports.</t>
+          <t>The Lions placed Blackshear (undisclosed) on injured reserve Monday.</t>
         </is>
       </c>
     </row>
@@ -39550,12 +39550,12 @@
       </c>
       <c r="B258" s="5" t="inlineStr">
         <is>
-          <t>Jabari Small</t>
+          <t>Michael Niese</t>
         </is>
       </c>
       <c r="C258" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D258" s="5" t="inlineStr">
@@ -39565,12 +39565,12 @@
       </c>
       <c r="E258" s="5" t="inlineStr">
         <is>
-          <t>Concussion</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F258" s="5" t="inlineStr">
         <is>
-          <t>Williams suffered a concussion during Detroit's preseason loss to the Commanders on Saturday, Justin Rogers of DetroitFootball.net reports.</t>
+          <t>Niese (leg) was spotted leaving the Lions' locker room in crutches after sustaining an injury in Saturday's preseason game against the Commanders, Eric Woodyard of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -39582,7 +39582,7 @@
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>Jacob Saylors</t>
+          <t>Jabari Small</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
@@ -39592,17 +39592,17 @@
       </c>
       <c r="D259" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E259" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Concussion</t>
         </is>
       </c>
       <c r="F259" s="4" t="inlineStr">
         <is>
-          <t>Saylors rushed six times for 32 yards while also giving up a fumble-six in Saturday's 17-13 preseason win over the Commanders.</t>
+          <t>Williams suffered a concussion during Detroit's preseason loss to the Commanders on Saturday, Justin Rogers of DetroitFootball.net reports.</t>
         </is>
       </c>
     </row>
@@ -39614,7 +39614,7 @@
       </c>
       <c r="B260" s="5" t="inlineStr">
         <is>
-          <t>Trayveon Williams</t>
+          <t>Jacob Saylors</t>
         </is>
       </c>
       <c r="C260" s="5" t="inlineStr">
@@ -39634,7 +39634,7 @@
       </c>
       <c r="F260" s="5" t="inlineStr">
         <is>
-          <t>Williams turned 10 carries into 36 yards and a touchdown while adding a 24-yard reception during the Lions' 17-13 preseason win over the Commanders on Saturday.</t>
+          <t>Saylors rushed six times for 32 yards while also giving up a fumble-six in Saturday's 17-13 preseason win over the Commanders.</t>
         </is>
       </c>
     </row>
@@ -39646,7 +39646,7 @@
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>Sione Vaki</t>
+          <t>Trayveon Williams</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
@@ -39656,17 +39656,17 @@
       </c>
       <c r="D261" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E261" s="4" t="inlineStr">
         <is>
-          <t>Spasms</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F261" s="4" t="inlineStr">
         <is>
-          <t>Vaki (back) didn't play in Detroit's preseason loss to the Commanders on Saturday, Justin Rogers of DetroitFootball.net reports.</t>
+          <t>Williams turned 10 carries into 36 yards and a touchdown while adding a 24-yard reception during the Lions' 17-13 preseason win over the Commanders on Saturday.</t>
         </is>
       </c>
     </row>
@@ -39678,27 +39678,27 @@
       </c>
       <c r="B262" s="5" t="inlineStr">
         <is>
-          <t>Joshua Dobbs</t>
+          <t>Sione Vaki</t>
         </is>
       </c>
       <c r="C262" s="5" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D262" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E262" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Spasms</t>
         </is>
       </c>
       <c r="F262" s="5" t="inlineStr">
         <is>
-          <t>Dobbs completed seven of his 12 passes for 74 yards and an interception while adding two carries for 53 yards and a touchdown on the ground in Saturday's 17-13 preseason win over the Commanders.</t>
+          <t>Vaki (back) didn't play in Detroit's preseason loss to the Commanders on Saturday, Justin Rogers of DetroitFootball.net reports.</t>
         </is>
       </c>
     </row>
@@ -39710,12 +39710,12 @@
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>Brock Wright</t>
+          <t>Joshua Dobbs</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D263" s="4" t="inlineStr">
@@ -39730,7 +39730,7 @@
       </c>
       <c r="F263" s="4" t="inlineStr">
         <is>
-          <t>Wright caught the first target of Thursday's preseason game against the Commanders, taking his sole reception for three yards.</t>
+          <t>Dobbs completed seven of his 12 passes for 74 yards and an interception while adding two carries for 53 yards and a touchdown on the ground in Saturday's 17-13 preseason win over the Commanders.</t>
         </is>
       </c>
     </row>
@@ -39742,12 +39742,12 @@
       </c>
       <c r="B264" s="5" t="inlineStr">
         <is>
-          <t>Jake Bates</t>
+          <t>Brock Wright</t>
         </is>
       </c>
       <c r="C264" s="5" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D264" s="5" t="inlineStr">
@@ -39762,7 +39762,7 @@
       </c>
       <c r="F264" s="5" t="inlineStr">
         <is>
-          <t>Bates converted one of two field-goal attempts and both PATs in Saturday's 17-13 preseason win over the Commanders.</t>
+          <t>Wright caught the first target of Thursday's preseason game against the Commanders, taking his sole reception for three yards.</t>
         </is>
       </c>
     </row>
@@ -39774,27 +39774,27 @@
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>Ennis Rakestraw Jr.</t>
+          <t>Jake Bates</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="D265" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E265" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F265" s="4" t="inlineStr">
         <is>
-          <t>Rakestraw didn't finish practice Thursday due to an apparent leg injury, Colton Pouncy of The Athletic reports.</t>
+          <t>Bates converted one of two field-goal attempts and both PATs in Saturday's 17-13 preseason win over the Commanders.</t>
         </is>
       </c>
     </row>
@@ -39806,12 +39806,12 @@
       </c>
       <c r="B266" s="5" t="inlineStr">
         <is>
-          <t>Jimmy Rolder</t>
+          <t>Ennis Rakestraw Jr.</t>
         </is>
       </c>
       <c r="C266" s="5" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D266" s="5" t="inlineStr">
@@ -39826,7 +39826,7 @@
       </c>
       <c r="F266" s="5" t="inlineStr">
         <is>
-          <t>Coach Dan Campbell said this week that Rolder (hamstring) could begin practicing pretty early in the season, Nolan Bianchi of The Detroit News reports.</t>
+          <t>Rakestraw didn't finish practice Thursday due to an apparent leg injury, Colton Pouncy of The Athletic reports.</t>
         </is>
       </c>
     </row>
@@ -39838,12 +39838,12 @@
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>Sam LaPorta</t>
+          <t>Jimmy Rolder</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D267" s="4" t="inlineStr">
@@ -39858,7 +39858,7 @@
       </c>
       <c r="F267" s="4" t="inlineStr">
         <is>
-          <t>LaPorta is dealing with a hip injury, and head coach Dan Campbell wouldn't commit Thursday to the tight end being available for Week 1 against the Saints, Tim Twentyman of the Lions' official site reports.</t>
+          <t>Coach Dan Campbell said this week that Rolder (hamstring) could begin practicing pretty early in the season, Nolan Bianchi of The Detroit News reports.</t>
         </is>
       </c>
     </row>
@@ -39870,27 +39870,27 @@
       </c>
       <c r="B268" s="5" t="inlineStr">
         <is>
-          <t>Jared Goff</t>
+          <t>Sam LaPorta</t>
         </is>
       </c>
       <c r="C268" s="5" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D268" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E268" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F268" s="5" t="inlineStr">
         <is>
-          <t>Goff will be rested for Saturday's preseason game against the Commanders, Tim Twentyman of the Lions' official site reports.</t>
+          <t>LaPorta is dealing with a hip injury, and head coach Dan Campbell wouldn't commit Thursday to the tight end being available for Week 1 against the Saints, Tim Twentyman of the Lions' official site reports.</t>
         </is>
       </c>
     </row>
@@ -39902,12 +39902,12 @@
       </c>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>Jared Goff</t>
         </is>
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D269" s="4" t="inlineStr">
@@ -39922,7 +39922,7 @@
       </c>
       <c r="F269" s="4" t="inlineStr">
         <is>
-          <t>Williams (shoulder) participated in team drills and 7-on-7s during Wednesday's practice, Tim Twentyman of the Lions' official site reports.</t>
+          <t>Goff will be rested for Saturday's preseason game against the Commanders, Tim Twentyman of the Lions' official site reports.</t>
         </is>
       </c>
     </row>
@@ -39934,27 +39934,27 @@
       </c>
       <c r="B270" s="5" t="inlineStr">
         <is>
-          <t>Payton Turner</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="C270" s="5" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D270" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E270" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F270" s="5" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>Williams (shoulder) participated in team drills and 7-on-7s during Wednesday's practice, Tim Twentyman of the Lions' official site reports.</t>
         </is>
       </c>
     </row>
@@ -39966,12 +39966,12 @@
       </c>
       <c r="B271" s="4" t="inlineStr">
         <is>
-          <t>Mekhi Wingo</t>
+          <t>Payton Turner</t>
         </is>
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D271" s="4" t="inlineStr">
@@ -39998,12 +39998,12 @@
       </c>
       <c r="B272" s="5" t="inlineStr">
         <is>
-          <t>Isiah Pacheco</t>
+          <t>Mekhi Wingo</t>
         </is>
       </c>
       <c r="C272" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="D272" s="5" t="inlineStr">
@@ -40013,7 +40013,7 @@
       </c>
       <c r="E272" s="5" t="inlineStr">
         <is>
-          <t>Sprain</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F272" s="5" t="inlineStr">
@@ -40030,12 +40030,12 @@
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>D.J. Reed</t>
+          <t>Isiah Pacheco</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D273" s="4" t="inlineStr">
@@ -40045,7 +40045,7 @@
       </c>
       <c r="E273" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Sprain</t>
         </is>
       </c>
       <c r="F273" s="4" t="inlineStr">
@@ -40062,12 +40062,12 @@
       </c>
       <c r="B274" s="5" t="inlineStr">
         <is>
-          <t>Malcolm Rodriguez</t>
+          <t>D.J. Reed</t>
         </is>
       </c>
       <c r="C274" s="5" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D274" s="5" t="inlineStr">
@@ -40094,27 +40094,27 @@
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>Cade Mays</t>
+          <t>Malcolm Rodriguez</t>
         </is>
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D275" s="4" t="inlineStr">
         <is>
-          <t>Out</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E275" s="4" t="inlineStr">
         <is>
-          <t>Fracture</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F275" s="4" t="inlineStr">
         <is>
-          <t>out</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -40126,25 +40126,29 @@
       </c>
       <c r="B276" s="5" t="inlineStr">
         <is>
-          <t>Thomas Harper</t>
+          <t>Cade Mays</t>
         </is>
       </c>
       <c r="C276" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D276" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="E276" s="5" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="F276" s="5" t="inlineStr"/>
+          <t>Fracture</t>
+        </is>
+      </c>
+      <c r="F276" s="5" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="4" t="inlineStr">
@@ -40154,7 +40158,7 @@
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>Dan Jackson</t>
+          <t>Thomas Harper</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr">
@@ -40182,7 +40186,7 @@
       </c>
       <c r="B278" s="5" t="inlineStr">
         <is>
-          <t>Christian Izien</t>
+          <t>Dan Jackson</t>
         </is>
       </c>
       <c r="C278" s="5" t="inlineStr">
@@ -40210,12 +40214,12 @@
       </c>
       <c r="B279" s="4" t="inlineStr">
         <is>
-          <t>Jahmyr Gibbs</t>
+          <t>Christian Izien</t>
         </is>
       </c>
       <c r="C279" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D279" s="4" t="inlineStr">
@@ -40228,11 +40232,7 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F279" s="4" t="inlineStr">
-        <is>
-          <t>Gibbs was held out of Thursday's preseason opener against the Bengals.</t>
-        </is>
-      </c>
+      <c r="F279" s="4" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" s="5" t="inlineStr">
@@ -41082,7 +41082,7 @@
       </c>
       <c r="F306" s="5" t="inlineStr">
         <is>
-          <t>Jordan (knee) did not participate at Monday's training-camp practice, Aaron Wilson of KPRC 2 Houston reports.</t>
+          <t>Jordan (knee) did not participate at Monday's training camp practice, Aaron Wilson of KPRC 2 Houston reports.</t>
         </is>
       </c>
     </row>
@@ -41126,7 +41126,7 @@
       </c>
       <c r="B308" s="5" t="inlineStr">
         <is>
-          <t>Josh Pitsenberger</t>
+          <t>British Brooks</t>
         </is>
       </c>
       <c r="C308" s="5" t="inlineStr">
@@ -41136,17 +41136,17 @@
       </c>
       <c r="D308" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E308" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Surgery</t>
         </is>
       </c>
       <c r="F308" s="5" t="inlineStr">
         <is>
-          <t>Pitsenberger (ankle) reached an injury settlement with the Texans on Monday, Aaron Wilson of KPRC 2 Houston reports.</t>
+          <t>Brooks (hand) was back at practice with the Texans on Monday, Aaron Wilson of KPRC 2 Houston reports.</t>
         </is>
       </c>
     </row>
@@ -41158,27 +41158,27 @@
       </c>
       <c r="B309" s="4" t="inlineStr">
         <is>
-          <t>British Brooks</t>
+          <t>Kayshon Boutte</t>
         </is>
       </c>
       <c r="C309" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D309" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E309" s="4" t="inlineStr">
         <is>
-          <t>Surgery</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F309" s="4" t="inlineStr">
         <is>
-          <t>Brooks (hand) was back at practice with the Texans on Monday, Aaron Wilson of KPRC 2 Houston reports.</t>
+          <t>The Patriots traded Boutte to the Texans for safety Jaylen Reed and a draft pick Monday, Tom Pelissero of Netflix reports.</t>
         </is>
       </c>
     </row>
@@ -41190,12 +41190,12 @@
       </c>
       <c r="B310" s="5" t="inlineStr">
         <is>
-          <t>Kayshon Boutte</t>
+          <t>George Odum</t>
         </is>
       </c>
       <c r="C310" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D310" s="5" t="inlineStr">
@@ -41210,7 +41210,7 @@
       </c>
       <c r="F310" s="5" t="inlineStr">
         <is>
-          <t>The Patriots traded Boutte to the Texans for safety Jaylen Reed and a draft pick Monday, Tom Pelissero of Netflix reports.</t>
+          <t>The Texans are expected to sign Odum to a contract as of Sunday, Aaron Wilson of KPRC 2 Houston reports.</t>
         </is>
       </c>
     </row>
@@ -41222,12 +41222,12 @@
       </c>
       <c r="B311" s="4" t="inlineStr">
         <is>
-          <t>George Odum</t>
+          <t>Deuce Vaughn</t>
         </is>
       </c>
       <c r="C311" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D311" s="4" t="inlineStr">
@@ -41242,7 +41242,7 @@
       </c>
       <c r="F311" s="4" t="inlineStr">
         <is>
-          <t>The Texans are expected to sign Odum to a contract as of Sunday, Aaron Wilson of KPRC 2 Houston reports.</t>
+          <t>The Texans are expected to sign Vaughn to a contract as of Sunday, Aaron Wilson of KPRC 2 Houston reports.</t>
         </is>
       </c>
     </row>
@@ -41254,27 +41254,27 @@
       </c>
       <c r="B312" s="5" t="inlineStr">
         <is>
-          <t>Deuce Vaughn</t>
+          <t>Wade Woodaz</t>
         </is>
       </c>
       <c r="C312" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D312" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E312" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Surgery</t>
         </is>
       </c>
       <c r="F312" s="5" t="inlineStr">
         <is>
-          <t>The Texans are expected to sign Vaughn to a contract as of Sunday, Aaron Wilson of KPRC 2 Houston reports.</t>
+          <t>Woodaz is scheduled to undergo surgery Monday to repair a broken thumb, Aaron Wilson of KPRC 2 Houston reports.</t>
         </is>
       </c>
     </row>
@@ -41286,7 +41286,7 @@
       </c>
       <c r="B313" s="4" t="inlineStr">
         <is>
-          <t>Wade Woodaz</t>
+          <t>E.J. Speed</t>
         </is>
       </c>
       <c r="C313" s="4" t="inlineStr">
@@ -41296,7 +41296,7 @@
       </c>
       <c r="D313" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="E313" s="4" t="inlineStr">
@@ -41306,7 +41306,7 @@
       </c>
       <c r="F313" s="4" t="inlineStr">
         <is>
-          <t>Woodaz is scheduled to undergo surgery Monday to repair a broken thumb, Aaron Wilson of KPRC 2 Houston reports.</t>
+          <t>Speed will miss the entire 2026 season due to a torn quadriceps tendon, Aaron Wilson of KPRC 2 Houston reports.</t>
         </is>
       </c>
     </row>
@@ -41318,7 +41318,7 @@
       </c>
       <c r="B314" s="5" t="inlineStr">
         <is>
-          <t>E.J. Speed</t>
+          <t>K.C. Ossai</t>
         </is>
       </c>
       <c r="C314" s="5" t="inlineStr">
@@ -41328,17 +41328,17 @@
       </c>
       <c r="D314" s="5" t="inlineStr">
         <is>
-          <t>Out</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E314" s="5" t="inlineStr">
         <is>
-          <t>Surgery</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F314" s="5" t="inlineStr">
         <is>
-          <t>Speed will miss the entire 2026 season due to a torn quadriceps tendon, Aaron Wilson of KPRC 2 Houston reports.</t>
+          <t>The Texans placed Ossai (undisclosed) on injured reserve Saturday.</t>
         </is>
       </c>
     </row>
@@ -41350,17 +41350,17 @@
       </c>
       <c r="B315" s="4" t="inlineStr">
         <is>
-          <t>K.C. Ossai</t>
+          <t>Dominique Robinson</t>
         </is>
       </c>
       <c r="C315" s="4" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D315" s="4" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E315" s="4" t="inlineStr">
@@ -41370,7 +41370,7 @@
       </c>
       <c r="F315" s="4" t="inlineStr">
         <is>
-          <t>The Texans placed Ossai (undisclosed) on injured reserve Saturday.</t>
+          <t>Robinson (calf) is considered day-to-day as of Friday, Aaron Wilson of KPRC 2 Houston reports.</t>
         </is>
       </c>
     </row>
@@ -41382,12 +41382,12 @@
       </c>
       <c r="B316" s="5" t="inlineStr">
         <is>
-          <t>Dominique Robinson</t>
+          <t>Noah Whittington</t>
         </is>
       </c>
       <c r="C316" s="5" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D316" s="5" t="inlineStr">
@@ -41402,7 +41402,7 @@
       </c>
       <c r="F316" s="5" t="inlineStr">
         <is>
-          <t>Robinson (calf) is considered day-to-day as of Friday, Aaron Wilson of KPRC 2 Houston reports.</t>
+          <t>Whittington (ankle) is regarded as day-to-day as of Friday, Aaron Wilson of KPRC 2 Houston reports.</t>
         </is>
       </c>
     </row>
@@ -41414,27 +41414,27 @@
       </c>
       <c r="B317" s="4" t="inlineStr">
         <is>
-          <t>Noah Whittington</t>
+          <t>Lewis Bond</t>
         </is>
       </c>
       <c r="C317" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D317" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E317" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F317" s="4" t="inlineStr">
         <is>
-          <t>Whittington (ankle) is regarded as day-to-day as of Friday, Aaron Wilson of KPRC 2 Houston reports.</t>
+          <t>Bond caught two of his three targets for 12 yards in Thursday night's 22-20 preseason loss to the Raiders.</t>
         </is>
       </c>
     </row>
@@ -41446,12 +41446,12 @@
       </c>
       <c r="B318" s="5" t="inlineStr">
         <is>
-          <t>Lewis Bond</t>
+          <t>Marlin Klein</t>
         </is>
       </c>
       <c r="C318" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D318" s="5" t="inlineStr">
@@ -41466,7 +41466,7 @@
       </c>
       <c r="F318" s="5" t="inlineStr">
         <is>
-          <t>Bond caught two of his three targets for 12 yards in Thursday night's 22-20 preseason loss to the Raiders.</t>
+          <t>Klein caught three of four targets for 31 yards in Thursday night's 22-20 preseason loss to the Raiders.</t>
         </is>
       </c>
     </row>
@@ -41478,12 +41478,12 @@
       </c>
       <c r="B319" s="4" t="inlineStr">
         <is>
-          <t>Marlin Klein</t>
+          <t>Ka'imi Fairbairn</t>
         </is>
       </c>
       <c r="C319" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="D319" s="4" t="inlineStr">
@@ -41498,7 +41498,7 @@
       </c>
       <c r="F319" s="4" t="inlineStr">
         <is>
-          <t>Klein caught three of four targets for 31 yards in Thursday night's 22-20 preseason loss to the Raiders.</t>
+          <t>Fairbairn converted both field-goal attempts and both extra-point tries in Thursday night's 22-20 preseason loss to the Raiders.</t>
         </is>
       </c>
     </row>
@@ -41510,12 +41510,12 @@
       </c>
       <c r="B320" s="5" t="inlineStr">
         <is>
-          <t>Ka'imi Fairbairn</t>
+          <t>Zay Jones</t>
         </is>
       </c>
       <c r="C320" s="5" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D320" s="5" t="inlineStr">
@@ -41530,7 +41530,7 @@
       </c>
       <c r="F320" s="5" t="inlineStr">
         <is>
-          <t>Fairbairn converted both field-goal attempts and both extra-point tries in Thursday night's 22-20 preseason loss to the Raiders.</t>
+          <t>Jones is signing a contract with the Texans after completing a tryout with the team Friday, Mike Garafolo of NFL Network reports.</t>
         </is>
       </c>
     </row>
@@ -41542,7 +41542,7 @@
       </c>
       <c r="B321" s="4" t="inlineStr">
         <is>
-          <t>Zay Jones</t>
+          <t>Sterling Shepard</t>
         </is>
       </c>
       <c r="C321" s="4" t="inlineStr">
@@ -41562,7 +41562,7 @@
       </c>
       <c r="F321" s="4" t="inlineStr">
         <is>
-          <t>Jones is signing a contract with the Texans after completing a tryout with the team Friday, Mike Garafolo of NFL Network reports.</t>
+          <t>Shepard is signing with Houston after trying out with the team Friday, Mike Garafolo of NFL Network reports.</t>
         </is>
       </c>
     </row>
@@ -41574,7 +41574,7 @@
       </c>
       <c r="B322" s="5" t="inlineStr">
         <is>
-          <t>Sterling Shepard</t>
+          <t>Jayden Higgins</t>
         </is>
       </c>
       <c r="C322" s="5" t="inlineStr">
@@ -41584,17 +41584,17 @@
       </c>
       <c r="D322" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E322" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Surgery</t>
         </is>
       </c>
       <c r="F322" s="5" t="inlineStr">
         <is>
-          <t>Shepard is signing with Houston after trying out with the team Friday, Mike Garafolo of NFL Network reports.</t>
+          <t>The Texans placed Higgins (knee) on injured reserve Friday, Adam Schefter of ESPN reports.</t>
         </is>
       </c>
     </row>
@@ -41606,7 +41606,7 @@
       </c>
       <c r="B323" s="4" t="inlineStr">
         <is>
-          <t>Jayden Higgins</t>
+          <t>Nico Collins</t>
         </is>
       </c>
       <c r="C323" s="4" t="inlineStr">
@@ -41616,17 +41616,17 @@
       </c>
       <c r="D323" s="4" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E323" s="4" t="inlineStr">
         <is>
-          <t>Surgery</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F323" s="4" t="inlineStr">
         <is>
-          <t>The Texans placed Higgins (knee) on injured reserve Friday, Adam Schefter of ESPN reports.</t>
+          <t>Collins didn't play in Thursday's preseason game against the Raiders.</t>
         </is>
       </c>
     </row>
@@ -41638,12 +41638,12 @@
       </c>
       <c r="B324" s="5" t="inlineStr">
         <is>
-          <t>Nico Collins</t>
+          <t>David Montgomery</t>
         </is>
       </c>
       <c r="C324" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D324" s="5" t="inlineStr">
@@ -41658,7 +41658,7 @@
       </c>
       <c r="F324" s="5" t="inlineStr">
         <is>
-          <t>Collins didn't play in Thursday's preseason game against the Raiders.</t>
+          <t>Montgomery did not play in Houston's preseason game against Las Vegas on Thursday, according to Texans Wire.</t>
         </is>
       </c>
     </row>
@@ -41670,12 +41670,12 @@
       </c>
       <c r="B325" s="4" t="inlineStr">
         <is>
-          <t>David Montgomery</t>
+          <t>Collin Wright</t>
         </is>
       </c>
       <c r="C325" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D325" s="4" t="inlineStr">
@@ -41688,11 +41688,7 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F325" s="4" t="inlineStr">
-        <is>
-          <t>Montgomery did not play in Houston's preseason game against Las Vegas on Thursday, according to Texans Wire.</t>
-        </is>
-      </c>
+      <c r="F325" s="4" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" s="5" t="inlineStr">
@@ -41702,12 +41698,12 @@
       </c>
       <c r="B326" s="5" t="inlineStr">
         <is>
-          <t>Collin Wright</t>
+          <t>Xavier Hutchinson</t>
         </is>
       </c>
       <c r="C326" s="5" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D326" s="5" t="inlineStr">
@@ -41720,7 +41716,11 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F326" s="5" t="inlineStr"/>
+      <c r="F326" s="5" t="inlineStr">
+        <is>
+          <t>Hutchinson caught one of two targets for minus-1 yard in Thursday's 22-20 preseason loss to the Raiders.</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="4" t="inlineStr">
@@ -41730,12 +41730,12 @@
       </c>
       <c r="B327" s="4" t="inlineStr">
         <is>
-          <t>Xavier Hutchinson</t>
+          <t>Woody Marks</t>
         </is>
       </c>
       <c r="C327" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D327" s="4" t="inlineStr">
@@ -41750,7 +41750,7 @@
       </c>
       <c r="F327" s="4" t="inlineStr">
         <is>
-          <t>Hutchinson caught one of two targets for minus-1 yard in Thursday's 22-20 preseason loss to the Raiders.</t>
+          <t>Marks rushed four times for 37 yards and a touchdown while catching his only target for six yards in Thursday's 22-20 preseason loss to the Raiders.</t>
         </is>
       </c>
     </row>
@@ -41762,12 +41762,12 @@
       </c>
       <c r="B328" s="5" t="inlineStr">
         <is>
-          <t>Woody Marks</t>
+          <t>C.J. Stroud</t>
         </is>
       </c>
       <c r="C328" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D328" s="5" t="inlineStr">
@@ -41782,7 +41782,7 @@
       </c>
       <c r="F328" s="5" t="inlineStr">
         <is>
-          <t>Marks rushed four times for 37 yards and a touchdown while catching his only target for six yards in Thursday's 22-20 preseason loss to the Raiders.</t>
+          <t>Stroud completed four of six passes for 27 yards in Thursday's 22-20 preseason loss to the Raiders.</t>
         </is>
       </c>
     </row>
@@ -41794,27 +41794,27 @@
       </c>
       <c r="B329" s="4" t="inlineStr">
         <is>
-          <t>C.J. Stroud</t>
+          <t>Jaylin Noel</t>
         </is>
       </c>
       <c r="C329" s="4" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D329" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E329" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F329" s="4" t="inlineStr">
         <is>
-          <t>Stroud completed four of six passes for 27 yards in Thursday's 22-20 preseason loss to the Raiders.</t>
+          <t>With Jayden Higgins having reportedly suffered a torn ACL, Noel (hamstring/finger) is a candidate to see added work in Houston's offense this coming season, DJ Bien-Aime of ESPN reports.</t>
         </is>
       </c>
     </row>
@@ -49049,7 +49049,7 @@
       </c>
       <c r="E557" s="4" t="inlineStr">
         <is>
-          <t>Hamstring</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F557" s="4" t="inlineStr">
@@ -49081,7 +49081,7 @@
       </c>
       <c r="E558" s="5" t="inlineStr">
         <is>
-          <t>Ankle</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F558" s="5" t="inlineStr">
@@ -49130,27 +49130,27 @@
       </c>
       <c r="B560" s="5" t="inlineStr">
         <is>
-          <t>Torricelli Simpkins III</t>
+          <t>Daniel Carlson</t>
         </is>
       </c>
       <c r="C560" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="D560" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E560" s="5" t="inlineStr">
         <is>
-          <t>Concussion</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F560" s="5" t="inlineStr">
         <is>
-          <t>Simpkins has entered the league's concussion protocol following the Saints' 34-0 loss to the Rams in Saturday's preseason game, Matthew Paras of The New Orleans Times-Picayune reports.</t>
+          <t>Carlson agreed to a contract with the Saints on Monday, Mike Garafolo of NFL Network reports.</t>
         </is>
       </c>
     </row>
@@ -49162,27 +49162,27 @@
       </c>
       <c r="B561" s="4" t="inlineStr">
         <is>
-          <t>Brien Taylor</t>
+          <t>Zamir White</t>
         </is>
       </c>
       <c r="C561" s="4" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D561" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E561" s="4" t="inlineStr">
         <is>
-          <t>Stinger</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F561" s="4" t="inlineStr">
         <is>
-          <t>Taylor was diagnosed with a neck injury following the Saints' 34-0 preseason loss to the Rams on Saturday, Matthew Paras of The New Orleans Times-Picayune reports.</t>
+          <t>White is being traded from San Francisco to New Orleans on Sunday in exchange for linebacker Deion Jones, per sources, Adam Schefter of ESPN reports.</t>
         </is>
       </c>
     </row>
@@ -49194,12 +49194,12 @@
       </c>
       <c r="B562" s="5" t="inlineStr">
         <is>
-          <t>Lorenzo Styles Jr.</t>
+          <t>Torricelli Simpkins III</t>
         </is>
       </c>
       <c r="C562" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D562" s="5" t="inlineStr">
@@ -49209,12 +49209,12 @@
       </c>
       <c r="E562" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Concussion</t>
         </is>
       </c>
       <c r="F562" s="5" t="inlineStr">
         <is>
-          <t>Styles sustained a calf injury during the Saints' 34-0 preseason loss to the Rams on Saturday, Matthew Paras of The New Orleans Times-Picayune reports.</t>
+          <t>Simpkins has entered the league's concussion protocol following the Saints' 34-0 loss to the Rams in Saturday's preseason game, Matthew Paras of The New Orleans Times-Picayune reports.</t>
         </is>
       </c>
     </row>
@@ -49226,12 +49226,12 @@
       </c>
       <c r="B563" s="4" t="inlineStr">
         <is>
-          <t>Devin Neal</t>
+          <t>Brien Taylor</t>
         </is>
       </c>
       <c r="C563" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="D563" s="4" t="inlineStr">
@@ -49241,12 +49241,12 @@
       </c>
       <c r="E563" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Stinger</t>
         </is>
       </c>
       <c r="F563" s="4" t="inlineStr">
         <is>
-          <t>Neal sustained a hamstring injury during the Saints' 34-0 preseason loss to the Rams on Saturday, Matthew Paras of The New Orleans Times-Picayune reports.</t>
+          <t>Taylor was diagnosed with a neck injury following the Saints' 34-0 preseason loss to the Rams on Saturday, Matthew Paras of The New Orleans Times-Picayune reports.</t>
         </is>
       </c>
     </row>
@@ -49258,12 +49258,12 @@
       </c>
       <c r="B564" s="5" t="inlineStr">
         <is>
-          <t>Bub Means</t>
+          <t>Lorenzo Styles Jr.</t>
         </is>
       </c>
       <c r="C564" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D564" s="5" t="inlineStr">
@@ -49278,7 +49278,7 @@
       </c>
       <c r="F564" s="5" t="inlineStr">
         <is>
-          <t>Means injured his hamstring during Saturday's 34-0 preseason loss to the Rams, Matthew Paras of The New Orleans Times-Picayune reports.</t>
+          <t>Styles sustained a calf injury during the Saints' 34-0 preseason loss to the Rams on Saturday, Matthew Paras of The New Orleans Times-Picayune reports.</t>
         </is>
       </c>
     </row>
@@ -49290,12 +49290,12 @@
       </c>
       <c r="B565" s="4" t="inlineStr">
         <is>
-          <t>Moliki Matavao</t>
+          <t>Devin Neal</t>
         </is>
       </c>
       <c r="C565" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D565" s="4" t="inlineStr">
@@ -49310,7 +49310,7 @@
       </c>
       <c r="F565" s="4" t="inlineStr">
         <is>
-          <t>Matavao was diagnosed with a knee injury following the Saints' 34-0 preseason loss to the Rams on Saturday, Matthew Paras of The New Orleans Times-Picayune reports.</t>
+          <t>Neal sustained a hamstring injury during the Saints' 34-0 preseason loss to the Rams on Saturday, Matthew Paras of The New Orleans Times-Picayune reports.</t>
         </is>
       </c>
     </row>
@@ -49322,27 +49322,27 @@
       </c>
       <c r="B566" s="5" t="inlineStr">
         <is>
-          <t>Kendre Miller</t>
+          <t>Bub Means</t>
         </is>
       </c>
       <c r="C566" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D566" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E566" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F566" s="5" t="inlineStr">
         <is>
-          <t>Miller turned six carries into 22 yards and did not haul in his lone target during the Saints' 34-0 preseason loss to the Rams on Saturday. He also returned one kickoff for 29 yards.</t>
+          <t>Means injured his hamstring during Saturday's 34-0 preseason loss to the Rams, Matthew Paras of The New Orleans Times-Picayune reports.</t>
         </is>
       </c>
     </row>
@@ -49354,27 +49354,27 @@
       </c>
       <c r="B567" s="4" t="inlineStr">
         <is>
-          <t>Spencer Rattler</t>
+          <t>Moliki Matavao</t>
         </is>
       </c>
       <c r="C567" s="4" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D567" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E567" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F567" s="4" t="inlineStr">
         <is>
-          <t>Rattler completed 14 of 23 passes for 141 yards, zero touchdowns and one interception while adding five carries for 21 yards during the Saints' 34-0 preseason loss to the Rams on Saturday.</t>
+          <t>Matavao was diagnosed with a knee injury following the Saints' 34-0 preseason loss to the Rams on Saturday, Matthew Paras of The New Orleans Times-Picayune reports.</t>
         </is>
       </c>
     </row>
@@ -49386,12 +49386,12 @@
       </c>
       <c r="B568" s="5" t="inlineStr">
         <is>
-          <t>Zach Wilson</t>
+          <t>Kendre Miller</t>
         </is>
       </c>
       <c r="C568" s="5" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D568" s="5" t="inlineStr">
@@ -49406,7 +49406,7 @@
       </c>
       <c r="F568" s="5" t="inlineStr">
         <is>
-          <t>Wilson completed six of 12 passes for 55 yards, zero touchdowns and one interception while adding four carries for 19 yards during the Saints' 34-0 loss to the Rams on Saturday.</t>
+          <t>Miller turned six carries into 22 yards and did not haul in his lone target during the Saints' 34-0 preseason loss to the Rams on Saturday. He also returned one kickoff for 29 yards.</t>
         </is>
       </c>
     </row>
@@ -49418,12 +49418,12 @@
       </c>
       <c r="B569" s="4" t="inlineStr">
         <is>
-          <t>Bryce Lance</t>
+          <t>Spencer Rattler</t>
         </is>
       </c>
       <c r="C569" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D569" s="4" t="inlineStr">
@@ -49438,7 +49438,7 @@
       </c>
       <c r="F569" s="4" t="inlineStr">
         <is>
-          <t>Lance caught both of his targets for 16 yards during the Saints' 34-0 preseason loss to the Rams on Saturday.</t>
+          <t>Rattler completed 14 of 23 passes for 141 yards, zero touchdowns and one interception while adding five carries for 21 yards during the Saints' 34-0 preseason loss to the Rams on Saturday.</t>
         </is>
       </c>
     </row>
@@ -49450,27 +49450,27 @@
       </c>
       <c r="B570" s="5" t="inlineStr">
         <is>
-          <t>John Ridgeway III</t>
+          <t>Zach Wilson</t>
         </is>
       </c>
       <c r="C570" s="5" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D570" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E570" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F570" s="5" t="inlineStr">
         <is>
-          <t>Ridgeway exited Thursday's practice with a foot injury, Nick Underhill of NewOrleans.Football reports.</t>
+          <t>Wilson completed six of 12 passes for 55 yards, zero touchdowns and one interception while adding four carries for 19 yards during the Saints' 34-0 loss to the Rams on Saturday.</t>
         </is>
       </c>
     </row>
@@ -49482,12 +49482,12 @@
       </c>
       <c r="B571" s="4" t="inlineStr">
         <is>
-          <t>Travis Etienne Jr.</t>
+          <t>Bryce Lance</t>
         </is>
       </c>
       <c r="C571" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D571" s="4" t="inlineStr">
@@ -49502,7 +49502,7 @@
       </c>
       <c r="F571" s="4" t="inlineStr">
         <is>
-          <t>Etienne could be in store for a heavier workload to begin the season after teammate Alvin Kamara (knee) sustained an MCL sprain during Tuesday's joint practice with the Cowboys, Jeff Duncan of The Athletic reports.</t>
+          <t>Lance caught both of his targets for 16 yards during the Saints' 34-0 preseason loss to the Rams on Saturday.</t>
         </is>
       </c>
     </row>
@@ -49514,12 +49514,12 @@
       </c>
       <c r="B572" s="5" t="inlineStr">
         <is>
-          <t>Alvin Kamara</t>
+          <t>John Ridgeway III</t>
         </is>
       </c>
       <c r="C572" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="D572" s="5" t="inlineStr">
@@ -49529,12 +49529,12 @@
       </c>
       <c r="E572" s="5" t="inlineStr">
         <is>
-          <t>Sprain</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F572" s="5" t="inlineStr">
         <is>
-          <t>Kamara (knee) is expected to be out for at least one month after sustaining an MCL sprain during Tuesday's joint practice with the Cowboys, Adam Schefter of ESPN reports.</t>
+          <t>Ridgeway exited Thursday's practice with a foot injury, Nick Underhill of NewOrleans.Football reports.</t>
         </is>
       </c>
     </row>
@@ -49546,27 +49546,27 @@
       </c>
       <c r="B573" s="4" t="inlineStr">
         <is>
-          <t>Jordyn Tyson</t>
+          <t>Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="C573" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D573" s="4" t="inlineStr">
         <is>
-          <t>Doubtful</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E573" s="4" t="inlineStr">
         <is>
-          <t>Strain</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F573" s="4" t="inlineStr">
         <is>
-          <t>doubtful</t>
+          <t>Etienne could be in store for a heavier workload to begin the season after teammate Alvin Kamara (knee) sustained an MCL sprain during Tuesday's joint practice with the Cowboys, Jeff Duncan of The Athletic reports.</t>
         </is>
       </c>
     </row>
@@ -49578,12 +49578,12 @@
       </c>
       <c r="B574" s="5" t="inlineStr">
         <is>
-          <t>Pete Werner</t>
+          <t>Alvin Kamara</t>
         </is>
       </c>
       <c r="C574" s="5" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D574" s="5" t="inlineStr">
@@ -49593,12 +49593,12 @@
       </c>
       <c r="E574" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Sprain</t>
         </is>
       </c>
       <c r="F574" s="5" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>Kamara (knee) is expected to be out for at least one month after sustaining an MCL sprain during Tuesday's joint practice with the Cowboys, Adam Schefter of ESPN reports.</t>
         </is>
       </c>
     </row>
@@ -49610,27 +49610,27 @@
       </c>
       <c r="B575" s="4" t="inlineStr">
         <is>
-          <t>Dillon Radunz</t>
+          <t>Jordyn Tyson</t>
         </is>
       </c>
       <c r="C575" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D575" s="4" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Doubtful</t>
         </is>
       </c>
       <c r="E575" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Strain</t>
         </is>
       </c>
       <c r="F575" s="4" t="inlineStr">
         <is>
-          <t>ir</t>
+          <t>doubtful</t>
         </is>
       </c>
     </row>
@@ -49642,17 +49642,17 @@
       </c>
       <c r="B576" s="5" t="inlineStr">
         <is>
-          <t>Brock Rechsteiner</t>
+          <t>Pete Werner</t>
         </is>
       </c>
       <c r="C576" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D576" s="5" t="inlineStr">
         <is>
-          <t>Suspension</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E576" s="5" t="inlineStr">
@@ -49662,7 +49662,7 @@
       </c>
       <c r="F576" s="5" t="inlineStr">
         <is>
-          <t>reserve-sus</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -49674,17 +49674,17 @@
       </c>
       <c r="B577" s="4" t="inlineStr">
         <is>
-          <t>Quincy Riley</t>
+          <t>Dillon Radunz</t>
         </is>
       </c>
       <c r="C577" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D577" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E577" s="4" t="inlineStr">
@@ -49694,7 +49694,7 @@
       </c>
       <c r="F577" s="4" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>ir</t>
         </is>
       </c>
     </row>
@@ -49706,17 +49706,17 @@
       </c>
       <c r="B578" s="5" t="inlineStr">
         <is>
-          <t>Chris Rumph II</t>
+          <t>Brock Rechsteiner</t>
         </is>
       </c>
       <c r="C578" s="5" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D578" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Suspension</t>
         </is>
       </c>
       <c r="E578" s="5" t="inlineStr">
@@ -49726,7 +49726,7 @@
       </c>
       <c r="F578" s="5" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>reserve-sus</t>
         </is>
       </c>
     </row>
@@ -49738,12 +49738,12 @@
       </c>
       <c r="B579" s="4" t="inlineStr">
         <is>
-          <t>Cameron Jordan</t>
+          <t>Quincy Riley</t>
         </is>
       </c>
       <c r="C579" s="4" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D579" s="4" t="inlineStr">
@@ -49817,12 +49817,12 @@
       </c>
       <c r="E581" s="4" t="inlineStr">
         <is>
-          <t>Undisclosed</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F581" s="4" t="inlineStr">
         <is>
-          <t>Johnson left Monday's practice due to an unspecified issue, Dan Bentonof USA Today reports.</t>
+          <t>Johnson left Monday's practice due to an unspecified issue, Dan Benton of USA Today reports.</t>
         </is>
       </c>
     </row>
@@ -51390,12 +51390,12 @@
       </c>
       <c r="B631" s="4" t="inlineStr">
         <is>
-          <t>Elijah Moore</t>
+          <t>Jordan Mims</t>
         </is>
       </c>
       <c r="C631" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D631" s="4" t="inlineStr">
@@ -51410,7 +51410,7 @@
       </c>
       <c r="F631" s="4" t="inlineStr">
         <is>
-          <t>Moore (neck) suited up for Monday's training camp practice, Olivia Reiner of The Philadelphia Inquirer reports.</t>
+          <t>The Eagles signed Mims to a contract Monday.</t>
         </is>
       </c>
     </row>
@@ -51422,12 +51422,12 @@
       </c>
       <c r="B632" s="5" t="inlineStr">
         <is>
-          <t>Dameon Pierce</t>
+          <t>Elijah Moore</t>
         </is>
       </c>
       <c r="C632" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D632" s="5" t="inlineStr">
@@ -51442,7 +51442,7 @@
       </c>
       <c r="F632" s="5" t="inlineStr">
         <is>
-          <t>Pierce (hamstring) participated in Monday's training camp practice, Brooks Kubena of The Athletic reports.</t>
+          <t>Moore (neck) suited up for Monday's training camp practice, Olivia Reiner of The Philadelphia Inquirer reports.</t>
         </is>
       </c>
     </row>
@@ -51454,12 +51454,12 @@
       </c>
       <c r="B633" s="4" t="inlineStr">
         <is>
-          <t>Dontayvion Wicks</t>
+          <t>Dameon Pierce</t>
         </is>
       </c>
       <c r="C633" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D633" s="4" t="inlineStr">
@@ -51474,7 +51474,7 @@
       </c>
       <c r="F633" s="4" t="inlineStr">
         <is>
-          <t>Wicks stood out with his route running during the Eagles' joint practices with the Patriots last Wednesday and Thursday, Cayden Steele of NJ.com reports.</t>
+          <t>Pierce (hamstring) participated in Monday's training camp practice, Brooks Kubena of The Athletic reports.</t>
         </is>
       </c>
     </row>
@@ -51486,27 +51486,27 @@
       </c>
       <c r="B634" s="5" t="inlineStr">
         <is>
-          <t>Eli Stowers</t>
+          <t>Dontayvion Wicks</t>
         </is>
       </c>
       <c r="C634" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D634" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E634" s="5" t="inlineStr">
         <is>
-          <t>Hamstring</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F634" s="5" t="inlineStr">
         <is>
-          <t>Stowers (hamstring) won't practice Monday, Martin Frank of The Delaware News Journal reports.</t>
+          <t>Wicks stood out with his route running during the Eagles' joint practices with the Patriots last Wednesday and Thursday, Cayden Steele of NJ.com reports.</t>
         </is>
       </c>
     </row>
@@ -51518,27 +51518,27 @@
       </c>
       <c r="B635" s="4" t="inlineStr">
         <is>
-          <t>Makai Lemon</t>
+          <t>Eli Stowers</t>
         </is>
       </c>
       <c r="C635" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D635" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E635" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F635" s="4" t="inlineStr">
         <is>
-          <t>Lemon (hamstring) was a full participant in Monday's practice, EJ Smith of The PHLY Sports reports.</t>
+          <t>Stowers (hamstring) won't practice Monday, Martin Frank of The Delaware News Journal reports.</t>
         </is>
       </c>
     </row>
@@ -51550,7 +51550,7 @@
       </c>
       <c r="B636" s="5" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>Makai Lemon</t>
         </is>
       </c>
       <c r="C636" s="5" t="inlineStr">
@@ -51570,7 +51570,7 @@
       </c>
       <c r="F636" s="5" t="inlineStr">
         <is>
-          <t>Smith (hamstring) is a full participant in Monday's practice, EJ Smith of PHLY Sports reports.</t>
+          <t>Lemon (hamstring) was a full participant in Monday's practice, EJ Smith of The PHLY Sports reports.</t>
         </is>
       </c>
     </row>
@@ -51582,12 +51582,12 @@
       </c>
       <c r="B637" s="4" t="inlineStr">
         <is>
-          <t>Jake Elliott</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="C637" s="4" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D637" s="4" t="inlineStr">
@@ -51602,7 +51602,7 @@
       </c>
       <c r="F637" s="4" t="inlineStr">
         <is>
-          <t>Elliott connected on all three of his extra-point tries and did not attempt any field goals in the Eagles' 24-21 preseason loss to the Patriots on Saturday.</t>
+          <t>Smith (hamstring) is a full participant in Monday's practice, EJ Smith of PHLY Sports reports.</t>
         </is>
       </c>
     </row>
@@ -51614,27 +51614,27 @@
       </c>
       <c r="B638" s="5" t="inlineStr">
         <is>
-          <t>Johnny Wilson</t>
+          <t>Jake Elliott</t>
         </is>
       </c>
       <c r="C638" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="D638" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E638" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F638" s="5" t="inlineStr">
         <is>
-          <t>Wilson (knee) reverted to Philadelphia's injured reserve Saturday, per the NFL's transaction log.</t>
+          <t>Elliott connected on all three of his extra-point tries and did not attempt any field goals in the Eagles' 24-21 preseason loss to the Patriots on Saturday.</t>
         </is>
       </c>
     </row>
@@ -51646,27 +51646,27 @@
       </c>
       <c r="B639" s="4" t="inlineStr">
         <is>
-          <t>Zeke Correll</t>
+          <t>Johnny Wilson</t>
         </is>
       </c>
       <c r="C639" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D639" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E639" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F639" s="4" t="inlineStr">
         <is>
-          <t>The Eagles signed Correll to a contract Friday.</t>
+          <t>Wilson (knee) reverted to Philadelphia's injured reserve Saturday, per the NFL's transaction log.</t>
         </is>
       </c>
     </row>
@@ -51678,27 +51678,27 @@
       </c>
       <c r="B640" s="5" t="inlineStr">
         <is>
-          <t>Tariq Castro-Fields</t>
+          <t>Zeke Correll</t>
         </is>
       </c>
       <c r="C640" s="5" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D640" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E640" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F640" s="5" t="inlineStr">
         <is>
-          <t>The Eagles placed Castro-Fields (heel) on injured reserve Friday.</t>
+          <t>The Eagles signed Correll to a contract Friday.</t>
         </is>
       </c>
     </row>
@@ -51710,27 +51710,27 @@
       </c>
       <c r="B641" s="4" t="inlineStr">
         <is>
-          <t>Brandon Hayes</t>
+          <t>Tariq Castro-Fields</t>
         </is>
       </c>
       <c r="C641" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D641" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E641" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F641" s="4" t="inlineStr">
         <is>
-          <t>The Eagles signed Hayes to a contract Friday.</t>
+          <t>The Eagles placed Castro-Fields (heel) on injured reserve Friday.</t>
         </is>
       </c>
     </row>
@@ -51742,27 +51742,27 @@
       </c>
       <c r="B642" s="5" t="inlineStr">
         <is>
-          <t>Jakorian Bennett</t>
+          <t>Brandon Hayes</t>
         </is>
       </c>
       <c r="C642" s="5" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D642" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E642" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F642" s="5" t="inlineStr">
         <is>
-          <t>Bennett (knee) did not practice Thursday, Andrew DiCecco of InsideTheBirds.com reports.</t>
+          <t>The Eagles signed Hayes to a contract Friday.</t>
         </is>
       </c>
     </row>
@@ -51774,12 +51774,12 @@
       </c>
       <c r="B643" s="4" t="inlineStr">
         <is>
-          <t>Byron Young</t>
+          <t>Jakorian Bennett</t>
         </is>
       </c>
       <c r="C643" s="4" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D643" s="4" t="inlineStr">
@@ -51794,7 +51794,7 @@
       </c>
       <c r="F643" s="4" t="inlineStr">
         <is>
-          <t>Young (shoulder) did not participate in Wednesday's practice, Dave Zangaro of NBC Sports Philadelphia reports.</t>
+          <t>Bennett (knee) did not practice Thursday, Andrew DiCecco of InsideTheBirds.com reports.</t>
         </is>
       </c>
     </row>
@@ -51806,12 +51806,12 @@
       </c>
       <c r="B644" s="5" t="inlineStr">
         <is>
-          <t>John Ojukwu</t>
+          <t>Byron Young</t>
         </is>
       </c>
       <c r="C644" s="5" t="inlineStr">
         <is>
-          <t>OT</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="D644" s="5" t="inlineStr">
@@ -51826,7 +51826,7 @@
       </c>
       <c r="F644" s="5" t="inlineStr">
         <is>
-          <t>Ojukwu (pectoral) did not participate during the Eagles' training camp practice Wednesday, Andrew DiCecco of InsideTheBirds.com reports.</t>
+          <t>Young (shoulder) did not participate in Wednesday's practice, Dave Zangaro of NBC Sports Philadelphia reports.</t>
         </is>
       </c>
     </row>
@@ -51838,12 +51838,12 @@
       </c>
       <c r="B645" s="4" t="inlineStr">
         <is>
-          <t>Shaun Wade</t>
+          <t>John Ojukwu</t>
         </is>
       </c>
       <c r="C645" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>OT</t>
         </is>
       </c>
       <c r="D645" s="4" t="inlineStr">
@@ -51858,7 +51858,7 @@
       </c>
       <c r="F645" s="4" t="inlineStr">
         <is>
-          <t>Wade (shoulder) did not participate in Wednesday's practice, Dave Zangaro of NBC Sports Philadelphia reports.</t>
+          <t>Ojukwu (pectoral) did not participate during the Eagles' training camp practice Wednesday, Andrew DiCecco of InsideTheBirds.com reports.</t>
         </is>
       </c>
     </row>
@@ -51870,7 +51870,7 @@
       </c>
       <c r="B646" s="5" t="inlineStr">
         <is>
-          <t>Quinyon Mitchell</t>
+          <t>Shaun Wade</t>
         </is>
       </c>
       <c r="C646" s="5" t="inlineStr">
@@ -51880,17 +51880,17 @@
       </c>
       <c r="D646" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E646" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F646" s="5" t="inlineStr">
         <is>
-          <t>Mitchell (lower body) was a full participant in Wednesday's joint practice with the Patriots, Tim McManus of ESPN.com reports.</t>
+          <t>Wade (shoulder) did not participate in Wednesday's practice, Dave Zangaro of NBC Sports Philadelphia reports.</t>
         </is>
       </c>
     </row>
@@ -51902,27 +51902,27 @@
       </c>
       <c r="B647" s="4" t="inlineStr">
         <is>
-          <t>Grant Calcaterra</t>
+          <t>Quinyon Mitchell</t>
         </is>
       </c>
       <c r="C647" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D647" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E647" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F647" s="4" t="inlineStr">
         <is>
-          <t>Calcatarra (back) did not participate in Wednesday's practice, Dave Zangaro of NBC Sports Philadelphia reports.</t>
+          <t>Mitchell (lower body) was a full participant in Wednesday's joint practice with the Patriots, Tim McManus of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -51934,27 +51934,27 @@
       </c>
       <c r="B648" s="5" t="inlineStr">
         <is>
-          <t>Jonathan Greenard</t>
+          <t>Grant Calcaterra</t>
         </is>
       </c>
       <c r="C648" s="5" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D648" s="5" t="inlineStr">
         <is>
-          <t>Out</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E648" s="5" t="inlineStr">
         <is>
-          <t>Surgery</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F648" s="5" t="inlineStr">
         <is>
-          <t>The Eagles are worried Greenard (pectoral) could miss the Week 1 divisional showdown with the Commanders due to injury, Mike Garafolo of NFL Network reports.</t>
+          <t>Calcatarra (back) did not participate in Wednesday's practice, Dave Zangaro of NBC Sports Philadelphia reports.</t>
         </is>
       </c>
     </row>
@@ -51966,27 +51966,27 @@
       </c>
       <c r="B649" s="4" t="inlineStr">
         <is>
-          <t>Tank Bigsby</t>
+          <t>Jonathan Greenard</t>
         </is>
       </c>
       <c r="C649" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D649" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="E649" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Surgery</t>
         </is>
       </c>
       <c r="F649" s="4" t="inlineStr">
         <is>
-          <t>Bigsby (toe) will participate in Wednesday's practice, Olivia Reiner of The Philadelphia Inquirer reports.</t>
+          <t>The Eagles are worried Greenard (pectoral) could miss the Week 1 divisional showdown with the Commanders due to injury, Mike Garafolo of NFL Network reports.</t>
         </is>
       </c>
     </row>
@@ -51998,27 +51998,27 @@
       </c>
       <c r="B650" s="5" t="inlineStr">
         <is>
-          <t>Danny Gray</t>
+          <t>Tank Bigsby</t>
         </is>
       </c>
       <c r="C650" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D650" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E650" s="5" t="inlineStr">
         <is>
-          <t>Concussion</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F650" s="5" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>Bigsby (toe) will participate in Wednesday's practice, Olivia Reiner of The Philadelphia Inquirer reports.</t>
         </is>
       </c>
     </row>
@@ -52030,12 +52030,12 @@
       </c>
       <c r="B651" s="4" t="inlineStr">
         <is>
-          <t>Jonathan Jones</t>
+          <t>Danny Gray</t>
         </is>
       </c>
       <c r="C651" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D651" s="4" t="inlineStr">
@@ -52045,7 +52045,7 @@
       </c>
       <c r="E651" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Concussion</t>
         </is>
       </c>
       <c r="F651" s="4" t="inlineStr">
@@ -52062,12 +52062,12 @@
       </c>
       <c r="B652" s="5" t="inlineStr">
         <is>
-          <t>Micah Morris</t>
+          <t>Jonathan Jones</t>
         </is>
       </c>
       <c r="C652" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D652" s="5" t="inlineStr">
@@ -52094,12 +52094,12 @@
       </c>
       <c r="B653" s="4" t="inlineStr">
         <is>
-          <t>Chance Campbell</t>
+          <t>Micah Morris</t>
         </is>
       </c>
       <c r="C653" s="4" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D653" s="4" t="inlineStr">
@@ -52126,12 +52126,12 @@
       </c>
       <c r="B654" s="5" t="inlineStr">
         <is>
-          <t>Britain Covey</t>
+          <t>Chance Campbell</t>
         </is>
       </c>
       <c r="C654" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D654" s="5" t="inlineStr">
@@ -52338,7 +52338,7 @@
       </c>
       <c r="F660" s="5" t="inlineStr">
         <is>
-          <t>Steelers head coach Mike McCarthy said that Ramsey (knee) will be activated from the PUP list Monday, Chris Adamski of TribLive.com reports.</t>
+          <t>Steelers head coach Mike McCarthy said that Ramsey (knee) will be activated from the active/PUP list Monday, Chris Adamski of TribLive.com reports.</t>
         </is>
       </c>
     </row>
@@ -52990,12 +52990,12 @@
       </c>
       <c r="B681" s="4" t="inlineStr">
         <is>
-          <t>Josiah Deguara</t>
+          <t>Deion Jones</t>
         </is>
       </c>
       <c r="C681" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D681" s="4" t="inlineStr">
@@ -53010,7 +53010,7 @@
       </c>
       <c r="F681" s="4" t="inlineStr">
         <is>
-          <t>Deguara was released by the 49ers on Monday.</t>
+          <t>Jones was traded from the Saints to the 49ers in exchange for running back Zamir White on Sunday, Adam Schefter of ESPN reports.</t>
         </is>
       </c>
     </row>
@@ -53778,7 +53778,7 @@
       </c>
       <c r="F705" s="4" t="inlineStr">
         <is>
-          <t>Thomas (hand) might be able to play in Seattle's preseason game versus Kansas City on Aug. 28, Brady Henderson of ESPN reports.</t>
+          <t>Thomas (hand) might be able to play in Seattle's preseason finale versus Kansas City on Friday, Brady Henderson of ESPN reports.</t>
         </is>
       </c>
     </row>
@@ -57038,10 +57038,10 @@
         </is>
       </c>
       <c r="D5" s="15" t="n">
-        <v>72.3</v>
+        <v>71.8</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>18.1</v>
@@ -57059,7 +57059,7 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>Wind 9 mph (gusts 18)</t>
+          <t>Wind 8 mph (gusts 18)</t>
         </is>
       </c>
     </row>
@@ -57080,10 +57080,10 @@
         </is>
       </c>
       <c r="D6" s="17" t="n">
-        <v>73.5</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="F6" s="17" t="n">
         <v>4.7</v>
@@ -57093,7 +57093,7 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Light drizzle</t>
         </is>
       </c>
       <c r="I6" s="24" t="n">
@@ -57118,10 +57118,10 @@
         </is>
       </c>
       <c r="D7" s="15" t="n">
-        <v>106.7</v>
+        <v>107.4</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>16.9</v>
+        <v>19.7</v>
       </c>
       <c r="F7" s="15" t="n">
         <v>18.8</v>
@@ -57160,10 +57160,10 @@
         </is>
       </c>
       <c r="D8" s="17" t="n">
-        <v>78.8</v>
+        <v>76.5</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="F8" s="17" t="n">
         <v>8.699999999999999</v>
@@ -57173,7 +57173,7 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>Mainly clear</t>
+          <t>Overcast</t>
         </is>
       </c>
       <c r="I8" s="24" t="n">
@@ -57201,7 +57201,7 @@
         <v>82.90000000000001</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="F9" s="15" t="n">
         <v>4.5</v>
@@ -57239,7 +57239,7 @@
         <v>89</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>7.7</v>
+        <v>2.7</v>
       </c>
       <c r="F10" s="17" t="n">
         <v>6.3</v>
@@ -57249,7 +57249,7 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>Thunderstorm</t>
+          <t>Overcast</t>
         </is>
       </c>
       <c r="I10" s="24" t="n">
@@ -57274,10 +57274,10 @@
         </is>
       </c>
       <c r="D11" s="15" t="n">
-        <v>74.59999999999999</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="F11" s="15" t="n">
         <v>14.8</v>
@@ -57316,10 +57316,10 @@
         </is>
       </c>
       <c r="D12" s="17" t="n">
-        <v>80.2</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>7.3</v>
+        <v>8.5</v>
       </c>
       <c r="F12" s="17" t="n">
         <v>13.9</v>
@@ -57354,10 +57354,10 @@
         </is>
       </c>
       <c r="D13" s="15" t="n">
-        <v>84.59999999999999</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>11.4</v>
+        <v>11.9</v>
       </c>
       <c r="F13" s="15" t="n">
         <v>13</v>
@@ -57367,7 +57367,7 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Light drizzle</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
@@ -57396,10 +57396,10 @@
         </is>
       </c>
       <c r="D14" s="17" t="n">
-        <v>79.3</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>2.7</v>
+        <v>4.9</v>
       </c>
       <c r="F14" s="17" t="n">
         <v>1.8</v>
@@ -57434,10 +57434,10 @@
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>86</v>
+        <v>81.5</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>7.3</v>
+        <v>5.8</v>
       </c>
       <c r="F15" s="15" t="n">
         <v>13.2</v>
@@ -57447,7 +57447,7 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Overcast</t>
         </is>
       </c>
       <c r="I15" s="9" t="n">
@@ -57472,10 +57472,10 @@
         </is>
       </c>
       <c r="D16" s="17" t="n">
-        <v>102.7</v>
+        <v>102.1</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>2.9</v>
+        <v>11.2</v>
       </c>
       <c r="F16" s="17" t="n">
         <v>3.8</v>
@@ -57493,7 +57493,7 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>103°F · retractable roof — effect halved</t>
+          <t>102°F · retractable roof — effect halved</t>
         </is>
       </c>
     </row>
@@ -57514,10 +57514,10 @@
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>63.4</v>
+        <v>65.7</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="F17" s="15" t="n">
         <v>16.8</v>
@@ -57552,10 +57552,10 @@
         </is>
       </c>
       <c r="D18" s="17" t="n">
-        <v>85.3</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>5.8</v>
+        <v>9.4</v>
       </c>
       <c r="F18" s="17" t="n">
         <v>6.5</v>
@@ -57590,10 +57590,10 @@
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>79.40000000000001</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>5.4</v>
+        <v>6.3</v>
       </c>
       <c r="F19" s="15" t="n">
         <v>6.3</v>
@@ -57628,10 +57628,10 @@
         </is>
       </c>
       <c r="D20" s="17" t="n">
-        <v>91.7</v>
+        <v>93.5</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="F20" s="17" t="n">
         <v>5.8</v>
@@ -57641,13 +57641,17 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>Partly cloudy</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="I20" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="5" t="inlineStr"/>
+        <v>-0.5</v>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>94°F</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -57665,15 +57669,21 @@
           <t>canopy</t>
         </is>
       </c>
-      <c r="D21" s="15" t="n"/>
-      <c r="E21" s="15" t="n"/>
-      <c r="F21" s="15" t="n"/>
+      <c r="D21" s="15" t="n">
+        <v>85.3</v>
+      </c>
+      <c r="E21" s="15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="F21" s="15" t="n">
+        <v>4</v>
+      </c>
       <c r="G21" s="15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="I21" s="9" t="n">

--- a/NFL_Edge_Model.xlsx
+++ b/NFL_Edge_Model.xlsx
@@ -692,7 +692,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Snapshot of the live model, generated 2026-08-26T03:36:14+00:00. Read-only: the model runs in the pipeline, not in this file.</t>
+          <t>Snapshot of the live model, generated 2026-08-26T07:34:34+00:00. Read-only: the model runs in the pipeline, not in this file.</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>2026-08-26T03:36:14+00:00</t>
+          <t>2026-08-26T07:34:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
         <v>0.0586</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>3.63</v>
+        <v>3.64</v>
       </c>
       <c r="K5" s="10" t="n">
         <v>0.5</v>
@@ -2615,16 +2615,16 @@
         <v>-102</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5931</v>
+        <v>0.5908</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>0.505</v>
       </c>
       <c r="H6" s="13" t="n">
-        <v>0.0507</v>
+        <v>0.0503</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>0.1746029192790318</v>
+        <v>0.1699312380468005</v>
       </c>
       <c r="J6" s="14" t="n">
         <v>0.15</v>
@@ -2840,16 +2840,16 @@
         <v>-115</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>0.61</v>
+        <v>0.6077</v>
       </c>
       <c r="G11" s="8" t="n">
         <v>0.5349</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>0.0483</v>
+        <v>0.0477</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>0.1404490184348804</v>
+        <v>0.1360905800626417</v>
       </c>
       <c r="J11" s="10" t="n">
         <v>0.15</v>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>ARI @ GB</t>
+          <t>NO @ DAL</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -2972,19 +2972,19 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5810999999999999</v>
+        <v>0.5921</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>0.5122</v>
+        <v>0.5238</v>
       </c>
       <c r="H14" s="13" t="n">
-        <v>0.0467</v>
+        <v>0.0465</v>
       </c>
       <c r="I14" s="13" t="n">
-        <v>0.1345490399276508</v>
+        <v>0.1303396931016658</v>
       </c>
       <c r="J14" s="14" t="n">
         <v>0.15</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>NO @ DAL</t>
+          <t>ARI @ GB</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -3017,19 +3017,19 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>0.5921</v>
+        <v>0.5787</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5122</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>0.0465</v>
+        <v>0.046</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>0.1303396931016658</v>
+        <v>0.1298449688602823</v>
       </c>
       <c r="J15" s="10" t="n">
         <v>0.15</v>
@@ -3228,42 +3228,38 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>ATL @ MIA</t>
+          <t>SF @ LAR</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>MIA +4.5</t>
+          <t>Under 48.5</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>-105</v>
+        <v>-112</v>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5542</v>
+        <v>0.5743</v>
       </c>
       <c r="G20" s="13" t="n">
-        <v>0.5122</v>
+        <v>0.5283</v>
       </c>
       <c r="H20" s="13" t="n">
-        <v>0.0354</v>
+        <v>0.0376</v>
       </c>
       <c r="I20" s="13" t="n">
-        <v>0.08192506535915522</v>
+        <v>0.08704472540980535</v>
       </c>
       <c r="J20" s="14" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -3273,7 +3269,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>SF @ LV</t>
+          <t>ATL @ MIA</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -3283,23 +3279,23 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>SF +3.5</t>
+          <t>MIA +4.5</t>
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>-112</v>
+        <v>-105</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>0.5672</v>
+        <v>0.5542</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>0.5283</v>
+        <v>0.5122</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>0.0335</v>
+        <v>0.0354</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>0.0736241139165047</v>
+        <v>0.08192506535915522</v>
       </c>
       <c r="J21" s="10" t="n">
         <v>0.15</v>
@@ -3318,33 +3314,33 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>MIN @ DEN</t>
+          <t>SF @ LV</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>MIN ML</t>
+          <t>SF +3.5</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>226</v>
+        <v>-112</v>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.3457</v>
+        <v>0.5672</v>
       </c>
       <c r="G22" s="13" t="n">
-        <v>0.3067</v>
+        <v>0.5283</v>
       </c>
       <c r="H22" s="13" t="n">
         <v>0.0335</v>
       </c>
       <c r="I22" s="13" t="n">
-        <v>0.1259887878605835</v>
+        <v>0.0736241139165047</v>
       </c>
       <c r="J22" s="14" t="n">
         <v>0.15</v>
@@ -3380,16 +3376,16 @@
         <v>122</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>0.489</v>
+        <v>0.4894</v>
       </c>
       <c r="G23" s="8" t="n">
         <v>0.4505</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>0.0333</v>
+        <v>0.0335</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>0.08480009267866795</v>
+        <v>0.08560353442839908</v>
       </c>
       <c r="J23" s="10" t="n">
         <v>0.15</v>
@@ -3498,42 +3494,38 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>NO @ DAL</t>
+          <t>WSH @ PHI</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>DAL -1.5</t>
+          <t>Under 46.5</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5468</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>0.5122</v>
+        <v>0.5238</v>
       </c>
       <c r="H26" s="13" t="n">
-        <v>0.0306</v>
+        <v>0.0304</v>
       </c>
       <c r="I26" s="13" t="n">
-        <v>0.0674877167838408</v>
+        <v>0.06527646820956157</v>
       </c>
       <c r="J26" s="14" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K26" s="5" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -3625,7 +3617,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>DET @ IND</t>
+          <t>NO @ DAL</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -3635,23 +3627,23 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>DET +3.5</t>
+          <t>DAL -1.5</t>
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>0.5512</v>
+        <v>0.5446</v>
       </c>
       <c r="G29" s="8" t="n">
-        <v>0.5192</v>
+        <v>0.5122</v>
       </c>
       <c r="H29" s="8" t="n">
-        <v>0.0288</v>
+        <v>0.0291</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>0.06165161489025794</v>
+        <v>0.06331691481874901</v>
       </c>
       <c r="J29" s="10" t="n">
         <v>0.15</v>
@@ -3670,38 +3662,42 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>DET @ BUF</t>
+          <t>DET @ IND</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Under 52.5</t>
+          <t>DET +3.5</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.5555</v>
+        <v>0.5512</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5192</v>
       </c>
       <c r="H30" s="13" t="n">
-        <v>0.0286</v>
+        <v>0.0288</v>
       </c>
       <c r="I30" s="13" t="n">
-        <v>0.06054070194253447</v>
+        <v>0.06165161489025794</v>
       </c>
       <c r="J30" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K30" s="5" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -3711,42 +3707,38 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>NYG @ NYJ</t>
+          <t>DET @ BUF</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>NYJ ML</t>
+          <t>Under 52.5</t>
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>144</v>
+        <v>-110</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>0.4396</v>
+        <v>0.5555</v>
       </c>
       <c r="G31" s="8" t="n">
-        <v>0.4098</v>
+        <v>0.5238</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>0.0272</v>
+        <v>0.0286</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>0.07206044783732779</v>
+        <v>0.06054070194253447</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -3756,38 +3748,42 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>TB @ CIN</t>
+          <t>MIN @ DEN</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Under 51.5</t>
+          <t>MIN ML</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>-110</v>
+        <v>226</v>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.553</v>
+        <v>0.3379</v>
       </c>
       <c r="G32" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.3067</v>
       </c>
       <c r="H32" s="13" t="n">
-        <v>0.0268</v>
+        <v>0.0282</v>
       </c>
       <c r="I32" s="13" t="n">
-        <v>0.05579199560862913</v>
+        <v>0.1007856972199768</v>
       </c>
       <c r="J32" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K32" s="5" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -3797,38 +3793,42 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>WSH @ PHI</t>
+          <t>NYG @ NYJ</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Under 46.5</t>
+          <t>NYJ ML</t>
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>-110</v>
+        <v>144</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>0.553</v>
+        <v>0.4404</v>
       </c>
       <c r="G33" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.4098</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>0.0268</v>
+        <v>0.0277</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>0.05578948952918739</v>
+        <v>0.07382229463065115</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K33" s="4" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -3838,42 +3838,38 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>MIN @ DEN</t>
+          <t>TB @ CIN</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>MIN +6</t>
+          <t>Under 51.5</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.5454</v>
+        <v>0.553</v>
       </c>
       <c r="G34" s="13" t="n">
-        <v>0.5192</v>
+        <v>0.5238</v>
       </c>
       <c r="H34" s="13" t="n">
-        <v>0.0244</v>
+        <v>0.0268</v>
       </c>
       <c r="I34" s="13" t="n">
-        <v>0.04865540372328658</v>
+        <v>0.05579199560862913</v>
       </c>
       <c r="J34" s="14" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K34" s="5" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -3969,33 +3965,33 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>ATL @ MIA</t>
+          <t>ARI @ GB</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>MIA ML</t>
+          <t>GB +2.5</t>
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>157</v>
+        <v>-110</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>0.4116</v>
+        <v>0.5466</v>
       </c>
       <c r="G37" s="8" t="n">
-        <v>0.3891</v>
+        <v>0.5238</v>
       </c>
       <c r="H37" s="8" t="n">
-        <v>0.0213</v>
+        <v>0.0216</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>0.05726396649039622</v>
+        <v>0.04346624116942094</v>
       </c>
       <c r="J37" s="10" t="n">
         <v>0.15</v>
@@ -4014,33 +4010,33 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>ARI @ GB</t>
+          <t>ATL @ MIA</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>GB +2.5</t>
+          <t>MIA ML</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>-110</v>
+        <v>157</v>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.5462</v>
+        <v>0.4116</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.3891</v>
       </c>
       <c r="H38" s="13" t="n">
-        <v>0.0212</v>
+        <v>0.0213</v>
       </c>
       <c r="I38" s="13" t="n">
-        <v>0.04278942584763024</v>
+        <v>0.05726396649039622</v>
       </c>
       <c r="J38" s="14" t="n">
         <v>0.15</v>
@@ -4100,7 +4096,7 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>TB @ JAX</t>
+          <t>NYG @ NYJ</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -4110,23 +4106,23 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>JAX +3</t>
+          <t>NYJ +3</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.5455</v>
+        <v>0.5339</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5122</v>
       </c>
       <c r="H40" s="13" t="n">
-        <v>0.0206</v>
+        <v>0.0207</v>
       </c>
       <c r="I40" s="13" t="n">
-        <v>0.03850724179393927</v>
+        <v>0.03940790724231108</v>
       </c>
       <c r="J40" s="14" t="n">
         <v>0.15</v>
@@ -4145,42 +4141,38 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>NO @ DAL</t>
+          <t>ARI @ LAC</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>DAL ML</t>
+          <t>Under 46.5</t>
         </is>
       </c>
       <c r="E41" s="7" t="n">
-        <v>-129</v>
+        <v>-110</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>0.585</v>
+        <v>0.5455</v>
       </c>
       <c r="G41" s="8" t="n">
-        <v>0.5633</v>
+        <v>0.5238</v>
       </c>
       <c r="H41" s="8" t="n">
-        <v>0.0206</v>
+        <v>0.0207</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>0.03817284307070956</v>
+        <v>0.04148808649207303</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K41" s="4" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -4190,7 +4182,7 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>NYG @ NYJ</t>
+          <t>TB @ JAX</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -4200,23 +4192,23 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>NYJ +3</t>
+          <t>JAX +3</t>
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.5332</v>
+        <v>0.5455</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>0.5122</v>
+        <v>0.5238</v>
       </c>
       <c r="H42" s="13" t="n">
-        <v>0.02</v>
+        <v>0.0206</v>
       </c>
       <c r="I42" s="13" t="n">
-        <v>0.03802280987400375</v>
+        <v>0.03850724179393927</v>
       </c>
       <c r="J42" s="14" t="n">
         <v>0.15</v>
@@ -4325,38 +4317,42 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>ARI @ LAC</t>
+          <t>NO @ DAL</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Under 46.5</t>
+          <t>DAL ML</t>
         </is>
       </c>
       <c r="E45" s="7" t="n">
-        <v>-110</v>
+        <v>-129</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>0.543</v>
+        <v>0.5829</v>
       </c>
       <c r="G45" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5633</v>
       </c>
       <c r="H45" s="8" t="n">
-        <v>0.0185</v>
+        <v>0.0188</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>0.03670380090148218</v>
+        <v>0.03444346645959295</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K45" s="4" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -4534,38 +4530,42 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>ARI @ LAC</t>
+          <t>MIN @ DEN</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>ARI ML</t>
+          <t>MIN +6</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>425</v>
+        <v>-108</v>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.2091</v>
+        <v>0.5371</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>0.1905</v>
+        <v>0.5192</v>
       </c>
       <c r="H50" s="13" t="n">
-        <v>0.018</v>
+        <v>0.0173</v>
       </c>
       <c r="I50" s="13" t="n">
-        <v>0.09737253173108573</v>
+        <v>0.03316891728877225</v>
       </c>
       <c r="J50" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K50" s="5" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -4575,33 +4575,33 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>ARI @ LAC</t>
+          <t>CLE @ JAX</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>ARI +10.5</t>
+          <t>Over 40.5</t>
         </is>
       </c>
       <c r="E51" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>0.5414</v>
+        <v>0.5405</v>
       </c>
       <c r="G51" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H51" s="8" t="n">
-        <v>0.017</v>
+        <v>0.0162</v>
       </c>
       <c r="I51" s="8" t="n">
-        <v>0.03363116077967093</v>
+        <v>0.03192423886530243</v>
       </c>
       <c r="J51" s="10" t="n">
         <v>0.5</v>
@@ -4616,38 +4616,42 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>CLE @ JAX</t>
+          <t>WSH @ BAL</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Over 40.5</t>
+          <t>BAL ML</t>
         </is>
       </c>
       <c r="E52" s="12" t="n">
-        <v>-110</v>
+        <v>-142</v>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.5405</v>
+        <v>0.6022999999999999</v>
       </c>
       <c r="G52" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5868</v>
       </c>
       <c r="H52" s="13" t="n">
-        <v>0.0162</v>
+        <v>0.0151</v>
       </c>
       <c r="I52" s="13" t="n">
-        <v>0.03192423886530243</v>
+        <v>0.02623584809213975</v>
       </c>
       <c r="J52" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K52" s="5" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -4657,7 +4661,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>WSH @ BAL</t>
+          <t>ARI @ LAC</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -4667,32 +4671,28 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>BAL ML</t>
+          <t>ARI ML</t>
         </is>
       </c>
       <c r="E53" s="7" t="n">
-        <v>-142</v>
+        <v>425</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>0.6022999999999999</v>
+        <v>0.205</v>
       </c>
       <c r="G53" s="8" t="n">
-        <v>0.5868</v>
+        <v>0.1905</v>
       </c>
       <c r="H53" s="8" t="n">
-        <v>0.0151</v>
+        <v>0.0142</v>
       </c>
       <c r="I53" s="8" t="n">
-        <v>0.02623584809213975</v>
+        <v>0.07571199247334481</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K53" s="4" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>WSH @ BAL</t>
+          <t>ARI @ LAC</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -5007,32 +5007,28 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>BAL -2.5</t>
+          <t>ARI +10.5</t>
         </is>
       </c>
       <c r="E61" s="7" t="n">
-        <v>-118</v>
+        <v>-110</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>0.5528</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="G61" s="8" t="n">
-        <v>0.5413</v>
+        <v>0.5238</v>
       </c>
       <c r="H61" s="8" t="n">
-        <v>0.0114</v>
+        <v>0.0118</v>
       </c>
       <c r="I61" s="8" t="n">
-        <v>0.02129064582996637</v>
+        <v>0.02285790008902983</v>
       </c>
       <c r="J61" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K61" s="4" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K61" s="4" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
@@ -5042,7 +5038,7 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>SEA @ KC</t>
+          <t>WSH @ BAL</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -5052,23 +5048,23 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>KC -1.5</t>
+          <t>BAL -2.5</t>
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>-105</v>
+        <v>-118</v>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.5228</v>
+        <v>0.5528</v>
       </c>
       <c r="G62" s="13" t="n">
-        <v>0.5122</v>
+        <v>0.5413</v>
       </c>
       <c r="H62" s="13" t="n">
-        <v>0.0104</v>
+        <v>0.0114</v>
       </c>
       <c r="I62" s="13" t="n">
-        <v>0.02063327317925817</v>
+        <v>0.02129064582996637</v>
       </c>
       <c r="J62" s="14" t="n">
         <v>0.15</v>
@@ -5087,7 +5083,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>CHI @ TEN</t>
+          <t>SEA @ KC</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -5097,23 +5093,23 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>CHI +3</t>
+          <t>KC -1.5</t>
         </is>
       </c>
       <c r="E63" s="7" t="n">
-        <v>-115</v>
+        <v>-105</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>0.5444</v>
+        <v>0.5228</v>
       </c>
       <c r="G63" s="8" t="n">
-        <v>0.5349</v>
+        <v>0.5122</v>
       </c>
       <c r="H63" s="8" t="n">
-        <v>0.0094</v>
+        <v>0.0104</v>
       </c>
       <c r="I63" s="8" t="n">
-        <v>0.01647476246217722</v>
+        <v>0.02063327317925817</v>
       </c>
       <c r="J63" s="10" t="n">
         <v>0.15</v>
@@ -5132,38 +5128,42 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>NE @ SEA</t>
+          <t>CIN @ PHI</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>NE +3.5</t>
+          <t>CIN ML</t>
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>-115</v>
+        <v>129</v>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.5444</v>
+        <v>0.4461</v>
       </c>
       <c r="G64" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.4367</v>
       </c>
       <c r="H64" s="13" t="n">
         <v>0.0094</v>
       </c>
       <c r="I64" s="13" t="n">
-        <v>0.01772449429322892</v>
+        <v>0.02145323959040912</v>
       </c>
       <c r="J64" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K64" s="5" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -5173,38 +5173,42 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>CHI @ CAR</t>
+          <t>CHI @ TEN</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>CAR ML</t>
+          <t>CHI +3</t>
         </is>
       </c>
       <c r="E65" s="7" t="n">
-        <v>120</v>
+        <v>-115</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>0.4632</v>
+        <v>0.5444</v>
       </c>
       <c r="G65" s="8" t="n">
-        <v>0.4545</v>
+        <v>0.5349</v>
       </c>
       <c r="H65" s="8" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0094</v>
       </c>
       <c r="I65" s="8" t="n">
-        <v>0.01878422835459448</v>
+        <v>0.01647476246217722</v>
       </c>
       <c r="J65" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K65" s="4" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K65" s="4" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -5214,7 +5218,7 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>CHI @ CAR</t>
+          <t>NE @ SEA</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
@@ -5224,23 +5228,23 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>CAR +2.5</t>
+          <t>NE +3.5</t>
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>-102</v>
+        <v>-115</v>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.5132</v>
+        <v>0.5444</v>
       </c>
       <c r="G66" s="13" t="n">
-        <v>0.505</v>
+        <v>0.5349</v>
       </c>
       <c r="H66" s="13" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0094</v>
       </c>
       <c r="I66" s="13" t="n">
-        <v>0.01628003057036898</v>
+        <v>0.01772449429322892</v>
       </c>
       <c r="J66" s="14" t="n">
         <v>0.5</v>
@@ -5255,7 +5259,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>HOU @ CAR</t>
+          <t>CHI @ CAR</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -5272,25 +5276,21 @@
         <v>120</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>0.4621</v>
+        <v>0.4632</v>
       </c>
       <c r="G67" s="8" t="n">
         <v>0.4545</v>
       </c>
       <c r="H67" s="8" t="n">
-        <v>0.0075</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="I67" s="8" t="n">
-        <v>0.01651048203051431</v>
+        <v>0.01878422835459448</v>
       </c>
       <c r="J67" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K67" s="4" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K67" s="4" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>NE @ CLE</t>
+          <t>CHI @ CAR</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
@@ -5310,32 +5310,28 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>NE -2.5</t>
+          <t>CAR +2.5</t>
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>-115</v>
+        <v>-102</v>
       </c>
       <c r="F68" s="13" t="n">
-        <v>0.5405</v>
+        <v>0.5132</v>
       </c>
       <c r="G68" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.505</v>
       </c>
       <c r="H68" s="13" t="n">
-        <v>0.0056</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="I68" s="13" t="n">
-        <v>0.01054414228881145</v>
+        <v>0.01628003057036898</v>
       </c>
       <c r="J68" s="14" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K68" s="5" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K68" s="5" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
@@ -5350,28 +5346,28 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>CIN ML</t>
+          <t>CIN +3</t>
         </is>
       </c>
       <c r="E69" s="7" t="n">
-        <v>129</v>
+        <v>-112</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>0.4423</v>
+        <v>0.536</v>
       </c>
       <c r="G69" s="8" t="n">
-        <v>0.4367</v>
+        <v>0.5283</v>
       </c>
       <c r="H69" s="8" t="n">
-        <v>0.0056</v>
+        <v>0.0076</v>
       </c>
       <c r="I69" s="8" t="n">
-        <v>0.01278537284601111</v>
+        <v>0.01351313943760185</v>
       </c>
       <c r="J69" s="10" t="n">
         <v>0.15</v>
@@ -5390,38 +5386,42 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>SF @ LAR</t>
+          <t>HOU @ CAR</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>SF +3.5</t>
+          <t>CAR ML</t>
         </is>
       </c>
       <c r="E70" s="12" t="n">
-        <v>-115</v>
+        <v>120</v>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.5403</v>
+        <v>0.4621</v>
       </c>
       <c r="G70" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.4545</v>
       </c>
       <c r="H70" s="13" t="n">
-        <v>0.0054</v>
+        <v>0.0075</v>
       </c>
       <c r="I70" s="13" t="n">
-        <v>0.01008502847574472</v>
+        <v>0.01651048203051431</v>
       </c>
       <c r="J70" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K70" s="5" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K70" s="5" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -5431,38 +5431,42 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>DEN @ KC</t>
+          <t>NE @ CLE</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Under 42.5</t>
+          <t>NE -2.5</t>
         </is>
       </c>
       <c r="E71" s="7" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>0.5279</v>
+        <v>0.5405</v>
       </c>
       <c r="G71" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5349</v>
       </c>
       <c r="H71" s="8" t="n">
-        <v>0.0041</v>
+        <v>0.0056</v>
       </c>
       <c r="I71" s="8" t="n">
-        <v>0.007840044051825923</v>
+        <v>0.01054414228881145</v>
       </c>
       <c r="J71" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K71" s="4" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K71" s="4" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
@@ -5472,7 +5476,7 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>BAL @ IND</t>
+          <t>SF @ LAR</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
@@ -5482,23 +5486,23 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>IND +3.5</t>
+          <t>SF +3.5</t>
         </is>
       </c>
       <c r="E72" s="12" t="n">
-        <v>-112</v>
+        <v>-115</v>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.5321</v>
+        <v>0.5403</v>
       </c>
       <c r="G72" s="13" t="n">
-        <v>0.5283</v>
+        <v>0.5349</v>
       </c>
       <c r="H72" s="13" t="n">
-        <v>0.0038</v>
+        <v>0.0054</v>
       </c>
       <c r="I72" s="13" t="n">
-        <v>0.007227421686627156</v>
+        <v>0.01008502847574472</v>
       </c>
       <c r="J72" s="14" t="n">
         <v>0.5</v>
@@ -5513,42 +5517,38 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>CIN @ PHI</t>
+          <t>DEN @ KC</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>CIN +3</t>
+          <t>Under 42.5</t>
         </is>
       </c>
       <c r="E73" s="7" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>0.532</v>
+        <v>0.5279</v>
       </c>
       <c r="G73" s="8" t="n">
-        <v>0.5283</v>
+        <v>0.5238</v>
       </c>
       <c r="H73" s="8" t="n">
-        <v>0.0037</v>
+        <v>0.0041</v>
       </c>
       <c r="I73" s="8" t="n">
-        <v>0.006448383712330863</v>
+        <v>0.007840044051825923</v>
       </c>
       <c r="J73" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K73" s="4" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K73" s="4" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
@@ -5563,28 +5563,28 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>IND ML</t>
+          <t>IND +3.5</t>
         </is>
       </c>
       <c r="E74" s="12" t="n">
-        <v>145</v>
+        <v>-112</v>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.4114</v>
+        <v>0.5321</v>
       </c>
       <c r="G74" s="13" t="n">
-        <v>0.4082</v>
+        <v>0.5283</v>
       </c>
       <c r="H74" s="13" t="n">
-        <v>0.0033</v>
+        <v>0.0038</v>
       </c>
       <c r="I74" s="13" t="n">
-        <v>0.007929117400102492</v>
+        <v>0.007227421686627156</v>
       </c>
       <c r="J74" s="14" t="n">
         <v>0.5</v>
@@ -5599,33 +5599,33 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>NE @ SEA</t>
+          <t>BAL @ IND</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Under 44.5</t>
+          <t>IND ML</t>
         </is>
       </c>
       <c r="E75" s="7" t="n">
-        <v>-110</v>
+        <v>145</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>0.5254</v>
+        <v>0.4114</v>
       </c>
       <c r="G75" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.4082</v>
       </c>
       <c r="H75" s="8" t="n">
-        <v>0.0016</v>
+        <v>0.0033</v>
       </c>
       <c r="I75" s="8" t="n">
-        <v>0.003017043983478351</v>
+        <v>0.007929117400102492</v>
       </c>
       <c r="J75" s="10" t="n">
         <v>0.5</v>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>BUF @ HOU</t>
+          <t>NE @ SEA</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Over 44.5</t>
+          <t>Under 44.5</t>
         </is>
       </c>
       <c r="E76" s="12" t="n">
@@ -5666,7 +5666,7 @@
         <v>0.0016</v>
       </c>
       <c r="I76" s="13" t="n">
-        <v>0.003023751045110934</v>
+        <v>0.003017043983478351</v>
       </c>
       <c r="J76" s="14" t="n">
         <v>0.5</v>
@@ -5681,42 +5681,38 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>PIT @ BUF</t>
+          <t>BUF @ HOU</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>BUF ML</t>
+          <t>Over 44.5</t>
         </is>
       </c>
       <c r="E77" s="7" t="n">
-        <v>-152</v>
+        <v>-110</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>0.6042</v>
+        <v>0.5254</v>
       </c>
       <c r="G77" s="8" t="n">
-        <v>0.6032</v>
+        <v>0.5238</v>
       </c>
       <c r="H77" s="8" t="n">
-        <v>0.0011</v>
+        <v>0.0016</v>
       </c>
       <c r="I77" s="8" t="n">
-        <v>0.001762885624806587</v>
+        <v>0.003023751045110934</v>
       </c>
       <c r="J77" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K77" s="4" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K77" s="4" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
@@ -5731,28 +5727,28 @@
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>BUF -3</t>
+          <t>BUF ML</t>
         </is>
       </c>
       <c r="E78" s="12" t="n">
-        <v>-108</v>
+        <v>-152</v>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.5198</v>
+        <v>0.6042</v>
       </c>
       <c r="G78" s="13" t="n">
-        <v>0.5192</v>
+        <v>0.6032</v>
       </c>
       <c r="H78" s="13" t="n">
-        <v>0.0005</v>
+        <v>0.0011</v>
       </c>
       <c r="I78" s="13" t="n">
-        <v>0.000957171010924851</v>
+        <v>0.001762885624806587</v>
       </c>
       <c r="J78" s="14" t="n">
         <v>0.15</v>
@@ -5771,33 +5767,33 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>SEA @ KC</t>
+          <t>PIT @ BUF</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>KC ML</t>
+          <t>BUF -3</t>
         </is>
       </c>
       <c r="E79" s="7" t="n">
-        <v>-127</v>
+        <v>-108</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>0.5597</v>
+        <v>0.5198</v>
       </c>
       <c r="G79" s="8" t="n">
-        <v>0.5595</v>
+        <v>0.5192</v>
       </c>
       <c r="H79" s="8" t="n">
-        <v>0.0002</v>
+        <v>0.0005</v>
       </c>
       <c r="I79" s="8" t="n">
-        <v>0.0003726041985263606</v>
+        <v>0.000957171010924851</v>
       </c>
       <c r="J79" s="10" t="n">
         <v>0.15</v>
@@ -5816,38 +5812,42 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>NYJ @ TEN</t>
+          <t>SEA @ KC</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>TEN -3</t>
+          <t>KC ML</t>
         </is>
       </c>
       <c r="E80" s="12" t="n">
-        <v>100</v>
+        <v>-127</v>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.4994</v>
+        <v>0.5597</v>
       </c>
       <c r="G80" s="13" t="n">
-        <v>0.5</v>
+        <v>0.5595</v>
       </c>
       <c r="H80" s="13" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0002</v>
       </c>
       <c r="I80" s="13" t="n">
-        <v>-0.00119086639414151</v>
+        <v>0.0003726041985263606</v>
       </c>
       <c r="J80" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K80" s="5" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K80" s="5" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
@@ -5857,33 +5857,33 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>TB @ CIN</t>
+          <t>NYJ @ TEN</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>TB ML</t>
+          <t>TEN -3</t>
         </is>
       </c>
       <c r="E81" s="7" t="n">
-        <v>164</v>
+        <v>100</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>0.3756</v>
+        <v>0.4982</v>
       </c>
       <c r="G81" s="8" t="n">
-        <v>0.3788</v>
+        <v>0.5</v>
       </c>
       <c r="H81" s="8" t="n">
-        <v>-0.0032</v>
+        <v>-0.0018</v>
       </c>
       <c r="I81" s="8" t="n">
-        <v>-0.008255833011393876</v>
+        <v>-0.003345842194787341</v>
       </c>
       <c r="J81" s="10" t="n">
         <v>0.5</v>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>NE @ CLE</t>
+          <t>TB @ CIN</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
@@ -5908,32 +5908,28 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>NE ML</t>
+          <t>TB ML</t>
         </is>
       </c>
       <c r="E82" s="12" t="n">
-        <v>-150</v>
+        <v>164</v>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.5967</v>
+        <v>0.3756</v>
       </c>
       <c r="G82" s="13" t="n">
-        <v>0.6</v>
+        <v>0.3788</v>
       </c>
       <c r="H82" s="13" t="n">
-        <v>-0.0033</v>
+        <v>-0.0032</v>
       </c>
       <c r="I82" s="13" t="n">
-        <v>-0.005438888888026017</v>
+        <v>-0.008255833011393876</v>
       </c>
       <c r="J82" s="14" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K82" s="5" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K82" s="5" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
@@ -5943,38 +5939,42 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>BAL @ IND</t>
+          <t>NE @ CLE</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Under 48.5</t>
+          <t>NE ML</t>
         </is>
       </c>
       <c r="E83" s="7" t="n">
-        <v>-110</v>
+        <v>-150</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>0.5178</v>
+        <v>0.5967</v>
       </c>
       <c r="G83" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.6</v>
       </c>
       <c r="H83" s="8" t="n">
-        <v>-0.006</v>
+        <v>-0.0033</v>
       </c>
       <c r="I83" s="8" t="n">
-        <v>-0.01149414935741505</v>
+        <v>-0.005438888888026017</v>
       </c>
       <c r="J83" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K83" s="4" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K83" s="4" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>NYJ @ TEN</t>
+          <t>WSH @ PHI</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
@@ -5994,23 +5994,23 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>TEN ML</t>
+          <t>WSH ML</t>
         </is>
       </c>
       <c r="E84" s="12" t="n">
-        <v>-148</v>
+        <v>170</v>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.5891</v>
+        <v>0.3666</v>
       </c>
       <c r="G84" s="13" t="n">
-        <v>0.5968</v>
+        <v>0.3704</v>
       </c>
       <c r="H84" s="13" t="n">
-        <v>-0.0076</v>
+        <v>-0.0038</v>
       </c>
       <c r="I84" s="13" t="n">
-        <v>-0.01268577114940572</v>
+        <v>-0.01008181798906627</v>
       </c>
       <c r="J84" s="14" t="n">
         <v>0.5</v>
@@ -6025,7 +6025,7 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>HOU @ CAR</t>
+          <t>WSH @ PHI</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -6035,32 +6035,28 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>CAR +2.5</t>
+          <t>WSH +4.5</t>
         </is>
       </c>
       <c r="E85" s="7" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>0.5202</v>
+        <v>0.5187</v>
       </c>
       <c r="G85" s="8" t="n">
-        <v>0.5283</v>
+        <v>0.5238</v>
       </c>
       <c r="H85" s="8" t="n">
-        <v>-0.008</v>
+        <v>-0.0051</v>
       </c>
       <c r="I85" s="8" t="n">
-        <v>-0.01528874769996574</v>
+        <v>-0.009708937707183729</v>
       </c>
       <c r="J85" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K85" s="4" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K85" s="4" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
@@ -6070,33 +6066,33 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>WSH @ PHI</t>
+          <t>BAL @ IND</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>WSH ML</t>
+          <t>Under 48.5</t>
         </is>
       </c>
       <c r="E86" s="12" t="n">
-        <v>170</v>
+        <v>-110</v>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.3621</v>
+        <v>0.5178</v>
       </c>
       <c r="G86" s="13" t="n">
-        <v>0.3704</v>
+        <v>0.5238</v>
       </c>
       <c r="H86" s="13" t="n">
-        <v>-0.008200000000000001</v>
+        <v>-0.006</v>
       </c>
       <c r="I86" s="13" t="n">
-        <v>-0.0221654724895739</v>
+        <v>-0.01149414935741505</v>
       </c>
       <c r="J86" s="14" t="n">
         <v>0.5</v>
@@ -6111,7 +6107,7 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>WSH @ PHI</t>
+          <t>HOU @ CAR</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -6121,28 +6117,32 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>WSH +4.5</t>
+          <t>CAR +2.5</t>
         </is>
       </c>
       <c r="E87" s="7" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>0.514</v>
+        <v>0.5202</v>
       </c>
       <c r="G87" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5283</v>
       </c>
       <c r="H87" s="8" t="n">
-        <v>-0.0097</v>
+        <v>-0.008</v>
       </c>
       <c r="I87" s="8" t="n">
-        <v>-0.01867446287821206</v>
+        <v>-0.01528874769996574</v>
       </c>
       <c r="J87" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K87" s="4" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K87" s="4" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
@@ -6152,33 +6152,33 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>MIA @ LV</t>
+          <t>NYJ @ TEN</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>MIA +3.5</t>
+          <t>TEN ML</t>
         </is>
       </c>
       <c r="E88" s="12" t="n">
-        <v>-110</v>
+        <v>-148</v>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.5139</v>
+        <v>0.5881</v>
       </c>
       <c r="G88" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5968</v>
       </c>
       <c r="H88" s="13" t="n">
-        <v>-0.0098</v>
+        <v>-0.0086</v>
       </c>
       <c r="I88" s="13" t="n">
-        <v>-0.0188509848594357</v>
+        <v>-0.01445678971273462</v>
       </c>
       <c r="J88" s="14" t="n">
         <v>0.5</v>
@@ -6193,7 +6193,7 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>GB @ MIN</t>
+          <t>MIA @ LV</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -6203,23 +6203,23 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>MIN -1.5</t>
+          <t>MIA +3.5</t>
         </is>
       </c>
       <c r="E89" s="7" t="n">
-        <v>-102</v>
+        <v>-110</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>0.4941</v>
+        <v>0.5139</v>
       </c>
       <c r="G89" s="8" t="n">
-        <v>0.505</v>
+        <v>0.5238</v>
       </c>
       <c r="H89" s="8" t="n">
-        <v>-0.0107</v>
+        <v>-0.0098</v>
       </c>
       <c r="I89" s="8" t="n">
-        <v>-0.02145629576645519</v>
+        <v>-0.0188509848594357</v>
       </c>
       <c r="J89" s="10" t="n">
         <v>0.5</v>
@@ -6316,33 +6316,33 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>SF @ LAR</t>
+          <t>DAL @ NYG</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>Under 48.5</t>
+          <t>NYG ML</t>
         </is>
       </c>
       <c r="E92" s="12" t="n">
-        <v>-112</v>
+        <v>124</v>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.5142</v>
+        <v>0.4324</v>
       </c>
       <c r="G92" s="13" t="n">
-        <v>0.5283</v>
+        <v>0.4464</v>
       </c>
       <c r="H92" s="13" t="n">
         <v>-0.0138</v>
       </c>
       <c r="I92" s="13" t="n">
-        <v>-0.02664269073720898</v>
+        <v>-0.0312262377799627</v>
       </c>
       <c r="J92" s="14" t="n">
         <v>0.5</v>
@@ -6357,33 +6357,33 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>GB @ MIN</t>
+          <t>DET @ BUF</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>MIN ML</t>
+          <t>BUF -3</t>
         </is>
       </c>
       <c r="E93" s="7" t="n">
-        <v>-118</v>
+        <v>-110</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>0.5269</v>
+        <v>0.5074</v>
       </c>
       <c r="G93" s="8" t="n">
-        <v>0.5413</v>
+        <v>0.5238</v>
       </c>
       <c r="H93" s="8" t="n">
-        <v>-0.0141</v>
+        <v>-0.016</v>
       </c>
       <c r="I93" s="8" t="n">
-        <v>-0.02634428265721017</v>
+        <v>-0.02914780992687066</v>
       </c>
       <c r="J93" s="10" t="n">
         <v>0.5</v>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>DET @ BUF</t>
+          <t>ATL @ PIT</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
@@ -6408,23 +6408,23 @@
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>BUF -3</t>
+          <t>ATL +3</t>
         </is>
       </c>
       <c r="E94" s="12" t="n">
-        <v>-110</v>
+        <v>100</v>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.5074</v>
+        <v>0.4825</v>
       </c>
       <c r="G94" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5</v>
       </c>
       <c r="H94" s="13" t="n">
-        <v>-0.016</v>
+        <v>-0.0169</v>
       </c>
       <c r="I94" s="13" t="n">
-        <v>-0.02914780992687066</v>
+        <v>-0.03243499506631287</v>
       </c>
       <c r="J94" s="14" t="n">
         <v>0.5</v>
@@ -6439,33 +6439,33 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>ATL @ PIT</t>
+          <t>BUF @ HOU</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>ATL +3</t>
+          <t>BUF ML</t>
         </is>
       </c>
       <c r="E95" s="7" t="n">
-        <v>100</v>
+        <v>-118</v>
       </c>
       <c r="F95" s="8" t="n">
-        <v>0.4825</v>
+        <v>0.5223</v>
       </c>
       <c r="G95" s="8" t="n">
-        <v>0.5</v>
+        <v>0.5413</v>
       </c>
       <c r="H95" s="8" t="n">
-        <v>-0.0169</v>
+        <v>-0.0182</v>
       </c>
       <c r="I95" s="8" t="n">
-        <v>-0.03243499506631287</v>
+        <v>-0.03469121578784312</v>
       </c>
       <c r="J95" s="10" t="n">
         <v>0.5</v>
@@ -6480,33 +6480,33 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>DAL @ NYG</t>
+          <t>DEN @ KC</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>NYG ML</t>
+          <t>DEN +3</t>
         </is>
       </c>
       <c r="E96" s="12" t="n">
-        <v>124</v>
+        <v>-115</v>
       </c>
       <c r="F96" s="13" t="n">
-        <v>0.428</v>
+        <v>0.5152</v>
       </c>
       <c r="G96" s="13" t="n">
-        <v>0.4464</v>
+        <v>0.5349</v>
       </c>
       <c r="H96" s="13" t="n">
-        <v>-0.0177</v>
+        <v>-0.0189</v>
       </c>
       <c r="I96" s="13" t="n">
-        <v>-0.04083371234377298</v>
+        <v>-0.03415300808174382</v>
       </c>
       <c r="J96" s="14" t="n">
         <v>0.5</v>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>DAL @ NYG</t>
+          <t>GB @ MIN</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -6531,23 +6531,23 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>DAL -2.5</t>
+          <t>MIN -1.5</t>
         </is>
       </c>
       <c r="E97" s="7" t="n">
-        <v>-115</v>
+        <v>-102</v>
       </c>
       <c r="F97" s="8" t="n">
-        <v>0.5164</v>
+        <v>0.4849</v>
       </c>
       <c r="G97" s="8" t="n">
-        <v>0.5349</v>
+        <v>0.505</v>
       </c>
       <c r="H97" s="8" t="n">
-        <v>-0.0178</v>
+        <v>-0.0192</v>
       </c>
       <c r="I97" s="8" t="n">
-        <v>-0.03448834596329842</v>
+        <v>-0.0397090995296181</v>
       </c>
       <c r="J97" s="10" t="n">
         <v>0.5</v>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>BUF @ HOU</t>
+          <t>DEN @ KC</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
@@ -6572,23 +6572,23 @@
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>BUF ML</t>
+          <t>DEN ML</t>
         </is>
       </c>
       <c r="E98" s="12" t="n">
-        <v>-118</v>
+        <v>124</v>
       </c>
       <c r="F98" s="13" t="n">
-        <v>0.5223</v>
+        <v>0.4263</v>
       </c>
       <c r="G98" s="13" t="n">
-        <v>0.5413</v>
+        <v>0.4464</v>
       </c>
       <c r="H98" s="13" t="n">
-        <v>-0.0182</v>
+        <v>-0.0193</v>
       </c>
       <c r="I98" s="13" t="n">
-        <v>-0.03469121578784312</v>
+        <v>-0.0447248472042151</v>
       </c>
       <c r="J98" s="14" t="n">
         <v>0.5</v>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>DEN @ KC</t>
+          <t>BUF @ HOU</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -6613,23 +6613,23 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>DEN +3</t>
+          <t>BUF -1.5</t>
         </is>
       </c>
       <c r="E99" s="7" t="n">
-        <v>-115</v>
+        <v>-105</v>
       </c>
       <c r="F99" s="8" t="n">
-        <v>0.5152</v>
+        <v>0.4919</v>
       </c>
       <c r="G99" s="8" t="n">
-        <v>0.5349</v>
+        <v>0.5122</v>
       </c>
       <c r="H99" s="8" t="n">
-        <v>-0.0189</v>
+        <v>-0.0194</v>
       </c>
       <c r="I99" s="8" t="n">
-        <v>-0.03415300808174382</v>
+        <v>-0.03965776108553809</v>
       </c>
       <c r="J99" s="10" t="n">
         <v>0.5</v>
@@ -6644,7 +6644,7 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>DEN @ KC</t>
+          <t>DET @ BUF</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
@@ -6654,23 +6654,23 @@
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>DEN ML</t>
+          <t>DET ML</t>
         </is>
       </c>
       <c r="E100" s="12" t="n">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="F100" s="13" t="n">
-        <v>0.4263</v>
+        <v>0.403</v>
       </c>
       <c r="G100" s="13" t="n">
-        <v>0.4464</v>
+        <v>0.4237</v>
       </c>
       <c r="H100" s="13" t="n">
-        <v>-0.0193</v>
+        <v>-0.0198</v>
       </c>
       <c r="I100" s="13" t="n">
-        <v>-0.0447248472042151</v>
+        <v>-0.04837902178463449</v>
       </c>
       <c r="J100" s="14" t="n">
         <v>0.5</v>
@@ -6685,33 +6685,33 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>BUF @ HOU</t>
+          <t>DET @ BUF</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>BUF -1.5</t>
+          <t>BUF ML</t>
         </is>
       </c>
       <c r="E101" s="7" t="n">
-        <v>-105</v>
+        <v>-162</v>
       </c>
       <c r="F101" s="8" t="n">
-        <v>0.4919</v>
+        <v>0.597</v>
       </c>
       <c r="G101" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.6183</v>
       </c>
       <c r="H101" s="8" t="n">
-        <v>-0.0194</v>
+        <v>-0.0204</v>
       </c>
       <c r="I101" s="8" t="n">
-        <v>-0.03965776108553809</v>
+        <v>-0.03425999460203544</v>
       </c>
       <c r="J101" s="10" t="n">
         <v>0.5</v>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>DET @ BUF</t>
+          <t>GB @ MIN</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
@@ -6736,23 +6736,23 @@
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>DET ML</t>
+          <t>GB ML</t>
         </is>
       </c>
       <c r="E102" s="12" t="n">
-        <v>136</v>
+        <v>-102</v>
       </c>
       <c r="F102" s="13" t="n">
-        <v>0.403</v>
+        <v>0.4824</v>
       </c>
       <c r="G102" s="13" t="n">
-        <v>0.4237</v>
+        <v>0.505</v>
       </c>
       <c r="H102" s="13" t="n">
-        <v>-0.0198</v>
+        <v>-0.0214</v>
       </c>
       <c r="I102" s="13" t="n">
-        <v>-0.04837902178463449</v>
+        <v>-0.04423890812367315</v>
       </c>
       <c r="J102" s="14" t="n">
         <v>0.5</v>
@@ -6767,33 +6767,33 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>DET @ BUF</t>
+          <t>DAL @ NYG</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>BUF ML</t>
+          <t>DAL -2.5</t>
         </is>
       </c>
       <c r="E103" s="7" t="n">
-        <v>-162</v>
+        <v>-115</v>
       </c>
       <c r="F103" s="8" t="n">
-        <v>0.597</v>
+        <v>0.5121</v>
       </c>
       <c r="G103" s="8" t="n">
-        <v>0.6183</v>
+        <v>0.5349</v>
       </c>
       <c r="H103" s="8" t="n">
-        <v>-0.0204</v>
+        <v>-0.0216</v>
       </c>
       <c r="I103" s="8" t="n">
-        <v>-0.03425999460203544</v>
+        <v>-0.04257813899062829</v>
       </c>
       <c r="J103" s="10" t="n">
         <v>0.5</v>
@@ -6808,33 +6808,33 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>DAL @ NYG</t>
+          <t>GB @ MIN</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>MIN ML</t>
         </is>
       </c>
       <c r="E104" s="12" t="n">
-        <v>-110</v>
+        <v>-118</v>
       </c>
       <c r="F104" s="13" t="n">
-        <v>0.5</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="G104" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5413</v>
       </c>
       <c r="H104" s="13" t="n">
-        <v>-0.0224</v>
+        <v>-0.0223</v>
       </c>
       <c r="I104" s="13" t="n">
-        <v>-0.04545406739379704</v>
+        <v>-0.04338098642890131</v>
       </c>
       <c r="J104" s="14" t="n">
         <v>0.5</v>
@@ -6859,7 +6859,7 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Under 48.5</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="E105" s="7" t="n">
@@ -6875,7 +6875,7 @@
         <v>-0.0224</v>
       </c>
       <c r="I105" s="8" t="n">
-        <v>-0.04545502351529379</v>
+        <v>-0.04545406739379704</v>
       </c>
       <c r="J105" s="10" t="n">
         <v>0.5</v>
@@ -6895,28 +6895,28 @@
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>DAL ML</t>
+          <t>Under 48.5</t>
         </is>
       </c>
       <c r="E106" s="12" t="n">
-        <v>-148</v>
+        <v>-110</v>
       </c>
       <c r="F106" s="13" t="n">
-        <v>0.572</v>
+        <v>0.5</v>
       </c>
       <c r="G106" s="13" t="n">
-        <v>0.5968</v>
+        <v>0.5238</v>
       </c>
       <c r="H106" s="13" t="n">
-        <v>-0.0233</v>
+        <v>-0.0224</v>
       </c>
       <c r="I106" s="13" t="n">
-        <v>-0.04120749617257097</v>
+        <v>-0.04545502351529379</v>
       </c>
       <c r="J106" s="14" t="n">
         <v>0.5</v>
@@ -6931,7 +6931,7 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>BUF @ HOU</t>
+          <t>DAL @ NYG</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
@@ -6941,23 +6941,23 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>HOU +1.5</t>
+          <t>NYG +2.5</t>
         </is>
       </c>
       <c r="E107" s="7" t="n">
-        <v>-115</v>
+        <v>-105</v>
       </c>
       <c r="F107" s="8" t="n">
-        <v>0.5081</v>
+        <v>0.4879</v>
       </c>
       <c r="G107" s="8" t="n">
-        <v>0.5349</v>
+        <v>0.5122</v>
       </c>
       <c r="H107" s="8" t="n">
-        <v>-0.0248</v>
+        <v>-0.0228</v>
       </c>
       <c r="I107" s="8" t="n">
-        <v>-0.0500414016328305</v>
+        <v>-0.04745162229439381</v>
       </c>
       <c r="J107" s="10" t="n">
         <v>0.5</v>
@@ -6972,33 +6972,33 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>BUF @ HOU</t>
+          <t>GB @ MIN</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>HOU ML</t>
+          <t>GB +1.5</t>
         </is>
       </c>
       <c r="E108" s="12" t="n">
-        <v>-102</v>
+        <v>-118</v>
       </c>
       <c r="F108" s="13" t="n">
-        <v>0.4777</v>
+        <v>0.5151</v>
       </c>
       <c r="G108" s="13" t="n">
-        <v>0.505</v>
+        <v>0.5413</v>
       </c>
       <c r="H108" s="13" t="n">
-        <v>-0.0252</v>
+        <v>-0.0244</v>
       </c>
       <c r="I108" s="13" t="n">
-        <v>-0.05355475771997914</v>
+        <v>-0.04837340421460867</v>
       </c>
       <c r="J108" s="14" t="n">
         <v>0.5</v>
@@ -7013,7 +7013,7 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>DEN @ KC</t>
+          <t>BUF @ HOU</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
@@ -7023,23 +7023,23 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>KC -3</t>
+          <t>HOU +1.5</t>
         </is>
       </c>
       <c r="E109" s="7" t="n">
-        <v>-105</v>
+        <v>-115</v>
       </c>
       <c r="F109" s="8" t="n">
-        <v>0.4848</v>
+        <v>0.5081</v>
       </c>
       <c r="G109" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.5349</v>
       </c>
       <c r="H109" s="8" t="n">
-        <v>-0.0253</v>
+        <v>-0.0248</v>
       </c>
       <c r="I109" s="8" t="n">
-        <v>-0.04962944240579342</v>
+        <v>-0.0500414016328305</v>
       </c>
       <c r="J109" s="10" t="n">
         <v>0.5</v>
@@ -7054,33 +7054,33 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>ATL @ PIT</t>
+          <t>BUF @ HOU</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>PIT -3</t>
+          <t>HOU ML</t>
         </is>
       </c>
       <c r="E110" s="12" t="n">
-        <v>-120</v>
+        <v>-102</v>
       </c>
       <c r="F110" s="13" t="n">
-        <v>0.5175</v>
+        <v>0.4777</v>
       </c>
       <c r="G110" s="13" t="n">
-        <v>0.5455</v>
+        <v>0.505</v>
       </c>
       <c r="H110" s="13" t="n">
-        <v>-0.0258</v>
+        <v>-0.0252</v>
       </c>
       <c r="I110" s="13" t="n">
-        <v>-0.0475877345714818</v>
+        <v>-0.05355475771997914</v>
       </c>
       <c r="J110" s="14" t="n">
         <v>0.5</v>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>DAL @ NYG</t>
+          <t>DEN @ KC</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
@@ -7105,23 +7105,23 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>NYG +2.5</t>
+          <t>KC -3</t>
         </is>
       </c>
       <c r="E111" s="7" t="n">
         <v>-105</v>
       </c>
       <c r="F111" s="8" t="n">
-        <v>0.4836</v>
+        <v>0.4848</v>
       </c>
       <c r="G111" s="8" t="n">
         <v>0.5122</v>
       </c>
       <c r="H111" s="8" t="n">
-        <v>-0.0263</v>
+        <v>-0.0253</v>
       </c>
       <c r="I111" s="8" t="n">
-        <v>-0.0558997671723252</v>
+        <v>-0.04962944240579342</v>
       </c>
       <c r="J111" s="10" t="n">
         <v>0.5</v>
@@ -7136,7 +7136,7 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>DET @ BUF</t>
+          <t>ATL @ PIT</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
@@ -7146,23 +7146,23 @@
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>DET +3</t>
+          <t>PIT -3</t>
         </is>
       </c>
       <c r="E112" s="12" t="n">
-        <v>-110</v>
+        <v>-120</v>
       </c>
       <c r="F112" s="13" t="n">
-        <v>0.4926</v>
+        <v>0.5175</v>
       </c>
       <c r="G112" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5455</v>
       </c>
       <c r="H112" s="13" t="n">
-        <v>-0.0282</v>
+        <v>-0.0258</v>
       </c>
       <c r="I112" s="13" t="n">
-        <v>-0.05520045726031053</v>
+        <v>-0.0475877345714818</v>
       </c>
       <c r="J112" s="14" t="n">
         <v>0.5</v>
@@ -7177,7 +7177,7 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>ATL @ PIT</t>
+          <t>DAL @ NYG</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
@@ -7187,23 +7187,23 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>PIT ML</t>
+          <t>DAL ML</t>
         </is>
       </c>
       <c r="E113" s="7" t="n">
-        <v>-175</v>
+        <v>-148</v>
       </c>
       <c r="F113" s="8" t="n">
-        <v>0.6048</v>
+        <v>0.5676</v>
       </c>
       <c r="G113" s="8" t="n">
-        <v>0.6364</v>
+        <v>0.5968</v>
       </c>
       <c r="H113" s="8" t="n">
-        <v>-0.0285</v>
+        <v>-0.0267</v>
       </c>
       <c r="I113" s="8" t="n">
-        <v>-0.04915349941279379</v>
+        <v>-0.04839268785189488</v>
       </c>
       <c r="J113" s="10" t="n">
         <v>0.5</v>
@@ -7218,33 +7218,33 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>GB @ MIN</t>
+          <t>DET @ BUF</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>GB ML</t>
+          <t>DET +3</t>
         </is>
       </c>
       <c r="E114" s="12" t="n">
-        <v>-102</v>
+        <v>-110</v>
       </c>
       <c r="F114" s="13" t="n">
-        <v>0.4731</v>
+        <v>0.4926</v>
       </c>
       <c r="G114" s="13" t="n">
-        <v>0.505</v>
+        <v>0.5238</v>
       </c>
       <c r="H114" s="13" t="n">
-        <v>-0.0287</v>
+        <v>-0.0282</v>
       </c>
       <c r="I114" s="13" t="n">
-        <v>-0.06250332799013569</v>
+        <v>-0.05520045726031053</v>
       </c>
       <c r="J114" s="14" t="n">
         <v>0.5</v>
@@ -7259,33 +7259,33 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>SF @ LAR</t>
+          <t>ATL @ PIT</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>PIT ML</t>
         </is>
       </c>
       <c r="E115" s="7" t="n">
-        <v>-108</v>
+        <v>-175</v>
       </c>
       <c r="F115" s="8" t="n">
-        <v>0.4858</v>
+        <v>0.6048</v>
       </c>
       <c r="G115" s="8" t="n">
-        <v>0.5192</v>
+        <v>0.6364</v>
       </c>
       <c r="H115" s="8" t="n">
-        <v>-0.0299</v>
+        <v>-0.0285</v>
       </c>
       <c r="I115" s="8" t="n">
-        <v>-0.06443622801301446</v>
+        <v>-0.04915349941279379</v>
       </c>
       <c r="J115" s="10" t="n">
         <v>0.5</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>WSH @ PHI</t>
+          <t>NYJ @ TEN</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
@@ -7351,23 +7351,23 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>PHI ML</t>
+          <t>NYJ ML</t>
         </is>
       </c>
       <c r="E117" s="7" t="n">
-        <v>-205</v>
+        <v>124</v>
       </c>
       <c r="F117" s="8" t="n">
-        <v>0.6379</v>
+        <v>0.4119</v>
       </c>
       <c r="G117" s="8" t="n">
-        <v>0.6721</v>
+        <v>0.4464</v>
       </c>
       <c r="H117" s="8" t="n">
-        <v>-0.0304</v>
+        <v>-0.0306</v>
       </c>
       <c r="I117" s="8" t="n">
-        <v>-0.05048414277708085</v>
+        <v>-0.07660481855710299</v>
       </c>
       <c r="J117" s="10" t="n">
         <v>0.5</v>
@@ -7423,7 +7423,7 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>GB @ MIN</t>
+          <t>MIA @ LV</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
@@ -7433,23 +7433,23 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>GB +1.5</t>
+          <t>LV -3.5</t>
         </is>
       </c>
       <c r="E119" s="7" t="n">
-        <v>-118</v>
+        <v>-110</v>
       </c>
       <c r="F119" s="8" t="n">
-        <v>0.5059</v>
+        <v>0.4861</v>
       </c>
       <c r="G119" s="8" t="n">
-        <v>0.5413</v>
+        <v>0.5238</v>
       </c>
       <c r="H119" s="8" t="n">
-        <v>-0.0312</v>
+        <v>-0.0328</v>
       </c>
       <c r="I119" s="8" t="n">
-        <v>-0.06540098201615635</v>
+        <v>-0.07205810604965518</v>
       </c>
       <c r="J119" s="10" t="n">
         <v>0.5</v>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>NYJ @ TEN</t>
+          <t>WSH @ PHI</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
@@ -7474,23 +7474,23 @@
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>NYJ ML</t>
+          <t>PHI ML</t>
         </is>
       </c>
       <c r="E120" s="12" t="n">
-        <v>124</v>
+        <v>-205</v>
       </c>
       <c r="F120" s="13" t="n">
-        <v>0.4109</v>
+        <v>0.6334</v>
       </c>
       <c r="G120" s="13" t="n">
-        <v>0.4464</v>
+        <v>0.6721</v>
       </c>
       <c r="H120" s="13" t="n">
-        <v>-0.0313</v>
+        <v>-0.0334</v>
       </c>
       <c r="I120" s="13" t="n">
-        <v>-0.07897314954737311</v>
+        <v>-0.05713941714668008</v>
       </c>
       <c r="J120" s="14" t="n">
         <v>0.5</v>
@@ -7505,7 +7505,7 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>MIA @ LV</t>
+          <t>HOU @ CAR</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
@@ -7515,28 +7515,32 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>LV -3.5</t>
+          <t>HOU -2.5</t>
         </is>
       </c>
       <c r="E121" s="7" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="F121" s="8" t="n">
-        <v>0.4861</v>
+        <v>0.4798</v>
       </c>
       <c r="G121" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5192</v>
       </c>
       <c r="H121" s="8" t="n">
-        <v>-0.0328</v>
+        <v>-0.0338</v>
       </c>
       <c r="I121" s="8" t="n">
-        <v>-0.07205810604965518</v>
+        <v>-0.07598852784685522</v>
       </c>
       <c r="J121" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K121" s="4" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K121" s="4" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
@@ -7546,33 +7550,33 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>WSH @ PHI</t>
+          <t>TB @ CIN</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>PHI -4.5</t>
+          <t>CIN ML</t>
         </is>
       </c>
       <c r="E122" s="12" t="n">
-        <v>-110</v>
+        <v>-198</v>
       </c>
       <c r="F122" s="13" t="n">
-        <v>0.486</v>
+        <v>0.6244</v>
       </c>
       <c r="G122" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.6644</v>
       </c>
       <c r="H122" s="13" t="n">
-        <v>-0.0328</v>
+        <v>-0.0342</v>
       </c>
       <c r="I122" s="13" t="n">
-        <v>-0.07223462803087871</v>
+        <v>-0.05977886130566457</v>
       </c>
       <c r="J122" s="14" t="n">
         <v>0.5</v>
@@ -7587,33 +7591,33 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>HOU @ CAR</t>
+          <t>NE @ CLE</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>HOU -2.5</t>
+          <t>CLE ML</t>
         </is>
       </c>
       <c r="E123" s="7" t="n">
-        <v>-108</v>
+        <v>125</v>
       </c>
       <c r="F123" s="8" t="n">
-        <v>0.4798</v>
+        <v>0.4033</v>
       </c>
       <c r="G123" s="8" t="n">
-        <v>0.5192</v>
+        <v>0.4444</v>
       </c>
       <c r="H123" s="8" t="n">
-        <v>-0.0338</v>
+        <v>-0.0349</v>
       </c>
       <c r="I123" s="8" t="n">
-        <v>-0.07598852784685522</v>
+        <v>-0.09179245906856626</v>
       </c>
       <c r="J123" s="10" t="n">
         <v>0.15</v>
@@ -7632,33 +7636,33 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>TB @ CIN</t>
+          <t>BAL @ IND</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>CIN ML</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="E124" s="12" t="n">
-        <v>-198</v>
+        <v>-110</v>
       </c>
       <c r="F124" s="13" t="n">
-        <v>0.6244</v>
+        <v>0.4822</v>
       </c>
       <c r="G124" s="13" t="n">
-        <v>0.6644</v>
+        <v>0.5238</v>
       </c>
       <c r="H124" s="13" t="n">
-        <v>-0.0342</v>
+        <v>-0.0351</v>
       </c>
       <c r="I124" s="13" t="n">
-        <v>-0.05977886130566457</v>
+        <v>-0.07941494155167578</v>
       </c>
       <c r="J124" s="14" t="n">
         <v>0.5</v>
@@ -7673,42 +7677,38 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>NE @ CLE</t>
+          <t>WSH @ PHI</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>CLE ML</t>
+          <t>PHI -4.5</t>
         </is>
       </c>
       <c r="E125" s="7" t="n">
-        <v>125</v>
+        <v>-110</v>
       </c>
       <c r="F125" s="8" t="n">
-        <v>0.4033</v>
+        <v>0.4813</v>
       </c>
       <c r="G125" s="8" t="n">
-        <v>0.4444</v>
+        <v>0.5238</v>
       </c>
       <c r="H125" s="8" t="n">
-        <v>-0.0349</v>
+        <v>-0.0357</v>
       </c>
       <c r="I125" s="8" t="n">
-        <v>-0.09179245906856626</v>
+        <v>-0.08120015320190704</v>
       </c>
       <c r="J125" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K125" s="4" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K125" s="4" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
@@ -7718,33 +7718,33 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>BAL @ IND</t>
+          <t>NYJ @ TEN</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>NYJ +3</t>
         </is>
       </c>
       <c r="E126" s="12" t="n">
-        <v>-110</v>
+        <v>-120</v>
       </c>
       <c r="F126" s="13" t="n">
-        <v>0.4822</v>
+        <v>0.5018</v>
       </c>
       <c r="G126" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5455</v>
       </c>
       <c r="H126" s="13" t="n">
-        <v>-0.0351</v>
+        <v>-0.0363</v>
       </c>
       <c r="I126" s="13" t="n">
-        <v>-0.07941494155167578</v>
+        <v>-0.07425212545539306</v>
       </c>
       <c r="J126" s="14" t="n">
         <v>0.5</v>
@@ -7804,38 +7804,42 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>NYJ @ TEN</t>
+          <t>SEA @ KC</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>NYJ +3</t>
+          <t>SEA ML</t>
         </is>
       </c>
       <c r="E128" s="12" t="n">
-        <v>-120</v>
+        <v>106</v>
       </c>
       <c r="F128" s="13" t="n">
-        <v>0.5006</v>
+        <v>0.4403</v>
       </c>
       <c r="G128" s="13" t="n">
-        <v>0.5455</v>
+        <v>0.4854</v>
       </c>
       <c r="H128" s="13" t="n">
-        <v>-0.037</v>
+        <v>-0.0371</v>
       </c>
       <c r="I128" s="13" t="n">
-        <v>-0.07622757500745125</v>
+        <v>-0.09212307533405412</v>
       </c>
       <c r="J128" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K128" s="5" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K128" s="5" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
@@ -7845,7 +7849,7 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>SEA @ KC</t>
+          <t>BAL @ IND</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
@@ -7855,32 +7859,28 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>SEA ML</t>
+          <t>BAL ML</t>
         </is>
       </c>
       <c r="E129" s="7" t="n">
-        <v>106</v>
+        <v>-175</v>
       </c>
       <c r="F129" s="8" t="n">
-        <v>0.4403</v>
+        <v>0.5886</v>
       </c>
       <c r="G129" s="8" t="n">
-        <v>0.4854</v>
+        <v>0.6364</v>
       </c>
       <c r="H129" s="8" t="n">
-        <v>-0.0371</v>
+        <v>-0.0385</v>
       </c>
       <c r="I129" s="8" t="n">
-        <v>-0.09212307533405412</v>
+        <v>-0.07443975605449066</v>
       </c>
       <c r="J129" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K129" s="4" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K129" s="4" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
@@ -7890,38 +7890,42 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>BAL @ IND</t>
+          <t>PIT @ BUF</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>BAL ML</t>
+          <t>PIT +3</t>
         </is>
       </c>
       <c r="E130" s="12" t="n">
-        <v>-175</v>
+        <v>-112</v>
       </c>
       <c r="F130" s="13" t="n">
-        <v>0.5886</v>
+        <v>0.4802</v>
       </c>
       <c r="G130" s="13" t="n">
-        <v>0.6364</v>
+        <v>0.5283</v>
       </c>
       <c r="H130" s="13" t="n">
-        <v>-0.0385</v>
+        <v>-0.0387</v>
       </c>
       <c r="I130" s="13" t="n">
-        <v>-0.07443975605449066</v>
+        <v>-0.08443032251086047</v>
       </c>
       <c r="J130" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K130" s="5" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K130" s="5" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
@@ -7931,42 +7935,38 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>PIT @ BUF</t>
+          <t>NE @ SEA</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>PIT +3</t>
+          <t>Over 44.5</t>
         </is>
       </c>
       <c r="E131" s="7" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="F131" s="8" t="n">
-        <v>0.4802</v>
+        <v>0.4746</v>
       </c>
       <c r="G131" s="8" t="n">
-        <v>0.5283</v>
+        <v>0.5238</v>
       </c>
       <c r="H131" s="8" t="n">
-        <v>-0.0387</v>
+        <v>-0.0392</v>
       </c>
       <c r="I131" s="8" t="n">
-        <v>-0.08443032251086047</v>
+        <v>-0.09392613489256912</v>
       </c>
       <c r="J131" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K131" s="4" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K131" s="4" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>NE @ SEA</t>
+          <t>BUF @ HOU</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>Over 44.5</t>
+          <t>Under 44.5</t>
         </is>
       </c>
       <c r="E132" s="12" t="n">
@@ -7999,10 +7999,10 @@
         <v>0.5238</v>
       </c>
       <c r="H132" s="13" t="n">
-        <v>-0.0392</v>
+        <v>-0.0393</v>
       </c>
       <c r="I132" s="13" t="n">
-        <v>-0.09392613489256912</v>
+        <v>-0.09393284195420176</v>
       </c>
       <c r="J132" s="14" t="n">
         <v>0.5</v>
@@ -8017,33 +8017,33 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>BUF @ HOU</t>
+          <t>CHI @ CAR</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Under 44.5</t>
+          <t>CHI ML</t>
         </is>
       </c>
       <c r="E133" s="7" t="n">
-        <v>-110</v>
+        <v>-142</v>
       </c>
       <c r="F133" s="8" t="n">
-        <v>0.4746</v>
+        <v>0.5368000000000001</v>
       </c>
       <c r="G133" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5868</v>
       </c>
       <c r="H133" s="8" t="n">
-        <v>-0.0393</v>
+        <v>-0.0396</v>
       </c>
       <c r="I133" s="8" t="n">
-        <v>-0.09393284195420176</v>
+        <v>-0.08434198923043995</v>
       </c>
       <c r="J133" s="10" t="n">
         <v>0.5</v>
@@ -8058,33 +8058,33 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>CHI @ CAR</t>
+          <t>BAL @ IND</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>CHI ML</t>
+          <t>BAL -3.5</t>
         </is>
       </c>
       <c r="E134" s="12" t="n">
-        <v>-142</v>
+        <v>-108</v>
       </c>
       <c r="F134" s="13" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.4679</v>
       </c>
       <c r="G134" s="13" t="n">
-        <v>0.5868</v>
+        <v>0.5192</v>
       </c>
       <c r="H134" s="13" t="n">
-        <v>-0.0396</v>
+        <v>-0.0403</v>
       </c>
       <c r="I134" s="13" t="n">
-        <v>-0.08434198923043995</v>
+        <v>-0.09889806147849689</v>
       </c>
       <c r="J134" s="14" t="n">
         <v>0.5</v>
@@ -8099,42 +8099,38 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>CIN @ PHI</t>
+          <t>DEN @ KC</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>PHI ML</t>
+          <t>Over 42.5</t>
         </is>
       </c>
       <c r="E135" s="7" t="n">
-        <v>-155</v>
+        <v>-110</v>
       </c>
       <c r="F135" s="8" t="n">
-        <v>0.5577</v>
+        <v>0.4721</v>
       </c>
       <c r="G135" s="8" t="n">
-        <v>0.6078</v>
+        <v>0.5238</v>
       </c>
       <c r="H135" s="8" t="n">
-        <v>-0.0397</v>
+        <v>-0.0404</v>
       </c>
       <c r="I135" s="8" t="n">
-        <v>-0.08178089975335062</v>
+        <v>-0.09874913496091675</v>
       </c>
       <c r="J135" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K135" s="4" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K135" s="4" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
@@ -8144,33 +8140,33 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>CIN @ PHI</t>
+          <t>HOU @ CAR</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>PHI -3</t>
+          <t>HOU ML</t>
         </is>
       </c>
       <c r="E136" s="12" t="n">
-        <v>-108</v>
+        <v>-144</v>
       </c>
       <c r="F136" s="13" t="n">
-        <v>0.468</v>
+        <v>0.5379</v>
       </c>
       <c r="G136" s="13" t="n">
-        <v>0.5192</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="H136" s="13" t="n">
-        <v>-0.0402</v>
+        <v>-0.0407</v>
       </c>
       <c r="I136" s="13" t="n">
-        <v>-0.09155647798971034</v>
+        <v>-0.08779449906398951</v>
       </c>
       <c r="J136" s="14" t="n">
         <v>0.15</v>
@@ -8189,7 +8185,7 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>BAL @ IND</t>
+          <t>SF @ LAR</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
@@ -8199,23 +8195,23 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>BAL -3.5</t>
+          <t>LAR -3.5</t>
         </is>
       </c>
       <c r="E137" s="7" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="F137" s="8" t="n">
-        <v>0.4679</v>
+        <v>0.4597</v>
       </c>
       <c r="G137" s="8" t="n">
-        <v>0.5192</v>
+        <v>0.5122</v>
       </c>
       <c r="H137" s="8" t="n">
-        <v>-0.0403</v>
+        <v>-0.0408</v>
       </c>
       <c r="I137" s="8" t="n">
-        <v>-0.09889806147849689</v>
+        <v>-0.1024475989508608</v>
       </c>
       <c r="J137" s="10" t="n">
         <v>0.5</v>
@@ -8230,38 +8226,42 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>DEN @ KC</t>
+          <t>NE @ CLE</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>Over 42.5</t>
+          <t>CLE +2.5</t>
         </is>
       </c>
       <c r="E138" s="12" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="F138" s="13" t="n">
-        <v>0.4721</v>
+        <v>0.4595</v>
       </c>
       <c r="G138" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5122</v>
       </c>
       <c r="H138" s="13" t="n">
-        <v>-0.0404</v>
+        <v>-0.0409</v>
       </c>
       <c r="I138" s="13" t="n">
-        <v>-0.09874913496091675</v>
+        <v>-0.1029270500313946</v>
       </c>
       <c r="J138" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K138" s="5" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K138" s="5" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
@@ -8271,7 +8271,7 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>HOU @ CAR</t>
+          <t>CIN @ PHI</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
@@ -8281,23 +8281,23 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>HOU ML</t>
+          <t>PHI ML</t>
         </is>
       </c>
       <c r="E139" s="7" t="n">
-        <v>-144</v>
+        <v>-155</v>
       </c>
       <c r="F139" s="8" t="n">
-        <v>0.5379</v>
+        <v>0.5538999999999999</v>
       </c>
       <c r="G139" s="8" t="n">
-        <v>0.5901999999999999</v>
+        <v>0.6078</v>
       </c>
       <c r="H139" s="8" t="n">
-        <v>-0.0407</v>
+        <v>-0.0415</v>
       </c>
       <c r="I139" s="8" t="n">
-        <v>-0.08779449906398951</v>
+        <v>-0.0880069805900533</v>
       </c>
       <c r="J139" s="10" t="n">
         <v>0.15</v>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>SF @ LAR</t>
+          <t>CHI @ CAR</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
@@ -8326,23 +8326,23 @@
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>LAR -3.5</t>
+          <t>CHI -2.5</t>
         </is>
       </c>
       <c r="E140" s="12" t="n">
-        <v>-105</v>
+        <v>-118</v>
       </c>
       <c r="F140" s="13" t="n">
-        <v>0.4597</v>
+        <v>0.4868</v>
       </c>
       <c r="G140" s="13" t="n">
-        <v>0.5122</v>
+        <v>0.5413</v>
       </c>
       <c r="H140" s="13" t="n">
-        <v>-0.0408</v>
+        <v>-0.0417</v>
       </c>
       <c r="I140" s="13" t="n">
-        <v>-0.1024475989508608</v>
+        <v>-0.1006042439907167</v>
       </c>
       <c r="J140" s="14" t="n">
         <v>0.5</v>
@@ -8357,42 +8357,38 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>NE @ CLE</t>
+          <t>MIA @ LV</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>CLE +2.5</t>
+          <t>LV ML</t>
         </is>
       </c>
       <c r="E141" s="7" t="n">
-        <v>-105</v>
+        <v>-205</v>
       </c>
       <c r="F141" s="8" t="n">
-        <v>0.4595</v>
+        <v>0.6176</v>
       </c>
       <c r="G141" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.6721</v>
       </c>
       <c r="H141" s="8" t="n">
-        <v>-0.0409</v>
+        <v>-0.0417</v>
       </c>
       <c r="I141" s="8" t="n">
-        <v>-0.1029270500313946</v>
+        <v>-0.08044651572494638</v>
       </c>
       <c r="J141" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K141" s="4" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K141" s="4" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
@@ -8402,7 +8398,7 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>CHI @ CAR</t>
+          <t>CIN @ PHI</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
@@ -8412,28 +8408,32 @@
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>CHI -2.5</t>
+          <t>PHI -3</t>
         </is>
       </c>
       <c r="E142" s="12" t="n">
-        <v>-118</v>
+        <v>-108</v>
       </c>
       <c r="F142" s="13" t="n">
-        <v>0.4868</v>
+        <v>0.464</v>
       </c>
       <c r="G142" s="13" t="n">
-        <v>0.5413</v>
+        <v>0.5192</v>
       </c>
       <c r="H142" s="13" t="n">
-        <v>-0.0417</v>
+        <v>-0.042</v>
       </c>
       <c r="I142" s="13" t="n">
-        <v>-0.1006042439907167</v>
+        <v>-0.09875821259437217</v>
       </c>
       <c r="J142" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K142" s="5" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K142" s="5" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>MIA @ LV</t>
+          <t>NO @ DET</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
@@ -8453,23 +8453,23 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>LV ML</t>
+          <t>DET ML</t>
         </is>
       </c>
       <c r="E143" s="7" t="n">
-        <v>-205</v>
+        <v>-305</v>
       </c>
       <c r="F143" s="8" t="n">
-        <v>0.6176</v>
+        <v>0.6977</v>
       </c>
       <c r="G143" s="8" t="n">
-        <v>0.6721</v>
+        <v>0.7531</v>
       </c>
       <c r="H143" s="8" t="n">
-        <v>-0.0417</v>
+        <v>-0.042</v>
       </c>
       <c r="I143" s="8" t="n">
-        <v>-0.08044651572494638</v>
+        <v>-0.07290108839170278</v>
       </c>
       <c r="J143" s="10" t="n">
         <v>0.5</v>
@@ -8484,7 +8484,7 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>NO @ DET</t>
+          <t>CHI @ TEN</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
@@ -8494,28 +8494,32 @@
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>DET ML</t>
+          <t>TEN ML</t>
         </is>
       </c>
       <c r="E144" s="12" t="n">
-        <v>-305</v>
+        <v>-152</v>
       </c>
       <c r="F144" s="13" t="n">
-        <v>0.6977</v>
+        <v>0.5466</v>
       </c>
       <c r="G144" s="13" t="n">
-        <v>0.7531</v>
+        <v>0.6032</v>
       </c>
       <c r="H144" s="13" t="n">
-        <v>-0.042</v>
+        <v>-0.0425</v>
       </c>
       <c r="I144" s="13" t="n">
-        <v>-0.07290108839170278</v>
+        <v>-0.09290306899169787</v>
       </c>
       <c r="J144" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K144" s="5" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K144" s="5" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
@@ -8530,28 +8534,28 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>TEN ML</t>
+          <t>TEN -3</t>
         </is>
       </c>
       <c r="E145" s="7" t="n">
-        <v>-152</v>
+        <v>-105</v>
       </c>
       <c r="F145" s="8" t="n">
-        <v>0.5466</v>
+        <v>0.4556</v>
       </c>
       <c r="G145" s="8" t="n">
-        <v>0.6032</v>
+        <v>0.5122</v>
       </c>
       <c r="H145" s="8" t="n">
         <v>-0.0425</v>
       </c>
       <c r="I145" s="8" t="n">
-        <v>-0.09290306899169787</v>
+        <v>-0.1025819120098156</v>
       </c>
       <c r="J145" s="10" t="n">
         <v>0.15</v>
@@ -8570,7 +8574,7 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>CHI @ TEN</t>
+          <t>NE @ SEA</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
@@ -8580,7 +8584,7 @@
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>TEN -3</t>
+          <t>SEA -3.5</t>
         </is>
       </c>
       <c r="E146" s="12" t="n">
@@ -8596,16 +8600,12 @@
         <v>-0.0425</v>
       </c>
       <c r="I146" s="13" t="n">
-        <v>-0.1025819120098156</v>
+        <v>-0.110425468569784</v>
       </c>
       <c r="J146" s="14" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K146" s="5" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K146" s="5" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
@@ -8615,38 +8615,42 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>NE @ SEA</t>
+          <t>ARI @ LAC</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>SEA -3.5</t>
+          <t>LAC ML</t>
         </is>
       </c>
       <c r="E147" s="7" t="n">
-        <v>-105</v>
+        <v>-575</v>
       </c>
       <c r="F147" s="8" t="n">
-        <v>0.4556</v>
+        <v>0.795</v>
       </c>
       <c r="G147" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.8519</v>
       </c>
       <c r="H147" s="8" t="n">
-        <v>-0.0425</v>
+        <v>-0.0426</v>
       </c>
       <c r="I147" s="8" t="n">
-        <v>-0.110425468569784</v>
+        <v>-0.0662897367869042</v>
       </c>
       <c r="J147" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="K147" s="4" t="inlineStr"/>
+      <c r="K147" s="4" t="inlineStr">
+        <is>
+          <t>price -575 outside the allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
@@ -8877,7 +8881,7 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>NO @ DET</t>
+          <t>ARI @ LAC</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
@@ -8887,23 +8891,23 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>DET -7</t>
+          <t>LAC -10.5</t>
         </is>
       </c>
       <c r="E153" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F153" s="8" t="n">
-        <v>0.4633</v>
+        <v>0.4642</v>
       </c>
       <c r="G153" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H153" s="8" t="n">
-        <v>-0.044</v>
+        <v>-0.0437</v>
       </c>
       <c r="I153" s="8" t="n">
-        <v>-0.1091954940217635</v>
+        <v>-0.1137669909981206</v>
       </c>
       <c r="J153" s="10" t="n">
         <v>0.5</v>
@@ -8918,42 +8922,38 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>ARI @ LAC</t>
+          <t>NO @ DET</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>LAC ML</t>
+          <t>DET -7</t>
         </is>
       </c>
       <c r="E154" s="12" t="n">
-        <v>-575</v>
+        <v>-110</v>
       </c>
       <c r="F154" s="13" t="n">
-        <v>0.7909</v>
+        <v>0.4633</v>
       </c>
       <c r="G154" s="13" t="n">
-        <v>0.8519</v>
+        <v>0.5238</v>
       </c>
       <c r="H154" s="13" t="n">
-        <v>-0.0442</v>
+        <v>-0.044</v>
       </c>
       <c r="I154" s="13" t="n">
-        <v>-0.07112757907313333</v>
+        <v>-0.1091954940217635</v>
       </c>
       <c r="J154" s="14" t="n">
         <v>0.5</v>
       </c>
-      <c r="K154" s="5" t="inlineStr">
-        <is>
-          <t>price -575 outside the allowed range</t>
-        </is>
-      </c>
+      <c r="K154" s="5" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
@@ -9131,38 +9131,42 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>CLE @ JAX</t>
+          <t>NO @ DAL</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>Under 40.5</t>
+          <t>NO ML</t>
         </is>
       </c>
       <c r="E159" s="7" t="n">
-        <v>-110</v>
+        <v>108</v>
       </c>
       <c r="F159" s="8" t="n">
-        <v>0.4595</v>
+        <v>0.4171</v>
       </c>
       <c r="G159" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.4808</v>
       </c>
       <c r="H159" s="8" t="n">
-        <v>-0.0453</v>
+        <v>-0.0451</v>
       </c>
       <c r="I159" s="8" t="n">
-        <v>-0.1228333297743933</v>
+        <v>-0.1312659311369053</v>
       </c>
       <c r="J159" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K159" s="4" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K159" s="4" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
@@ -9172,33 +9176,33 @@
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>ARI @ LAC</t>
+          <t>CLE @ JAX</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>LAC -10.5</t>
+          <t>Under 40.5</t>
         </is>
       </c>
       <c r="E160" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F160" s="13" t="n">
-        <v>0.4586</v>
+        <v>0.4595</v>
       </c>
       <c r="G160" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H160" s="13" t="n">
-        <v>-0.0456</v>
+        <v>-0.0453</v>
       </c>
       <c r="I160" s="13" t="n">
-        <v>-0.1245402516887618</v>
+        <v>-0.1228333297743933</v>
       </c>
       <c r="J160" s="14" t="n">
         <v>0.5</v>
@@ -9213,33 +9217,33 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>TB @ JAX</t>
+          <t>MIN @ DEN</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>TB ML</t>
+          <t>DEN -6</t>
         </is>
       </c>
       <c r="E161" s="7" t="n">
-        <v>-156</v>
+        <v>-112</v>
       </c>
       <c r="F161" s="8" t="n">
-        <v>0.5435</v>
+        <v>0.4629</v>
       </c>
       <c r="G161" s="8" t="n">
-        <v>0.6094000000000001</v>
+        <v>0.5283</v>
       </c>
       <c r="H161" s="8" t="n">
-        <v>-0.0458</v>
+        <v>-0.0457</v>
       </c>
       <c r="I161" s="8" t="n">
-        <v>-0.107120555488541</v>
+        <v>-0.1193157194379108</v>
       </c>
       <c r="J161" s="10" t="n">
         <v>0.15</v>
@@ -9258,7 +9262,7 @@
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>NO @ DAL</t>
+          <t>TB @ JAX</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
@@ -9268,23 +9272,23 @@
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>NO ML</t>
+          <t>TB ML</t>
         </is>
       </c>
       <c r="E162" s="12" t="n">
-        <v>108</v>
+        <v>-156</v>
       </c>
       <c r="F162" s="13" t="n">
-        <v>0.415</v>
+        <v>0.5435</v>
       </c>
       <c r="G162" s="13" t="n">
-        <v>0.4808</v>
+        <v>0.6094000000000001</v>
       </c>
       <c r="H162" s="13" t="n">
         <v>-0.0458</v>
       </c>
       <c r="I162" s="13" t="n">
-        <v>-0.1356374885155444</v>
+        <v>-0.107120555488541</v>
       </c>
       <c r="J162" s="14" t="n">
         <v>0.15</v>
@@ -9303,7 +9307,7 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>ARI @ LAC</t>
+          <t>MIA @ LV</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
@@ -9313,7 +9317,7 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>Over 46.5</t>
+          <t>Under 40.5</t>
         </is>
       </c>
       <c r="E163" s="7" t="n">
@@ -9329,7 +9333,7 @@
         <v>-0.0461</v>
       </c>
       <c r="I163" s="8" t="n">
-        <v>-0.1276128918105729</v>
+        <v>-0.1276251689568088</v>
       </c>
       <c r="J163" s="10" t="n">
         <v>0.5</v>
@@ -9344,38 +9348,42 @@
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>MIA @ LV</t>
+          <t>LAR @ LAC</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>Under 40.5</t>
+          <t>LAC -3.5</t>
         </is>
       </c>
       <c r="E164" s="12" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="F164" s="13" t="n">
-        <v>0.457</v>
+        <v>0.4609</v>
       </c>
       <c r="G164" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5283</v>
       </c>
       <c r="H164" s="13" t="n">
-        <v>-0.0461</v>
+        <v>-0.0463</v>
       </c>
       <c r="I164" s="13" t="n">
-        <v>-0.1276251689568088</v>
+        <v>-0.1275004997636998</v>
       </c>
       <c r="J164" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K164" s="5" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K164" s="5" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
@@ -9385,33 +9393,33 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>LAR @ LAC</t>
+          <t>ATL @ MIA</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>LAC -3.5</t>
+          <t>ATL ML</t>
         </is>
       </c>
       <c r="E165" s="7" t="n">
-        <v>-112</v>
+        <v>-191</v>
       </c>
       <c r="F165" s="8" t="n">
-        <v>0.4609</v>
+        <v>0.5884</v>
       </c>
       <c r="G165" s="8" t="n">
-        <v>0.5283</v>
+        <v>0.6564</v>
       </c>
       <c r="H165" s="8" t="n">
-        <v>-0.0463</v>
+        <v>-0.0464</v>
       </c>
       <c r="I165" s="8" t="n">
-        <v>-0.1275004997636998</v>
+        <v>-0.1025987872915858</v>
       </c>
       <c r="J165" s="10" t="n">
         <v>0.15</v>
@@ -9430,33 +9438,33 @@
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>ATL @ MIA</t>
+          <t>NYG @ NYJ</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>ATL ML</t>
+          <t>NYG -3</t>
         </is>
       </c>
       <c r="E166" s="12" t="n">
-        <v>-191</v>
+        <v>-115</v>
       </c>
       <c r="F166" s="13" t="n">
-        <v>0.5884</v>
+        <v>0.4661</v>
       </c>
       <c r="G166" s="13" t="n">
-        <v>0.6564</v>
+        <v>0.5349</v>
       </c>
       <c r="H166" s="13" t="n">
-        <v>-0.0464</v>
+        <v>-0.0467</v>
       </c>
       <c r="I166" s="13" t="n">
-        <v>-0.1025987872915858</v>
+        <v>-0.1194812544089797</v>
       </c>
       <c r="J166" s="14" t="n">
         <v>0.15</v>
@@ -9475,33 +9483,33 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>NYG @ NYJ</t>
+          <t>DET @ IND</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>NYG -3</t>
+          <t>IND ML</t>
         </is>
       </c>
       <c r="E167" s="7" t="n">
-        <v>-115</v>
+        <v>-173</v>
       </c>
       <c r="F167" s="8" t="n">
-        <v>0.4668</v>
+        <v>0.5649</v>
       </c>
       <c r="G167" s="8" t="n">
-        <v>0.5349</v>
+        <v>0.6337</v>
       </c>
       <c r="H167" s="8" t="n">
-        <v>-0.0465</v>
+        <v>-0.0467</v>
       </c>
       <c r="I167" s="8" t="n">
-        <v>-0.1181521168831401</v>
+        <v>-0.107543470257828</v>
       </c>
       <c r="J167" s="10" t="n">
         <v>0.15</v>
@@ -9520,33 +9528,33 @@
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>DET @ IND</t>
+          <t>TB @ JAX</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>IND ML</t>
+          <t>TB -3</t>
         </is>
       </c>
       <c r="E168" s="12" t="n">
-        <v>-173</v>
+        <v>-110</v>
       </c>
       <c r="F168" s="13" t="n">
-        <v>0.5649</v>
+        <v>0.4545</v>
       </c>
       <c r="G168" s="13" t="n">
-        <v>0.6337</v>
+        <v>0.5238</v>
       </c>
       <c r="H168" s="13" t="n">
-        <v>-0.0467</v>
+        <v>-0.0468</v>
       </c>
       <c r="I168" s="13" t="n">
-        <v>-0.107543470257828</v>
+        <v>-0.1229706592278252</v>
       </c>
       <c r="J168" s="14" t="n">
         <v>0.15</v>
@@ -9565,17 +9573,17 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>TB @ JAX</t>
+          <t>ARI @ LAC</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>TB -3</t>
+          <t>Over 46.5</t>
         </is>
       </c>
       <c r="E169" s="7" t="n">
@@ -9591,16 +9599,12 @@
         <v>-0.0468</v>
       </c>
       <c r="I169" s="8" t="n">
-        <v>-0.1229706592278252</v>
+        <v>-0.1323971774011638</v>
       </c>
       <c r="J169" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K169" s="4" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K169" s="4" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="5" t="inlineStr">
@@ -9610,7 +9614,7 @@
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>ARI @ GB</t>
+          <t>CLE @ JAX</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
@@ -9620,14 +9624,14 @@
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>ARI -2.5</t>
+          <t>JAX -7.5</t>
         </is>
       </c>
       <c r="E170" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F170" s="13" t="n">
-        <v>0.4538</v>
+        <v>0.454</v>
       </c>
       <c r="G170" s="13" t="n">
         <v>0.5238</v>
@@ -9636,16 +9640,12 @@
         <v>-0.047</v>
       </c>
       <c r="I170" s="13" t="n">
-        <v>-0.1336985167567211</v>
+        <v>-0.1333147546894979</v>
       </c>
       <c r="J170" s="14" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K170" s="5" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K170" s="5" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
@@ -9655,7 +9655,7 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>CLE @ JAX</t>
+          <t>ARI @ GB</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
@@ -9665,28 +9665,32 @@
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>JAX -7.5</t>
+          <t>ARI -2.5</t>
         </is>
       </c>
       <c r="E171" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F171" s="8" t="n">
-        <v>0.454</v>
+        <v>0.4534</v>
       </c>
       <c r="G171" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H171" s="8" t="n">
-        <v>-0.047</v>
+        <v>-0.0471</v>
       </c>
       <c r="I171" s="8" t="n">
-        <v>-0.1333147546894979</v>
+        <v>-0.1343753320785118</v>
       </c>
       <c r="J171" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K171" s="4" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K171" s="4" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
@@ -9754,16 +9758,16 @@
         <v>-173</v>
       </c>
       <c r="F173" s="8" t="n">
-        <v>0.5604</v>
+        <v>0.5596</v>
       </c>
       <c r="G173" s="8" t="n">
         <v>0.6337</v>
       </c>
       <c r="H173" s="8" t="n">
-        <v>-0.0479</v>
+        <v>-0.048</v>
       </c>
       <c r="I173" s="8" t="n">
-        <v>-0.1146900352578891</v>
+        <v>-0.1158293344332618</v>
       </c>
       <c r="J173" s="10" t="n">
         <v>0.15</v>
@@ -9787,28 +9791,28 @@
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>DEN -6</t>
+          <t>DEN ML</t>
         </is>
       </c>
       <c r="E174" s="12" t="n">
-        <v>-112</v>
+        <v>-279</v>
       </c>
       <c r="F174" s="13" t="n">
-        <v>0.4546</v>
+        <v>0.6621</v>
       </c>
       <c r="G174" s="13" t="n">
-        <v>0.5283</v>
+        <v>0.7361</v>
       </c>
       <c r="H174" s="13" t="n">
         <v>-0.048</v>
       </c>
       <c r="I174" s="13" t="n">
-        <v>-0.1345517528459403</v>
+        <v>-0.09977622696744701</v>
       </c>
       <c r="J174" s="14" t="n">
         <v>0.15</v>
@@ -9913,7 +9917,7 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>WSH @ PHI</t>
+          <t>NO @ DET</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
@@ -9923,23 +9927,23 @@
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>Over 46.5</t>
+          <t>Over 49.5</t>
         </is>
       </c>
       <c r="E177" s="7" t="n">
-        <v>-110</v>
+        <v>-102</v>
       </c>
       <c r="F177" s="8" t="n">
-        <v>0.447</v>
+        <v>0.426</v>
       </c>
       <c r="G177" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.505</v>
       </c>
       <c r="H177" s="8" t="n">
-        <v>-0.0487</v>
+        <v>-0.0491</v>
       </c>
       <c r="I177" s="8" t="n">
-        <v>-0.1466985804382782</v>
+        <v>-0.1562575749131983</v>
       </c>
       <c r="J177" s="10" t="n">
         <v>0.5</v>
@@ -9954,38 +9958,42 @@
       </c>
       <c r="B178" s="5" t="inlineStr">
         <is>
-          <t>NO @ DET</t>
+          <t>NO @ DAL</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>Over 49.5</t>
+          <t>NO +1.5</t>
         </is>
       </c>
       <c r="E178" s="12" t="n">
-        <v>-102</v>
+        <v>-115</v>
       </c>
       <c r="F178" s="13" t="n">
-        <v>0.426</v>
+        <v>0.4554</v>
       </c>
       <c r="G178" s="13" t="n">
-        <v>0.505</v>
+        <v>0.5349</v>
       </c>
       <c r="H178" s="13" t="n">
-        <v>-0.0491</v>
+        <v>-0.0492</v>
       </c>
       <c r="I178" s="13" t="n">
-        <v>-0.1562575749131983</v>
+        <v>-0.1486481167352391</v>
       </c>
       <c r="J178" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K178" s="5" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K178" s="5" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
@@ -10081,42 +10089,38 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>NO @ DAL</t>
+          <t>WSH @ PHI</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>NO +1.5</t>
+          <t>Over 46.5</t>
         </is>
       </c>
       <c r="E181" s="7" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="F181" s="8" t="n">
-        <v>0.4532</v>
+        <v>0.442</v>
       </c>
       <c r="G181" s="8" t="n">
-        <v>0.5349</v>
+        <v>0.5238</v>
       </c>
       <c r="H181" s="8" t="n">
-        <v>-0.0496</v>
+        <v>-0.0497</v>
       </c>
       <c r="I181" s="8" t="n">
-        <v>-0.1526420023921615</v>
+        <v>-0.1561855591186524</v>
       </c>
       <c r="J181" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K181" s="4" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K181" s="4" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="5" t="inlineStr">
@@ -10126,7 +10130,7 @@
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>MIN @ DEN</t>
+          <t>ARI @ GB</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
@@ -10136,23 +10140,23 @@
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>DEN ML</t>
+          <t>ARI ML</t>
         </is>
       </c>
       <c r="E182" s="12" t="n">
-        <v>-279</v>
+        <v>-146</v>
       </c>
       <c r="F182" s="13" t="n">
-        <v>0.6543</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="G182" s="13" t="n">
-        <v>0.7361</v>
+        <v>0.5935</v>
       </c>
       <c r="H182" s="13" t="n">
-        <v>-0.0497</v>
+        <v>-0.0498</v>
       </c>
       <c r="I182" s="13" t="n">
-        <v>-0.1102728979838294</v>
+        <v>-0.1383534680448956</v>
       </c>
       <c r="J182" s="14" t="n">
         <v>0.15</v>
@@ -10171,7 +10175,7 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>ARI @ GB</t>
+          <t>SF @ LV</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
@@ -10181,23 +10185,23 @@
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>ARI ML</t>
+          <t>LV ML</t>
         </is>
       </c>
       <c r="E183" s="7" t="n">
-        <v>-146</v>
+        <v>-174</v>
       </c>
       <c r="F183" s="8" t="n">
-        <v>0.511</v>
+        <v>0.552</v>
       </c>
       <c r="G183" s="8" t="n">
-        <v>0.5935</v>
+        <v>0.635</v>
       </c>
       <c r="H183" s="8" t="n">
-        <v>-0.0498</v>
+        <v>-0.0499</v>
       </c>
       <c r="I183" s="8" t="n">
-        <v>-0.1377436259674803</v>
+        <v>-0.1296335457567894</v>
       </c>
       <c r="J183" s="10" t="n">
         <v>0.15</v>
@@ -10216,33 +10220,33 @@
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>SF @ LV</t>
+          <t>SEA @ KC</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>LV ML</t>
+          <t>Under 36.5</t>
         </is>
       </c>
       <c r="E184" s="12" t="n">
-        <v>-174</v>
+        <v>-110</v>
       </c>
       <c r="F184" s="13" t="n">
-        <v>0.552</v>
+        <v>0.4395</v>
       </c>
       <c r="G184" s="13" t="n">
-        <v>0.635</v>
+        <v>0.5238</v>
       </c>
       <c r="H184" s="13" t="n">
-        <v>-0.0499</v>
+        <v>-0.0501</v>
       </c>
       <c r="I184" s="13" t="n">
-        <v>-0.1296335457567894</v>
+        <v>-0.1609576252652765</v>
       </c>
       <c r="J184" s="14" t="n">
         <v>0.15</v>
@@ -10261,33 +10265,33 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>SEA @ KC</t>
+          <t>SF @ LV</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>Under 36.5</t>
+          <t>LV -3.5</t>
         </is>
       </c>
       <c r="E185" s="7" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="F185" s="8" t="n">
-        <v>0.4395</v>
+        <v>0.4328</v>
       </c>
       <c r="G185" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5192</v>
       </c>
       <c r="H185" s="8" t="n">
-        <v>-0.0501</v>
+        <v>-0.0504</v>
       </c>
       <c r="I185" s="8" t="n">
-        <v>-0.1609576252652765</v>
+        <v>-0.1664547238731173</v>
       </c>
       <c r="J185" s="10" t="n">
         <v>0.15</v>
@@ -10306,7 +10310,7 @@
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>SF @ LV</t>
+          <t>ATL @ MIA</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
@@ -10316,23 +10320,23 @@
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>LV -3.5</t>
+          <t>ATL -4.5</t>
         </is>
       </c>
       <c r="E186" s="12" t="n">
-        <v>-108</v>
+        <v>-115</v>
       </c>
       <c r="F186" s="13" t="n">
-        <v>0.4328</v>
+        <v>0.4458</v>
       </c>
       <c r="G186" s="13" t="n">
-        <v>0.5192</v>
+        <v>0.5349</v>
       </c>
       <c r="H186" s="13" t="n">
-        <v>-0.0504</v>
+        <v>-0.0508</v>
       </c>
       <c r="I186" s="13" t="n">
-        <v>-0.1664547238731173</v>
+        <v>-0.1664669501795517</v>
       </c>
       <c r="J186" s="14" t="n">
         <v>0.15</v>
@@ -10351,42 +10355,38 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>ATL @ MIA</t>
+          <t>SF @ LAR</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>ATL -4.5</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="E187" s="7" t="n">
-        <v>-115</v>
+        <v>-108</v>
       </c>
       <c r="F187" s="8" t="n">
-        <v>0.4458</v>
+        <v>0.4257</v>
       </c>
       <c r="G187" s="8" t="n">
-        <v>0.5349</v>
+        <v>0.5192</v>
       </c>
       <c r="H187" s="8" t="n">
-        <v>-0.0508</v>
+        <v>-0.0514</v>
       </c>
       <c r="I187" s="8" t="n">
-        <v>-0.1664669501795517</v>
+        <v>-0.1801097974819543</v>
       </c>
       <c r="J187" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K187" s="4" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K187" s="4" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="5" t="inlineStr">
@@ -10617,7 +10617,7 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>NO @ DAL</t>
+          <t>ARI @ GB</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
@@ -10631,19 +10631,19 @@
         </is>
       </c>
       <c r="E193" s="7" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="F193" s="8" t="n">
-        <v>0.4079</v>
+        <v>0.4213</v>
       </c>
       <c r="G193" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5349</v>
       </c>
       <c r="H193" s="8" t="n">
-        <v>-0.0534</v>
+        <v>-0.0533</v>
       </c>
       <c r="I193" s="8" t="n">
-        <v>-0.2212487840107566</v>
+        <v>-0.2123541960560287</v>
       </c>
       <c r="J193" s="10" t="n">
         <v>0.15</v>
@@ -10662,7 +10662,7 @@
       </c>
       <c r="B194" s="5" t="inlineStr">
         <is>
-          <t>ARI @ GB</t>
+          <t>NO @ DAL</t>
         </is>
       </c>
       <c r="C194" s="5" t="inlineStr">
@@ -10676,19 +10676,19 @@
         </is>
       </c>
       <c r="E194" s="12" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="F194" s="13" t="n">
-        <v>0.4189</v>
+        <v>0.4079</v>
       </c>
       <c r="G194" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.5238</v>
       </c>
       <c r="H194" s="13" t="n">
         <v>-0.0534</v>
       </c>
       <c r="I194" s="13" t="n">
-        <v>-0.2168587307048448</v>
+        <v>-0.2212487840107566</v>
       </c>
       <c r="J194" s="14" t="n">
         <v>0.15</v>
@@ -10797,7 +10797,7 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>TB @ JAX</t>
+          <t>CHI @ TEN</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
@@ -10807,23 +10807,23 @@
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>Under 34.5</t>
+          <t>Under 36.5</t>
         </is>
       </c>
       <c r="E197" s="7" t="n">
         <v>-105</v>
       </c>
       <c r="F197" s="8" t="n">
-        <v>0.39</v>
+        <v>0.3923</v>
       </c>
       <c r="G197" s="8" t="n">
         <v>0.5122</v>
       </c>
       <c r="H197" s="8" t="n">
-        <v>-0.0537</v>
+        <v>-0.0536</v>
       </c>
       <c r="I197" s="8" t="n">
-        <v>-0.2386136146596633</v>
+        <v>-0.2340347918040657</v>
       </c>
       <c r="J197" s="10" t="n">
         <v>0.15</v>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="B198" s="5" t="inlineStr">
         <is>
-          <t>CHI @ TEN</t>
+          <t>TB @ JAX</t>
         </is>
       </c>
       <c r="C198" s="5" t="inlineStr">
@@ -10852,7 +10852,7 @@
       </c>
       <c r="D198" s="5" t="inlineStr">
         <is>
-          <t>Under 36.5</t>
+          <t>Under 34.5</t>
         </is>
       </c>
       <c r="E198" s="12" t="n">
@@ -10868,7 +10868,7 @@
         <v>-0.0537</v>
       </c>
       <c r="I198" s="13" t="n">
-        <v>-0.2385862949989949</v>
+        <v>-0.2386136146596633</v>
       </c>
       <c r="J198" s="14" t="n">
         <v>0.15</v>
@@ -11039,16 +11039,16 @@
         <v>-118</v>
       </c>
       <c r="F202" s="13" t="n">
-        <v>0.4069</v>
+        <v>0.4092</v>
       </c>
       <c r="G202" s="13" t="n">
         <v>0.5413</v>
       </c>
       <c r="H202" s="13" t="n">
-        <v>-0.0542</v>
+        <v>-0.0541</v>
       </c>
       <c r="I202" s="13" t="n">
-        <v>-0.2482996523363212</v>
+        <v>-0.243941559372741</v>
       </c>
       <c r="J202" s="14" t="n">
         <v>0.15</v>
@@ -11928,7 +11928,7 @@
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>-2.57</v>
+        <v>-2.33</v>
       </c>
       <c r="E10" s="9" t="n">
         <v>2.5</v>
@@ -11962,13 +11962,13 @@
         </is>
       </c>
       <c r="D11" s="24" t="n">
-        <v>10.72</v>
+        <v>11.02</v>
       </c>
       <c r="E11" s="24" t="n">
         <v>-10.5</v>
       </c>
       <c r="F11" s="25" t="n">
-        <v>44.8</v>
+        <v>44.7</v>
       </c>
       <c r="G11" s="25" t="n">
         <v>46.5</v>
@@ -11996,7 +11996,7 @@
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>1.14</v>
+        <v>0.63</v>
       </c>
       <c r="E12" s="9" t="n">
         <v>-1.5</v>
@@ -12064,13 +12064,13 @@
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>4.86</v>
+        <v>4.6</v>
       </c>
       <c r="E14" s="9" t="n">
         <v>-4.5</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>44.4</v>
+        <v>44.2</v>
       </c>
       <c r="G14" s="11" t="n">
         <v>46.5</v>
@@ -12302,7 +12302,7 @@
         </is>
       </c>
       <c r="D21" s="24" t="n">
-        <v>3.53</v>
+        <v>3.47</v>
       </c>
       <c r="E21" s="24" t="n">
         <v>-3</v>
@@ -12376,7 +12376,7 @@
         <v>-3.5</v>
       </c>
       <c r="F23" s="25" t="n">
-        <v>48</v>
+        <v>45.6</v>
       </c>
       <c r="G23" s="25" t="n">
         <v>48.5</v>
@@ -12444,7 +12444,7 @@
         <v>-3</v>
       </c>
       <c r="F25" s="25" t="n">
-        <v>40.8</v>
+        <v>40.7</v>
       </c>
       <c r="G25" s="25" t="n">
         <v>36.5</v>
@@ -12506,7 +12506,7 @@
         </is>
       </c>
       <c r="D27" s="24" t="n">
-        <v>4.57</v>
+        <v>5.02</v>
       </c>
       <c r="E27" s="24" t="n">
         <v>-6</v>
@@ -12540,13 +12540,13 @@
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
       <c r="E28" s="9" t="n">
         <v>-3</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>40.5</v>
+        <v>40.4</v>
       </c>
       <c r="G28" s="11" t="n">
         <v>36.5</v>
@@ -12608,7 +12608,7 @@
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>3.94</v>
+        <v>3.82</v>
       </c>
       <c r="E30" s="9" t="n">
         <v>-1.5</v>
@@ -12642,13 +12642,13 @@
         </is>
       </c>
       <c r="D31" s="24" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="E31" s="24" t="n">
         <v>2.5</v>
       </c>
       <c r="F31" s="25" t="n">
-        <v>41.9</v>
+        <v>41.8</v>
       </c>
       <c r="G31" s="25" t="n">
         <v>38.5</v>
@@ -12676,7 +12676,7 @@
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>-1.25</v>
+        <v>-1.21</v>
       </c>
       <c r="E32" s="9" t="n">
         <v>3</v>
@@ -13342,7 +13342,7 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D11" s="16" t="n">
         <v>1.91</v>
@@ -13374,7 +13374,7 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D12" s="18" t="n">
         <v>1.9</v>
@@ -13406,7 +13406,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D13" s="16" t="n">
         <v>1.89</v>
@@ -31680,12 +31680,12 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Xavier Weaver</t>
+          <t>Trey Benson</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -31700,7 +31700,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Weaver (hamstring) was placed on injured reserve by the Cardinals on Monday.</t>
+          <t>Benson (knee) reverted to the Cardinals' injured reserve list Tuesday, David Furones of the South Florida Sun Sentinel reports.</t>
         </is>
       </c>
     </row>
@@ -31712,17 +31712,17 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>James Conner</t>
+          <t>Xavier Weaver</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -31732,7 +31732,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Conner (foot) didn't take part in Monday's practice, Theo Mackie of The Arizona Republic reports.</t>
+          <t>Weaver (hamstring) was placed on injured reserve by the Cardinals on Monday.</t>
         </is>
       </c>
     </row>
@@ -31744,12 +31744,12 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Carson Beck</t>
+          <t>James Conner</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -31764,7 +31764,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Beck (ribs) continued to be a limited participant at Monday's practice, Bo Brack of GoPHNX.com reports.</t>
+          <t>Conner (foot) didn't take part in Monday's practice, Theo Mackie of The Arizona Republic reports.</t>
         </is>
       </c>
     </row>
@@ -31776,27 +31776,27 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Josh Sweat</t>
+          <t>Carson Beck</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Sweat (knee) was activated from the active/PUP list Monday, Darren Urban of the Cardinals' official site reports.</t>
+          <t>Beck (ribs) continued to be a limited participant at Monday's practice, Bo Brack of GoPHNX.com reports.</t>
         </is>
       </c>
     </row>
@@ -31808,27 +31808,27 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>Josh Sweat</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Sprain</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Coach Mike LaFleur said Monday that Love is progressing in his recovery from a high-ankle sprain but will remain sidelined this week, Darren Urban of the Cardinals' official site reports.</t>
+          <t>Sweat (knee) was activated from the active/PUP list Monday, Darren Urban of the Cardinals' official site reports.</t>
         </is>
       </c>
     </row>
@@ -31840,27 +31840,27 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Chad Ryland</t>
+          <t>Jeremiyah Love</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Sprain</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Ryland made field goals of 38 and 31 yards, missed a 62-yarder wide right and knocked through his only extra-point try in the Cardinals' 34-13 preseason loss to the Cowboys on Saturday.</t>
+          <t>Coach Mike LaFleur said Monday that Love is progressing in his recovery from a high-ankle sprain but will remain sidelined this week, Darren Urban of the Cardinals' official site reports.</t>
         </is>
       </c>
     </row>
@@ -31872,27 +31872,27 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Dadrion Taylor-Demerson</t>
+          <t>Chad Ryland</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Taylor-Demerson is questionable to return to Saturday's preseason game against the Cowboys due to a rib injury.</t>
+          <t>Ryland made field goals of 38 and 31 yards, missed a 62-yarder wide right and knocked through his only extra-point try in the Cardinals' 34-13 preseason loss to the Cowboys on Saturday.</t>
         </is>
       </c>
     </row>
@@ -31904,12 +31904,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Blake Gillikin</t>
+          <t>Dadrion Taylor-Demerson</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -31924,7 +31924,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Gillikin sustained a groin injury during pregame warmups and is questionable to play in Saturday's preseason game against the Cowboys, Darren Urban of the Cardinals' official site reports.</t>
+          <t>Taylor-Demerson is questionable to return to Saturday's preseason game against the Cowboys due to a rib injury.</t>
         </is>
       </c>
     </row>
@@ -31936,17 +31936,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Tip Reiman</t>
+          <t>Blake Gillikin</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Out</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -31956,7 +31956,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Reiman (ankle) will not be back for the start of the regular season, Darren Urban of the Cardinals' official site reports.</t>
+          <t>Gillikin sustained a groin injury during pregame warmups and is questionable to play in Saturday's preseason game against the Cowboys, Darren Urban of the Cardinals' official site reports.</t>
         </is>
       </c>
     </row>
@@ -31968,27 +31968,27 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Garrett Williams</t>
+          <t>Tip Reiman</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Williams (Achilles) was activated from the PUP list by the Cardinals on Thursday, Darren Urban of the Cardinals' official site reports.</t>
+          <t>Reiman (ankle) will not be back for the start of the regular season, Darren Urban of the Cardinals' official site reports.</t>
         </is>
       </c>
     </row>
@@ -32000,12 +32000,12 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Jacoby Brissett</t>
+          <t>Garrett Williams</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -32020,7 +32020,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Coach Mike LaFleur said Thursday that Brissett won't suit up for Saturday's preseason game against the Cowboys, Josh Weinfuss of ESPN.com reports.</t>
+          <t>Williams (Achilles) was activated from the PUP list by the Cardinals on Thursday, Darren Urban of the Cardinals' official site reports.</t>
         </is>
       </c>
     </row>
@@ -32032,27 +32032,27 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Elijah Higgins</t>
+          <t>Jacoby Brissett</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Concussion</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>Coach Mike LaFleur said Thursday that Brissett won't suit up for Saturday's preseason game against the Cowboys, Josh Weinfuss of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -32064,25 +32064,29 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Valentin Senn</t>
+          <t>Elijah Higgins</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>OT</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr"/>
+          <t>Concussion</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>questionable</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -32092,29 +32096,25 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Chase Bisontis</t>
+          <t>Valentin Senn</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>OT</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Surgery</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>ir</t>
-        </is>
-      </c>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -32124,12 +32124,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Joey Blount</t>
+          <t>Chase Bisontis</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -32139,7 +32139,7 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Stinger</t>
+          <t>Surgery</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -32156,27 +32156,27 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Zachary Carter</t>
+          <t>Joey Blount</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Stinger</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>ir</t>
         </is>
       </c>
     </row>
@@ -32188,17 +32188,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Jameson Geers</t>
+          <t>Zachary Carter</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -32208,7 +32208,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>ir</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -32220,27 +32220,27 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Tyler Allgeier</t>
+          <t>Jameson Geers</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Allgeier could open the regular season as the Cardinals' primary running back, as Adam Schefter of ESPN reports that Jeremiyah Love sustained a high-ankle sprain in Thursday's preseason win over the Raiders.</t>
+          <t>ir</t>
         </is>
       </c>
     </row>
@@ -32252,7 +32252,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Tre Stewart</t>
+          <t>Tyler Allgeier</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -32272,7 +32272,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>The Cardinals signed Stewart to a contract Saturday.</t>
+          <t>Allgeier could open the regular season as the Cardinals' primary running back, as Adam Schefter of ESPN reports that Jeremiyah Love sustained a high-ankle sprain in Thursday's preseason win over the Raiders.</t>
         </is>
       </c>
     </row>
@@ -32284,12 +32284,12 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Trey McBride</t>
+          <t>Tre Stewart</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -32304,7 +32304,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>McBride played one snap in Thursday's 27-14 preseason win over the Raiders.</t>
+          <t>The Cardinals signed Stewart to a contract Saturday.</t>
         </is>
       </c>
     </row>
@@ -32316,12 +32316,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr.</t>
+          <t>Trey McBride</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -32336,7 +32336,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>Harrison brought in his only target for seven yards and a touchdown and also drew a 20-yard pass interference penalty in the Cardinals' 27-14 preseason win over the Raiders on Thursday.</t>
+          <t>McBride played one snap in Thursday's 27-14 preseason win over the Raiders.</t>
         </is>
       </c>
     </row>
@@ -32348,7 +32348,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -32368,7 +32368,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Wilson brought in both targets for 23 yards in the Cardinals' 27-14 preseason win over the Raiders on Thursday.</t>
+          <t>Harrison brought in his only target for seven yards and a touchdown and also drew a 20-yard pass interference penalty in the Cardinals' 27-14 preseason win over the Raiders on Thursday.</t>
         </is>
       </c>
     </row>
@@ -32380,12 +32380,12 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Shawn Bowman</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -32400,7 +32400,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>The Cardinals signed Bowman to a contract Sunday, Zach Gershman of the team's official site reports.</t>
+          <t>Wilson brought in both targets for 23 yards in the Cardinals' 27-14 preseason win over the Raiders on Thursday.</t>
         </is>
       </c>
     </row>
@@ -32412,12 +32412,12 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Karson Sharar</t>
+          <t>Shawn Bowman</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -32432,7 +32432,7 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Sharar (hamstring) recorded four tackles (one solo) during the Cardinals' 33-30 loss to the Panthers in Thursday's Hall of Fame Game.</t>
+          <t>The Cardinals signed Bowman to a contract Sunday, Zach Gershman of the team's official site reports.</t>
         </is>
       </c>
     </row>
@@ -38000,27 +38000,27 @@
       </c>
       <c r="B206" s="5" t="inlineStr">
         <is>
-          <t>DJ Rogers</t>
+          <t>Kelvin Gilliam Jr.</t>
         </is>
       </c>
       <c r="C206" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="D206" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E206" s="5" t="inlineStr">
         <is>
-          <t>Knee</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F206" s="5" t="inlineStr">
         <is>
-          <t>Rogers (knee) did not participate in Tuesday's practice session, Calvin Watkins of The Dallas Morning News reports.</t>
+          <t>Gilliam (triceps) reverted to Dallas' injured reserve Tuesday, Tommy Yarrish of the team's official site reports.</t>
         </is>
       </c>
     </row>
@@ -38032,7 +38032,7 @@
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>Mitch Van Vooren</t>
+          <t>DJ Rogers</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
@@ -38042,17 +38042,17 @@
       </c>
       <c r="D207" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E207" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Knee</t>
         </is>
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>Van Vooren signed with the Cowboys on Monday, Nick Harris of the Fort Worth Star-Telegram reports.</t>
+          <t>Rogers (knee) did not participate in Tuesday's practice session, Calvin Watkins of The Dallas Morning News reports.</t>
         </is>
       </c>
     </row>
@@ -38064,12 +38064,12 @@
       </c>
       <c r="B208" s="5" t="inlineStr">
         <is>
-          <t>Joe Milton III</t>
+          <t>Mitch Van Vooren</t>
         </is>
       </c>
       <c r="C208" s="5" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D208" s="5" t="inlineStr">
@@ -38084,7 +38084,7 @@
       </c>
       <c r="F208" s="5" t="inlineStr">
         <is>
-          <t>Milton completed nine of 13 passes for 179 yards with two touchdowns and no interceptions and rushed three times for two yards and another score in the Cowboys' 34-13 preseason win over the Cardinals on Saturday.</t>
+          <t>Van Vooren signed with the Cowboys on Monday, Nick Harris of the Fort Worth Star-Telegram reports.</t>
         </is>
       </c>
     </row>
@@ -38096,12 +38096,12 @@
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>Jaydon Blue</t>
+          <t>Joe Milton III</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D209" s="4" t="inlineStr">
@@ -38116,7 +38116,7 @@
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>Blue (shoulder) rushed 15 times for 75 yards in the Cowboys' 34-13 preseason win over the Cardinals on Saturday. He also returned one kickoff for 26 yards.</t>
+          <t>Milton completed nine of 13 passes for 179 yards with two touchdowns and no interceptions and rushed three times for two yards and another score in the Cowboys' 34-13 preseason win over the Cardinals on Saturday.</t>
         </is>
       </c>
     </row>
@@ -38128,7 +38128,7 @@
       </c>
       <c r="B210" s="5" t="inlineStr">
         <is>
-          <t>Malik Davis</t>
+          <t>Jaydon Blue</t>
         </is>
       </c>
       <c r="C210" s="5" t="inlineStr">
@@ -38148,7 +38148,7 @@
       </c>
       <c r="F210" s="5" t="inlineStr">
         <is>
-          <t>Davis rushed five times for 29 yards and brought in his only target for an eight-yard touchdown in the Cowboys' 34-13 preseason win over the Cardinals on Saturday. He also committed a fumble but recovered and ran back one kickoff for 31 yards.</t>
+          <t>Blue (shoulder) rushed 15 times for 75 yards in the Cowboys' 34-13 preseason win over the Cardinals on Saturday. He also returned one kickoff for 26 yards.</t>
         </is>
       </c>
     </row>
@@ -38160,27 +38160,27 @@
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>Julius Wood</t>
+          <t>Malik Davis</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D211" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E211" s="4" t="inlineStr">
         <is>
-          <t>Concussion</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F211" s="4" t="inlineStr">
         <is>
-          <t>Wood has entered the league's concussion protocol and has been ruled out for the rest of Saturday's preseason game against the Cardinals, Patrik Walker of the Cowboys' official site reports.</t>
+          <t>Davis rushed five times for 29 yards and brought in his only target for an eight-yard touchdown in the Cowboys' 34-13 preseason win over the Cardinals on Saturday. He also committed a fumble but recovered and ran back one kickoff for 31 yards.</t>
         </is>
       </c>
     </row>
@@ -38192,12 +38192,12 @@
       </c>
       <c r="B212" s="5" t="inlineStr">
         <is>
-          <t>Zion Childress</t>
+          <t>Julius Wood</t>
         </is>
       </c>
       <c r="C212" s="5" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D212" s="5" t="inlineStr">
@@ -38207,12 +38207,12 @@
       </c>
       <c r="E212" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Concussion</t>
         </is>
       </c>
       <c r="F212" s="5" t="inlineStr">
         <is>
-          <t>Childress (hamstring) returned to practice as a limited participant Thursday, Calvin Watkins of The Dallas Morning News reports.</t>
+          <t>Wood has entered the league's concussion protocol and has been ruled out for the rest of Saturday's preseason game against the Cardinals, Patrik Walker of the Cowboys' official site reports.</t>
         </is>
       </c>
     </row>
@@ -38224,12 +38224,12 @@
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>Michael Trigg</t>
+          <t>Zion Childress</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D213" s="4" t="inlineStr">
@@ -38244,7 +38244,7 @@
       </c>
       <c r="F213" s="4" t="inlineStr">
         <is>
-          <t>Trigg (toe) did not practice Thursday, Tommy Yarrish of the Cowboys' official site reports.</t>
+          <t>Childress (hamstring) returned to practice as a limited participant Thursday, Calvin Watkins of The Dallas Morning News reports.</t>
         </is>
       </c>
     </row>
@@ -38256,12 +38256,12 @@
       </c>
       <c r="B214" s="5" t="inlineStr">
         <is>
-          <t>Tyler Guyton</t>
+          <t>Michael Trigg</t>
         </is>
       </c>
       <c r="C214" s="5" t="inlineStr">
         <is>
-          <t>OT</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D214" s="5" t="inlineStr">
@@ -38271,12 +38271,12 @@
       </c>
       <c r="E214" s="5" t="inlineStr">
         <is>
-          <t>Soreness</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F214" s="5" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>Trigg (toe) did not practice Thursday, Tommy Yarrish of the Cowboys' official site reports.</t>
         </is>
       </c>
     </row>
@@ -38288,25 +38288,29 @@
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>Jalen Thompson</t>
+          <t>Tyler Guyton</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>OT</t>
         </is>
       </c>
       <c r="D215" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E215" s="4" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="F215" s="4" t="inlineStr"/>
+          <t>Soreness</t>
+        </is>
+      </c>
+      <c r="F215" s="4" t="inlineStr">
+        <is>
+          <t>questionable</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="5" t="inlineStr">
@@ -38316,29 +38320,25 @@
       </c>
       <c r="B216" s="5" t="inlineStr">
         <is>
-          <t>Jonathan Bullard</t>
+          <t>Jalen Thompson</t>
         </is>
       </c>
       <c r="C216" s="5" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D216" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E216" s="5" t="inlineStr">
         <is>
-          <t>Soreness</t>
-        </is>
-      </c>
-      <c r="F216" s="5" t="inlineStr">
-        <is>
-          <t>questionable</t>
-        </is>
-      </c>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F216" s="5" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
@@ -38348,27 +38348,27 @@
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>Princeton Fant</t>
+          <t>Jonathan Bullard</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="D217" s="4" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E217" s="4" t="inlineStr">
         <is>
-          <t>Surgery</t>
+          <t>Soreness</t>
         </is>
       </c>
       <c r="F217" s="4" t="inlineStr">
         <is>
-          <t>ir</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -38380,25 +38380,29 @@
       </c>
       <c r="B218" s="5" t="inlineStr">
         <is>
-          <t>Ajani Cornelius</t>
+          <t>Princeton Fant</t>
         </is>
       </c>
       <c r="C218" s="5" t="inlineStr">
         <is>
-          <t>OT</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D218" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E218" s="5" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="F218" s="5" t="inlineStr"/>
+          <t>Surgery</t>
+        </is>
+      </c>
+      <c r="F218" s="5" t="inlineStr">
+        <is>
+          <t>ir</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
@@ -38408,12 +38412,12 @@
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>P.J. Locke</t>
+          <t>Ajani Cornelius</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>OT</t>
         </is>
       </c>
       <c r="D219" s="4" t="inlineStr">
@@ -38436,12 +38440,12 @@
       </c>
       <c r="B220" s="5" t="inlineStr">
         <is>
-          <t>James Houston</t>
+          <t>P.J. Locke</t>
         </is>
       </c>
       <c r="C220" s="5" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D220" s="5" t="inlineStr">
@@ -38464,7 +38468,7 @@
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>DeMarvion Overshown</t>
+          <t>James Houston</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
@@ -38482,11 +38486,7 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F221" s="4" t="inlineStr">
-        <is>
-          <t>Overshown (lower body) participated at the Cowboys' training camp practice Monday, Todd Archer of ESPN.com reports.</t>
-        </is>
-      </c>
+      <c r="F221" s="4" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="5" t="inlineStr">
@@ -38496,7 +38496,7 @@
       </c>
       <c r="B222" s="5" t="inlineStr">
         <is>
-          <t>Jaishawn Barham</t>
+          <t>DeMarvion Overshown</t>
         </is>
       </c>
       <c r="C222" s="5" t="inlineStr">
@@ -38516,7 +38516,7 @@
       </c>
       <c r="F222" s="5" t="inlineStr">
         <is>
-          <t>Barham (groin) returned to practice Monday, Todd Archer of ESPN.com reports.</t>
+          <t>Overshown (lower body) participated at the Cowboys' training camp practice Monday, Todd Archer of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -38528,7 +38528,7 @@
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>Von Miller</t>
+          <t>Jaishawn Barham</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
@@ -38548,7 +38548,7 @@
       </c>
       <c r="F223" s="4" t="inlineStr">
         <is>
-          <t>Miller is not expected to practice with the Cowboys this week, Calvin Watkins of The Dallas Morning News reports.</t>
+          <t>Barham (groin) returned to practice Monday, Todd Archer of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -38560,12 +38560,12 @@
       </c>
       <c r="B224" s="5" t="inlineStr">
         <is>
-          <t>Alijah Clark</t>
+          <t>Von Miller</t>
         </is>
       </c>
       <c r="C224" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D224" s="5" t="inlineStr">
@@ -38580,7 +38580,7 @@
       </c>
       <c r="F224" s="5" t="inlineStr">
         <is>
-          <t>Clark (ankle) recorded one tackle in the Cowboys' 17-7 preseason win over the Seahawks on Saturday.</t>
+          <t>Miller is not expected to practice with the Cowboys this week, Calvin Watkins of The Dallas Morning News reports.</t>
         </is>
       </c>
     </row>
@@ -38592,12 +38592,12 @@
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>Camden Brown</t>
+          <t>Alijah Clark</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D225" s="4" t="inlineStr">
@@ -38612,7 +38612,7 @@
       </c>
       <c r="F225" s="4" t="inlineStr">
         <is>
-          <t>Brown caught all three of his targets for 62 yards and two touchdowns during Saturday night's preseason game against the Seahawks.</t>
+          <t>Clark (ankle) recorded one tackle in the Cowboys' 17-7 preseason win over the Seahawks on Saturday.</t>
         </is>
       </c>
     </row>
@@ -38624,7 +38624,7 @@
       </c>
       <c r="B226" s="5" t="inlineStr">
         <is>
-          <t>Anthony Smith</t>
+          <t>Camden Brown</t>
         </is>
       </c>
       <c r="C226" s="5" t="inlineStr">
@@ -38644,7 +38644,7 @@
       </c>
       <c r="F226" s="5" t="inlineStr">
         <is>
-          <t>Smith brought in two of five targets for 28 yards and rushed once for nine yards in the Cowboys' 17-7 preseason win over the Seahawks on Saturday.</t>
+          <t>Brown caught all three of his targets for 62 yards and two touchdowns during Saturday night's preseason game against the Seahawks.</t>
         </is>
       </c>
     </row>
@@ -38656,7 +38656,7 @@
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>Marquez Valdes-Scantling</t>
+          <t>Anthony Smith</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr">
@@ -38676,7 +38676,7 @@
       </c>
       <c r="F227" s="4" t="inlineStr">
         <is>
-          <t>Valdes-Scantling failed to bring in his only target in the Cowboys' 17-7 preseason win over the Seahawks on Saturday.</t>
+          <t>Smith brought in two of five targets for 28 yards and rushed once for nine yards in the Cowboys' 17-7 preseason win over the Seahawks on Saturday.</t>
         </is>
       </c>
     </row>
@@ -38688,12 +38688,12 @@
       </c>
       <c r="B228" s="5" t="inlineStr">
         <is>
-          <t>Brandon Aubrey</t>
+          <t>Marquez Valdes-Scantling</t>
         </is>
       </c>
       <c r="C228" s="5" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D228" s="5" t="inlineStr">
@@ -38708,7 +38708,7 @@
       </c>
       <c r="F228" s="5" t="inlineStr">
         <is>
-          <t>Aubrey made his only field-goal attempt from 29 yards and knocked home both extra-point tries in the Cowboys' 17-7 preseason win over the Seahawks on Saturday.</t>
+          <t>Valdes-Scantling failed to bring in his only target in the Cowboys' 17-7 preseason win over the Seahawks on Saturday.</t>
         </is>
       </c>
     </row>
@@ -38720,12 +38720,12 @@
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>Ryan Flournoy</t>
+          <t>Brandon Aubrey</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="D229" s="4" t="inlineStr">
@@ -38740,7 +38740,7 @@
       </c>
       <c r="F229" s="4" t="inlineStr">
         <is>
-          <t>Flournoy isn't suited up ahead of Saturday's preseason opener versus Seattle, Nick Harris of the Fort Worth Star-Telegram reports.</t>
+          <t>Aubrey made his only field-goal attempt from 29 yards and knocked home both extra-point tries in the Cowboys' 17-7 preseason win over the Seahawks on Saturday.</t>
         </is>
       </c>
     </row>
@@ -45148,7 +45148,7 @@
       </c>
       <c r="F431" s="4" t="inlineStr">
         <is>
-          <t>Chargers offensive coordinator Mike McDaniel  said Monday that there had been "a mild setback" with Mitchell.</t>
+          <t>Chargers offensive coordinator Mike McDaniel  said Monday that there had been "a mild setback" with Mitchell with an undisclosed issue.</t>
         </is>
       </c>
     </row>
@@ -47516,27 +47516,27 @@
       </c>
       <c r="B506" s="5" t="inlineStr">
         <is>
-          <t>Matt Lauter</t>
+          <t>Tyreek Chappell</t>
         </is>
       </c>
       <c r="C506" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D506" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E506" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F506" s="5" t="inlineStr">
         <is>
-          <t>Lauter signed a contract with the Vikings on Monday.</t>
+          <t>Chappell (undisclosed) reverted to the Vikings' injured reserve list Tuesday, per the NFL's transaction log.</t>
         </is>
       </c>
     </row>
@@ -47548,17 +47548,17 @@
       </c>
       <c r="B507" s="4" t="inlineStr">
         <is>
-          <t>J.J. McCarthy</t>
+          <t>Taki Taimani</t>
         </is>
       </c>
       <c r="C507" s="4" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="D507" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E507" s="4" t="inlineStr">
@@ -47568,7 +47568,7 @@
       </c>
       <c r="F507" s="4" t="inlineStr">
         <is>
-          <t>McCarthy (undisclosed) participated in Monday's practice, Kevin Seifert of ESPN.com reports.</t>
+          <t>Taimani (undisclosed) reverted to the Vikings' injured reserve list Tuesday, per the NFL's transaction log.</t>
         </is>
       </c>
     </row>
@@ -47580,12 +47580,12 @@
       </c>
       <c r="B508" s="5" t="inlineStr">
         <is>
-          <t>Will Reichard</t>
+          <t>Matt Lauter</t>
         </is>
       </c>
       <c r="C508" s="5" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D508" s="5" t="inlineStr">
@@ -47600,7 +47600,7 @@
       </c>
       <c r="F508" s="5" t="inlineStr">
         <is>
-          <t>Reichard is a perfect 3-for-3 on field goals through the first two preseason games, with a long of 54 yards.</t>
+          <t>Lauter signed a contract with the Vikings on Monday.</t>
         </is>
       </c>
     </row>
@@ -47612,7 +47612,7 @@
       </c>
       <c r="B509" s="4" t="inlineStr">
         <is>
-          <t>Max Brosmer</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="C509" s="4" t="inlineStr">
@@ -47622,17 +47622,17 @@
       </c>
       <c r="D509" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E509" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F509" s="4" t="inlineStr">
         <is>
-          <t>Brosmer completed 11 of 17 passes for 98 yards and an interception while logging a four-yard carry during the Vikings' 13-3 preseason loss to the Ravens on Saturday.</t>
+          <t>McCarthy (undisclosed) participated in Monday's practice, Kevin Seifert of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -47644,12 +47644,12 @@
       </c>
       <c r="B510" s="5" t="inlineStr">
         <is>
-          <t>Carson Wentz</t>
+          <t>Will Reichard</t>
         </is>
       </c>
       <c r="C510" s="5" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="D510" s="5" t="inlineStr">
@@ -47664,7 +47664,7 @@
       </c>
       <c r="F510" s="5" t="inlineStr">
         <is>
-          <t>Wentz completed nine of 11 passes for 92 yards during the Vikings' 13-3 preseason loss to the Ravens on Saturday.</t>
+          <t>Reichard is a perfect 3-for-3 on field goals through the first two preseason games, with a long of 54 yards.</t>
         </is>
       </c>
     </row>
@@ -47676,12 +47676,12 @@
       </c>
       <c r="B511" s="4" t="inlineStr">
         <is>
-          <t>Demond Claiborne</t>
+          <t>Max Brosmer</t>
         </is>
       </c>
       <c r="C511" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D511" s="4" t="inlineStr">
@@ -47696,7 +47696,7 @@
       </c>
       <c r="F511" s="4" t="inlineStr">
         <is>
-          <t>Claiborne turned eight carries into 18 yards and caught his lone target for seven yards during the Vikings' 13-3 loss to the Ravens on Saturday. He also returned one kickoff for 21 yards.</t>
+          <t>Brosmer completed 11 of 17 passes for 98 yards and an interception while logging a four-yard carry during the Vikings' 13-3 preseason loss to the Ravens on Saturday.</t>
         </is>
       </c>
     </row>
@@ -47708,7 +47708,7 @@
       </c>
       <c r="B512" s="5" t="inlineStr">
         <is>
-          <t>Kyler Murray</t>
+          <t>Carson Wentz</t>
         </is>
       </c>
       <c r="C512" s="5" t="inlineStr">
@@ -47728,7 +47728,7 @@
       </c>
       <c r="F512" s="5" t="inlineStr">
         <is>
-          <t>Murray isn't expected to suit up for Saturday's preseason game against the Ravens, Kevin Seifert of ESPN.com reports.</t>
+          <t>Wentz completed nine of 11 passes for 92 yards during the Vikings' 13-3 preseason loss to the Ravens on Saturday.</t>
         </is>
       </c>
     </row>
@@ -47740,27 +47740,27 @@
       </c>
       <c r="B513" s="4" t="inlineStr">
         <is>
-          <t>Caleb Tiernan</t>
+          <t>Demond Claiborne</t>
         </is>
       </c>
       <c r="C513" s="4" t="inlineStr">
         <is>
-          <t>OT</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D513" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E513" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F513" s="4" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>Claiborne turned eight carries into 18 yards and caught his lone target for seven yards during the Vikings' 13-3 loss to the Ravens on Saturday. He also returned one kickoff for 21 yards.</t>
         </is>
       </c>
     </row>
@@ -47772,27 +47772,27 @@
       </c>
       <c r="B514" s="5" t="inlineStr">
         <is>
-          <t>Jakobe Thomas</t>
+          <t>Kyler Murray</t>
         </is>
       </c>
       <c r="C514" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D514" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E514" s="5" t="inlineStr">
         <is>
-          <t>Soreness</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F514" s="5" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>Murray isn't expected to suit up for Saturday's preseason game against the Ravens, Kevin Seifert of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -47804,17 +47804,17 @@
       </c>
       <c r="B515" s="4" t="inlineStr">
         <is>
-          <t>Jamal Adams</t>
+          <t>Caleb Tiernan</t>
         </is>
       </c>
       <c r="C515" s="4" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>OT</t>
         </is>
       </c>
       <c r="D515" s="4" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E515" s="4" t="inlineStr">
@@ -47824,7 +47824,7 @@
       </c>
       <c r="F515" s="4" t="inlineStr">
         <is>
-          <t>ir</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -47836,25 +47836,29 @@
       </c>
       <c r="B516" s="5" t="inlineStr">
         <is>
-          <t>Gavin Bartholomew</t>
+          <t>Jakobe Thomas</t>
         </is>
       </c>
       <c r="C516" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D516" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E516" s="5" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="F516" s="5" t="inlineStr"/>
+          <t>Soreness</t>
+        </is>
+      </c>
+      <c r="F516" s="5" t="inlineStr">
+        <is>
+          <t>questionable</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" s="4" t="inlineStr">
@@ -47864,25 +47868,29 @@
       </c>
       <c r="B517" s="4" t="inlineStr">
         <is>
-          <t>Joshua Metellus</t>
+          <t>Jamal Adams</t>
         </is>
       </c>
       <c r="C517" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D517" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E517" s="4" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="F517" s="4" t="inlineStr"/>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F517" s="4" t="inlineStr">
+        <is>
+          <t>ir</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" s="5" t="inlineStr">
@@ -47892,12 +47900,12 @@
       </c>
       <c r="B518" s="5" t="inlineStr">
         <is>
-          <t>Elijah Williams</t>
+          <t>Gavin Bartholomew</t>
         </is>
       </c>
       <c r="C518" s="5" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D518" s="5" t="inlineStr">
@@ -47920,7 +47928,7 @@
       </c>
       <c r="B519" s="4" t="inlineStr">
         <is>
-          <t>Jay Ward</t>
+          <t>Joshua Metellus</t>
         </is>
       </c>
       <c r="C519" s="4" t="inlineStr">
@@ -47938,11 +47946,7 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F519" s="4" t="inlineStr">
-        <is>
-          <t>Ward logged two solo tackles during Saturday's preseason opener against the Giants.</t>
-        </is>
-      </c>
+      <c r="F519" s="4" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" s="5" t="inlineStr">
@@ -47952,12 +47956,12 @@
       </c>
       <c r="B520" s="5" t="inlineStr">
         <is>
-          <t>Jauan Jennings</t>
+          <t>Elijah Williams</t>
         </is>
       </c>
       <c r="C520" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D520" s="5" t="inlineStr">
@@ -47970,11 +47974,7 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F520" s="5" t="inlineStr">
-        <is>
-          <t>Jennings played four snaps on offense and didn't show up in the box score otherwise during the Vikings' 13-10 preseason win over the Giants on Saturday.</t>
-        </is>
-      </c>
+      <c r="F520" s="5" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" s="4" t="inlineStr">
@@ -47984,12 +47984,12 @@
       </c>
       <c r="B521" s="4" t="inlineStr">
         <is>
-          <t>T.J. Hockenson</t>
+          <t>Jay Ward</t>
         </is>
       </c>
       <c r="C521" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D521" s="4" t="inlineStr">
@@ -48004,7 +48004,7 @@
       </c>
       <c r="F521" s="4" t="inlineStr">
         <is>
-          <t>Hockenson played five snaps on offense and didn't show up in the box score otherwise during the Vikings' 13-10 preseason win over the Giants on Saturday.</t>
+          <t>Ward logged two solo tackles during Saturday's preseason opener against the Giants.</t>
         </is>
       </c>
     </row>
@@ -48016,7 +48016,7 @@
       </c>
       <c r="B522" s="5" t="inlineStr">
         <is>
-          <t>Jordan Addison</t>
+          <t>Jauan Jennings</t>
         </is>
       </c>
       <c r="C522" s="5" t="inlineStr">
@@ -48036,7 +48036,7 @@
       </c>
       <c r="F522" s="5" t="inlineStr">
         <is>
-          <t>Addison (thumb) caught his only target for eight yards in Saturday's 13-10 preseason win over the Giants.</t>
+          <t>Jennings played four snaps on offense and didn't show up in the box score otherwise during the Vikings' 13-10 preseason win over the Giants on Saturday.</t>
         </is>
       </c>
     </row>
@@ -48048,12 +48048,12 @@
       </c>
       <c r="B523" s="4" t="inlineStr">
         <is>
-          <t>Jordan Mason</t>
+          <t>T.J. Hockenson</t>
         </is>
       </c>
       <c r="C523" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D523" s="4" t="inlineStr">
@@ -48068,7 +48068,7 @@
       </c>
       <c r="F523" s="4" t="inlineStr">
         <is>
-          <t>Mason carried the ball three times for 17 yards in Saturday's 13-10 preseason win over the Giants.</t>
+          <t>Hockenson played five snaps on offense and didn't show up in the box score otherwise during the Vikings' 13-10 preseason win over the Giants on Saturday.</t>
         </is>
       </c>
     </row>
@@ -48080,12 +48080,12 @@
       </c>
       <c r="B524" s="5" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr.</t>
+          <t>Jordan Addison</t>
         </is>
       </c>
       <c r="C524" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D524" s="5" t="inlineStr">
@@ -48100,7 +48100,7 @@
       </c>
       <c r="F524" s="5" t="inlineStr">
         <is>
-          <t>Jones carried the ball three times for 27 yards in Saturday's 13-10 preseason win over the Giants. He failed to catch his only target.</t>
+          <t>Addison (thumb) caught his only target for eight yards in Saturday's 13-10 preseason win over the Giants.</t>
         </is>
       </c>
     </row>
@@ -48112,12 +48112,12 @@
       </c>
       <c r="B525" s="4" t="inlineStr">
         <is>
-          <t>Justin Jefferson</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="C525" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D525" s="4" t="inlineStr">
@@ -48132,7 +48132,7 @@
       </c>
       <c r="F525" s="4" t="inlineStr">
         <is>
-          <t>Jefferson and newly named starting quarterback Kyler Murray have been starting to click at practice, Will Ragatz of Bring Me The Sports reports.</t>
+          <t>Mason carried the ball three times for 17 yards in Saturday's 13-10 preseason win over the Giants.</t>
         </is>
       </c>
     </row>
@@ -48144,7 +48144,7 @@
       </c>
       <c r="B526" s="5" t="inlineStr">
         <is>
-          <t>Jermar Jefferson</t>
+          <t>Aaron Jones Sr.</t>
         </is>
       </c>
       <c r="C526" s="5" t="inlineStr">
@@ -48164,7 +48164,7 @@
       </c>
       <c r="F526" s="5" t="inlineStr">
         <is>
-          <t>The Vikings signed Jefferson on Wednesday.</t>
+          <t>Jones carried the ball three times for 27 yards in Saturday's 13-10 preseason win over the Giants. He failed to catch his only target.</t>
         </is>
       </c>
     </row>
@@ -48176,12 +48176,12 @@
       </c>
       <c r="B527" s="4" t="inlineStr">
         <is>
-          <t>Josh Oliver</t>
+          <t>Justin Jefferson</t>
         </is>
       </c>
       <c r="C527" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D527" s="4" t="inlineStr">
@@ -48196,7 +48196,7 @@
       </c>
       <c r="F527" s="4" t="inlineStr">
         <is>
-          <t>Oliver was participating in the Vikings' training camp activities Saturday.</t>
+          <t>Jefferson and newly named starting quarterback Kyler Murray have been starting to click at practice, Will Ragatz of Bring Me The Sports reports.</t>
         </is>
       </c>
     </row>
@@ -48208,12 +48208,12 @@
       </c>
       <c r="B528" s="5" t="inlineStr">
         <is>
-          <t>Caleb Banks</t>
+          <t>Jermar Jefferson</t>
         </is>
       </c>
       <c r="C528" s="5" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D528" s="5" t="inlineStr">
@@ -48228,7 +48228,7 @@
       </c>
       <c r="F528" s="5" t="inlineStr">
         <is>
-          <t>Banks (foot) is participating at the Vikings' training camp, Jason Harmon of Sports Illustrated reports.</t>
+          <t>The Vikings signed Jefferson on Wednesday.</t>
         </is>
       </c>
     </row>
@@ -48240,12 +48240,12 @@
       </c>
       <c r="B529" s="4" t="inlineStr">
         <is>
-          <t>Christian Darrisaw</t>
+          <t>Josh Oliver</t>
         </is>
       </c>
       <c r="C529" s="4" t="inlineStr">
         <is>
-          <t>OT</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D529" s="4" t="inlineStr">
@@ -48258,7 +48258,11 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F529" s="4" t="inlineStr"/>
+      <c r="F529" s="4" t="inlineStr">
+        <is>
+          <t>Oliver was participating in the Vikings' training camp activities Saturday.</t>
+        </is>
+      </c>
     </row>
     <row r="530">
       <c r="A530" s="5" t="inlineStr">
@@ -50652,12 +50656,12 @@
       </c>
       <c r="B605" s="4" t="inlineStr">
         <is>
-          <t>Sam Scott</t>
+          <t>Kenyon Sadiq</t>
         </is>
       </c>
       <c r="C605" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D605" s="4" t="inlineStr">
@@ -50667,12 +50671,12 @@
       </c>
       <c r="E605" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Surgery</t>
         </is>
       </c>
       <c r="F605" s="4" t="inlineStr">
         <is>
-          <t>The Jets waived Scott (undisclosed) with an injury settlement Tuesday.</t>
+          <t>Jets offensive coordinator Frank Reich said Tuesday that Sadiq (hernia) will be worked in slowly at the start of the regular season, Zack Rosenblatt of The Athletic reports.</t>
         </is>
       </c>
     </row>
@@ -50684,12 +50688,12 @@
       </c>
       <c r="B606" s="5" t="inlineStr">
         <is>
-          <t>Kenyon Sadiq</t>
+          <t>Isaiah Davis</t>
         </is>
       </c>
       <c r="C606" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D606" s="5" t="inlineStr">
@@ -50699,12 +50703,12 @@
       </c>
       <c r="E606" s="5" t="inlineStr">
         <is>
-          <t>Surgery</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F606" s="5" t="inlineStr">
         <is>
-          <t>Jets offensive coordinator Frank Reich said Tuesday that Sadiq (hernia) will be worked in slowly at the start of the regular season, Zack Rosenblatt of The Athletic reports.</t>
+          <t>Davis (knee) worked out on a side field with a trainer during Tuesday's practice, Zack Rosenblatt of The Athletic reports.</t>
         </is>
       </c>
     </row>
@@ -50716,27 +50720,27 @@
       </c>
       <c r="B607" s="4" t="inlineStr">
         <is>
-          <t>Isaiah Davis</t>
+          <t>Jason Sanders</t>
         </is>
       </c>
       <c r="C607" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="D607" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E607" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F607" s="4" t="inlineStr">
         <is>
-          <t>Davis (knee) worked out on a side field with a trainer during Tuesday's practice, Zack Rosenblatt of The Athletic reports.</t>
+          <t>Sanders appears to be the frontrunner to open the season as the Jets' kicker after Cade York was waived Tuesday, Ryan Dunleavy of the New York Post reports.</t>
         </is>
       </c>
     </row>
@@ -50748,27 +50752,27 @@
       </c>
       <c r="B608" s="5" t="inlineStr">
         <is>
-          <t>Jason Sanders</t>
+          <t>Nathan Voorhis</t>
         </is>
       </c>
       <c r="C608" s="5" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D608" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E608" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F608" s="5" t="inlineStr">
         <is>
-          <t>Sanders appears to be the frontrunner to open the season as the Jets' kicker after Cade York was waived Tuesday, Ryan Dunleavy of the New York Post reports.</t>
+          <t>Voorhis (undisclosed) reverted to injured reserve with the Jets on Monday, Aaron Wilson of KPRC 2 Houston reports.</t>
         </is>
       </c>
     </row>
@@ -50780,12 +50784,12 @@
       </c>
       <c r="B609" s="4" t="inlineStr">
         <is>
-          <t>Nathan Voorhis</t>
+          <t>Caullin Lacy</t>
         </is>
       </c>
       <c r="C609" s="4" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D609" s="4" t="inlineStr">
@@ -50800,7 +50804,7 @@
       </c>
       <c r="F609" s="4" t="inlineStr">
         <is>
-          <t>Voorhis (undisclosed) reverted to injured reserve with the Jets on Monday, Aaron Wilson of KPRC 2 Houston reports.</t>
+          <t>Lacy (undisclosed) reverted to the Jets' injured reserve Monday, Aaron Wilson of KPRC 2 Houston reports.</t>
         </is>
       </c>
     </row>
@@ -50812,27 +50816,27 @@
       </c>
       <c r="B610" s="5" t="inlineStr">
         <is>
-          <t>Caullin Lacy</t>
+          <t>Breece Hall</t>
         </is>
       </c>
       <c r="C610" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D610" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E610" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Strain</t>
         </is>
       </c>
       <c r="F610" s="5" t="inlineStr">
         <is>
-          <t>Lacy (undisclosed) reverted to the Jets' injured reserve Monday, Aaron Wilson of KPRC 2 Houston reports.</t>
+          <t>Hall (groin) took part in agility drills on the side at Monday's practice, Brian Costello of the New York Post reports.</t>
         </is>
       </c>
     </row>
@@ -50844,7 +50848,7 @@
       </c>
       <c r="B611" s="4" t="inlineStr">
         <is>
-          <t>Breece Hall</t>
+          <t>Dominic Richardson</t>
         </is>
       </c>
       <c r="C611" s="4" t="inlineStr">
@@ -50854,17 +50858,17 @@
       </c>
       <c r="D611" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E611" s="4" t="inlineStr">
         <is>
-          <t>Strain</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F611" s="4" t="inlineStr">
         <is>
-          <t>Hall (groin) took part in agility drills on the side at Monday's practice, Brian Costello of the New York Post reports.</t>
+          <t>The Jets signed Richardson to a contract Sunday.</t>
         </is>
       </c>
     </row>
@@ -50876,12 +50880,12 @@
       </c>
       <c r="B612" s="5" t="inlineStr">
         <is>
-          <t>Dominic Richardson</t>
+          <t>Cade Klubnik</t>
         </is>
       </c>
       <c r="C612" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D612" s="5" t="inlineStr">
@@ -50896,7 +50900,7 @@
       </c>
       <c r="F612" s="5" t="inlineStr">
         <is>
-          <t>The Jets signed Richardson to a contract Sunday.</t>
+          <t>Klubnik completed 10 of 14 passes for 75 yards and recorded a 16-yard carry during the Jets' 17-0 preseason win over the Steelers on Friday.</t>
         </is>
       </c>
     </row>
@@ -50908,12 +50912,12 @@
       </c>
       <c r="B613" s="4" t="inlineStr">
         <is>
-          <t>Cade Klubnik</t>
+          <t>Mason Taylor</t>
         </is>
       </c>
       <c r="C613" s="4" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D613" s="4" t="inlineStr">
@@ -50928,7 +50932,7 @@
       </c>
       <c r="F613" s="4" t="inlineStr">
         <is>
-          <t>Klubnik completed 10 of 14 passes for 75 yards and recorded a 16-yard carry during the Jets' 17-0 preseason win over the Steelers on Friday.</t>
+          <t>Taylor caught his only target for 10 yards in Friday's 17-0 preseason win over the Steelers.</t>
         </is>
       </c>
     </row>
@@ -50940,12 +50944,12 @@
       </c>
       <c r="B614" s="5" t="inlineStr">
         <is>
-          <t>Mason Taylor</t>
+          <t>Adonai Mitchell</t>
         </is>
       </c>
       <c r="C614" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D614" s="5" t="inlineStr">
@@ -50960,7 +50964,7 @@
       </c>
       <c r="F614" s="5" t="inlineStr">
         <is>
-          <t>Taylor caught his only target for 10 yards in Friday's 17-0 preseason win over the Steelers.</t>
+          <t>Mitchell caught both of his targets for 29 yards in Friday's 17-0 preseason win over the Steelers.</t>
         </is>
       </c>
     </row>
@@ -50972,12 +50976,12 @@
       </c>
       <c r="B615" s="4" t="inlineStr">
         <is>
-          <t>Adonai Mitchell</t>
+          <t>Braelon Allen</t>
         </is>
       </c>
       <c r="C615" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D615" s="4" t="inlineStr">
@@ -50992,7 +50996,7 @@
       </c>
       <c r="F615" s="4" t="inlineStr">
         <is>
-          <t>Mitchell caught both of his targets for 29 yards in Friday's 17-0 preseason win over the Steelers.</t>
+          <t>Allen rushed three times for four yards and caught his lone target for five yards in Friday's 17-0 preseason win over the Steelers.</t>
         </is>
       </c>
     </row>
@@ -51004,12 +51008,12 @@
       </c>
       <c r="B616" s="5" t="inlineStr">
         <is>
-          <t>Braelon Allen</t>
+          <t>Omar Cooper Jr.</t>
         </is>
       </c>
       <c r="C616" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D616" s="5" t="inlineStr">
@@ -51024,7 +51028,7 @@
       </c>
       <c r="F616" s="5" t="inlineStr">
         <is>
-          <t>Allen rushed three times for four yards and caught his lone target for five yards in Friday's 17-0 preseason win over the Steelers.</t>
+          <t>Cooper caught his only target for nine yards in Friday's 17-0 preseason win over the Steelers.</t>
         </is>
       </c>
     </row>
@@ -51036,12 +51040,12 @@
       </c>
       <c r="B617" s="4" t="inlineStr">
         <is>
-          <t>Omar Cooper Jr.</t>
+          <t>Geno Smith</t>
         </is>
       </c>
       <c r="C617" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D617" s="4" t="inlineStr">
@@ -51056,7 +51060,7 @@
       </c>
       <c r="F617" s="4" t="inlineStr">
         <is>
-          <t>Cooper caught his only target for nine yards in Friday's 17-0 preseason win over the Steelers.</t>
+          <t>Smith completed all seven of his pass attempts for 65 yards and a touchdown in Friday's 17-0 preseason win over the Steelers.</t>
         </is>
       </c>
     </row>
@@ -51068,12 +51072,12 @@
       </c>
       <c r="B618" s="5" t="inlineStr">
         <is>
-          <t>Geno Smith</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="C618" s="5" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D618" s="5" t="inlineStr">
@@ -51088,7 +51092,7 @@
       </c>
       <c r="F618" s="5" t="inlineStr">
         <is>
-          <t>Smith completed all seven of his pass attempts for 65 yards and a touchdown in Friday's 17-0 preseason win over the Steelers.</t>
+          <t>Wilson caught his only target for 10 yards in Friday's 17-0 preseason win over the Steelers.</t>
         </is>
       </c>
     </row>
@@ -51100,27 +51104,27 @@
       </c>
       <c r="B619" s="4" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>Chase Curtis</t>
         </is>
       </c>
       <c r="C619" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D619" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E619" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F619" s="4" t="inlineStr">
         <is>
-          <t>Wilson caught his only target for 10 yards in Friday's 17-0 preseason win over the Steelers.</t>
+          <t>Curtis (knee) is out for the remainder of Friday's preseason contest at Pittsburgh.</t>
         </is>
       </c>
     </row>
@@ -51132,27 +51136,27 @@
       </c>
       <c r="B620" s="5" t="inlineStr">
         <is>
-          <t>Chase Curtis</t>
+          <t>Kingsley Jonathan</t>
         </is>
       </c>
       <c r="C620" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D620" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E620" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Bruise</t>
         </is>
       </c>
       <c r="F620" s="5" t="inlineStr">
         <is>
-          <t>Curtis (knee) is out for the remainder of Friday's preseason contest at Pittsburgh.</t>
+          <t>Jonathan (thigh) reverted to the Jets' injured reserve Wednesday, Aaron Wilson of KPRC 2 Houston reports.</t>
         </is>
       </c>
     </row>
@@ -51164,27 +51168,27 @@
       </c>
       <c r="B621" s="4" t="inlineStr">
         <is>
-          <t>Kingsley Jonathan</t>
+          <t>Qwan'tez Stiggers</t>
         </is>
       </c>
       <c r="C621" s="4" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D621" s="4" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E621" s="4" t="inlineStr">
         <is>
-          <t>Bruise</t>
+          <t>Concussion</t>
         </is>
       </c>
       <c r="F621" s="4" t="inlineStr">
         <is>
-          <t>Jonathan (thigh) reverted to the Jets' injured reserve Wednesday, Aaron Wilson of KPRC 2 Houston reports.</t>
+          <t>Stiggers (concussion) was a limited participant in Wednesday's practice, Rich Cimini of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -51196,27 +51200,27 @@
       </c>
       <c r="B622" s="5" t="inlineStr">
         <is>
-          <t>Qwan'tez Stiggers</t>
+          <t>Junior Bergen</t>
         </is>
       </c>
       <c r="C622" s="5" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D622" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E622" s="5" t="inlineStr">
         <is>
-          <t>Concussion</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F622" s="5" t="inlineStr">
         <is>
-          <t>Stiggers (concussion) was a limited participant in Wednesday's practice, Rich Cimini of ESPN.com reports.</t>
+          <t>The Jets signed Bergen to a contract Wednesday, Eric Allen of the team's official site reports.</t>
         </is>
       </c>
     </row>
@@ -51228,27 +51232,27 @@
       </c>
       <c r="B623" s="4" t="inlineStr">
         <is>
-          <t>Junior Bergen</t>
+          <t>Nahshon Wright</t>
         </is>
       </c>
       <c r="C623" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D623" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E623" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Strain</t>
         </is>
       </c>
       <c r="F623" s="4" t="inlineStr">
         <is>
-          <t>The Jets signed Bergen to a contract Wednesday, Eric Allen of the team's official site reports.</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -51260,12 +51264,12 @@
       </c>
       <c r="B624" s="5" t="inlineStr">
         <is>
-          <t>Nahshon Wright</t>
+          <t>VJ Payne</t>
         </is>
       </c>
       <c r="C624" s="5" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D624" s="5" t="inlineStr">
@@ -51275,7 +51279,7 @@
       </c>
       <c r="E624" s="5" t="inlineStr">
         <is>
-          <t>Strain</t>
+          <t>Bruise</t>
         </is>
       </c>
       <c r="F624" s="5" t="inlineStr">
@@ -51292,12 +51296,12 @@
       </c>
       <c r="B625" s="4" t="inlineStr">
         <is>
-          <t>VJ Payne</t>
+          <t>Mory Bamba</t>
         </is>
       </c>
       <c r="C625" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D625" s="4" t="inlineStr">
@@ -51307,7 +51311,7 @@
       </c>
       <c r="E625" s="4" t="inlineStr">
         <is>
-          <t>Bruise</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F625" s="4" t="inlineStr">
@@ -51324,29 +51328,25 @@
       </c>
       <c r="B626" s="5" t="inlineStr">
         <is>
-          <t>Mory Bamba</t>
+          <t>Joseph Ossai</t>
         </is>
       </c>
       <c r="C626" s="5" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D626" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E626" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="F626" s="5" t="inlineStr">
-        <is>
-          <t>questionable</t>
-        </is>
-      </c>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F626" s="5" t="inlineStr"/>
     </row>
     <row r="627">
       <c r="A627" s="4" t="inlineStr">
@@ -51356,12 +51356,12 @@
       </c>
       <c r="B627" s="4" t="inlineStr">
         <is>
-          <t>Joseph Ossai</t>
+          <t>Kiko Mauigoa</t>
         </is>
       </c>
       <c r="C627" s="4" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D627" s="4" t="inlineStr">
@@ -51384,12 +51384,12 @@
       </c>
       <c r="B628" s="5" t="inlineStr">
         <is>
-          <t>Kiko Mauigoa</t>
+          <t>T'Vondre Sweat</t>
         </is>
       </c>
       <c r="C628" s="5" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="D628" s="5" t="inlineStr">
@@ -51412,12 +51412,12 @@
       </c>
       <c r="B629" s="4" t="inlineStr">
         <is>
-          <t>T'Vondre Sweat</t>
+          <t>Andre Cisco</t>
         </is>
       </c>
       <c r="C629" s="4" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D629" s="4" t="inlineStr">
@@ -51440,17 +51440,17 @@
       </c>
       <c r="B630" s="5" t="inlineStr">
         <is>
-          <t>Markel Bell</t>
+          <t>Ja'Quinden Jackson</t>
         </is>
       </c>
       <c r="C630" s="5" t="inlineStr">
         <is>
-          <t>OT</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D630" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E630" s="5" t="inlineStr">
@@ -51460,7 +51460,7 @@
       </c>
       <c r="F630" s="5" t="inlineStr">
         <is>
-          <t>Bell (thumb) sat out of practice Monday, Brooks Kubena of The Athletic reports.</t>
+          <t>Jackson (undisclosed) reverted from waivers to Philadelphia's injured reserve list Tuesday, per the NFL's transaction log.</t>
         </is>
       </c>
     </row>
@@ -51472,27 +51472,27 @@
       </c>
       <c r="B631" s="4" t="inlineStr">
         <is>
-          <t>Jordan Mims</t>
+          <t>Markel Bell</t>
         </is>
       </c>
       <c r="C631" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>OT</t>
         </is>
       </c>
       <c r="D631" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E631" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F631" s="4" t="inlineStr">
         <is>
-          <t>The Eagles signed Mims to a contract Monday.</t>
+          <t>Bell (thumb) sat out of practice Monday, Brooks Kubena of The Athletic reports.</t>
         </is>
       </c>
     </row>
@@ -51504,12 +51504,12 @@
       </c>
       <c r="B632" s="5" t="inlineStr">
         <is>
-          <t>Elijah Moore</t>
+          <t>Jordan Mims</t>
         </is>
       </c>
       <c r="C632" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D632" s="5" t="inlineStr">
@@ -51524,7 +51524,7 @@
       </c>
       <c r="F632" s="5" t="inlineStr">
         <is>
-          <t>Moore (neck) suited up for Monday's training camp practice, Olivia Reiner of The Philadelphia Inquirer reports.</t>
+          <t>The Eagles signed Mims to a contract Monday.</t>
         </is>
       </c>
     </row>
@@ -51536,12 +51536,12 @@
       </c>
       <c r="B633" s="4" t="inlineStr">
         <is>
-          <t>Dameon Pierce</t>
+          <t>Elijah Moore</t>
         </is>
       </c>
       <c r="C633" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D633" s="4" t="inlineStr">
@@ -51556,7 +51556,7 @@
       </c>
       <c r="F633" s="4" t="inlineStr">
         <is>
-          <t>Pierce (hamstring) participated in Monday's training camp practice, Brooks Kubena of The Athletic reports.</t>
+          <t>Moore (neck) suited up for Monday's training camp practice, Olivia Reiner of The Philadelphia Inquirer reports.</t>
         </is>
       </c>
     </row>
@@ -51568,12 +51568,12 @@
       </c>
       <c r="B634" s="5" t="inlineStr">
         <is>
-          <t>Dontayvion Wicks</t>
+          <t>Dameon Pierce</t>
         </is>
       </c>
       <c r="C634" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D634" s="5" t="inlineStr">
@@ -51588,7 +51588,7 @@
       </c>
       <c r="F634" s="5" t="inlineStr">
         <is>
-          <t>Wicks stood out with his route running during the Eagles' joint practices with the Patriots last Wednesday and Thursday, Cayden Steele of NJ.com reports.</t>
+          <t>Pierce (hamstring) participated in Monday's training camp practice, Brooks Kubena of The Athletic reports.</t>
         </is>
       </c>
     </row>
@@ -51600,27 +51600,27 @@
       </c>
       <c r="B635" s="4" t="inlineStr">
         <is>
-          <t>Eli Stowers</t>
+          <t>Dontayvion Wicks</t>
         </is>
       </c>
       <c r="C635" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D635" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E635" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F635" s="4" t="inlineStr">
         <is>
-          <t>Stowers (hamstring) won't practice Monday, Martin Frank of The Delaware News Journal reports.</t>
+          <t>Wicks stood out with his route running during the Eagles' joint practices with the Patriots last Wednesday and Thursday, Cayden Steele of NJ.com reports.</t>
         </is>
       </c>
     </row>
@@ -51632,27 +51632,27 @@
       </c>
       <c r="B636" s="5" t="inlineStr">
         <is>
-          <t>Makai Lemon</t>
+          <t>Eli Stowers</t>
         </is>
       </c>
       <c r="C636" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D636" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E636" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F636" s="5" t="inlineStr">
         <is>
-          <t>Lemon (hamstring) was a full participant in Monday's practice, EJ Smith of The PHLY Sports reports.</t>
+          <t>Stowers (hamstring) won't practice Monday, Martin Frank of The Delaware News Journal reports.</t>
         </is>
       </c>
     </row>
@@ -51664,7 +51664,7 @@
       </c>
       <c r="B637" s="4" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>Makai Lemon</t>
         </is>
       </c>
       <c r="C637" s="4" t="inlineStr">
@@ -51684,7 +51684,7 @@
       </c>
       <c r="F637" s="4" t="inlineStr">
         <is>
-          <t>Smith (hamstring) is a full participant in Monday's practice, EJ Smith of PHLY Sports reports.</t>
+          <t>Lemon (hamstring) was a full participant in Monday's practice, EJ Smith of The PHLY Sports reports.</t>
         </is>
       </c>
     </row>
@@ -51696,12 +51696,12 @@
       </c>
       <c r="B638" s="5" t="inlineStr">
         <is>
-          <t>Jake Elliott</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="C638" s="5" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D638" s="5" t="inlineStr">
@@ -51716,7 +51716,7 @@
       </c>
       <c r="F638" s="5" t="inlineStr">
         <is>
-          <t>Elliott connected on all three of his extra-point tries and did not attempt any field goals in the Eagles' 24-21 preseason loss to the Patriots on Saturday.</t>
+          <t>Smith (hamstring) is a full participant in Monday's practice, EJ Smith of PHLY Sports reports.</t>
         </is>
       </c>
     </row>
@@ -51728,27 +51728,27 @@
       </c>
       <c r="B639" s="4" t="inlineStr">
         <is>
-          <t>Johnny Wilson</t>
+          <t>Jake Elliott</t>
         </is>
       </c>
       <c r="C639" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="D639" s="4" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E639" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F639" s="4" t="inlineStr">
         <is>
-          <t>Wilson (knee) reverted to Philadelphia's injured reserve Saturday, per the NFL's transaction log.</t>
+          <t>Elliott connected on all three of his extra-point tries and did not attempt any field goals in the Eagles' 24-21 preseason loss to the Patriots on Saturday.</t>
         </is>
       </c>
     </row>
@@ -51760,27 +51760,27 @@
       </c>
       <c r="B640" s="5" t="inlineStr">
         <is>
-          <t>Zeke Correll</t>
+          <t>Johnny Wilson</t>
         </is>
       </c>
       <c r="C640" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D640" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E640" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F640" s="5" t="inlineStr">
         <is>
-          <t>The Eagles signed Correll to a contract Friday.</t>
+          <t>Wilson (knee) reverted to Philadelphia's injured reserve Saturday, per the NFL's transaction log.</t>
         </is>
       </c>
     </row>
@@ -51792,27 +51792,27 @@
       </c>
       <c r="B641" s="4" t="inlineStr">
         <is>
-          <t>Tariq Castro-Fields</t>
+          <t>Zeke Correll</t>
         </is>
       </c>
       <c r="C641" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D641" s="4" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E641" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F641" s="4" t="inlineStr">
         <is>
-          <t>The Eagles placed Castro-Fields (heel) on injured reserve Friday.</t>
+          <t>The Eagles signed Correll to a contract Friday.</t>
         </is>
       </c>
     </row>
@@ -51824,27 +51824,27 @@
       </c>
       <c r="B642" s="5" t="inlineStr">
         <is>
-          <t>Brandon Hayes</t>
+          <t>Tariq Castro-Fields</t>
         </is>
       </c>
       <c r="C642" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D642" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E642" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F642" s="5" t="inlineStr">
         <is>
-          <t>The Eagles signed Hayes to a contract Friday.</t>
+          <t>The Eagles placed Castro-Fields (heel) on injured reserve Friday.</t>
         </is>
       </c>
     </row>
@@ -51856,27 +51856,27 @@
       </c>
       <c r="B643" s="4" t="inlineStr">
         <is>
-          <t>Jakorian Bennett</t>
+          <t>Brandon Hayes</t>
         </is>
       </c>
       <c r="C643" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D643" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E643" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F643" s="4" t="inlineStr">
         <is>
-          <t>Bennett (knee) did not practice Thursday, Andrew DiCecco of InsideTheBirds.com reports.</t>
+          <t>The Eagles signed Hayes to a contract Friday.</t>
         </is>
       </c>
     </row>
@@ -51888,12 +51888,12 @@
       </c>
       <c r="B644" s="5" t="inlineStr">
         <is>
-          <t>Byron Young</t>
+          <t>Jakorian Bennett</t>
         </is>
       </c>
       <c r="C644" s="5" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D644" s="5" t="inlineStr">
@@ -51908,7 +51908,7 @@
       </c>
       <c r="F644" s="5" t="inlineStr">
         <is>
-          <t>Young (shoulder) did not participate in Wednesday's practice, Dave Zangaro of NBC Sports Philadelphia reports.</t>
+          <t>Bennett (knee) did not practice Thursday, Andrew DiCecco of InsideTheBirds.com reports.</t>
         </is>
       </c>
     </row>
@@ -51920,12 +51920,12 @@
       </c>
       <c r="B645" s="4" t="inlineStr">
         <is>
-          <t>John Ojukwu</t>
+          <t>Byron Young</t>
         </is>
       </c>
       <c r="C645" s="4" t="inlineStr">
         <is>
-          <t>OT</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="D645" s="4" t="inlineStr">
@@ -51940,7 +51940,7 @@
       </c>
       <c r="F645" s="4" t="inlineStr">
         <is>
-          <t>Ojukwu (pectoral) did not participate during the Eagles' training camp practice Wednesday, Andrew DiCecco of InsideTheBirds.com reports.</t>
+          <t>Young (shoulder) did not participate in Wednesday's practice, Dave Zangaro of NBC Sports Philadelphia reports.</t>
         </is>
       </c>
     </row>
@@ -51952,12 +51952,12 @@
       </c>
       <c r="B646" s="5" t="inlineStr">
         <is>
-          <t>Shaun Wade</t>
+          <t>John Ojukwu</t>
         </is>
       </c>
       <c r="C646" s="5" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>OT</t>
         </is>
       </c>
       <c r="D646" s="5" t="inlineStr">
@@ -51972,7 +51972,7 @@
       </c>
       <c r="F646" s="5" t="inlineStr">
         <is>
-          <t>Wade (shoulder) did not participate in Wednesday's practice, Dave Zangaro of NBC Sports Philadelphia reports.</t>
+          <t>Ojukwu (pectoral) did not participate during the Eagles' training camp practice Wednesday, Andrew DiCecco of InsideTheBirds.com reports.</t>
         </is>
       </c>
     </row>
@@ -51984,7 +51984,7 @@
       </c>
       <c r="B647" s="4" t="inlineStr">
         <is>
-          <t>Quinyon Mitchell</t>
+          <t>Shaun Wade</t>
         </is>
       </c>
       <c r="C647" s="4" t="inlineStr">
@@ -51994,17 +51994,17 @@
       </c>
       <c r="D647" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E647" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F647" s="4" t="inlineStr">
         <is>
-          <t>Mitchell (lower body) was a full participant in Wednesday's joint practice with the Patriots, Tim McManus of ESPN.com reports.</t>
+          <t>Wade (shoulder) did not participate in Wednesday's practice, Dave Zangaro of NBC Sports Philadelphia reports.</t>
         </is>
       </c>
     </row>
@@ -52016,27 +52016,27 @@
       </c>
       <c r="B648" s="5" t="inlineStr">
         <is>
-          <t>Grant Calcaterra</t>
+          <t>Quinyon Mitchell</t>
         </is>
       </c>
       <c r="C648" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D648" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E648" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F648" s="5" t="inlineStr">
         <is>
-          <t>Calcatarra (back) did not participate in Wednesday's practice, Dave Zangaro of NBC Sports Philadelphia reports.</t>
+          <t>Mitchell (lower body) was a full participant in Wednesday's joint practice with the Patriots, Tim McManus of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -52048,27 +52048,27 @@
       </c>
       <c r="B649" s="4" t="inlineStr">
         <is>
-          <t>Jonathan Greenard</t>
+          <t>Grant Calcaterra</t>
         </is>
       </c>
       <c r="C649" s="4" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D649" s="4" t="inlineStr">
         <is>
-          <t>Out</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E649" s="4" t="inlineStr">
         <is>
-          <t>Surgery</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F649" s="4" t="inlineStr">
         <is>
-          <t>The Eagles are worried Greenard (pectoral) could miss the Week 1 divisional showdown with the Commanders due to injury, Mike Garafolo of NFL Network reports.</t>
+          <t>Calcatarra (back) did not participate in Wednesday's practice, Dave Zangaro of NBC Sports Philadelphia reports.</t>
         </is>
       </c>
     </row>
@@ -52080,27 +52080,27 @@
       </c>
       <c r="B650" s="5" t="inlineStr">
         <is>
-          <t>Tank Bigsby</t>
+          <t>Jonathan Greenard</t>
         </is>
       </c>
       <c r="C650" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D650" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="E650" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Surgery</t>
         </is>
       </c>
       <c r="F650" s="5" t="inlineStr">
         <is>
-          <t>Bigsby (toe) will participate in Wednesday's practice, Olivia Reiner of The Philadelphia Inquirer reports.</t>
+          <t>The Eagles are worried Greenard (pectoral) could miss the Week 1 divisional showdown with the Commanders due to injury, Mike Garafolo of NFL Network reports.</t>
         </is>
       </c>
     </row>
@@ -52112,27 +52112,27 @@
       </c>
       <c r="B651" s="4" t="inlineStr">
         <is>
-          <t>Danny Gray</t>
+          <t>Tank Bigsby</t>
         </is>
       </c>
       <c r="C651" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D651" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E651" s="4" t="inlineStr">
         <is>
-          <t>Concussion</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F651" s="4" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>Bigsby (toe) will participate in Wednesday's practice, Olivia Reiner of The Philadelphia Inquirer reports.</t>
         </is>
       </c>
     </row>
@@ -52144,12 +52144,12 @@
       </c>
       <c r="B652" s="5" t="inlineStr">
         <is>
-          <t>Jonathan Jones</t>
+          <t>Danny Gray</t>
         </is>
       </c>
       <c r="C652" s="5" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D652" s="5" t="inlineStr">
@@ -52159,7 +52159,7 @@
       </c>
       <c r="E652" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Concussion</t>
         </is>
       </c>
       <c r="F652" s="5" t="inlineStr">
@@ -52176,12 +52176,12 @@
       </c>
       <c r="B653" s="4" t="inlineStr">
         <is>
-          <t>Micah Morris</t>
+          <t>Jonathan Jones</t>
         </is>
       </c>
       <c r="C653" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D653" s="4" t="inlineStr">
@@ -52208,12 +52208,12 @@
       </c>
       <c r="B654" s="5" t="inlineStr">
         <is>
-          <t>Chance Campbell</t>
+          <t>Micah Morris</t>
         </is>
       </c>
       <c r="C654" s="5" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D654" s="5" t="inlineStr">
@@ -57127,10 +57127,10 @@
         <v>72.09999999999999</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>10.8</v>
+        <v>11.5</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>14</v>
@@ -57145,7 +57145,7 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>Wind 11 mph (gusts 20)</t>
+          <t>Wind 12 mph (gusts 20)</t>
         </is>
       </c>
     </row>
@@ -57166,13 +57166,13 @@
         </is>
       </c>
       <c r="D6" s="17" t="n">
-        <v>72.8</v>
+        <v>73</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="F6" s="17" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="G6" s="17" t="n">
         <v>2</v>
@@ -57204,13 +57204,13 @@
         </is>
       </c>
       <c r="D7" s="15" t="n">
-        <v>106.9</v>
+        <v>107.4</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>9.300000000000001</v>
+        <v>19.3</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>16.6</v>
+        <v>18.4</v>
       </c>
       <c r="G7" s="15" t="n">
         <v>1</v>
@@ -57246,13 +57246,13 @@
         </is>
       </c>
       <c r="D8" s="17" t="n">
-        <v>79</v>
+        <v>79.2</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>8.1</v>
+        <v>7.3</v>
       </c>
       <c r="F8" s="17" t="n">
-        <v>3.1</v>
+        <v>5.1</v>
       </c>
       <c r="G8" s="17" t="n">
         <v>0</v>
@@ -57284,13 +57284,13 @@
         </is>
       </c>
       <c r="D9" s="15" t="n">
-        <v>83.3</v>
+        <v>85.3</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>5.8</v>
+        <v>6.3</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>8.5</v>
+        <v>10.1</v>
       </c>
       <c r="G9" s="15" t="n">
         <v>27</v>
@@ -57322,13 +57322,13 @@
         </is>
       </c>
       <c r="D10" s="17" t="n">
-        <v>89</v>
+        <v>89.2</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>13</v>
+        <v>13.4</v>
       </c>
       <c r="F10" s="17" t="n">
-        <v>13.2</v>
+        <v>14.1</v>
       </c>
       <c r="G10" s="17" t="n">
         <v>35</v>
@@ -57343,7 +57343,7 @@
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>Wind 13 mph (gusts 13) · canopy — wind damped</t>
+          <t>Wind 13 mph (gusts 14) · canopy — wind damped</t>
         </is>
       </c>
     </row>
@@ -57364,20 +57364,20 @@
         </is>
       </c>
       <c r="D11" s="15" t="n">
-        <v>83.5</v>
+        <v>79</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>9.5</v>
+        <v>5.6</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>16.6</v>
+        <v>12.3</v>
       </c>
       <c r="G11" s="15" t="n">
         <v>75</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Overcast</t>
+          <t>Light drizzle</t>
         </is>
       </c>
       <c r="I11" s="9" t="n">
@@ -57406,13 +57406,13 @@
         </is>
       </c>
       <c r="D12" s="17" t="n">
-        <v>83.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="F12" s="17" t="n">
-        <v>9.6</v>
+        <v>10.7</v>
       </c>
       <c r="G12" s="17" t="n">
         <v>23</v>
@@ -57444,20 +57444,20 @@
         </is>
       </c>
       <c r="D13" s="15" t="n">
-        <v>77.8</v>
+        <v>87.8</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>10.1</v>
+        <v>6.8</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>14.8</v>
+        <v>8.5</v>
       </c>
       <c r="G13" s="15" t="n">
         <v>72</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Rain showers</t>
+          <t>Light drizzle</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
@@ -57486,13 +57486,13 @@
         </is>
       </c>
       <c r="D14" s="17" t="n">
-        <v>80.5</v>
+        <v>79.8</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="F14" s="17" t="n">
-        <v>2.7</v>
+        <v>5.8</v>
       </c>
       <c r="G14" s="17" t="n">
         <v>33</v>
@@ -57524,13 +57524,13 @@
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>85.3</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>10.1</v>
+        <v>10.5</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>19.2</v>
+        <v>19.9</v>
       </c>
       <c r="G15" s="15" t="n">
         <v>0</v>
@@ -57545,7 +57545,7 @@
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>Wind 10 mph (gusts 19)</t>
+          <t>Wind 10 mph (gusts 20)</t>
         </is>
       </c>
     </row>
@@ -57566,10 +57566,10 @@
         </is>
       </c>
       <c r="D16" s="17" t="n">
-        <v>102.3</v>
+        <v>102.1</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="F16" s="17" t="n">
         <v>8.699999999999999</v>
@@ -57608,20 +57608,20 @@
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>68.90000000000001</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>17.2</v>
+        <v>18.3</v>
       </c>
       <c r="G17" s="15" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Mainly clear</t>
+          <t>Partly cloudy</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
@@ -57629,7 +57629,7 @@
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>Wind 12 mph (gusts 17)</t>
+          <t>Wind 12 mph (gusts 18)</t>
         </is>
       </c>
     </row>
@@ -57650,13 +57650,13 @@
         </is>
       </c>
       <c r="D18" s="17" t="n">
-        <v>85.90000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>5.2</v>
+        <v>10.3</v>
       </c>
       <c r="F18" s="17" t="n">
-        <v>9.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="G18" s="17" t="n">
         <v>8</v>
@@ -57691,10 +57691,10 @@
         <v>81.2</v>
       </c>
       <c r="E19" s="15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F19" s="15" t="n">
         <v>5.4</v>
-      </c>
-      <c r="F19" s="15" t="n">
-        <v>6.7</v>
       </c>
       <c r="G19" s="15" t="n">
         <v>0</v>
@@ -57726,26 +57726,30 @@
         </is>
       </c>
       <c r="D20" s="17" t="n">
-        <v>87.5</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>8.1</v>
+        <v>2.6</v>
       </c>
       <c r="F20" s="17" t="n">
-        <v>7.6</v>
+        <v>6.3</v>
       </c>
       <c r="G20" s="17" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>Overcast</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="I20" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="5" t="inlineStr"/>
+        <v>-0.5</v>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>94°F</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -57764,16 +57768,16 @@
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>79.8</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="G21" s="15" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
@@ -57801,21 +57805,31 @@
           <t>open</t>
         </is>
       </c>
-      <c r="D22" s="17" t="n"/>
-      <c r="E22" s="17" t="n"/>
-      <c r="F22" s="17" t="n"/>
+      <c r="D22" s="17" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="F22" s="17" t="n">
+        <v>44.7</v>
+      </c>
       <c r="G22" s="17" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Overcast</t>
         </is>
       </c>
       <c r="I22" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="5" t="inlineStr"/>
+        <v>-4.5</v>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>Wind 19 mph (gusts 45)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">

--- a/NFL_Edge_Model.xlsx
+++ b/NFL_Edge_Model.xlsx
@@ -692,7 +692,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Snapshot of the live model, generated 2026-08-26T07:34:34+00:00. Read-only: the model runs in the pipeline, not in this file.</t>
+          <t>Snapshot of the live model, generated 2026-08-26T14:25:39+00:00. Read-only: the model runs in the pipeline, not in this file.</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>2026-08-26T07:34:34+00:00</t>
+          <t>2026-08-26T14:25:39+00:00</t>
         </is>
       </c>
     </row>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>WSH @ BAL</t>
+          <t>PIT @ BUF</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -2653,14 +2653,14 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Over 34.5</t>
+          <t>Over 35.5</t>
         </is>
       </c>
       <c r="E7" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>0.6086</v>
+        <v>0.6085</v>
       </c>
       <c r="G7" s="8" t="n">
         <v>0.5238</v>
@@ -2669,7 +2669,7 @@
         <v>0.0502</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>0.1617788238702841</v>
+        <v>0.1617634272081301</v>
       </c>
       <c r="J7" s="10" t="n">
         <v>0.15</v>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>PIT @ BUF</t>
+          <t>WSH @ BAL</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2698,23 +2698,23 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Over 35.5</t>
+          <t>Over 34.5</t>
         </is>
       </c>
       <c r="E8" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.6039</v>
+        <v>0.6086</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H8" s="13" t="n">
-        <v>0.0493</v>
+        <v>0.0502</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>0.1528813412160536</v>
+        <v>0.1617788238702841</v>
       </c>
       <c r="J8" s="14" t="n">
         <v>0.15</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>ARI @ GB</t>
+          <t>LAR @ LAC</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -3017,19 +3017,19 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>0.5787</v>
+        <v>0.5897</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.5238</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>0.046</v>
+        <v>0.0458</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>0.1298449688602823</v>
+        <v>0.1257861101459882</v>
       </c>
       <c r="J15" s="10" t="n">
         <v>0.15</v>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>LAR @ LAC</t>
+          <t>SF @ LV</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -3058,23 +3058,23 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Over 38.5</t>
+          <t>Over 37.5</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5897</v>
+        <v>0.5834</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5192</v>
       </c>
       <c r="H16" s="13" t="n">
-        <v>0.0458</v>
+        <v>0.0453</v>
       </c>
       <c r="I16" s="13" t="n">
-        <v>0.1257861101459882</v>
+        <v>0.1235669393172453</v>
       </c>
       <c r="J16" s="14" t="n">
         <v>0.15</v>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>SF @ LV</t>
+          <t>HOU @ CAR</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -3103,23 +3103,23 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Over 37.5</t>
+          <t>Over 36.5</t>
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>0.5834</v>
+        <v>0.5739</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>0.5192</v>
+        <v>0.5122</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>0.0453</v>
+        <v>0.0444</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>0.1235669393172453</v>
+        <v>0.1204110788803935</v>
       </c>
       <c r="J17" s="10" t="n">
         <v>0.15</v>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>HOU @ CAR</t>
+          <t>NE @ CLE</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -3148,23 +3148,23 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Over 36.5</t>
+          <t>Over 35.5</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
         <v>-105</v>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5739</v>
+        <v>0.5714</v>
       </c>
       <c r="G18" s="13" t="n">
         <v>0.5122</v>
       </c>
       <c r="H18" s="13" t="n">
-        <v>0.0444</v>
+        <v>0.0436</v>
       </c>
       <c r="I18" s="13" t="n">
-        <v>0.1204110788803935</v>
+        <v>0.1156809773671671</v>
       </c>
       <c r="J18" s="14" t="n">
         <v>0.15</v>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>NE @ CLE</t>
+          <t>ARI @ GB</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -3193,7 +3193,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Over 35.5</t>
+          <t>Over 38.5</t>
         </is>
       </c>
       <c r="E19" s="7" t="n">
@@ -3209,7 +3209,7 @@
         <v>0.0436</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>0.1156809773671671</v>
+        <v>0.1156447435682119</v>
       </c>
       <c r="J19" s="10" t="n">
         <v>0.15</v>
@@ -3269,33 +3269,33 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>ATL @ MIA</t>
+          <t>SEA @ KC</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>MIA +4.5</t>
+          <t>Over 36.5</t>
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>0.5542</v>
+        <v>0.5679</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.5238</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>0.0354</v>
+        <v>0.0366</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>0.08192506535915522</v>
+        <v>0.08416173853360265</v>
       </c>
       <c r="J21" s="10" t="n">
         <v>0.15</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>SF @ LV</t>
+          <t>ATL @ MIA</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -3324,23 +3324,23 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>SF +3.5</t>
+          <t>MIA +4.5</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>-112</v>
+        <v>-105</v>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5672</v>
+        <v>0.5542</v>
       </c>
       <c r="G22" s="13" t="n">
-        <v>0.5283</v>
+        <v>0.5122</v>
       </c>
       <c r="H22" s="13" t="n">
-        <v>0.0335</v>
+        <v>0.0354</v>
       </c>
       <c r="I22" s="13" t="n">
-        <v>0.0736241139165047</v>
+        <v>0.08192506535915522</v>
       </c>
       <c r="J22" s="14" t="n">
         <v>0.15</v>
@@ -3449,33 +3449,33 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>SEA @ KC</t>
+          <t>SF @ LV</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Over 36.5</t>
+          <t>SF +3.5</t>
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>0.5605</v>
+        <v>0.5695</v>
       </c>
       <c r="G25" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5349</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>0.0321</v>
+        <v>0.0307</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>0.07004853435618563</v>
+        <v>0.06466918237539143</v>
       </c>
       <c r="J25" s="10" t="n">
         <v>0.15</v>
@@ -3762,19 +3762,19 @@
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.3379</v>
+        <v>0.3318</v>
       </c>
       <c r="G32" s="13" t="n">
-        <v>0.3067</v>
+        <v>0.3021</v>
       </c>
       <c r="H32" s="13" t="n">
-        <v>0.0282</v>
+        <v>0.0271</v>
       </c>
       <c r="I32" s="13" t="n">
-        <v>0.1007856972199768</v>
+        <v>0.09750786515620957</v>
       </c>
       <c r="J32" s="14" t="n">
         <v>0.15</v>
@@ -3807,19 +3807,19 @@
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>0.4404</v>
+        <v>0.4377</v>
       </c>
       <c r="G33" s="8" t="n">
-        <v>0.4098</v>
+        <v>0.4082</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>0.0277</v>
+        <v>0.027</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>0.07382229463065115</v>
+        <v>0.07164487259187802</v>
       </c>
       <c r="J33" s="10" t="n">
         <v>0.15</v>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>NYG @ NYJ</t>
+          <t>TB @ JAX</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -4106,23 +4106,23 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>NYJ +3</t>
+          <t>JAX +3</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.5339</v>
+        <v>0.5459000000000001</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>0.5122</v>
+        <v>0.5238</v>
       </c>
       <c r="H40" s="13" t="n">
-        <v>0.0207</v>
+        <v>0.021</v>
       </c>
       <c r="I40" s="13" t="n">
-        <v>0.03940790724231108</v>
+        <v>0.03918077037938406</v>
       </c>
       <c r="J40" s="14" t="n">
         <v>0.15</v>
@@ -4187,28 +4187,28 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>JAX +3</t>
+          <t>JAX ML</t>
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>-110</v>
+        <v>129</v>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.5455</v>
+        <v>0.4569</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.4367</v>
       </c>
       <c r="H42" s="13" t="n">
-        <v>0.0206</v>
+        <v>0.0193</v>
       </c>
       <c r="I42" s="13" t="n">
-        <v>0.03850724179393927</v>
+        <v>0.0457892075180627</v>
       </c>
       <c r="J42" s="14" t="n">
         <v>0.15</v>
@@ -4272,33 +4272,33 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>TB @ JAX</t>
+          <t>NYG @ NYJ</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>JAX ML</t>
+          <t>NYJ +3</t>
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>129</v>
+        <v>-105</v>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.4565</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>0.4367</v>
+        <v>0.5122</v>
       </c>
       <c r="H44" s="13" t="n">
-        <v>0.019</v>
+        <v>0.0188</v>
       </c>
       <c r="I44" s="13" t="n">
-        <v>0.04496072028550879</v>
+        <v>0.03559751624243812</v>
       </c>
       <c r="J44" s="14" t="n">
         <v>0.15</v>
@@ -4540,23 +4540,23 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>MIN +6</t>
+          <t>MIN +6.5</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.5371</v>
+        <v>0.5459000000000001</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>0.5192</v>
+        <v>0.5283</v>
       </c>
       <c r="H50" s="13" t="n">
-        <v>0.0173</v>
+        <v>0.017</v>
       </c>
       <c r="I50" s="13" t="n">
-        <v>0.03316891728877225</v>
+        <v>0.03321966498070866</v>
       </c>
       <c r="J50" s="14" t="n">
         <v>0.15</v>
@@ -5128,33 +5128,33 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>CIN @ PHI</t>
+          <t>CHI @ TEN</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>CIN ML</t>
+          <t>CHI +3</t>
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>129</v>
+        <v>-115</v>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.4461</v>
+        <v>0.5444</v>
       </c>
       <c r="G64" s="13" t="n">
-        <v>0.4367</v>
+        <v>0.5349</v>
       </c>
       <c r="H64" s="13" t="n">
         <v>0.0094</v>
       </c>
       <c r="I64" s="13" t="n">
-        <v>0.02145323959040912</v>
+        <v>0.01647476246217722</v>
       </c>
       <c r="J64" s="14" t="n">
         <v>0.15</v>
@@ -5173,7 +5173,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>CHI @ TEN</t>
+          <t>NE @ SEA</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>CHI +3</t>
+          <t>NE +3.5</t>
         </is>
       </c>
       <c r="E65" s="7" t="n">
@@ -5199,16 +5199,12 @@
         <v>0.0094</v>
       </c>
       <c r="I65" s="8" t="n">
-        <v>0.01647476246217722</v>
+        <v>0.01772449429322892</v>
       </c>
       <c r="J65" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K65" s="4" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K65" s="4" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -5218,33 +5214,33 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>NE @ SEA</t>
+          <t>CHI @ CAR</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>NE +3.5</t>
+          <t>CAR ML</t>
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>-115</v>
+        <v>120</v>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.5444</v>
+        <v>0.4632</v>
       </c>
       <c r="G66" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.4545</v>
       </c>
       <c r="H66" s="13" t="n">
-        <v>0.0094</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="I66" s="13" t="n">
-        <v>0.01772449429322892</v>
+        <v>0.01878422835459448</v>
       </c>
       <c r="J66" s="14" t="n">
         <v>0.5</v>
@@ -5264,28 +5260,28 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>CAR ML</t>
+          <t>CAR +2.5</t>
         </is>
       </c>
       <c r="E67" s="7" t="n">
-        <v>120</v>
+        <v>-102</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>0.4632</v>
+        <v>0.5132</v>
       </c>
       <c r="G67" s="8" t="n">
-        <v>0.4545</v>
+        <v>0.505</v>
       </c>
       <c r="H67" s="8" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="I67" s="8" t="n">
-        <v>0.01878422835459448</v>
+        <v>0.01628003057036898</v>
       </c>
       <c r="J67" s="10" t="n">
         <v>0.5</v>
@@ -5300,7 +5296,7 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>CHI @ CAR</t>
+          <t>CIN @ PHI</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
@@ -5310,28 +5306,32 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>CAR +2.5</t>
+          <t>CIN +3</t>
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>-102</v>
+        <v>-112</v>
       </c>
       <c r="F68" s="13" t="n">
-        <v>0.5132</v>
+        <v>0.536</v>
       </c>
       <c r="G68" s="13" t="n">
-        <v>0.505</v>
+        <v>0.5283</v>
       </c>
       <c r="H68" s="13" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0076</v>
       </c>
       <c r="I68" s="13" t="n">
-        <v>0.01628003057036898</v>
+        <v>0.01351313943760185</v>
       </c>
       <c r="J68" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K68" s="5" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K68" s="5" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
@@ -5341,33 +5341,33 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>CIN @ PHI</t>
+          <t>HOU @ CAR</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>CIN +3</t>
+          <t>CAR ML</t>
         </is>
       </c>
       <c r="E69" s="7" t="n">
-        <v>-112</v>
+        <v>120</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>0.536</v>
+        <v>0.4621</v>
       </c>
       <c r="G69" s="8" t="n">
-        <v>0.5283</v>
+        <v>0.4545</v>
       </c>
       <c r="H69" s="8" t="n">
-        <v>0.0076</v>
+        <v>0.0075</v>
       </c>
       <c r="I69" s="8" t="n">
-        <v>0.01351313943760185</v>
+        <v>0.01651048203051431</v>
       </c>
       <c r="J69" s="10" t="n">
         <v>0.15</v>
@@ -5386,7 +5386,7 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>HOU @ CAR</t>
+          <t>CIN @ PHI</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
@@ -5396,23 +5396,23 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>CAR ML</t>
+          <t>CIN ML</t>
         </is>
       </c>
       <c r="E70" s="12" t="n">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.4621</v>
+        <v>0.4475</v>
       </c>
       <c r="G70" s="13" t="n">
-        <v>0.4545</v>
+        <v>0.4405</v>
       </c>
       <c r="H70" s="13" t="n">
-        <v>0.0075</v>
+        <v>0.007</v>
       </c>
       <c r="I70" s="13" t="n">
-        <v>0.01651048203051431</v>
+        <v>0.0157719128249183</v>
       </c>
       <c r="J70" s="14" t="n">
         <v>0.15</v>
@@ -5517,38 +5517,42 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>DEN @ KC</t>
+          <t>SEA @ KC</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Under 42.5</t>
+          <t>KC ML</t>
         </is>
       </c>
       <c r="E73" s="7" t="n">
-        <v>-110</v>
+        <v>-124</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>0.5279</v>
+        <v>0.5579</v>
       </c>
       <c r="G73" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5536</v>
       </c>
       <c r="H73" s="8" t="n">
-        <v>0.0041</v>
+        <v>0.0043</v>
       </c>
       <c r="I73" s="8" t="n">
-        <v>0.007840044051825923</v>
+        <v>0.007764785888535131</v>
       </c>
       <c r="J73" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K73" s="4" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K73" s="4" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
@@ -5558,33 +5562,33 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>BAL @ IND</t>
+          <t>DEN @ KC</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>IND +3.5</t>
+          <t>Under 42.5</t>
         </is>
       </c>
       <c r="E74" s="12" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.5321</v>
+        <v>0.5279</v>
       </c>
       <c r="G74" s="13" t="n">
-        <v>0.5283</v>
+        <v>0.5238</v>
       </c>
       <c r="H74" s="13" t="n">
-        <v>0.0038</v>
+        <v>0.0041</v>
       </c>
       <c r="I74" s="13" t="n">
-        <v>0.007227421686627156</v>
+        <v>0.007840044051825923</v>
       </c>
       <c r="J74" s="14" t="n">
         <v>0.5</v>
@@ -5604,28 +5608,28 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>IND ML</t>
+          <t>IND +3.5</t>
         </is>
       </c>
       <c r="E75" s="7" t="n">
-        <v>145</v>
+        <v>-112</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>0.4114</v>
+        <v>0.5321</v>
       </c>
       <c r="G75" s="8" t="n">
-        <v>0.4082</v>
+        <v>0.5283</v>
       </c>
       <c r="H75" s="8" t="n">
-        <v>0.0033</v>
+        <v>0.0038</v>
       </c>
       <c r="I75" s="8" t="n">
-        <v>0.007929117400102492</v>
+        <v>0.007227421686627156</v>
       </c>
       <c r="J75" s="10" t="n">
         <v>0.5</v>
@@ -5640,33 +5644,33 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>NE @ SEA</t>
+          <t>BAL @ IND</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Under 44.5</t>
+          <t>IND ML</t>
         </is>
       </c>
       <c r="E76" s="12" t="n">
-        <v>-110</v>
+        <v>145</v>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.5254</v>
+        <v>0.4114</v>
       </c>
       <c r="G76" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.4082</v>
       </c>
       <c r="H76" s="13" t="n">
-        <v>0.0016</v>
+        <v>0.0033</v>
       </c>
       <c r="I76" s="13" t="n">
-        <v>0.003017043983478351</v>
+        <v>0.007929117400102492</v>
       </c>
       <c r="J76" s="14" t="n">
         <v>0.5</v>
@@ -5681,7 +5685,7 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>BUF @ HOU</t>
+          <t>NE @ SEA</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -5691,7 +5695,7 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Over 44.5</t>
+          <t>Under 44.5</t>
         </is>
       </c>
       <c r="E77" s="7" t="n">
@@ -5707,7 +5711,7 @@
         <v>0.0016</v>
       </c>
       <c r="I77" s="8" t="n">
-        <v>0.003023751045110934</v>
+        <v>0.003017043983478351</v>
       </c>
       <c r="J77" s="10" t="n">
         <v>0.5</v>
@@ -5722,42 +5726,38 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>PIT @ BUF</t>
+          <t>BUF @ HOU</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>BUF ML</t>
+          <t>Over 44.5</t>
         </is>
       </c>
       <c r="E78" s="12" t="n">
-        <v>-152</v>
+        <v>-110</v>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.6042</v>
+        <v>0.5254</v>
       </c>
       <c r="G78" s="13" t="n">
-        <v>0.6032</v>
+        <v>0.5238</v>
       </c>
       <c r="H78" s="13" t="n">
-        <v>0.0011</v>
+        <v>0.0016</v>
       </c>
       <c r="I78" s="13" t="n">
-        <v>0.001762885624806587</v>
+        <v>0.003023751045110934</v>
       </c>
       <c r="J78" s="14" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K78" s="5" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K78" s="5" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -5772,28 +5772,28 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>BUF -3</t>
+          <t>BUF ML</t>
         </is>
       </c>
       <c r="E79" s="7" t="n">
-        <v>-108</v>
+        <v>-152</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>0.5198</v>
+        <v>0.6042</v>
       </c>
       <c r="G79" s="8" t="n">
-        <v>0.5192</v>
+        <v>0.6032</v>
       </c>
       <c r="H79" s="8" t="n">
-        <v>0.0005</v>
+        <v>0.0011</v>
       </c>
       <c r="I79" s="8" t="n">
-        <v>0.000957171010924851</v>
+        <v>0.001762885624806587</v>
       </c>
       <c r="J79" s="10" t="n">
         <v>0.15</v>
@@ -5812,33 +5812,33 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>SEA @ KC</t>
+          <t>PIT @ BUF</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>KC ML</t>
+          <t>BUF -3</t>
         </is>
       </c>
       <c r="E80" s="12" t="n">
-        <v>-127</v>
+        <v>-108</v>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.5597</v>
+        <v>0.5198</v>
       </c>
       <c r="G80" s="13" t="n">
-        <v>0.5595</v>
+        <v>0.5192</v>
       </c>
       <c r="H80" s="13" t="n">
-        <v>0.0002</v>
+        <v>0.0005</v>
       </c>
       <c r="I80" s="13" t="n">
-        <v>0.0003726041985263606</v>
+        <v>0.000957171010924851</v>
       </c>
       <c r="J80" s="14" t="n">
         <v>0.15</v>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>TB @ CIN</t>
+          <t>NE @ CLE</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
@@ -5908,28 +5908,32 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>TB ML</t>
+          <t>NE ML</t>
         </is>
       </c>
       <c r="E82" s="12" t="n">
-        <v>164</v>
+        <v>-150</v>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.3756</v>
+        <v>0.5967</v>
       </c>
       <c r="G82" s="13" t="n">
-        <v>0.3788</v>
+        <v>0.6</v>
       </c>
       <c r="H82" s="13" t="n">
-        <v>-0.0032</v>
+        <v>-0.0033</v>
       </c>
       <c r="I82" s="13" t="n">
-        <v>-0.008255833011393876</v>
+        <v>-0.005438888888026017</v>
       </c>
       <c r="J82" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K82" s="5" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K82" s="5" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
@@ -5939,7 +5943,7 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>NE @ CLE</t>
+          <t>TB @ CIN</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -5949,32 +5953,28 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>NE ML</t>
+          <t>TB ML</t>
         </is>
       </c>
       <c r="E83" s="7" t="n">
-        <v>-150</v>
+        <v>164</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>0.5967</v>
+        <v>0.3749</v>
       </c>
       <c r="G83" s="8" t="n">
-        <v>0.6</v>
+        <v>0.3788</v>
       </c>
       <c r="H83" s="8" t="n">
-        <v>-0.0033</v>
+        <v>-0.0038</v>
       </c>
       <c r="I83" s="8" t="n">
-        <v>-0.005438888888026017</v>
+        <v>-0.01009121467833307</v>
       </c>
       <c r="J83" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K83" s="4" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K83" s="4" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
@@ -6234,33 +6234,33 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>TB @ CIN</t>
+          <t>DAL @ NYG</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>TB +3.5</t>
+          <t>NYG ML</t>
         </is>
       </c>
       <c r="E90" s="12" t="n">
-        <v>-105</v>
+        <v>124</v>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.5004</v>
+        <v>0.4353</v>
       </c>
       <c r="G90" s="13" t="n">
-        <v>0.5122</v>
+        <v>0.4464</v>
       </c>
       <c r="H90" s="13" t="n">
-        <v>-0.0116</v>
+        <v>-0.011</v>
       </c>
       <c r="I90" s="13" t="n">
-        <v>-0.02299267509243297</v>
+        <v>-0.02480764428745663</v>
       </c>
       <c r="J90" s="14" t="n">
         <v>0.5</v>
@@ -6275,33 +6275,33 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>ATL @ PIT</t>
+          <t>TB @ CIN</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>ATL ML</t>
+          <t>TB +3.5</t>
         </is>
       </c>
       <c r="E91" s="7" t="n">
-        <v>145</v>
+        <v>-105</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>0.3952</v>
+        <v>0.4997</v>
       </c>
       <c r="G91" s="8" t="n">
-        <v>0.4082</v>
+        <v>0.5122</v>
       </c>
       <c r="H91" s="8" t="n">
-        <v>-0.0127</v>
+        <v>-0.0123</v>
       </c>
       <c r="I91" s="8" t="n">
-        <v>-0.03150835492349835</v>
+        <v>-0.02440079818666258</v>
       </c>
       <c r="J91" s="10" t="n">
         <v>0.5</v>
@@ -6316,7 +6316,7 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>DAL @ NYG</t>
+          <t>ATL @ PIT</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
@@ -6326,23 +6326,23 @@
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>NYG ML</t>
+          <t>ATL ML</t>
         </is>
       </c>
       <c r="E92" s="12" t="n">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.4324</v>
+        <v>0.3952</v>
       </c>
       <c r="G92" s="13" t="n">
-        <v>0.4464</v>
+        <v>0.4082</v>
       </c>
       <c r="H92" s="13" t="n">
-        <v>-0.0138</v>
+        <v>-0.0127</v>
       </c>
       <c r="I92" s="13" t="n">
-        <v>-0.0312262377799627</v>
+        <v>-0.03150835492349835</v>
       </c>
       <c r="J92" s="14" t="n">
         <v>0.5</v>
@@ -6685,33 +6685,33 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>DET @ BUF</t>
+          <t>DAL @ NYG</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>BUF ML</t>
+          <t>Under 48.5</t>
         </is>
       </c>
       <c r="E101" s="7" t="n">
-        <v>-162</v>
+        <v>-110</v>
       </c>
       <c r="F101" s="8" t="n">
-        <v>0.597</v>
+        <v>0.5024999999999999</v>
       </c>
       <c r="G101" s="8" t="n">
-        <v>0.6183</v>
+        <v>0.5238</v>
       </c>
       <c r="H101" s="8" t="n">
-        <v>-0.0204</v>
+        <v>-0.0203</v>
       </c>
       <c r="I101" s="8" t="n">
-        <v>-0.03425999460203544</v>
+        <v>-0.04059973386935589</v>
       </c>
       <c r="J101" s="10" t="n">
         <v>0.5</v>
@@ -6726,33 +6726,33 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>GB @ MIN</t>
+          <t>DAL @ NYG</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>GB ML</t>
+          <t>NYG +2.5</t>
         </is>
       </c>
       <c r="E102" s="12" t="n">
-        <v>-102</v>
+        <v>-105</v>
       </c>
       <c r="F102" s="13" t="n">
-        <v>0.4824</v>
+        <v>0.4908</v>
       </c>
       <c r="G102" s="13" t="n">
-        <v>0.505</v>
+        <v>0.5122</v>
       </c>
       <c r="H102" s="13" t="n">
-        <v>-0.0214</v>
+        <v>-0.0204</v>
       </c>
       <c r="I102" s="13" t="n">
-        <v>-0.04423890812367315</v>
+        <v>-0.04181814209862056</v>
       </c>
       <c r="J102" s="14" t="n">
         <v>0.5</v>
@@ -6767,33 +6767,33 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>DAL @ NYG</t>
+          <t>DET @ BUF</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>DAL -2.5</t>
+          <t>BUF ML</t>
         </is>
       </c>
       <c r="E103" s="7" t="n">
-        <v>-115</v>
+        <v>-162</v>
       </c>
       <c r="F103" s="8" t="n">
-        <v>0.5121</v>
+        <v>0.597</v>
       </c>
       <c r="G103" s="8" t="n">
-        <v>0.5349</v>
+        <v>0.6183</v>
       </c>
       <c r="H103" s="8" t="n">
-        <v>-0.0216</v>
+        <v>-0.0204</v>
       </c>
       <c r="I103" s="8" t="n">
-        <v>-0.04257813899062829</v>
+        <v>-0.03425999460203544</v>
       </c>
       <c r="J103" s="10" t="n">
         <v>0.5</v>
@@ -6818,23 +6818,23 @@
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>MIN ML</t>
+          <t>GB ML</t>
         </is>
       </c>
       <c r="E104" s="12" t="n">
-        <v>-118</v>
+        <v>-102</v>
       </c>
       <c r="F104" s="13" t="n">
-        <v>0.5175999999999999</v>
+        <v>0.4824</v>
       </c>
       <c r="G104" s="13" t="n">
-        <v>0.5413</v>
+        <v>0.505</v>
       </c>
       <c r="H104" s="13" t="n">
-        <v>-0.0223</v>
+        <v>-0.0214</v>
       </c>
       <c r="I104" s="13" t="n">
-        <v>-0.04338098642890131</v>
+        <v>-0.04423890812367315</v>
       </c>
       <c r="J104" s="14" t="n">
         <v>0.5</v>
@@ -6849,33 +6849,33 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>DAL @ NYG</t>
+          <t>GB @ MIN</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>MIN ML</t>
         </is>
       </c>
       <c r="E105" s="7" t="n">
-        <v>-110</v>
+        <v>-118</v>
       </c>
       <c r="F105" s="8" t="n">
-        <v>0.5</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="G105" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5413</v>
       </c>
       <c r="H105" s="8" t="n">
-        <v>-0.0224</v>
+        <v>-0.0223</v>
       </c>
       <c r="I105" s="8" t="n">
-        <v>-0.04545406739379704</v>
+        <v>-0.04338098642890131</v>
       </c>
       <c r="J105" s="10" t="n">
         <v>0.5</v>
@@ -6895,28 +6895,28 @@
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>Under 48.5</t>
+          <t>DAL -2.5</t>
         </is>
       </c>
       <c r="E106" s="12" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="F106" s="13" t="n">
-        <v>0.5</v>
+        <v>0.5092</v>
       </c>
       <c r="G106" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5349</v>
       </c>
       <c r="H106" s="13" t="n">
-        <v>-0.0224</v>
+        <v>-0.0239</v>
       </c>
       <c r="I106" s="13" t="n">
-        <v>-0.04545502351529379</v>
+        <v>-0.04797265926293287</v>
       </c>
       <c r="J106" s="14" t="n">
         <v>0.5</v>
@@ -6931,7 +6931,7 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>DAL @ NYG</t>
+          <t>GB @ MIN</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
@@ -6941,23 +6941,23 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>NYG +2.5</t>
+          <t>GB +1.5</t>
         </is>
       </c>
       <c r="E107" s="7" t="n">
-        <v>-105</v>
+        <v>-118</v>
       </c>
       <c r="F107" s="8" t="n">
-        <v>0.4879</v>
+        <v>0.5151</v>
       </c>
       <c r="G107" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.5413</v>
       </c>
       <c r="H107" s="8" t="n">
-        <v>-0.0228</v>
+        <v>-0.0244</v>
       </c>
       <c r="I107" s="8" t="n">
-        <v>-0.04745162229439381</v>
+        <v>-0.04837340421460867</v>
       </c>
       <c r="J107" s="10" t="n">
         <v>0.5</v>
@@ -6972,33 +6972,33 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>GB @ MIN</t>
+          <t>DAL @ NYG</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>GB +1.5</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="E108" s="12" t="n">
-        <v>-118</v>
+        <v>-110</v>
       </c>
       <c r="F108" s="13" t="n">
-        <v>0.5151</v>
+        <v>0.4975</v>
       </c>
       <c r="G108" s="13" t="n">
-        <v>0.5413</v>
+        <v>0.5238</v>
       </c>
       <c r="H108" s="13" t="n">
-        <v>-0.0244</v>
+        <v>-0.0245</v>
       </c>
       <c r="I108" s="13" t="n">
-        <v>-0.04837340421460867</v>
+        <v>-0.05030935703973494</v>
       </c>
       <c r="J108" s="14" t="n">
         <v>0.5</v>
@@ -7177,33 +7177,33 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>DAL @ NYG</t>
+          <t>DET @ BUF</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>DAL ML</t>
+          <t>DET +3</t>
         </is>
       </c>
       <c r="E113" s="7" t="n">
-        <v>-148</v>
+        <v>-110</v>
       </c>
       <c r="F113" s="8" t="n">
-        <v>0.5676</v>
+        <v>0.4926</v>
       </c>
       <c r="G113" s="8" t="n">
-        <v>0.5968</v>
+        <v>0.5238</v>
       </c>
       <c r="H113" s="8" t="n">
-        <v>-0.0267</v>
+        <v>-0.0282</v>
       </c>
       <c r="I113" s="8" t="n">
-        <v>-0.04839268785189488</v>
+        <v>-0.05520045726031053</v>
       </c>
       <c r="J113" s="10" t="n">
         <v>0.5</v>
@@ -7218,33 +7218,33 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>DET @ BUF</t>
+          <t>ATL @ PIT</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>DET +3</t>
+          <t>PIT ML</t>
         </is>
       </c>
       <c r="E114" s="12" t="n">
-        <v>-110</v>
+        <v>-175</v>
       </c>
       <c r="F114" s="13" t="n">
-        <v>0.4926</v>
+        <v>0.6048</v>
       </c>
       <c r="G114" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.6364</v>
       </c>
       <c r="H114" s="13" t="n">
-        <v>-0.0282</v>
+        <v>-0.0285</v>
       </c>
       <c r="I114" s="13" t="n">
-        <v>-0.05520045726031053</v>
+        <v>-0.04915349941279379</v>
       </c>
       <c r="J114" s="14" t="n">
         <v>0.5</v>
@@ -7259,7 +7259,7 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>ATL @ PIT</t>
+          <t>DAL @ NYG</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
@@ -7269,23 +7269,23 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>PIT ML</t>
+          <t>DAL ML</t>
         </is>
       </c>
       <c r="E115" s="7" t="n">
-        <v>-175</v>
+        <v>-148</v>
       </c>
       <c r="F115" s="8" t="n">
-        <v>0.6048</v>
+        <v>0.5647</v>
       </c>
       <c r="G115" s="8" t="n">
-        <v>0.6364</v>
+        <v>0.5968</v>
       </c>
       <c r="H115" s="8" t="n">
-        <v>-0.0285</v>
+        <v>-0.0288</v>
       </c>
       <c r="I115" s="8" t="n">
-        <v>-0.04915349941279379</v>
+        <v>-0.0531930963995294</v>
       </c>
       <c r="J115" s="10" t="n">
         <v>0.5</v>
@@ -7399,16 +7399,16 @@
         <v>-115</v>
       </c>
       <c r="F118" s="13" t="n">
-        <v>0.4996</v>
+        <v>0.5003</v>
       </c>
       <c r="G118" s="13" t="n">
         <v>0.5349</v>
       </c>
       <c r="H118" s="13" t="n">
-        <v>-0.0311</v>
+        <v>-0.0306</v>
       </c>
       <c r="I118" s="13" t="n">
-        <v>-0.06599959108328007</v>
+        <v>-0.06465119749463816</v>
       </c>
       <c r="J118" s="14" t="n">
         <v>0.5</v>
@@ -7567,16 +7567,16 @@
         <v>-198</v>
       </c>
       <c r="F122" s="13" t="n">
-        <v>0.6244</v>
+        <v>0.6251</v>
       </c>
       <c r="G122" s="13" t="n">
         <v>0.6644</v>
       </c>
       <c r="H122" s="13" t="n">
-        <v>-0.0342</v>
+        <v>-0.0338</v>
       </c>
       <c r="I122" s="13" t="n">
-        <v>-0.05977886130566457</v>
+        <v>-0.05873299277527144</v>
       </c>
       <c r="J122" s="14" t="n">
         <v>0.5</v>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>SEA @ KC</t>
+          <t>BAL @ IND</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
@@ -7814,32 +7814,28 @@
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>SEA ML</t>
+          <t>BAL ML</t>
         </is>
       </c>
       <c r="E128" s="12" t="n">
-        <v>106</v>
+        <v>-175</v>
       </c>
       <c r="F128" s="13" t="n">
-        <v>0.4403</v>
+        <v>0.5886</v>
       </c>
       <c r="G128" s="13" t="n">
-        <v>0.4854</v>
+        <v>0.6364</v>
       </c>
       <c r="H128" s="13" t="n">
-        <v>-0.0371</v>
+        <v>-0.0385</v>
       </c>
       <c r="I128" s="13" t="n">
-        <v>-0.09212307533405412</v>
+        <v>-0.07443975605449066</v>
       </c>
       <c r="J128" s="14" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K128" s="5" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K128" s="5" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
@@ -7849,38 +7845,42 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>BAL @ IND</t>
+          <t>PIT @ BUF</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>BAL ML</t>
+          <t>PIT +3</t>
         </is>
       </c>
       <c r="E129" s="7" t="n">
-        <v>-175</v>
+        <v>-112</v>
       </c>
       <c r="F129" s="8" t="n">
-        <v>0.5886</v>
+        <v>0.4802</v>
       </c>
       <c r="G129" s="8" t="n">
-        <v>0.6364</v>
+        <v>0.5283</v>
       </c>
       <c r="H129" s="8" t="n">
-        <v>-0.0385</v>
+        <v>-0.0387</v>
       </c>
       <c r="I129" s="8" t="n">
-        <v>-0.07443975605449066</v>
+        <v>-0.08443032251086047</v>
       </c>
       <c r="J129" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K129" s="4" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K129" s="4" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
@@ -7890,33 +7890,33 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>PIT @ BUF</t>
+          <t>SEA @ KC</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>PIT +3</t>
+          <t>SEA ML</t>
         </is>
       </c>
       <c r="E130" s="12" t="n">
-        <v>-112</v>
+        <v>104</v>
       </c>
       <c r="F130" s="13" t="n">
-        <v>0.4802</v>
+        <v>0.4421</v>
       </c>
       <c r="G130" s="13" t="n">
-        <v>0.5283</v>
+        <v>0.4902</v>
       </c>
       <c r="H130" s="13" t="n">
         <v>-0.0387</v>
       </c>
       <c r="I130" s="13" t="n">
-        <v>-0.08443032251086047</v>
+        <v>-0.09726550442471876</v>
       </c>
       <c r="J130" s="14" t="n">
         <v>0.15</v>
@@ -8058,38 +8058,42 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>BAL @ IND</t>
+          <t>CIN @ PHI</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>BAL -3.5</t>
+          <t>PHI ML</t>
         </is>
       </c>
       <c r="E134" s="12" t="n">
-        <v>-108</v>
+        <v>-152</v>
       </c>
       <c r="F134" s="13" t="n">
-        <v>0.4679</v>
+        <v>0.5525</v>
       </c>
       <c r="G134" s="13" t="n">
-        <v>0.5192</v>
+        <v>0.6032</v>
       </c>
       <c r="H134" s="13" t="n">
-        <v>-0.0403</v>
+        <v>-0.04</v>
       </c>
       <c r="I134" s="13" t="n">
-        <v>-0.09889806147849689</v>
+        <v>-0.08332647212039995</v>
       </c>
       <c r="J134" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K134" s="5" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K134" s="5" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
@@ -8099,33 +8103,33 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>DEN @ KC</t>
+          <t>BAL @ IND</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Over 42.5</t>
+          <t>BAL -3.5</t>
         </is>
       </c>
       <c r="E135" s="7" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="F135" s="8" t="n">
-        <v>0.4721</v>
+        <v>0.4679</v>
       </c>
       <c r="G135" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5192</v>
       </c>
       <c r="H135" s="8" t="n">
-        <v>-0.0404</v>
+        <v>-0.0403</v>
       </c>
       <c r="I135" s="8" t="n">
-        <v>-0.09874913496091675</v>
+        <v>-0.09889806147849689</v>
       </c>
       <c r="J135" s="10" t="n">
         <v>0.5</v>
@@ -8140,42 +8144,38 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>HOU @ CAR</t>
+          <t>DEN @ KC</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>HOU ML</t>
+          <t>Over 42.5</t>
         </is>
       </c>
       <c r="E136" s="12" t="n">
-        <v>-144</v>
+        <v>-110</v>
       </c>
       <c r="F136" s="13" t="n">
-        <v>0.5379</v>
+        <v>0.4721</v>
       </c>
       <c r="G136" s="13" t="n">
-        <v>0.5901999999999999</v>
+        <v>0.5238</v>
       </c>
       <c r="H136" s="13" t="n">
-        <v>-0.0407</v>
+        <v>-0.0404</v>
       </c>
       <c r="I136" s="13" t="n">
-        <v>-0.08779449906398951</v>
+        <v>-0.09874913496091675</v>
       </c>
       <c r="J136" s="14" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K136" s="5" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K136" s="5" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
@@ -8185,38 +8185,42 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>SF @ LAR</t>
+          <t>HOU @ CAR</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>LAR -3.5</t>
+          <t>HOU ML</t>
         </is>
       </c>
       <c r="E137" s="7" t="n">
-        <v>-105</v>
+        <v>-144</v>
       </c>
       <c r="F137" s="8" t="n">
-        <v>0.4597</v>
+        <v>0.5379</v>
       </c>
       <c r="G137" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="H137" s="8" t="n">
-        <v>-0.0408</v>
+        <v>-0.0407</v>
       </c>
       <c r="I137" s="8" t="n">
-        <v>-0.1024475989508608</v>
+        <v>-0.08779449906398951</v>
       </c>
       <c r="J137" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K137" s="4" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K137" s="4" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
@@ -8226,7 +8230,7 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>NE @ CLE</t>
+          <t>SF @ LAR</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
@@ -8236,32 +8240,28 @@
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>CLE +2.5</t>
+          <t>LAR -3.5</t>
         </is>
       </c>
       <c r="E138" s="12" t="n">
         <v>-105</v>
       </c>
       <c r="F138" s="13" t="n">
-        <v>0.4595</v>
+        <v>0.4597</v>
       </c>
       <c r="G138" s="13" t="n">
         <v>0.5122</v>
       </c>
       <c r="H138" s="13" t="n">
-        <v>-0.0409</v>
+        <v>-0.0408</v>
       </c>
       <c r="I138" s="13" t="n">
-        <v>-0.1029270500313946</v>
+        <v>-0.1024475989508608</v>
       </c>
       <c r="J138" s="14" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K138" s="5" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K138" s="5" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
@@ -8271,33 +8271,33 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>CIN @ PHI</t>
+          <t>NE @ CLE</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>PHI ML</t>
+          <t>CLE +2.5</t>
         </is>
       </c>
       <c r="E139" s="7" t="n">
-        <v>-155</v>
+        <v>-105</v>
       </c>
       <c r="F139" s="8" t="n">
-        <v>0.5538999999999999</v>
+        <v>0.4595</v>
       </c>
       <c r="G139" s="8" t="n">
-        <v>0.6078</v>
+        <v>0.5122</v>
       </c>
       <c r="H139" s="8" t="n">
-        <v>-0.0415</v>
+        <v>-0.0409</v>
       </c>
       <c r="I139" s="8" t="n">
-        <v>-0.0880069805900533</v>
+        <v>-0.1029270500313946</v>
       </c>
       <c r="J139" s="10" t="n">
         <v>0.15</v>
@@ -9227,23 +9227,23 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>DEN -6</t>
+          <t>DEN -6.5</t>
         </is>
       </c>
       <c r="E161" s="7" t="n">
-        <v>-112</v>
+        <v>-108</v>
       </c>
       <c r="F161" s="8" t="n">
-        <v>0.4629</v>
+        <v>0.4541</v>
       </c>
       <c r="G161" s="8" t="n">
-        <v>0.5283</v>
+        <v>0.5192</v>
       </c>
       <c r="H161" s="8" t="n">
-        <v>-0.0457</v>
+        <v>-0.0456</v>
       </c>
       <c r="I161" s="8" t="n">
-        <v>-0.1193157194379108</v>
+        <v>-0.1253443970733136</v>
       </c>
       <c r="J161" s="10" t="n">
         <v>0.15</v>
@@ -9279,16 +9279,16 @@
         <v>-156</v>
       </c>
       <c r="F162" s="13" t="n">
-        <v>0.5435</v>
+        <v>0.5431</v>
       </c>
       <c r="G162" s="13" t="n">
         <v>0.6094000000000001</v>
       </c>
       <c r="H162" s="13" t="n">
-        <v>-0.0458</v>
+        <v>-0.0459</v>
       </c>
       <c r="I162" s="13" t="n">
-        <v>-0.107120555488541</v>
+        <v>-0.1077142006461029</v>
       </c>
       <c r="J162" s="14" t="n">
         <v>0.15</v>
@@ -9307,38 +9307,42 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>MIA @ LV</t>
+          <t>NYG @ NYJ</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>Under 40.5</t>
+          <t>NYG -3</t>
         </is>
       </c>
       <c r="E163" s="7" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="F163" s="8" t="n">
-        <v>0.457</v>
+        <v>0.4682</v>
       </c>
       <c r="G163" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5349</v>
       </c>
       <c r="H163" s="8" t="n">
         <v>-0.0461</v>
       </c>
       <c r="I163" s="8" t="n">
-        <v>-0.1276251689568088</v>
+        <v>-0.1158249279882236</v>
       </c>
       <c r="J163" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K163" s="4" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K163" s="4" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
@@ -9348,42 +9352,38 @@
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>LAR @ LAC</t>
+          <t>MIA @ LV</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>LAC -3.5</t>
+          <t>Under 40.5</t>
         </is>
       </c>
       <c r="E164" s="12" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="F164" s="13" t="n">
-        <v>0.4609</v>
+        <v>0.457</v>
       </c>
       <c r="G164" s="13" t="n">
-        <v>0.5283</v>
+        <v>0.5238</v>
       </c>
       <c r="H164" s="13" t="n">
-        <v>-0.0463</v>
+        <v>-0.0461</v>
       </c>
       <c r="I164" s="13" t="n">
-        <v>-0.1275004997636998</v>
+        <v>-0.1276251689568088</v>
       </c>
       <c r="J164" s="14" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K164" s="5" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K164" s="5" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
@@ -9393,33 +9393,33 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>ATL @ MIA</t>
+          <t>LAR @ LAC</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>ATL ML</t>
+          <t>LAC -3.5</t>
         </is>
       </c>
       <c r="E165" s="7" t="n">
-        <v>-191</v>
+        <v>-112</v>
       </c>
       <c r="F165" s="8" t="n">
-        <v>0.5884</v>
+        <v>0.4609</v>
       </c>
       <c r="G165" s="8" t="n">
-        <v>0.6564</v>
+        <v>0.5283</v>
       </c>
       <c r="H165" s="8" t="n">
-        <v>-0.0464</v>
+        <v>-0.0463</v>
       </c>
       <c r="I165" s="8" t="n">
-        <v>-0.1025987872915858</v>
+        <v>-0.1275004997636998</v>
       </c>
       <c r="J165" s="10" t="n">
         <v>0.15</v>
@@ -9438,33 +9438,33 @@
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>NYG @ NYJ</t>
+          <t>ATL @ MIA</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>NYG -3</t>
+          <t>ATL ML</t>
         </is>
       </c>
       <c r="E166" s="12" t="n">
-        <v>-115</v>
+        <v>-191</v>
       </c>
       <c r="F166" s="13" t="n">
-        <v>0.4661</v>
+        <v>0.5884</v>
       </c>
       <c r="G166" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.6564</v>
       </c>
       <c r="H166" s="13" t="n">
-        <v>-0.0467</v>
+        <v>-0.0464</v>
       </c>
       <c r="I166" s="13" t="n">
-        <v>-0.1194812544089797</v>
+        <v>-0.1025987872915858</v>
       </c>
       <c r="J166" s="14" t="n">
         <v>0.15</v>
@@ -9528,17 +9528,17 @@
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>TB @ JAX</t>
+          <t>ARI @ LAC</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>TB -3</t>
+          <t>Over 46.5</t>
         </is>
       </c>
       <c r="E168" s="12" t="n">
@@ -9554,16 +9554,12 @@
         <v>-0.0468</v>
       </c>
       <c r="I168" s="13" t="n">
-        <v>-0.1229706592278252</v>
+        <v>-0.1323971774011638</v>
       </c>
       <c r="J168" s="14" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K168" s="5" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K168" s="5" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
@@ -9573,38 +9569,42 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>ARI @ LAC</t>
+          <t>TB @ JAX</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>Over 46.5</t>
+          <t>TB -3</t>
         </is>
       </c>
       <c r="E169" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F169" s="8" t="n">
-        <v>0.4545</v>
+        <v>0.4541</v>
       </c>
       <c r="G169" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H169" s="8" t="n">
-        <v>-0.0468</v>
+        <v>-0.0469</v>
       </c>
       <c r="I169" s="8" t="n">
-        <v>-0.1323971774011638</v>
+        <v>-0.1236459032538395</v>
       </c>
       <c r="J169" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K169" s="4" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K169" s="4" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="5" t="inlineStr">
@@ -9741,7 +9741,7 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>NYG @ NYJ</t>
+          <t>MIN @ DEN</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
@@ -9751,23 +9751,23 @@
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>NYG ML</t>
+          <t>DEN ML</t>
         </is>
       </c>
       <c r="E173" s="7" t="n">
-        <v>-173</v>
+        <v>-287</v>
       </c>
       <c r="F173" s="8" t="n">
-        <v>0.5596</v>
+        <v>0.6682</v>
       </c>
       <c r="G173" s="8" t="n">
-        <v>0.6337</v>
+        <v>0.7416</v>
       </c>
       <c r="H173" s="8" t="n">
-        <v>-0.048</v>
+        <v>-0.0479</v>
       </c>
       <c r="I173" s="8" t="n">
-        <v>-0.1158293344332618</v>
+        <v>-0.09817789651343922</v>
       </c>
       <c r="J173" s="10" t="n">
         <v>0.15</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>MIN @ DEN</t>
+          <t>NYG @ NYJ</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
@@ -9796,23 +9796,23 @@
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>DEN ML</t>
+          <t>NYG ML</t>
         </is>
       </c>
       <c r="E174" s="12" t="n">
-        <v>-279</v>
+        <v>-175</v>
       </c>
       <c r="F174" s="13" t="n">
-        <v>0.6621</v>
+        <v>0.5623</v>
       </c>
       <c r="G174" s="13" t="n">
-        <v>0.7361</v>
+        <v>0.6364</v>
       </c>
       <c r="H174" s="13" t="n">
         <v>-0.048</v>
       </c>
       <c r="I174" s="13" t="n">
-        <v>-0.09977622696744701</v>
+        <v>-0.1152978777350247</v>
       </c>
       <c r="J174" s="14" t="n">
         <v>0.15</v>
@@ -10089,38 +10089,42 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>WSH @ PHI</t>
+          <t>SF @ LV</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>Over 46.5</t>
+          <t>LV -3.5</t>
         </is>
       </c>
       <c r="E181" s="7" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="F181" s="8" t="n">
-        <v>0.442</v>
+        <v>0.4305</v>
       </c>
       <c r="G181" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5122</v>
       </c>
       <c r="H181" s="8" t="n">
-        <v>-0.0497</v>
+        <v>-0.0496</v>
       </c>
       <c r="I181" s="8" t="n">
-        <v>-0.1561855591186524</v>
+        <v>-0.1594496555703148</v>
       </c>
       <c r="J181" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K181" s="4" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K181" s="4" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="5" t="inlineStr">
@@ -10130,42 +10134,38 @@
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>ARI @ GB</t>
+          <t>WSH @ PHI</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>ARI ML</t>
+          <t>Over 46.5</t>
         </is>
       </c>
       <c r="E182" s="12" t="n">
-        <v>-146</v>
+        <v>-110</v>
       </c>
       <c r="F182" s="13" t="n">
-        <v>0.5106000000000001</v>
+        <v>0.442</v>
       </c>
       <c r="G182" s="13" t="n">
-        <v>0.5935</v>
+        <v>0.5238</v>
       </c>
       <c r="H182" s="13" t="n">
-        <v>-0.0498</v>
+        <v>-0.0497</v>
       </c>
       <c r="I182" s="13" t="n">
-        <v>-0.1383534680448956</v>
+        <v>-0.1561855591186524</v>
       </c>
       <c r="J182" s="14" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K182" s="5" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K182" s="5" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>SF @ LV</t>
+          <t>ARI @ GB</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
@@ -10185,23 +10185,23 @@
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>LV ML</t>
+          <t>ARI ML</t>
         </is>
       </c>
       <c r="E183" s="7" t="n">
-        <v>-174</v>
+        <v>-146</v>
       </c>
       <c r="F183" s="8" t="n">
-        <v>0.552</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="G183" s="8" t="n">
-        <v>0.635</v>
+        <v>0.5935</v>
       </c>
       <c r="H183" s="8" t="n">
-        <v>-0.0499</v>
+        <v>-0.0498</v>
       </c>
       <c r="I183" s="8" t="n">
-        <v>-0.1296335457567894</v>
+        <v>-0.1383534680448956</v>
       </c>
       <c r="J183" s="10" t="n">
         <v>0.15</v>
@@ -10220,33 +10220,33 @@
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>SEA @ KC</t>
+          <t>SF @ LV</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>Under 36.5</t>
+          <t>LV ML</t>
         </is>
       </c>
       <c r="E184" s="12" t="n">
-        <v>-110</v>
+        <v>-174</v>
       </c>
       <c r="F184" s="13" t="n">
-        <v>0.4395</v>
+        <v>0.552</v>
       </c>
       <c r="G184" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.635</v>
       </c>
       <c r="H184" s="13" t="n">
-        <v>-0.0501</v>
+        <v>-0.0499</v>
       </c>
       <c r="I184" s="13" t="n">
-        <v>-0.1609576252652765</v>
+        <v>-0.1296335457567894</v>
       </c>
       <c r="J184" s="14" t="n">
         <v>0.15</v>
@@ -10265,7 +10265,7 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>SF @ LV</t>
+          <t>ATL @ MIA</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
@@ -10275,23 +10275,23 @@
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>LV -3.5</t>
+          <t>ATL -4.5</t>
         </is>
       </c>
       <c r="E185" s="7" t="n">
-        <v>-108</v>
+        <v>-115</v>
       </c>
       <c r="F185" s="8" t="n">
-        <v>0.4328</v>
+        <v>0.4458</v>
       </c>
       <c r="G185" s="8" t="n">
-        <v>0.5192</v>
+        <v>0.5349</v>
       </c>
       <c r="H185" s="8" t="n">
-        <v>-0.0504</v>
+        <v>-0.0508</v>
       </c>
       <c r="I185" s="8" t="n">
-        <v>-0.1664547238731173</v>
+        <v>-0.1664669501795517</v>
       </c>
       <c r="J185" s="10" t="n">
         <v>0.15</v>
@@ -10310,33 +10310,33 @@
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>ATL @ MIA</t>
+          <t>SEA @ KC</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>ATL -4.5</t>
+          <t>Under 36.5</t>
         </is>
       </c>
       <c r="E186" s="12" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="F186" s="13" t="n">
-        <v>0.4458</v>
+        <v>0.4321</v>
       </c>
       <c r="G186" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.5238</v>
       </c>
       <c r="H186" s="13" t="n">
-        <v>-0.0508</v>
+        <v>-0.0512</v>
       </c>
       <c r="I186" s="13" t="n">
-        <v>-0.1664669501795517</v>
+        <v>-0.1750708294426935</v>
       </c>
       <c r="J186" s="14" t="n">
         <v>0.15</v>
@@ -10441,7 +10441,7 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>NYJ @ TEN</t>
+          <t>ARI @ GB</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
@@ -10455,24 +10455,28 @@
         </is>
       </c>
       <c r="E189" s="7" t="n">
-        <v>-105</v>
+        <v>-115</v>
       </c>
       <c r="F189" s="8" t="n">
-        <v>0.4065</v>
+        <v>0.4286</v>
       </c>
       <c r="G189" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.5349</v>
       </c>
       <c r="H189" s="8" t="n">
         <v>-0.0527</v>
       </c>
       <c r="I189" s="8" t="n">
-        <v>-0.2063365822009</v>
+        <v>-0.1987563133002072</v>
       </c>
       <c r="J189" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K189" s="4" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K189" s="4" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="5" t="inlineStr">
@@ -10482,7 +10486,7 @@
       </c>
       <c r="B190" s="5" t="inlineStr">
         <is>
-          <t>HOU @ CAR</t>
+          <t>NYJ @ TEN</t>
         </is>
       </c>
       <c r="C190" s="5" t="inlineStr">
@@ -10492,32 +10496,28 @@
       </c>
       <c r="D190" s="5" t="inlineStr">
         <is>
-          <t>Under 36.5</t>
+          <t>Under 38.5</t>
         </is>
       </c>
       <c r="E190" s="12" t="n">
-        <v>-115</v>
+        <v>-105</v>
       </c>
       <c r="F190" s="13" t="n">
-        <v>0.4261</v>
+        <v>0.4065</v>
       </c>
       <c r="G190" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.5122</v>
       </c>
       <c r="H190" s="13" t="n">
-        <v>-0.0529</v>
+        <v>-0.0527</v>
       </c>
       <c r="I190" s="13" t="n">
-        <v>-0.2033204710805889</v>
+        <v>-0.2063365822009</v>
       </c>
       <c r="J190" s="14" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K190" s="5" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K190" s="5" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
@@ -10527,7 +10527,7 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>SF @ LV</t>
+          <t>HOU @ CAR</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
@@ -10537,23 +10537,23 @@
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>Under 37.5</t>
+          <t>Under 36.5</t>
         </is>
       </c>
       <c r="E191" s="7" t="n">
-        <v>-112</v>
+        <v>-115</v>
       </c>
       <c r="F191" s="8" t="n">
-        <v>0.4166</v>
+        <v>0.4261</v>
       </c>
       <c r="G191" s="8" t="n">
-        <v>0.5283</v>
+        <v>0.5349</v>
       </c>
       <c r="H191" s="8" t="n">
-        <v>-0.0531</v>
+        <v>-0.0529</v>
       </c>
       <c r="I191" s="8" t="n">
-        <v>-0.211417781705342</v>
+        <v>-0.2033204710805889</v>
       </c>
       <c r="J191" s="10" t="n">
         <v>0.15</v>
@@ -10572,7 +10572,7 @@
       </c>
       <c r="B192" s="5" t="inlineStr">
         <is>
-          <t>LAR @ LAC</t>
+          <t>SF @ LV</t>
         </is>
       </c>
       <c r="C192" s="5" t="inlineStr">
@@ -10582,23 +10582,23 @@
       </c>
       <c r="D192" s="5" t="inlineStr">
         <is>
-          <t>Under 38.5</t>
+          <t>Under 37.5</t>
         </is>
       </c>
       <c r="E192" s="12" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="F192" s="13" t="n">
-        <v>0.4103</v>
+        <v>0.4166</v>
       </c>
       <c r="G192" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5283</v>
       </c>
       <c r="H192" s="13" t="n">
-        <v>-0.0533</v>
+        <v>-0.0531</v>
       </c>
       <c r="I192" s="13" t="n">
-        <v>-0.2166952010550791</v>
+        <v>-0.211417781705342</v>
       </c>
       <c r="J192" s="14" t="n">
         <v>0.15</v>
@@ -10617,7 +10617,7 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>ARI @ GB</t>
+          <t>LAR @ LAC</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
@@ -10631,19 +10631,19 @@
         </is>
       </c>
       <c r="E193" s="7" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="F193" s="8" t="n">
-        <v>0.4213</v>
+        <v>0.4103</v>
       </c>
       <c r="G193" s="8" t="n">
-        <v>0.5349</v>
+        <v>0.5238</v>
       </c>
       <c r="H193" s="8" t="n">
         <v>-0.0533</v>
       </c>
       <c r="I193" s="8" t="n">
-        <v>-0.2123541960560287</v>
+        <v>-0.2166952010550791</v>
       </c>
       <c r="J193" s="10" t="n">
         <v>0.15</v>
@@ -10949,16 +10949,16 @@
         <v>-110</v>
       </c>
       <c r="F200" s="13" t="n">
-        <v>0.3961</v>
+        <v>0.3915</v>
       </c>
       <c r="G200" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H200" s="13" t="n">
-        <v>-0.054</v>
+        <v>-0.0541</v>
       </c>
       <c r="I200" s="13" t="n">
-        <v>-0.2437904321251443</v>
+        <v>-0.252672518117221</v>
       </c>
       <c r="J200" s="14" t="n">
         <v>0.15</v>
@@ -11928,13 +11928,13 @@
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>-2.33</v>
+        <v>-2.17</v>
       </c>
       <c r="E10" s="9" t="n">
         <v>2.5</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="G10" s="11" t="n">
         <v>48.5</v>
@@ -12336,7 +12336,7 @@
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>4.24</v>
+        <v>4.28</v>
       </c>
       <c r="E22" s="9" t="n">
         <v>-3.5</v>
@@ -12506,10 +12506,10 @@
         </is>
       </c>
       <c r="D27" s="24" t="n">
-        <v>5.02</v>
+        <v>5.28</v>
       </c>
       <c r="E27" s="24" t="n">
-        <v>-6</v>
+        <v>-6.5</v>
       </c>
       <c r="F27" s="25" t="n">
         <v>40.6</v>
@@ -12580,7 +12580,7 @@
         <v>-1.5</v>
       </c>
       <c r="F29" s="25" t="n">
-        <v>38.9</v>
+        <v>39.2</v>
       </c>
       <c r="G29" s="25" t="n">
         <v>36.5</v>
@@ -12648,7 +12648,7 @@
         <v>2.5</v>
       </c>
       <c r="F31" s="25" t="n">
-        <v>41.8</v>
+        <v>41.5</v>
       </c>
       <c r="G31" s="25" t="n">
         <v>38.5</v>
@@ -12676,7 +12676,7 @@
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>-1.21</v>
+        <v>-1.32</v>
       </c>
       <c r="E32" s="9" t="n">
         <v>3</v>
@@ -12710,7 +12710,7 @@
         </is>
       </c>
       <c r="D33" s="24" t="n">
-        <v>-0.8</v>
+        <v>-0.78</v>
       </c>
       <c r="E33" s="24" t="n">
         <v>3</v>
@@ -12954,7 +12954,7 @@
         <v>-3</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>39.7</v>
+        <v>39.9</v>
       </c>
       <c r="G40" s="11" t="n">
         <v>35.5</v>
@@ -16177,10 +16177,10 @@
         <v>36.5</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>-173</v>
+        <v>-175</v>
       </c>
       <c r="J45" s="7" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K45" s="15" t="n">
         <v>0</v>
@@ -16283,10 +16283,10 @@
         <v>36.5</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J47" s="7" t="n">
-        <v>-155</v>
+        <v>-152</v>
       </c>
       <c r="K47" s="15" t="n">
         <v>0</v>
@@ -16336,10 +16336,10 @@
         <v>36.5</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>-127</v>
+        <v>-124</v>
       </c>
       <c r="K48" s="17" t="n">
         <v>0</v>
@@ -16489,16 +16489,16 @@
         </is>
       </c>
       <c r="G51" s="9" t="n">
-        <v>-6</v>
+        <v>-6.5</v>
       </c>
       <c r="H51" s="11" t="n">
         <v>39.5</v>
       </c>
       <c r="I51" s="7" t="n">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="J51" s="7" t="n">
-        <v>-279</v>
+        <v>-287</v>
       </c>
       <c r="K51" s="15" t="n">
         <v>0</v>
@@ -19302,10 +19302,10 @@
         <v>45.5</v>
       </c>
       <c r="I104" s="12" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="J104" s="12" t="n">
-        <v>-325</v>
+        <v>-310</v>
       </c>
       <c r="K104" s="17" t="n">
         <v>0</v>
@@ -21104,10 +21104,10 @@
         <v>44.5</v>
       </c>
       <c r="I138" s="12" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="J138" s="12" t="n">
-        <v>-135</v>
+        <v>-142</v>
       </c>
       <c r="K138" s="17" t="n">
         <v>0</v>
@@ -21899,10 +21899,10 @@
         <v>43.5</v>
       </c>
       <c r="I153" s="7" t="n">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="J153" s="7" t="n">
-        <v>-245</v>
+        <v>-238</v>
       </c>
       <c r="K153" s="15" t="n">
         <v>0</v>
@@ -27517,10 +27517,10 @@
         <v>45.5</v>
       </c>
       <c r="I259" s="7" t="n">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="J259" s="7" t="n">
-        <v>-375</v>
+        <v>-380</v>
       </c>
       <c r="K259" s="15" t="n">
         <v>0</v>
@@ -29849,10 +29849,10 @@
         <v>49.5</v>
       </c>
       <c r="I303" s="7" t="n">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="J303" s="7" t="n">
-        <v>-225</v>
+        <v>-218</v>
       </c>
       <c r="K303" s="15" t="n">
         <v>0</v>
@@ -33228,27 +33228,27 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Danny Pinter</t>
+          <t>Jamon Johnson</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Out</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Surgery</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>out</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -33260,27 +33260,27 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>Jamon Johnson</t>
+          <t>Danny Pinter</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Surgery</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>out</t>
         </is>
       </c>
     </row>
@@ -42732,7 +42732,7 @@
       </c>
       <c r="F355" s="4" t="inlineStr">
         <is>
-          <t>Thomas (upper body) was shaken up after catching a touchdown in joint practice Tuesday against the Buccaneers but is still in full uniform, Mia O'Brien of 1010 XL 92.5 FM Jacksonville reports.</t>
+          <t>Thomas (shoulder) was present on the field for Wednesday's joint practice with the Buccaneers while sporting a no-contact jersey, John Shipley of SI.com reports.</t>
         </is>
       </c>
     </row>
@@ -49860,7 +49860,7 @@
       </c>
       <c r="B580" s="5" t="inlineStr">
         <is>
-          <t>Calvin Austin III</t>
+          <t>Odell Beckham Jr.</t>
         </is>
       </c>
       <c r="C580" s="5" t="inlineStr">
@@ -49870,17 +49870,17 @@
       </c>
       <c r="D580" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E580" s="5" t="inlineStr">
         <is>
-          <t>Knee</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F580" s="5" t="inlineStr">
         <is>
-          <t>Austin was carted off the field at Tuesday's practice with an apparent right knee injury, Jordan Raanan of ESPN.com reports.</t>
+          <t>Beckham's chances of winning a spot on the Giants' 53-man roster appear to have increased after Calvin Austin (knee) sustained a season-ending ACL tear in Tuesday's practice, Jordan Raanan of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -49892,12 +49892,12 @@
       </c>
       <c r="B581" s="4" t="inlineStr">
         <is>
-          <t>Najee Harris</t>
+          <t>Malachi Fields</t>
         </is>
       </c>
       <c r="C581" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D581" s="4" t="inlineStr">
@@ -49912,7 +49912,7 @@
       </c>
       <c r="F581" s="4" t="inlineStr">
         <is>
-          <t>Harris is listed as the Giants' co-No. 2 RB along with Tyrone Tracy and Devin Singletary behind Cam Skattebo on the team's unofficial depth chart.</t>
+          <t>Fields could be one of multiple Giants receivers that benefits from added opportunities to begin the season after Calvin Austin (knee) sustained a torn ACL during Tuesday's practice, Jordan Raanan of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -49924,12 +49924,12 @@
       </c>
       <c r="B582" s="5" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Darnell Mooney</t>
         </is>
       </c>
       <c r="C582" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D582" s="5" t="inlineStr">
@@ -49944,7 +49944,7 @@
       </c>
       <c r="F582" s="5" t="inlineStr">
         <is>
-          <t>Skattebo is listed as the Giants' starting running back on the team's unofficial depth chart for the preseason finale versus the Jets, Jordan Raanan of ESPN.com reports.</t>
+          <t>Mooney could have a chance to open the season as the Giants' No. 3 receiver after Calvin Austin (knee) sustained a torn ACL in Tuesday's practice, Jordan Ranaan of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -49956,27 +49956,27 @@
       </c>
       <c r="B583" s="4" t="inlineStr">
         <is>
-          <t>Colton Hood</t>
+          <t>Calvin Austin III</t>
         </is>
       </c>
       <c r="C583" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D583" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Doubtful</t>
         </is>
       </c>
       <c r="E583" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Knee</t>
         </is>
       </c>
       <c r="F583" s="4" t="inlineStr">
         <is>
-          <t>Hood (quadriceps) is expected to return to practice this week, Paul Schwartz of New York Post reports.</t>
+          <t>Austin is expected to miss the 2026 season after he sustained a torn ACL in his right knee while running a route during Tuesday's practice, Jordan Raanan of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -49988,27 +49988,27 @@
       </c>
       <c r="B584" s="5" t="inlineStr">
         <is>
-          <t>Theo Johnson</t>
+          <t>Najee Harris</t>
         </is>
       </c>
       <c r="C584" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D584" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E584" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F584" s="5" t="inlineStr">
         <is>
-          <t>Johnson left Monday's practice due to an unspecified issue, Dan Benton of USA Today reports.</t>
+          <t>Harris is listed as the Giants' co-No. 2 RB along with Tyrone Tracy and Devin Singletary behind Cam Skattebo on the team's unofficial depth chart.</t>
         </is>
       </c>
     </row>
@@ -50020,27 +50020,27 @@
       </c>
       <c r="B585" s="4" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C585" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D585" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E585" s="4" t="inlineStr">
         <is>
-          <t>Surgery</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F585" s="4" t="inlineStr">
         <is>
-          <t>Giants coach John Harbaugh said Sunday that Nabers (knee) could be out of his red non-contact jersey at some point this week, Evan Barnes of Newsday reports.</t>
+          <t>Skattebo is listed as the Giants' starting running back on the team's unofficial depth chart for the preseason finale versus the Jets, Jordan Raanan of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -50052,12 +50052,12 @@
       </c>
       <c r="B586" s="5" t="inlineStr">
         <is>
-          <t>Joshua Ezeudu</t>
+          <t>Colton Hood</t>
         </is>
       </c>
       <c r="C586" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D586" s="5" t="inlineStr">
@@ -50072,7 +50072,7 @@
       </c>
       <c r="F586" s="5" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>Hood (quadriceps) is expected to return to practice this week, Paul Schwartz of New York Post reports.</t>
         </is>
       </c>
     </row>
@@ -50084,12 +50084,12 @@
       </c>
       <c r="B587" s="4" t="inlineStr">
         <is>
-          <t>Braxton Berrios</t>
+          <t>Theo Johnson</t>
         </is>
       </c>
       <c r="C587" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D587" s="4" t="inlineStr">
@@ -50104,7 +50104,7 @@
       </c>
       <c r="F587" s="4" t="inlineStr">
         <is>
-          <t>Head coach John Harbaugh told reporters that Berrios did not play in Saturday's 26-3 preseason win over the Dolphins due to a soft-tissue issue, Paul Schwartz of the New York Post reports.</t>
+          <t>Johnson left Monday's practice due to an unspecified issue, Dan Benton of USA Today reports.</t>
         </is>
       </c>
     </row>
@@ -50116,7 +50116,7 @@
       </c>
       <c r="B588" s="5" t="inlineStr">
         <is>
-          <t>Darius Slayton</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="C588" s="5" t="inlineStr">
@@ -50126,17 +50126,17 @@
       </c>
       <c r="D588" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E588" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Surgery</t>
         </is>
       </c>
       <c r="F588" s="5" t="inlineStr">
         <is>
-          <t>Slayton caught four of six targets for 58 yards in Saturday's 26-3 preseason win over the Dolphins.</t>
+          <t>Giants coach John Harbaugh said Sunday that Nabers (knee) could be out of his red non-contact jersey at some point this week, Evan Barnes of Newsday reports.</t>
         </is>
       </c>
     </row>
@@ -50148,27 +50148,27 @@
       </c>
       <c r="B589" s="4" t="inlineStr">
         <is>
-          <t>Tyrone Tracy Jr.</t>
+          <t>Braxton Berrios</t>
         </is>
       </c>
       <c r="C589" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D589" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E589" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F589" s="4" t="inlineStr">
         <is>
-          <t>Tracy rushed six times for 26 yards, caught all three of his targets for 22 yards and lost a fumble in Saturday's 26-3 preseason win over the Dolphins.</t>
+          <t>Head coach John Harbaugh told reporters that Berrios did not play in Saturday's 26-3 preseason win over the Dolphins due to a soft-tissue issue, Paul Schwartz of the New York Post reports.</t>
         </is>
       </c>
     </row>
@@ -50180,12 +50180,12 @@
       </c>
       <c r="B590" s="5" t="inlineStr">
         <is>
-          <t>Devin Singletary</t>
+          <t>Darius Slayton</t>
         </is>
       </c>
       <c r="C590" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D590" s="5" t="inlineStr">
@@ -50200,7 +50200,7 @@
       </c>
       <c r="F590" s="5" t="inlineStr">
         <is>
-          <t>Singletary rushed eight times for 40 yards and a touchdown while catching his only target for four yards in Saturday's 26-3 preseason win over the Dolphins.</t>
+          <t>Slayton caught four of six targets for 58 yards in Saturday's 26-3 preseason win over the Dolphins.</t>
         </is>
       </c>
     </row>
@@ -50212,12 +50212,12 @@
       </c>
       <c r="B591" s="4" t="inlineStr">
         <is>
-          <t>Jaxson Dart</t>
+          <t>Tyrone Tracy Jr.</t>
         </is>
       </c>
       <c r="C591" s="4" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D591" s="4" t="inlineStr">
@@ -50232,7 +50232,7 @@
       </c>
       <c r="F591" s="4" t="inlineStr">
         <is>
-          <t>Dart didn't suit up for Saturday's 26-3 preseason win over the Dolphins.</t>
+          <t>Tracy rushed six times for 26 yards, caught all three of his targets for 22 yards and lost a fumble in Saturday's 26-3 preseason win over the Dolphins.</t>
         </is>
       </c>
     </row>
@@ -50244,27 +50244,27 @@
       </c>
       <c r="B592" s="5" t="inlineStr">
         <is>
-          <t>Francis Mauigoa</t>
+          <t>Devin Singletary</t>
         </is>
       </c>
       <c r="C592" s="5" t="inlineStr">
         <is>
-          <t>OT</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D592" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E592" s="5" t="inlineStr">
         <is>
-          <t>Stinger</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F592" s="5" t="inlineStr">
         <is>
-          <t>Mauigoa (upper body) had to leave Thursday's joint practice with the Dolphins due to a stinger, Dan Benton of USA Today reports.</t>
+          <t>Singletary rushed eight times for 40 yards and a touchdown while catching his only target for four yards in Saturday's 26-3 preseason win over the Dolphins.</t>
         </is>
       </c>
     </row>
@@ -50276,27 +50276,27 @@
       </c>
       <c r="B593" s="4" t="inlineStr">
         <is>
-          <t>Greg Newsome II</t>
+          <t>Jaxson Dart</t>
         </is>
       </c>
       <c r="C593" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D593" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E593" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F593" s="4" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>Dart didn't suit up for Saturday's 26-3 preseason win over the Dolphins.</t>
         </is>
       </c>
     </row>
@@ -50308,12 +50308,12 @@
       </c>
       <c r="B594" s="5" t="inlineStr">
         <is>
-          <t>Lucas Patrick</t>
+          <t>Francis Mauigoa</t>
         </is>
       </c>
       <c r="C594" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>OT</t>
         </is>
       </c>
       <c r="D594" s="5" t="inlineStr">
@@ -50323,12 +50323,12 @@
       </c>
       <c r="E594" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Stinger</t>
         </is>
       </c>
       <c r="F594" s="5" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>Mauigoa (upper body) had to leave Thursday's joint practice with the Dolphins due to a stinger, Dan Benton of USA Today reports.</t>
         </is>
       </c>
     </row>
@@ -50340,7 +50340,7 @@
       </c>
       <c r="B595" s="4" t="inlineStr">
         <is>
-          <t>Dru Phillips</t>
+          <t>Greg Newsome II</t>
         </is>
       </c>
       <c r="C595" s="4" t="inlineStr">
@@ -50355,7 +50355,7 @@
       </c>
       <c r="E595" s="4" t="inlineStr">
         <is>
-          <t>Sprain</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F595" s="4" t="inlineStr">
@@ -50372,27 +50372,27 @@
       </c>
       <c r="B596" s="5" t="inlineStr">
         <is>
-          <t>Roy Robertson-Harris</t>
+          <t>Lucas Patrick</t>
         </is>
       </c>
       <c r="C596" s="5" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D596" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E596" s="5" t="inlineStr">
         <is>
-          <t>Surgery</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F596" s="5" t="inlineStr">
         <is>
-          <t>ir</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -50404,12 +50404,12 @@
       </c>
       <c r="B597" s="4" t="inlineStr">
         <is>
-          <t>John Michael Schmitz Jr.</t>
+          <t>Dru Phillips</t>
         </is>
       </c>
       <c r="C597" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D597" s="4" t="inlineStr">
@@ -50419,7 +50419,7 @@
       </c>
       <c r="E597" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Sprain</t>
         </is>
       </c>
       <c r="F597" s="4" t="inlineStr">
@@ -50436,27 +50436,27 @@
       </c>
       <c r="B598" s="5" t="inlineStr">
         <is>
-          <t>Jalin Hyatt</t>
+          <t>Roy Robertson-Harris</t>
         </is>
       </c>
       <c r="C598" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="D598" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E598" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Surgery</t>
         </is>
       </c>
       <c r="F598" s="5" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>ir</t>
         </is>
       </c>
     </row>
@@ -50468,17 +50468,17 @@
       </c>
       <c r="B599" s="4" t="inlineStr">
         <is>
-          <t>DJ James</t>
+          <t>John Michael Schmitz Jr.</t>
         </is>
       </c>
       <c r="C599" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D599" s="4" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E599" s="4" t="inlineStr">
@@ -50488,7 +50488,7 @@
       </c>
       <c r="F599" s="4" t="inlineStr">
         <is>
-          <t>ir</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -50500,17 +50500,17 @@
       </c>
       <c r="B600" s="5" t="inlineStr">
         <is>
-          <t>Dante Miller</t>
+          <t>Jalin Hyatt</t>
         </is>
       </c>
       <c r="C600" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D600" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E600" s="5" t="inlineStr">
@@ -50520,7 +50520,7 @@
       </c>
       <c r="F600" s="5" t="inlineStr">
         <is>
-          <t>ir</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -50532,7 +50532,7 @@
       </c>
       <c r="B601" s="4" t="inlineStr">
         <is>
-          <t>Paulson Adebo</t>
+          <t>DJ James</t>
         </is>
       </c>
       <c r="C601" s="4" t="inlineStr">
@@ -50542,7 +50542,7 @@
       </c>
       <c r="D601" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E601" s="4" t="inlineStr">
@@ -50552,7 +50552,7 @@
       </c>
       <c r="F601" s="4" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>ir</t>
         </is>
       </c>
     </row>
@@ -50564,17 +50564,17 @@
       </c>
       <c r="B602" s="5" t="inlineStr">
         <is>
-          <t>Anquin Barnes Jr.</t>
+          <t>Dante Miller</t>
         </is>
       </c>
       <c r="C602" s="5" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D602" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E602" s="5" t="inlineStr">
@@ -50584,7 +50584,7 @@
       </c>
       <c r="F602" s="5" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>ir</t>
         </is>
       </c>
     </row>
@@ -50596,7 +50596,7 @@
       </c>
       <c r="B603" s="4" t="inlineStr">
         <is>
-          <t>Jarrick Bernard-Converse</t>
+          <t>Paulson Adebo</t>
         </is>
       </c>
       <c r="C603" s="4" t="inlineStr">
@@ -50606,7 +50606,7 @@
       </c>
       <c r="D603" s="4" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E603" s="4" t="inlineStr">
@@ -50616,7 +50616,7 @@
       </c>
       <c r="F603" s="4" t="inlineStr">
         <is>
-          <t>ir</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -50628,25 +50628,29 @@
       </c>
       <c r="B604" s="5" t="inlineStr">
         <is>
-          <t>Jevon Holland</t>
+          <t>Anquin Barnes Jr.</t>
         </is>
       </c>
       <c r="C604" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="D604" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E604" s="5" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="F604" s="5" t="inlineStr"/>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F604" s="5" t="inlineStr">
+        <is>
+          <t>questionable</t>
+        </is>
+      </c>
     </row>
     <row r="605">
       <c r="A605" s="4" t="inlineStr">
@@ -54640,27 +54644,27 @@
       </c>
       <c r="B730" s="5" t="inlineStr">
         <is>
-          <t>Deshawn McKnight</t>
+          <t>Rueben Bain Jr.</t>
         </is>
       </c>
       <c r="C730" s="5" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D730" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E730" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Sprain</t>
         </is>
       </c>
       <c r="F730" s="5" t="inlineStr">
         <is>
-          <t>The Buccaneers placed McKnight (hamstring) on injured reserve Tuesday, Scott Smith of the team's official site reports.</t>
+          <t>Bain sustained an AC sprain, but the injury is not believed to be serious, Adam Schefter of ESPN reports.</t>
         </is>
       </c>
     </row>
@@ -54672,27 +54676,27 @@
       </c>
       <c r="B731" s="4" t="inlineStr">
         <is>
-          <t>Matthew Henry</t>
+          <t>Deshawn McKnight</t>
         </is>
       </c>
       <c r="C731" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="D731" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E731" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F731" s="4" t="inlineStr">
         <is>
-          <t>The Buccaneers signed Henry as an undrafted free agent Tuesday, Scott Smith of the team's official site reports.</t>
+          <t>The Buccaneers placed McKnight (hamstring) on injured reserve Tuesday, Scott Smith of the team's official site reports.</t>
         </is>
       </c>
     </row>
@@ -54704,12 +54708,12 @@
       </c>
       <c r="B732" s="5" t="inlineStr">
         <is>
-          <t>Cade Otton</t>
+          <t>Matthew Henry</t>
         </is>
       </c>
       <c r="C732" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D732" s="5" t="inlineStr">
@@ -54724,7 +54728,7 @@
       </c>
       <c r="F732" s="5" t="inlineStr">
         <is>
-          <t>Otton (undisclosed) returned to practice Tuesday, Rick Stroud of the Tampa Bay Times reports.</t>
+          <t>The Buccaneers signed Henry as an undrafted free agent Tuesday, Scott Smith of the team's official site reports.</t>
         </is>
       </c>
     </row>
@@ -54736,12 +54740,12 @@
       </c>
       <c r="B733" s="4" t="inlineStr">
         <is>
-          <t>Tristan Wirfs</t>
+          <t>Cade Otton</t>
         </is>
       </c>
       <c r="C733" s="4" t="inlineStr">
         <is>
-          <t>OT</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D733" s="4" t="inlineStr">
@@ -54756,7 +54760,7 @@
       </c>
       <c r="F733" s="4" t="inlineStr">
         <is>
-          <t>Wirfs (hamstring) practiced in full-team drills Tuesday, Greg Auman of Fox Sports reports.</t>
+          <t>Otton (undisclosed) returned to practice Tuesday, Rick Stroud of the Tampa Bay Times reports.</t>
         </is>
       </c>
     </row>
@@ -54768,27 +54772,27 @@
       </c>
       <c r="B734" s="5" t="inlineStr">
         <is>
-          <t>Jalen McMillan</t>
+          <t>Tristan Wirfs</t>
         </is>
       </c>
       <c r="C734" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>OT</t>
         </is>
       </c>
       <c r="D734" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E734" s="5" t="inlineStr">
         <is>
-          <t>Soreness</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F734" s="5" t="inlineStr">
         <is>
-          <t>McMillan (knee) isn't participating in Tuesday's practice, Greg Auman of Fox Sports reports.</t>
+          <t>Wirfs (hamstring) practiced in full-team drills Tuesday, Greg Auman of Fox Sports reports.</t>
         </is>
       </c>
     </row>
@@ -54800,7 +54804,7 @@
       </c>
       <c r="B735" s="4" t="inlineStr">
         <is>
-          <t>Tez Johnson</t>
+          <t>Jalen McMillan</t>
         </is>
       </c>
       <c r="C735" s="4" t="inlineStr">
@@ -54815,12 +54819,12 @@
       </c>
       <c r="E735" s="4" t="inlineStr">
         <is>
-          <t>Strain</t>
+          <t>Soreness</t>
         </is>
       </c>
       <c r="F735" s="4" t="inlineStr">
         <is>
-          <t>Johnson (groin) is taking part in Tuesday's practice, Greg Auman of Fox Sports reports.</t>
+          <t>McMillan (knee) isn't participating in Tuesday's practice, Greg Auman of Fox Sports reports.</t>
         </is>
       </c>
     </row>
@@ -54832,7 +54836,7 @@
       </c>
       <c r="B736" s="5" t="inlineStr">
         <is>
-          <t>Emeka Egbuka</t>
+          <t>Tez Johnson</t>
         </is>
       </c>
       <c r="C736" s="5" t="inlineStr">
@@ -54847,12 +54851,12 @@
       </c>
       <c r="E736" s="5" t="inlineStr">
         <is>
-          <t>Sprain</t>
+          <t>Strain</t>
         </is>
       </c>
       <c r="F736" s="5" t="inlineStr">
         <is>
-          <t>Egbuka (toe) isn't participating in Tuesday's practice, Greg Auman of Fox Sports reports.</t>
+          <t>Johnson (groin) is taking part in Tuesday's practice, Greg Auman of Fox Sports reports.</t>
         </is>
       </c>
     </row>
@@ -54864,7 +54868,7 @@
       </c>
       <c r="B737" s="4" t="inlineStr">
         <is>
-          <t>Ted Hurst III</t>
+          <t>Emeka Egbuka</t>
         </is>
       </c>
       <c r="C737" s="4" t="inlineStr">
@@ -54874,17 +54878,17 @@
       </c>
       <c r="D737" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E737" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Sprain</t>
         </is>
       </c>
       <c r="F737" s="4" t="inlineStr">
         <is>
-          <t>Hurst failed to bring in his only target in the Buccaneers' 16-15 preseason win over the Chiefs on Saturday.</t>
+          <t>Egbuka (toe) isn't participating in Tuesday's practice, Greg Auman of Fox Sports reports.</t>
         </is>
       </c>
     </row>
@@ -54896,27 +54900,27 @@
       </c>
       <c r="B738" s="5" t="inlineStr">
         <is>
-          <t>Chris Braswell</t>
+          <t>Ted Hurst III</t>
         </is>
       </c>
       <c r="C738" s="5" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D738" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E738" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F738" s="5" t="inlineStr">
         <is>
-          <t>Braswell (undisclosed) did not play in the Buccaneers' 16-15 preseason win over the Chiefs on Saturday, Greg Auman of Fox Sports reports.</t>
+          <t>Hurst failed to bring in his only target in the Buccaneers' 16-15 preseason win over the Chiefs on Saturday.</t>
         </is>
       </c>
     </row>
@@ -54928,27 +54932,27 @@
       </c>
       <c r="B739" s="4" t="inlineStr">
         <is>
-          <t>Baker Mayfield</t>
+          <t>Chris Braswell</t>
         </is>
       </c>
       <c r="C739" s="4" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D739" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E739" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F739" s="4" t="inlineStr">
         <is>
-          <t>Mayfield completed two of four passes for 10 yards with no touchdowns or interceptions in the Buccaneers' 16-15 preseason win over the Chiefs on Saturday.</t>
+          <t>Braswell (undisclosed) did not play in the Buccaneers' 16-15 preseason win over the Chiefs on Saturday, Greg Auman of Fox Sports reports.</t>
         </is>
       </c>
     </row>
@@ -54960,12 +54964,12 @@
       </c>
       <c r="B740" s="5" t="inlineStr">
         <is>
-          <t>Kenny Gainwell</t>
+          <t>Baker Mayfield</t>
         </is>
       </c>
       <c r="C740" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D740" s="5" t="inlineStr">
@@ -54980,7 +54984,7 @@
       </c>
       <c r="F740" s="5" t="inlineStr">
         <is>
-          <t>Gainwell rushed once for no gain in the Buccaneers' 16-15 preseason win over the Chiefs on Saturday.</t>
+          <t>Mayfield completed two of four passes for 10 yards with no touchdowns or interceptions in the Buccaneers' 16-15 preseason win over the Chiefs on Saturday.</t>
         </is>
       </c>
     </row>
@@ -54992,7 +54996,7 @@
       </c>
       <c r="B741" s="4" t="inlineStr">
         <is>
-          <t>Bucky Irving</t>
+          <t>Kenny Gainwell</t>
         </is>
       </c>
       <c r="C741" s="4" t="inlineStr">
@@ -55012,7 +55016,7 @@
       </c>
       <c r="F741" s="4" t="inlineStr">
         <is>
-          <t>Irving rushed three times for 14 yards in the Buccaneers' 16-15 preseason win over the Chiefs on Saturday.</t>
+          <t>Gainwell rushed once for no gain in the Buccaneers' 16-15 preseason win over the Chiefs on Saturday.</t>
         </is>
       </c>
     </row>
@@ -55024,27 +55028,27 @@
       </c>
       <c r="B742" s="5" t="inlineStr">
         <is>
-          <t>Dennis Houston</t>
+          <t>Bucky Irving</t>
         </is>
       </c>
       <c r="C742" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D742" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E742" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F742" s="5" t="inlineStr">
         <is>
-          <t>Houston has been ruled out for the rest of Saturday's preseason game against the Chiefs due to a groin injury.</t>
+          <t>Irving rushed three times for 14 yards in the Buccaneers' 16-15 preseason win over the Chiefs on Saturday.</t>
         </is>
       </c>
     </row>
@@ -55056,27 +55060,27 @@
       </c>
       <c r="B743" s="4" t="inlineStr">
         <is>
-          <t>Zyon McCollum</t>
+          <t>Dennis Houston</t>
         </is>
       </c>
       <c r="C743" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D743" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E743" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F743" s="4" t="inlineStr">
         <is>
-          <t>McCollum (groin) practiced Thursday and might even see some snaps in Saturday's preseason game against the Chiefs, Scott Smith of the Buccaneers' official site reports.</t>
+          <t>Houston has been ruled out for the rest of Saturday's preseason game against the Chiefs due to a groin injury.</t>
         </is>
       </c>
     </row>
@@ -55088,12 +55092,12 @@
       </c>
       <c r="B744" s="5" t="inlineStr">
         <is>
-          <t>Vita Vea</t>
+          <t>Zyon McCollum</t>
         </is>
       </c>
       <c r="C744" s="5" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D744" s="5" t="inlineStr">
@@ -55108,7 +55112,7 @@
       </c>
       <c r="F744" s="5" t="inlineStr">
         <is>
-          <t>Vea (back) and the Buccaneers reached an agreement on a one-year, $30 million extension Wednesday, Adam Schefter of ESPN reports.</t>
+          <t>McCollum (groin) practiced Thursday and might even see some snaps in Saturday's preseason game against the Chiefs, Scott Smith of the Buccaneers' official site reports.</t>
         </is>
       </c>
     </row>
@@ -55120,12 +55124,12 @@
       </c>
       <c r="B745" s="4" t="inlineStr">
         <is>
-          <t>JJ Roberts</t>
+          <t>Vita Vea</t>
         </is>
       </c>
       <c r="C745" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="D745" s="4" t="inlineStr">
@@ -55138,7 +55142,11 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F745" s="4" t="inlineStr"/>
+      <c r="F745" s="4" t="inlineStr">
+        <is>
+          <t>Vea (back) and the Buccaneers reached an agreement on a one-year, $30 million extension Wednesday, Adam Schefter of ESPN reports.</t>
+        </is>
+      </c>
     </row>
     <row r="746">
       <c r="A746" s="5" t="inlineStr">
@@ -55148,29 +55156,25 @@
       </c>
       <c r="B746" s="5" t="inlineStr">
         <is>
-          <t>Billy Schrauth</t>
+          <t>JJ Roberts</t>
         </is>
       </c>
       <c r="C746" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D746" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E746" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="F746" s="5" t="inlineStr">
-        <is>
-          <t>Schrauth (knee) did not participate in Tuesday's practice, Greg Auman of Fox Sports reports.</t>
-        </is>
-      </c>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F746" s="5" t="inlineStr"/>
     </row>
     <row r="747">
       <c r="A747" s="4" t="inlineStr">
@@ -55180,27 +55184,27 @@
       </c>
       <c r="B747" s="4" t="inlineStr">
         <is>
-          <t>Jake Browning</t>
+          <t>Billy Schrauth</t>
         </is>
       </c>
       <c r="C747" s="4" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D747" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E747" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F747" s="4" t="inlineStr">
         <is>
-          <t>Browning (back) practiced Monday after missing Friday's preseason game against the Jets, Rick Stroud of the Tampa Bay Times reports.</t>
+          <t>Schrauth (knee) did not participate in Tuesday's practice, Greg Auman of Fox Sports reports.</t>
         </is>
       </c>
     </row>
@@ -55212,12 +55216,12 @@
       </c>
       <c r="B748" s="5" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr.</t>
+          <t>Jake Browning</t>
         </is>
       </c>
       <c r="C748" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D748" s="5" t="inlineStr">
@@ -55232,7 +55236,7 @@
       </c>
       <c r="F748" s="5" t="inlineStr">
         <is>
-          <t>Godwin didn't play in Friday's 24-16 preseason victory over the Jets.</t>
+          <t>Browning (back) practiced Monday after missing Friday's preseason game against the Jets, Rick Stroud of the Tampa Bay Times reports.</t>
         </is>
       </c>
     </row>
@@ -55244,12 +55248,12 @@
       </c>
       <c r="B749" s="4" t="inlineStr">
         <is>
-          <t>Sean Tucker</t>
+          <t>Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="C749" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D749" s="4" t="inlineStr">
@@ -55264,7 +55268,7 @@
       </c>
       <c r="F749" s="4" t="inlineStr">
         <is>
-          <t>Tucker rushed four times for 12 yards and brought in both targets for 11 yards in the Buccaneers' 24-16 preseason win over the Jets on Friday.</t>
+          <t>Godwin didn't play in Friday's 24-16 preseason victory over the Jets.</t>
         </is>
       </c>
     </row>
@@ -55276,12 +55280,12 @@
       </c>
       <c r="B750" s="5" t="inlineStr">
         <is>
-          <t>Roman Parodie</t>
+          <t>Sean Tucker</t>
         </is>
       </c>
       <c r="C750" s="5" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D750" s="5" t="inlineStr">
@@ -55296,7 +55300,7 @@
       </c>
       <c r="F750" s="5" t="inlineStr">
         <is>
-          <t>The Bucs signed Parodie to a contract Monday, Gabriel Kahalan of the team's official site reports.</t>
+          <t>Tucker rushed four times for 12 yards and brought in both targets for 11 yards in the Buccaneers' 24-16 preseason win over the Jets on Friday.</t>
         </is>
       </c>
     </row>
@@ -55308,12 +55312,12 @@
       </c>
       <c r="B751" s="4" t="inlineStr">
         <is>
-          <t>David Walker</t>
+          <t>Roman Parodie</t>
         </is>
       </c>
       <c r="C751" s="4" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D751" s="4" t="inlineStr">
@@ -55328,7 +55332,7 @@
       </c>
       <c r="F751" s="4" t="inlineStr">
         <is>
-          <t>Walker (knee) passed his physical and is back to full health for training camp, Rick Stroud of the Tampa Bay Times reports.</t>
+          <t>The Bucs signed Parodie to a contract Monday, Gabriel Kahalan of the team's official site reports.</t>
         </is>
       </c>
     </row>
@@ -55340,12 +55344,12 @@
       </c>
       <c r="B752" s="5" t="inlineStr">
         <is>
-          <t>Benjamin Morrison</t>
+          <t>David Walker</t>
         </is>
       </c>
       <c r="C752" s="5" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D752" s="5" t="inlineStr">
@@ -55360,7 +55364,7 @@
       </c>
       <c r="F752" s="5" t="inlineStr">
         <is>
-          <t>Morrison (hamstring) was a full participant in Sunday's training camp practice, Greg Auman of Fox Sports reports.</t>
+          <t>Walker (knee) passed his physical and is back to full health for training camp, Rick Stroud of the Tampa Bay Times reports.</t>
         </is>
       </c>
     </row>
@@ -55372,12 +55376,12 @@
       </c>
       <c r="B753" s="4" t="inlineStr">
         <is>
-          <t>Ko Kieft</t>
+          <t>Benjamin Morrison</t>
         </is>
       </c>
       <c r="C753" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D753" s="4" t="inlineStr">
@@ -55392,7 +55396,7 @@
       </c>
       <c r="F753" s="4" t="inlineStr">
         <is>
-          <t>Kieft (leg) is on the field participating in the Buccaneers' training camp activities.</t>
+          <t>Morrison (hamstring) was a full participant in Sunday's training camp practice, Greg Auman of Fox Sports reports.</t>
         </is>
       </c>
     </row>
@@ -55404,12 +55408,12 @@
       </c>
       <c r="B754" s="5" t="inlineStr">
         <is>
-          <t>Ifeatu Melifonwu</t>
+          <t>Ko Kieft</t>
         </is>
       </c>
       <c r="C754" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D754" s="5" t="inlineStr">
@@ -55424,7 +55428,7 @@
       </c>
       <c r="F754" s="5" t="inlineStr">
         <is>
-          <t>The Buccaneers signed Melifonwu to a one-year contract Wednesday, Adam Schefter of ESPN reports.</t>
+          <t>Kieft (leg) is on the field participating in the Buccaneers' training camp activities.</t>
         </is>
       </c>
     </row>
@@ -57124,16 +57128,16 @@
         </is>
       </c>
       <c r="D5" s="15" t="n">
-        <v>72.09999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>20</v>
+        <v>17.9</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
@@ -57141,13 +57145,9 @@
         </is>
       </c>
       <c r="I5" s="9" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>Wind 12 mph (gusts 20)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -57166,13 +57166,13 @@
         </is>
       </c>
       <c r="D6" s="17" t="n">
-        <v>73</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>4.9</v>
+        <v>2.2</v>
       </c>
       <c r="F6" s="17" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="G6" s="17" t="n">
         <v>2</v>
@@ -57204,13 +57204,13 @@
         </is>
       </c>
       <c r="D7" s="15" t="n">
-        <v>107.4</v>
+        <v>106.3</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>19.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>18.4</v>
+        <v>17.7</v>
       </c>
       <c r="G7" s="15" t="n">
         <v>1</v>
@@ -57246,13 +57246,13 @@
         </is>
       </c>
       <c r="D8" s="17" t="n">
-        <v>79.2</v>
+        <v>78.2</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
       <c r="F8" s="17" t="n">
-        <v>5.1</v>
+        <v>11.6</v>
       </c>
       <c r="G8" s="17" t="n">
         <v>0</v>
@@ -57284,16 +57284,16 @@
         </is>
       </c>
       <c r="D9" s="15" t="n">
-        <v>85.3</v>
+        <v>86.2</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>6.3</v>
+        <v>5</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>10.1</v>
+        <v>5.6</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
@@ -57325,13 +57325,13 @@
         <v>89.2</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>13.4</v>
+        <v>13.2</v>
       </c>
       <c r="F10" s="17" t="n">
-        <v>14.1</v>
+        <v>13.6</v>
       </c>
       <c r="G10" s="17" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
@@ -57364,16 +57364,16 @@
         </is>
       </c>
       <c r="D11" s="15" t="n">
-        <v>79</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>12.3</v>
+        <v>9.4</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
@@ -57385,7 +57385,7 @@
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>75% chance of rain</t>
+          <t>58% chance of rain</t>
         </is>
       </c>
     </row>
@@ -57406,16 +57406,16 @@
         </is>
       </c>
       <c r="D12" s="17" t="n">
-        <v>84.90000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>7.3</v>
+        <v>8.1</v>
       </c>
       <c r="F12" s="17" t="n">
-        <v>10.7</v>
+        <v>11.4</v>
       </c>
       <c r="G12" s="17" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
@@ -57444,20 +57444,20 @@
         </is>
       </c>
       <c r="D13" s="15" t="n">
-        <v>87.8</v>
+        <v>78.7</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>6.8</v>
+        <v>5.1</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G13" s="15" t="n">
         <v>72</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Light drizzle</t>
+          <t>Rain showers</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
@@ -57486,16 +57486,16 @@
         </is>
       </c>
       <c r="D14" s="17" t="n">
-        <v>79.8</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="F14" s="17" t="n">
-        <v>5.8</v>
+        <v>14.8</v>
       </c>
       <c r="G14" s="17" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
@@ -57524,13 +57524,13 @@
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>85.09999999999999</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>10.5</v>
+        <v>9.1</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>19.9</v>
+        <v>17</v>
       </c>
       <c r="G15" s="15" t="n">
         <v>0</v>
@@ -57541,13 +57541,9 @@
         </is>
       </c>
       <c r="I15" s="9" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>Wind 10 mph (gusts 20)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -57566,16 +57562,16 @@
         </is>
       </c>
       <c r="D16" s="17" t="n">
-        <v>102.1</v>
+        <v>102.5</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F16" s="17" t="n">
-        <v>8.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G16" s="17" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
@@ -57608,28 +57604,28 @@
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>68.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>12.1</v>
+        <v>15.6</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>18.3</v>
+        <v>23.5</v>
       </c>
       <c r="G17" s="15" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Partly cloudy</t>
+          <t>Overcast</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
-        <v>-0.8</v>
+        <v>-1.8</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>Wind 12 mph (gusts 18)</t>
+          <t>Wind 16 mph (gusts 24)</t>
         </is>
       </c>
     </row>
@@ -57650,20 +57646,20 @@
         </is>
       </c>
       <c r="D18" s="17" t="n">
-        <v>82.3</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>10.3</v>
+        <v>5.9</v>
       </c>
       <c r="F18" s="17" t="n">
-        <v>8.5</v>
+        <v>6.3</v>
       </c>
       <c r="G18" s="17" t="n">
         <v>8</v>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>Light drizzle</t>
+          <t>Partly cloudy</t>
         </is>
       </c>
       <c r="I18" s="24" t="n">
@@ -57688,20 +57684,20 @@
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>81.2</v>
+        <v>79</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>5.4</v>
+        <v>2.7</v>
       </c>
       <c r="G19" s="15" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Overcast</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
@@ -57726,16 +57722,16 @@
         </is>
       </c>
       <c r="D20" s="17" t="n">
-        <v>93.59999999999999</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="F20" s="17" t="n">
-        <v>6.3</v>
+        <v>4.9</v>
       </c>
       <c r="G20" s="17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
@@ -57747,7 +57743,7 @@
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>94°F</t>
+          <t>93°F</t>
         </is>
       </c>
     </row>
@@ -57768,20 +57764,20 @@
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>81.40000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="F21" s="15" t="n">
         <v>4.5</v>
       </c>
       <c r="G21" s="15" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>Partly cloudy</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="I21" s="9" t="n">
@@ -57806,20 +57802,20 @@
         </is>
       </c>
       <c r="D22" s="17" t="n">
-        <v>67.90000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>19.3</v>
+        <v>11.7</v>
       </c>
       <c r="F22" s="17" t="n">
         <v>44.7</v>
       </c>
       <c r="G22" s="17" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>Overcast</t>
+          <t>Mainly clear</t>
         </is>
       </c>
       <c r="I22" s="24" t="n">
@@ -57827,7 +57823,7 @@
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>Wind 19 mph (gusts 45)</t>
+          <t>Wind 12 mph (gusts 45)</t>
         </is>
       </c>
     </row>

--- a/NFL_Edge_Model.xlsx
+++ b/NFL_Edge_Model.xlsx
@@ -692,7 +692,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Snapshot of the live model, generated 2026-08-29T12:02:24+00:00. Read-only: the model runs in the pipeline, not in this file.</t>
+          <t>Snapshot of the live model, generated 2026-08-29T16:02:14+00:00. Read-only: the model runs in the pipeline, not in this file.</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>2026-08-29T12:02:24+00:00</t>
+          <t>2026-08-29T16:02:14+00:00</t>
         </is>
       </c>
     </row>
@@ -2703,23 +2703,23 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Over 36.5</t>
+          <t>Over 35.5</t>
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>-105</v>
+        <v>-108</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>0.6071</v>
+        <v>0.6116</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.5192</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>0.0516</v>
+        <v>0.0513</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>0.1852068112339181</v>
+        <v>0.1779746843903312</v>
       </c>
       <c r="J7" s="10" t="n">
         <v>0.15</v>
@@ -2748,23 +2748,23 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Over 36.5</t>
+          <t>Over 37.5</t>
         </is>
       </c>
       <c r="E8" s="12" t="n">
-        <v>-115</v>
+        <v>-105</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.6077</v>
+        <v>0.5954</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.5122</v>
       </c>
       <c r="H8" s="13" t="n">
-        <v>0.0477</v>
+        <v>0.0499</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>0.1360905800626417</v>
+        <v>0.16244286923895</v>
       </c>
       <c r="J8" s="15" t="n">
         <v>0.15</v>
@@ -3074,42 +3074,38 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>DET @ IND</t>
+          <t>WSH @ PHI</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>DET +4.5</t>
+          <t>Under 45.5</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>-115</v>
+        <v>-105</v>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5392</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.5122</v>
       </c>
       <c r="H16" s="13" t="n">
-        <v>0.0259</v>
+        <v>0.0251</v>
       </c>
       <c r="I16" s="13" t="n">
-        <v>0.05250654582616154</v>
+        <v>0.05280703547074495</v>
       </c>
       <c r="J16" s="15" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -3119,7 +3115,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>WSH @ PHI</t>
+          <t>DET @ BUF</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -3129,23 +3125,23 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Under 45.5</t>
+          <t>Under 52.5</t>
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>0.5392</v>
+        <v>0.5505</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.5238</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>0.0251</v>
+        <v>0.0248</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>0.05280703547074495</v>
+        <v>0.05103388963377431</v>
       </c>
       <c r="J17" s="10" t="n">
         <v>0.5</v>
@@ -3160,7 +3156,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>DET @ BUF</t>
+          <t>GB @ NYJ</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -3170,7 +3166,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Under 52.5</t>
+          <t>Over 42.5</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
@@ -3186,7 +3182,7 @@
         <v>0.0248</v>
       </c>
       <c r="I18" s="13" t="n">
-        <v>0.05103388963377431</v>
+        <v>0.05103768389435415</v>
       </c>
       <c r="J18" s="15" t="n">
         <v>0.5</v>
@@ -3201,7 +3197,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>GB @ NYJ</t>
+          <t>GB @ MIN</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -3211,23 +3207,23 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Over 42.5</t>
+          <t>Under 45.5</t>
         </is>
       </c>
       <c r="E19" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>0.5505</v>
+        <v>0.548</v>
       </c>
       <c r="G19" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>0.0248</v>
+        <v>0.0228</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>0.05103768389435415</v>
+        <v>0.04626263390290908</v>
       </c>
       <c r="J19" s="10" t="n">
         <v>0.5</v>
@@ -3242,33 +3238,33 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>GB @ MIN</t>
+          <t>CLE @ JAX</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Under 45.5</t>
+          <t>CLE +7.5</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.548</v>
+        <v>0.5478</v>
       </c>
       <c r="G20" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H20" s="13" t="n">
-        <v>0.0228</v>
+        <v>0.0226</v>
       </c>
       <c r="I20" s="13" t="n">
-        <v>0.04626263390290908</v>
+        <v>0.04586136556664278</v>
       </c>
       <c r="J20" s="15" t="n">
         <v>0.5</v>
@@ -3283,7 +3279,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>CLE @ JAX</t>
+          <t>DET @ IND</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -3293,28 +3289,32 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>CLE +7.5</t>
+          <t>DET +3.5</t>
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>0.5478</v>
+        <v>0.5515</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5283</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>0.0226</v>
+        <v>0.0219</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>0.04586136556664278</v>
+        <v>0.04383126209439547</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K21" s="4" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -3488,33 +3488,33 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>GB @ NYJ</t>
+          <t>NYG @ LAR</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>NYJ ML</t>
+          <t>NYG +8.5</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>195</v>
+        <v>-110</v>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.359</v>
+        <v>0.5444</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>0.339</v>
+        <v>0.5238</v>
       </c>
       <c r="H26" s="13" t="n">
-        <v>0.0191</v>
+        <v>0.0197</v>
       </c>
       <c r="I26" s="13" t="n">
-        <v>0.05843731370944838</v>
+        <v>0.0393979976176152</v>
       </c>
       <c r="J26" s="15" t="n">
         <v>0.5</v>
@@ -3529,33 +3529,33 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>NO @ BAL</t>
+          <t>GB @ NYJ</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>NO +7.5</t>
+          <t>NYJ ML</t>
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>-110</v>
+        <v>195</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>0.5437</v>
+        <v>0.359</v>
       </c>
       <c r="G27" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.339</v>
       </c>
       <c r="H27" s="8" t="n">
-        <v>0.019</v>
+        <v>0.0191</v>
       </c>
       <c r="I27" s="8" t="n">
-        <v>0.03790456959418603</v>
+        <v>0.05843731370944838</v>
       </c>
       <c r="J27" s="10" t="n">
         <v>0.5</v>
@@ -3570,33 +3570,33 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>MIA @ LV</t>
+          <t>NO @ BAL</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Over 40.5</t>
+          <t>NO +7.5</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.543</v>
+        <v>0.5437</v>
       </c>
       <c r="G28" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H28" s="13" t="n">
-        <v>0.0185</v>
+        <v>0.019</v>
       </c>
       <c r="I28" s="13" t="n">
-        <v>0.03671607804771798</v>
+        <v>0.03790456959418603</v>
       </c>
       <c r="J28" s="15" t="n">
         <v>0.5</v>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>WSH @ DAL</t>
+          <t>MIA @ LV</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Under 51.5</t>
+          <t>Over 40.5</t>
         </is>
       </c>
       <c r="E29" s="7" t="n">
@@ -3637,7 +3637,7 @@
         <v>0.0185</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>0.03670597155556737</v>
+        <v>0.03671607804771798</v>
       </c>
       <c r="J29" s="10" t="n">
         <v>0.5</v>
@@ -3652,42 +3652,38 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>CHI @ TEN</t>
+          <t>WSH @ DAL</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>CHI ML</t>
+          <t>Under 51.5</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>126</v>
+        <v>-110</v>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.4615</v>
+        <v>0.543</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>0.4425</v>
+        <v>0.5238</v>
       </c>
       <c r="H30" s="13" t="n">
-        <v>0.0183</v>
+        <v>0.0185</v>
       </c>
       <c r="I30" s="13" t="n">
-        <v>0.04249672938867266</v>
+        <v>0.03670597155556737</v>
       </c>
       <c r="J30" s="15" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -3861,38 +3857,42 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>NYG @ LAR</t>
+          <t>CHI @ TEN</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>NYG +8.5</t>
+          <t>CHI ML</t>
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>-110</v>
+        <v>123</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>0.5395</v>
+        <v>0.4635</v>
       </c>
       <c r="G35" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.4484</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>0.0153</v>
+        <v>0.0147</v>
       </c>
       <c r="I35" s="8" t="n">
-        <v>0.02993648495691575</v>
+        <v>0.03334633394405739</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K35" s="4" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -3902,42 +3902,38 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>DET @ IND</t>
+          <t>NO @ DET</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>DET ML</t>
+          <t>NO +7</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>149</v>
+        <v>-110</v>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.4168</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>0.4016</v>
+        <v>0.5238</v>
       </c>
       <c r="H36" s="13" t="n">
-        <v>0.0149</v>
+        <v>0.0146</v>
       </c>
       <c r="I36" s="13" t="n">
-        <v>0.03758872870190388</v>
+        <v>0.02707237376244487</v>
       </c>
       <c r="J36" s="15" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K36" s="5" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -3947,7 +3943,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>NO @ DET</t>
+          <t>BAL @ IND</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -3957,23 +3953,23 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>NO +7</t>
+          <t>IND +3.5</t>
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>0.5387999999999999</v>
+        <v>0.543</v>
       </c>
       <c r="G37" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5283</v>
       </c>
       <c r="H37" s="8" t="n">
-        <v>0.0146</v>
+        <v>0.0143</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>0.02707237376244487</v>
+        <v>0.02777315817801496</v>
       </c>
       <c r="J37" s="10" t="n">
         <v>0.5</v>
@@ -3988,33 +3984,33 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>MIN @ CHI</t>
+          <t>IND @ KC</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>MIN ML</t>
+          <t>IND +6.5</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>164</v>
+        <v>-110</v>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.3935</v>
+        <v>0.5384</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>0.3788</v>
+        <v>0.5238</v>
       </c>
       <c r="H38" s="13" t="n">
-        <v>0.0144</v>
+        <v>0.0143</v>
       </c>
       <c r="I38" s="13" t="n">
-        <v>0.03852271973064392</v>
+        <v>0.02788617775875746</v>
       </c>
       <c r="J38" s="15" t="n">
         <v>0.5</v>
@@ -4029,33 +4025,33 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>BAL @ IND</t>
+          <t>ATL @ PIT</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>IND +3.5</t>
+          <t>Over 41.5</t>
         </is>
       </c>
       <c r="E39" s="7" t="n">
-        <v>-112</v>
+        <v>-115</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>0.543</v>
+        <v>0.5493</v>
       </c>
       <c r="G39" s="8" t="n">
-        <v>0.5283</v>
+        <v>0.5349</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>0.0143</v>
+        <v>0.0141</v>
       </c>
       <c r="I39" s="8" t="n">
-        <v>0.02777315817801496</v>
+        <v>0.02702299932041741</v>
       </c>
       <c r="J39" s="10" t="n">
         <v>0.5</v>
@@ -4070,33 +4066,33 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>IND @ KC</t>
+          <t>BAL @ IND</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>IND +6.5</t>
+          <t>IND ML</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>-110</v>
+        <v>145</v>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.5384</v>
+        <v>0.4224</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.4082</v>
       </c>
       <c r="H40" s="13" t="n">
-        <v>0.0143</v>
+        <v>0.0139</v>
       </c>
       <c r="I40" s="13" t="n">
-        <v>0.02788617775875746</v>
+        <v>0.03462735268929273</v>
       </c>
       <c r="J40" s="15" t="n">
         <v>0.5</v>
@@ -4111,33 +4107,33 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>ATL @ PIT</t>
+          <t>NO @ DET</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Over 41.5</t>
+          <t>NO ML</t>
         </is>
       </c>
       <c r="E41" s="7" t="n">
-        <v>-115</v>
+        <v>245</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>0.5493</v>
+        <v>0.3041</v>
       </c>
       <c r="G41" s="8" t="n">
-        <v>0.5349</v>
+        <v>0.2899</v>
       </c>
       <c r="H41" s="8" t="n">
-        <v>0.0141</v>
+        <v>0.0139</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>0.02702299932041741</v>
+        <v>0.04863743274212984</v>
       </c>
       <c r="J41" s="10" t="n">
         <v>0.5</v>
@@ -4152,7 +4148,7 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>BAL @ IND</t>
+          <t>MIN @ CHI</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -4162,23 +4158,23 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>IND ML</t>
+          <t>MIN ML</t>
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.4224</v>
+        <v>0.393</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>0.4082</v>
+        <v>0.3788</v>
       </c>
       <c r="H42" s="13" t="n">
         <v>0.0139</v>
       </c>
       <c r="I42" s="13" t="n">
-        <v>0.03462735268929273</v>
+        <v>0.03712217810050522</v>
       </c>
       <c r="J42" s="15" t="n">
         <v>0.5</v>
@@ -4193,33 +4189,33 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>NO @ DET</t>
+          <t>NO @ BAL</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>NO ML</t>
+          <t>Under 46.5</t>
         </is>
       </c>
       <c r="E43" s="7" t="n">
-        <v>245</v>
+        <v>-110</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>0.3041</v>
+        <v>0.538</v>
       </c>
       <c r="G43" s="8" t="n">
-        <v>0.2899</v>
+        <v>0.5238</v>
       </c>
       <c r="H43" s="8" t="n">
         <v>0.0139</v>
       </c>
       <c r="I43" s="8" t="n">
-        <v>0.04863743274212984</v>
+        <v>0.02711217952171041</v>
       </c>
       <c r="J43" s="10" t="n">
         <v>0.5</v>
@@ -4234,33 +4230,33 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>NO @ BAL</t>
+          <t>NYG @ LAR</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Under 46.5</t>
+          <t>NYG ML</t>
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>-110</v>
+        <v>295</v>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.538</v>
+        <v>0.267</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.2532</v>
       </c>
       <c r="H44" s="13" t="n">
-        <v>0.0139</v>
+        <v>0.0136</v>
       </c>
       <c r="I44" s="13" t="n">
-        <v>0.02711217952171041</v>
+        <v>0.05443040042096803</v>
       </c>
       <c r="J44" s="15" t="n">
         <v>0.5</v>
@@ -4562,38 +4558,42 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>ARI @ LAC</t>
+          <t>DET @ IND</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>ARI +10.5</t>
+          <t>DET ML</t>
         </is>
       </c>
       <c r="E52" s="12" t="n">
-        <v>-110</v>
+        <v>134</v>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.5335</v>
+        <v>0.4374</v>
       </c>
       <c r="G52" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.4274</v>
       </c>
       <c r="H52" s="13" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="I52" s="13" t="n">
-        <v>0.01853454908740365</v>
+        <v>0.02329680065868189</v>
       </c>
       <c r="J52" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K52" s="5" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -4603,33 +4603,33 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>NYG @ LAR</t>
+          <t>ARI @ LAC</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>NYG ML</t>
+          <t>ARI +10.5</t>
         </is>
       </c>
       <c r="E53" s="7" t="n">
-        <v>295</v>
+        <v>-110</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>0.2629</v>
+        <v>0.5335</v>
       </c>
       <c r="G53" s="8" t="n">
-        <v>0.2532</v>
+        <v>0.5238</v>
       </c>
       <c r="H53" s="8" t="n">
         <v>0.009599999999999999</v>
       </c>
       <c r="I53" s="8" t="n">
-        <v>0.03799490368777525</v>
+        <v>0.01853454908740365</v>
       </c>
       <c r="J53" s="10" t="n">
         <v>0.5</v>
@@ -5099,7 +5099,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>CLE @ TB</t>
+          <t>DAL @ NYG</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -5109,23 +5109,23 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>CLE ML</t>
+          <t>NYG ML</t>
         </is>
       </c>
       <c r="E65" s="7" t="n">
-        <v>195</v>
+        <v>124</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>0.3384</v>
+        <v>0.4465</v>
       </c>
       <c r="G65" s="8" t="n">
-        <v>0.339</v>
+        <v>0.4464</v>
       </c>
       <c r="H65" s="8" t="n">
-        <v>-0.0005</v>
+        <v>0.0001</v>
       </c>
       <c r="I65" s="8" t="n">
-        <v>-0.001566199273758007</v>
+        <v>0.0001527392243889647</v>
       </c>
       <c r="J65" s="10" t="n">
         <v>0.5</v>
@@ -5140,33 +5140,33 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>NE @ SEA</t>
+          <t>CLE @ TB</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Under 44.5</t>
+          <t>CLE ML</t>
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>-110</v>
+        <v>195</v>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.5229</v>
+        <v>0.3384</v>
       </c>
       <c r="G66" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.339</v>
       </c>
       <c r="H66" s="13" t="n">
-        <v>-0.001</v>
+        <v>-0.0005</v>
       </c>
       <c r="I66" s="13" t="n">
-        <v>-0.001817132797922338</v>
+        <v>-0.001566199273758007</v>
       </c>
       <c r="J66" s="15" t="n">
         <v>0.5</v>
@@ -5181,33 +5181,33 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>MIN @ CHI</t>
+          <t>NE @ SEA</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>MIN +3.5</t>
+          <t>Under 44.5</t>
         </is>
       </c>
       <c r="E67" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>0.5224</v>
+        <v>0.5229</v>
       </c>
       <c r="G67" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H67" s="8" t="n">
-        <v>-0.0014</v>
+        <v>-0.001</v>
       </c>
       <c r="I67" s="8" t="n">
-        <v>-0.002738831104669937</v>
+        <v>-0.001817132797922338</v>
       </c>
       <c r="J67" s="10" t="n">
         <v>0.5</v>
@@ -5222,33 +5222,33 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>BUF @ HOU</t>
+          <t>MIN @ CHI</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Over 44.5</t>
+          <t>MIN +3.5</t>
         </is>
       </c>
       <c r="E68" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F68" s="13" t="n">
-        <v>0.5203</v>
+        <v>0.5218</v>
       </c>
       <c r="G68" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H68" s="13" t="n">
-        <v>-0.0035</v>
+        <v>-0.002</v>
       </c>
       <c r="I68" s="13" t="n">
-        <v>-0.006648938044830577</v>
+        <v>-0.003765641878485049</v>
       </c>
       <c r="J68" s="15" t="n">
         <v>0.5</v>
@@ -5263,33 +5263,33 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>CIN @ HOU</t>
+          <t>BUF @ HOU</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>CIN +2.5</t>
+          <t>Over 44.5</t>
         </is>
       </c>
       <c r="E69" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>0.5194</v>
+        <v>0.5203</v>
       </c>
       <c r="G69" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H69" s="8" t="n">
-        <v>-0.0044</v>
+        <v>-0.0035</v>
       </c>
       <c r="I69" s="8" t="n">
-        <v>-0.008364259554241027</v>
+        <v>-0.006648938044830577</v>
       </c>
       <c r="J69" s="10" t="n">
         <v>0.5</v>
@@ -5304,33 +5304,33 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>DAL @ NYG</t>
+          <t>CIN @ HOU</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>NYG ML</t>
+          <t>CIN +2.5</t>
         </is>
       </c>
       <c r="E70" s="12" t="n">
-        <v>124</v>
+        <v>-110</v>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.4418</v>
+        <v>0.5194</v>
       </c>
       <c r="G70" s="13" t="n">
-        <v>0.4464</v>
+        <v>0.5238</v>
       </c>
       <c r="H70" s="13" t="n">
-        <v>-0.0046</v>
+        <v>-0.0044</v>
       </c>
       <c r="I70" s="13" t="n">
-        <v>-0.01033017716423079</v>
+        <v>-0.008364259554241027</v>
       </c>
       <c r="J70" s="15" t="n">
         <v>0.5</v>
@@ -5632,33 +5632,33 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>ATL @ PIT</t>
+          <t>DAL @ NYG</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>ATL ML</t>
+          <t>NYG +2.5</t>
         </is>
       </c>
       <c r="E78" s="12" t="n">
-        <v>145</v>
+        <v>-105</v>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.3979</v>
+        <v>0.502</v>
       </c>
       <c r="G78" s="13" t="n">
-        <v>0.4082</v>
+        <v>0.5122</v>
       </c>
       <c r="H78" s="13" t="n">
-        <v>-0.0102</v>
+        <v>-0.0101</v>
       </c>
       <c r="I78" s="13" t="n">
-        <v>-0.02504479551253269</v>
+        <v>-0.01999076800371946</v>
       </c>
       <c r="J78" s="15" t="n">
         <v>0.5</v>
@@ -5673,33 +5673,33 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>PHI @ TEN</t>
+          <t>ATL @ PIT</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Over 42.5</t>
+          <t>ATL ML</t>
         </is>
       </c>
       <c r="E79" s="7" t="n">
-        <v>-110</v>
+        <v>145</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>0.5127</v>
+        <v>0.3979</v>
       </c>
       <c r="G79" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.4082</v>
       </c>
       <c r="H79" s="8" t="n">
-        <v>-0.0109</v>
+        <v>-0.0102</v>
       </c>
       <c r="I79" s="8" t="n">
-        <v>-0.0211809310724152</v>
+        <v>-0.02504479551253269</v>
       </c>
       <c r="J79" s="10" t="n">
         <v>0.5</v>
@@ -5714,7 +5714,7 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>SEA @ ARI</t>
+          <t>PHI @ TEN</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
@@ -5724,7 +5724,7 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Under 44.5</t>
+          <t>Over 42.5</t>
         </is>
       </c>
       <c r="E80" s="12" t="n">
@@ -5737,10 +5737,10 @@
         <v>0.5238</v>
       </c>
       <c r="H80" s="13" t="n">
-        <v>-0.011</v>
+        <v>-0.0109</v>
       </c>
       <c r="I80" s="13" t="n">
-        <v>-0.02119113285229918</v>
+        <v>-0.0211809310724152</v>
       </c>
       <c r="J80" s="15" t="n">
         <v>0.5</v>
@@ -5755,33 +5755,33 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>JAX @ DEN</t>
+          <t>SEA @ ARI</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>DEN ML</t>
+          <t>Under 44.5</t>
         </is>
       </c>
       <c r="E81" s="7" t="n">
-        <v>-142</v>
+        <v>-110</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>0.5744</v>
+        <v>0.5127</v>
       </c>
       <c r="G81" s="8" t="n">
-        <v>0.5868</v>
+        <v>0.5238</v>
       </c>
       <c r="H81" s="8" t="n">
-        <v>-0.0122</v>
+        <v>-0.011</v>
       </c>
       <c r="I81" s="8" t="n">
-        <v>-0.0209817079416707</v>
+        <v>-0.02119113285229918</v>
       </c>
       <c r="J81" s="10" t="n">
         <v>0.5</v>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>BUF @ HOU</t>
+          <t>JAX @ DEN</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
@@ -5806,23 +5806,23 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>BUF ML</t>
+          <t>DEN ML</t>
         </is>
       </c>
       <c r="E82" s="12" t="n">
-        <v>-118</v>
+        <v>-142</v>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.5286999999999999</v>
+        <v>0.5744</v>
       </c>
       <c r="G82" s="13" t="n">
-        <v>0.5413</v>
+        <v>0.5868</v>
       </c>
       <c r="H82" s="13" t="n">
-        <v>-0.0124</v>
+        <v>-0.0122</v>
       </c>
       <c r="I82" s="13" t="n">
-        <v>-0.02300840316915115</v>
+        <v>-0.0209817079416707</v>
       </c>
       <c r="J82" s="15" t="n">
         <v>0.5</v>
@@ -5837,7 +5837,7 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>NYJ @ TEN</t>
+          <t>BUF @ HOU</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -5847,23 +5847,23 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>TEN ML</t>
+          <t>BUF ML</t>
         </is>
       </c>
       <c r="E83" s="7" t="n">
-        <v>-148</v>
+        <v>-118</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>0.584</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="G83" s="8" t="n">
-        <v>0.5968</v>
+        <v>0.5413</v>
       </c>
       <c r="H83" s="8" t="n">
-        <v>-0.0126</v>
+        <v>-0.0124</v>
       </c>
       <c r="I83" s="8" t="n">
-        <v>-0.0212609610159244</v>
+        <v>-0.02300840316915115</v>
       </c>
       <c r="J83" s="10" t="n">
         <v>0.5</v>
@@ -5878,33 +5878,33 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>JAX @ DEN</t>
+          <t>NYJ @ TEN</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>DEN -2.5</t>
+          <t>TEN ML</t>
         </is>
       </c>
       <c r="E84" s="12" t="n">
-        <v>-115</v>
+        <v>-148</v>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.5218</v>
+        <v>0.584</v>
       </c>
       <c r="G84" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.5968</v>
       </c>
       <c r="H84" s="13" t="n">
-        <v>-0.0128</v>
+        <v>-0.0126</v>
       </c>
       <c r="I84" s="13" t="n">
-        <v>-0.02438228253311814</v>
+        <v>-0.0212609610159244</v>
       </c>
       <c r="J84" s="15" t="n">
         <v>0.5</v>
@@ -5919,7 +5919,7 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>BUF @ HOU</t>
+          <t>JAX @ DEN</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -5929,23 +5929,23 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>BUF -1.5</t>
+          <t>DEN -2.5</t>
         </is>
       </c>
       <c r="E85" s="7" t="n">
-        <v>-105</v>
+        <v>-115</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>0.4982</v>
+        <v>0.5218</v>
       </c>
       <c r="G85" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.5349</v>
       </c>
       <c r="H85" s="8" t="n">
-        <v>-0.0137</v>
+        <v>-0.0128</v>
       </c>
       <c r="I85" s="8" t="n">
-        <v>-0.02730543519254441</v>
+        <v>-0.02438228253311814</v>
       </c>
       <c r="J85" s="10" t="n">
         <v>0.5</v>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>ATL @ PIT</t>
+          <t>BUF @ HOU</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
@@ -5970,23 +5970,23 @@
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>ATL +3</t>
+          <t>BUF -1.5</t>
         </is>
       </c>
       <c r="E86" s="12" t="n">
-        <v>100</v>
+        <v>-105</v>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.4854</v>
+        <v>0.4982</v>
       </c>
       <c r="G86" s="13" t="n">
-        <v>0.5</v>
+        <v>0.5122</v>
       </c>
       <c r="H86" s="13" t="n">
-        <v>-0.0142</v>
+        <v>-0.0137</v>
       </c>
       <c r="I86" s="13" t="n">
-        <v>-0.02704745105357476</v>
+        <v>-0.02730543519254441</v>
       </c>
       <c r="J86" s="15" t="n">
         <v>0.5</v>
@@ -6001,7 +6001,7 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>DAL @ NYG</t>
+          <t>ATL @ PIT</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -6011,23 +6011,23 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>NYG +2.5</t>
+          <t>ATL +3</t>
         </is>
       </c>
       <c r="E87" s="7" t="n">
-        <v>-105</v>
+        <v>100</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>0.4973</v>
+        <v>0.4854</v>
       </c>
       <c r="G87" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.5</v>
       </c>
       <c r="H87" s="8" t="n">
-        <v>-0.0146</v>
+        <v>-0.0142</v>
       </c>
       <c r="I87" s="8" t="n">
-        <v>-0.02914246245697694</v>
+        <v>-0.02704745105357476</v>
       </c>
       <c r="J87" s="10" t="n">
         <v>0.5</v>
@@ -6042,33 +6042,33 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>NYG @ LAR</t>
+          <t>DET @ BUF</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>BUF ML</t>
         </is>
       </c>
       <c r="E88" s="12" t="n">
-        <v>-110</v>
+        <v>-155</v>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.5924</v>
       </c>
       <c r="G88" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.6078</v>
       </c>
       <c r="H88" s="13" t="n">
-        <v>-0.0157</v>
+        <v>-0.015</v>
       </c>
       <c r="I88" s="13" t="n">
-        <v>-0.03089006208946088</v>
+        <v>-0.02513499119431295</v>
       </c>
       <c r="J88" s="15" t="n">
         <v>0.5</v>
@@ -6083,33 +6083,33 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>GB @ MIN</t>
+          <t>NYG @ LAR</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>GB ML</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="E89" s="7" t="n">
-        <v>-102</v>
+        <v>-110</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>0.4881</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="G89" s="8" t="n">
-        <v>0.505</v>
+        <v>0.5238</v>
       </c>
       <c r="H89" s="8" t="n">
-        <v>-0.0164</v>
+        <v>-0.0157</v>
       </c>
       <c r="I89" s="8" t="n">
-        <v>-0.03312296297617506</v>
+        <v>-0.03089006208946088</v>
       </c>
       <c r="J89" s="10" t="n">
         <v>0.5</v>
@@ -6124,7 +6124,7 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>WSH @ DAL</t>
+          <t>GB @ MIN</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
@@ -6134,23 +6134,23 @@
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>WSH ML</t>
+          <t>GB ML</t>
         </is>
       </c>
       <c r="E90" s="12" t="n">
-        <v>170</v>
+        <v>-102</v>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.3533</v>
+        <v>0.4886</v>
       </c>
       <c r="G90" s="13" t="n">
-        <v>0.3704</v>
+        <v>0.505</v>
       </c>
       <c r="H90" s="13" t="n">
-        <v>-0.0165</v>
+        <v>-0.0159</v>
       </c>
       <c r="I90" s="13" t="n">
-        <v>-0.04566378539151861</v>
+        <v>-0.03204689381793407</v>
       </c>
       <c r="J90" s="15" t="n">
         <v>0.5</v>
@@ -6165,33 +6165,33 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>DET @ BUF</t>
+          <t>WSH @ DAL</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>BUF -3</t>
+          <t>WSH ML</t>
         </is>
       </c>
       <c r="E91" s="7" t="n">
-        <v>-110</v>
+        <v>170</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>0.5064</v>
+        <v>0.3533</v>
       </c>
       <c r="G91" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.3704</v>
       </c>
       <c r="H91" s="8" t="n">
-        <v>-0.0169</v>
+        <v>-0.0165</v>
       </c>
       <c r="I91" s="8" t="n">
-        <v>-0.03086196457727386</v>
+        <v>-0.04566378539151861</v>
       </c>
       <c r="J91" s="10" t="n">
         <v>0.5</v>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>TB @ CIN</t>
+          <t>DET @ BUF</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
@@ -6216,23 +6216,23 @@
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>TB +3.5</t>
+          <t>BUF -3</t>
         </is>
       </c>
       <c r="E92" s="12" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.4941</v>
+        <v>0.5064</v>
       </c>
       <c r="G92" s="13" t="n">
-        <v>0.5122</v>
+        <v>0.5238</v>
       </c>
       <c r="H92" s="13" t="n">
-        <v>-0.0175</v>
+        <v>-0.0169</v>
       </c>
       <c r="I92" s="13" t="n">
-        <v>-0.0353192413197938</v>
+        <v>-0.03086196457727386</v>
       </c>
       <c r="J92" s="15" t="n">
         <v>0.5</v>
@@ -6247,33 +6247,33 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>BAL @ IND</t>
+          <t>TB @ CIN</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Under 48.5</t>
+          <t>TB +3.5</t>
         </is>
       </c>
       <c r="E93" s="7" t="n">
-        <v>-115</v>
+        <v>-105</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>0.5165</v>
+        <v>0.4941</v>
       </c>
       <c r="G93" s="8" t="n">
-        <v>0.5349</v>
+        <v>0.5122</v>
       </c>
       <c r="H93" s="8" t="n">
-        <v>-0.0177</v>
+        <v>-0.0175</v>
       </c>
       <c r="I93" s="8" t="n">
-        <v>-0.03436382238512642</v>
+        <v>-0.0353192413197938</v>
       </c>
       <c r="J93" s="10" t="n">
         <v>0.5</v>
@@ -6288,33 +6288,33 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>DET @ BUF</t>
+          <t>BAL @ IND</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>DET ML</t>
+          <t>Under 48.5</t>
         </is>
       </c>
       <c r="E94" s="12" t="n">
-        <v>136</v>
+        <v>-115</v>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.4039</v>
+        <v>0.5165</v>
       </c>
       <c r="G94" s="13" t="n">
-        <v>0.4237</v>
+        <v>0.5349</v>
       </c>
       <c r="H94" s="13" t="n">
-        <v>-0.019</v>
+        <v>-0.0177</v>
       </c>
       <c r="I94" s="13" t="n">
-        <v>-0.0463007800836539</v>
+        <v>-0.03436382238512642</v>
       </c>
       <c r="J94" s="15" t="n">
         <v>0.5</v>
@@ -6346,16 +6346,16 @@
         <v>-118</v>
       </c>
       <c r="F95" s="8" t="n">
-        <v>0.5207000000000001</v>
+        <v>0.5212</v>
       </c>
       <c r="G95" s="8" t="n">
         <v>0.5413</v>
       </c>
       <c r="H95" s="8" t="n">
-        <v>-0.0197</v>
+        <v>-0.0192</v>
       </c>
       <c r="I95" s="8" t="n">
-        <v>-0.03803380630560044</v>
+        <v>-0.0370338349032584</v>
       </c>
       <c r="J95" s="10" t="n">
         <v>0.5</v>
@@ -6657,33 +6657,33 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>DET @ BUF</t>
+          <t>CAR @ ATL</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>BUF ML</t>
+          <t>Under 44.5</t>
         </is>
       </c>
       <c r="E103" s="7" t="n">
-        <v>-162</v>
+        <v>-118</v>
       </c>
       <c r="F103" s="8" t="n">
-        <v>0.5961</v>
+        <v>0.5188</v>
       </c>
       <c r="G103" s="8" t="n">
-        <v>0.6183</v>
+        <v>0.5413</v>
       </c>
       <c r="H103" s="8" t="n">
-        <v>-0.0211</v>
+        <v>-0.0213</v>
       </c>
       <c r="I103" s="8" t="n">
-        <v>-0.03568367419305923</v>
+        <v>-0.04156327600671267</v>
       </c>
       <c r="J103" s="10" t="n">
         <v>0.5</v>
@@ -6698,33 +6698,33 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>CAR @ ATL</t>
+          <t>DEN @ KC</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>Under 44.5</t>
+          <t>DEN +3</t>
         </is>
       </c>
       <c r="E104" s="12" t="n">
-        <v>-118</v>
+        <v>-115</v>
       </c>
       <c r="F104" s="13" t="n">
-        <v>0.5188</v>
+        <v>0.5119</v>
       </c>
       <c r="G104" s="13" t="n">
-        <v>0.5413</v>
+        <v>0.5349</v>
       </c>
       <c r="H104" s="13" t="n">
-        <v>-0.0213</v>
+        <v>-0.0217</v>
       </c>
       <c r="I104" s="13" t="n">
-        <v>-0.04156327600671267</v>
+        <v>-0.03984800728432142</v>
       </c>
       <c r="J104" s="15" t="n">
         <v>0.5</v>
@@ -6744,28 +6744,28 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>DEN +3</t>
+          <t>DEN ML</t>
         </is>
       </c>
       <c r="E105" s="7" t="n">
-        <v>-115</v>
+        <v>124</v>
       </c>
       <c r="F105" s="8" t="n">
-        <v>0.5119</v>
+        <v>0.4232</v>
       </c>
       <c r="G105" s="8" t="n">
-        <v>0.5349</v>
+        <v>0.4464</v>
       </c>
       <c r="H105" s="8" t="n">
-        <v>-0.0217</v>
+        <v>-0.0219</v>
       </c>
       <c r="I105" s="8" t="n">
-        <v>-0.03984800728432142</v>
+        <v>-0.05151341570750978</v>
       </c>
       <c r="J105" s="10" t="n">
         <v>0.5</v>
@@ -6780,33 +6780,33 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>DEN @ KC</t>
+          <t>DAL @ NYG</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>DEN ML</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="E106" s="12" t="n">
-        <v>124</v>
+        <v>-110</v>
       </c>
       <c r="F106" s="13" t="n">
-        <v>0.4232</v>
+        <v>0.5</v>
       </c>
       <c r="G106" s="13" t="n">
-        <v>0.4464</v>
+        <v>0.5238</v>
       </c>
       <c r="H106" s="13" t="n">
-        <v>-0.0219</v>
+        <v>-0.0224</v>
       </c>
       <c r="I106" s="13" t="n">
-        <v>-0.05151341570750978</v>
+        <v>-0.04545406739379704</v>
       </c>
       <c r="J106" s="15" t="n">
         <v>0.5</v>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>Under 48.5</t>
         </is>
       </c>
       <c r="E107" s="7" t="n">
@@ -6847,7 +6847,7 @@
         <v>-0.0224</v>
       </c>
       <c r="I107" s="8" t="n">
-        <v>-0.04545406739379704</v>
+        <v>-0.04545502351529379</v>
       </c>
       <c r="J107" s="10" t="n">
         <v>0.5</v>
@@ -6862,7 +6862,7 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>DAL @ NYG</t>
+          <t>CAR @ ATL</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
@@ -6872,23 +6872,23 @@
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>Under 48.5</t>
+          <t>Over 44.5</t>
         </is>
       </c>
       <c r="E108" s="12" t="n">
-        <v>-110</v>
+        <v>-102</v>
       </c>
       <c r="F108" s="13" t="n">
-        <v>0.5</v>
+        <v>0.4812</v>
       </c>
       <c r="G108" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.505</v>
       </c>
       <c r="H108" s="13" t="n">
         <v>-0.0224</v>
       </c>
       <c r="I108" s="13" t="n">
-        <v>-0.04545502351529379</v>
+        <v>-0.04700925315272514</v>
       </c>
       <c r="J108" s="15" t="n">
         <v>0.5</v>
@@ -6903,7 +6903,7 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>CAR @ ATL</t>
+          <t>PIT @ NE</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
@@ -6913,23 +6913,23 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Over 44.5</t>
+          <t>Over 43.5</t>
         </is>
       </c>
       <c r="E109" s="7" t="n">
-        <v>-102</v>
+        <v>-110</v>
       </c>
       <c r="F109" s="8" t="n">
-        <v>0.4812</v>
+        <v>0.5</v>
       </c>
       <c r="G109" s="8" t="n">
-        <v>0.505</v>
+        <v>0.5238</v>
       </c>
       <c r="H109" s="8" t="n">
         <v>-0.0224</v>
       </c>
       <c r="I109" s="8" t="n">
-        <v>-0.04700925315272514</v>
+        <v>-0.04544960421788274</v>
       </c>
       <c r="J109" s="10" t="n">
         <v>0.5</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>Over 43.5</t>
+          <t>Under 43.5</t>
         </is>
       </c>
       <c r="E110" s="12" t="n">
@@ -6970,7 +6970,7 @@
         <v>-0.0224</v>
       </c>
       <c r="I110" s="13" t="n">
-        <v>-0.04544960421788274</v>
+        <v>-0.04545948669120808</v>
       </c>
       <c r="J110" s="15" t="n">
         <v>0.5</v>
@@ -6985,33 +6985,33 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>PIT @ NE</t>
+          <t>DEN @ KC</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Under 43.5</t>
+          <t>KC -3</t>
         </is>
       </c>
       <c r="E111" s="7" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="F111" s="8" t="n">
-        <v>0.5</v>
+        <v>0.4881</v>
       </c>
       <c r="G111" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5122</v>
       </c>
       <c r="H111" s="8" t="n">
-        <v>-0.0224</v>
+        <v>-0.0227</v>
       </c>
       <c r="I111" s="8" t="n">
-        <v>-0.04545948669120808</v>
+        <v>-0.04367765948996361</v>
       </c>
       <c r="J111" s="10" t="n">
         <v>0.5</v>
@@ -7026,33 +7026,33 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>DEN @ KC</t>
+          <t>WSH @ DAL</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>KC -3</t>
+          <t>DAL ML</t>
         </is>
       </c>
       <c r="E112" s="12" t="n">
-        <v>-105</v>
+        <v>-205</v>
       </c>
       <c r="F112" s="13" t="n">
-        <v>0.4881</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="G112" s="13" t="n">
-        <v>0.5122</v>
+        <v>0.6721</v>
       </c>
       <c r="H112" s="13" t="n">
-        <v>-0.0227</v>
+        <v>-0.0238</v>
       </c>
       <c r="I112" s="13" t="n">
-        <v>-0.04367765948996361</v>
+        <v>-0.03754257584553977</v>
       </c>
       <c r="J112" s="15" t="n">
         <v>0.5</v>
@@ -7067,33 +7067,33 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>WSH @ DAL</t>
+          <t>GB @ MIN</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>DAL ML</t>
+          <t>MIN -1.5</t>
         </is>
       </c>
       <c r="E113" s="7" t="n">
-        <v>-205</v>
+        <v>-102</v>
       </c>
       <c r="F113" s="8" t="n">
-        <v>0.6467000000000001</v>
+        <v>0.4788</v>
       </c>
       <c r="G113" s="8" t="n">
-        <v>0.6721</v>
+        <v>0.505</v>
       </c>
       <c r="H113" s="8" t="n">
-        <v>-0.0238</v>
+        <v>-0.0244</v>
       </c>
       <c r="I113" s="8" t="n">
-        <v>-0.03754257584553977</v>
+        <v>-0.05186461194666003</v>
       </c>
       <c r="J113" s="10" t="n">
         <v>0.5</v>
@@ -7108,7 +7108,7 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>GB @ MIN</t>
+          <t>CAR @ ATL</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
@@ -7118,23 +7118,23 @@
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>MIN -1.5</t>
+          <t>CAR +1.5</t>
         </is>
       </c>
       <c r="E114" s="12" t="n">
-        <v>-102</v>
+        <v>-110</v>
       </c>
       <c r="F114" s="13" t="n">
-        <v>0.4793</v>
+        <v>0.4976</v>
       </c>
       <c r="G114" s="13" t="n">
-        <v>0.505</v>
+        <v>0.5238</v>
       </c>
       <c r="H114" s="13" t="n">
-        <v>-0.0239</v>
+        <v>-0.0244</v>
       </c>
       <c r="I114" s="13" t="n">
-        <v>-0.05079268721441393</v>
+        <v>-0.0499656551548569</v>
       </c>
       <c r="J114" s="15" t="n">
         <v>0.5</v>
@@ -7149,33 +7149,33 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>CAR @ ATL</t>
+          <t>CIN @ HOU</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>CAR +1.5</t>
+          <t>Under 46.5</t>
         </is>
       </c>
       <c r="E115" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F115" s="8" t="n">
-        <v>0.4976</v>
+        <v>0.4975</v>
       </c>
       <c r="G115" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H115" s="8" t="n">
-        <v>-0.0244</v>
+        <v>-0.0245</v>
       </c>
       <c r="I115" s="8" t="n">
-        <v>-0.0499656551548569</v>
+        <v>-0.05031105788036128</v>
       </c>
       <c r="J115" s="10" t="n">
         <v>0.5</v>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>CIN @ HOU</t>
+          <t>CLE @ TB</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>Under 46.5</t>
+          <t>Under 42.5</t>
         </is>
       </c>
       <c r="E116" s="12" t="n">
@@ -7216,7 +7216,7 @@
         <v>-0.0245</v>
       </c>
       <c r="I116" s="13" t="n">
-        <v>-0.05031105788036128</v>
+        <v>-0.05031725382596147</v>
       </c>
       <c r="J116" s="15" t="n">
         <v>0.5</v>
@@ -7231,7 +7231,7 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>CLE @ TB</t>
+          <t>MIA @ SF</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Under 42.5</t>
+          <t>Over 46.5</t>
         </is>
       </c>
       <c r="E117" s="7" t="n">
@@ -7257,7 +7257,7 @@
         <v>-0.0245</v>
       </c>
       <c r="I117" s="8" t="n">
-        <v>-0.05031725382596147</v>
+        <v>-0.05030855398815443</v>
       </c>
       <c r="J117" s="10" t="n">
         <v>0.5</v>
@@ -7272,33 +7272,33 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>MIA @ SF</t>
+          <t>WSH @ DAL</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>Over 46.5</t>
+          <t>WSH +4.5</t>
         </is>
       </c>
       <c r="E118" s="12" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="F118" s="13" t="n">
-        <v>0.4975</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="G118" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5349</v>
       </c>
       <c r="H118" s="13" t="n">
         <v>-0.0245</v>
       </c>
       <c r="I118" s="13" t="n">
-        <v>-0.05030855398815443</v>
+        <v>-0.04916540928875934</v>
       </c>
       <c r="J118" s="15" t="n">
         <v>0.5</v>
@@ -7313,33 +7313,33 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>WSH @ DAL</t>
+          <t>DET @ BUF</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>WSH +4.5</t>
+          <t>DET ML</t>
         </is>
       </c>
       <c r="E119" s="7" t="n">
-        <v>-115</v>
+        <v>130</v>
       </c>
       <c r="F119" s="8" t="n">
-        <v>0.5086000000000001</v>
+        <v>0.4076</v>
       </c>
       <c r="G119" s="8" t="n">
-        <v>0.5349</v>
+        <v>0.4348</v>
       </c>
       <c r="H119" s="8" t="n">
-        <v>-0.0245</v>
+        <v>-0.0252</v>
       </c>
       <c r="I119" s="8" t="n">
-        <v>-0.04916540928875934</v>
+        <v>-0.06204501268553664</v>
       </c>
       <c r="J119" s="10" t="n">
         <v>0.5</v>
@@ -7494,16 +7494,16 @@
         <v>-118</v>
       </c>
       <c r="F123" s="8" t="n">
-        <v>0.5119</v>
+        <v>0.5114</v>
       </c>
       <c r="G123" s="8" t="n">
         <v>0.5413</v>
       </c>
       <c r="H123" s="8" t="n">
-        <v>-0.0269</v>
+        <v>-0.0273</v>
       </c>
       <c r="I123" s="8" t="n">
-        <v>-0.05375021104836747</v>
+        <v>-0.05475401394857082</v>
       </c>
       <c r="J123" s="10" t="n">
         <v>0.5</v>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>DAL @ NYG</t>
+          <t>BUF @ HOU</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
@@ -7733,23 +7733,23 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>DAL -2.5</t>
+          <t>HOU +1.5</t>
         </is>
       </c>
       <c r="E129" s="7" t="n">
         <v>-115</v>
       </c>
       <c r="F129" s="8" t="n">
-        <v>0.5027</v>
+        <v>0.5018</v>
       </c>
       <c r="G129" s="8" t="n">
         <v>0.5349</v>
       </c>
       <c r="H129" s="8" t="n">
-        <v>-0.0289</v>
+        <v>-0.0296</v>
       </c>
       <c r="I129" s="8" t="n">
-        <v>-0.06011066426442196</v>
+        <v>-0.06186976884531548</v>
       </c>
       <c r="J129" s="10" t="n">
         <v>0.5</v>
@@ -7769,28 +7769,28 @@
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>HOU +1.5</t>
+          <t>HOU ML</t>
         </is>
       </c>
       <c r="E130" s="12" t="n">
-        <v>-115</v>
+        <v>-102</v>
       </c>
       <c r="F130" s="13" t="n">
-        <v>0.5018</v>
+        <v>0.4713</v>
       </c>
       <c r="G130" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.505</v>
       </c>
       <c r="H130" s="13" t="n">
-        <v>-0.0296</v>
+        <v>-0.03</v>
       </c>
       <c r="I130" s="13" t="n">
-        <v>-0.06186976884531548</v>
+        <v>-0.0660797247707034</v>
       </c>
       <c r="J130" s="15" t="n">
         <v>0.5</v>
@@ -7805,7 +7805,7 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>BUF @ HOU</t>
+          <t>TB @ CIN</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
@@ -7815,23 +7815,23 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>HOU ML</t>
+          <t>CIN ML</t>
         </is>
       </c>
       <c r="E131" s="7" t="n">
-        <v>-102</v>
+        <v>-198</v>
       </c>
       <c r="F131" s="8" t="n">
-        <v>0.4713</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="G131" s="8" t="n">
-        <v>0.505</v>
+        <v>0.6644</v>
       </c>
       <c r="H131" s="8" t="n">
-        <v>-0.03</v>
+        <v>-0.0302</v>
       </c>
       <c r="I131" s="8" t="n">
-        <v>-0.0660797247707034</v>
+        <v>-0.0506557505942366</v>
       </c>
       <c r="J131" s="10" t="n">
         <v>0.5</v>
@@ -7846,33 +7846,33 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>TB @ CIN</t>
+          <t>JAX @ DEN</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>CIN ML</t>
+          <t>JAX +2.5</t>
         </is>
       </c>
       <c r="E132" s="12" t="n">
-        <v>-198</v>
+        <v>-105</v>
       </c>
       <c r="F132" s="13" t="n">
-        <v>0.6304999999999999</v>
+        <v>0.4782</v>
       </c>
       <c r="G132" s="13" t="n">
-        <v>0.6644</v>
+        <v>0.5122</v>
       </c>
       <c r="H132" s="13" t="n">
-        <v>-0.0302</v>
+        <v>-0.0303</v>
       </c>
       <c r="I132" s="13" t="n">
-        <v>-0.0506557505942366</v>
+        <v>-0.06645349675666634</v>
       </c>
       <c r="J132" s="15" t="n">
         <v>0.5</v>
@@ -7887,33 +7887,33 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>JAX @ DEN</t>
+          <t>ATL @ PIT</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>JAX +2.5</t>
+          <t>PIT ML</t>
         </is>
       </c>
       <c r="E133" s="7" t="n">
-        <v>-105</v>
+        <v>-175</v>
       </c>
       <c r="F133" s="8" t="n">
-        <v>0.4782</v>
+        <v>0.6021</v>
       </c>
       <c r="G133" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.6364</v>
       </c>
       <c r="H133" s="8" t="n">
-        <v>-0.0303</v>
+        <v>-0.0304</v>
       </c>
       <c r="I133" s="8" t="n">
-        <v>-0.06645349675666634</v>
+        <v>-0.05329758870682888</v>
       </c>
       <c r="J133" s="10" t="n">
         <v>0.5</v>
@@ -7928,33 +7928,33 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>ATL @ PIT</t>
+          <t>PHI @ TEN</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>PIT ML</t>
+          <t>Under 42.5</t>
         </is>
       </c>
       <c r="E134" s="12" t="n">
-        <v>-175</v>
+        <v>-110</v>
       </c>
       <c r="F134" s="13" t="n">
-        <v>0.6021</v>
+        <v>0.4873</v>
       </c>
       <c r="G134" s="13" t="n">
-        <v>0.6364</v>
+        <v>0.5238</v>
       </c>
       <c r="H134" s="13" t="n">
-        <v>-0.0304</v>
+        <v>-0.032</v>
       </c>
       <c r="I134" s="13" t="n">
-        <v>-0.05329758870682888</v>
+        <v>-0.06972815983667563</v>
       </c>
       <c r="J134" s="15" t="n">
         <v>0.5</v>
@@ -7969,7 +7969,7 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>PHI @ TEN</t>
+          <t>SEA @ ARI</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
@@ -7979,7 +7979,7 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Under 42.5</t>
+          <t>Over 44.5</t>
         </is>
       </c>
       <c r="E135" s="7" t="n">
@@ -7995,7 +7995,7 @@
         <v>-0.032</v>
       </c>
       <c r="I135" s="8" t="n">
-        <v>-0.06972815983667563</v>
+        <v>-0.06971795805679165</v>
       </c>
       <c r="J135" s="10" t="n">
         <v>0.5</v>
@@ -8010,33 +8010,33 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>SEA @ ARI</t>
+          <t>DAL @ NYG</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>Over 44.5</t>
+          <t>DAL -2.5</t>
         </is>
       </c>
       <c r="E136" s="12" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="F136" s="13" t="n">
-        <v>0.4873</v>
+        <v>0.498</v>
       </c>
       <c r="G136" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5349</v>
       </c>
       <c r="H136" s="13" t="n">
-        <v>-0.032</v>
+        <v>-0.0322</v>
       </c>
       <c r="I136" s="13" t="n">
-        <v>-0.06971795805679165</v>
+        <v>-0.06887416383100897</v>
       </c>
       <c r="J136" s="15" t="n">
         <v>0.5</v>
@@ -8174,33 +8174,33 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>DAL @ NYG</t>
+          <t>NYJ @ TEN</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>DAL ML</t>
+          <t>NYJ +3</t>
         </is>
       </c>
       <c r="E140" s="12" t="n">
-        <v>-148</v>
+        <v>-120</v>
       </c>
       <c r="F140" s="13" t="n">
-        <v>0.5582</v>
+        <v>0.5063</v>
       </c>
       <c r="G140" s="13" t="n">
-        <v>0.5968</v>
+        <v>0.5455</v>
       </c>
       <c r="H140" s="13" t="n">
-        <v>-0.0333</v>
+        <v>-0.0337</v>
       </c>
       <c r="I140" s="13" t="n">
-        <v>-0.06402096304141452</v>
+        <v>-0.06668104813467374</v>
       </c>
       <c r="J140" s="15" t="n">
         <v>0.5</v>
@@ -8215,33 +8215,33 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>NYJ @ TEN</t>
+          <t>JAX @ DEN</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>NYJ +3</t>
+          <t>Under 43.5</t>
         </is>
       </c>
       <c r="E141" s="7" t="n">
-        <v>-120</v>
+        <v>-110</v>
       </c>
       <c r="F141" s="8" t="n">
-        <v>0.5063</v>
+        <v>0.4822</v>
       </c>
       <c r="G141" s="8" t="n">
-        <v>0.5455</v>
+        <v>0.5238</v>
       </c>
       <c r="H141" s="8" t="n">
-        <v>-0.0337</v>
+        <v>-0.0351</v>
       </c>
       <c r="I141" s="8" t="n">
-        <v>-0.06668104813467374</v>
+        <v>-0.07941938779748492</v>
       </c>
       <c r="J141" s="10" t="n">
         <v>0.5</v>
@@ -8256,33 +8256,33 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>JAX @ DEN</t>
+          <t>CIN @ HOU</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>Under 43.5</t>
+          <t>HOU ML</t>
         </is>
       </c>
       <c r="E142" s="12" t="n">
-        <v>-110</v>
+        <v>-135</v>
       </c>
       <c r="F142" s="13" t="n">
-        <v>0.4822</v>
+        <v>0.5324</v>
       </c>
       <c r="G142" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5745</v>
       </c>
       <c r="H142" s="13" t="n">
-        <v>-0.0351</v>
+        <v>-0.0354</v>
       </c>
       <c r="I142" s="13" t="n">
-        <v>-0.07941938779748492</v>
+        <v>-0.07250610709313532</v>
       </c>
       <c r="J142" s="15" t="n">
         <v>0.5</v>
@@ -8297,7 +8297,7 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>CIN @ HOU</t>
+          <t>CLE @ TB</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
@@ -8307,23 +8307,23 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>HOU ML</t>
+          <t>TB ML</t>
         </is>
       </c>
       <c r="E143" s="7" t="n">
-        <v>-135</v>
+        <v>-238</v>
       </c>
       <c r="F143" s="8" t="n">
-        <v>0.5324</v>
+        <v>0.6616</v>
       </c>
       <c r="G143" s="8" t="n">
-        <v>0.5745</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="H143" s="8" t="n">
-        <v>-0.0354</v>
+        <v>-0.0357</v>
       </c>
       <c r="I143" s="8" t="n">
-        <v>-0.07250610709313532</v>
+        <v>-0.05998211080884869</v>
       </c>
       <c r="J143" s="10" t="n">
         <v>0.5</v>
@@ -8338,33 +8338,33 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>CLE @ TB</t>
+          <t>PIT @ NE</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>TB ML</t>
+          <t>NE -4.5</t>
         </is>
       </c>
       <c r="E144" s="12" t="n">
-        <v>-238</v>
+        <v>-110</v>
       </c>
       <c r="F144" s="13" t="n">
-        <v>0.6616</v>
+        <v>0.4813</v>
       </c>
       <c r="G144" s="13" t="n">
-        <v>0.7040999999999999</v>
+        <v>0.5238</v>
       </c>
       <c r="H144" s="13" t="n">
         <v>-0.0357</v>
       </c>
       <c r="I144" s="13" t="n">
-        <v>-0.05998211080884869</v>
+        <v>-0.08120015320190704</v>
       </c>
       <c r="J144" s="15" t="n">
         <v>0.5</v>
@@ -8379,33 +8379,33 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>PIT @ NE</t>
+          <t>DAL @ NYG</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>NE -4.5</t>
+          <t>DAL ML</t>
         </is>
       </c>
       <c r="E145" s="7" t="n">
-        <v>-110</v>
+        <v>-148</v>
       </c>
       <c r="F145" s="8" t="n">
-        <v>0.4813</v>
+        <v>0.5535</v>
       </c>
       <c r="G145" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5968</v>
       </c>
       <c r="H145" s="8" t="n">
-        <v>-0.0357</v>
+        <v>-0.0361</v>
       </c>
       <c r="I145" s="8" t="n">
-        <v>-0.08120015320190704</v>
+        <v>-0.07186151632566973</v>
       </c>
       <c r="J145" s="10" t="n">
         <v>0.5</v>
@@ -8601,16 +8601,16 @@
         <v>-110</v>
       </c>
       <c r="F150" s="13" t="n">
-        <v>0.4776</v>
+        <v>0.4782</v>
       </c>
       <c r="G150" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H150" s="13" t="n">
-        <v>-0.0377</v>
+        <v>-0.0374</v>
       </c>
       <c r="I150" s="13" t="n">
-        <v>-0.08817025980442089</v>
+        <v>-0.08714344903060578</v>
       </c>
       <c r="J150" s="15" t="n">
         <v>0.5</v>
@@ -8957,40 +8957,40 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>NYG @ LAR</t>
+          <t>CHI @ TEN</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>LAR ML</t>
+          <t>TEN -2.5</t>
         </is>
       </c>
       <c r="E159" s="7" t="n">
-        <v>-375</v>
+        <v>-115</v>
       </c>
       <c r="F159" s="8" t="n">
-        <v>0.7371</v>
+        <v>0.4818</v>
       </c>
       <c r="G159" s="8" t="n">
-        <v>0.7895</v>
+        <v>0.5349</v>
       </c>
       <c r="H159" s="8" t="n">
-        <v>-0.0407</v>
+        <v>-0.041</v>
       </c>
       <c r="I159" s="8" t="n">
-        <v>-0.06578729953790932</v>
+        <v>-0.09915168795045587</v>
       </c>
       <c r="J159" s="10" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>price -375 outside the allowed range</t>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
         </is>
       </c>
     </row>
@@ -9002,40 +9002,40 @@
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>CHI @ TEN</t>
+          <t>LV @ LAC</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>TEN -2.5</t>
+          <t>LAC ML</t>
         </is>
       </c>
       <c r="E160" s="12" t="n">
-        <v>-115</v>
+        <v>-375</v>
       </c>
       <c r="F160" s="13" t="n">
-        <v>0.4818</v>
+        <v>0.7348</v>
       </c>
       <c r="G160" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.7895</v>
       </c>
       <c r="H160" s="13" t="n">
-        <v>-0.041</v>
+        <v>-0.0417</v>
       </c>
       <c r="I160" s="13" t="n">
-        <v>-0.09915168795045587</v>
+        <v>-0.06870592645055049</v>
       </c>
       <c r="J160" s="15" t="n">
-        <v>0.15</v>
+        <v>0.5</v>
       </c>
       <c r="K160" s="5" t="inlineStr">
         <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+          <t>price -375 outside the allowed range</t>
         </is>
       </c>
     </row>
@@ -9047,7 +9047,7 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>LV @ LAC</t>
+          <t>MIA @ LV</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
@@ -9057,32 +9057,28 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>LAC ML</t>
+          <t>LV ML</t>
         </is>
       </c>
       <c r="E161" s="7" t="n">
-        <v>-375</v>
+        <v>-205</v>
       </c>
       <c r="F161" s="8" t="n">
-        <v>0.7348</v>
+        <v>0.6167</v>
       </c>
       <c r="G161" s="8" t="n">
-        <v>0.7895</v>
+        <v>0.6721</v>
       </c>
       <c r="H161" s="8" t="n">
-        <v>-0.0417</v>
+        <v>-0.0421</v>
       </c>
       <c r="I161" s="8" t="n">
-        <v>-0.06870592645055049</v>
+        <v>-0.08175258168803778</v>
       </c>
       <c r="J161" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="K161" s="4" t="inlineStr">
-        <is>
-          <t>price -375 outside the allowed range</t>
-        </is>
-      </c>
+      <c r="K161" s="4" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="5" t="inlineStr">
@@ -9092,7 +9088,7 @@
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>MIA @ LV</t>
+          <t>DET @ IND</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
@@ -9102,28 +9098,32 @@
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>LV ML</t>
+          <t>IND ML</t>
         </is>
       </c>
       <c r="E162" s="12" t="n">
-        <v>-205</v>
+        <v>-162</v>
       </c>
       <c r="F162" s="13" t="n">
-        <v>0.6167</v>
+        <v>0.5626</v>
       </c>
       <c r="G162" s="13" t="n">
-        <v>0.6721</v>
+        <v>0.6183</v>
       </c>
       <c r="H162" s="13" t="n">
-        <v>-0.0421</v>
+        <v>-0.0422</v>
       </c>
       <c r="I162" s="13" t="n">
-        <v>-0.08175258168803778</v>
+        <v>-0.08930554821596898</v>
       </c>
       <c r="J162" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K162" s="5" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K162" s="5" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>NO @ DET</t>
+          <t>NYG @ LAR</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
@@ -9143,28 +9143,32 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>DET ML</t>
+          <t>LAR ML</t>
         </is>
       </c>
       <c r="E163" s="7" t="n">
-        <v>-305</v>
+        <v>-375</v>
       </c>
       <c r="F163" s="8" t="n">
-        <v>0.6959</v>
+        <v>0.733</v>
       </c>
       <c r="G163" s="8" t="n">
-        <v>0.7531</v>
+        <v>0.7895</v>
       </c>
       <c r="H163" s="8" t="n">
-        <v>-0.0428</v>
+        <v>-0.0425</v>
       </c>
       <c r="I163" s="8" t="n">
-        <v>-0.07528238844296944</v>
+        <v>-0.07105312127310925</v>
       </c>
       <c r="J163" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="K163" s="4" t="inlineStr"/>
+      <c r="K163" s="4" t="inlineStr">
+        <is>
+          <t>price -375 outside the allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
@@ -9174,33 +9178,33 @@
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>ARI @ LAC</t>
+          <t>NO @ DET</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>LAC -10.5</t>
+          <t>DET ML</t>
         </is>
       </c>
       <c r="E164" s="12" t="n">
-        <v>-110</v>
+        <v>-305</v>
       </c>
       <c r="F164" s="13" t="n">
-        <v>0.4665</v>
+        <v>0.6959</v>
       </c>
       <c r="G164" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.7531</v>
       </c>
       <c r="H164" s="13" t="n">
         <v>-0.0428</v>
       </c>
       <c r="I164" s="13" t="n">
-        <v>-0.1094436399964945</v>
+        <v>-0.07528238844296944</v>
       </c>
       <c r="J164" s="15" t="n">
         <v>0.5</v>
@@ -9215,33 +9219,33 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>MIN @ CHI</t>
+          <t>ARI @ LAC</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>CHI ML</t>
+          <t>LAC -10.5</t>
         </is>
       </c>
       <c r="E165" s="7" t="n">
-        <v>-198</v>
+        <v>-110</v>
       </c>
       <c r="F165" s="8" t="n">
-        <v>0.6065</v>
+        <v>0.4665</v>
       </c>
       <c r="G165" s="8" t="n">
-        <v>0.6644</v>
+        <v>0.5238</v>
       </c>
       <c r="H165" s="8" t="n">
-        <v>-0.0431</v>
+        <v>-0.0428</v>
       </c>
       <c r="I165" s="8" t="n">
-        <v>-0.08643650728381846</v>
+        <v>-0.1094436399964945</v>
       </c>
       <c r="J165" s="10" t="n">
         <v>0.5</v>
@@ -9256,7 +9260,7 @@
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>SF @ LAR</t>
+          <t>MIN @ CHI</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
@@ -9266,23 +9270,23 @@
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>LAR ML</t>
+          <t>CHI ML</t>
         </is>
       </c>
       <c r="E166" s="12" t="n">
-        <v>-185</v>
+        <v>-198</v>
       </c>
       <c r="F166" s="13" t="n">
-        <v>0.5903</v>
+        <v>0.607</v>
       </c>
       <c r="G166" s="13" t="n">
-        <v>0.6491</v>
+        <v>0.6644</v>
       </c>
       <c r="H166" s="13" t="n">
-        <v>-0.0434</v>
+        <v>-0.0429</v>
       </c>
       <c r="I166" s="13" t="n">
-        <v>-0.08977907104745825</v>
+        <v>-0.08563834061144193</v>
       </c>
       <c r="J166" s="15" t="n">
         <v>0.5</v>
@@ -9297,38 +9301,42 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>SF @ LAR</t>
+          <t>CHI @ TEN</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>TEN ML</t>
         </is>
       </c>
       <c r="E167" s="7" t="n">
-        <v>-108</v>
+        <v>-147</v>
       </c>
       <c r="F167" s="8" t="n">
-        <v>0.4605</v>
+        <v>0.5365</v>
       </c>
       <c r="G167" s="8" t="n">
-        <v>0.5192</v>
+        <v>0.5951</v>
       </c>
       <c r="H167" s="8" t="n">
-        <v>-0.0434</v>
+        <v>-0.0433</v>
       </c>
       <c r="I167" s="8" t="n">
-        <v>-0.1131636139255568</v>
+        <v>-0.09768201779898872</v>
       </c>
       <c r="J167" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K167" s="4" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K167" s="4" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
@@ -9338,7 +9346,7 @@
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>BAL @ IND</t>
+          <t>SF @ LAR</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
@@ -9348,23 +9356,23 @@
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>BAL ML</t>
+          <t>LAR ML</t>
         </is>
       </c>
       <c r="E168" s="12" t="n">
-        <v>-175</v>
+        <v>-185</v>
       </c>
       <c r="F168" s="13" t="n">
-        <v>0.5776</v>
+        <v>0.5903</v>
       </c>
       <c r="G168" s="13" t="n">
-        <v>0.6364</v>
+        <v>0.6491</v>
       </c>
       <c r="H168" s="13" t="n">
         <v>-0.0434</v>
       </c>
       <c r="I168" s="13" t="n">
-        <v>-0.0915593756167985</v>
+        <v>-0.08977907104745825</v>
       </c>
       <c r="J168" s="15" t="n">
         <v>0.5</v>
@@ -9379,7 +9387,7 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>CHI @ CAR</t>
+          <t>SF @ LAR</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
@@ -9389,23 +9397,23 @@
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>Over 47.5</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="E169" s="7" t="n">
-        <v>-115</v>
+        <v>-108</v>
       </c>
       <c r="F169" s="8" t="n">
-        <v>0.4759</v>
+        <v>0.4605</v>
       </c>
       <c r="G169" s="8" t="n">
-        <v>0.5349</v>
+        <v>0.5192</v>
       </c>
       <c r="H169" s="8" t="n">
-        <v>-0.0435</v>
+        <v>-0.0434</v>
       </c>
       <c r="I169" s="8" t="n">
-        <v>-0.1103290525258087</v>
+        <v>-0.1131636139255568</v>
       </c>
       <c r="J169" s="10" t="n">
         <v>0.5</v>
@@ -9420,33 +9428,33 @@
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>MIN @ CHI</t>
+          <t>BAL @ IND</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>Over 45.5</t>
+          <t>BAL ML</t>
         </is>
       </c>
       <c r="E170" s="12" t="n">
-        <v>-110</v>
+        <v>-175</v>
       </c>
       <c r="F170" s="13" t="n">
-        <v>0.4645</v>
+        <v>0.5776</v>
       </c>
       <c r="G170" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.6364</v>
       </c>
       <c r="H170" s="13" t="n">
-        <v>-0.0436</v>
+        <v>-0.0434</v>
       </c>
       <c r="I170" s="13" t="n">
-        <v>-0.1132136058104599</v>
+        <v>-0.0915593756167985</v>
       </c>
       <c r="J170" s="15" t="n">
         <v>0.5</v>
@@ -9461,7 +9469,7 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>LV @ LAC</t>
+          <t>CHI @ CAR</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
@@ -9471,23 +9479,23 @@
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>Over 42.5</t>
+          <t>Over 47.5</t>
         </is>
       </c>
       <c r="E171" s="7" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="F171" s="8" t="n">
-        <v>0.4645</v>
+        <v>0.4759</v>
       </c>
       <c r="G171" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5349</v>
       </c>
       <c r="H171" s="8" t="n">
-        <v>-0.0436</v>
+        <v>-0.0435</v>
       </c>
       <c r="I171" s="8" t="n">
-        <v>-0.1132045300743653</v>
+        <v>-0.1103290525258087</v>
       </c>
       <c r="J171" s="10" t="n">
         <v>0.5</v>
@@ -9502,33 +9510,33 @@
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
-          <t>GB @ NYJ</t>
+          <t>MIN @ CHI</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>GB -5.5</t>
+          <t>Over 45.5</t>
         </is>
       </c>
       <c r="E172" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F172" s="13" t="n">
-        <v>0.4639</v>
+        <v>0.4645</v>
       </c>
       <c r="G172" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H172" s="13" t="n">
-        <v>-0.0438</v>
+        <v>-0.0436</v>
       </c>
       <c r="I172" s="13" t="n">
-        <v>-0.1143110927608268</v>
+        <v>-0.1132136058104599</v>
       </c>
       <c r="J172" s="15" t="n">
         <v>0.5</v>
@@ -9543,33 +9551,33 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>NO @ BAL</t>
+          <t>LV @ LAC</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>BAL ML</t>
+          <t>Over 42.5</t>
         </is>
       </c>
       <c r="E173" s="7" t="n">
-        <v>-340</v>
+        <v>-110</v>
       </c>
       <c r="F173" s="8" t="n">
-        <v>0.7123</v>
+        <v>0.4645</v>
       </c>
       <c r="G173" s="8" t="n">
-        <v>0.7727000000000001</v>
+        <v>0.5238</v>
       </c>
       <c r="H173" s="8" t="n">
-        <v>-0.044</v>
+        <v>-0.0436</v>
       </c>
       <c r="I173" s="8" t="n">
-        <v>-0.07758141143790784</v>
+        <v>-0.1132045300743653</v>
       </c>
       <c r="J173" s="10" t="n">
         <v>0.5</v>
@@ -9584,33 +9592,33 @@
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>ATL @ PIT</t>
+          <t>GB @ NYJ</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>Under 41.5</t>
+          <t>GB -5.5</t>
         </is>
       </c>
       <c r="E174" s="12" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="F174" s="13" t="n">
-        <v>0.4507</v>
+        <v>0.4639</v>
       </c>
       <c r="G174" s="13" t="n">
-        <v>0.5122</v>
+        <v>0.5238</v>
       </c>
       <c r="H174" s="13" t="n">
-        <v>-0.0444</v>
+        <v>-0.0438</v>
       </c>
       <c r="I174" s="13" t="n">
-        <v>-0.1201358675073684</v>
+        <v>-0.1143110927608268</v>
       </c>
       <c r="J174" s="15" t="n">
         <v>0.5</v>
@@ -9630,28 +9638,28 @@
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>Over 46.5</t>
+          <t>BAL ML</t>
         </is>
       </c>
       <c r="E175" s="7" t="n">
-        <v>-110</v>
+        <v>-340</v>
       </c>
       <c r="F175" s="8" t="n">
-        <v>0.462</v>
+        <v>0.7123</v>
       </c>
       <c r="G175" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="H175" s="8" t="n">
-        <v>-0.0445</v>
+        <v>-0.044</v>
       </c>
       <c r="I175" s="8" t="n">
-        <v>-0.1180212704308012</v>
+        <v>-0.07758141143790784</v>
       </c>
       <c r="J175" s="10" t="n">
         <v>0.5</v>
@@ -9666,42 +9674,38 @@
       </c>
       <c r="B176" s="5" t="inlineStr">
         <is>
-          <t>DET @ IND</t>
+          <t>ATL @ PIT</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
-          <t>IND ML</t>
+          <t>Under 41.5</t>
         </is>
       </c>
       <c r="E176" s="12" t="n">
-        <v>-182</v>
+        <v>-105</v>
       </c>
       <c r="F176" s="13" t="n">
-        <v>0.5832000000000001</v>
+        <v>0.4507</v>
       </c>
       <c r="G176" s="13" t="n">
-        <v>0.6454</v>
+        <v>0.5122</v>
       </c>
       <c r="H176" s="13" t="n">
-        <v>-0.0446</v>
+        <v>-0.0444</v>
       </c>
       <c r="I176" s="13" t="n">
-        <v>-0.09556355401233901</v>
+        <v>-0.1201358675073684</v>
       </c>
       <c r="J176" s="15" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K176" s="5" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K176" s="5" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
@@ -9711,33 +9715,33 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>BAL @ IND</t>
+          <t>NO @ BAL</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>BAL -3.5</t>
+          <t>Over 46.5</t>
         </is>
       </c>
       <c r="E177" s="7" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="F177" s="8" t="n">
-        <v>0.457</v>
+        <v>0.462</v>
       </c>
       <c r="G177" s="8" t="n">
-        <v>0.5192</v>
+        <v>0.5238</v>
       </c>
       <c r="H177" s="8" t="n">
-        <v>-0.0446</v>
+        <v>-0.0445</v>
       </c>
       <c r="I177" s="8" t="n">
-        <v>-0.1198027381601606</v>
+        <v>-0.1180212704308012</v>
       </c>
       <c r="J177" s="10" t="n">
         <v>0.5</v>
@@ -9752,7 +9756,7 @@
       </c>
       <c r="B178" s="5" t="inlineStr">
         <is>
-          <t>IND @ KC</t>
+          <t>BAL @ IND</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
@@ -9762,23 +9766,23 @@
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>KC -6.5</t>
+          <t>BAL -3.5</t>
         </is>
       </c>
       <c r="E178" s="12" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="F178" s="13" t="n">
-        <v>0.4616</v>
+        <v>0.457</v>
       </c>
       <c r="G178" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5192</v>
       </c>
       <c r="H178" s="13" t="n">
         <v>-0.0446</v>
       </c>
       <c r="I178" s="13" t="n">
-        <v>-0.1187952686678482</v>
+        <v>-0.1198027381601606</v>
       </c>
       <c r="J178" s="15" t="n">
         <v>0.5</v>
@@ -9793,7 +9797,7 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>NO @ DET</t>
+          <t>IND @ KC</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
@@ -9803,23 +9807,23 @@
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>DET -7</t>
+          <t>KC -6.5</t>
         </is>
       </c>
       <c r="E179" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F179" s="8" t="n">
-        <v>0.4612</v>
+        <v>0.4616</v>
       </c>
       <c r="G179" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H179" s="8" t="n">
-        <v>-0.0448</v>
+        <v>-0.0446</v>
       </c>
       <c r="I179" s="8" t="n">
-        <v>-0.1129977568976037</v>
+        <v>-0.1187952686678482</v>
       </c>
       <c r="J179" s="10" t="n">
         <v>0.5</v>
@@ -9834,42 +9838,38 @@
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>CHI @ TEN</t>
+          <t>NO @ DET</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>TEN ML</t>
+          <t>DET -7</t>
         </is>
       </c>
       <c r="E180" s="12" t="n">
-        <v>-151</v>
+        <v>-110</v>
       </c>
       <c r="F180" s="13" t="n">
-        <v>0.5385</v>
+        <v>0.4612</v>
       </c>
       <c r="G180" s="13" t="n">
-        <v>0.6016</v>
+        <v>0.5238</v>
       </c>
       <c r="H180" s="13" t="n">
-        <v>-0.0449</v>
+        <v>-0.0448</v>
       </c>
       <c r="I180" s="13" t="n">
-        <v>-0.1038571814867415</v>
+        <v>-0.1129977568976037</v>
       </c>
       <c r="J180" s="15" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K180" s="5" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K180" s="5" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
@@ -9920,33 +9920,33 @@
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>NYG @ LAR</t>
+          <t>PHI @ TEN</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>LAR -8.5</t>
+          <t>PHI ML</t>
         </is>
       </c>
       <c r="E182" s="12" t="n">
-        <v>-110</v>
+        <v>-205</v>
       </c>
       <c r="F182" s="13" t="n">
-        <v>0.4605</v>
+        <v>0.608</v>
       </c>
       <c r="G182" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.6721</v>
       </c>
       <c r="H182" s="13" t="n">
-        <v>-0.045</v>
+        <v>-0.0453</v>
       </c>
       <c r="I182" s="13" t="n">
-        <v>-0.1208455758660066</v>
+        <v>-0.09460753841254194</v>
       </c>
       <c r="J182" s="15" t="n">
         <v>0.5</v>
@@ -9961,33 +9961,33 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>PHI @ TEN</t>
+          <t>IND @ KC</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>PHI ML</t>
+          <t>Over 47.5</t>
         </is>
       </c>
       <c r="E183" s="7" t="n">
-        <v>-205</v>
+        <v>-110</v>
       </c>
       <c r="F183" s="8" t="n">
-        <v>0.608</v>
+        <v>0.4595</v>
       </c>
       <c r="G183" s="8" t="n">
-        <v>0.6721</v>
+        <v>0.5238</v>
       </c>
       <c r="H183" s="8" t="n">
         <v>-0.0453</v>
       </c>
       <c r="I183" s="8" t="n">
-        <v>-0.09460753841254194</v>
+        <v>-0.1228216242035979</v>
       </c>
       <c r="J183" s="10" t="n">
         <v>0.5</v>
@@ -10002,33 +10002,33 @@
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>IND @ KC</t>
+          <t>LV @ LAC</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>Over 47.5</t>
+          <t>LAC -8.5</t>
         </is>
       </c>
       <c r="E184" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F184" s="13" t="n">
-        <v>0.4595</v>
+        <v>0.4578</v>
       </c>
       <c r="G184" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H184" s="13" t="n">
-        <v>-0.0453</v>
+        <v>-0.0459</v>
       </c>
       <c r="I184" s="13" t="n">
-        <v>-0.1228216242035979</v>
+        <v>-0.1261070906377938</v>
       </c>
       <c r="J184" s="15" t="n">
         <v>0.5</v>
@@ -10043,33 +10043,33 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>LV @ LAC</t>
+          <t>MIA @ LV</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>LAC -8.5</t>
+          <t>Under 40.5</t>
         </is>
       </c>
       <c r="E185" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F185" s="8" t="n">
-        <v>0.4578</v>
+        <v>0.457</v>
       </c>
       <c r="G185" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H185" s="8" t="n">
-        <v>-0.0459</v>
+        <v>-0.0461</v>
       </c>
       <c r="I185" s="8" t="n">
-        <v>-0.1261070906377938</v>
+        <v>-0.1276251689568088</v>
       </c>
       <c r="J185" s="10" t="n">
         <v>0.5</v>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>MIA @ LV</t>
+          <t>WSH @ DAL</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>Under 40.5</t>
+          <t>Over 51.5</t>
         </is>
       </c>
       <c r="E186" s="12" t="n">
@@ -10110,7 +10110,7 @@
         <v>-0.0461</v>
       </c>
       <c r="I186" s="13" t="n">
-        <v>-0.1276251689568088</v>
+        <v>-0.1276150624646581</v>
       </c>
       <c r="J186" s="15" t="n">
         <v>0.5</v>
@@ -10125,33 +10125,33 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>WSH @ DAL</t>
+          <t>NO @ BAL</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>Over 51.5</t>
+          <t>BAL -7.5</t>
         </is>
       </c>
       <c r="E187" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F187" s="8" t="n">
-        <v>0.457</v>
+        <v>0.4563</v>
       </c>
       <c r="G187" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H187" s="8" t="n">
-        <v>-0.0461</v>
+        <v>-0.0463</v>
       </c>
       <c r="I187" s="8" t="n">
-        <v>-0.1276150624646581</v>
+        <v>-0.1288136605032769</v>
       </c>
       <c r="J187" s="10" t="n">
         <v>0.5</v>
@@ -10166,7 +10166,7 @@
       </c>
       <c r="B188" s="5" t="inlineStr">
         <is>
-          <t>NO @ BAL</t>
+          <t>PHI @ TEN</t>
         </is>
       </c>
       <c r="C188" s="5" t="inlineStr">
@@ -10176,23 +10176,23 @@
       </c>
       <c r="D188" s="5" t="inlineStr">
         <is>
-          <t>BAL -7.5</t>
+          <t>PHI -4.5</t>
         </is>
       </c>
       <c r="E188" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F188" s="13" t="n">
-        <v>0.4563</v>
+        <v>0.4555</v>
       </c>
       <c r="G188" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H188" s="13" t="n">
-        <v>-0.0463</v>
+        <v>-0.0465</v>
       </c>
       <c r="I188" s="13" t="n">
-        <v>-0.1288136605032769</v>
+        <v>-0.1304583911227734</v>
       </c>
       <c r="J188" s="15" t="n">
         <v>0.5</v>
@@ -10207,7 +10207,7 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>PHI @ TEN</t>
+          <t>NYG @ LAR</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
@@ -10217,14 +10217,14 @@
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>PHI -4.5</t>
+          <t>LAR -8.5</t>
         </is>
       </c>
       <c r="E189" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F189" s="8" t="n">
-        <v>0.4555</v>
+        <v>0.4556</v>
       </c>
       <c r="G189" s="8" t="n">
         <v>0.5238</v>
@@ -10233,7 +10233,7 @@
         <v>-0.0465</v>
       </c>
       <c r="I189" s="8" t="n">
-        <v>-0.1304583911227734</v>
+        <v>-0.1303070885267061</v>
       </c>
       <c r="J189" s="10" t="n">
         <v>0.5</v>
@@ -10330,7 +10330,7 @@
       </c>
       <c r="B192" s="5" t="inlineStr">
         <is>
-          <t>CLE @ JAX</t>
+          <t>DET @ IND</t>
         </is>
       </c>
       <c r="C192" s="5" t="inlineStr">
@@ -10340,28 +10340,32 @@
       </c>
       <c r="D192" s="5" t="inlineStr">
         <is>
-          <t>JAX -7.5</t>
+          <t>IND -3.5</t>
         </is>
       </c>
       <c r="E192" s="12" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="F192" s="13" t="n">
-        <v>0.4522</v>
+        <v>0.4485</v>
       </c>
       <c r="G192" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5192</v>
       </c>
       <c r="H192" s="13" t="n">
-        <v>-0.0474</v>
+        <v>-0.0472</v>
       </c>
       <c r="I192" s="13" t="n">
-        <v>-0.1367704564757336</v>
+        <v>-0.1361413819772465</v>
       </c>
       <c r="J192" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K192" s="5" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="K192" s="5" t="inlineStr">
+        <is>
+          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
@@ -10371,33 +10375,33 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>GB @ MIN</t>
+          <t>CLE @ JAX</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>Over 45.5</t>
+          <t>JAX -7.5</t>
         </is>
       </c>
       <c r="E193" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F193" s="8" t="n">
-        <v>0.452</v>
+        <v>0.4522</v>
       </c>
       <c r="G193" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H193" s="8" t="n">
-        <v>-0.0475</v>
+        <v>-0.0474</v>
       </c>
       <c r="I193" s="8" t="n">
-        <v>-0.1371717248119999</v>
+        <v>-0.1367704564757336</v>
       </c>
       <c r="J193" s="10" t="n">
         <v>0.5</v>
@@ -10412,7 +10416,7 @@
       </c>
       <c r="B194" s="5" t="inlineStr">
         <is>
-          <t>WSH @ PHI</t>
+          <t>GB @ MIN</t>
         </is>
       </c>
       <c r="C194" s="5" t="inlineStr">
@@ -10426,19 +10430,19 @@
         </is>
       </c>
       <c r="E194" s="12" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="F194" s="13" t="n">
-        <v>0.4608</v>
+        <v>0.452</v>
       </c>
       <c r="G194" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.5238</v>
       </c>
       <c r="H194" s="13" t="n">
-        <v>-0.048</v>
+        <v>-0.0475</v>
       </c>
       <c r="I194" s="13" t="n">
-        <v>-0.138584043510162</v>
+        <v>-0.1371717248119999</v>
       </c>
       <c r="J194" s="15" t="n">
         <v>0.5</v>
@@ -10453,7 +10457,7 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>DET @ BUF</t>
+          <t>WSH @ PHI</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
@@ -10463,23 +10467,23 @@
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>Over 52.5</t>
+          <t>Over 45.5</t>
         </is>
       </c>
       <c r="E195" s="7" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="F195" s="8" t="n">
-        <v>0.4495</v>
+        <v>0.4608</v>
       </c>
       <c r="G195" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5349</v>
       </c>
       <c r="H195" s="8" t="n">
-        <v>-0.0481</v>
+        <v>-0.048</v>
       </c>
       <c r="I195" s="8" t="n">
-        <v>-0.1419429805428652</v>
+        <v>-0.138584043510162</v>
       </c>
       <c r="J195" s="10" t="n">
         <v>0.5</v>
@@ -10494,7 +10498,7 @@
       </c>
       <c r="B196" s="5" t="inlineStr">
         <is>
-          <t>GB @ NYJ</t>
+          <t>DET @ BUF</t>
         </is>
       </c>
       <c r="C196" s="5" t="inlineStr">
@@ -10504,7 +10508,7 @@
       </c>
       <c r="D196" s="5" t="inlineStr">
         <is>
-          <t>Under 42.5</t>
+          <t>Over 52.5</t>
         </is>
       </c>
       <c r="E196" s="12" t="n">
@@ -10520,7 +10524,7 @@
         <v>-0.0481</v>
       </c>
       <c r="I196" s="13" t="n">
-        <v>-0.1419467748034449</v>
+        <v>-0.1419429805428652</v>
       </c>
       <c r="J196" s="15" t="n">
         <v>0.5</v>
@@ -10535,42 +10539,38 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>DET @ IND</t>
+          <t>GB @ NYJ</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>IND -4.5</t>
+          <t>Under 42.5</t>
         </is>
       </c>
       <c r="E197" s="7" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="F197" s="8" t="n">
-        <v>0.437</v>
+        <v>0.4495</v>
       </c>
       <c r="G197" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.5238</v>
       </c>
       <c r="H197" s="8" t="n">
-        <v>-0.0483</v>
+        <v>-0.0481</v>
       </c>
       <c r="I197" s="8" t="n">
-        <v>-0.14674825328247</v>
+        <v>-0.1419467748034449</v>
       </c>
       <c r="J197" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K197" s="4" t="inlineStr">
-        <is>
-          <t>Preseason — priced for reference only. Preseason results are decided by how long the starters played, which no rating model sees.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="K197" s="4" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="5" t="inlineStr">
@@ -10971,23 +10971,23 @@
       </c>
       <c r="D207" s="4" t="inlineStr">
         <is>
-          <t>Under 36.5</t>
+          <t>Under 37.5</t>
         </is>
       </c>
       <c r="E207" s="7" t="n">
-        <v>-105</v>
+        <v>-115</v>
       </c>
       <c r="F207" s="8" t="n">
-        <v>0.3923</v>
+        <v>0.4046</v>
       </c>
       <c r="G207" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.5349</v>
       </c>
       <c r="H207" s="8" t="n">
-        <v>-0.0536</v>
+        <v>-0.054</v>
       </c>
       <c r="I207" s="8" t="n">
-        <v>-0.2340347918040657</v>
+        <v>-0.243569364711317</v>
       </c>
       <c r="J207" s="10" t="n">
         <v>0.15</v>
@@ -11016,23 +11016,23 @@
       </c>
       <c r="D208" s="5" t="inlineStr">
         <is>
-          <t>Under 36.5</t>
+          <t>Under 35.5</t>
         </is>
       </c>
       <c r="E208" s="12" t="n">
-        <v>-115</v>
+        <v>-112</v>
       </c>
       <c r="F208" s="13" t="n">
-        <v>0.3929</v>
+        <v>0.3884</v>
       </c>
       <c r="G208" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.5283</v>
       </c>
       <c r="H208" s="13" t="n">
-        <v>-0.0544</v>
+        <v>-0.0543</v>
       </c>
       <c r="I208" s="13" t="n">
-        <v>-0.2653677100150881</v>
+        <v>-0.2648913278589037</v>
       </c>
       <c r="J208" s="15" t="n">
         <v>0.15</v>
@@ -11920,7 +11920,7 @@
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>8.5</v>
+        <v>8.23</v>
       </c>
       <c r="E8" s="9" t="n">
         <v>-8.5</v>
@@ -12294,7 +12294,7 @@
         </is>
       </c>
       <c r="D19" s="14" t="n">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="E19" s="14" t="n">
         <v>-3.5</v>
@@ -12498,7 +12498,7 @@
         </is>
       </c>
       <c r="D25" s="14" t="n">
-        <v>-1.81</v>
+        <v>-1.55</v>
       </c>
       <c r="E25" s="14" t="n">
         <v>2.5</v>
@@ -12566,7 +12566,7 @@
         </is>
       </c>
       <c r="D27" s="14" t="n">
-        <v>0.32</v>
+        <v>0.29</v>
       </c>
       <c r="E27" s="14" t="n">
         <v>-1.5</v>
@@ -13014,10 +13014,10 @@
         <v>-2.5</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>40.7</v>
+        <v>41.5</v>
       </c>
       <c r="G40" s="11" t="n">
-        <v>36.5</v>
+        <v>37.5</v>
       </c>
       <c r="H40" s="7" t="n"/>
       <c r="I40" s="17" t="n"/>
@@ -13042,16 +13042,16 @@
         </is>
       </c>
       <c r="D41" s="14" t="n">
-        <v>2.33</v>
+        <v>1.68</v>
       </c>
       <c r="E41" s="14" t="n">
-        <v>-4.5</v>
+        <v>-3.5</v>
       </c>
       <c r="F41" s="16" t="n">
-        <v>41</v>
+        <v>40.1</v>
       </c>
       <c r="G41" s="16" t="n">
-        <v>36.5</v>
+        <v>35.5</v>
       </c>
       <c r="H41" s="12" t="n"/>
       <c r="I41" s="19" t="n"/>
@@ -17388,16 +17388,16 @@
         </is>
       </c>
       <c r="G52" s="14" t="n">
-        <v>-4.5</v>
+        <v>-3.5</v>
       </c>
       <c r="H52" s="16" t="n">
-        <v>36.5</v>
+        <v>35.5</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>-182</v>
+        <v>-162</v>
       </c>
       <c r="K52" s="19" t="n">
         <v>0</v>
@@ -17444,13 +17444,13 @@
         <v>-2.5</v>
       </c>
       <c r="H53" s="11" t="n">
-        <v>36.5</v>
+        <v>37.5</v>
       </c>
       <c r="I53" s="7" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="J53" s="7" t="n">
-        <v>-151</v>
+        <v>-147</v>
       </c>
       <c r="K53" s="17" t="n">
         <v>0</v>
@@ -18348,10 +18348,10 @@
         <v>52.5</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>-162</v>
+        <v>-155</v>
       </c>
       <c r="K70" s="19" t="n">
         <v>0</v>
@@ -22215,10 +22215,10 @@
         <v>47.5</v>
       </c>
       <c r="I143" s="7" t="n">
-        <v>-270</v>
+        <v>-278</v>
       </c>
       <c r="J143" s="7" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="K143" s="17" t="n">
         <v>0</v>
@@ -25766,10 +25766,10 @@
         <v>49.5</v>
       </c>
       <c r="I210" s="12" t="n">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="J210" s="12" t="n">
-        <v>-225</v>
+        <v>-218</v>
       </c>
       <c r="K210" s="19" t="n">
         <v>0</v>
@@ -38022,27 +38022,27 @@
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>Quinshon Judkins</t>
+          <t>Carson Schwesinger</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F180" s="5" t="inlineStr">
         <is>
-          <t>Judkins didn't play in Thursday's exhibition win over New England.</t>
+          <t>Schwesinger (undisclosed) will participate in Saturday's practice, Zac Jackson of The Athletic reports.</t>
         </is>
       </c>
     </row>
@@ -38054,27 +38054,27 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>Joe Royer</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E181" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>Royer (personal) did not play in Thursday's preseason finale against the Patriots.</t>
+          <t>Judkins didn't play in Thursday's exhibition win over New England.</t>
         </is>
       </c>
     </row>
@@ -38086,7 +38086,7 @@
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>Harold Fannin Jr.</t>
+          <t>Joe Royer</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
@@ -38096,17 +38096,17 @@
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F182" s="5" t="inlineStr">
         <is>
-          <t>Fannin did not play in the Browns' 37-13 preseason win over the Patriots on Thursday.</t>
+          <t>Royer (personal) did not play in Thursday's preseason finale against the Patriots.</t>
         </is>
       </c>
     </row>
@@ -38118,12 +38118,12 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Mekhi Blackmon</t>
+          <t>Harold Fannin Jr.</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr">
@@ -38138,7 +38138,7 @@
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>The Browns claimed Blackmon off waivers from the Colts on Friday, Howard Balzer of USA Today reports.</t>
+          <t>Fannin did not play in the Browns' 37-13 preseason win over the Patriots on Thursday.</t>
         </is>
       </c>
     </row>
@@ -38150,12 +38150,12 @@
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>Carsen Ryan</t>
+          <t>Mekhi Blackmon</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D184" s="5" t="inlineStr">
@@ -38170,7 +38170,7 @@
       </c>
       <c r="F184" s="5" t="inlineStr">
         <is>
-          <t>Ryan (foot) caught both of his targets for nine yards in Thursday's 37-13 preseason win over the Patriots.</t>
+          <t>The Browns claimed Blackmon off waivers from the Colts on Friday, Howard Balzer of USA Today reports.</t>
         </is>
       </c>
     </row>
@@ -38182,12 +38182,12 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>Taylen Green</t>
+          <t>Carsen Ryan</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
@@ -38202,7 +38202,7 @@
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>Green completed five of seven passes for 27 yards while rushing eight times for 66 yards in Thursday's 37-13 preseason win over the Patriots.</t>
+          <t>Ryan (foot) caught both of his targets for nine yards in Thursday's 37-13 preseason win over the Patriots.</t>
         </is>
       </c>
     </row>
@@ -38214,7 +38214,7 @@
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>Dillon Gabriel</t>
+          <t>Taylen Green</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
@@ -38234,7 +38234,7 @@
       </c>
       <c r="F186" s="5" t="inlineStr">
         <is>
-          <t>Gabriel completed 12 of 15 passes for 186 yards and three touchdowns while rushing four times for three yards in Thursday's 37-13 preseason win over the Patriots.</t>
+          <t>Green completed five of seven passes for 27 yards while rushing eight times for 66 yards in Thursday's 37-13 preseason win over the Patriots.</t>
         </is>
       </c>
     </row>
@@ -38246,12 +38246,12 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>Andre Szmyt</t>
+          <t>Dillon Gabriel</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr">
@@ -38266,7 +38266,7 @@
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>Szmyt converted all three of his field-goal attempts and went 4-for-4 on PATs in Thursday's 37-13 preseason win over the Patriots.</t>
+          <t>Gabriel completed 12 of 15 passes for 186 yards and three touchdowns while rushing four times for three yards in Thursday's 37-13 preseason win over the Patriots.</t>
         </is>
       </c>
     </row>
@@ -38278,27 +38278,27 @@
       </c>
       <c r="B188" s="5" t="inlineStr">
         <is>
-          <t>Elijah Chatman</t>
+          <t>Andre Szmyt</t>
         </is>
       </c>
       <c r="C188" s="5" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="D188" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E188" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F188" s="5" t="inlineStr">
         <is>
-          <t>Chatman (quadriceps) will not return to Thursday's preseason finale against the Patriots.</t>
+          <t>Szmyt converted all three of his field-goal attempts and went 4-for-4 on PATs in Thursday's 37-13 preseason win over the Patriots.</t>
         </is>
       </c>
     </row>
@@ -38310,12 +38310,12 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>Edefuan Ulofoshio</t>
+          <t>Elijah Chatman</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr">
@@ -38330,7 +38330,7 @@
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>Ulofoshio (biceps) will not return to Thursday's matchup with the Patriots.</t>
+          <t>Chatman (quadriceps) will not return to Thursday's preseason finale against the Patriots.</t>
         </is>
       </c>
     </row>
@@ -38342,7 +38342,7 @@
       </c>
       <c r="B190" s="5" t="inlineStr">
         <is>
-          <t>Carson Schwesinger</t>
+          <t>Edefuan Ulofoshio</t>
         </is>
       </c>
       <c r="C190" s="5" t="inlineStr">
@@ -38362,7 +38362,7 @@
       </c>
       <c r="F190" s="5" t="inlineStr">
         <is>
-          <t>Schwesinger (undisclosed) isn't expected to play in Thursday's preseason game against the Patriots, Kelsey Russo of the Browns' official site reports.</t>
+          <t>Ulofoshio (biceps) will not return to Thursday's matchup with the Patriots.</t>
         </is>
       </c>
     </row>
@@ -39598,27 +39598,27 @@
       </c>
       <c r="B230" s="5" t="inlineStr">
         <is>
-          <t>Justin Joly</t>
+          <t>Marvin Mims Jr.</t>
         </is>
       </c>
       <c r="C230" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D230" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E230" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Bruise</t>
         </is>
       </c>
       <c r="F230" s="5" t="inlineStr">
         <is>
-          <t>Joly secured both targets for 95 yards and a touchdown in the Broncos' 34-6 preseason win over the Vikings on Friday.</t>
+          <t>Head coach Sean Payton told reporters that Mims bruised his foot during the Broncos' 34-6 preseason win over the Vikings on Friday, Chris Tomasson of The Denver Gazette reports.</t>
         </is>
       </c>
     </row>
@@ -39630,12 +39630,12 @@
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>Troy Franklin</t>
+          <t>Justin Joly</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D231" s="4" t="inlineStr">
@@ -39650,7 +39650,7 @@
       </c>
       <c r="F231" s="4" t="inlineStr">
         <is>
-          <t>Franklin failed to secure his only target in the Broncos' 34-6 preseason win over the Vikings on Friday.</t>
+          <t>Joly secured both targets for 95 yards and a touchdown in the Broncos' 34-6 preseason win over the Vikings on Friday.</t>
         </is>
       </c>
     </row>
@@ -39662,27 +39662,27 @@
       </c>
       <c r="B232" s="5" t="inlineStr">
         <is>
-          <t>Reese Taylor</t>
+          <t>Troy Franklin</t>
         </is>
       </c>
       <c r="C232" s="5" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D232" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E232" s="5" t="inlineStr">
         <is>
-          <t>Concussion</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F232" s="5" t="inlineStr">
         <is>
-          <t>Taylor has entered the league's concussion protocol and will not return to Friday's preseason game against the Vikings, Zac Stevens of TheDNVR.com reports.</t>
+          <t>Franklin failed to secure his only target in the Broncos' 34-6 preseason win over the Vikings on Friday.</t>
         </is>
       </c>
     </row>
@@ -39694,12 +39694,12 @@
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>Marvin Mims Jr.</t>
+          <t>Reese Taylor</t>
         </is>
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D233" s="4" t="inlineStr">
@@ -39709,12 +39709,12 @@
       </c>
       <c r="E233" s="4" t="inlineStr">
         <is>
-          <t>Foot</t>
+          <t>Concussion</t>
         </is>
       </c>
       <c r="F233" s="4" t="inlineStr">
         <is>
-          <t>Mims (foot) went to the locker room during the first quarter of Friday's preseason game against the Vikings and is questionable to return, Zac Stevens of TheDNVR.com reports.</t>
+          <t>Taylor has entered the league's concussion protocol and will not return to Friday's preseason game against the Vikings, Zac Stevens of TheDNVR.com reports.</t>
         </is>
       </c>
     </row>
@@ -48342,27 +48342,27 @@
       </c>
       <c r="B505" s="4" t="inlineStr">
         <is>
-          <t>Will Reichard</t>
+          <t>Jacob Thomas</t>
         </is>
       </c>
       <c r="C505" s="4" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D505" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E505" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Ankle</t>
         </is>
       </c>
       <c r="F505" s="4" t="inlineStr">
         <is>
-          <t>Reichard connected on field goals of 46 and 28 yards in the Vikings' 34-6 preseason loss to the Broncos on Friday.</t>
+          <t>Thomas suffered an ankle sprain during Friday night's preseason finale against the Broncos, Kevin Seifert of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -48374,12 +48374,12 @@
       </c>
       <c r="B506" s="5" t="inlineStr">
         <is>
-          <t>Demond Claiborne</t>
+          <t>Will Reichard</t>
         </is>
       </c>
       <c r="C506" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="D506" s="5" t="inlineStr">
@@ -48394,7 +48394,7 @@
       </c>
       <c r="F506" s="5" t="inlineStr">
         <is>
-          <t>Claiborne rushed eight times for 21 yards in the Vikings' 34-6 preseason loss to the Broncos on Friday. He also returned two kickoffs for 55 yards.</t>
+          <t>Reichard connected on field goals of 46 and 28 yards in the Vikings' 34-6 preseason loss to the Broncos on Friday.</t>
         </is>
       </c>
     </row>
@@ -48406,12 +48406,12 @@
       </c>
       <c r="B507" s="4" t="inlineStr">
         <is>
-          <t>Carson Wentz</t>
+          <t>Demond Claiborne</t>
         </is>
       </c>
       <c r="C507" s="4" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D507" s="4" t="inlineStr">
@@ -48426,7 +48426,7 @@
       </c>
       <c r="F507" s="4" t="inlineStr">
         <is>
-          <t>Wentz completed three of four passes for 15 yards with no touchdowns or interceptions and ran once for no gain in Friday's 34-6 preseason loss to the Broncos. He also fumbled once but recovered.</t>
+          <t>Claiborne rushed eight times for 21 yards in the Vikings' 34-6 preseason loss to the Broncos on Friday. He also returned two kickoffs for 55 yards.</t>
         </is>
       </c>
     </row>
@@ -48438,7 +48438,7 @@
       </c>
       <c r="B508" s="5" t="inlineStr">
         <is>
-          <t>J.J. McCarthy</t>
+          <t>Carson Wentz</t>
         </is>
       </c>
       <c r="C508" s="5" t="inlineStr">
@@ -48448,17 +48448,17 @@
       </c>
       <c r="D508" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E508" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F508" s="5" t="inlineStr">
         <is>
-          <t>McCarthy (ankle) won't suit up for Friday's preseason game at Denver, Alec Lewis of The Athletic reports.</t>
+          <t>Wentz completed three of four passes for 15 yards with no touchdowns or interceptions and ran once for no gain in Friday's 34-6 preseason loss to the Broncos. He also fumbled once but recovered.</t>
         </is>
       </c>
     </row>
@@ -48470,17 +48470,17 @@
       </c>
       <c r="B509" s="4" t="inlineStr">
         <is>
-          <t>Dwight McGlothern Jr.</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="C509" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D509" s="4" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E509" s="4" t="inlineStr">
@@ -48490,7 +48490,7 @@
       </c>
       <c r="F509" s="4" t="inlineStr">
         <is>
-          <t>McGlothern (undisclosed) reverted to injured reserve with Minnesota on Wednesday, per the NFL's official transaction log.</t>
+          <t>McCarthy (ankle) won't suit up for Friday's preseason game at Denver, Alec Lewis of The Athletic reports.</t>
         </is>
       </c>
     </row>
@@ -48502,27 +48502,27 @@
       </c>
       <c r="B510" s="5" t="inlineStr">
         <is>
-          <t>Jeshaun Jones</t>
+          <t>Dwight McGlothern Jr.</t>
         </is>
       </c>
       <c r="C510" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D510" s="5" t="inlineStr">
         <is>
-          <t>Suspension</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E510" s="5" t="inlineStr">
         <is>
-          <t>Suspension</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F510" s="5" t="inlineStr">
         <is>
-          <t>The NFL suspended Jones three games Tuesday for violating the league's substance-abuse policy, Mike Garafolo of NFL Network reports.</t>
+          <t>McGlothern (undisclosed) reverted to injured reserve with Minnesota on Wednesday, per the NFL's official transaction log.</t>
         </is>
       </c>
     </row>
@@ -48534,27 +48534,27 @@
       </c>
       <c r="B511" s="4" t="inlineStr">
         <is>
-          <t>Tyreek Chappell</t>
+          <t>Jeshaun Jones</t>
         </is>
       </c>
       <c r="C511" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D511" s="4" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Suspension</t>
         </is>
       </c>
       <c r="E511" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Suspension</t>
         </is>
       </c>
       <c r="F511" s="4" t="inlineStr">
         <is>
-          <t>Chappell (undisclosed) reverted to the Vikings' injured reserve list Tuesday, per the NFL's transaction log.</t>
+          <t>The NFL suspended Jones three games Tuesday for violating the league's substance-abuse policy, Mike Garafolo of NFL Network reports.</t>
         </is>
       </c>
     </row>
@@ -48566,12 +48566,12 @@
       </c>
       <c r="B512" s="5" t="inlineStr">
         <is>
-          <t>Taki Taimani</t>
+          <t>Tyreek Chappell</t>
         </is>
       </c>
       <c r="C512" s="5" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D512" s="5" t="inlineStr">
@@ -48586,7 +48586,7 @@
       </c>
       <c r="F512" s="5" t="inlineStr">
         <is>
-          <t>Taimani (undisclosed) reverted to the Vikings' injured reserve list Tuesday, per the NFL's transaction log.</t>
+          <t>Chappell (undisclosed) reverted to the Vikings' injured reserve list Tuesday, per the NFL's transaction log.</t>
         </is>
       </c>
     </row>
@@ -48598,27 +48598,27 @@
       </c>
       <c r="B513" s="4" t="inlineStr">
         <is>
-          <t>Matt Lauter</t>
+          <t>Taki Taimani</t>
         </is>
       </c>
       <c r="C513" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="D513" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E513" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F513" s="4" t="inlineStr">
         <is>
-          <t>Lauter signed a contract with the Vikings on Monday.</t>
+          <t>Taimani (undisclosed) reverted to the Vikings' injured reserve list Tuesday, per the NFL's transaction log.</t>
         </is>
       </c>
     </row>
@@ -48630,12 +48630,12 @@
       </c>
       <c r="B514" s="5" t="inlineStr">
         <is>
-          <t>Max Brosmer</t>
+          <t>Matt Lauter</t>
         </is>
       </c>
       <c r="C514" s="5" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D514" s="5" t="inlineStr">
@@ -48650,7 +48650,7 @@
       </c>
       <c r="F514" s="5" t="inlineStr">
         <is>
-          <t>Brosmer completed 11 of 17 passes for 98 yards and an interception while logging a four-yard carry during the Vikings' 13-3 preseason loss to the Ravens on Saturday.</t>
+          <t>Lauter signed a contract with the Vikings on Monday.</t>
         </is>
       </c>
     </row>
@@ -48662,7 +48662,7 @@
       </c>
       <c r="B515" s="4" t="inlineStr">
         <is>
-          <t>Kyler Murray</t>
+          <t>Max Brosmer</t>
         </is>
       </c>
       <c r="C515" s="4" t="inlineStr">
@@ -48682,7 +48682,7 @@
       </c>
       <c r="F515" s="4" t="inlineStr">
         <is>
-          <t>Murray isn't expected to suit up for Saturday's preseason game against the Ravens, Kevin Seifert of ESPN.com reports.</t>
+          <t>Brosmer completed 11 of 17 passes for 98 yards and an interception while logging a four-yard carry during the Vikings' 13-3 preseason loss to the Ravens on Saturday.</t>
         </is>
       </c>
     </row>
@@ -48694,27 +48694,27 @@
       </c>
       <c r="B516" s="5" t="inlineStr">
         <is>
-          <t>Caleb Tiernan</t>
+          <t>Kyler Murray</t>
         </is>
       </c>
       <c r="C516" s="5" t="inlineStr">
         <is>
-          <t>OT</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D516" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E516" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F516" s="5" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>Murray isn't expected to suit up for Saturday's preseason game against the Ravens, Kevin Seifert of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -48726,12 +48726,12 @@
       </c>
       <c r="B517" s="4" t="inlineStr">
         <is>
-          <t>Jakobe Thomas</t>
+          <t>Caleb Tiernan</t>
         </is>
       </c>
       <c r="C517" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>OT</t>
         </is>
       </c>
       <c r="D517" s="4" t="inlineStr">
@@ -48741,7 +48741,7 @@
       </c>
       <c r="E517" s="4" t="inlineStr">
         <is>
-          <t>Soreness</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F517" s="4" t="inlineStr">
@@ -48758,27 +48758,27 @@
       </c>
       <c r="B518" s="5" t="inlineStr">
         <is>
-          <t>Jamal Adams</t>
+          <t>Jakobe Thomas</t>
         </is>
       </c>
       <c r="C518" s="5" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D518" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E518" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Soreness</t>
         </is>
       </c>
       <c r="F518" s="5" t="inlineStr">
         <is>
-          <t>ir</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -48790,25 +48790,29 @@
       </c>
       <c r="B519" s="4" t="inlineStr">
         <is>
-          <t>Gavin Bartholomew</t>
+          <t>Jamal Adams</t>
         </is>
       </c>
       <c r="C519" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D519" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E519" s="4" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="F519" s="4" t="inlineStr"/>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F519" s="4" t="inlineStr">
+        <is>
+          <t>ir</t>
+        </is>
+      </c>
     </row>
     <row r="520">
       <c r="A520" s="5" t="inlineStr">
@@ -48818,12 +48822,12 @@
       </c>
       <c r="B520" s="5" t="inlineStr">
         <is>
-          <t>Joshua Metellus</t>
+          <t>Gavin Bartholomew</t>
         </is>
       </c>
       <c r="C520" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D520" s="5" t="inlineStr">
@@ -48846,12 +48850,12 @@
       </c>
       <c r="B521" s="4" t="inlineStr">
         <is>
-          <t>Elijah Williams</t>
+          <t>Joshua Metellus</t>
         </is>
       </c>
       <c r="C521" s="4" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D521" s="4" t="inlineStr">
@@ -48874,12 +48878,12 @@
       </c>
       <c r="B522" s="5" t="inlineStr">
         <is>
-          <t>Jay Ward</t>
+          <t>Elijah Williams</t>
         </is>
       </c>
       <c r="C522" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D522" s="5" t="inlineStr">
@@ -48892,11 +48896,7 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F522" s="5" t="inlineStr">
-        <is>
-          <t>Ward logged two solo tackles during Saturday's preseason opener against the Giants.</t>
-        </is>
-      </c>
+      <c r="F522" s="5" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" s="4" t="inlineStr">
@@ -48906,12 +48906,12 @@
       </c>
       <c r="B523" s="4" t="inlineStr">
         <is>
-          <t>Jauan Jennings</t>
+          <t>Jay Ward</t>
         </is>
       </c>
       <c r="C523" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D523" s="4" t="inlineStr">
@@ -48926,7 +48926,7 @@
       </c>
       <c r="F523" s="4" t="inlineStr">
         <is>
-          <t>Jennings played four snaps on offense and didn't show up in the box score otherwise during the Vikings' 13-10 preseason win over the Giants on Saturday.</t>
+          <t>Ward logged two solo tackles during Saturday's preseason opener against the Giants.</t>
         </is>
       </c>
     </row>
@@ -48938,12 +48938,12 @@
       </c>
       <c r="B524" s="5" t="inlineStr">
         <is>
-          <t>T.J. Hockenson</t>
+          <t>Jauan Jennings</t>
         </is>
       </c>
       <c r="C524" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D524" s="5" t="inlineStr">
@@ -48958,7 +48958,7 @@
       </c>
       <c r="F524" s="5" t="inlineStr">
         <is>
-          <t>Hockenson played five snaps on offense and didn't show up in the box score otherwise during the Vikings' 13-10 preseason win over the Giants on Saturday.</t>
+          <t>Jennings played four snaps on offense and didn't show up in the box score otherwise during the Vikings' 13-10 preseason win over the Giants on Saturday.</t>
         </is>
       </c>
     </row>
@@ -48970,12 +48970,12 @@
       </c>
       <c r="B525" s="4" t="inlineStr">
         <is>
-          <t>Jordan Addison</t>
+          <t>T.J. Hockenson</t>
         </is>
       </c>
       <c r="C525" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D525" s="4" t="inlineStr">
@@ -48990,7 +48990,7 @@
       </c>
       <c r="F525" s="4" t="inlineStr">
         <is>
-          <t>Addison (thumb) caught his only target for eight yards in Saturday's 13-10 preseason win over the Giants.</t>
+          <t>Hockenson played five snaps on offense and didn't show up in the box score otherwise during the Vikings' 13-10 preseason win over the Giants on Saturday.</t>
         </is>
       </c>
     </row>
@@ -49002,12 +49002,12 @@
       </c>
       <c r="B526" s="5" t="inlineStr">
         <is>
-          <t>Jordan Mason</t>
+          <t>Jordan Addison</t>
         </is>
       </c>
       <c r="C526" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D526" s="5" t="inlineStr">
@@ -49022,7 +49022,7 @@
       </c>
       <c r="F526" s="5" t="inlineStr">
         <is>
-          <t>Mason carried the ball three times for 17 yards in Saturday's 13-10 preseason win over the Giants.</t>
+          <t>Addison (thumb) caught his only target for eight yards in Saturday's 13-10 preseason win over the Giants.</t>
         </is>
       </c>
     </row>
@@ -49034,7 +49034,7 @@
       </c>
       <c r="B527" s="4" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr.</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="C527" s="4" t="inlineStr">
@@ -49054,7 +49054,7 @@
       </c>
       <c r="F527" s="4" t="inlineStr">
         <is>
-          <t>Jones carried the ball three times for 27 yards in Saturday's 13-10 preseason win over the Giants. He failed to catch his only target.</t>
+          <t>Mason carried the ball three times for 17 yards in Saturday's 13-10 preseason win over the Giants.</t>
         </is>
       </c>
     </row>
@@ -49066,12 +49066,12 @@
       </c>
       <c r="B528" s="5" t="inlineStr">
         <is>
-          <t>Justin Jefferson</t>
+          <t>Aaron Jones Sr.</t>
         </is>
       </c>
       <c r="C528" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D528" s="5" t="inlineStr">
@@ -49086,7 +49086,7 @@
       </c>
       <c r="F528" s="5" t="inlineStr">
         <is>
-          <t>Jefferson and newly named starting quarterback Kyler Murray have been starting to click at practice, Will Ragatz of Bring Me The Sports reports.</t>
+          <t>Jones carried the ball three times for 27 yards in Saturday's 13-10 preseason win over the Giants. He failed to catch his only target.</t>
         </is>
       </c>
     </row>
@@ -49098,12 +49098,12 @@
       </c>
       <c r="B529" s="4" t="inlineStr">
         <is>
-          <t>Jermar Jefferson</t>
+          <t>Justin Jefferson</t>
         </is>
       </c>
       <c r="C529" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D529" s="4" t="inlineStr">
@@ -49118,7 +49118,7 @@
       </c>
       <c r="F529" s="4" t="inlineStr">
         <is>
-          <t>The Vikings signed Jefferson on Wednesday.</t>
+          <t>Jefferson and newly named starting quarterback Kyler Murray have been starting to click at practice, Will Ragatz of Bring Me The Sports reports.</t>
         </is>
       </c>
     </row>
@@ -50722,27 +50722,27 @@
       </c>
       <c r="B580" s="5" t="inlineStr">
         <is>
-          <t>Tyrone Tracy Jr.</t>
+          <t>CJ Okoye</t>
         </is>
       </c>
       <c r="C580" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="D580" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E580" s="5" t="inlineStr">
         <is>
-          <t>Neck</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F580" s="5" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>The Ravens traded Okoye to the Giants in exchange for a 2027 seventh-round pick Saturday, Ian Rapoport of ESPN and NFL Network reports.</t>
         </is>
       </c>
     </row>
@@ -50754,27 +50754,27 @@
       </c>
       <c r="B581" s="4" t="inlineStr">
         <is>
-          <t>Braxton Berrios</t>
+          <t>Tyrone Tracy Jr.</t>
         </is>
       </c>
       <c r="C581" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D581" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E581" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Neck</t>
         </is>
       </c>
       <c r="F581" s="4" t="inlineStr">
         <is>
-          <t>Berrios (undisclosed) caught one of four targets for 15 yards and lost a fumble in Friday's 23-6 preseason win over the Jets. He also had a 10-yard punt return.</t>
+          <t>Tracy (neck) is dealing with a stinger, but it is not believed to be a major injury, Dan Duggan of The Athletic reports.</t>
         </is>
       </c>
     </row>
@@ -50786,7 +50786,7 @@
       </c>
       <c r="B582" s="5" t="inlineStr">
         <is>
-          <t>Odell Beckham Jr.</t>
+          <t>Braxton Berrios</t>
         </is>
       </c>
       <c r="C582" s="5" t="inlineStr">
@@ -50806,7 +50806,7 @@
       </c>
       <c r="F582" s="5" t="inlineStr">
         <is>
-          <t>Beckham caught three of six targets for 53 yards in Friday's 23-6 preseason win over the Jets.</t>
+          <t>Berrios (undisclosed) caught one of four targets for 15 yards and lost a fumble in Friday's 23-6 preseason win over the Jets. He also had a 10-yard punt return.</t>
         </is>
       </c>
     </row>
@@ -50818,12 +50818,12 @@
       </c>
       <c r="B583" s="4" t="inlineStr">
         <is>
-          <t>Najee Harris</t>
+          <t>Odell Beckham Jr.</t>
         </is>
       </c>
       <c r="C583" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D583" s="4" t="inlineStr">
@@ -50838,7 +50838,7 @@
       </c>
       <c r="F583" s="4" t="inlineStr">
         <is>
-          <t>Harris rushed 11 times for 39 yards and added a 20-yard reception on his lone target in Friday's 23-6 preseason win over the Jets.</t>
+          <t>Beckham caught three of six targets for 53 yards in Friday's 23-6 preseason win over the Jets.</t>
         </is>
       </c>
     </row>
@@ -50850,12 +50850,12 @@
       </c>
       <c r="B584" s="5" t="inlineStr">
         <is>
-          <t>Dominic Zvada</t>
+          <t>Najee Harris</t>
         </is>
       </c>
       <c r="C584" s="5" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D584" s="5" t="inlineStr">
@@ -50870,7 +50870,7 @@
       </c>
       <c r="F584" s="5" t="inlineStr">
         <is>
-          <t>Zvada, per head coach John Harbaugh, will open the season as the Giants' kicker, Pat Leonard of the New York Daily News reports.</t>
+          <t>Harris rushed 11 times for 39 yards and added a 20-yard reception on his lone target in Friday's 23-6 preseason win over the Jets.</t>
         </is>
       </c>
     </row>
@@ -50882,12 +50882,12 @@
       </c>
       <c r="B585" s="4" t="inlineStr">
         <is>
-          <t>Devin Singletary</t>
+          <t>Dominic Zvada</t>
         </is>
       </c>
       <c r="C585" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="D585" s="4" t="inlineStr">
@@ -50902,7 +50902,7 @@
       </c>
       <c r="F585" s="4" t="inlineStr">
         <is>
-          <t>Singletary isn't in uniform ahead of Friday's preseason contest against the Jets, Ryan Dunleavy of the New York Post reports.</t>
+          <t>Zvada, per head coach John Harbaugh, will open the season as the Giants' kicker, Pat Leonard of the New York Daily News reports.</t>
         </is>
       </c>
     </row>
@@ -50914,27 +50914,27 @@
       </c>
       <c r="B586" s="5" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Devin Singletary</t>
         </is>
       </c>
       <c r="C586" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D586" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E586" s="5" t="inlineStr">
         <is>
-          <t>Surgery</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F586" s="5" t="inlineStr">
         <is>
-          <t>Nabers (knee) isn't suited up for Friday's preseason game versus the Jets, Pat Leonard of the New York Daily News reports.</t>
+          <t>Singletary isn't in uniform ahead of Friday's preseason contest against the Jets, Ryan Dunleavy of the New York Post reports.</t>
         </is>
       </c>
     </row>
@@ -50946,7 +50946,7 @@
       </c>
       <c r="B587" s="4" t="inlineStr">
         <is>
-          <t>Calvin Austin III</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="C587" s="4" t="inlineStr">
@@ -50956,17 +50956,17 @@
       </c>
       <c r="D587" s="4" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E587" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Surgery</t>
         </is>
       </c>
       <c r="F587" s="4" t="inlineStr">
         <is>
-          <t>The Giants placed Austin (knee) on injured reserve Thursday, Patricia Traina of SI.com reports.</t>
+          <t>Nabers (knee) isn't suited up for Friday's preseason game versus the Jets, Pat Leonard of the New York Daily News reports.</t>
         </is>
       </c>
     </row>
@@ -50978,7 +50978,7 @@
       </c>
       <c r="B588" s="5" t="inlineStr">
         <is>
-          <t>Kobe Prentice</t>
+          <t>Calvin Austin III</t>
         </is>
       </c>
       <c r="C588" s="5" t="inlineStr">
@@ -50988,17 +50988,17 @@
       </c>
       <c r="D588" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E588" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F588" s="5" t="inlineStr">
         <is>
-          <t>The Giants signed Prentice to a contract Wednesday, Dan Salomone of the team's official site reports.</t>
+          <t>The Giants placed Austin (knee) on injured reserve Thursday, Patricia Traina of SI.com reports.</t>
         </is>
       </c>
     </row>
@@ -51010,12 +51010,12 @@
       </c>
       <c r="B589" s="4" t="inlineStr">
         <is>
-          <t>Josiah Deguara</t>
+          <t>Kobe Prentice</t>
         </is>
       </c>
       <c r="C589" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D589" s="4" t="inlineStr">
@@ -51030,7 +51030,7 @@
       </c>
       <c r="F589" s="4" t="inlineStr">
         <is>
-          <t>The Giants signed Deguara to a contract Wednesday, Dan Salomone of the team's official site reports.</t>
+          <t>The Giants signed Prentice to a contract Wednesday, Dan Salomone of the team's official site reports.</t>
         </is>
       </c>
     </row>
@@ -51042,7 +51042,7 @@
       </c>
       <c r="B590" s="5" t="inlineStr">
         <is>
-          <t>Theo Johnson</t>
+          <t>Josiah Deguara</t>
         </is>
       </c>
       <c r="C590" s="5" t="inlineStr">
@@ -51052,17 +51052,17 @@
       </c>
       <c r="D590" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E590" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F590" s="5" t="inlineStr">
         <is>
-          <t>Johnson missed Wednesday's practice due to a shoulder injury, Evan Barnes of Newsday reports.</t>
+          <t>The Giants signed Deguara to a contract Wednesday, Dan Salomone of the team's official site reports.</t>
         </is>
       </c>
     </row>
@@ -51074,27 +51074,27 @@
       </c>
       <c r="B591" s="4" t="inlineStr">
         <is>
-          <t>Malachi Fields</t>
+          <t>Theo Johnson</t>
         </is>
       </c>
       <c r="C591" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D591" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E591" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F591" s="4" t="inlineStr">
         <is>
-          <t>Fields could be one of multiple Giants receivers who benefits from added opportunities to begin the season after Calvin Austin (knee) sustained a torn ACL during Tuesday's practice, Jordan Raanan of ESPN.com reports.</t>
+          <t>Johnson missed Wednesday's practice due to a shoulder injury, Evan Barnes of Newsday reports.</t>
         </is>
       </c>
     </row>
@@ -51106,7 +51106,7 @@
       </c>
       <c r="B592" s="5" t="inlineStr">
         <is>
-          <t>Darnell Mooney</t>
+          <t>Malachi Fields</t>
         </is>
       </c>
       <c r="C592" s="5" t="inlineStr">
@@ -51126,7 +51126,7 @@
       </c>
       <c r="F592" s="5" t="inlineStr">
         <is>
-          <t>Mooney could have a chance to open the season as the Giants' No. 3 receiver after Calvin Austin (knee) sustained a torn ACL in Tuesday's practice, Jordan Ranaan of ESPN.com reports.</t>
+          <t>Fields could be one of multiple Giants receivers who benefits from added opportunities to begin the season after Calvin Austin (knee) sustained a torn ACL during Tuesday's practice, Jordan Raanan of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -51138,12 +51138,12 @@
       </c>
       <c r="B593" s="4" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Darnell Mooney</t>
         </is>
       </c>
       <c r="C593" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D593" s="4" t="inlineStr">
@@ -51158,7 +51158,7 @@
       </c>
       <c r="F593" s="4" t="inlineStr">
         <is>
-          <t>Skattebo is listed as the Giants' starting running back on the team's unofficial depth chart for the preseason finale versus the Jets, Jordan Raanan of ESPN.com reports.</t>
+          <t>Mooney could have a chance to open the season as the Giants' No. 3 receiver after Calvin Austin (knee) sustained a torn ACL in Tuesday's practice, Jordan Ranaan of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -51170,27 +51170,27 @@
       </c>
       <c r="B594" s="5" t="inlineStr">
         <is>
-          <t>Colton Hood</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C594" s="5" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D594" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E594" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F594" s="5" t="inlineStr">
         <is>
-          <t>Hood (quadriceps) is expected to return to practice this week, Paul Schwartz of New York Post reports.</t>
+          <t>Skattebo is listed as the Giants' starting running back on the team's unofficial depth chart for the preseason finale versus the Jets, Jordan Raanan of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -51202,27 +51202,27 @@
       </c>
       <c r="B595" s="4" t="inlineStr">
         <is>
-          <t>Darius Slayton</t>
+          <t>Colton Hood</t>
         </is>
       </c>
       <c r="C595" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D595" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E595" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F595" s="4" t="inlineStr">
         <is>
-          <t>Slayton caught four of six targets for 58 yards in Saturday's 26-3 preseason win over the Dolphins.</t>
+          <t>Hood (quadriceps) is expected to return to practice this week, Paul Schwartz of New York Post reports.</t>
         </is>
       </c>
     </row>
@@ -51234,12 +51234,12 @@
       </c>
       <c r="B596" s="5" t="inlineStr">
         <is>
-          <t>Jaxson Dart</t>
+          <t>Darius Slayton</t>
         </is>
       </c>
       <c r="C596" s="5" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D596" s="5" t="inlineStr">
@@ -51254,7 +51254,7 @@
       </c>
       <c r="F596" s="5" t="inlineStr">
         <is>
-          <t>Dart didn't suit up for Saturday's 26-3 preseason win over the Dolphins.</t>
+          <t>Slayton caught four of six targets for 58 yards in Saturday's 26-3 preseason win over the Dolphins.</t>
         </is>
       </c>
     </row>
@@ -51266,27 +51266,27 @@
       </c>
       <c r="B597" s="4" t="inlineStr">
         <is>
-          <t>Francis Mauigoa</t>
+          <t>Jaxson Dart</t>
         </is>
       </c>
       <c r="C597" s="4" t="inlineStr">
         <is>
-          <t>OT</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D597" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E597" s="4" t="inlineStr">
         <is>
-          <t>Stinger</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F597" s="4" t="inlineStr">
         <is>
-          <t>Mauigoa (upper body) had to leave Thursday's joint practice with the Dolphins due to a stinger, Dan Benton of USA Today reports.</t>
+          <t>Dart didn't suit up for Saturday's 26-3 preseason win over the Dolphins.</t>
         </is>
       </c>
     </row>
@@ -51298,12 +51298,12 @@
       </c>
       <c r="B598" s="5" t="inlineStr">
         <is>
-          <t>Greg Newsome II</t>
+          <t>Francis Mauigoa</t>
         </is>
       </c>
       <c r="C598" s="5" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>OT</t>
         </is>
       </c>
       <c r="D598" s="5" t="inlineStr">
@@ -51313,12 +51313,12 @@
       </c>
       <c r="E598" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Stinger</t>
         </is>
       </c>
       <c r="F598" s="5" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>Mauigoa (upper body) had to leave Thursday's joint practice with the Dolphins due to a stinger, Dan Benton of USA Today reports.</t>
         </is>
       </c>
     </row>
@@ -51330,12 +51330,12 @@
       </c>
       <c r="B599" s="4" t="inlineStr">
         <is>
-          <t>Lucas Patrick</t>
+          <t>Greg Newsome II</t>
         </is>
       </c>
       <c r="C599" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D599" s="4" t="inlineStr">
@@ -51362,12 +51362,12 @@
       </c>
       <c r="B600" s="5" t="inlineStr">
         <is>
-          <t>Dru Phillips</t>
+          <t>Lucas Patrick</t>
         </is>
       </c>
       <c r="C600" s="5" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D600" s="5" t="inlineStr">
@@ -51377,7 +51377,7 @@
       </c>
       <c r="E600" s="5" t="inlineStr">
         <is>
-          <t>Sprain</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F600" s="5" t="inlineStr">
@@ -51394,27 +51394,27 @@
       </c>
       <c r="B601" s="4" t="inlineStr">
         <is>
-          <t>Roy Robertson-Harris</t>
+          <t>Dru Phillips</t>
         </is>
       </c>
       <c r="C601" s="4" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D601" s="4" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E601" s="4" t="inlineStr">
         <is>
-          <t>Surgery</t>
+          <t>Sprain</t>
         </is>
       </c>
       <c r="F601" s="4" t="inlineStr">
         <is>
-          <t>ir</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -51426,27 +51426,27 @@
       </c>
       <c r="B602" s="5" t="inlineStr">
         <is>
-          <t>John Michael Schmitz Jr.</t>
+          <t>Roy Robertson-Harris</t>
         </is>
       </c>
       <c r="C602" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="D602" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E602" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Surgery</t>
         </is>
       </c>
       <c r="F602" s="5" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>ir</t>
         </is>
       </c>
     </row>
@@ -51458,12 +51458,12 @@
       </c>
       <c r="B603" s="4" t="inlineStr">
         <is>
-          <t>Jalin Hyatt</t>
+          <t>John Michael Schmitz Jr.</t>
         </is>
       </c>
       <c r="C603" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D603" s="4" t="inlineStr">
@@ -51490,17 +51490,17 @@
       </c>
       <c r="B604" s="5" t="inlineStr">
         <is>
-          <t>DJ James</t>
+          <t>Jalin Hyatt</t>
         </is>
       </c>
       <c r="C604" s="5" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D604" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E604" s="5" t="inlineStr">
@@ -51510,7 +51510,7 @@
       </c>
       <c r="F604" s="5" t="inlineStr">
         <is>
-          <t>ir</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -55514,7 +55514,7 @@
       </c>
       <c r="B730" s="5" t="inlineStr">
         <is>
-          <t>Tez Johnson</t>
+          <t>Jalen McMillan</t>
         </is>
       </c>
       <c r="C730" s="5" t="inlineStr">
@@ -55524,17 +55524,17 @@
       </c>
       <c r="D730" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E730" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Soreness</t>
         </is>
       </c>
       <c r="F730" s="5" t="inlineStr">
         <is>
-          <t>Johnson secured one of three targets for nine yards in the Buccaneers' 19-0 preseason loss to the Jaguars on Friday.</t>
+          <t>Head coach Todd Bowles said Saturday that he expects McMillan (knee) to be available for the Buccaneers' Week 1 clash against the Bengals on Sunday, Sept. 13, Greg Auman of Fox Sports reports.</t>
         </is>
       </c>
     </row>
@@ -55546,12 +55546,12 @@
       </c>
       <c r="B731" s="4" t="inlineStr">
         <is>
-          <t>Sean Tucker</t>
+          <t>Tez Johnson</t>
         </is>
       </c>
       <c r="C731" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D731" s="4" t="inlineStr">
@@ -55566,7 +55566,7 @@
       </c>
       <c r="F731" s="4" t="inlineStr">
         <is>
-          <t>Tucker rushed five times for 15 yards and secured his only target for minus-1 yard in the Buccaneers' 19-0 preseason loss to the Jaguars on Friday.</t>
+          <t>Johnson secured one of three targets for nine yards in the Buccaneers' 19-0 preseason loss to the Jaguars on Friday.</t>
         </is>
       </c>
     </row>
@@ -55578,27 +55578,27 @@
       </c>
       <c r="B732" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Kamara</t>
+          <t>Sean Tucker</t>
         </is>
       </c>
       <c r="C732" s="5" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D732" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E732" s="5" t="inlineStr">
         <is>
-          <t>Knee</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F732" s="5" t="inlineStr">
         <is>
-          <t>Kamara (knee) is believed to have suffered an injury during Friday's preseason finale against the Jaguars, Jenna Laine of ESPN.com reports.</t>
+          <t>Tucker rushed five times for 15 yards and secured his only target for minus-1 yard in the Buccaneers' 19-0 preseason loss to the Jaguars on Friday.</t>
         </is>
       </c>
     </row>
@@ -55610,27 +55610,27 @@
       </c>
       <c r="B733" s="4" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>Mohamed Kamara</t>
         </is>
       </c>
       <c r="C733" s="4" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D733" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E733" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Knee</t>
         </is>
       </c>
       <c r="F733" s="4" t="inlineStr">
         <is>
-          <t>Daniels completed eight of 15 passes for 57 yards with no touchdowns or interceptions and rushed four times for nine yards in the Buccaneers' 19-0 preseason loss to the Jaguars on Friday. He also lost a fumble.</t>
+          <t>Kamara (knee) is believed to have suffered an injury during Friday's preseason finale against the Jaguars, Jenna Laine of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -55642,27 +55642,27 @@
       </c>
       <c r="B734" s="5" t="inlineStr">
         <is>
-          <t>Keionte Scott</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="C734" s="5" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D734" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E734" s="5" t="inlineStr">
         <is>
-          <t>Knee</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F734" s="5" t="inlineStr">
         <is>
-          <t>Scott (knee) suffered an injury during Friday's preseason finale against the Jaguars, Jenna Laine of ESPN.com reports.</t>
+          <t>Daniels completed eight of 15 passes for 57 yards with no touchdowns or interceptions and rushed four times for nine yards in the Buccaneers' 19-0 preseason loss to the Jaguars on Friday. He also lost a fumble.</t>
         </is>
       </c>
     </row>
@@ -55674,12 +55674,12 @@
       </c>
       <c r="B735" s="4" t="inlineStr">
         <is>
-          <t>Xavier Williams</t>
+          <t>Keionte Scott</t>
         </is>
       </c>
       <c r="C735" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D735" s="4" t="inlineStr">
@@ -55689,12 +55689,12 @@
       </c>
       <c r="E735" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Knee</t>
         </is>
       </c>
       <c r="F735" s="4" t="inlineStr">
         <is>
-          <t>Williams (hip) is questionable to return to Friday's preseason finale against the Jaguars, Scott Smith of the Buccaneers' official site reports.</t>
+          <t>Scott (knee) suffered an injury during Friday's preseason finale against the Jaguars, Jenna Laine of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -55706,12 +55706,12 @@
       </c>
       <c r="B736" s="5" t="inlineStr">
         <is>
-          <t>Emeka Egbuka</t>
+          <t>Xavier Williams</t>
         </is>
       </c>
       <c r="C736" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D736" s="5" t="inlineStr">
@@ -55721,12 +55721,12 @@
       </c>
       <c r="E736" s="5" t="inlineStr">
         <is>
-          <t>Sprain</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F736" s="5" t="inlineStr">
         <is>
-          <t>Egbuka (toe) continues to rest and recover with the goal of being ready for Week 1, Greg Auman of Fox Sports reports.</t>
+          <t>Williams (hip) is questionable to return to Friday's preseason finale against the Jaguars, Scott Smith of the Buccaneers' official site reports.</t>
         </is>
       </c>
     </row>
@@ -55738,7 +55738,7 @@
       </c>
       <c r="B737" s="4" t="inlineStr">
         <is>
-          <t>Dennis Houston</t>
+          <t>Emeka Egbuka</t>
         </is>
       </c>
       <c r="C737" s="4" t="inlineStr">
@@ -55748,17 +55748,17 @@
       </c>
       <c r="D737" s="4" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E737" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Sprain</t>
         </is>
       </c>
       <c r="F737" s="4" t="inlineStr">
         <is>
-          <t>Houston (groin) reverted to the Buccaneers' injured-reserve list Thursday, Aaron Wilson of KPRC 2 Houston reports.</t>
+          <t>Egbuka (toe) continues to rest and recover with the goal of being ready for Week 1, Greg Auman of Fox Sports reports.</t>
         </is>
       </c>
     </row>
@@ -55770,17 +55770,17 @@
       </c>
       <c r="B738" s="5" t="inlineStr">
         <is>
-          <t>Josh Hayes</t>
+          <t>Dennis Houston</t>
         </is>
       </c>
       <c r="C738" s="5" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D738" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E738" s="5" t="inlineStr">
@@ -55790,7 +55790,7 @@
       </c>
       <c r="F738" s="5" t="inlineStr">
         <is>
-          <t>Hayes (undisclosed) did not participate in Wednesday's practice, PewterReport.com reports.</t>
+          <t>Houston (groin) reverted to the Buccaneers' injured-reserve list Thursday, Aaron Wilson of KPRC 2 Houston reports.</t>
         </is>
       </c>
     </row>
@@ -55802,27 +55802,27 @@
       </c>
       <c r="B739" s="4" t="inlineStr">
         <is>
-          <t>Jha'Quan Jackson</t>
+          <t>Josh Hayes</t>
         </is>
       </c>
       <c r="C739" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D739" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E739" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F739" s="4" t="inlineStr">
         <is>
-          <t>Jackson and the Buccaneers agreed on a contract Wednesday, Scott Smith of the team's official website reports.</t>
+          <t>Hayes (undisclosed) did not participate in Wednesday's practice, PewterReport.com reports.</t>
         </is>
       </c>
     </row>
@@ -55834,7 +55834,7 @@
       </c>
       <c r="B740" s="5" t="inlineStr">
         <is>
-          <t>Jalen McMillan</t>
+          <t>Jha'Quan Jackson</t>
         </is>
       </c>
       <c r="C740" s="5" t="inlineStr">
@@ -55844,17 +55844,17 @@
       </c>
       <c r="D740" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E740" s="5" t="inlineStr">
         <is>
-          <t>Soreness</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F740" s="5" t="inlineStr">
         <is>
-          <t>McMillan (knee) didn't travel with the Buccaneers to Jacksonville for Wednesday's joint practice with the Jaguars, PewterReport.com reports.</t>
+          <t>Jackson and the Buccaneers agreed on a contract Wednesday, Scott Smith of the team's official website reports.</t>
         </is>
       </c>
     </row>
@@ -58010,13 +58010,13 @@
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>81</v>
+        <v>80.7</v>
       </c>
       <c r="E5" s="17" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="F5" s="17" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="G5" s="17" t="n">
         <v>0</v>
@@ -58048,20 +58048,20 @@
         </is>
       </c>
       <c r="D6" s="19" t="n">
-        <v>92.40000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="E6" s="19" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="F6" s="19" t="n">
-        <v>8.1</v>
+        <v>8.9</v>
       </c>
       <c r="G6" s="19" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>Overcast</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="I6" s="14" t="n">
@@ -58069,7 +58069,7 @@
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>92°F</t>
+          <t>93°F</t>
         </is>
       </c>
     </row>
@@ -58096,10 +58096,10 @@
         <v>7.5</v>
       </c>
       <c r="F7" s="17" t="n">
-        <v>7.4</v>
+        <v>10.3</v>
       </c>
       <c r="G7" s="17" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
@@ -58176,10 +58176,10 @@
         <v>6.6</v>
       </c>
       <c r="F9" s="17" t="n">
-        <v>4.3</v>
+        <v>9.6</v>
       </c>
       <c r="G9" s="17" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
@@ -58214,10 +58214,10 @@
         <v>7.4</v>
       </c>
       <c r="F10" s="19" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="G10" s="19" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
@@ -58252,10 +58252,10 @@
         <v>3.6</v>
       </c>
       <c r="F11" s="17" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="G11" s="17" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
@@ -58294,10 +58294,10 @@
         <v>5.4</v>
       </c>
       <c r="F12" s="19" t="n">
-        <v>4.9</v>
+        <v>10.3</v>
       </c>
       <c r="G12" s="19" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
@@ -58332,10 +58332,10 @@
         <v>11.5</v>
       </c>
       <c r="F13" s="17" t="n">
-        <v>16.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G13" s="17" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
@@ -58370,10 +58370,10 @@
         <v>2.8</v>
       </c>
       <c r="F14" s="19" t="n">
-        <v>11</v>
+        <v>3.1</v>
       </c>
       <c r="G14" s="19" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
@@ -58412,10 +58412,10 @@
         <v>3</v>
       </c>
       <c r="F15" s="17" t="n">
-        <v>8.300000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="G15" s="17" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
@@ -58454,10 +58454,10 @@
         <v>4.7</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="G16" s="19" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
@@ -58492,10 +58492,10 @@
         <v>4.2</v>
       </c>
       <c r="F17" s="17" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="G17" s="17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
@@ -58530,10 +58530,10 @@
         <v>5.4</v>
       </c>
       <c r="F18" s="19" t="n">
-        <v>8.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G18" s="19" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
@@ -58572,10 +58572,10 @@
         <v>7.3</v>
       </c>
       <c r="F19" s="17" t="n">
-        <v>11.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G19" s="17" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
@@ -58614,10 +58614,10 @@
         <v>10.4</v>
       </c>
       <c r="F20" s="19" t="n">
-        <v>2.5</v>
+        <v>13.2</v>
       </c>
       <c r="G20" s="19" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
@@ -58652,10 +58652,10 @@
         <v>11.4</v>
       </c>
       <c r="F21" s="17" t="n">
-        <v>8.699999999999999</v>
+        <v>15.9</v>
       </c>
       <c r="G21" s="17" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>

--- a/NFL_Edge_Model.xlsx
+++ b/NFL_Edge_Model.xlsx
@@ -692,7 +692,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Snapshot of the live model, generated 2026-08-30T05:08:09+00:00. Read-only: the model runs in the pipeline, not in this file.</t>
+          <t>Snapshot of the live model, generated 2026-08-30T12:02:30+00:00. Read-only: the model runs in the pipeline, not in this file.</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>2026-08-30T05:08:09+00:00</t>
+          <t>2026-08-30T12:02:30+00:00</t>
         </is>
       </c>
     </row>
@@ -2402,49 +2402,49 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>SEA @ ARI</t>
+          <t>NYJ @ TEN</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>ARI +10</t>
+          <t>Over 38.5</t>
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>0.5810999999999999</v>
+        <v>0.5959</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5349</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>0.0428</v>
+        <v>0.0442</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>0.0573</v>
+        <v>0.061</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>2.05</v>
+        <v>3.67</v>
       </c>
       <c r="K5" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="L5" s="11" t="n">
-        <v>26</v>
+        <v>19.7</v>
       </c>
       <c r="M5" s="11" t="n">
-        <v>18</v>
+        <v>22.5</v>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -2456,49 +2456,49 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>NYJ @ TEN</t>
+          <t>SEA @ ARI</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Over 38.5</t>
+          <t>ARI +10</t>
         </is>
       </c>
       <c r="E6" s="12" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5887</v>
+        <v>0.5810999999999999</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.5238</v>
       </c>
       <c r="H6" s="13" t="n">
-        <v>0.0414</v>
+        <v>0.0428</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>0.0538</v>
+        <v>0.0573</v>
       </c>
       <c r="J6" s="14" t="n">
-        <v>3.43</v>
+        <v>2.05</v>
       </c>
       <c r="K6" s="15" t="n">
         <v>0.5</v>
       </c>
       <c r="L6" s="16" t="n">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="M6" s="16" t="n">
-        <v>22.4</v>
+        <v>18</v>
       </c>
       <c r="N6" s="5" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -2611,33 +2611,33 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>SEA @ ARI</t>
+          <t>NYJ @ TEN</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>ARI +10</t>
+          <t>Over 38.5</t>
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>0.5810999999999999</v>
+        <v>0.5959</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5349</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>0.0428</v>
+        <v>0.0442</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>0.1045800419711989</v>
+        <v>0.1140265738794688</v>
       </c>
       <c r="J5" s="10" t="n">
         <v>0.5</v>
@@ -2652,33 +2652,33 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>NYJ @ TEN</t>
+          <t>SEA @ ARI</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Over 38.5</t>
+          <t>ARI +10</t>
         </is>
       </c>
       <c r="E6" s="12" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5887</v>
+        <v>0.5810999999999999</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.5238</v>
       </c>
       <c r="H6" s="13" t="n">
-        <v>0.0414</v>
+        <v>0.0428</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>0.1006026658878491</v>
+        <v>0.1045800419711989</v>
       </c>
       <c r="J6" s="15" t="n">
         <v>0.5</v>
@@ -2738,33 +2738,33 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>TB @ CIN</t>
+          <t>MIA @ SF</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Under 50.5</t>
+          <t>MIA ML</t>
         </is>
       </c>
       <c r="E8" s="12" t="n">
-        <v>-102</v>
+        <v>470</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.547</v>
+        <v>0.2162</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>0.505</v>
+        <v>0.1754</v>
       </c>
       <c r="H8" s="13" t="n">
-        <v>0.0354</v>
+        <v>0.0347</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>0.08318811058747821</v>
+        <v>0.2308888381235092</v>
       </c>
       <c r="J8" s="15" t="n">
         <v>0.5</v>
@@ -2779,33 +2779,33 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>MIA @ SF</t>
+          <t>NO @ DET</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>MIA ML</t>
+          <t>Under 48.5</t>
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>470</v>
+        <v>-102</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>0.2162</v>
+        <v>0.5445</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>0.1754</v>
+        <v>0.505</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>0.0347</v>
+        <v>0.0339</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>0.2308888381235092</v>
+        <v>0.07825152568482774</v>
       </c>
       <c r="J9" s="10" t="n">
         <v>0.5</v>
@@ -2820,33 +2820,33 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>NO @ DET</t>
+          <t>CLE @ JAX</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Under 48.5</t>
+          <t>CLE ML</t>
         </is>
       </c>
       <c r="E10" s="12" t="n">
-        <v>-102</v>
+        <v>300</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5445</v>
+        <v>0.2851</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>0.505</v>
+        <v>0.25</v>
       </c>
       <c r="H10" s="13" t="n">
-        <v>0.0339</v>
+        <v>0.031</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>0.07825152568482774</v>
+        <v>0.1391236234118228</v>
       </c>
       <c r="J10" s="15" t="n">
         <v>0.5</v>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>CLE @ JAX</t>
+          <t>IND @ KC</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -2871,23 +2871,23 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>CLE ML</t>
+          <t>IND ML</t>
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>0.2851</v>
+        <v>0.3198</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>0.25</v>
+        <v>0.2857</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>0.031</v>
+        <v>0.0303</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>0.1391236234118228</v>
+        <v>0.1184707164983309</v>
       </c>
       <c r="J11" s="10" t="n">
         <v>0.5</v>
@@ -2902,33 +2902,33 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>IND @ KC</t>
+          <t>MIA @ SF</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>IND ML</t>
+          <t>MIA +10.5</t>
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>250</v>
+        <v>-110</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.3198</v>
+        <v>0.5573</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>0.2857</v>
+        <v>0.5238</v>
       </c>
       <c r="H12" s="13" t="n">
-        <v>0.0303</v>
+        <v>0.0299</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>0.1184707164983309</v>
+        <v>0.0638464411277132</v>
       </c>
       <c r="J12" s="15" t="n">
         <v>0.5</v>
@@ -2943,33 +2943,33 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>MIA @ SF</t>
+          <t>TB @ CIN</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>MIA +10.5</t>
+          <t>Under 50.5</t>
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>-110</v>
+        <v>-102</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>0.5573</v>
+        <v>0.537</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.505</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>0.0299</v>
+        <v>0.0288</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0.0638464411277132</v>
+        <v>0.06338928083930406</v>
       </c>
       <c r="J13" s="10" t="n">
         <v>0.5</v>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>WSH @ PHI</t>
+          <t>SF @ LAR</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -3035,23 +3035,23 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Under 45.5</t>
+          <t>Under 48.5</t>
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>-105</v>
+        <v>-112</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>0.5392</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.5283</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>0.0251</v>
+        <v>0.0264</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>0.05280703547074495</v>
+        <v>0.05438999086165447</v>
       </c>
       <c r="J15" s="10" t="n">
         <v>0.5</v>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>DET @ BUF</t>
+          <t>WSH @ PHI</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -3076,23 +3076,23 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Under 52.5</t>
+          <t>Under 45.5</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5505</v>
+        <v>0.5392</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5122</v>
       </c>
       <c r="H16" s="13" t="n">
-        <v>0.0248</v>
+        <v>0.0251</v>
       </c>
       <c r="I16" s="13" t="n">
-        <v>0.05103388963377431</v>
+        <v>0.05280703547074495</v>
       </c>
       <c r="J16" s="15" t="n">
         <v>0.5</v>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>GB @ NYJ</t>
+          <t>DET @ BUF</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Over 42.5</t>
+          <t>Under 52.5</t>
         </is>
       </c>
       <c r="E17" s="7" t="n">
@@ -3133,7 +3133,7 @@
         <v>0.0248</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>0.05103768389435415</v>
+        <v>0.05103388963377431</v>
       </c>
       <c r="J17" s="10" t="n">
         <v>0.5</v>
@@ -3148,33 +3148,33 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>CLE @ JAX</t>
+          <t>GB @ NYJ</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>CLE +7.5</t>
+          <t>Over 42.5</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5482</v>
+        <v>0.5505</v>
       </c>
       <c r="G18" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H18" s="13" t="n">
-        <v>0.0229</v>
+        <v>0.0248</v>
       </c>
       <c r="I18" s="13" t="n">
-        <v>0.04655179375627749</v>
+        <v>0.05103768389435415</v>
       </c>
       <c r="J18" s="15" t="n">
         <v>0.5</v>
@@ -3189,33 +3189,33 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>GB @ MIN</t>
+          <t>CLE @ JAX</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Under 45.5</t>
+          <t>CLE +7.5</t>
         </is>
       </c>
       <c r="E19" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>0.548</v>
+        <v>0.5482</v>
       </c>
       <c r="G19" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>0.0228</v>
+        <v>0.0229</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>0.04626263390290908</v>
+        <v>0.04655179375627749</v>
       </c>
       <c r="J19" s="10" t="n">
         <v>0.5</v>
@@ -3230,33 +3230,33 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>GB @ NYJ</t>
+          <t>GB @ MIN</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>NYJ ML</t>
+          <t>Under 45.5</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>195</v>
+        <v>-110</v>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.3591</v>
+        <v>0.548</v>
       </c>
       <c r="G20" s="13" t="n">
-        <v>0.339</v>
+        <v>0.5238</v>
       </c>
       <c r="H20" s="13" t="n">
-        <v>0.0193</v>
+        <v>0.0228</v>
       </c>
       <c r="I20" s="13" t="n">
-        <v>0.05894822625366258</v>
+        <v>0.04626263390290908</v>
       </c>
       <c r="J20" s="15" t="n">
         <v>0.5</v>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>MIA @ LV</t>
+          <t>CLE @ JAX</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -3288,16 +3288,16 @@
         <v>-110</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>0.543</v>
+        <v>0.5455</v>
       </c>
       <c r="G21" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>0.0185</v>
+        <v>0.0207</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>0.03671607804771798</v>
+        <v>0.04150009863343507</v>
       </c>
       <c r="J21" s="10" t="n">
         <v>0.5</v>
@@ -3312,7 +3312,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>NO @ BAL</t>
+          <t>DEN @ KC</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -3322,23 +3322,23 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Under 46.5</t>
+          <t>Under 42.5</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.543</v>
+        <v>0.5455</v>
       </c>
       <c r="G22" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H22" s="13" t="n">
-        <v>0.0185</v>
+        <v>0.0207</v>
       </c>
       <c r="I22" s="13" t="n">
-        <v>0.03670380090148218</v>
+        <v>0.0414763555925613</v>
       </c>
       <c r="J22" s="15" t="n">
         <v>0.5</v>
@@ -3353,33 +3353,33 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>WSH @ DAL</t>
+          <t>GB @ NYJ</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Under 51.5</t>
+          <t>NYJ ML</t>
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>-110</v>
+        <v>195</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>0.543</v>
+        <v>0.3591</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.339</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>0.0185</v>
+        <v>0.0193</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>0.03670597155556737</v>
+        <v>0.05894822625366258</v>
       </c>
       <c r="J23" s="10" t="n">
         <v>0.5</v>
@@ -3394,33 +3394,33 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>LV @ LAC</t>
+          <t>MIA @ LV</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>LV +8.5</t>
+          <t>Over 40.5</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5422</v>
+        <v>0.543</v>
       </c>
       <c r="G24" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H24" s="13" t="n">
-        <v>0.0178</v>
+        <v>0.0185</v>
       </c>
       <c r="I24" s="13" t="n">
-        <v>0.03519799972870302</v>
+        <v>0.03671607804771798</v>
       </c>
       <c r="J24" s="15" t="n">
         <v>0.5</v>
@@ -3435,33 +3435,33 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>SF @ LAR</t>
+          <t>NO @ BAL</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>SF ML</t>
+          <t>Under 46.5</t>
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>154</v>
+        <v>-110</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>0.4115</v>
+        <v>0.543</v>
       </c>
       <c r="G25" s="8" t="n">
-        <v>0.3937</v>
+        <v>0.5238</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>0.0172</v>
+        <v>0.0185</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>0.04474685390028676</v>
+        <v>0.03670380090148218</v>
       </c>
       <c r="J25" s="10" t="n">
         <v>0.5</v>
@@ -3476,33 +3476,33 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>PHI @ TEN</t>
+          <t>WSH @ DAL</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>TEN ML</t>
+          <t>Under 51.5</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>170</v>
+        <v>-110</v>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.3877</v>
+        <v>0.543</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>0.3704</v>
+        <v>0.5238</v>
       </c>
       <c r="H26" s="13" t="n">
-        <v>0.0168</v>
+        <v>0.0185</v>
       </c>
       <c r="I26" s="13" t="n">
-        <v>0.04648874007508352</v>
+        <v>0.03670597155556737</v>
       </c>
       <c r="J26" s="15" t="n">
         <v>0.5</v>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>NYG @ LAR</t>
+          <t>LV @ LAC</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -3527,23 +3527,23 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>NYG +8.5</t>
+          <t>LV +8.5</t>
         </is>
       </c>
       <c r="E27" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>0.5406</v>
+        <v>0.5422</v>
       </c>
       <c r="G27" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H27" s="8" t="n">
-        <v>0.0163</v>
+        <v>0.0178</v>
       </c>
       <c r="I27" s="8" t="n">
-        <v>0.03204259594583803</v>
+        <v>0.03519799972870302</v>
       </c>
       <c r="J27" s="10" t="n">
         <v>0.5</v>
@@ -3558,33 +3558,33 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>CLE @ JAX</t>
+          <t>SF @ LAR</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Over 40.5</t>
+          <t>SF ML</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>-110</v>
+        <v>154</v>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5405</v>
+        <v>0.4115</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.3937</v>
       </c>
       <c r="H28" s="13" t="n">
-        <v>0.0162</v>
+        <v>0.0172</v>
       </c>
       <c r="I28" s="13" t="n">
-        <v>0.03192423886530243</v>
+        <v>0.04474685390028676</v>
       </c>
       <c r="J28" s="15" t="n">
         <v>0.5</v>
@@ -3604,28 +3604,28 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>TEN +4.5</t>
+          <t>TEN ML</t>
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>-110</v>
+        <v>170</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>0.5403</v>
+        <v>0.3877</v>
       </c>
       <c r="G29" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.3704</v>
       </c>
       <c r="H29" s="8" t="n">
-        <v>0.016</v>
+        <v>0.0168</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>0.03139671505204372</v>
+        <v>0.04648874007508352</v>
       </c>
       <c r="J29" s="10" t="n">
         <v>0.5</v>
@@ -3640,33 +3640,33 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>NO @ BAL</t>
+          <t>NYG @ LAR</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>NO ML</t>
+          <t>NYG +8.5</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>280</v>
+        <v>-110</v>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.2795</v>
+        <v>0.5406</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>0.2632</v>
+        <v>0.5238</v>
       </c>
       <c r="H30" s="13" t="n">
-        <v>0.0159</v>
+        <v>0.0163</v>
       </c>
       <c r="I30" s="13" t="n">
-        <v>0.06160995661143953</v>
+        <v>0.03204259594583803</v>
       </c>
       <c r="J30" s="15" t="n">
         <v>0.5</v>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>NO @ DET</t>
+          <t>PHI @ TEN</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -3691,23 +3691,23 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>NO +7</t>
+          <t>TEN +4.5</t>
         </is>
       </c>
       <c r="E31" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>0.5382</v>
+        <v>0.5403</v>
       </c>
       <c r="G31" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>0.0141</v>
+        <v>0.016</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>0.02603693637090604</v>
+        <v>0.03139671505204372</v>
       </c>
       <c r="J31" s="10" t="n">
         <v>0.5</v>
@@ -3722,33 +3722,33 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>IND @ KC</t>
+          <t>NO @ BAL</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Under 47.5</t>
+          <t>NO ML</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>-110</v>
+        <v>280</v>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.538</v>
+        <v>0.2795</v>
       </c>
       <c r="G32" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.2632</v>
       </c>
       <c r="H32" s="13" t="n">
-        <v>0.0139</v>
+        <v>0.0159</v>
       </c>
       <c r="I32" s="13" t="n">
-        <v>0.02711300098876335</v>
+        <v>0.06160995661143953</v>
       </c>
       <c r="J32" s="15" t="n">
         <v>0.5</v>
@@ -3763,33 +3763,33 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>MIN @ CHI</t>
+          <t>ATL @ PIT</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>MIN ML</t>
+          <t>Over 41.5</t>
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>164</v>
+        <v>-115</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>0.3928</v>
+        <v>0.5493</v>
       </c>
       <c r="G33" s="8" t="n">
-        <v>0.3788</v>
+        <v>0.5349</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>0.0137</v>
+        <v>0.0141</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>0.03665546876206616</v>
+        <v>0.02702299932041741</v>
       </c>
       <c r="J33" s="10" t="n">
         <v>0.5</v>
@@ -3809,28 +3809,28 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>NO ML</t>
+          <t>NO +7</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>245</v>
+        <v>-110</v>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.3036</v>
+        <v>0.5382</v>
       </c>
       <c r="G34" s="13" t="n">
-        <v>0.2899</v>
+        <v>0.5238</v>
       </c>
       <c r="H34" s="13" t="n">
-        <v>0.0134</v>
+        <v>0.0141</v>
       </c>
       <c r="I34" s="13" t="n">
-        <v>0.04694678102894134</v>
+        <v>0.02603693637090604</v>
       </c>
       <c r="J34" s="15" t="n">
         <v>0.5</v>
@@ -3845,33 +3845,33 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>BAL @ IND</t>
+          <t>IND @ KC</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>IND ML</t>
+          <t>Under 47.5</t>
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>150</v>
+        <v>-110</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>0.4136</v>
+        <v>0.538</v>
       </c>
       <c r="G35" s="8" t="n">
-        <v>0.4</v>
+        <v>0.5238</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>0.0133</v>
+        <v>0.0139</v>
       </c>
       <c r="I35" s="8" t="n">
-        <v>0.03366146021632732</v>
+        <v>0.02711300098876335</v>
       </c>
       <c r="J35" s="10" t="n">
         <v>0.5</v>
@@ -3886,33 +3886,33 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>IND @ KC</t>
+          <t>MIN @ CHI</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>IND +6.5</t>
+          <t>MIN ML</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>-110</v>
+        <v>164</v>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.5373</v>
+        <v>0.3928</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.3788</v>
       </c>
       <c r="H36" s="13" t="n">
-        <v>0.0133</v>
+        <v>0.0137</v>
       </c>
       <c r="I36" s="13" t="n">
-        <v>0.02582562516297304</v>
+        <v>0.03665546876206616</v>
       </c>
       <c r="J36" s="15" t="n">
         <v>0.5</v>
@@ -3927,33 +3927,33 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>NO @ BAL</t>
+          <t>NO @ DET</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>NO +7.5</t>
+          <t>NO ML</t>
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>-110</v>
+        <v>245</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>0.5371</v>
+        <v>0.3036</v>
       </c>
       <c r="G37" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.2899</v>
       </c>
       <c r="H37" s="8" t="n">
-        <v>0.013</v>
+        <v>0.0134</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>0.02539146355259436</v>
+        <v>0.04694678102894134</v>
       </c>
       <c r="J37" s="10" t="n">
         <v>0.5</v>
@@ -3968,7 +3968,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>NYG @ LAR</t>
+          <t>BAL @ IND</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -3978,23 +3978,23 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>NYG ML</t>
+          <t>IND ML</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.2628</v>
+        <v>0.4136</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="H38" s="13" t="n">
-        <v>0.0126</v>
+        <v>0.0133</v>
       </c>
       <c r="I38" s="13" t="n">
-        <v>0.05081583493908304</v>
+        <v>0.03366146021632732</v>
       </c>
       <c r="J38" s="15" t="n">
         <v>0.5</v>
@@ -4009,7 +4009,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>GB @ NYJ</t>
+          <t>IND @ KC</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -4019,23 +4019,23 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>NYJ +5.5</t>
+          <t>IND +6.5</t>
         </is>
       </c>
       <c r="E39" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>0.5362</v>
+        <v>0.5373</v>
       </c>
       <c r="G39" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>0.0122</v>
+        <v>0.0133</v>
       </c>
       <c r="I39" s="8" t="n">
-        <v>0.0237441898766132</v>
+        <v>0.02582562516297304</v>
       </c>
       <c r="J39" s="10" t="n">
         <v>0.5</v>
@@ -4050,33 +4050,33 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>CHI @ CAR</t>
+          <t>NO @ BAL</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Under 47.5</t>
+          <t>NO +7.5</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.5241</v>
+        <v>0.5371</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>0.5122</v>
+        <v>0.5238</v>
       </c>
       <c r="H40" s="13" t="n">
-        <v>0.0118</v>
+        <v>0.013</v>
       </c>
       <c r="I40" s="13" t="n">
-        <v>0.02330043912717339</v>
+        <v>0.02539146355259436</v>
       </c>
       <c r="J40" s="15" t="n">
         <v>0.5</v>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>LV @ LAC</t>
+          <t>NYG @ LAR</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -4101,23 +4101,23 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>LV ML</t>
+          <t>NYG ML</t>
         </is>
       </c>
       <c r="E41" s="7" t="n">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>0.2652</v>
+        <v>0.2628</v>
       </c>
       <c r="G41" s="8" t="n">
-        <v>0.2532</v>
+        <v>0.25</v>
       </c>
       <c r="H41" s="8" t="n">
-        <v>0.0118</v>
+        <v>0.0126</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>0.04710447684912145</v>
+        <v>0.05081583493908304</v>
       </c>
       <c r="J41" s="10" t="n">
         <v>0.5</v>
@@ -4132,33 +4132,33 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>MIN @ CHI</t>
+          <t>GB @ NYJ</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Under 45.5</t>
+          <t>NYJ +5.5</t>
         </is>
       </c>
       <c r="E42" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.5355</v>
+        <v>0.5362</v>
       </c>
       <c r="G42" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H42" s="13" t="n">
-        <v>0.0115</v>
+        <v>0.0122</v>
       </c>
       <c r="I42" s="13" t="n">
-        <v>0.02230451490136909</v>
+        <v>0.0237441898766132</v>
       </c>
       <c r="J42" s="15" t="n">
         <v>0.5</v>
@@ -4173,7 +4173,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>LV @ LAC</t>
+          <t>CHI @ CAR</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -4183,23 +4183,23 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Under 42.5</t>
+          <t>Under 47.5</t>
         </is>
       </c>
       <c r="E43" s="7" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>0.5355</v>
+        <v>0.5241</v>
       </c>
       <c r="G43" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5122</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>0.0115</v>
+        <v>0.0118</v>
       </c>
       <c r="I43" s="8" t="n">
-        <v>0.02229543916527443</v>
+        <v>0.02330043912717339</v>
       </c>
       <c r="J43" s="10" t="n">
         <v>0.5</v>
@@ -4214,33 +4214,33 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>ARI @ LAC</t>
+          <t>LV @ LAC</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>ARI +10.5</t>
+          <t>LV ML</t>
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>-110</v>
+        <v>295</v>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.5335</v>
+        <v>0.2652</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.2532</v>
       </c>
       <c r="H44" s="13" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0118</v>
       </c>
       <c r="I44" s="13" t="n">
-        <v>0.01853454908740365</v>
+        <v>0.04710447684912145</v>
       </c>
       <c r="J44" s="15" t="n">
         <v>0.5</v>
@@ -4255,33 +4255,33 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>BAL @ IND</t>
+          <t>MIN @ CHI</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>IND +3.5</t>
+          <t>Under 45.5</t>
         </is>
       </c>
       <c r="E45" s="7" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.5355</v>
       </c>
       <c r="G45" s="8" t="n">
-        <v>0.5283</v>
+        <v>0.5238</v>
       </c>
       <c r="H45" s="8" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0115</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>0.01600179892448023</v>
+        <v>0.02230451490136909</v>
       </c>
       <c r="J45" s="10" t="n">
         <v>0.5</v>
@@ -4296,33 +4296,33 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>NE @ SEA</t>
+          <t>LV @ LAC</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>NE ML</t>
+          <t>Under 42.5</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>145</v>
+        <v>-110</v>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.4165</v>
+        <v>0.5355</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>0.4082</v>
+        <v>0.5238</v>
       </c>
       <c r="H46" s="13" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0115</v>
       </c>
       <c r="I46" s="13" t="n">
-        <v>0.02016139816970663</v>
+        <v>0.02229543916527443</v>
       </c>
       <c r="J46" s="15" t="n">
         <v>0.5</v>
@@ -4337,33 +4337,33 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>CHI @ CAR</t>
+          <t>ARI @ LAC</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>CAR ML</t>
+          <t>ARI +10.5</t>
         </is>
       </c>
       <c r="E47" s="7" t="n">
-        <v>120</v>
+        <v>-110</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>0.4628</v>
+        <v>0.5335</v>
       </c>
       <c r="G47" s="8" t="n">
-        <v>0.4545</v>
+        <v>0.5238</v>
       </c>
       <c r="H47" s="8" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="I47" s="8" t="n">
-        <v>0.01798834225121759</v>
+        <v>0.01853454908740365</v>
       </c>
       <c r="J47" s="10" t="n">
         <v>0.5</v>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>CHI @ CAR</t>
+          <t>BAL @ IND</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
@@ -4388,23 +4388,23 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>CAR +2.5</t>
+          <t>IND +3.5</t>
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>-102</v>
+        <v>-112</v>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.5128</v>
+        <v>0.5368000000000001</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>0.505</v>
+        <v>0.5283</v>
       </c>
       <c r="H48" s="13" t="n">
-        <v>0.0078</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="I48" s="13" t="n">
-        <v>0.01556823154421605</v>
+        <v>0.01600179892448023</v>
       </c>
       <c r="J48" s="15" t="n">
         <v>0.5</v>
@@ -4419,7 +4419,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>ARI @ LAC</t>
+          <t>NE @ SEA</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -4429,23 +4429,23 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>ARI ML</t>
+          <t>NE ML</t>
         </is>
       </c>
       <c r="E49" s="7" t="n">
-        <v>400</v>
+        <v>145</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>0.2065</v>
+        <v>0.4165</v>
       </c>
       <c r="G49" s="8" t="n">
-        <v>0.2</v>
+        <v>0.4082</v>
       </c>
       <c r="H49" s="8" t="n">
-        <v>0.0065</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="I49" s="8" t="n">
-        <v>0.03246196673429513</v>
+        <v>0.02016139816970663</v>
       </c>
       <c r="J49" s="10" t="n">
         <v>0.5</v>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>MIA @ LV</t>
+          <t>CHI @ CAR</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -4470,23 +4470,23 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>MIA ML</t>
+          <t>CAR ML</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>164</v>
+        <v>120</v>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.3853</v>
+        <v>0.4628</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>0.3788</v>
+        <v>0.4545</v>
       </c>
       <c r="H50" s="13" t="n">
-        <v>0.0065</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="I50" s="13" t="n">
-        <v>0.01711869710462766</v>
+        <v>0.01798834225121759</v>
       </c>
       <c r="J50" s="15" t="n">
         <v>0.5</v>
@@ -4501,33 +4501,33 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>PIT @ NE</t>
+          <t>CHI @ CAR</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>PIT ML</t>
+          <t>CAR +2.5</t>
         </is>
       </c>
       <c r="E51" s="7" t="n">
-        <v>180</v>
+        <v>-102</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>0.3627</v>
+        <v>0.5128</v>
       </c>
       <c r="G51" s="8" t="n">
-        <v>0.3571</v>
+        <v>0.505</v>
       </c>
       <c r="H51" s="8" t="n">
-        <v>0.0055</v>
+        <v>0.0078</v>
       </c>
       <c r="I51" s="8" t="n">
-        <v>0.0153316632185424</v>
+        <v>0.01556823154421605</v>
       </c>
       <c r="J51" s="10" t="n">
         <v>0.5</v>
@@ -4542,33 +4542,33 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>NE @ SEA</t>
+          <t>ARI @ LAC</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>NE +3.5</t>
+          <t>ARI ML</t>
         </is>
       </c>
       <c r="E52" s="12" t="n">
-        <v>-115</v>
+        <v>400</v>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.5394</v>
+        <v>0.2065</v>
       </c>
       <c r="G52" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.2</v>
       </c>
       <c r="H52" s="13" t="n">
-        <v>0.0045</v>
+        <v>0.0065</v>
       </c>
       <c r="I52" s="13" t="n">
-        <v>0.00842156579131853</v>
+        <v>0.03246196673429513</v>
       </c>
       <c r="J52" s="15" t="n">
         <v>0.5</v>
@@ -4583,33 +4583,33 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>BAL @ IND</t>
+          <t>MIA @ LV</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Under 48.5</t>
+          <t>MIA ML</t>
         </is>
       </c>
       <c r="E53" s="7" t="n">
-        <v>-115</v>
+        <v>164</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>0.5393</v>
+        <v>0.3853</v>
       </c>
       <c r="G53" s="8" t="n">
-        <v>0.5349</v>
+        <v>0.3788</v>
       </c>
       <c r="H53" s="8" t="n">
-        <v>0.0044</v>
+        <v>0.0065</v>
       </c>
       <c r="I53" s="8" t="n">
-        <v>0.008230624751543902</v>
+        <v>0.01711869710462766</v>
       </c>
       <c r="J53" s="10" t="n">
         <v>0.5</v>
@@ -4624,33 +4624,33 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>SF @ LAR</t>
+          <t>PIT @ NE</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>SF +3.5</t>
+          <t>PIT ML</t>
         </is>
       </c>
       <c r="E54" s="12" t="n">
-        <v>-115</v>
+        <v>180</v>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.539</v>
+        <v>0.3627</v>
       </c>
       <c r="G54" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.3571</v>
       </c>
       <c r="H54" s="13" t="n">
-        <v>0.0041</v>
+        <v>0.0055</v>
       </c>
       <c r="I54" s="13" t="n">
-        <v>0.007755919659725108</v>
+        <v>0.0153316632185424</v>
       </c>
       <c r="J54" s="15" t="n">
         <v>0.5</v>
@@ -4665,33 +4665,33 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>CLE @ TB</t>
+          <t>NE @ SEA</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>CLE ML</t>
+          <t>NE +3.5</t>
         </is>
       </c>
       <c r="E55" s="7" t="n">
-        <v>200</v>
+        <v>-115</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>0.3369</v>
+        <v>0.5394</v>
       </c>
       <c r="G55" s="8" t="n">
-        <v>0.3333</v>
+        <v>0.5349</v>
       </c>
       <c r="H55" s="8" t="n">
-        <v>0.0035</v>
+        <v>0.0045</v>
       </c>
       <c r="I55" s="8" t="n">
-        <v>0.01047456634726629</v>
+        <v>0.00842156579131853</v>
       </c>
       <c r="J55" s="10" t="n">
         <v>0.5</v>
@@ -4706,33 +4706,33 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>DEN @ KC</t>
+          <t>SF @ LAR</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Under 42.5</t>
+          <t>SF +3.5</t>
         </is>
       </c>
       <c r="E56" s="12" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.5254</v>
+        <v>0.539</v>
       </c>
       <c r="G56" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5349</v>
       </c>
       <c r="H56" s="13" t="n">
-        <v>0.0016</v>
+        <v>0.0041</v>
       </c>
       <c r="I56" s="13" t="n">
-        <v>0.003010730423656016</v>
+        <v>0.007755919659725108</v>
       </c>
       <c r="J56" s="15" t="n">
         <v>0.5</v>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>CIN @ HOU</t>
+          <t>CLE @ TB</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -4757,23 +4757,23 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>CIN ML</t>
+          <t>CLE ML</t>
         </is>
       </c>
       <c r="E57" s="7" t="n">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>0.4674</v>
+        <v>0.3369</v>
       </c>
       <c r="G57" s="8" t="n">
-        <v>0.4673</v>
+        <v>0.3333</v>
       </c>
       <c r="H57" s="8" t="n">
-        <v>0.0001</v>
+        <v>0.0035</v>
       </c>
       <c r="I57" s="8" t="n">
-        <v>0.00018904111275031</v>
+        <v>0.01047456634726629</v>
       </c>
       <c r="J57" s="10" t="n">
         <v>0.5</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>NE @ SEA</t>
+          <t>BUF @ HOU</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -4798,23 +4798,23 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Under 44.5</t>
+          <t>Over 44.5</t>
         </is>
       </c>
       <c r="E58" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.5229</v>
+        <v>0.5254</v>
       </c>
       <c r="G58" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H58" s="13" t="n">
-        <v>-0.001</v>
+        <v>0.0016</v>
       </c>
       <c r="I58" s="13" t="n">
-        <v>-0.001817132797922338</v>
+        <v>0.003023751045110934</v>
       </c>
       <c r="J58" s="15" t="n">
         <v>0.5</v>
@@ -4829,33 +4829,33 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>SF @ LAR</t>
+          <t>CIN @ HOU</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Under 48.5</t>
+          <t>CIN ML</t>
         </is>
       </c>
       <c r="E59" s="7" t="n">
-        <v>-112</v>
+        <v>114</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>0.5269</v>
+        <v>0.4674</v>
       </c>
       <c r="G59" s="8" t="n">
-        <v>0.5283</v>
+        <v>0.4673</v>
       </c>
       <c r="H59" s="8" t="n">
-        <v>-0.0014</v>
+        <v>0.0001</v>
       </c>
       <c r="I59" s="8" t="n">
-        <v>-0.002639744160511492</v>
+        <v>0.00018904111275031</v>
       </c>
       <c r="J59" s="10" t="n">
         <v>0.5</v>
@@ -4870,33 +4870,33 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>MIN @ CHI</t>
+          <t>NE @ SEA</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>MIN +3.5</t>
+          <t>Under 44.5</t>
         </is>
       </c>
       <c r="E60" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.5217000000000001</v>
+        <v>0.5229</v>
       </c>
       <c r="G60" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H60" s="13" t="n">
-        <v>-0.0022</v>
+        <v>-0.001</v>
       </c>
       <c r="I60" s="13" t="n">
-        <v>-0.004107965639567612</v>
+        <v>-0.001817132797922338</v>
       </c>
       <c r="J60" s="15" t="n">
         <v>0.5</v>
@@ -4911,33 +4911,33 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>WSH @ PHI</t>
+          <t>MIN @ CHI</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>WSH ML</t>
+          <t>MIN +3.5</t>
         </is>
       </c>
       <c r="E61" s="7" t="n">
-        <v>180</v>
+        <v>-110</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>0.3531</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="G61" s="8" t="n">
-        <v>0.3571</v>
+        <v>0.5238</v>
       </c>
       <c r="H61" s="8" t="n">
-        <v>-0.004</v>
+        <v>-0.0022</v>
       </c>
       <c r="I61" s="8" t="n">
-        <v>-0.01110652616800833</v>
+        <v>-0.004107965639567612</v>
       </c>
       <c r="J61" s="10" t="n">
         <v>0.5</v>
@@ -4952,33 +4952,33 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>PIT @ NE</t>
+          <t>WSH @ PHI</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>PIT +4.5</t>
+          <t>WSH ML</t>
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>-110</v>
+        <v>180</v>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.5193</v>
+        <v>0.3531</v>
       </c>
       <c r="G62" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.3571</v>
       </c>
       <c r="H62" s="13" t="n">
-        <v>-0.0045</v>
+        <v>-0.004</v>
       </c>
       <c r="I62" s="13" t="n">
-        <v>-0.008675557202874884</v>
+        <v>-0.01110652616800833</v>
       </c>
       <c r="J62" s="15" t="n">
         <v>0.5</v>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>CIN @ HOU</t>
+          <t>PIT @ NE</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -5003,23 +5003,23 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>CIN +2.5</t>
+          <t>PIT +4.5</t>
         </is>
       </c>
       <c r="E63" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>0.5192</v>
+        <v>0.5193</v>
       </c>
       <c r="G63" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H63" s="8" t="n">
-        <v>-0.0046</v>
+        <v>-0.0045</v>
       </c>
       <c r="I63" s="8" t="n">
-        <v>-0.008707316411936561</v>
+        <v>-0.008675557202874884</v>
       </c>
       <c r="J63" s="10" t="n">
         <v>0.5</v>
@@ -5034,33 +5034,33 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>BUF @ HOU</t>
+          <t>CIN @ HOU</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Over 44.5</t>
+          <t>CIN +2.5</t>
         </is>
       </c>
       <c r="E64" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.5178</v>
+        <v>0.5192</v>
       </c>
       <c r="G64" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H64" s="13" t="n">
-        <v>-0.006</v>
+        <v>-0.0046</v>
       </c>
       <c r="I64" s="13" t="n">
-        <v>-0.01149109637649182</v>
+        <v>-0.008707316411936561</v>
       </c>
       <c r="J64" s="15" t="n">
         <v>0.5</v>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>ATL @ PIT</t>
+          <t>PHI @ TEN</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
@@ -5290,23 +5290,23 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Over 41.5</t>
+          <t>Over 42.5</t>
         </is>
       </c>
       <c r="E70" s="12" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.5241</v>
+        <v>0.5127</v>
       </c>
       <c r="G70" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.5238</v>
       </c>
       <c r="H70" s="13" t="n">
-        <v>-0.0106</v>
+        <v>-0.0109</v>
       </c>
       <c r="I70" s="13" t="n">
-        <v>-0.02011942946105738</v>
+        <v>-0.0211809310724152</v>
       </c>
       <c r="J70" s="15" t="n">
         <v>0.5</v>
@@ -5321,7 +5321,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>PHI @ TEN</t>
+          <t>SEA @ ARI</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Over 42.5</t>
+          <t>Under 44.5</t>
         </is>
       </c>
       <c r="E71" s="7" t="n">
@@ -5344,10 +5344,10 @@
         <v>0.5238</v>
       </c>
       <c r="H71" s="8" t="n">
-        <v>-0.0109</v>
+        <v>-0.011</v>
       </c>
       <c r="I71" s="8" t="n">
-        <v>-0.0211809310724152</v>
+        <v>-0.02119113285229918</v>
       </c>
       <c r="J71" s="10" t="n">
         <v>0.5</v>
@@ -5362,33 +5362,33 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>SEA @ ARI</t>
+          <t>NYJ @ TEN</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Under 44.5</t>
+          <t>TEN -3</t>
         </is>
       </c>
       <c r="E72" s="12" t="n">
-        <v>-110</v>
+        <v>100</v>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.5127</v>
+        <v>0.487</v>
       </c>
       <c r="G72" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5</v>
       </c>
       <c r="H72" s="13" t="n">
-        <v>-0.011</v>
+        <v>-0.0128</v>
       </c>
       <c r="I72" s="13" t="n">
-        <v>-0.02119113285229918</v>
+        <v>-0.02417095898762545</v>
       </c>
       <c r="J72" s="15" t="n">
         <v>0.5</v>
@@ -5403,33 +5403,33 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>NYJ @ TEN</t>
+          <t>JAX @ DEN</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>TEN -3</t>
+          <t>DEN ML</t>
         </is>
       </c>
       <c r="E73" s="7" t="n">
-        <v>100</v>
+        <v>-142</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>0.487</v>
+        <v>0.5736</v>
       </c>
       <c r="G73" s="8" t="n">
-        <v>0.5</v>
+        <v>0.5868</v>
       </c>
       <c r="H73" s="8" t="n">
-        <v>-0.0128</v>
+        <v>-0.0129</v>
       </c>
       <c r="I73" s="8" t="n">
-        <v>-0.02417095898762545</v>
+        <v>-0.02219386302481374</v>
       </c>
       <c r="J73" s="10" t="n">
         <v>0.5</v>
@@ -5444,7 +5444,7 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>JAX @ DEN</t>
+          <t>BUF @ HOU</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
@@ -5454,23 +5454,23 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>DEN ML</t>
+          <t>BUF ML</t>
         </is>
       </c>
       <c r="E74" s="12" t="n">
-        <v>-142</v>
+        <v>-118</v>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.5736</v>
+        <v>0.5276</v>
       </c>
       <c r="G74" s="13" t="n">
-        <v>0.5868</v>
+        <v>0.5413</v>
       </c>
       <c r="H74" s="13" t="n">
-        <v>-0.0129</v>
+        <v>-0.0134</v>
       </c>
       <c r="I74" s="13" t="n">
-        <v>-0.02219386302481374</v>
+        <v>-0.02500971522359302</v>
       </c>
       <c r="J74" s="15" t="n">
         <v>0.5</v>
@@ -5485,33 +5485,33 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>BUF @ HOU</t>
+          <t>JAX @ DEN</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>BUF ML</t>
+          <t>DEN -2.5</t>
         </is>
       </c>
       <c r="E75" s="7" t="n">
-        <v>-118</v>
+        <v>-115</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>0.5276</v>
+        <v>0.5211</v>
       </c>
       <c r="G75" s="8" t="n">
-        <v>0.5413</v>
+        <v>0.5349</v>
       </c>
       <c r="H75" s="8" t="n">
-        <v>-0.0134</v>
+        <v>-0.0135</v>
       </c>
       <c r="I75" s="8" t="n">
-        <v>-0.02500971522359302</v>
+        <v>-0.02572923154910695</v>
       </c>
       <c r="J75" s="10" t="n">
         <v>0.5</v>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>JAX @ DEN</t>
+          <t>WSH @ PHI</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
@@ -5536,23 +5536,23 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>DEN -2.5</t>
+          <t>WSH +4.5</t>
         </is>
       </c>
       <c r="E76" s="12" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.5211</v>
+        <v>0.5093</v>
       </c>
       <c r="G76" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.5238</v>
       </c>
       <c r="H76" s="13" t="n">
-        <v>-0.0135</v>
+        <v>-0.0142</v>
       </c>
       <c r="I76" s="13" t="n">
-        <v>-0.02572923154910695</v>
+        <v>-0.02765523184807078</v>
       </c>
       <c r="J76" s="15" t="n">
         <v>0.5</v>
@@ -5567,33 +5567,33 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>WSH @ PHI</t>
+          <t>ATL @ PIT</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>WSH +4.5</t>
+          <t>ATL ML</t>
         </is>
       </c>
       <c r="E77" s="7" t="n">
-        <v>-110</v>
+        <v>145</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>0.5093</v>
+        <v>0.3932</v>
       </c>
       <c r="G77" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.4082</v>
       </c>
       <c r="H77" s="8" t="n">
-        <v>-0.0142</v>
+        <v>-0.0146</v>
       </c>
       <c r="I77" s="8" t="n">
-        <v>-0.02765523184807078</v>
+        <v>-0.03623808452237598</v>
       </c>
       <c r="J77" s="10" t="n">
         <v>0.5</v>
@@ -5608,33 +5608,33 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>ATL @ PIT</t>
+          <t>BUF @ HOU</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>ATL ML</t>
+          <t>BUF -1.5</t>
         </is>
       </c>
       <c r="E78" s="12" t="n">
-        <v>145</v>
+        <v>-105</v>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.3932</v>
+        <v>0.4971</v>
       </c>
       <c r="G78" s="13" t="n">
-        <v>0.4082</v>
+        <v>0.5122</v>
       </c>
       <c r="H78" s="13" t="n">
-        <v>-0.0146</v>
+        <v>-0.0147</v>
       </c>
       <c r="I78" s="13" t="n">
-        <v>-0.03623808452237598</v>
+        <v>-0.02942318222228196</v>
       </c>
       <c r="J78" s="15" t="n">
         <v>0.5</v>
@@ -5649,7 +5649,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>BUF @ HOU</t>
+          <t>GB @ MIN</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -5659,23 +5659,23 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>BUF -1.5</t>
+          <t>GB +1.5</t>
         </is>
       </c>
       <c r="E79" s="7" t="n">
-        <v>-105</v>
+        <v>-115</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>0.4971</v>
+        <v>0.519</v>
       </c>
       <c r="G79" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.5349</v>
       </c>
       <c r="H79" s="8" t="n">
-        <v>-0.0147</v>
+        <v>-0.0155</v>
       </c>
       <c r="I79" s="8" t="n">
-        <v>-0.02942318222228196</v>
+        <v>-0.0297833252608401</v>
       </c>
       <c r="J79" s="10" t="n">
         <v>0.5</v>
@@ -5895,33 +5895,33 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>DET @ BUF</t>
+          <t>BAL @ IND</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>BUF -3</t>
+          <t>Under 48.5</t>
         </is>
       </c>
       <c r="E85" s="7" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>0.5052</v>
+        <v>0.5165</v>
       </c>
       <c r="G85" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5349</v>
       </c>
       <c r="H85" s="8" t="n">
-        <v>-0.0179</v>
+        <v>-0.0177</v>
       </c>
       <c r="I85" s="8" t="n">
-        <v>-0.03291897912759417</v>
+        <v>-0.03436382238512642</v>
       </c>
       <c r="J85" s="10" t="n">
         <v>0.5</v>
@@ -5936,33 +5936,33 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>NYG @ LAR</t>
+          <t>DET @ BUF</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>BUF -3</t>
         </is>
       </c>
       <c r="E86" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.5051</v>
+        <v>0.5052</v>
       </c>
       <c r="G86" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H86" s="13" t="n">
-        <v>-0.018</v>
+        <v>-0.0179</v>
       </c>
       <c r="I86" s="13" t="n">
-        <v>-0.0357439529371551</v>
+        <v>-0.03291897912759417</v>
       </c>
       <c r="J86" s="15" t="n">
         <v>0.5</v>
@@ -5977,33 +5977,33 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>NYJ @ TEN</t>
+          <t>NYG @ LAR</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>TEN ML</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="E87" s="7" t="n">
-        <v>-148</v>
+        <v>-110</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>0.5777</v>
+        <v>0.5051</v>
       </c>
       <c r="G87" s="8" t="n">
-        <v>0.5968</v>
+        <v>0.5238</v>
       </c>
       <c r="H87" s="8" t="n">
-        <v>-0.0183</v>
+        <v>-0.018</v>
       </c>
       <c r="I87" s="8" t="n">
-        <v>-0.03165883941683079</v>
+        <v>-0.0357439529371551</v>
       </c>
       <c r="J87" s="10" t="n">
         <v>0.5</v>
@@ -6018,33 +6018,33 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>ATL @ PIT</t>
+          <t>NYJ @ TEN</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>ATL +3</t>
+          <t>TEN ML</t>
         </is>
       </c>
       <c r="E88" s="12" t="n">
-        <v>100</v>
+        <v>-148</v>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.4804</v>
+        <v>0.5777</v>
       </c>
       <c r="G88" s="13" t="n">
-        <v>0.5</v>
+        <v>0.5968</v>
       </c>
       <c r="H88" s="13" t="n">
-        <v>-0.0188</v>
+        <v>-0.0183</v>
       </c>
       <c r="I88" s="13" t="n">
-        <v>-0.03638566872259713</v>
+        <v>-0.03165883941683079</v>
       </c>
       <c r="J88" s="15" t="n">
         <v>0.5</v>
@@ -6059,33 +6059,33 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>WSH @ DAL</t>
+          <t>ATL @ PIT</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>DAL ML</t>
+          <t>ATL +3</t>
         </is>
       </c>
       <c r="E89" s="7" t="n">
-        <v>-198</v>
+        <v>100</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>0.6448</v>
+        <v>0.4804</v>
       </c>
       <c r="G89" s="8" t="n">
-        <v>0.6644</v>
+        <v>0.5</v>
       </c>
       <c r="H89" s="8" t="n">
         <v>-0.0188</v>
       </c>
       <c r="I89" s="8" t="n">
-        <v>-0.02929582789724111</v>
+        <v>-0.03638566872259713</v>
       </c>
       <c r="J89" s="10" t="n">
         <v>0.5</v>
@@ -6105,28 +6105,28 @@
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>DAL -4.5</t>
+          <t>DAL ML</t>
         </is>
       </c>
       <c r="E90" s="12" t="n">
-        <v>-105</v>
+        <v>-198</v>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.4923</v>
+        <v>0.6448</v>
       </c>
       <c r="G90" s="13" t="n">
-        <v>0.5122</v>
+        <v>0.6644</v>
       </c>
       <c r="H90" s="13" t="n">
-        <v>-0.0191</v>
+        <v>-0.0188</v>
       </c>
       <c r="I90" s="13" t="n">
-        <v>-0.03880269598770819</v>
+        <v>-0.02929582789724111</v>
       </c>
       <c r="J90" s="15" t="n">
         <v>0.5</v>
@@ -6141,7 +6141,7 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>GB @ MIN</t>
+          <t>WSH @ DAL</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -6151,23 +6151,23 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>GB +1.5</t>
+          <t>DAL -4.5</t>
         </is>
       </c>
       <c r="E91" s="7" t="n">
-        <v>-118</v>
+        <v>-105</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>0.5212</v>
+        <v>0.4923</v>
       </c>
       <c r="G91" s="8" t="n">
-        <v>0.5413</v>
+        <v>0.5122</v>
       </c>
       <c r="H91" s="8" t="n">
-        <v>-0.0192</v>
+        <v>-0.0191</v>
       </c>
       <c r="I91" s="8" t="n">
-        <v>-0.0370338349032584</v>
+        <v>-0.03880269598770819</v>
       </c>
       <c r="J91" s="10" t="n">
         <v>0.5</v>
@@ -6879,33 +6879,33 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>GB @ MIN</t>
+          <t>DAL @ NYG</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>MIN -1.5</t>
+          <t>Under 48.5</t>
         </is>
       </c>
       <c r="E109" s="7" t="n">
-        <v>-102</v>
+        <v>-110</v>
       </c>
       <c r="F109" s="8" t="n">
-        <v>0.4788</v>
+        <v>0.4975</v>
       </c>
       <c r="G109" s="8" t="n">
-        <v>0.505</v>
+        <v>0.5238</v>
       </c>
       <c r="H109" s="8" t="n">
-        <v>-0.0244</v>
+        <v>-0.0245</v>
       </c>
       <c r="I109" s="8" t="n">
-        <v>-0.05186461194666003</v>
+        <v>-0.05031031389922158</v>
       </c>
       <c r="J109" s="10" t="n">
         <v>0.5</v>
@@ -6920,17 +6920,17 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>DAL @ NYG</t>
+          <t>CAR @ ATL</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>Under 48.5</t>
+          <t>ATL -1.5</t>
         </is>
       </c>
       <c r="E110" s="12" t="n">
@@ -6946,7 +6946,7 @@
         <v>-0.0245</v>
       </c>
       <c r="I110" s="13" t="n">
-        <v>-0.05031031389922158</v>
+        <v>-0.0502615685566572</v>
       </c>
       <c r="J110" s="15" t="n">
         <v>0.5</v>
@@ -6961,17 +6961,17 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>CAR @ ATL</t>
+          <t>CIN @ HOU</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>ATL -1.5</t>
+          <t>Under 46.5</t>
         </is>
       </c>
       <c r="E111" s="7" t="n">
@@ -6987,7 +6987,7 @@
         <v>-0.0245</v>
       </c>
       <c r="I111" s="8" t="n">
-        <v>-0.0502615685566572</v>
+        <v>-0.05031105788036128</v>
       </c>
       <c r="J111" s="10" t="n">
         <v>0.5</v>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>CIN @ HOU</t>
+          <t>CLE @ TB</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>Under 46.5</t>
+          <t>Under 42.5</t>
         </is>
       </c>
       <c r="E112" s="12" t="n">
@@ -7028,7 +7028,7 @@
         <v>-0.0245</v>
       </c>
       <c r="I112" s="13" t="n">
-        <v>-0.05031105788036128</v>
+        <v>-0.05031725382596147</v>
       </c>
       <c r="J112" s="15" t="n">
         <v>0.5</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>CLE @ TB</t>
+          <t>MIA @ SF</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Under 42.5</t>
+          <t>Over 46.5</t>
         </is>
       </c>
       <c r="E113" s="7" t="n">
@@ -7069,7 +7069,7 @@
         <v>-0.0245</v>
       </c>
       <c r="I113" s="8" t="n">
-        <v>-0.05031725382596147</v>
+        <v>-0.05030855398815443</v>
       </c>
       <c r="J113" s="10" t="n">
         <v>0.5</v>
@@ -7084,33 +7084,33 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>MIA @ SF</t>
+          <t>WSH @ DAL</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>Over 46.5</t>
+          <t>WSH +4.5</t>
         </is>
       </c>
       <c r="E114" s="12" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="F114" s="13" t="n">
-        <v>0.4975</v>
+        <v>0.5077</v>
       </c>
       <c r="G114" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5349</v>
       </c>
       <c r="H114" s="13" t="n">
-        <v>-0.0245</v>
+        <v>-0.0252</v>
       </c>
       <c r="I114" s="13" t="n">
-        <v>-0.05030855398815443</v>
+        <v>-0.05086019673711512</v>
       </c>
       <c r="J114" s="15" t="n">
         <v>0.5</v>
@@ -7125,33 +7125,33 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>WSH @ DAL</t>
+          <t>JAX @ DEN</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>WSH +4.5</t>
+          <t>JAX ML</t>
         </is>
       </c>
       <c r="E115" s="7" t="n">
-        <v>-115</v>
+        <v>120</v>
       </c>
       <c r="F115" s="8" t="n">
-        <v>0.5077</v>
+        <v>0.4264</v>
       </c>
       <c r="G115" s="8" t="n">
-        <v>0.5349</v>
+        <v>0.4545</v>
       </c>
       <c r="H115" s="8" t="n">
-        <v>-0.0252</v>
+        <v>-0.026</v>
       </c>
       <c r="I115" s="8" t="n">
-        <v>-0.05086019673711512</v>
+        <v>-0.06145809889024723</v>
       </c>
       <c r="J115" s="10" t="n">
         <v>0.5</v>
@@ -7166,33 +7166,33 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>JAX @ DEN</t>
+          <t>BAL @ IND</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>JAX ML</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="E116" s="12" t="n">
-        <v>120</v>
+        <v>-105</v>
       </c>
       <c r="F116" s="13" t="n">
-        <v>0.4264</v>
+        <v>0.4835</v>
       </c>
       <c r="G116" s="13" t="n">
-        <v>0.4545</v>
+        <v>0.5122</v>
       </c>
       <c r="H116" s="13" t="n">
-        <v>-0.026</v>
+        <v>-0.0263</v>
       </c>
       <c r="I116" s="13" t="n">
-        <v>-0.06145809889024723</v>
+        <v>-0.05602980674510061</v>
       </c>
       <c r="J116" s="15" t="n">
         <v>0.5</v>
@@ -7494,7 +7494,7 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>BUF @ HOU</t>
+          <t>GB @ MIN</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
@@ -7504,23 +7504,23 @@
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>HOU +1.5</t>
+          <t>MIN -1.5</t>
         </is>
       </c>
       <c r="E124" s="12" t="n">
-        <v>-115</v>
+        <v>-105</v>
       </c>
       <c r="F124" s="13" t="n">
-        <v>0.5029</v>
+        <v>0.481</v>
       </c>
       <c r="G124" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.5122</v>
       </c>
       <c r="H124" s="13" t="n">
-        <v>-0.0288</v>
+        <v>-0.0282</v>
       </c>
       <c r="I124" s="13" t="n">
-        <v>-0.05984185201832393</v>
+        <v>-0.06081320518164768</v>
       </c>
       <c r="J124" s="15" t="n">
         <v>0.5</v>
@@ -7535,7 +7535,7 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>NYJ @ TEN</t>
+          <t>BUF @ HOU</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
@@ -7545,23 +7545,23 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>NYJ +3</t>
+          <t>HOU +1.5</t>
         </is>
       </c>
       <c r="E125" s="7" t="n">
-        <v>-120</v>
+        <v>-115</v>
       </c>
       <c r="F125" s="8" t="n">
-        <v>0.513</v>
+        <v>0.5029</v>
       </c>
       <c r="G125" s="8" t="n">
-        <v>0.5455</v>
+        <v>0.5349</v>
       </c>
       <c r="H125" s="8" t="n">
-        <v>-0.0291</v>
+        <v>-0.0288</v>
       </c>
       <c r="I125" s="8" t="n">
-        <v>-0.05516746946063461</v>
+        <v>-0.05984185201832393</v>
       </c>
       <c r="J125" s="10" t="n">
         <v>0.5</v>
@@ -7576,33 +7576,33 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>BUF @ HOU</t>
+          <t>NYJ @ TEN</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>HOU ML</t>
+          <t>NYJ +3</t>
         </is>
       </c>
       <c r="E126" s="12" t="n">
-        <v>-102</v>
+        <v>-120</v>
       </c>
       <c r="F126" s="13" t="n">
-        <v>0.4724</v>
+        <v>0.513</v>
       </c>
       <c r="G126" s="13" t="n">
-        <v>0.505</v>
+        <v>0.5455</v>
       </c>
       <c r="H126" s="13" t="n">
-        <v>-0.0292</v>
+        <v>-0.0291</v>
       </c>
       <c r="I126" s="13" t="n">
-        <v>-0.06393411301888563</v>
+        <v>-0.05516746946063461</v>
       </c>
       <c r="J126" s="15" t="n">
         <v>0.5</v>
@@ -7617,33 +7617,33 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>WSH @ PHI</t>
+          <t>BUF @ HOU</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>PHI -4.5</t>
+          <t>HOU ML</t>
         </is>
       </c>
       <c r="E127" s="7" t="n">
-        <v>-110</v>
+        <v>-102</v>
       </c>
       <c r="F127" s="8" t="n">
-        <v>0.4907</v>
+        <v>0.4724</v>
       </c>
       <c r="G127" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.505</v>
       </c>
       <c r="H127" s="8" t="n">
-        <v>-0.0296</v>
+        <v>-0.0292</v>
       </c>
       <c r="I127" s="8" t="n">
-        <v>-0.06325385906102005</v>
+        <v>-0.06393411301888563</v>
       </c>
       <c r="J127" s="10" t="n">
         <v>0.5</v>
@@ -7658,7 +7658,7 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>JAX @ DEN</t>
+          <t>WSH @ PHI</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
@@ -7668,23 +7668,23 @@
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>JAX +2.5</t>
+          <t>PHI -4.5</t>
         </is>
       </c>
       <c r="E128" s="12" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="F128" s="13" t="n">
-        <v>0.4789</v>
+        <v>0.4907</v>
       </c>
       <c r="G128" s="13" t="n">
-        <v>0.5122</v>
+        <v>0.5238</v>
       </c>
       <c r="H128" s="13" t="n">
-        <v>-0.0298</v>
+        <v>-0.0296</v>
       </c>
       <c r="I128" s="13" t="n">
-        <v>-0.06504688222501909</v>
+        <v>-0.06325385906102005</v>
       </c>
       <c r="J128" s="15" t="n">
         <v>0.5</v>
@@ -7699,33 +7699,33 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>TB @ CIN</t>
+          <t>JAX @ DEN</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>CIN ML</t>
+          <t>JAX +2.5</t>
         </is>
       </c>
       <c r="E129" s="7" t="n">
-        <v>-198</v>
+        <v>-105</v>
       </c>
       <c r="F129" s="8" t="n">
-        <v>0.6303</v>
+        <v>0.4789</v>
       </c>
       <c r="G129" s="8" t="n">
-        <v>0.6644</v>
+        <v>0.5122</v>
       </c>
       <c r="H129" s="8" t="n">
-        <v>-0.0303</v>
+        <v>-0.0298</v>
       </c>
       <c r="I129" s="8" t="n">
-        <v>-0.05091550753083285</v>
+        <v>-0.06504688222501909</v>
       </c>
       <c r="J129" s="10" t="n">
         <v>0.5</v>
@@ -7740,33 +7740,33 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>ATL @ PIT</t>
+          <t>TB @ CIN</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>Under 41.5</t>
+          <t>CIN ML</t>
         </is>
       </c>
       <c r="E130" s="12" t="n">
-        <v>-105</v>
+        <v>-198</v>
       </c>
       <c r="F130" s="13" t="n">
-        <v>0.4759</v>
+        <v>0.6303</v>
       </c>
       <c r="G130" s="13" t="n">
-        <v>0.5122</v>
+        <v>0.6644</v>
       </c>
       <c r="H130" s="13" t="n">
-        <v>-0.0318</v>
+        <v>-0.0303</v>
       </c>
       <c r="I130" s="13" t="n">
-        <v>-0.0709051805295936</v>
+        <v>-0.05091550753083285</v>
       </c>
       <c r="J130" s="15" t="n">
         <v>0.5</v>
@@ -8027,7 +8027,7 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>BUF @ HOU</t>
+          <t>JAX @ DEN</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Under 44.5</t>
+          <t>Under 43.5</t>
         </is>
       </c>
       <c r="E137" s="7" t="n">
@@ -8053,7 +8053,7 @@
         <v>-0.0351</v>
       </c>
       <c r="I137" s="8" t="n">
-        <v>-0.07941799453259901</v>
+        <v>-0.07941938779748492</v>
       </c>
       <c r="J137" s="10" t="n">
         <v>0.5</v>
@@ -8068,33 +8068,33 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>JAX @ DEN</t>
+          <t>CIN @ HOU</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>Under 43.5</t>
+          <t>HOU ML</t>
         </is>
       </c>
       <c r="E138" s="12" t="n">
-        <v>-110</v>
+        <v>-135</v>
       </c>
       <c r="F138" s="13" t="n">
-        <v>0.4822</v>
+        <v>0.5326</v>
       </c>
       <c r="G138" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5745</v>
       </c>
       <c r="H138" s="13" t="n">
-        <v>-0.0351</v>
+        <v>-0.0353</v>
       </c>
       <c r="I138" s="13" t="n">
-        <v>-0.07941938779748492</v>
+        <v>-0.07219123952960282</v>
       </c>
       <c r="J138" s="15" t="n">
         <v>0.5</v>
@@ -8114,28 +8114,28 @@
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>HOU ML</t>
+          <t>HOU -2.5</t>
         </is>
       </c>
       <c r="E139" s="7" t="n">
-        <v>-135</v>
+        <v>-110</v>
       </c>
       <c r="F139" s="8" t="n">
-        <v>0.5326</v>
+        <v>0.4808</v>
       </c>
       <c r="G139" s="8" t="n">
-        <v>0.5745</v>
+        <v>0.5238</v>
       </c>
       <c r="H139" s="8" t="n">
-        <v>-0.0353</v>
+        <v>-0.036</v>
       </c>
       <c r="I139" s="8" t="n">
-        <v>-0.07219123952960282</v>
+        <v>-0.08220177449715427</v>
       </c>
       <c r="J139" s="10" t="n">
         <v>0.5</v>
@@ -8150,7 +8150,7 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>CIN @ HOU</t>
+          <t>PIT @ NE</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
@@ -8160,14 +8160,14 @@
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>HOU -2.5</t>
+          <t>NE -4.5</t>
         </is>
       </c>
       <c r="E140" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F140" s="13" t="n">
-        <v>0.4808</v>
+        <v>0.4807</v>
       </c>
       <c r="G140" s="13" t="n">
         <v>0.5238</v>
@@ -8176,7 +8176,7 @@
         <v>-0.036</v>
       </c>
       <c r="I140" s="13" t="n">
-        <v>-0.08220177449715427</v>
+        <v>-0.08223353370621594</v>
       </c>
       <c r="J140" s="15" t="n">
         <v>0.5</v>
@@ -8191,7 +8191,7 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>PIT @ NE</t>
+          <t>MIN @ CHI</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
@@ -8201,23 +8201,23 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>NE -4.5</t>
+          <t>CHI -3.5</t>
         </is>
       </c>
       <c r="E141" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F141" s="8" t="n">
-        <v>0.4807</v>
+        <v>0.4783</v>
       </c>
       <c r="G141" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H141" s="8" t="n">
-        <v>-0.036</v>
+        <v>-0.0373</v>
       </c>
       <c r="I141" s="8" t="n">
-        <v>-0.08223353370621594</v>
+        <v>-0.08680112526952322</v>
       </c>
       <c r="J141" s="10" t="n">
         <v>0.5</v>
@@ -8232,33 +8232,33 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>MIN @ CHI</t>
+          <t>NE @ SEA</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>CHI -3.5</t>
+          <t>Over 44.5</t>
         </is>
       </c>
       <c r="E142" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F142" s="13" t="n">
-        <v>0.4783</v>
+        <v>0.4771</v>
       </c>
       <c r="G142" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H142" s="13" t="n">
-        <v>-0.0373</v>
+        <v>-0.038</v>
       </c>
       <c r="I142" s="13" t="n">
-        <v>-0.08680112526952322</v>
+        <v>-0.08909195811116855</v>
       </c>
       <c r="J142" s="15" t="n">
         <v>0.5</v>
@@ -8273,33 +8273,33 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>SF @ LAR</t>
+          <t>CLE @ TB</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>TB ML</t>
         </is>
       </c>
       <c r="E143" s="7" t="n">
-        <v>-108</v>
+        <v>-245</v>
       </c>
       <c r="F143" s="8" t="n">
-        <v>0.4731</v>
+        <v>0.6631</v>
       </c>
       <c r="G143" s="8" t="n">
-        <v>0.5192</v>
+        <v>0.7101</v>
       </c>
       <c r="H143" s="8" t="n">
-        <v>-0.0377</v>
+        <v>-0.0381</v>
       </c>
       <c r="I143" s="8" t="n">
-        <v>-0.08885851327903233</v>
+        <v>-0.0656322697737271</v>
       </c>
       <c r="J143" s="10" t="n">
         <v>0.5</v>
@@ -8314,33 +8314,33 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>NE @ SEA</t>
+          <t>PIT @ NE</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>Over 44.5</t>
+          <t>NE ML</t>
         </is>
       </c>
       <c r="E144" s="12" t="n">
-        <v>-110</v>
+        <v>-218</v>
       </c>
       <c r="F144" s="13" t="n">
-        <v>0.4771</v>
+        <v>0.6373</v>
       </c>
       <c r="G144" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.6855</v>
       </c>
       <c r="H144" s="13" t="n">
-        <v>-0.038</v>
+        <v>-0.0388</v>
       </c>
       <c r="I144" s="13" t="n">
-        <v>-0.08909195811116855</v>
+        <v>-0.06971050752804403</v>
       </c>
       <c r="J144" s="15" t="n">
         <v>0.5</v>
@@ -8355,7 +8355,7 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>CLE @ TB</t>
+          <t>ARI @ LAC</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
@@ -8365,28 +8365,32 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>TB ML</t>
+          <t>LAC ML</t>
         </is>
       </c>
       <c r="E145" s="7" t="n">
-        <v>-245</v>
+        <v>-535</v>
       </c>
       <c r="F145" s="8" t="n">
-        <v>0.6631</v>
+        <v>0.7935</v>
       </c>
       <c r="G145" s="8" t="n">
-        <v>0.7101</v>
+        <v>0.8425</v>
       </c>
       <c r="H145" s="8" t="n">
-        <v>-0.0381</v>
+        <v>-0.0392</v>
       </c>
       <c r="I145" s="8" t="n">
-        <v>-0.0656322697737271</v>
+        <v>-0.05784122572580089</v>
       </c>
       <c r="J145" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="K145" s="4" t="inlineStr"/>
+      <c r="K145" s="4" t="inlineStr">
+        <is>
+          <t>price -535 outside the allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
@@ -8396,33 +8400,33 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>PIT @ NE</t>
+          <t>BUF @ HOU</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>NE ML</t>
+          <t>Under 44.5</t>
         </is>
       </c>
       <c r="E146" s="12" t="n">
-        <v>-218</v>
+        <v>-110</v>
       </c>
       <c r="F146" s="13" t="n">
-        <v>0.6373</v>
+        <v>0.4746</v>
       </c>
       <c r="G146" s="13" t="n">
-        <v>0.6855</v>
+        <v>0.5238</v>
       </c>
       <c r="H146" s="13" t="n">
-        <v>-0.0388</v>
+        <v>-0.0393</v>
       </c>
       <c r="I146" s="13" t="n">
-        <v>-0.06971050752804403</v>
+        <v>-0.09393284195420176</v>
       </c>
       <c r="J146" s="15" t="n">
         <v>0.5</v>
@@ -8437,7 +8441,7 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>ARI @ LAC</t>
+          <t>CHI @ CAR</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
@@ -8447,32 +8451,28 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>LAC ML</t>
+          <t>CHI ML</t>
         </is>
       </c>
       <c r="E147" s="7" t="n">
-        <v>-535</v>
+        <v>-142</v>
       </c>
       <c r="F147" s="8" t="n">
-        <v>0.7935</v>
+        <v>0.5372</v>
       </c>
       <c r="G147" s="8" t="n">
-        <v>0.8425</v>
+        <v>0.5868</v>
       </c>
       <c r="H147" s="8" t="n">
-        <v>-0.0392</v>
+        <v>-0.0394</v>
       </c>
       <c r="I147" s="8" t="n">
-        <v>-0.05784122572580089</v>
+        <v>-0.08372550837688442</v>
       </c>
       <c r="J147" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="K147" s="4" t="inlineStr">
-        <is>
-          <t>price -535 outside the allowed range</t>
-        </is>
-      </c>
+      <c r="K147" s="4" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
@@ -8482,33 +8482,33 @@
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>DEN @ KC</t>
+          <t>MIA @ LV</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>Over 42.5</t>
+          <t>LV ML</t>
         </is>
       </c>
       <c r="E148" s="12" t="n">
-        <v>-110</v>
+        <v>-198</v>
       </c>
       <c r="F148" s="13" t="n">
-        <v>0.4746</v>
+        <v>0.6147</v>
       </c>
       <c r="G148" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.6644</v>
       </c>
       <c r="H148" s="13" t="n">
-        <v>-0.0392</v>
+        <v>-0.0395</v>
       </c>
       <c r="I148" s="13" t="n">
-        <v>-0.0939198213327469</v>
+        <v>-0.07423866374687454</v>
       </c>
       <c r="J148" s="15" t="n">
         <v>0.5</v>
@@ -8523,33 +8523,33 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>CHI @ CAR</t>
+          <t>SF @ LAR</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>CHI ML</t>
+          <t>LAR -3.5</t>
         </is>
       </c>
       <c r="E149" s="7" t="n">
-        <v>-142</v>
+        <v>-105</v>
       </c>
       <c r="F149" s="8" t="n">
-        <v>0.5372</v>
+        <v>0.461</v>
       </c>
       <c r="G149" s="8" t="n">
-        <v>0.5868</v>
+        <v>0.5122</v>
       </c>
       <c r="H149" s="8" t="n">
-        <v>-0.0394</v>
+        <v>-0.0402</v>
       </c>
       <c r="I149" s="8" t="n">
-        <v>-0.08372550837688442</v>
+        <v>-0.1000153180942645</v>
       </c>
       <c r="J149" s="10" t="n">
         <v>0.5</v>
@@ -8564,33 +8564,33 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>MIA @ LV</t>
+          <t>NE @ SEA</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>LV ML</t>
+          <t>SEA -3.5</t>
         </is>
       </c>
       <c r="E150" s="12" t="n">
-        <v>-198</v>
+        <v>-105</v>
       </c>
       <c r="F150" s="13" t="n">
-        <v>0.6147</v>
+        <v>0.4606</v>
       </c>
       <c r="G150" s="13" t="n">
-        <v>0.6644</v>
+        <v>0.5122</v>
       </c>
       <c r="H150" s="13" t="n">
-        <v>-0.0395</v>
+        <v>-0.0404</v>
       </c>
       <c r="I150" s="13" t="n">
-        <v>-0.07423866374687454</v>
+        <v>-0.1007104502117536</v>
       </c>
       <c r="J150" s="15" t="n">
         <v>0.5</v>
@@ -8605,33 +8605,33 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>SF @ LAR</t>
+          <t>NE @ SEA</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>LAR -3.5</t>
+          <t>SEA ML</t>
         </is>
       </c>
       <c r="E151" s="7" t="n">
-        <v>-105</v>
+        <v>-175</v>
       </c>
       <c r="F151" s="8" t="n">
-        <v>0.461</v>
+        <v>0.5835</v>
       </c>
       <c r="G151" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.6364</v>
       </c>
       <c r="H151" s="8" t="n">
-        <v>-0.0402</v>
+        <v>-0.0409</v>
       </c>
       <c r="I151" s="8" t="n">
-        <v>-0.1000153180942645</v>
+        <v>-0.08228327848316069</v>
       </c>
       <c r="J151" s="10" t="n">
         <v>0.5</v>
@@ -8646,33 +8646,33 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>BAL @ IND</t>
+          <t>CHI @ CAR</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>CHI -2.5</t>
         </is>
       </c>
       <c r="E152" s="12" t="n">
-        <v>-105</v>
+        <v>-118</v>
       </c>
       <c r="F152" s="13" t="n">
-        <v>0.4607</v>
+        <v>0.4872</v>
       </c>
       <c r="G152" s="13" t="n">
-        <v>0.5122</v>
+        <v>0.5413</v>
       </c>
       <c r="H152" s="13" t="n">
-        <v>-0.0403</v>
+        <v>-0.0415</v>
       </c>
       <c r="I152" s="13" t="n">
-        <v>-0.1005110510971273</v>
+        <v>-0.09994022472802433</v>
       </c>
       <c r="J152" s="15" t="n">
         <v>0.5</v>
@@ -8687,38 +8687,42 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>NE @ SEA</t>
+          <t>LV @ LAC</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>SEA -3.5</t>
+          <t>LAC ML</t>
         </is>
       </c>
       <c r="E153" s="7" t="n">
-        <v>-105</v>
+        <v>-375</v>
       </c>
       <c r="F153" s="8" t="n">
-        <v>0.4606</v>
+        <v>0.7348</v>
       </c>
       <c r="G153" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.7895</v>
       </c>
       <c r="H153" s="8" t="n">
-        <v>-0.0404</v>
+        <v>-0.0417</v>
       </c>
       <c r="I153" s="8" t="n">
-        <v>-0.1007104502117536</v>
+        <v>-0.06870592645055049</v>
       </c>
       <c r="J153" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="K153" s="4" t="inlineStr"/>
+      <c r="K153" s="4" t="inlineStr">
+        <is>
+          <t>price -375 outside the allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
@@ -8728,7 +8732,7 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>NE @ SEA</t>
+          <t>NYG @ LAR</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
@@ -8738,28 +8742,32 @@
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>SEA ML</t>
+          <t>LAR ML</t>
         </is>
       </c>
       <c r="E154" s="12" t="n">
-        <v>-175</v>
+        <v>-380</v>
       </c>
       <c r="F154" s="13" t="n">
-        <v>0.5835</v>
+        <v>0.7372</v>
       </c>
       <c r="G154" s="13" t="n">
-        <v>0.6364</v>
+        <v>0.7917</v>
       </c>
       <c r="H154" s="13" t="n">
-        <v>-0.0409</v>
+        <v>-0.0417</v>
       </c>
       <c r="I154" s="13" t="n">
-        <v>-0.08228327848316069</v>
+        <v>-0.06828284274607094</v>
       </c>
       <c r="J154" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="K154" s="5" t="inlineStr"/>
+      <c r="K154" s="5" t="inlineStr">
+        <is>
+          <t>price -380 outside the allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
@@ -8769,7 +8777,7 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>CHI @ CAR</t>
+          <t>BAL @ IND</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
@@ -8779,23 +8787,23 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>CHI -2.5</t>
+          <t>BAL -3.5</t>
         </is>
       </c>
       <c r="E155" s="7" t="n">
-        <v>-118</v>
+        <v>-108</v>
       </c>
       <c r="F155" s="8" t="n">
-        <v>0.4872</v>
+        <v>0.4632</v>
       </c>
       <c r="G155" s="8" t="n">
-        <v>0.5413</v>
+        <v>0.5192</v>
       </c>
       <c r="H155" s="8" t="n">
-        <v>-0.0415</v>
+        <v>-0.0423</v>
       </c>
       <c r="I155" s="8" t="n">
-        <v>-0.09994022472802433</v>
+        <v>-0.1078257297233006</v>
       </c>
       <c r="J155" s="10" t="n">
         <v>0.5</v>
@@ -8810,7 +8818,7 @@
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>LV @ LAC</t>
+          <t>BAL @ IND</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
@@ -8820,32 +8828,28 @@
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>LAC ML</t>
+          <t>BAL ML</t>
         </is>
       </c>
       <c r="E156" s="12" t="n">
-        <v>-375</v>
+        <v>-180</v>
       </c>
       <c r="F156" s="13" t="n">
-        <v>0.7348</v>
+        <v>0.5864</v>
       </c>
       <c r="G156" s="13" t="n">
-        <v>0.7895</v>
+        <v>0.6429</v>
       </c>
       <c r="H156" s="13" t="n">
-        <v>-0.0417</v>
+        <v>-0.0425</v>
       </c>
       <c r="I156" s="13" t="n">
-        <v>-0.06870592645055049</v>
+        <v>-0.08702187948637286</v>
       </c>
       <c r="J156" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="K156" s="5" t="inlineStr">
-        <is>
-          <t>price -375 outside the allowed range</t>
-        </is>
-      </c>
+      <c r="K156" s="5" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
@@ -8855,7 +8859,7 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>NYG @ LAR</t>
+          <t>NO @ DET</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
@@ -8865,32 +8869,28 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>LAR ML</t>
+          <t>DET ML</t>
         </is>
       </c>
       <c r="E157" s="7" t="n">
-        <v>-380</v>
+        <v>-305</v>
       </c>
       <c r="F157" s="8" t="n">
-        <v>0.7372</v>
+        <v>0.6964</v>
       </c>
       <c r="G157" s="8" t="n">
-        <v>0.7917</v>
+        <v>0.7531</v>
       </c>
       <c r="H157" s="8" t="n">
-        <v>-0.0417</v>
+        <v>-0.0426</v>
       </c>
       <c r="I157" s="8" t="n">
-        <v>-0.06828284274607094</v>
+        <v>-0.07463213538982388</v>
       </c>
       <c r="J157" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="K157" s="4" t="inlineStr">
-        <is>
-          <t>price -380 outside the allowed range</t>
-        </is>
-      </c>
+      <c r="K157" s="4" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
@@ -8900,7 +8900,7 @@
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>BAL @ IND</t>
+          <t>ARI @ LAC</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
@@ -8910,23 +8910,23 @@
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>BAL -3.5</t>
+          <t>LAC -10.5</t>
         </is>
       </c>
       <c r="E158" s="12" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="F158" s="13" t="n">
-        <v>0.4632</v>
+        <v>0.4665</v>
       </c>
       <c r="G158" s="13" t="n">
-        <v>0.5192</v>
+        <v>0.5238</v>
       </c>
       <c r="H158" s="13" t="n">
-        <v>-0.0423</v>
+        <v>-0.0428</v>
       </c>
       <c r="I158" s="13" t="n">
-        <v>-0.1078257297233006</v>
+        <v>-0.1094436399964945</v>
       </c>
       <c r="J158" s="15" t="n">
         <v>0.5</v>
@@ -8941,7 +8941,7 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>BAL @ IND</t>
+          <t>MIN @ CHI</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
@@ -8951,23 +8951,23 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>BAL ML</t>
+          <t>CHI ML</t>
         </is>
       </c>
       <c r="E159" s="7" t="n">
-        <v>-180</v>
+        <v>-198</v>
       </c>
       <c r="F159" s="8" t="n">
-        <v>0.5864</v>
+        <v>0.6072</v>
       </c>
       <c r="G159" s="8" t="n">
-        <v>0.6429</v>
+        <v>0.6644</v>
       </c>
       <c r="H159" s="8" t="n">
-        <v>-0.0425</v>
+        <v>-0.0428</v>
       </c>
       <c r="I159" s="8" t="n">
-        <v>-0.08702187948637286</v>
+        <v>-0.08537236419210453</v>
       </c>
       <c r="J159" s="10" t="n">
         <v>0.5</v>
@@ -8982,33 +8982,33 @@
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>NO @ DET</t>
+          <t>CHI @ CAR</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>DET ML</t>
+          <t>Over 47.5</t>
         </is>
       </c>
       <c r="E160" s="12" t="n">
-        <v>-305</v>
+        <v>-115</v>
       </c>
       <c r="F160" s="13" t="n">
-        <v>0.6964</v>
+        <v>0.4759</v>
       </c>
       <c r="G160" s="13" t="n">
-        <v>0.7531</v>
+        <v>0.5349</v>
       </c>
       <c r="H160" s="13" t="n">
-        <v>-0.0426</v>
+        <v>-0.0435</v>
       </c>
       <c r="I160" s="13" t="n">
-        <v>-0.07463213538982388</v>
+        <v>-0.1103290525258087</v>
       </c>
       <c r="J160" s="15" t="n">
         <v>0.5</v>
@@ -9023,33 +9023,33 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>ARI @ LAC</t>
+          <t>MIN @ CHI</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>LAC -10.5</t>
+          <t>Over 45.5</t>
         </is>
       </c>
       <c r="E161" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F161" s="8" t="n">
-        <v>0.4665</v>
+        <v>0.4645</v>
       </c>
       <c r="G161" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H161" s="8" t="n">
-        <v>-0.0428</v>
+        <v>-0.0436</v>
       </c>
       <c r="I161" s="8" t="n">
-        <v>-0.1094436399964945</v>
+        <v>-0.1132136058104599</v>
       </c>
       <c r="J161" s="10" t="n">
         <v>0.5</v>
@@ -9064,33 +9064,33 @@
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>MIN @ CHI</t>
+          <t>LV @ LAC</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>CHI ML</t>
+          <t>Over 42.5</t>
         </is>
       </c>
       <c r="E162" s="12" t="n">
-        <v>-198</v>
+        <v>-110</v>
       </c>
       <c r="F162" s="13" t="n">
-        <v>0.6072</v>
+        <v>0.4645</v>
       </c>
       <c r="G162" s="13" t="n">
-        <v>0.6644</v>
+        <v>0.5238</v>
       </c>
       <c r="H162" s="13" t="n">
-        <v>-0.0428</v>
+        <v>-0.0436</v>
       </c>
       <c r="I162" s="13" t="n">
-        <v>-0.08537236419210453</v>
+        <v>-0.1132045300743653</v>
       </c>
       <c r="J162" s="15" t="n">
         <v>0.5</v>
@@ -9105,38 +9105,42 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>CHI @ CAR</t>
+          <t>NO @ BAL</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>Over 47.5</t>
+          <t>BAL ML</t>
         </is>
       </c>
       <c r="E163" s="7" t="n">
-        <v>-115</v>
+        <v>-355</v>
       </c>
       <c r="F163" s="8" t="n">
-        <v>0.4759</v>
+        <v>0.7205</v>
       </c>
       <c r="G163" s="8" t="n">
-        <v>0.5349</v>
+        <v>0.7802</v>
       </c>
       <c r="H163" s="8" t="n">
-        <v>-0.0435</v>
+        <v>-0.0437</v>
       </c>
       <c r="I163" s="8" t="n">
-        <v>-0.1103290525258087</v>
+        <v>-0.07594524744761211</v>
       </c>
       <c r="J163" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="K163" s="4" t="inlineStr"/>
+      <c r="K163" s="4" t="inlineStr">
+        <is>
+          <t>price -355 outside the allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
@@ -9146,33 +9150,33 @@
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>MIN @ CHI</t>
+          <t>PHI @ TEN</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>Over 45.5</t>
+          <t>PHI ML</t>
         </is>
       </c>
       <c r="E164" s="12" t="n">
-        <v>-110</v>
+        <v>-205</v>
       </c>
       <c r="F164" s="13" t="n">
-        <v>0.4645</v>
+        <v>0.6123</v>
       </c>
       <c r="G164" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.6721</v>
       </c>
       <c r="H164" s="13" t="n">
-        <v>-0.0436</v>
+        <v>-0.0438</v>
       </c>
       <c r="I164" s="13" t="n">
-        <v>-0.1132136058104599</v>
+        <v>-0.08829898217785048</v>
       </c>
       <c r="J164" s="15" t="n">
         <v>0.5</v>
@@ -9187,33 +9191,33 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>LV @ LAC</t>
+          <t>GB @ NYJ</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>Over 42.5</t>
+          <t>GB -5.5</t>
         </is>
       </c>
       <c r="E165" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F165" s="8" t="n">
-        <v>0.4645</v>
+        <v>0.4638</v>
       </c>
       <c r="G165" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H165" s="8" t="n">
-        <v>-0.0436</v>
+        <v>-0.0439</v>
       </c>
       <c r="I165" s="8" t="n">
-        <v>-0.1132045300743653</v>
+        <v>-0.114653280785704</v>
       </c>
       <c r="J165" s="10" t="n">
         <v>0.5</v>
@@ -9228,7 +9232,7 @@
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>NO @ BAL</t>
+          <t>SF @ LAR</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
@@ -9238,32 +9242,28 @@
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>BAL ML</t>
+          <t>LAR ML</t>
         </is>
       </c>
       <c r="E166" s="12" t="n">
-        <v>-355</v>
+        <v>-185</v>
       </c>
       <c r="F166" s="13" t="n">
-        <v>0.7205</v>
+        <v>0.5885</v>
       </c>
       <c r="G166" s="13" t="n">
-        <v>0.7802</v>
+        <v>0.6491</v>
       </c>
       <c r="H166" s="13" t="n">
-        <v>-0.0437</v>
+        <v>-0.0441</v>
       </c>
       <c r="I166" s="13" t="n">
-        <v>-0.07594524744761211</v>
+        <v>-0.09252744165458121</v>
       </c>
       <c r="J166" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="K166" s="5" t="inlineStr">
-        <is>
-          <t>price -355 outside the allowed range</t>
-        </is>
-      </c>
+      <c r="K166" s="5" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
@@ -9273,33 +9273,33 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>PHI @ TEN</t>
+          <t>NO @ BAL</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>PHI ML</t>
+          <t>BAL -7.5</t>
         </is>
       </c>
       <c r="E167" s="7" t="n">
-        <v>-205</v>
+        <v>-110</v>
       </c>
       <c r="F167" s="8" t="n">
-        <v>0.6123</v>
+        <v>0.4629</v>
       </c>
       <c r="G167" s="8" t="n">
-        <v>0.6721</v>
+        <v>0.5238</v>
       </c>
       <c r="H167" s="8" t="n">
-        <v>-0.0438</v>
+        <v>-0.0442</v>
       </c>
       <c r="I167" s="8" t="n">
-        <v>-0.08829898217785048</v>
+        <v>-0.1163005544616851</v>
       </c>
       <c r="J167" s="10" t="n">
         <v>0.5</v>
@@ -9314,7 +9314,7 @@
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>GB @ NYJ</t>
+          <t>IND @ KC</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
@@ -9324,23 +9324,23 @@
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>GB -5.5</t>
+          <t>KC -6.5</t>
         </is>
       </c>
       <c r="E168" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F168" s="13" t="n">
-        <v>0.4638</v>
+        <v>0.4627</v>
       </c>
       <c r="G168" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H168" s="13" t="n">
-        <v>-0.0439</v>
+        <v>-0.0443</v>
       </c>
       <c r="I168" s="13" t="n">
-        <v>-0.114653280785704</v>
+        <v>-0.1167347160720638</v>
       </c>
       <c r="J168" s="15" t="n">
         <v>0.5</v>
@@ -9355,33 +9355,33 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>SF @ LAR</t>
+          <t>ATL @ PIT</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>LAR ML</t>
+          <t>Under 41.5</t>
         </is>
       </c>
       <c r="E169" s="7" t="n">
-        <v>-185</v>
+        <v>-105</v>
       </c>
       <c r="F169" s="8" t="n">
-        <v>0.5885</v>
+        <v>0.4507</v>
       </c>
       <c r="G169" s="8" t="n">
-        <v>0.6491</v>
+        <v>0.5122</v>
       </c>
       <c r="H169" s="8" t="n">
-        <v>-0.0441</v>
+        <v>-0.0444</v>
       </c>
       <c r="I169" s="8" t="n">
-        <v>-0.09252744165458121</v>
+        <v>-0.1201358675073684</v>
       </c>
       <c r="J169" s="10" t="n">
         <v>0.5</v>
@@ -9396,33 +9396,33 @@
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>NO @ BAL</t>
+          <t>IND @ KC</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>BAL -7.5</t>
+          <t>Over 47.5</t>
         </is>
       </c>
       <c r="E170" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F170" s="13" t="n">
-        <v>0.4629</v>
+        <v>0.462</v>
       </c>
       <c r="G170" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H170" s="13" t="n">
-        <v>-0.0442</v>
+        <v>-0.0445</v>
       </c>
       <c r="I170" s="13" t="n">
-        <v>-0.1163005544616851</v>
+        <v>-0.1180220918978541</v>
       </c>
       <c r="J170" s="15" t="n">
         <v>0.5</v>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>IND @ KC</t>
+          <t>NO @ DET</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
@@ -9447,23 +9447,23 @@
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>KC -6.5</t>
+          <t>DET -7</t>
         </is>
       </c>
       <c r="E171" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F171" s="8" t="n">
-        <v>0.4627</v>
+        <v>0.4618</v>
       </c>
       <c r="G171" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H171" s="8" t="n">
-        <v>-0.0443</v>
+        <v>-0.0446</v>
       </c>
       <c r="I171" s="8" t="n">
-        <v>-0.1167347160720638</v>
+        <v>-0.1119613290895949</v>
       </c>
       <c r="J171" s="10" t="n">
         <v>0.5</v>
@@ -9478,33 +9478,33 @@
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
-          <t>IND @ KC</t>
+          <t>GB @ NYJ</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>Over 47.5</t>
+          <t>GB ML</t>
         </is>
       </c>
       <c r="E172" s="12" t="n">
-        <v>-110</v>
+        <v>-238</v>
       </c>
       <c r="F172" s="13" t="n">
-        <v>0.462</v>
+        <v>0.6409</v>
       </c>
       <c r="G172" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="H172" s="13" t="n">
-        <v>-0.0445</v>
+        <v>-0.045</v>
       </c>
       <c r="I172" s="13" t="n">
-        <v>-0.1180220918978541</v>
+        <v>-0.08909904384068018</v>
       </c>
       <c r="J172" s="15" t="n">
         <v>0.5</v>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>NO @ DET</t>
+          <t>PHI @ TEN</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
@@ -9529,23 +9529,23 @@
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>DET -7</t>
+          <t>PHI -4.5</t>
         </is>
       </c>
       <c r="E173" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F173" s="8" t="n">
-        <v>0.4618</v>
+        <v>0.4597</v>
       </c>
       <c r="G173" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H173" s="8" t="n">
-        <v>-0.0446</v>
+        <v>-0.0452</v>
       </c>
       <c r="I173" s="8" t="n">
-        <v>-0.1119613290895949</v>
+        <v>-0.1223058059611346</v>
       </c>
       <c r="J173" s="10" t="n">
         <v>0.5</v>
@@ -9560,33 +9560,33 @@
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>GB @ NYJ</t>
+          <t>NYG @ LAR</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>GB ML</t>
+          <t>LAR -8.5</t>
         </is>
       </c>
       <c r="E174" s="12" t="n">
-        <v>-238</v>
+        <v>-110</v>
       </c>
       <c r="F174" s="13" t="n">
-        <v>0.6409</v>
+        <v>0.4594</v>
       </c>
       <c r="G174" s="13" t="n">
-        <v>0.7040999999999999</v>
+        <v>0.5238</v>
       </c>
       <c r="H174" s="13" t="n">
-        <v>-0.045</v>
+        <v>-0.0454</v>
       </c>
       <c r="I174" s="13" t="n">
-        <v>-0.08909904384068018</v>
+        <v>-0.1229516868549289</v>
       </c>
       <c r="J174" s="15" t="n">
         <v>0.5</v>
@@ -9601,7 +9601,7 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>PHI @ TEN</t>
+          <t>LV @ LAC</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
@@ -9611,23 +9611,23 @@
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>PHI -4.5</t>
+          <t>LAC -8.5</t>
         </is>
       </c>
       <c r="E175" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F175" s="8" t="n">
-        <v>0.4597</v>
+        <v>0.4578</v>
       </c>
       <c r="G175" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H175" s="8" t="n">
-        <v>-0.0452</v>
+        <v>-0.0459</v>
       </c>
       <c r="I175" s="8" t="n">
-        <v>-0.1223058059611346</v>
+        <v>-0.1261070906377938</v>
       </c>
       <c r="J175" s="10" t="n">
         <v>0.5</v>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="B176" s="5" t="inlineStr">
         <is>
-          <t>CLE @ JAX</t>
+          <t>MIA @ LV</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
@@ -9659,16 +9659,16 @@
         <v>-110</v>
       </c>
       <c r="F176" s="13" t="n">
-        <v>0.4595</v>
+        <v>0.457</v>
       </c>
       <c r="G176" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H176" s="13" t="n">
-        <v>-0.0453</v>
+        <v>-0.0461</v>
       </c>
       <c r="I176" s="13" t="n">
-        <v>-0.1228333297743933</v>
+        <v>-0.1276251689568088</v>
       </c>
       <c r="J176" s="15" t="n">
         <v>0.5</v>
@@ -9683,33 +9683,33 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>NYG @ LAR</t>
+          <t>NO @ BAL</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>LAR -8.5</t>
+          <t>Over 46.5</t>
         </is>
       </c>
       <c r="E177" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F177" s="8" t="n">
-        <v>0.4594</v>
+        <v>0.457</v>
       </c>
       <c r="G177" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H177" s="8" t="n">
-        <v>-0.0454</v>
+        <v>-0.0461</v>
       </c>
       <c r="I177" s="8" t="n">
-        <v>-0.1229516868549289</v>
+        <v>-0.1276128918105729</v>
       </c>
       <c r="J177" s="10" t="n">
         <v>0.5</v>
@@ -9724,33 +9724,33 @@
       </c>
       <c r="B178" s="5" t="inlineStr">
         <is>
-          <t>LV @ LAC</t>
+          <t>WSH @ DAL</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>LAC -8.5</t>
+          <t>Over 51.5</t>
         </is>
       </c>
       <c r="E178" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F178" s="13" t="n">
-        <v>0.4578</v>
+        <v>0.457</v>
       </c>
       <c r="G178" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H178" s="13" t="n">
-        <v>-0.0459</v>
+        <v>-0.0461</v>
       </c>
       <c r="I178" s="13" t="n">
-        <v>-0.1261070906377938</v>
+        <v>-0.1276150624646581</v>
       </c>
       <c r="J178" s="15" t="n">
         <v>0.5</v>
@@ -9765,7 +9765,7 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>MIA @ LV</t>
+          <t>CLE @ JAX</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
@@ -9782,16 +9782,16 @@
         <v>-110</v>
       </c>
       <c r="F179" s="8" t="n">
-        <v>0.457</v>
+        <v>0.4545</v>
       </c>
       <c r="G179" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H179" s="8" t="n">
-        <v>-0.0461</v>
+        <v>-0.0468</v>
       </c>
       <c r="I179" s="8" t="n">
-        <v>-0.1276251689568088</v>
+        <v>-0.1324091895425259</v>
       </c>
       <c r="J179" s="10" t="n">
         <v>0.5</v>
@@ -9806,7 +9806,7 @@
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>NO @ BAL</t>
+          <t>DEN @ KC</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
@@ -9816,23 +9816,23 @@
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>Over 46.5</t>
+          <t>Over 42.5</t>
         </is>
       </c>
       <c r="E180" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F180" s="13" t="n">
-        <v>0.457</v>
+        <v>0.4545</v>
       </c>
       <c r="G180" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H180" s="13" t="n">
-        <v>-0.0461</v>
+        <v>-0.0468</v>
       </c>
       <c r="I180" s="13" t="n">
-        <v>-0.1276128918105729</v>
+        <v>-0.1323854465016522</v>
       </c>
       <c r="J180" s="15" t="n">
         <v>0.5</v>
@@ -9847,33 +9847,33 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>WSH @ DAL</t>
+          <t>CLE @ JAX</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>Over 51.5</t>
+          <t>JAX -7.5</t>
         </is>
       </c>
       <c r="E181" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F181" s="8" t="n">
-        <v>0.457</v>
+        <v>0.4518</v>
       </c>
       <c r="G181" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H181" s="8" t="n">
-        <v>-0.0461</v>
+        <v>-0.0475</v>
       </c>
       <c r="I181" s="8" t="n">
-        <v>-0.1276150624646581</v>
+        <v>-0.1374608846653683</v>
       </c>
       <c r="J181" s="10" t="n">
         <v>0.5</v>
@@ -9888,24 +9888,24 @@
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>CLE @ JAX</t>
+          <t>GB @ MIN</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>JAX -7.5</t>
+          <t>Over 45.5</t>
         </is>
       </c>
       <c r="E182" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F182" s="13" t="n">
-        <v>0.4518</v>
+        <v>0.452</v>
       </c>
       <c r="G182" s="13" t="n">
         <v>0.5238</v>
@@ -9914,7 +9914,7 @@
         <v>-0.0475</v>
       </c>
       <c r="I182" s="13" t="n">
-        <v>-0.1374608846653683</v>
+        <v>-0.1371717248119999</v>
       </c>
       <c r="J182" s="15" t="n">
         <v>0.5</v>
@@ -9929,7 +9929,7 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>GB @ MIN</t>
+          <t>WSH @ PHI</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
@@ -9943,19 +9943,19 @@
         </is>
       </c>
       <c r="E183" s="7" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="F183" s="8" t="n">
-        <v>0.452</v>
+        <v>0.4608</v>
       </c>
       <c r="G183" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5349</v>
       </c>
       <c r="H183" s="8" t="n">
-        <v>-0.0475</v>
+        <v>-0.048</v>
       </c>
       <c r="I183" s="8" t="n">
-        <v>-0.1371717248119999</v>
+        <v>-0.138584043510162</v>
       </c>
       <c r="J183" s="10" t="n">
         <v>0.5</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>WSH @ PHI</t>
+          <t>DET @ BUF</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
@@ -9980,23 +9980,23 @@
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>Over 45.5</t>
+          <t>Over 52.5</t>
         </is>
       </c>
       <c r="E184" s="12" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="F184" s="13" t="n">
-        <v>0.4608</v>
+        <v>0.4495</v>
       </c>
       <c r="G184" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.5238</v>
       </c>
       <c r="H184" s="13" t="n">
-        <v>-0.048</v>
+        <v>-0.0481</v>
       </c>
       <c r="I184" s="13" t="n">
-        <v>-0.138584043510162</v>
+        <v>-0.1419429805428652</v>
       </c>
       <c r="J184" s="15" t="n">
         <v>0.5</v>
@@ -10011,7 +10011,7 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>DET @ BUF</t>
+          <t>GB @ NYJ</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
@@ -10021,7 +10021,7 @@
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>Over 52.5</t>
+          <t>Under 42.5</t>
         </is>
       </c>
       <c r="E185" s="7" t="n">
@@ -10037,7 +10037,7 @@
         <v>-0.0481</v>
       </c>
       <c r="I185" s="8" t="n">
-        <v>-0.1419429805428652</v>
+        <v>-0.1419467748034449</v>
       </c>
       <c r="J185" s="10" t="n">
         <v>0.5</v>
@@ -10052,7 +10052,7 @@
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>GB @ NYJ</t>
+          <t>SF @ LAR</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
@@ -10062,23 +10062,23 @@
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>Under 42.5</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="E186" s="12" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="F186" s="13" t="n">
-        <v>0.4495</v>
+        <v>0.443</v>
       </c>
       <c r="G186" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5192</v>
       </c>
       <c r="H186" s="13" t="n">
-        <v>-0.0481</v>
+        <v>-0.0485</v>
       </c>
       <c r="I186" s="13" t="n">
-        <v>-0.1419467748034449</v>
+        <v>-0.1468845749088531</v>
       </c>
       <c r="J186" s="15" t="n">
         <v>0.5</v>
@@ -10220,33 +10220,33 @@
       </c>
       <c r="B190" s="5" t="inlineStr">
         <is>
-          <t>MIA @ SF</t>
+          <t>TB @ CIN</t>
         </is>
       </c>
       <c r="C190" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D190" s="5" t="inlineStr">
         <is>
-          <t>SF -10.5</t>
+          <t>Over 50.5</t>
         </is>
       </c>
       <c r="E190" s="12" t="n">
-        <v>-110</v>
+        <v>-118</v>
       </c>
       <c r="F190" s="13" t="n">
-        <v>0.4427</v>
+        <v>0.463</v>
       </c>
       <c r="G190" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5413</v>
       </c>
       <c r="H190" s="13" t="n">
-        <v>-0.0495</v>
+        <v>-0.049</v>
       </c>
       <c r="I190" s="13" t="n">
-        <v>-0.154755532036804</v>
+        <v>-0.1445512690360282</v>
       </c>
       <c r="J190" s="15" t="n">
         <v>0.5</v>
@@ -10266,37 +10266,33 @@
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>SF ML</t>
+          <t>SF -10.5</t>
         </is>
       </c>
       <c r="E191" s="7" t="n">
-        <v>-650</v>
+        <v>-110</v>
       </c>
       <c r="F191" s="8" t="n">
-        <v>0.7838000000000001</v>
+        <v>0.4427</v>
       </c>
       <c r="G191" s="8" t="n">
-        <v>0.8667</v>
+        <v>0.5238</v>
       </c>
       <c r="H191" s="8" t="n">
-        <v>-0.0499</v>
+        <v>-0.0495</v>
       </c>
       <c r="I191" s="8" t="n">
-        <v>-0.09497961537517048</v>
+        <v>-0.154755532036804</v>
       </c>
       <c r="J191" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="K191" s="4" t="inlineStr">
-        <is>
-          <t>price -650 outside the allowed range</t>
-        </is>
-      </c>
+      <c r="K191" s="4" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="5" t="inlineStr">
@@ -10306,38 +10302,42 @@
       </c>
       <c r="B192" s="5" t="inlineStr">
         <is>
-          <t>NO @ DET</t>
+          <t>MIA @ SF</t>
         </is>
       </c>
       <c r="C192" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D192" s="5" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>SF ML</t>
         </is>
       </c>
       <c r="E192" s="12" t="n">
-        <v>-118</v>
+        <v>-650</v>
       </c>
       <c r="F192" s="13" t="n">
-        <v>0.4555</v>
+        <v>0.7838000000000001</v>
       </c>
       <c r="G192" s="13" t="n">
-        <v>0.5413</v>
+        <v>0.8667</v>
       </c>
       <c r="H192" s="13" t="n">
-        <v>-0.0503</v>
+        <v>-0.0499</v>
       </c>
       <c r="I192" s="13" t="n">
-        <v>-0.1584158803963682</v>
+        <v>-0.09497961537517048</v>
       </c>
       <c r="J192" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="K192" s="5" t="inlineStr"/>
+      <c r="K192" s="5" t="inlineStr">
+        <is>
+          <t>price -650 outside the allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
@@ -10347,7 +10347,7 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>TB @ CIN</t>
+          <t>NO @ DET</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
@@ -10357,23 +10357,23 @@
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>Over 50.5</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="E193" s="7" t="n">
         <v>-118</v>
       </c>
       <c r="F193" s="8" t="n">
-        <v>0.453</v>
+        <v>0.4555</v>
       </c>
       <c r="G193" s="8" t="n">
         <v>0.5413</v>
       </c>
       <c r="H193" s="8" t="n">
-        <v>-0.0507</v>
+        <v>-0.0503</v>
       </c>
       <c r="I193" s="8" t="n">
-        <v>-0.1630210952770249</v>
+        <v>-0.1584158803963682</v>
       </c>
       <c r="J193" s="10" t="n">
         <v>0.5</v>
@@ -10433,33 +10433,33 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>NYJ @ TEN</t>
+          <t>SEA @ ARI</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>Under 38.5</t>
+          <t>SEA -10</t>
         </is>
       </c>
       <c r="E195" s="7" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="F195" s="8" t="n">
-        <v>0.4113</v>
+        <v>0.4189</v>
       </c>
       <c r="G195" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.5238</v>
       </c>
       <c r="H195" s="8" t="n">
-        <v>-0.0523</v>
+        <v>-0.0526</v>
       </c>
       <c r="I195" s="8" t="n">
-        <v>-0.1969748770013751</v>
+        <v>-0.1914752374467777</v>
       </c>
       <c r="J195" s="10" t="n">
         <v>0.5</v>
@@ -10474,33 +10474,33 @@
       </c>
       <c r="B196" s="5" t="inlineStr">
         <is>
-          <t>SEA @ ARI</t>
+          <t>NYJ @ TEN</t>
         </is>
       </c>
       <c r="C196" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D196" s="5" t="inlineStr">
         <is>
-          <t>SEA -10</t>
+          <t>Under 38.5</t>
         </is>
       </c>
       <c r="E196" s="12" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="F196" s="13" t="n">
-        <v>0.4189</v>
+        <v>0.4041</v>
       </c>
       <c r="G196" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5122</v>
       </c>
       <c r="H196" s="13" t="n">
-        <v>-0.0526</v>
+        <v>-0.0529</v>
       </c>
       <c r="I196" s="13" t="n">
-        <v>-0.1914752374467777</v>
+        <v>-0.2109934210059127</v>
       </c>
       <c r="J196" s="15" t="n">
         <v>0.5</v>
@@ -11934,7 +11934,7 @@
         <v>-3</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>41.5</v>
+        <v>40.7</v>
       </c>
       <c r="G24" s="11" t="n">
         <v>42.5</v>
@@ -12138,7 +12138,7 @@
         <v>-3</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>42.3</v>
+        <v>43.3</v>
       </c>
       <c r="G30" s="11" t="n">
         <v>41.5</v>
@@ -12172,7 +12172,7 @@
         <v>3.5</v>
       </c>
       <c r="F31" s="16" t="n">
-        <v>47.1</v>
+        <v>48</v>
       </c>
       <c r="G31" s="16" t="n">
         <v>48.5</v>
@@ -12206,7 +12206,7 @@
         <v>1.5</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>45.2</v>
+        <v>45.5</v>
       </c>
       <c r="G32" s="11" t="n">
         <v>44.5</v>
@@ -12274,7 +12274,7 @@
         <v>-7.5</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>42.1</v>
+        <v>42.3</v>
       </c>
       <c r="G34" s="11" t="n">
         <v>40.5</v>
@@ -12342,7 +12342,7 @@
         <v>-3</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>41.9</v>
+        <v>42.2</v>
       </c>
       <c r="G36" s="11" t="n">
         <v>38.5</v>
@@ -12376,7 +12376,7 @@
         <v>-3.5</v>
       </c>
       <c r="F37" s="16" t="n">
-        <v>48.4</v>
+        <v>48.8</v>
       </c>
       <c r="G37" s="16" t="n">
         <v>50.5</v>
@@ -12410,7 +12410,7 @@
         <v>-3.5</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>47.5</v>
+        <v>46.3</v>
       </c>
       <c r="G38" s="11" t="n">
         <v>48.5</v>
@@ -22938,10 +22938,10 @@
         <v>49.5</v>
       </c>
       <c r="I166" s="12" t="n">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="J166" s="12" t="n">
-        <v>-218</v>
+        <v>-225</v>
       </c>
       <c r="K166" s="19" t="n">
         <v>0</v>
@@ -30835,10 +30835,10 @@
         <v>46.5</v>
       </c>
       <c r="I315" s="7" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="J315" s="7" t="n">
-        <v>-122</v>
+        <v>-125</v>
       </c>
       <c r="K315" s="17" t="n">
         <v>0</v>
@@ -32878,7 +32878,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>The Falcons placed Hall (undisclosed) on injured reserve, Aaron Wilson of KPRC 2 Houston reports.</t>
+          <t>The Falcons placed Hall (undisclosed) on injured reserve Saturday, Aaron Wilson of KPRC 2 Houston reports.</t>
         </is>
       </c>
     </row>
@@ -38434,7 +38434,7 @@
       </c>
       <c r="F208" s="5" t="inlineStr">
         <is>
-          <t>Smith caught three of his four targets for 19 yards during The Cowboys' preseason game Friday versus the Saints.</t>
+          <t>Smith caught three of his four targets for 19 yards during the Cowboys' preseason game Friday versus the Saints.</t>
         </is>
       </c>
     </row>
@@ -46265,7 +46265,7 @@
       </c>
       <c r="E455" s="4" t="inlineStr">
         <is>
-          <t>Undisclosed</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F455" s="4" t="inlineStr">
@@ -57518,20 +57518,20 @@
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>82.3</v>
+        <v>73.3</v>
       </c>
       <c r="E5" s="17" t="n">
-        <v>6.3</v>
+        <v>6.9</v>
       </c>
       <c r="F5" s="17" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="G5" s="17" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Overcast</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="I5" s="9" t="n">
@@ -57556,28 +57556,28 @@
         </is>
       </c>
       <c r="D6" s="19" t="n">
-        <v>62.9</v>
+        <v>64</v>
       </c>
       <c r="E6" s="19" t="n">
-        <v>7.8</v>
+        <v>13.4</v>
       </c>
       <c r="F6" s="19" t="n">
-        <v>18.6</v>
+        <v>30</v>
       </c>
       <c r="G6" s="19" t="n">
         <v>6</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>Partly cloudy</t>
+          <t>Mainly clear</t>
         </is>
       </c>
       <c r="I6" s="14" t="n">
-        <v>-0.8</v>
+        <v>-3</v>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>Wind 8 mph (gusts 19)</t>
+          <t>Wind 13 mph (gusts 30)</t>
         </is>
       </c>
     </row>
@@ -57598,30 +57598,26 @@
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>56.5</v>
+        <v>65</v>
       </c>
       <c r="E7" s="17" t="n">
-        <v>6.7</v>
+        <v>7.4</v>
       </c>
       <c r="F7" s="17" t="n">
-        <v>23.5</v>
+        <v>9.6</v>
       </c>
       <c r="G7" s="17" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Light rain</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="I7" s="9" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>Wind 7 mph (gusts 24)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -57640,30 +57636,26 @@
         </is>
       </c>
       <c r="D8" s="19" t="n">
-        <v>68.8</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="E8" s="19" t="n">
-        <v>10.4</v>
+        <v>5.3</v>
       </c>
       <c r="F8" s="19" t="n">
-        <v>27.1</v>
+        <v>4.9</v>
       </c>
       <c r="G8" s="19" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>Rain showers</t>
+          <t>Partly cloudy</t>
         </is>
       </c>
       <c r="I8" s="14" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>Wind 10 mph (gusts 27) · retractable roof — effect halved</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -57682,30 +57674,26 @@
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>74.59999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="E9" s="17" t="n">
-        <v>5.8</v>
+        <v>7.7</v>
       </c>
       <c r="F9" s="17" t="n">
-        <v>19.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G9" s="17" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Violent showers</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="I9" s="9" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>Wind 6 mph (gusts 19) · retractable roof — effect halved</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -57724,16 +57712,16 @@
         </is>
       </c>
       <c r="D10" s="19" t="n">
-        <v>83.5</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="E10" s="19" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="F10" s="19" t="n">
-        <v>6.3</v>
+        <v>15</v>
       </c>
       <c r="G10" s="19" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
@@ -57762,30 +57750,26 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>99.09999999999999</v>
+        <v>86.8</v>
       </c>
       <c r="E11" s="17" t="n">
-        <v>4</v>
+        <v>10.1</v>
       </c>
       <c r="F11" s="17" t="n">
-        <v>3.4</v>
+        <v>17.2</v>
       </c>
       <c r="G11" s="17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Drizzle</t>
         </is>
       </c>
       <c r="I11" s="9" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>99°F</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -57804,20 +57788,20 @@
         </is>
       </c>
       <c r="D12" s="19" t="n">
-        <v>59.4</v>
+        <v>67.5</v>
       </c>
       <c r="E12" s="19" t="n">
-        <v>12.2</v>
+        <v>3.9</v>
       </c>
       <c r="F12" s="19" t="n">
-        <v>26.8</v>
+        <v>5.1</v>
       </c>
       <c r="G12" s="19" t="n">
         <v>15</v>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>Overcast</t>
+          <t>Mainly clear</t>
         </is>
       </c>
       <c r="I12" s="14" t="n">
@@ -57846,30 +57830,26 @@
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>91.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="E13" s="17" t="n">
-        <v>11.1</v>
+        <v>4.3</v>
       </c>
       <c r="F13" s="17" t="n">
-        <v>18.8</v>
+        <v>5.6</v>
       </c>
       <c r="G13" s="17" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Mainly clear</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>Wind 11 mph (gusts 19)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -57888,30 +57868,26 @@
         </is>
       </c>
       <c r="D14" s="19" t="n">
-        <v>64.5</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="E14" s="19" t="n">
-        <v>8.800000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="F14" s="19" t="n">
-        <v>19.5</v>
+        <v>5.1</v>
       </c>
       <c r="G14" s="19" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>Rain showers</t>
+          <t>Mainly clear</t>
         </is>
       </c>
       <c r="I14" s="14" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>Wind 9 mph (gusts 20)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -57930,16 +57906,16 @@
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>81.3</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E15" s="17" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F15" s="17" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="G15" s="17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
@@ -57968,20 +57944,20 @@
         </is>
       </c>
       <c r="D16" s="19" t="n">
-        <v>78.09999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="E16" s="19" t="n">
-        <v>14</v>
+        <v>8.5</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>23.5</v>
+        <v>9.6</v>
       </c>
       <c r="G16" s="19" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Overcast</t>
         </is>
       </c>
       <c r="I16" s="14" t="n">
@@ -58010,16 +57986,16 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>99.5</v>
+        <v>100.6</v>
       </c>
       <c r="E17" s="17" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="F17" s="17" t="n">
-        <v>5.4</v>
+        <v>8.1</v>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
@@ -58052,20 +58028,20 @@
         </is>
       </c>
       <c r="D18" s="19" t="n">
-        <v>70.7</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E18" s="19" t="n">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="F18" s="19" t="n">
-        <v>12.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G18" s="19" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>Overcast</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="I18" s="14" t="n">
@@ -58090,20 +58066,20 @@
         </is>
       </c>
       <c r="D19" s="17" t="n">
-        <v>65.09999999999999</v>
+        <v>61.3</v>
       </c>
       <c r="E19" s="17" t="n">
-        <v>3.9</v>
+        <v>11.6</v>
       </c>
       <c r="F19" s="17" t="n">
-        <v>8.5</v>
+        <v>11.4</v>
       </c>
       <c r="G19" s="17" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Overcast</t>
+          <t>Mainly clear</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
@@ -58127,21 +58103,31 @@
           <t>open</t>
         </is>
       </c>
-      <c r="D20" s="19" t="n"/>
-      <c r="E20" s="19" t="n"/>
-      <c r="F20" s="19" t="n"/>
+      <c r="D20" s="19" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="E20" s="19" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="F20" s="19" t="n">
+        <v>19</v>
+      </c>
       <c r="G20" s="19" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mainly clear</t>
         </is>
       </c>
       <c r="I20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="5" t="inlineStr"/>
+        <v>-1.3</v>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>Wind 10 mph (gusts 19) · 96°F</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">

--- a/NFL_Edge_Model.xlsx
+++ b/NFL_Edge_Model.xlsx
@@ -692,7 +692,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Snapshot of the live model, generated 2026-08-30T12:02:30+00:00. Read-only: the model runs in the pipeline, not in this file.</t>
+          <t>Snapshot of the live model, generated 2026-08-30T16:02:16+00:00. Read-only: the model runs in the pipeline, not in this file.</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>2026-08-30T12:02:30+00:00</t>
+          <t>2026-08-30T16:02:16+00:00</t>
         </is>
       </c>
     </row>
@@ -2752,19 +2752,19 @@
         </is>
       </c>
       <c r="E8" s="12" t="n">
-        <v>470</v>
+        <v>490</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.2162</v>
+        <v>0.2143</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>0.1754</v>
+        <v>0.1695</v>
       </c>
       <c r="H8" s="13" t="n">
-        <v>0.0347</v>
+        <v>0.037</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>0.2308888381235092</v>
+        <v>0.2626569442200044</v>
       </c>
       <c r="J8" s="15" t="n">
         <v>0.5</v>
@@ -2834,19 +2834,19 @@
         </is>
       </c>
       <c r="E10" s="12" t="n">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.2851</v>
+        <v>0.283</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>0.25</v>
+        <v>0.2439</v>
       </c>
       <c r="H10" s="13" t="n">
-        <v>0.031</v>
+        <v>0.0336</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>0.1391236234118228</v>
+        <v>0.1590009143552775</v>
       </c>
       <c r="J10" s="15" t="n">
         <v>0.5</v>
@@ -3312,33 +3312,33 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>DEN @ KC</t>
+          <t>GB @ NYJ</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Under 42.5</t>
+          <t>NYJ ML</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>-110</v>
+        <v>195</v>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5455</v>
+        <v>0.3591</v>
       </c>
       <c r="G22" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.339</v>
       </c>
       <c r="H22" s="13" t="n">
-        <v>0.0207</v>
+        <v>0.0193</v>
       </c>
       <c r="I22" s="13" t="n">
-        <v>0.0414763555925613</v>
+        <v>0.05894822625366258</v>
       </c>
       <c r="J22" s="15" t="n">
         <v>0.5</v>
@@ -3353,33 +3353,33 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>GB @ NYJ</t>
+          <t>MIA @ LV</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>NYJ ML</t>
+          <t>Over 40.5</t>
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>195</v>
+        <v>-110</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>0.3591</v>
+        <v>0.543</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>0.339</v>
+        <v>0.5238</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>0.0193</v>
+        <v>0.0185</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>0.05894822625366258</v>
+        <v>0.03671607804771798</v>
       </c>
       <c r="J23" s="10" t="n">
         <v>0.5</v>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>MIA @ LV</t>
+          <t>NO @ BAL</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Over 40.5</t>
+          <t>Under 46.5</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
@@ -3420,7 +3420,7 @@
         <v>0.0185</v>
       </c>
       <c r="I24" s="13" t="n">
-        <v>0.03671607804771798</v>
+        <v>0.03670380090148218</v>
       </c>
       <c r="J24" s="15" t="n">
         <v>0.5</v>
@@ -3435,7 +3435,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>NO @ BAL</t>
+          <t>WSH @ DAL</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Under 46.5</t>
+          <t>Under 51.5</t>
         </is>
       </c>
       <c r="E25" s="7" t="n">
@@ -3461,7 +3461,7 @@
         <v>0.0185</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>0.03670380090148218</v>
+        <v>0.03670597155556737</v>
       </c>
       <c r="J25" s="10" t="n">
         <v>0.5</v>
@@ -3476,33 +3476,33 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>WSH @ DAL</t>
+          <t>LV @ LAC</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Under 51.5</t>
+          <t>LV +8.5</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.543</v>
+        <v>0.5422</v>
       </c>
       <c r="G26" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H26" s="13" t="n">
-        <v>0.0185</v>
+        <v>0.0178</v>
       </c>
       <c r="I26" s="13" t="n">
-        <v>0.03670597155556737</v>
+        <v>0.03519799972870302</v>
       </c>
       <c r="J26" s="15" t="n">
         <v>0.5</v>
@@ -3517,33 +3517,33 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>LV @ LAC</t>
+          <t>SF @ LAR</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>LV +8.5</t>
+          <t>SF ML</t>
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>-110</v>
+        <v>154</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>0.5422</v>
+        <v>0.4115</v>
       </c>
       <c r="G27" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.3937</v>
       </c>
       <c r="H27" s="8" t="n">
-        <v>0.0178</v>
+        <v>0.0172</v>
       </c>
       <c r="I27" s="8" t="n">
-        <v>0.03519799972870302</v>
+        <v>0.04474685390028676</v>
       </c>
       <c r="J27" s="10" t="n">
         <v>0.5</v>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>SF @ LAR</t>
+          <t>PHI @ TEN</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -3568,23 +3568,23 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>SF ML</t>
+          <t>TEN ML</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.4115</v>
+        <v>0.3877</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>0.3937</v>
+        <v>0.3704</v>
       </c>
       <c r="H28" s="13" t="n">
-        <v>0.0172</v>
+        <v>0.0168</v>
       </c>
       <c r="I28" s="13" t="n">
-        <v>0.04474685390028676</v>
+        <v>0.04648874007508352</v>
       </c>
       <c r="J28" s="15" t="n">
         <v>0.5</v>
@@ -3599,33 +3599,33 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>PHI @ TEN</t>
+          <t>NYG @ LAR</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>TEN ML</t>
+          <t>NYG +8.5</t>
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>170</v>
+        <v>-110</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>0.3877</v>
+        <v>0.5406</v>
       </c>
       <c r="G29" s="8" t="n">
-        <v>0.3704</v>
+        <v>0.5238</v>
       </c>
       <c r="H29" s="8" t="n">
-        <v>0.0168</v>
+        <v>0.0163</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>0.04648874007508352</v>
+        <v>0.03204259594583803</v>
       </c>
       <c r="J29" s="10" t="n">
         <v>0.5</v>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>NYG @ LAR</t>
+          <t>PHI @ TEN</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -3650,23 +3650,23 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>NYG +8.5</t>
+          <t>TEN +4.5</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.5406</v>
+        <v>0.5403</v>
       </c>
       <c r="G30" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H30" s="13" t="n">
-        <v>0.0163</v>
+        <v>0.016</v>
       </c>
       <c r="I30" s="13" t="n">
-        <v>0.03204259594583803</v>
+        <v>0.03139671505204372</v>
       </c>
       <c r="J30" s="15" t="n">
         <v>0.5</v>
@@ -3681,33 +3681,33 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>PHI @ TEN</t>
+          <t>NO @ BAL</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>TEN +4.5</t>
+          <t>NO ML</t>
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>-110</v>
+        <v>280</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>0.5403</v>
+        <v>0.2795</v>
       </c>
       <c r="G31" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.2632</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>0.016</v>
+        <v>0.0159</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>0.03139671505204372</v>
+        <v>0.06160995661143953</v>
       </c>
       <c r="J31" s="10" t="n">
         <v>0.5</v>
@@ -3722,33 +3722,33 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>NO @ BAL</t>
+          <t>ATL @ PIT</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>NO ML</t>
+          <t>Over 41.5</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>280</v>
+        <v>-115</v>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.2795</v>
+        <v>0.5493</v>
       </c>
       <c r="G32" s="13" t="n">
-        <v>0.2632</v>
+        <v>0.5349</v>
       </c>
       <c r="H32" s="13" t="n">
-        <v>0.0159</v>
+        <v>0.0141</v>
       </c>
       <c r="I32" s="13" t="n">
-        <v>0.06160995661143953</v>
+        <v>0.02702299932041741</v>
       </c>
       <c r="J32" s="15" t="n">
         <v>0.5</v>
@@ -3763,33 +3763,33 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>ATL @ PIT</t>
+          <t>NO @ DET</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Over 41.5</t>
+          <t>NO +7</t>
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>0.5493</v>
+        <v>0.5382</v>
       </c>
       <c r="G33" s="8" t="n">
-        <v>0.5349</v>
+        <v>0.5238</v>
       </c>
       <c r="H33" s="8" t="n">
         <v>0.0141</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>0.02702299932041741</v>
+        <v>0.02603693637090604</v>
       </c>
       <c r="J33" s="10" t="n">
         <v>0.5</v>
@@ -3804,33 +3804,33 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>NO @ DET</t>
+          <t>MIN @ CHI</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>NO +7</t>
+          <t>MIN ML</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>-110</v>
+        <v>164</v>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.5382</v>
+        <v>0.3932</v>
       </c>
       <c r="G34" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.3788</v>
       </c>
       <c r="H34" s="13" t="n">
-        <v>0.0141</v>
+        <v>0.014</v>
       </c>
       <c r="I34" s="13" t="n">
-        <v>0.02603693637090604</v>
+        <v>0.03758895650875493</v>
       </c>
       <c r="J34" s="15" t="n">
         <v>0.5</v>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>MIN @ CHI</t>
+          <t>NE @ SEA</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -3896,23 +3896,23 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>MIN ML</t>
+          <t>NE ML</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.3928</v>
+        <v>0.4139</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>0.3788</v>
+        <v>0.4</v>
       </c>
       <c r="H36" s="13" t="n">
         <v>0.0137</v>
       </c>
       <c r="I36" s="13" t="n">
-        <v>0.03665546876206616</v>
+        <v>0.03455435468958357</v>
       </c>
       <c r="J36" s="15" t="n">
         <v>0.5</v>
@@ -4378,33 +4378,33 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>BAL @ IND</t>
+          <t>DEN @ KC</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>IND +3.5</t>
+          <t>Under 42.5</t>
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.533</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>0.5283</v>
+        <v>0.5238</v>
       </c>
       <c r="H48" s="13" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0091</v>
       </c>
       <c r="I48" s="13" t="n">
-        <v>0.01600179892448023</v>
+        <v>0.01748285606424699</v>
       </c>
       <c r="J48" s="15" t="n">
         <v>0.5</v>
@@ -4419,33 +4419,33 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>NE @ SEA</t>
+          <t>BAL @ IND</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>NE ML</t>
+          <t>IND +3.5</t>
         </is>
       </c>
       <c r="E49" s="7" t="n">
-        <v>145</v>
+        <v>-112</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>0.4165</v>
+        <v>0.5368000000000001</v>
       </c>
       <c r="G49" s="8" t="n">
-        <v>0.4082</v>
+        <v>0.5283</v>
       </c>
       <c r="H49" s="8" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="I49" s="8" t="n">
-        <v>0.02016139816970663</v>
+        <v>0.01600179892448023</v>
       </c>
       <c r="J49" s="10" t="n">
         <v>0.5</v>
@@ -4477,16 +4477,16 @@
         <v>120</v>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.4628</v>
+        <v>0.463</v>
       </c>
       <c r="G50" s="13" t="n">
         <v>0.4545</v>
       </c>
       <c r="H50" s="13" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="I50" s="13" t="n">
-        <v>0.01798834225121759</v>
+        <v>0.01838627799312309</v>
       </c>
       <c r="J50" s="15" t="n">
         <v>0.5</v>
@@ -4518,16 +4518,16 @@
         <v>-102</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>0.5128</v>
+        <v>0.513</v>
       </c>
       <c r="G51" s="8" t="n">
         <v>0.505</v>
       </c>
       <c r="H51" s="8" t="n">
-        <v>0.0078</v>
+        <v>0.008</v>
       </c>
       <c r="I51" s="8" t="n">
-        <v>0.01556823154421605</v>
+        <v>0.01592414103017281</v>
       </c>
       <c r="J51" s="10" t="n">
         <v>0.5</v>
@@ -4747,33 +4747,33 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>CLE @ TB</t>
+          <t>BUF @ HOU</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>CLE ML</t>
+          <t>Over 44.5</t>
         </is>
       </c>
       <c r="E57" s="7" t="n">
-        <v>200</v>
+        <v>-110</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>0.3369</v>
+        <v>0.5254</v>
       </c>
       <c r="G57" s="8" t="n">
-        <v>0.3333</v>
+        <v>0.5238</v>
       </c>
       <c r="H57" s="8" t="n">
-        <v>0.0035</v>
+        <v>0.0016</v>
       </c>
       <c r="I57" s="8" t="n">
-        <v>0.01047456634726629</v>
+        <v>0.003023751045110934</v>
       </c>
       <c r="J57" s="10" t="n">
         <v>0.5</v>
@@ -4788,33 +4788,33 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>BUF @ HOU</t>
+          <t>CIN @ HOU</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Over 44.5</t>
+          <t>CIN ML</t>
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>-110</v>
+        <v>114</v>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.5254</v>
+        <v>0.4674</v>
       </c>
       <c r="G58" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.4673</v>
       </c>
       <c r="H58" s="13" t="n">
-        <v>0.0016</v>
+        <v>0.0001</v>
       </c>
       <c r="I58" s="13" t="n">
-        <v>0.003023751045110934</v>
+        <v>0.00018904111275031</v>
       </c>
       <c r="J58" s="15" t="n">
         <v>0.5</v>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>CIN @ HOU</t>
+          <t>CLE @ TB</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -4839,23 +4839,23 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>CIN ML</t>
+          <t>CLE ML</t>
         </is>
       </c>
       <c r="E59" s="7" t="n">
-        <v>114</v>
+        <v>195</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>0.4674</v>
+        <v>0.3388</v>
       </c>
       <c r="G59" s="8" t="n">
-        <v>0.4673</v>
+        <v>0.339</v>
       </c>
       <c r="H59" s="8" t="n">
-        <v>0.0001</v>
+        <v>-0.0002</v>
       </c>
       <c r="I59" s="8" t="n">
-        <v>0.00018904111275031</v>
+        <v>-0.000571712906591304</v>
       </c>
       <c r="J59" s="10" t="n">
         <v>0.5</v>
@@ -4928,16 +4928,16 @@
         <v>-110</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>0.5217000000000001</v>
+        <v>0.522</v>
       </c>
       <c r="G61" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H61" s="8" t="n">
-        <v>-0.0022</v>
+        <v>-0.0018</v>
       </c>
       <c r="I61" s="8" t="n">
-        <v>-0.004107965639567612</v>
+        <v>-0.003423344769942216</v>
       </c>
       <c r="J61" s="10" t="n">
         <v>0.5</v>
@@ -5444,33 +5444,33 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>BUF @ HOU</t>
+          <t>CAR @ ATL</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>BUF ML</t>
+          <t>Under 43.5</t>
         </is>
       </c>
       <c r="E74" s="12" t="n">
-        <v>-118</v>
+        <v>-102</v>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.5276</v>
+        <v>0.4914</v>
       </c>
       <c r="G74" s="13" t="n">
-        <v>0.5413</v>
+        <v>0.505</v>
       </c>
       <c r="H74" s="13" t="n">
-        <v>-0.0134</v>
+        <v>-0.0133</v>
       </c>
       <c r="I74" s="13" t="n">
-        <v>-0.02500971522359302</v>
+        <v>-0.0268812324569056</v>
       </c>
       <c r="J74" s="15" t="n">
         <v>0.5</v>
@@ -5485,33 +5485,33 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>JAX @ DEN</t>
+          <t>BUF @ HOU</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>DEN -2.5</t>
+          <t>BUF ML</t>
         </is>
       </c>
       <c r="E75" s="7" t="n">
-        <v>-115</v>
+        <v>-118</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>0.5211</v>
+        <v>0.5276</v>
       </c>
       <c r="G75" s="8" t="n">
-        <v>0.5349</v>
+        <v>0.5413</v>
       </c>
       <c r="H75" s="8" t="n">
-        <v>-0.0135</v>
+        <v>-0.0134</v>
       </c>
       <c r="I75" s="8" t="n">
-        <v>-0.02572923154910695</v>
+        <v>-0.02500971522359302</v>
       </c>
       <c r="J75" s="10" t="n">
         <v>0.5</v>
@@ -5526,33 +5526,33 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>WSH @ PHI</t>
+          <t>DAL @ NYG</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>WSH +4.5</t>
+          <t>Under 48.5</t>
         </is>
       </c>
       <c r="E76" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.5093</v>
+        <v>0.5102</v>
       </c>
       <c r="G76" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H76" s="13" t="n">
-        <v>-0.0142</v>
+        <v>-0.0134</v>
       </c>
       <c r="I76" s="13" t="n">
-        <v>-0.02765523184807078</v>
+        <v>-0.02603853905277531</v>
       </c>
       <c r="J76" s="15" t="n">
         <v>0.5</v>
@@ -5567,33 +5567,33 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>ATL @ PIT</t>
+          <t>JAX @ DEN</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>ATL ML</t>
+          <t>DEN -2.5</t>
         </is>
       </c>
       <c r="E77" s="7" t="n">
-        <v>145</v>
+        <v>-115</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>0.3932</v>
+        <v>0.5211</v>
       </c>
       <c r="G77" s="8" t="n">
-        <v>0.4082</v>
+        <v>0.5349</v>
       </c>
       <c r="H77" s="8" t="n">
-        <v>-0.0146</v>
+        <v>-0.0135</v>
       </c>
       <c r="I77" s="8" t="n">
-        <v>-0.03623808452237598</v>
+        <v>-0.02572923154910695</v>
       </c>
       <c r="J77" s="10" t="n">
         <v>0.5</v>
@@ -5608,7 +5608,7 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>BUF @ HOU</t>
+          <t>WSH @ PHI</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
@@ -5618,23 +5618,23 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>BUF -1.5</t>
+          <t>WSH +4.5</t>
         </is>
       </c>
       <c r="E78" s="12" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.4971</v>
+        <v>0.5093</v>
       </c>
       <c r="G78" s="13" t="n">
-        <v>0.5122</v>
+        <v>0.5238</v>
       </c>
       <c r="H78" s="13" t="n">
-        <v>-0.0147</v>
+        <v>-0.0142</v>
       </c>
       <c r="I78" s="13" t="n">
-        <v>-0.02942318222228196</v>
+        <v>-0.02765523184807078</v>
       </c>
       <c r="J78" s="15" t="n">
         <v>0.5</v>
@@ -5649,7 +5649,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>GB @ MIN</t>
+          <t>BUF @ HOU</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -5659,23 +5659,23 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>GB +1.5</t>
+          <t>BUF -1.5</t>
         </is>
       </c>
       <c r="E79" s="7" t="n">
-        <v>-115</v>
+        <v>-105</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>0.519</v>
+        <v>0.4971</v>
       </c>
       <c r="G79" s="8" t="n">
-        <v>0.5349</v>
+        <v>0.5122</v>
       </c>
       <c r="H79" s="8" t="n">
-        <v>-0.0155</v>
+        <v>-0.0147</v>
       </c>
       <c r="I79" s="8" t="n">
-        <v>-0.0297833252608401</v>
+        <v>-0.02942318222228196</v>
       </c>
       <c r="J79" s="10" t="n">
         <v>0.5</v>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>GB @ MIN</t>
+          <t>CAR @ ATL</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
@@ -5700,23 +5700,23 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>GB ML</t>
+          <t>CAR ML</t>
         </is>
       </c>
       <c r="E80" s="12" t="n">
-        <v>-102</v>
+        <v>105</v>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.4886</v>
+        <v>0.4724</v>
       </c>
       <c r="G80" s="13" t="n">
-        <v>0.505</v>
+        <v>0.4878</v>
       </c>
       <c r="H80" s="13" t="n">
-        <v>-0.0159</v>
+        <v>-0.015</v>
       </c>
       <c r="I80" s="13" t="n">
-        <v>-0.03204689381793407</v>
+        <v>-0.03134330882717018</v>
       </c>
       <c r="J80" s="15" t="n">
         <v>0.5</v>
@@ -5731,33 +5731,33 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>DAL @ NYG</t>
+          <t>GB @ MIN</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>NYG +2.5</t>
+          <t>GB ML</t>
         </is>
       </c>
       <c r="E81" s="7" t="n">
-        <v>-105</v>
+        <v>-102</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>0.4958</v>
+        <v>0.4886</v>
       </c>
       <c r="G81" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.505</v>
       </c>
       <c r="H81" s="8" t="n">
         <v>-0.0159</v>
       </c>
       <c r="I81" s="8" t="n">
-        <v>-0.03195906596080356</v>
+        <v>-0.03204689381793407</v>
       </c>
       <c r="J81" s="10" t="n">
         <v>0.5</v>
@@ -5772,33 +5772,33 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>DET @ BUF</t>
+          <t>DAL @ NYG</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>BUF ML</t>
+          <t>NYG +2.5</t>
         </is>
       </c>
       <c r="E82" s="12" t="n">
-        <v>-155</v>
+        <v>-105</v>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.5914</v>
+        <v>0.4958</v>
       </c>
       <c r="G82" s="13" t="n">
-        <v>0.6078</v>
+        <v>0.5122</v>
       </c>
       <c r="H82" s="13" t="n">
-        <v>-0.016</v>
+        <v>-0.0159</v>
       </c>
       <c r="I82" s="13" t="n">
-        <v>-0.02687447684864447</v>
+        <v>-0.03195906596080356</v>
       </c>
       <c r="J82" s="15" t="n">
         <v>0.5</v>
@@ -5813,7 +5813,7 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>CAR @ ATL</t>
+          <t>DET @ BUF</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -5823,23 +5823,23 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>CAR ML</t>
+          <t>BUF ML</t>
         </is>
       </c>
       <c r="E83" s="7" t="n">
-        <v>105</v>
+        <v>-155</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>0.4706</v>
+        <v>0.5914</v>
       </c>
       <c r="G83" s="8" t="n">
-        <v>0.4878</v>
+        <v>0.6078</v>
       </c>
       <c r="H83" s="8" t="n">
-        <v>-0.0167</v>
+        <v>-0.016</v>
       </c>
       <c r="I83" s="8" t="n">
-        <v>-0.03504968895990251</v>
+        <v>-0.02687447684864447</v>
       </c>
       <c r="J83" s="10" t="n">
         <v>0.5</v>
@@ -5854,33 +5854,33 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>TB @ CIN</t>
+          <t>ATL @ PIT</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>TB +3.5</t>
+          <t>ATL ML</t>
         </is>
       </c>
       <c r="E84" s="12" t="n">
-        <v>-105</v>
+        <v>145</v>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.4943</v>
+        <v>0.3915</v>
       </c>
       <c r="G84" s="13" t="n">
-        <v>0.5122</v>
+        <v>0.4082</v>
       </c>
       <c r="H84" s="13" t="n">
-        <v>-0.0173</v>
+        <v>-0.0162</v>
       </c>
       <c r="I84" s="13" t="n">
-        <v>-0.03496690833587163</v>
+        <v>-0.04053010815715519</v>
       </c>
       <c r="J84" s="15" t="n">
         <v>0.5</v>
@@ -5895,33 +5895,33 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>BAL @ IND</t>
+          <t>TB @ CIN</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Under 48.5</t>
+          <t>TB +3.5</t>
         </is>
       </c>
       <c r="E85" s="7" t="n">
-        <v>-115</v>
+        <v>-105</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>0.5165</v>
+        <v>0.4943</v>
       </c>
       <c r="G85" s="8" t="n">
-        <v>0.5349</v>
+        <v>0.5122</v>
       </c>
       <c r="H85" s="8" t="n">
-        <v>-0.0177</v>
+        <v>-0.0173</v>
       </c>
       <c r="I85" s="8" t="n">
-        <v>-0.03436382238512642</v>
+        <v>-0.03496690833587163</v>
       </c>
       <c r="J85" s="10" t="n">
         <v>0.5</v>
@@ -5936,33 +5936,33 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>DET @ BUF</t>
+          <t>BAL @ IND</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>BUF -3</t>
+          <t>Under 48.5</t>
         </is>
       </c>
       <c r="E86" s="12" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.5052</v>
+        <v>0.5165</v>
       </c>
       <c r="G86" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5349</v>
       </c>
       <c r="H86" s="13" t="n">
-        <v>-0.0179</v>
+        <v>-0.0177</v>
       </c>
       <c r="I86" s="13" t="n">
-        <v>-0.03291897912759417</v>
+        <v>-0.03436382238512642</v>
       </c>
       <c r="J86" s="15" t="n">
         <v>0.5</v>
@@ -5977,33 +5977,33 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>NYG @ LAR</t>
+          <t>DET @ BUF</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>BUF -3</t>
         </is>
       </c>
       <c r="E87" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>0.5051</v>
+        <v>0.5052</v>
       </c>
       <c r="G87" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H87" s="8" t="n">
-        <v>-0.018</v>
+        <v>-0.0179</v>
       </c>
       <c r="I87" s="8" t="n">
-        <v>-0.0357439529371551</v>
+        <v>-0.03291897912759417</v>
       </c>
       <c r="J87" s="10" t="n">
         <v>0.5</v>
@@ -6018,33 +6018,33 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>NYJ @ TEN</t>
+          <t>NYG @ LAR</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>TEN ML</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="E88" s="12" t="n">
-        <v>-148</v>
+        <v>-110</v>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.5777</v>
+        <v>0.5051</v>
       </c>
       <c r="G88" s="13" t="n">
-        <v>0.5968</v>
+        <v>0.5238</v>
       </c>
       <c r="H88" s="13" t="n">
-        <v>-0.0183</v>
+        <v>-0.018</v>
       </c>
       <c r="I88" s="13" t="n">
-        <v>-0.03165883941683079</v>
+        <v>-0.0357439529371551</v>
       </c>
       <c r="J88" s="15" t="n">
         <v>0.5</v>
@@ -6059,33 +6059,33 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>ATL @ PIT</t>
+          <t>NYJ @ TEN</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>ATL +3</t>
+          <t>TEN ML</t>
         </is>
       </c>
       <c r="E89" s="7" t="n">
-        <v>100</v>
+        <v>-148</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>0.4804</v>
+        <v>0.5777</v>
       </c>
       <c r="G89" s="8" t="n">
-        <v>0.5</v>
+        <v>0.5968</v>
       </c>
       <c r="H89" s="8" t="n">
-        <v>-0.0188</v>
+        <v>-0.0183</v>
       </c>
       <c r="I89" s="8" t="n">
-        <v>-0.03638566872259713</v>
+        <v>-0.03165883941683079</v>
       </c>
       <c r="J89" s="10" t="n">
         <v>0.5</v>
@@ -6100,33 +6100,33 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>WSH @ DAL</t>
+          <t>CAR @ ATL</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>DAL ML</t>
+          <t>CAR +1.5</t>
         </is>
       </c>
       <c r="E90" s="12" t="n">
-        <v>-198</v>
+        <v>-110</v>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.6448</v>
+        <v>0.5043</v>
       </c>
       <c r="G90" s="13" t="n">
-        <v>0.6644</v>
+        <v>0.5238</v>
       </c>
       <c r="H90" s="13" t="n">
-        <v>-0.0188</v>
+        <v>-0.0187</v>
       </c>
       <c r="I90" s="13" t="n">
-        <v>-0.02929582789724111</v>
+        <v>-0.03719694996903322</v>
       </c>
       <c r="J90" s="15" t="n">
         <v>0.5</v>
@@ -6146,28 +6146,28 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>DAL -4.5</t>
+          <t>DAL ML</t>
         </is>
       </c>
       <c r="E91" s="7" t="n">
-        <v>-105</v>
+        <v>-198</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>0.4923</v>
+        <v>0.6448</v>
       </c>
       <c r="G91" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.6644</v>
       </c>
       <c r="H91" s="8" t="n">
-        <v>-0.0191</v>
+        <v>-0.0188</v>
       </c>
       <c r="I91" s="8" t="n">
-        <v>-0.03880269598770819</v>
+        <v>-0.02929582789724111</v>
       </c>
       <c r="J91" s="10" t="n">
         <v>0.5</v>
@@ -6182,33 +6182,33 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>DAL @ NYG</t>
+          <t>WSH @ DAL</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>DAL -4.5</t>
         </is>
       </c>
       <c r="E92" s="12" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.4923</v>
       </c>
       <c r="G92" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5122</v>
       </c>
       <c r="H92" s="13" t="n">
-        <v>-0.0203</v>
+        <v>-0.0191</v>
       </c>
       <c r="I92" s="13" t="n">
-        <v>-0.04059877700986925</v>
+        <v>-0.03880269598770819</v>
       </c>
       <c r="J92" s="15" t="n">
         <v>0.5</v>
@@ -6223,7 +6223,7 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>CAR @ ATL</t>
+          <t>GB @ MIN</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -6233,23 +6233,23 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>CAR +1.5</t>
+          <t>GB +1.5</t>
         </is>
       </c>
       <c r="E93" s="7" t="n">
-        <v>-110</v>
+        <v>-118</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.5212</v>
       </c>
       <c r="G93" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5413</v>
       </c>
       <c r="H93" s="8" t="n">
-        <v>-0.0203</v>
+        <v>-0.0192</v>
       </c>
       <c r="I93" s="8" t="n">
-        <v>-0.04064752235243363</v>
+        <v>-0.0370338349032584</v>
       </c>
       <c r="J93" s="10" t="n">
         <v>0.5</v>
@@ -6387,7 +6387,7 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>DEN @ KC</t>
+          <t>ATL @ PIT</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -6397,23 +6397,23 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>KC -3</t>
+          <t>ATL +3</t>
         </is>
       </c>
       <c r="E97" s="7" t="n">
-        <v>-105</v>
+        <v>100</v>
       </c>
       <c r="F97" s="8" t="n">
-        <v>0.49</v>
+        <v>0.4785</v>
       </c>
       <c r="G97" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.5</v>
       </c>
       <c r="H97" s="8" t="n">
-        <v>-0.021</v>
+        <v>-0.0205</v>
       </c>
       <c r="I97" s="8" t="n">
-        <v>-0.04017506121040948</v>
+        <v>-0.03997684987151184</v>
       </c>
       <c r="J97" s="10" t="n">
         <v>0.5</v>
@@ -6428,33 +6428,33 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>CAR @ ATL</t>
+          <t>DEN @ KC</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>Under 44.5</t>
+          <t>KC -3</t>
         </is>
       </c>
       <c r="E98" s="12" t="n">
-        <v>-118</v>
+        <v>-105</v>
       </c>
       <c r="F98" s="13" t="n">
-        <v>0.5188</v>
+        <v>0.49</v>
       </c>
       <c r="G98" s="13" t="n">
-        <v>0.5413</v>
+        <v>0.5122</v>
       </c>
       <c r="H98" s="13" t="n">
-        <v>-0.0213</v>
+        <v>-0.021</v>
       </c>
       <c r="I98" s="13" t="n">
-        <v>-0.04156327600671267</v>
+        <v>-0.04017506121040948</v>
       </c>
       <c r="J98" s="15" t="n">
         <v>0.5</v>
@@ -6510,7 +6510,7 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>CAR @ ATL</t>
+          <t>PIT @ NE</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
@@ -6520,23 +6520,23 @@
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>Over 44.5</t>
+          <t>Over 43.5</t>
         </is>
       </c>
       <c r="E100" s="12" t="n">
-        <v>-102</v>
+        <v>-110</v>
       </c>
       <c r="F100" s="13" t="n">
-        <v>0.4812</v>
+        <v>0.5</v>
       </c>
       <c r="G100" s="13" t="n">
-        <v>0.505</v>
+        <v>0.5238</v>
       </c>
       <c r="H100" s="13" t="n">
         <v>-0.0224</v>
       </c>
       <c r="I100" s="13" t="n">
-        <v>-0.04700925315272514</v>
+        <v>-0.04544960421788274</v>
       </c>
       <c r="J100" s="15" t="n">
         <v>0.5</v>
@@ -6561,7 +6561,7 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Over 43.5</t>
+          <t>Under 43.5</t>
         </is>
       </c>
       <c r="E101" s="7" t="n">
@@ -6577,7 +6577,7 @@
         <v>-0.0224</v>
       </c>
       <c r="I101" s="8" t="n">
-        <v>-0.04544960421788274</v>
+        <v>-0.04545948669120808</v>
       </c>
       <c r="J101" s="10" t="n">
         <v>0.5</v>
@@ -6592,33 +6592,33 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>PIT @ NE</t>
+          <t>ATL @ PIT</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>Under 43.5</t>
+          <t>PIT -3</t>
         </is>
       </c>
       <c r="E102" s="12" t="n">
-        <v>-110</v>
+        <v>-120</v>
       </c>
       <c r="F102" s="13" t="n">
-        <v>0.5</v>
+        <v>0.5215</v>
       </c>
       <c r="G102" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5455</v>
       </c>
       <c r="H102" s="13" t="n">
-        <v>-0.0224</v>
+        <v>-0.0225</v>
       </c>
       <c r="I102" s="13" t="n">
-        <v>-0.04545948669120808</v>
+        <v>-0.04067635893968785</v>
       </c>
       <c r="J102" s="15" t="n">
         <v>0.5</v>
@@ -6756,33 +6756,33 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>ATL @ PIT</t>
+          <t>DET @ BUF</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>PIT -3</t>
+          <t>DET ML</t>
         </is>
       </c>
       <c r="E106" s="12" t="n">
-        <v>-120</v>
+        <v>130</v>
       </c>
       <c r="F106" s="13" t="n">
-        <v>0.5196</v>
+        <v>0.4086</v>
       </c>
       <c r="G106" s="13" t="n">
-        <v>0.5455</v>
+        <v>0.4348</v>
       </c>
       <c r="H106" s="13" t="n">
-        <v>-0.0241</v>
+        <v>-0.0243</v>
       </c>
       <c r="I106" s="13" t="n">
-        <v>-0.04396716143770635</v>
+        <v>-0.0596122601785285</v>
       </c>
       <c r="J106" s="15" t="n">
         <v>0.5</v>
@@ -6797,33 +6797,33 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>DET @ BUF</t>
+          <t>GB @ MIN</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>DET ML</t>
+          <t>MIN -1.5</t>
         </is>
       </c>
       <c r="E107" s="7" t="n">
-        <v>130</v>
+        <v>-102</v>
       </c>
       <c r="F107" s="8" t="n">
-        <v>0.4086</v>
+        <v>0.4788</v>
       </c>
       <c r="G107" s="8" t="n">
-        <v>0.4348</v>
+        <v>0.505</v>
       </c>
       <c r="H107" s="8" t="n">
-        <v>-0.0243</v>
+        <v>-0.0244</v>
       </c>
       <c r="I107" s="8" t="n">
-        <v>-0.0596122601785285</v>
+        <v>-0.05186461194666003</v>
       </c>
       <c r="J107" s="10" t="n">
         <v>0.5</v>
@@ -6838,33 +6838,33 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>CAR @ ATL</t>
+          <t>CIN @ HOU</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>ATL ML</t>
+          <t>Under 46.5</t>
         </is>
       </c>
       <c r="E108" s="12" t="n">
-        <v>-125</v>
+        <v>-110</v>
       </c>
       <c r="F108" s="13" t="n">
-        <v>0.5294</v>
+        <v>0.4975</v>
       </c>
       <c r="G108" s="13" t="n">
-        <v>0.5556</v>
+        <v>0.5238</v>
       </c>
       <c r="H108" s="13" t="n">
-        <v>-0.0243</v>
+        <v>-0.0245</v>
       </c>
       <c r="I108" s="13" t="n">
-        <v>-0.04657391447871934</v>
+        <v>-0.05031105788036128</v>
       </c>
       <c r="J108" s="15" t="n">
         <v>0.5</v>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>DAL @ NYG</t>
+          <t>CLE @ TB</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Under 48.5</t>
+          <t>Under 42.5</t>
         </is>
       </c>
       <c r="E109" s="7" t="n">
@@ -6905,7 +6905,7 @@
         <v>-0.0245</v>
       </c>
       <c r="I109" s="8" t="n">
-        <v>-0.05031031389922158</v>
+        <v>-0.05031725382596147</v>
       </c>
       <c r="J109" s="10" t="n">
         <v>0.5</v>
@@ -6920,17 +6920,17 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>CAR @ ATL</t>
+          <t>MIA @ SF</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>ATL -1.5</t>
+          <t>Over 46.5</t>
         </is>
       </c>
       <c r="E110" s="12" t="n">
@@ -6946,7 +6946,7 @@
         <v>-0.0245</v>
       </c>
       <c r="I110" s="13" t="n">
-        <v>-0.0502615685566572</v>
+        <v>-0.05030855398815443</v>
       </c>
       <c r="J110" s="15" t="n">
         <v>0.5</v>
@@ -6961,33 +6961,33 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>CIN @ HOU</t>
+          <t>WSH @ DAL</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Under 46.5</t>
+          <t>WSH +4.5</t>
         </is>
       </c>
       <c r="E111" s="7" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="F111" s="8" t="n">
-        <v>0.4975</v>
+        <v>0.5077</v>
       </c>
       <c r="G111" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5349</v>
       </c>
       <c r="H111" s="8" t="n">
-        <v>-0.0245</v>
+        <v>-0.0252</v>
       </c>
       <c r="I111" s="8" t="n">
-        <v>-0.05031105788036128</v>
+        <v>-0.05086019673711512</v>
       </c>
       <c r="J111" s="10" t="n">
         <v>0.5</v>
@@ -7002,33 +7002,33 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>CLE @ TB</t>
+          <t>ATL @ PIT</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>Under 42.5</t>
+          <t>PIT ML</t>
         </is>
       </c>
       <c r="E112" s="12" t="n">
-        <v>-110</v>
+        <v>-175</v>
       </c>
       <c r="F112" s="13" t="n">
-        <v>0.4975</v>
+        <v>0.6085</v>
       </c>
       <c r="G112" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.6364</v>
       </c>
       <c r="H112" s="13" t="n">
-        <v>-0.0245</v>
+        <v>-0.0257</v>
       </c>
       <c r="I112" s="13" t="n">
-        <v>-0.05031725382596147</v>
+        <v>-0.04336934675698939</v>
       </c>
       <c r="J112" s="15" t="n">
         <v>0.5</v>
@@ -7043,33 +7043,33 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>MIA @ SF</t>
+          <t>CAR @ ATL</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Over 46.5</t>
+          <t>ATL ML</t>
         </is>
       </c>
       <c r="E113" s="7" t="n">
-        <v>-110</v>
+        <v>-125</v>
       </c>
       <c r="F113" s="8" t="n">
-        <v>0.4975</v>
+        <v>0.5276</v>
       </c>
       <c r="G113" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5556</v>
       </c>
       <c r="H113" s="8" t="n">
-        <v>-0.0245</v>
+        <v>-0.0258</v>
       </c>
       <c r="I113" s="8" t="n">
-        <v>-0.05030855398815443</v>
+        <v>-0.04982797157483926</v>
       </c>
       <c r="J113" s="10" t="n">
         <v>0.5</v>
@@ -7084,7 +7084,7 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>WSH @ DAL</t>
+          <t>CAR @ ATL</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
@@ -7094,23 +7094,23 @@
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>WSH +4.5</t>
+          <t>ATL -1.5</t>
         </is>
       </c>
       <c r="E114" s="12" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="F114" s="13" t="n">
-        <v>0.5077</v>
+        <v>0.4957</v>
       </c>
       <c r="G114" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.5238</v>
       </c>
       <c r="H114" s="13" t="n">
-        <v>-0.0252</v>
+        <v>-0.0259</v>
       </c>
       <c r="I114" s="13" t="n">
-        <v>-0.05086019673711512</v>
+        <v>-0.05371214094005761</v>
       </c>
       <c r="J114" s="15" t="n">
         <v>0.5</v>
@@ -7371,7 +7371,7 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>ATL @ PIT</t>
+          <t>GB @ MIN</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
@@ -7381,23 +7381,23 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>PIT ML</t>
+          <t>MIN ML</t>
         </is>
       </c>
       <c r="E121" s="7" t="n">
-        <v>-175</v>
+        <v>-118</v>
       </c>
       <c r="F121" s="8" t="n">
-        <v>0.6068</v>
+        <v>0.5114</v>
       </c>
       <c r="G121" s="8" t="n">
-        <v>0.6364</v>
+        <v>0.5413</v>
       </c>
       <c r="H121" s="8" t="n">
-        <v>-0.027</v>
+        <v>-0.0273</v>
       </c>
       <c r="I121" s="8" t="n">
-        <v>-0.04612109241313134</v>
+        <v>-0.05475401394857082</v>
       </c>
       <c r="J121" s="10" t="n">
         <v>0.5</v>
@@ -7412,33 +7412,33 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>GB @ MIN</t>
+          <t>DAL @ NYG</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>MIN ML</t>
+          <t>DAL -2.5</t>
         </is>
       </c>
       <c r="E122" s="12" t="n">
-        <v>-118</v>
+        <v>-115</v>
       </c>
       <c r="F122" s="13" t="n">
-        <v>0.5114</v>
+        <v>0.5042</v>
       </c>
       <c r="G122" s="13" t="n">
-        <v>0.5413</v>
+        <v>0.5349</v>
       </c>
       <c r="H122" s="13" t="n">
-        <v>-0.0273</v>
+        <v>-0.0279</v>
       </c>
       <c r="I122" s="13" t="n">
-        <v>-0.05475401394857082</v>
+        <v>-0.05741353492830803</v>
       </c>
       <c r="J122" s="15" t="n">
         <v>0.5</v>
@@ -7453,7 +7453,7 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>DAL @ NYG</t>
+          <t>BUF @ HOU</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
@@ -7463,23 +7463,23 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>DAL -2.5</t>
+          <t>HOU +1.5</t>
         </is>
       </c>
       <c r="E123" s="7" t="n">
         <v>-115</v>
       </c>
       <c r="F123" s="8" t="n">
-        <v>0.5042</v>
+        <v>0.5029</v>
       </c>
       <c r="G123" s="8" t="n">
         <v>0.5349</v>
       </c>
       <c r="H123" s="8" t="n">
-        <v>-0.0279</v>
+        <v>-0.0288</v>
       </c>
       <c r="I123" s="8" t="n">
-        <v>-0.05741353492830803</v>
+        <v>-0.05984185201832393</v>
       </c>
       <c r="J123" s="10" t="n">
         <v>0.5</v>
@@ -7494,7 +7494,7 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>GB @ MIN</t>
+          <t>NYJ @ TEN</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
@@ -7504,23 +7504,23 @@
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>MIN -1.5</t>
+          <t>NYJ +3</t>
         </is>
       </c>
       <c r="E124" s="12" t="n">
-        <v>-105</v>
+        <v>-120</v>
       </c>
       <c r="F124" s="13" t="n">
-        <v>0.481</v>
+        <v>0.513</v>
       </c>
       <c r="G124" s="13" t="n">
-        <v>0.5122</v>
+        <v>0.5455</v>
       </c>
       <c r="H124" s="13" t="n">
-        <v>-0.0282</v>
+        <v>-0.0291</v>
       </c>
       <c r="I124" s="13" t="n">
-        <v>-0.06081320518164768</v>
+        <v>-0.05516746946063461</v>
       </c>
       <c r="J124" s="15" t="n">
         <v>0.5</v>
@@ -7540,28 +7540,28 @@
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>HOU +1.5</t>
+          <t>HOU ML</t>
         </is>
       </c>
       <c r="E125" s="7" t="n">
-        <v>-115</v>
+        <v>-102</v>
       </c>
       <c r="F125" s="8" t="n">
-        <v>0.5029</v>
+        <v>0.4724</v>
       </c>
       <c r="G125" s="8" t="n">
-        <v>0.5349</v>
+        <v>0.505</v>
       </c>
       <c r="H125" s="8" t="n">
-        <v>-0.0288</v>
+        <v>-0.0292</v>
       </c>
       <c r="I125" s="8" t="n">
-        <v>-0.05984185201832393</v>
+        <v>-0.06393411301888563</v>
       </c>
       <c r="J125" s="10" t="n">
         <v>0.5</v>
@@ -7576,33 +7576,33 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>NYJ @ TEN</t>
+          <t>CAR @ ATL</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>NYJ +3</t>
+          <t>Over 43.5</t>
         </is>
       </c>
       <c r="E126" s="12" t="n">
-        <v>-120</v>
+        <v>-118</v>
       </c>
       <c r="F126" s="13" t="n">
-        <v>0.513</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="G126" s="13" t="n">
-        <v>0.5455</v>
+        <v>0.5413</v>
       </c>
       <c r="H126" s="13" t="n">
-        <v>-0.0291</v>
+        <v>-0.0293</v>
       </c>
       <c r="I126" s="13" t="n">
-        <v>-0.05516746946063461</v>
+        <v>-0.06034019613560354</v>
       </c>
       <c r="J126" s="15" t="n">
         <v>0.5</v>
@@ -7617,33 +7617,33 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>BUF @ HOU</t>
+          <t>WSH @ PHI</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>HOU ML</t>
+          <t>PHI -4.5</t>
         </is>
       </c>
       <c r="E127" s="7" t="n">
-        <v>-102</v>
+        <v>-110</v>
       </c>
       <c r="F127" s="8" t="n">
-        <v>0.4724</v>
+        <v>0.4907</v>
       </c>
       <c r="G127" s="8" t="n">
-        <v>0.505</v>
+        <v>0.5238</v>
       </c>
       <c r="H127" s="8" t="n">
-        <v>-0.0292</v>
+        <v>-0.0296</v>
       </c>
       <c r="I127" s="8" t="n">
-        <v>-0.06393411301888563</v>
+        <v>-0.06325385906102005</v>
       </c>
       <c r="J127" s="10" t="n">
         <v>0.5</v>
@@ -7658,7 +7658,7 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>WSH @ PHI</t>
+          <t>JAX @ DEN</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
@@ -7668,23 +7668,23 @@
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>PHI -4.5</t>
+          <t>JAX +2.5</t>
         </is>
       </c>
       <c r="E128" s="12" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="F128" s="13" t="n">
-        <v>0.4907</v>
+        <v>0.4789</v>
       </c>
       <c r="G128" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5122</v>
       </c>
       <c r="H128" s="13" t="n">
-        <v>-0.0296</v>
+        <v>-0.0298</v>
       </c>
       <c r="I128" s="13" t="n">
-        <v>-0.06325385906102005</v>
+        <v>-0.06504688222501909</v>
       </c>
       <c r="J128" s="15" t="n">
         <v>0.5</v>
@@ -7699,33 +7699,33 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>JAX @ DEN</t>
+          <t>DAL @ NYG</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>JAX +2.5</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="E129" s="7" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="F129" s="8" t="n">
-        <v>0.4789</v>
+        <v>0.4898</v>
       </c>
       <c r="G129" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.5238</v>
       </c>
       <c r="H129" s="8" t="n">
-        <v>-0.0298</v>
+        <v>-0.0302</v>
       </c>
       <c r="I129" s="8" t="n">
-        <v>-0.06504688222501909</v>
+        <v>-0.06487055185631552</v>
       </c>
       <c r="J129" s="10" t="n">
         <v>0.5</v>
@@ -8109,33 +8109,33 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>CIN @ HOU</t>
+          <t>CLE @ TB</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>HOU -2.5</t>
+          <t>TB ML</t>
         </is>
       </c>
       <c r="E139" s="7" t="n">
-        <v>-110</v>
+        <v>-238</v>
       </c>
       <c r="F139" s="8" t="n">
-        <v>0.4808</v>
+        <v>0.6612</v>
       </c>
       <c r="G139" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="H139" s="8" t="n">
-        <v>-0.036</v>
+        <v>-0.0359</v>
       </c>
       <c r="I139" s="8" t="n">
-        <v>-0.08220177449715427</v>
+        <v>-0.06046058463111287</v>
       </c>
       <c r="J139" s="10" t="n">
         <v>0.5</v>
@@ -8150,7 +8150,7 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>PIT @ NE</t>
+          <t>CIN @ HOU</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
@@ -8160,14 +8160,14 @@
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>NE -4.5</t>
+          <t>HOU -2.5</t>
         </is>
       </c>
       <c r="E140" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F140" s="13" t="n">
-        <v>0.4807</v>
+        <v>0.4808</v>
       </c>
       <c r="G140" s="13" t="n">
         <v>0.5238</v>
@@ -8176,7 +8176,7 @@
         <v>-0.036</v>
       </c>
       <c r="I140" s="13" t="n">
-        <v>-0.08223353370621594</v>
+        <v>-0.08220177449715427</v>
       </c>
       <c r="J140" s="15" t="n">
         <v>0.5</v>
@@ -8191,7 +8191,7 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>MIN @ CHI</t>
+          <t>PIT @ NE</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
@@ -8201,23 +8201,23 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>CHI -3.5</t>
+          <t>NE -4.5</t>
         </is>
       </c>
       <c r="E141" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F141" s="8" t="n">
-        <v>0.4783</v>
+        <v>0.4807</v>
       </c>
       <c r="G141" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H141" s="8" t="n">
-        <v>-0.0373</v>
+        <v>-0.036</v>
       </c>
       <c r="I141" s="8" t="n">
-        <v>-0.08680112526952322</v>
+        <v>-0.08223353370621594</v>
       </c>
       <c r="J141" s="10" t="n">
         <v>0.5</v>
@@ -8232,33 +8232,33 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>NE @ SEA</t>
+          <t>MIN @ CHI</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>Over 44.5</t>
+          <t>CHI -3.5</t>
         </is>
       </c>
       <c r="E142" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F142" s="13" t="n">
-        <v>0.4771</v>
+        <v>0.478</v>
       </c>
       <c r="G142" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H142" s="13" t="n">
-        <v>-0.038</v>
+        <v>-0.0375</v>
       </c>
       <c r="I142" s="13" t="n">
-        <v>-0.08909195811116855</v>
+        <v>-0.08748574613914867</v>
       </c>
       <c r="J142" s="15" t="n">
         <v>0.5</v>
@@ -8273,33 +8273,33 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>CLE @ TB</t>
+          <t>NE @ SEA</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>TB ML</t>
+          <t>Over 44.5</t>
         </is>
       </c>
       <c r="E143" s="7" t="n">
-        <v>-245</v>
+        <v>-110</v>
       </c>
       <c r="F143" s="8" t="n">
-        <v>0.6631</v>
+        <v>0.4771</v>
       </c>
       <c r="G143" s="8" t="n">
-        <v>0.7101</v>
+        <v>0.5238</v>
       </c>
       <c r="H143" s="8" t="n">
-        <v>-0.0381</v>
+        <v>-0.038</v>
       </c>
       <c r="I143" s="8" t="n">
-        <v>-0.0656322697737271</v>
+        <v>-0.08909195811116855</v>
       </c>
       <c r="J143" s="10" t="n">
         <v>0.5</v>
@@ -8458,16 +8458,16 @@
         <v>-142</v>
       </c>
       <c r="F147" s="8" t="n">
-        <v>0.5372</v>
+        <v>0.537</v>
       </c>
       <c r="G147" s="8" t="n">
         <v>0.5868</v>
       </c>
       <c r="H147" s="8" t="n">
-        <v>-0.0394</v>
+        <v>-0.0395</v>
       </c>
       <c r="I147" s="8" t="n">
-        <v>-0.08372550837688442</v>
+        <v>-0.08403374298532729</v>
       </c>
       <c r="J147" s="10" t="n">
         <v>0.5</v>
@@ -8605,33 +8605,33 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>NE @ SEA</t>
+          <t>CHI @ CAR</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>SEA ML</t>
+          <t>CHI -2.5</t>
         </is>
       </c>
       <c r="E151" s="7" t="n">
-        <v>-175</v>
+        <v>-118</v>
       </c>
       <c r="F151" s="8" t="n">
-        <v>0.5835</v>
+        <v>0.487</v>
       </c>
       <c r="G151" s="8" t="n">
-        <v>0.6364</v>
+        <v>0.5413</v>
       </c>
       <c r="H151" s="8" t="n">
-        <v>-0.0409</v>
+        <v>-0.0416</v>
       </c>
       <c r="I151" s="8" t="n">
-        <v>-0.08228327848316069</v>
+        <v>-0.1002722436628177</v>
       </c>
       <c r="J151" s="10" t="n">
         <v>0.5</v>
@@ -8646,38 +8646,42 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>CHI @ CAR</t>
+          <t>LV @ LAC</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>CHI -2.5</t>
+          <t>LAC ML</t>
         </is>
       </c>
       <c r="E152" s="12" t="n">
-        <v>-118</v>
+        <v>-375</v>
       </c>
       <c r="F152" s="13" t="n">
-        <v>0.4872</v>
+        <v>0.7348</v>
       </c>
       <c r="G152" s="13" t="n">
-        <v>0.5413</v>
+        <v>0.7895</v>
       </c>
       <c r="H152" s="13" t="n">
-        <v>-0.0415</v>
+        <v>-0.0417</v>
       </c>
       <c r="I152" s="13" t="n">
-        <v>-0.09994022472802433</v>
+        <v>-0.06870592645055049</v>
       </c>
       <c r="J152" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="K152" s="5" t="inlineStr"/>
+      <c r="K152" s="5" t="inlineStr">
+        <is>
+          <t>price -375 outside the allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
@@ -8687,7 +8691,7 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>LV @ LAC</t>
+          <t>NYG @ LAR</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
@@ -8697,30 +8701,30 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>LAC ML</t>
+          <t>LAR ML</t>
         </is>
       </c>
       <c r="E153" s="7" t="n">
-        <v>-375</v>
+        <v>-380</v>
       </c>
       <c r="F153" s="8" t="n">
-        <v>0.7348</v>
+        <v>0.7372</v>
       </c>
       <c r="G153" s="8" t="n">
-        <v>0.7895</v>
+        <v>0.7917</v>
       </c>
       <c r="H153" s="8" t="n">
         <v>-0.0417</v>
       </c>
       <c r="I153" s="8" t="n">
-        <v>-0.06870592645055049</v>
+        <v>-0.06828284274607094</v>
       </c>
       <c r="J153" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>price -375 outside the allowed range</t>
+          <t>price -380 outside the allowed range</t>
         </is>
       </c>
     </row>
@@ -8732,42 +8736,38 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>NYG @ LAR</t>
+          <t>BAL @ IND</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>LAR ML</t>
+          <t>BAL -3.5</t>
         </is>
       </c>
       <c r="E154" s="12" t="n">
-        <v>-380</v>
+        <v>-108</v>
       </c>
       <c r="F154" s="13" t="n">
-        <v>0.7372</v>
+        <v>0.4632</v>
       </c>
       <c r="G154" s="13" t="n">
-        <v>0.7917</v>
+        <v>0.5192</v>
       </c>
       <c r="H154" s="13" t="n">
-        <v>-0.0417</v>
+        <v>-0.0423</v>
       </c>
       <c r="I154" s="13" t="n">
-        <v>-0.06828284274607094</v>
+        <v>-0.1078257297233006</v>
       </c>
       <c r="J154" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="K154" s="5" t="inlineStr">
-        <is>
-          <t>price -380 outside the allowed range</t>
-        </is>
-      </c>
+      <c r="K154" s="5" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
@@ -8782,28 +8782,28 @@
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>BAL -3.5</t>
+          <t>BAL ML</t>
         </is>
       </c>
       <c r="E155" s="7" t="n">
-        <v>-108</v>
+        <v>-180</v>
       </c>
       <c r="F155" s="8" t="n">
-        <v>0.4632</v>
+        <v>0.5864</v>
       </c>
       <c r="G155" s="8" t="n">
-        <v>0.5192</v>
+        <v>0.6429</v>
       </c>
       <c r="H155" s="8" t="n">
-        <v>-0.0423</v>
+        <v>-0.0425</v>
       </c>
       <c r="I155" s="8" t="n">
-        <v>-0.1078257297233006</v>
+        <v>-0.08702187948637286</v>
       </c>
       <c r="J155" s="10" t="n">
         <v>0.5</v>
@@ -8818,7 +8818,7 @@
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>BAL @ IND</t>
+          <t>NE @ SEA</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
@@ -8828,23 +8828,23 @@
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>BAL ML</t>
+          <t>SEA ML</t>
         </is>
       </c>
       <c r="E156" s="12" t="n">
         <v>-180</v>
       </c>
       <c r="F156" s="13" t="n">
-        <v>0.5864</v>
+        <v>0.5861</v>
       </c>
       <c r="G156" s="13" t="n">
         <v>0.6429</v>
       </c>
       <c r="H156" s="13" t="n">
-        <v>-0.0425</v>
+        <v>-0.0426</v>
       </c>
       <c r="I156" s="13" t="n">
-        <v>-0.08702187948637286</v>
+        <v>-0.08757731214682052</v>
       </c>
       <c r="J156" s="15" t="n">
         <v>0.5</v>
@@ -8900,33 +8900,33 @@
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>ARI @ LAC</t>
+          <t>DEN @ KC</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>LAC -10.5</t>
+          <t>Over 42.5</t>
         </is>
       </c>
       <c r="E158" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F158" s="13" t="n">
-        <v>0.4665</v>
+        <v>0.467</v>
       </c>
       <c r="G158" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H158" s="13" t="n">
-        <v>-0.0428</v>
+        <v>-0.0426</v>
       </c>
       <c r="I158" s="13" t="n">
-        <v>-0.1094436399964945</v>
+        <v>-0.1083919469733378</v>
       </c>
       <c r="J158" s="15" t="n">
         <v>0.5</v>
@@ -8941,33 +8941,33 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>MIN @ CHI</t>
+          <t>ARI @ LAC</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>CHI ML</t>
+          <t>LAC -10.5</t>
         </is>
       </c>
       <c r="E159" s="7" t="n">
-        <v>-198</v>
+        <v>-110</v>
       </c>
       <c r="F159" s="8" t="n">
-        <v>0.6072</v>
+        <v>0.4665</v>
       </c>
       <c r="G159" s="8" t="n">
-        <v>0.6644</v>
+        <v>0.5238</v>
       </c>
       <c r="H159" s="8" t="n">
         <v>-0.0428</v>
       </c>
       <c r="I159" s="8" t="n">
-        <v>-0.08537236419210453</v>
+        <v>-0.1094436399964945</v>
       </c>
       <c r="J159" s="10" t="n">
         <v>0.5</v>
@@ -8982,33 +8982,33 @@
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>CHI @ CAR</t>
+          <t>MIN @ CHI</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>Over 47.5</t>
+          <t>CHI ML</t>
         </is>
       </c>
       <c r="E160" s="12" t="n">
-        <v>-115</v>
+        <v>-198</v>
       </c>
       <c r="F160" s="13" t="n">
-        <v>0.4759</v>
+        <v>0.6068</v>
       </c>
       <c r="G160" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.6644</v>
       </c>
       <c r="H160" s="13" t="n">
-        <v>-0.0435</v>
+        <v>-0.0429</v>
       </c>
       <c r="I160" s="13" t="n">
-        <v>-0.1103290525258087</v>
+        <v>-0.08590435667615604</v>
       </c>
       <c r="J160" s="15" t="n">
         <v>0.5</v>
@@ -9023,7 +9023,7 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>MIN @ CHI</t>
+          <t>CHI @ CAR</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
@@ -9033,23 +9033,23 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>Over 45.5</t>
+          <t>Over 47.5</t>
         </is>
       </c>
       <c r="E161" s="7" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="F161" s="8" t="n">
-        <v>0.4645</v>
+        <v>0.4759</v>
       </c>
       <c r="G161" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5349</v>
       </c>
       <c r="H161" s="8" t="n">
-        <v>-0.0436</v>
+        <v>-0.0435</v>
       </c>
       <c r="I161" s="8" t="n">
-        <v>-0.1132136058104599</v>
+        <v>-0.1103290525258087</v>
       </c>
       <c r="J161" s="10" t="n">
         <v>0.5</v>
@@ -9064,7 +9064,7 @@
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>LV @ LAC</t>
+          <t>MIN @ CHI</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>Over 42.5</t>
+          <t>Over 45.5</t>
         </is>
       </c>
       <c r="E162" s="12" t="n">
@@ -9090,7 +9090,7 @@
         <v>-0.0436</v>
       </c>
       <c r="I162" s="13" t="n">
-        <v>-0.1132045300743653</v>
+        <v>-0.1132136058104599</v>
       </c>
       <c r="J162" s="15" t="n">
         <v>0.5</v>
@@ -9105,42 +9105,38 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>NO @ BAL</t>
+          <t>LV @ LAC</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>BAL ML</t>
+          <t>Over 42.5</t>
         </is>
       </c>
       <c r="E163" s="7" t="n">
-        <v>-355</v>
+        <v>-110</v>
       </c>
       <c r="F163" s="8" t="n">
-        <v>0.7205</v>
+        <v>0.4645</v>
       </c>
       <c r="G163" s="8" t="n">
-        <v>0.7802</v>
+        <v>0.5238</v>
       </c>
       <c r="H163" s="8" t="n">
-        <v>-0.0437</v>
+        <v>-0.0436</v>
       </c>
       <c r="I163" s="8" t="n">
-        <v>-0.07594524744761211</v>
+        <v>-0.1132045300743653</v>
       </c>
       <c r="J163" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="K163" s="4" t="inlineStr">
-        <is>
-          <t>price -355 outside the allowed range</t>
-        </is>
-      </c>
+      <c r="K163" s="4" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
@@ -9150,7 +9146,7 @@
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>PHI @ TEN</t>
+          <t>NO @ BAL</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
@@ -9160,28 +9156,32 @@
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>PHI ML</t>
+          <t>BAL ML</t>
         </is>
       </c>
       <c r="E164" s="12" t="n">
-        <v>-205</v>
+        <v>-355</v>
       </c>
       <c r="F164" s="13" t="n">
-        <v>0.6123</v>
+        <v>0.7205</v>
       </c>
       <c r="G164" s="13" t="n">
-        <v>0.6721</v>
+        <v>0.7802</v>
       </c>
       <c r="H164" s="13" t="n">
-        <v>-0.0438</v>
+        <v>-0.0437</v>
       </c>
       <c r="I164" s="13" t="n">
-        <v>-0.08829898217785048</v>
+        <v>-0.07594524744761211</v>
       </c>
       <c r="J164" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="K164" s="5" t="inlineStr"/>
+      <c r="K164" s="5" t="inlineStr">
+        <is>
+          <t>price -355 outside the allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
@@ -9191,33 +9191,33 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>GB @ NYJ</t>
+          <t>PHI @ TEN</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>GB -5.5</t>
+          <t>PHI ML</t>
         </is>
       </c>
       <c r="E165" s="7" t="n">
-        <v>-110</v>
+        <v>-205</v>
       </c>
       <c r="F165" s="8" t="n">
-        <v>0.4638</v>
+        <v>0.6123</v>
       </c>
       <c r="G165" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.6721</v>
       </c>
       <c r="H165" s="8" t="n">
-        <v>-0.0439</v>
+        <v>-0.0438</v>
       </c>
       <c r="I165" s="8" t="n">
-        <v>-0.114653280785704</v>
+        <v>-0.08829898217785048</v>
       </c>
       <c r="J165" s="10" t="n">
         <v>0.5</v>
@@ -9232,33 +9232,33 @@
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>SF @ LAR</t>
+          <t>GB @ NYJ</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>LAR ML</t>
+          <t>GB -5.5</t>
         </is>
       </c>
       <c r="E166" s="12" t="n">
-        <v>-185</v>
+        <v>-110</v>
       </c>
       <c r="F166" s="13" t="n">
-        <v>0.5885</v>
+        <v>0.4638</v>
       </c>
       <c r="G166" s="13" t="n">
-        <v>0.6491</v>
+        <v>0.5238</v>
       </c>
       <c r="H166" s="13" t="n">
-        <v>-0.0441</v>
+        <v>-0.0439</v>
       </c>
       <c r="I166" s="13" t="n">
-        <v>-0.09252744165458121</v>
+        <v>-0.114653280785704</v>
       </c>
       <c r="J166" s="15" t="n">
         <v>0.5</v>
@@ -9273,33 +9273,33 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>NO @ BAL</t>
+          <t>SF @ LAR</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>BAL -7.5</t>
+          <t>LAR ML</t>
         </is>
       </c>
       <c r="E167" s="7" t="n">
-        <v>-110</v>
+        <v>-185</v>
       </c>
       <c r="F167" s="8" t="n">
-        <v>0.4629</v>
+        <v>0.5885</v>
       </c>
       <c r="G167" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.6491</v>
       </c>
       <c r="H167" s="8" t="n">
-        <v>-0.0442</v>
+        <v>-0.0441</v>
       </c>
       <c r="I167" s="8" t="n">
-        <v>-0.1163005544616851</v>
+        <v>-0.09252744165458121</v>
       </c>
       <c r="J167" s="10" t="n">
         <v>0.5</v>
@@ -9314,7 +9314,7 @@
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>IND @ KC</t>
+          <t>NO @ BAL</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
@@ -9324,23 +9324,23 @@
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>KC -6.5</t>
+          <t>BAL -7.5</t>
         </is>
       </c>
       <c r="E168" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F168" s="13" t="n">
-        <v>0.4627</v>
+        <v>0.4629</v>
       </c>
       <c r="G168" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H168" s="13" t="n">
-        <v>-0.0443</v>
+        <v>-0.0442</v>
       </c>
       <c r="I168" s="13" t="n">
-        <v>-0.1167347160720638</v>
+        <v>-0.1163005544616851</v>
       </c>
       <c r="J168" s="15" t="n">
         <v>0.5</v>
@@ -9355,33 +9355,33 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>ATL @ PIT</t>
+          <t>IND @ KC</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>Under 41.5</t>
+          <t>KC -6.5</t>
         </is>
       </c>
       <c r="E169" s="7" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="F169" s="8" t="n">
-        <v>0.4507</v>
+        <v>0.4627</v>
       </c>
       <c r="G169" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.5238</v>
       </c>
       <c r="H169" s="8" t="n">
-        <v>-0.0444</v>
+        <v>-0.0443</v>
       </c>
       <c r="I169" s="8" t="n">
-        <v>-0.1201358675073684</v>
+        <v>-0.1167347160720638</v>
       </c>
       <c r="J169" s="10" t="n">
         <v>0.5</v>
@@ -9396,7 +9396,7 @@
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>IND @ KC</t>
+          <t>ATL @ PIT</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
@@ -9406,23 +9406,23 @@
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>Over 47.5</t>
+          <t>Under 41.5</t>
         </is>
       </c>
       <c r="E170" s="12" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="F170" s="13" t="n">
-        <v>0.462</v>
+        <v>0.4507</v>
       </c>
       <c r="G170" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5122</v>
       </c>
       <c r="H170" s="13" t="n">
-        <v>-0.0445</v>
+        <v>-0.0444</v>
       </c>
       <c r="I170" s="13" t="n">
-        <v>-0.1180220918978541</v>
+        <v>-0.1201358675073684</v>
       </c>
       <c r="J170" s="15" t="n">
         <v>0.5</v>
@@ -9437,33 +9437,33 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>NO @ DET</t>
+          <t>IND @ KC</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>DET -7</t>
+          <t>Over 47.5</t>
         </is>
       </c>
       <c r="E171" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F171" s="8" t="n">
-        <v>0.4618</v>
+        <v>0.462</v>
       </c>
       <c r="G171" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H171" s="8" t="n">
-        <v>-0.0446</v>
+        <v>-0.0445</v>
       </c>
       <c r="I171" s="8" t="n">
-        <v>-0.1119613290895949</v>
+        <v>-0.1180220918978541</v>
       </c>
       <c r="J171" s="10" t="n">
         <v>0.5</v>
@@ -9478,33 +9478,33 @@
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
-          <t>GB @ NYJ</t>
+          <t>NO @ DET</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>GB ML</t>
+          <t>DET -7</t>
         </is>
       </c>
       <c r="E172" s="12" t="n">
-        <v>-238</v>
+        <v>-110</v>
       </c>
       <c r="F172" s="13" t="n">
-        <v>0.6409</v>
+        <v>0.4618</v>
       </c>
       <c r="G172" s="13" t="n">
-        <v>0.7040999999999999</v>
+        <v>0.5238</v>
       </c>
       <c r="H172" s="13" t="n">
-        <v>-0.045</v>
+        <v>-0.0446</v>
       </c>
       <c r="I172" s="13" t="n">
-        <v>-0.08909904384068018</v>
+        <v>-0.1119613290895949</v>
       </c>
       <c r="J172" s="15" t="n">
         <v>0.5</v>
@@ -9519,33 +9519,33 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>PHI @ TEN</t>
+          <t>GB @ NYJ</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>PHI -4.5</t>
+          <t>GB ML</t>
         </is>
       </c>
       <c r="E173" s="7" t="n">
-        <v>-110</v>
+        <v>-238</v>
       </c>
       <c r="F173" s="8" t="n">
-        <v>0.4597</v>
+        <v>0.6409</v>
       </c>
       <c r="G173" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="H173" s="8" t="n">
-        <v>-0.0452</v>
+        <v>-0.045</v>
       </c>
       <c r="I173" s="8" t="n">
-        <v>-0.1223058059611346</v>
+        <v>-0.08909904384068018</v>
       </c>
       <c r="J173" s="10" t="n">
         <v>0.5</v>
@@ -9560,7 +9560,7 @@
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>NYG @ LAR</t>
+          <t>PHI @ TEN</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
@@ -9570,23 +9570,23 @@
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>LAR -8.5</t>
+          <t>PHI -4.5</t>
         </is>
       </c>
       <c r="E174" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F174" s="13" t="n">
-        <v>0.4594</v>
+        <v>0.4597</v>
       </c>
       <c r="G174" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H174" s="13" t="n">
-        <v>-0.0454</v>
+        <v>-0.0452</v>
       </c>
       <c r="I174" s="13" t="n">
-        <v>-0.1229516868549289</v>
+        <v>-0.1223058059611346</v>
       </c>
       <c r="J174" s="15" t="n">
         <v>0.5</v>
@@ -9601,7 +9601,7 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>LV @ LAC</t>
+          <t>NYG @ LAR</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
@@ -9611,23 +9611,23 @@
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>LAC -8.5</t>
+          <t>LAR -8.5</t>
         </is>
       </c>
       <c r="E175" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F175" s="8" t="n">
-        <v>0.4578</v>
+        <v>0.4594</v>
       </c>
       <c r="G175" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H175" s="8" t="n">
-        <v>-0.0459</v>
+        <v>-0.0454</v>
       </c>
       <c r="I175" s="8" t="n">
-        <v>-0.1261070906377938</v>
+        <v>-0.1229516868549289</v>
       </c>
       <c r="J175" s="10" t="n">
         <v>0.5</v>
@@ -9642,33 +9642,33 @@
       </c>
       <c r="B176" s="5" t="inlineStr">
         <is>
-          <t>MIA @ LV</t>
+          <t>LV @ LAC</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
-          <t>Under 40.5</t>
+          <t>LAC -8.5</t>
         </is>
       </c>
       <c r="E176" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F176" s="13" t="n">
-        <v>0.457</v>
+        <v>0.4578</v>
       </c>
       <c r="G176" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H176" s="13" t="n">
-        <v>-0.0461</v>
+        <v>-0.0459</v>
       </c>
       <c r="I176" s="13" t="n">
-        <v>-0.1276251689568088</v>
+        <v>-0.1261070906377938</v>
       </c>
       <c r="J176" s="15" t="n">
         <v>0.5</v>
@@ -9683,7 +9683,7 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>NO @ BAL</t>
+          <t>MIA @ LV</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>Over 46.5</t>
+          <t>Under 40.5</t>
         </is>
       </c>
       <c r="E177" s="7" t="n">
@@ -9709,7 +9709,7 @@
         <v>-0.0461</v>
       </c>
       <c r="I177" s="8" t="n">
-        <v>-0.1276128918105729</v>
+        <v>-0.1276251689568088</v>
       </c>
       <c r="J177" s="10" t="n">
         <v>0.5</v>
@@ -9724,7 +9724,7 @@
       </c>
       <c r="B178" s="5" t="inlineStr">
         <is>
-          <t>WSH @ DAL</t>
+          <t>NO @ BAL</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
@@ -9734,7 +9734,7 @@
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>Over 51.5</t>
+          <t>Over 46.5</t>
         </is>
       </c>
       <c r="E178" s="12" t="n">
@@ -9750,7 +9750,7 @@
         <v>-0.0461</v>
       </c>
       <c r="I178" s="13" t="n">
-        <v>-0.1276150624646581</v>
+        <v>-0.1276128918105729</v>
       </c>
       <c r="J178" s="15" t="n">
         <v>0.5</v>
@@ -9765,7 +9765,7 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>CLE @ JAX</t>
+          <t>WSH @ DAL</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
@@ -9775,23 +9775,23 @@
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>Under 40.5</t>
+          <t>Over 51.5</t>
         </is>
       </c>
       <c r="E179" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F179" s="8" t="n">
-        <v>0.4545</v>
+        <v>0.457</v>
       </c>
       <c r="G179" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H179" s="8" t="n">
-        <v>-0.0468</v>
+        <v>-0.0461</v>
       </c>
       <c r="I179" s="8" t="n">
-        <v>-0.1324091895425259</v>
+        <v>-0.1276150624646581</v>
       </c>
       <c r="J179" s="10" t="n">
         <v>0.5</v>
@@ -9806,7 +9806,7 @@
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>DEN @ KC</t>
+          <t>CLE @ JAX</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>Over 42.5</t>
+          <t>Under 40.5</t>
         </is>
       </c>
       <c r="E180" s="12" t="n">
@@ -9832,7 +9832,7 @@
         <v>-0.0468</v>
       </c>
       <c r="I180" s="13" t="n">
-        <v>-0.1323854465016522</v>
+        <v>-0.1324091895425259</v>
       </c>
       <c r="J180" s="15" t="n">
         <v>0.5</v>
@@ -10134,42 +10134,38 @@
       </c>
       <c r="B188" s="5" t="inlineStr">
         <is>
-          <t>CLE @ JAX</t>
+          <t>ARI @ LAC</t>
         </is>
       </c>
       <c r="C188" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D188" s="5" t="inlineStr">
         <is>
-          <t>JAX ML</t>
+          <t>Over 46.5</t>
         </is>
       </c>
       <c r="E188" s="12" t="n">
-        <v>-380</v>
+        <v>-115</v>
       </c>
       <c r="F188" s="13" t="n">
-        <v>0.7149</v>
+        <v>0.4583</v>
       </c>
       <c r="G188" s="13" t="n">
-        <v>0.7917</v>
+        <v>0.5349</v>
       </c>
       <c r="H188" s="13" t="n">
         <v>-0.0486</v>
       </c>
       <c r="I188" s="13" t="n">
-        <v>-0.09614737199153012</v>
+        <v>-0.1432706098634677</v>
       </c>
       <c r="J188" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="K188" s="5" t="inlineStr">
-        <is>
-          <t>price -380 outside the allowed range</t>
-        </is>
-      </c>
+      <c r="K188" s="5" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
@@ -10179,7 +10175,7 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>ARI @ LAC</t>
+          <t>TB @ CIN</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
@@ -10189,23 +10185,23 @@
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>Over 46.5</t>
+          <t>Over 50.5</t>
         </is>
       </c>
       <c r="E189" s="7" t="n">
-        <v>-115</v>
+        <v>-118</v>
       </c>
       <c r="F189" s="8" t="n">
-        <v>0.4583</v>
+        <v>0.463</v>
       </c>
       <c r="G189" s="8" t="n">
-        <v>0.5349</v>
+        <v>0.5413</v>
       </c>
       <c r="H189" s="8" t="n">
-        <v>-0.0486</v>
+        <v>-0.049</v>
       </c>
       <c r="I189" s="8" t="n">
-        <v>-0.1432706098634677</v>
+        <v>-0.1445512690360282</v>
       </c>
       <c r="J189" s="10" t="n">
         <v>0.5</v>
@@ -10220,38 +10216,42 @@
       </c>
       <c r="B190" s="5" t="inlineStr">
         <is>
-          <t>TB @ CIN</t>
+          <t>CLE @ JAX</t>
         </is>
       </c>
       <c r="C190" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D190" s="5" t="inlineStr">
         <is>
-          <t>Over 50.5</t>
+          <t>JAX ML</t>
         </is>
       </c>
       <c r="E190" s="12" t="n">
-        <v>-118</v>
+        <v>-395</v>
       </c>
       <c r="F190" s="13" t="n">
-        <v>0.463</v>
+        <v>0.717</v>
       </c>
       <c r="G190" s="13" t="n">
-        <v>0.5413</v>
+        <v>0.798</v>
       </c>
       <c r="H190" s="13" t="n">
-        <v>-0.049</v>
+        <v>-0.0495</v>
       </c>
       <c r="I190" s="13" t="n">
-        <v>-0.1445512690360282</v>
+        <v>-0.1006671259229107</v>
       </c>
       <c r="J190" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="K190" s="5" t="inlineStr"/>
+      <c r="K190" s="5" t="inlineStr">
+        <is>
+          <t>price -395 outside the allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
@@ -10302,42 +10302,38 @@
       </c>
       <c r="B192" s="5" t="inlineStr">
         <is>
-          <t>MIA @ SF</t>
+          <t>NO @ DET</t>
         </is>
       </c>
       <c r="C192" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D192" s="5" t="inlineStr">
         <is>
-          <t>SF ML</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="E192" s="12" t="n">
-        <v>-650</v>
+        <v>-118</v>
       </c>
       <c r="F192" s="13" t="n">
-        <v>0.7838000000000001</v>
+        <v>0.4555</v>
       </c>
       <c r="G192" s="13" t="n">
-        <v>0.8667</v>
+        <v>0.5413</v>
       </c>
       <c r="H192" s="13" t="n">
-        <v>-0.0499</v>
+        <v>-0.0503</v>
       </c>
       <c r="I192" s="13" t="n">
-        <v>-0.09497961537517048</v>
+        <v>-0.1584158803963682</v>
       </c>
       <c r="J192" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="K192" s="5" t="inlineStr">
-        <is>
-          <t>price -650 outside the allowed range</t>
-        </is>
-      </c>
+      <c r="K192" s="5" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
@@ -10347,38 +10343,42 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>NO @ DET</t>
+          <t>MIA @ SF</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>SF ML</t>
         </is>
       </c>
       <c r="E193" s="7" t="n">
-        <v>-118</v>
+        <v>-675</v>
       </c>
       <c r="F193" s="8" t="n">
-        <v>0.4555</v>
+        <v>0.7857</v>
       </c>
       <c r="G193" s="8" t="n">
-        <v>0.5413</v>
+        <v>0.871</v>
       </c>
       <c r="H193" s="8" t="n">
         <v>-0.0503</v>
       </c>
       <c r="I193" s="8" t="n">
-        <v>-0.1584158803963682</v>
+        <v>-0.09723961818731934</v>
       </c>
       <c r="J193" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="K193" s="4" t="inlineStr"/>
+      <c r="K193" s="4" t="inlineStr">
+        <is>
+          <t>price -675 outside the allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="5" t="inlineStr">
@@ -11622,16 +11622,16 @@
         </is>
       </c>
       <c r="D15" s="14" t="n">
-        <v>0.99</v>
+        <v>0.89</v>
       </c>
       <c r="E15" s="14" t="n">
         <v>-1.5</v>
       </c>
       <c r="F15" s="16" t="n">
-        <v>44</v>
+        <v>43.6</v>
       </c>
       <c r="G15" s="16" t="n">
-        <v>44.5</v>
+        <v>43.5</v>
       </c>
       <c r="H15" s="12" t="n"/>
       <c r="I15" s="19" t="n"/>
@@ -11758,7 +11758,7 @@
         </is>
       </c>
       <c r="D19" s="14" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="E19" s="14" t="n">
         <v>-3.5</v>
@@ -11934,7 +11934,7 @@
         <v>-3</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>40.7</v>
+        <v>41.2</v>
       </c>
       <c r="G24" s="11" t="n">
         <v>42.5</v>
@@ -11968,7 +11968,7 @@
         <v>2.5</v>
       </c>
       <c r="F25" s="16" t="n">
-        <v>48.6</v>
+        <v>48.1</v>
       </c>
       <c r="G25" s="16" t="n">
         <v>48.5</v>
@@ -12132,7 +12132,7 @@
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>3.79</v>
+        <v>3.89</v>
       </c>
       <c r="E30" s="9" t="n">
         <v>-3</v>
@@ -12234,7 +12234,7 @@
         </is>
       </c>
       <c r="D33" s="14" t="n">
-        <v>-0.82</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E33" s="14" t="n">
         <v>2.5</v>
@@ -17004,10 +17004,10 @@
         <v>44.5</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>-175</v>
+        <v>-180</v>
       </c>
       <c r="K54" s="19" t="n">
         <v>0</v>
@@ -17322,10 +17322,10 @@
         <v>40.5</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>-380</v>
+        <v>-395</v>
       </c>
       <c r="K60" s="19" t="n">
         <v>0</v>
@@ -17902,7 +17902,7 @@
         <v>-1.5</v>
       </c>
       <c r="H71" s="11" t="n">
-        <v>44.5</v>
+        <v>43.5</v>
       </c>
       <c r="I71" s="7" t="n">
         <v>105</v>
@@ -18011,10 +18011,10 @@
         <v>42.5</v>
       </c>
       <c r="I73" s="7" t="n">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="J73" s="7" t="n">
-        <v>-245</v>
+        <v>-238</v>
       </c>
       <c r="K73" s="17" t="n">
         <v>0</v>
@@ -18435,10 +18435,10 @@
         <v>46.5</v>
       </c>
       <c r="I81" s="7" t="n">
-        <v>470</v>
+        <v>490</v>
       </c>
       <c r="J81" s="7" t="n">
-        <v>-650</v>
+        <v>-675</v>
       </c>
       <c r="K81" s="17" t="n">
         <v>0</v>
@@ -18753,10 +18753,10 @@
         <v>39.5</v>
       </c>
       <c r="I87" s="7" t="n">
-        <v>-122</v>
+        <v>-125</v>
       </c>
       <c r="J87" s="7" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="K87" s="17" t="n">
         <v>0</v>
@@ -18912,10 +18912,10 @@
         <v>44.5</v>
       </c>
       <c r="I90" s="12" t="n">
-        <v>-425</v>
+        <v>-455</v>
       </c>
       <c r="J90" s="12" t="n">
-        <v>330</v>
+        <v>350</v>
       </c>
       <c r="K90" s="19" t="n">
         <v>0</v>
@@ -20076,10 +20076,10 @@
         <v>43.5</v>
       </c>
       <c r="I112" s="12" t="n">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="J112" s="12" t="n">
-        <v>-395</v>
+        <v>-410</v>
       </c>
       <c r="K112" s="19" t="n">
         <v>0</v>
@@ -21348,10 +21348,10 @@
         <v>43.5</v>
       </c>
       <c r="I136" s="12" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="J136" s="12" t="n">
-        <v>-270</v>
+        <v>-285</v>
       </c>
       <c r="K136" s="19" t="n">
         <v>0</v>
@@ -22196,10 +22196,10 @@
         <v>41.5</v>
       </c>
       <c r="I152" s="12" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="J152" s="12" t="n">
-        <v>-135</v>
+        <v>-142</v>
       </c>
       <c r="K152" s="19" t="n">
         <v>0</v>
@@ -22779,10 +22779,10 @@
         <v>46.5</v>
       </c>
       <c r="I163" s="7" t="n">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="J163" s="7" t="n">
-        <v>-225</v>
+        <v>-218</v>
       </c>
       <c r="K163" s="17" t="n">
         <v>0</v>
@@ -25111,10 +25111,10 @@
         <v>46.5</v>
       </c>
       <c r="I207" s="7" t="n">
-        <v>-122</v>
+        <v>-125</v>
       </c>
       <c r="J207" s="7" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="K207" s="17" t="n">
         <v>0</v>
@@ -25164,10 +25164,10 @@
         <v>47.5</v>
       </c>
       <c r="I208" s="12" t="n">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="J208" s="12" t="n">
-        <v>-625</v>
+        <v>-650</v>
       </c>
       <c r="K208" s="19" t="n">
         <v>0</v>
@@ -26436,10 +26436,10 @@
         <v>44.5</v>
       </c>
       <c r="I232" s="12" t="n">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="J232" s="12" t="n">
-        <v>-198</v>
+        <v>-205</v>
       </c>
       <c r="K232" s="19" t="n">
         <v>0</v>
@@ -26913,10 +26913,10 @@
         <v>42.5</v>
       </c>
       <c r="I241" s="7" t="n">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="J241" s="7" t="n">
-        <v>-455</v>
+        <v>-440</v>
       </c>
       <c r="K241" s="17" t="n">
         <v>0</v>
@@ -27231,10 +27231,10 @@
         <v>43.5</v>
       </c>
       <c r="I247" s="7" t="n">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="J247" s="7" t="n">
-        <v>-225</v>
+        <v>-218</v>
       </c>
       <c r="K247" s="17" t="n">
         <v>0</v>
@@ -27337,10 +27337,10 @@
         <v>46.5</v>
       </c>
       <c r="I249" s="7" t="n">
-        <v>-250</v>
+        <v>-245</v>
       </c>
       <c r="J249" s="7" t="n">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="K249" s="17" t="n">
         <v>0</v>
@@ -27602,10 +27602,10 @@
         <v>48.5</v>
       </c>
       <c r="I254" s="12" t="n">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="J254" s="12" t="n">
-        <v>-258</v>
+        <v>-265</v>
       </c>
       <c r="K254" s="19" t="n">
         <v>0</v>
@@ -27973,10 +27973,10 @@
         <v>44.5</v>
       </c>
       <c r="I261" s="7" t="n">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="J261" s="7" t="n">
-        <v>-162</v>
+        <v>-155</v>
       </c>
       <c r="K261" s="17" t="n">
         <v>0</v>
@@ -29192,10 +29192,10 @@
         <v>45.5</v>
       </c>
       <c r="I284" s="12" t="n">
-        <v>-122</v>
+        <v>-125</v>
       </c>
       <c r="J284" s="12" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="K284" s="19" t="n">
         <v>0</v>
@@ -29404,10 +29404,10 @@
         <v>45.5</v>
       </c>
       <c r="I288" s="12" t="n">
-        <v>-340</v>
+        <v>-355</v>
       </c>
       <c r="J288" s="12" t="n">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="K288" s="19" t="n">
         <v>0</v>
@@ -29457,10 +29457,10 @@
         <v>40.5</v>
       </c>
       <c r="I289" s="7" t="n">
-        <v>-278</v>
+        <v>-270</v>
       </c>
       <c r="J289" s="7" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="K289" s="17" t="n">
         <v>0</v>
@@ -29881,10 +29881,10 @@
         <v>48.5</v>
       </c>
       <c r="I297" s="7" t="n">
-        <v>-205</v>
+        <v>-218</v>
       </c>
       <c r="J297" s="7" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="K297" s="17" t="n">
         <v>0</v>
@@ -29934,10 +29934,10 @@
         <v>48.5</v>
       </c>
       <c r="I298" s="12" t="n">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="J298" s="12" t="n">
-        <v>-185</v>
+        <v>-192</v>
       </c>
       <c r="K298" s="19" t="n">
         <v>0</v>
@@ -29987,10 +29987,10 @@
         <v>47.5</v>
       </c>
       <c r="I299" s="7" t="n">
-        <v>-360</v>
+        <v>-380</v>
       </c>
       <c r="J299" s="7" t="n">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="K299" s="17" t="n">
         <v>0</v>
@@ -30835,10 +30835,10 @@
         <v>46.5</v>
       </c>
       <c r="I315" s="7" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="J315" s="7" t="n">
-        <v>-125</v>
+        <v>-122</v>
       </c>
       <c r="K315" s="17" t="n">
         <v>0</v>
@@ -31312,10 +31312,10 @@
         <v>43.5</v>
       </c>
       <c r="I324" s="12" t="n">
-        <v>-122</v>
+        <v>-125</v>
       </c>
       <c r="J324" s="12" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="K324" s="19" t="n">
         <v>0</v>
@@ -31998,12 +31998,12 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Reggie Virgil</t>
+          <t>Hunter Long</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -32018,7 +32018,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Virgil caught three of six targets for 23 yards in a loss to Green Bay during Friday's exhibition contest.</t>
+          <t>Long has been traded from Jacksonville to the Cardinals, Ian Rapoport of NFL Network reports.</t>
         </is>
       </c>
     </row>
@@ -32030,7 +32030,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Jalen Brooks</t>
+          <t>Reggie Virgil</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -32050,7 +32050,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Brooks caught all four of his targets for 57 yards during Friday's exhibition loss to Green Bay.</t>
+          <t>Virgil caught three of six targets for 23 yards in a loss to Green Bay during Friday's exhibition contest.</t>
         </is>
       </c>
     </row>
@@ -32062,27 +32062,27 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>Jalen Brooks</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Sprain</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Love (ankle) did not play in Friday's preseason loss to the Packers, but per Cardinals team reporter Zach Gershman, he was able to work out prior to the game.</t>
+          <t>Brooks caught all four of his targets for 57 yards during Friday's exhibition loss to Green Bay.</t>
         </is>
       </c>
     </row>
@@ -32094,27 +32094,27 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Elijah Higgins</t>
+          <t>Jeremiyah Love</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Sprain</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Higgins (concussion) caught two passes on three targets for 15 yards during Friday's 42-38 preseason loss to Green Bay.</t>
+          <t>Love (ankle) did not play in Friday's preseason loss to the Packers, but per Cardinals team reporter Zach Gershman, he was able to work out prior to the game.</t>
         </is>
       </c>
     </row>
@@ -32126,12 +32126,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Gardner Minshew II</t>
+          <t>Elijah Higgins</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -32146,7 +32146,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Minshew completed seven of nine passes for 126 yards and a touchdown while taking a 10-yard sack during the Cardinals' 42-38 preseason loss to the Packers on Friday.</t>
+          <t>Higgins (concussion) caught two passes on three targets for 15 yards during Friday's 42-38 preseason loss to Green Bay.</t>
         </is>
       </c>
     </row>
@@ -32158,27 +32158,27 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Ihmir Smith-Marsette</t>
+          <t>Gardner Minshew II</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Ankle</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Smith-Marsette (ankle) will not return to Friday night's preseason finale against the Packers, Darren Urban of the Cardinals' official site reports.</t>
+          <t>Minshew completed seven of nine passes for 126 yards and a touchdown while taking a 10-yard sack during the Cardinals' 42-38 preseason loss to the Packers on Friday.</t>
         </is>
       </c>
     </row>
@@ -32190,12 +32190,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>James Conner</t>
+          <t>Ihmir Smith-Marsette</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -32205,12 +32205,12 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Ankle</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Cardinals coach Mike LaFleur said Wednesday that it's "too early to tell" if Conner (foot) will be ready for Week 1 against the Chargers, Theo Mackie of The Arizona Republic reports.</t>
+          <t>Smith-Marsette (ankle) will not return to Friday night's preseason finale against the Packers, Darren Urban of the Cardinals' official site reports.</t>
         </is>
       </c>
     </row>
@@ -32222,27 +32222,27 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Hjalte Froholdt</t>
+          <t>James Conner</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Arizona signed Froholdt to a two-year, $20 million contract extension Tuesday, Ian Rapoport of ESPN and NFL Network reports.</t>
+          <t>Cardinals coach Mike LaFleur said Wednesday that it's "too early to tell" if Conner (foot) will be ready for Week 1 against the Chargers, Theo Mackie of The Arizona Republic reports.</t>
         </is>
       </c>
     </row>
@@ -32254,27 +32254,27 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Trey Benson</t>
+          <t>Hjalte Froholdt</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Benson (knee) reverted to the Cardinals' injured reserve list Tuesday, David Furones of the South Florida Sun Sentinel reports.</t>
+          <t>Arizona signed Froholdt to a two-year, $20 million contract extension Tuesday, Ian Rapoport of ESPN and NFL Network reports.</t>
         </is>
       </c>
     </row>
@@ -32286,12 +32286,12 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Xavier Weaver</t>
+          <t>Trey Benson</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -32306,7 +32306,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Weaver (hamstring) was placed on injured reserve by the Cardinals on Monday.</t>
+          <t>Benson (knee) reverted to the Cardinals' injured reserve list Tuesday, David Furones of the South Florida Sun Sentinel reports.</t>
         </is>
       </c>
     </row>
@@ -32318,17 +32318,17 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Carson Beck</t>
+          <t>Xavier Weaver</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -32338,7 +32338,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Beck (ribs) continued to be a limited participant at Monday's practice, Bo Brack of GoPHNX.com reports.</t>
+          <t>Weaver (hamstring) was placed on injured reserve by the Cardinals on Monday.</t>
         </is>
       </c>
     </row>
@@ -32350,27 +32350,27 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Josh Sweat</t>
+          <t>Carson Beck</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Sweat (knee) was activated from the active/PUP list Monday, Darren Urban of the Cardinals' official site reports.</t>
+          <t>Beck (ribs) continued to be a limited participant at Monday's practice, Bo Brack of GoPHNX.com reports.</t>
         </is>
       </c>
     </row>
@@ -32382,12 +32382,12 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Chad Ryland</t>
+          <t>Josh Sweat</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -32402,7 +32402,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Ryland made field goals of 38 and 31 yards, missed a 62-yarder wide right and knocked through his only extra-point try in the Cardinals' 34-13 preseason loss to the Cowboys on Saturday.</t>
+          <t>Sweat (knee) was activated from the active/PUP list Monday, Darren Urban of the Cardinals' official site reports.</t>
         </is>
       </c>
     </row>
@@ -32414,27 +32414,27 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Dadrion Taylor-Demerson</t>
+          <t>Chad Ryland</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Taylor-Demerson is questionable to return to Saturday's preseason game against the Cowboys due to a rib injury.</t>
+          <t>Ryland made field goals of 38 and 31 yards, missed a 62-yarder wide right and knocked through his only extra-point try in the Cardinals' 34-13 preseason loss to the Cowboys on Saturday.</t>
         </is>
       </c>
     </row>
@@ -32446,12 +32446,12 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Blake Gillikin</t>
+          <t>Dadrion Taylor-Demerson</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -32466,7 +32466,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Gillikin sustained a groin injury during pregame warmups and is questionable to play in Saturday's preseason game against the Cowboys, Darren Urban of the Cardinals' official site reports.</t>
+          <t>Taylor-Demerson is questionable to return to Saturday's preseason game against the Cowboys due to a rib injury.</t>
         </is>
       </c>
     </row>
@@ -32478,17 +32478,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Tip Reiman</t>
+          <t>Blake Gillikin</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Out</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -32498,7 +32498,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Reiman (ankle) will not be back for the start of the regular season, Darren Urban of the Cardinals' official site reports.</t>
+          <t>Gillikin sustained a groin injury during pregame warmups and is questionable to play in Saturday's preseason game against the Cowboys, Darren Urban of the Cardinals' official site reports.</t>
         </is>
       </c>
     </row>
@@ -32510,27 +32510,27 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Garrett Williams</t>
+          <t>Tip Reiman</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Williams (Achilles) was activated from the PUP list by the Cardinals on Thursday, Darren Urban of the Cardinals' official site reports.</t>
+          <t>Reiman (ankle) will not be back for the start of the regular season, Darren Urban of the Cardinals' official site reports.</t>
         </is>
       </c>
     </row>
@@ -32542,12 +32542,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Jacoby Brissett</t>
+          <t>Garrett Williams</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -32562,7 +32562,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Coach Mike LaFleur said Thursday that Brissett won't suit up for Saturday's preseason game against the Cowboys, Josh Weinfuss of ESPN.com reports.</t>
+          <t>Williams (Achilles) was activated from the PUP list by the Cardinals on Thursday, Darren Urban of the Cardinals' official site reports.</t>
         </is>
       </c>
     </row>
@@ -32574,12 +32574,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Valentin Senn</t>
+          <t>Jacoby Brissett</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>OT</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -32592,7 +32592,11 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Coach Mike LaFleur said Thursday that Brissett won't suit up for Saturday's preseason game against the Cowboys, Josh Weinfuss of ESPN.com reports.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -32602,29 +32606,25 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Chase Bisontis</t>
+          <t>Valentin Senn</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>OT</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Surgery</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>ir</t>
-        </is>
-      </c>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -32634,12 +32634,12 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Joey Blount</t>
+          <t>Chase Bisontis</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -32649,7 +32649,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Stinger</t>
+          <t>Surgery</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -32666,27 +32666,27 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Zachary Carter</t>
+          <t>Joey Blount</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Stinger</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>ir</t>
         </is>
       </c>
     </row>
@@ -32698,17 +32698,17 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Jameson Geers</t>
+          <t>Zachary Carter</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -32718,7 +32718,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>ir</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -32730,27 +32730,27 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Tyler Allgeier</t>
+          <t>Jameson Geers</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Allgeier could open the regular season as the Cardinals' primary running back, as Adam Schefter of ESPN reports that Jeremiyah Love sustained a high-ankle sprain in Thursday's preseason win over the Raiders.</t>
+          <t>ir</t>
         </is>
       </c>
     </row>
@@ -32762,7 +32762,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Tre Stewart</t>
+          <t>Tyler Allgeier</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -32782,7 +32782,7 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>The Cardinals signed Stewart to a contract Saturday.</t>
+          <t>Allgeier could open the regular season as the Cardinals' primary running back, as Adam Schefter of ESPN reports that Jeremiyah Love sustained a high-ankle sprain in Thursday's preseason win over the Raiders.</t>
         </is>
       </c>
     </row>
@@ -32794,27 +32794,27 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Zachariah Branch</t>
+          <t>Gervon Dexter Sr.</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Branch returned a punt for 18 yards during the Falcons' 17-12 preseason win over the Dolphins on Friday.</t>
+          <t>Dexter (hamstring) was traded to the Falcons on Sunday, NFL reporter Jordan Schultz.</t>
         </is>
       </c>
     </row>
@@ -32826,27 +32826,27 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Drake London</t>
+          <t>Da'Shawn Hand</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Leg</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>London played eight snaps on offense and didn't show up in the box score otherwise during the Falcons' 17-12 preseason win over the Dolphins on Friday.</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -32858,27 +32858,27 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Darren Hall</t>
+          <t>Zachariah Branch</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>The Falcons placed Hall (undisclosed) on injured reserve Saturday, Aaron Wilson of KPRC 2 Houston reports.</t>
+          <t>Branch returned a punt for 18 yards during the Falcons' 17-12 preseason win over the Dolphins on Friday.</t>
         </is>
       </c>
     </row>
@@ -32890,12 +32890,12 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Cooper Rush</t>
+          <t>Drake London</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -32910,7 +32910,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Rush completed 13 of his 18 pass attempts for 106 yards and a touchdown in Friday's preseason finale against the Dolphins.</t>
+          <t>London played eight snaps on offense and didn't show up in the box score otherwise during the Falcons' 17-12 preseason win over the Dolphins on Friday.</t>
         </is>
       </c>
     </row>
@@ -32922,27 +32922,27 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Jahan Dotson</t>
+          <t>Darren Hall</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Dotson caught all three of his targets for 27 yards in Friday's 17-12 preseason win over the Dolphins.</t>
+          <t>The Falcons placed Hall (undisclosed) on injured reserve Saturday, Aaron Wilson of KPRC 2 Houston reports.</t>
         </is>
       </c>
     </row>
@@ -32954,12 +32954,12 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Brian Robinson Jr.</t>
+          <t>Cooper Rush</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -32974,7 +32974,7 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>Robinson rushed five times for 14 yards and a touchdown, caught his only target for nine yards and lost a fumble in Friday's 17-12 preseason win over the Dolphins.</t>
+          <t>Rush completed 13 of his 18 pass attempts for 106 yards and a touchdown in Friday's preseason finale against the Dolphins.</t>
         </is>
       </c>
     </row>
@@ -32986,12 +32986,12 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Kyle Pitts Sr.</t>
+          <t>Jahan Dotson</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -33006,7 +33006,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Pitts caught all three of his targets for 59 yards in Friday's 17-12 preseason win over the Dolphins.</t>
+          <t>Dotson caught all three of his targets for 27 yards in Friday's 17-12 preseason win over the Dolphins.</t>
         </is>
       </c>
     </row>
@@ -33018,12 +33018,12 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Tua Tagovailoa</t>
+          <t>Brian Robinson Jr.</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -33038,7 +33038,7 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>Tagovailoa completed seven of eight passes for 95 yards in Friday's 17-12 preseason win over the Dolphins. He also rushed once for no gain and lost a fumble.</t>
+          <t>Robinson rushed five times for 14 yards and a touchdown, caught his only target for nine yards and lost a fumble in Friday's 17-12 preseason win over the Dolphins.</t>
         </is>
       </c>
     </row>
@@ -33050,27 +33050,27 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Michael Penix Jr.</t>
+          <t>Kyle Pitts Sr.</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>Surgery</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Penix (knee) won't play in Friday's preseason game in Miami, but he believes he'll be available for a Week 1 road matchup with the Steelers on Sunday, Sept. 13, Tori McElhaney of the Falcons' official site reports.</t>
+          <t>Pitts caught all three of his targets for 59 yards in Friday's 17-12 preseason win over the Dolphins.</t>
         </is>
       </c>
     </row>
@@ -33082,12 +33082,12 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Nick Folk</t>
+          <t>Tua Tagovailoa</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -33102,7 +33102,7 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Folk made both of his field-goal attempts and all four PAT tries in Saturday's 34-6 preseason win over the Colts.</t>
+          <t>Tagovailoa completed seven of eight passes for 95 yards in Friday's 17-12 preseason win over the Dolphins. He also rushed once for no gain and lost a fumble.</t>
         </is>
       </c>
     </row>
@@ -33114,12 +33114,12 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Kam Dewberry</t>
+          <t>Michael Penix Jr.</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -33129,12 +33129,12 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Surgery</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Dewberry (leg) exited Saturday's preseason game against the Colts early, Tori McElhaney of the Falcons' official site reports.</t>
+          <t>Penix (knee) won't play in Friday's preseason game in Miami, but he believes he'll be available for a Week 1 road matchup with the Steelers on Sunday, Sept. 13, Tori McElhaney of the Falcons' official site reports.</t>
         </is>
       </c>
     </row>
@@ -33146,27 +33146,27 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Trey Sermon</t>
+          <t>Nick Folk</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>The Falcons placed Sermon (undisclosed) on injured reserve Wednesday, Tori McElhaney of the team's official site reports.</t>
+          <t>Folk made both of his field-goal attempts and all four PAT tries in Saturday's 34-6 preseason win over the Colts.</t>
         </is>
       </c>
     </row>
@@ -33178,27 +33178,27 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Divine Deablo</t>
+          <t>Kam Dewberry</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Deablo (ankle) participated during the Falcons' training camp practice Wednesday, D. Orlando Ledbetter of bowtiesports.com reports.</t>
+          <t>Dewberry (leg) exited Saturday's preseason game against the Colts early, Tori McElhaney of the Falcons' official site reports.</t>
         </is>
       </c>
     </row>
@@ -33210,12 +33210,12 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Malik Verdon</t>
+          <t>Trey Sermon</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -33230,7 +33230,7 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>ir</t>
+          <t>The Falcons placed Sermon (undisclosed) on injured reserve Wednesday, Tori McElhaney of the team's official site reports.</t>
         </is>
       </c>
     </row>
@@ -33242,7 +33242,7 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Jalon Walker</t>
+          <t>Divine Deablo</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -33252,17 +33252,17 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>Surgery</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>ir</t>
+          <t>Deablo (ankle) participated during the Falcons' training camp practice Wednesday, D. Orlando Ledbetter of bowtiesports.com reports.</t>
         </is>
       </c>
     </row>
@@ -33274,7 +33274,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>James Pearce Jr.</t>
+          <t>Malik Verdon</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -33284,7 +33284,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Suspension</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -33294,7 +33294,7 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>reserve-sus</t>
+          <t>ir</t>
         </is>
       </c>
     </row>
@@ -33306,25 +33306,29 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Cameron Sample</t>
+          <t>Jalon Walker</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="F46" s="5" t="inlineStr"/>
+          <t>Surgery</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>ir</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -33334,25 +33338,29 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Xavier Watts</t>
+          <t>James Pearce Jr.</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Suspension</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr"/>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>reserve-sus</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -33362,12 +33370,12 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Beaux Collins</t>
+          <t>Cameron Sample</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -33390,12 +33398,12 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Zach Harrison</t>
+          <t>Xavier Watts</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -33418,12 +33426,12 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Za'Darius Smith</t>
+          <t>Beaux Collins</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -33436,11 +33444,7 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>The Falcons signed Smith to a one-year contract Tuesday, Will McFadden of the team's official site reports.</t>
-        </is>
-      </c>
+      <c r="F50" s="5" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -33450,12 +33454,12 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Jessie Bates III</t>
+          <t>Zach Harrison</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -33468,11 +33472,7 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>Bates (back) returned to practice Monday, Josh Kendall of The Athletic reports.</t>
-        </is>
-      </c>
+      <c r="F51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -33482,12 +33482,12 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>DeMarcco Hellams</t>
+          <t>Za'Darius Smith</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -33502,7 +33502,7 @@
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Hellams (hamstring) recorded four tackles (three solo) during the Falcons' 27-7 preseason loss to the Broncos on Friday.</t>
+          <t>The Falcons signed Smith to a one-year contract Tuesday, Will McFadden of the team's official site reports.</t>
         </is>
       </c>
     </row>
@@ -33514,12 +33514,12 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Bijan Robinson</t>
+          <t>Jessie Bates III</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -33534,7 +33534,7 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Robinson did not play in the Falcons' 27-7 preseason loss to the Broncos on Friday.</t>
+          <t>Bates (back) returned to practice Monday, Josh Kendall of The Athletic reports.</t>
         </is>
       </c>
     </row>
@@ -33546,12 +33546,12 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Nick Muse</t>
+          <t>DeMarcco Hellams</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -33566,7 +33566,7 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>The Falcons signed Muse to a contract Tuesday, Tori McElhaney of the team's official site reports.</t>
+          <t>Hellams (hamstring) recorded four tackles (three solo) during the Falcons' 27-7 preseason loss to the Broncos on Friday.</t>
         </is>
       </c>
     </row>
@@ -36142,12 +36142,12 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>Gervon Dexter Sr.</t>
+          <t>Austin Booker</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
@@ -36162,7 +36162,7 @@
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>Dexter (hamstring) is unavailable for Saturday's preseason matchup with the Titans, Brad Biggs of the Chicago Tribune reports.</t>
+          <t>Booker has a groin injury and his status is "week-to-week," Brad Biggs of the Chicago Tribune reports.</t>
         </is>
       </c>
     </row>
@@ -36174,27 +36174,27 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Austin Booker</t>
+          <t>Nephi Sewell</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Concussion</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>Booker has a groin injury and his status is "week-to-week," Brad Biggs of the Chicago Tribune reports.</t>
+          <t>The Bears placed Sewell (concussion) on injured reserve Tuesday.</t>
         </is>
       </c>
     </row>
@@ -36206,7 +36206,7 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>Nephi Sewell</t>
+          <t>Keyshaun Elliott</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
@@ -36216,17 +36216,17 @@
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>Concussion</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>The Bears placed Sewell (concussion) on injured reserve Tuesday.</t>
+          <t>The Bears activated Elliott (undisclosed) from the active/PUP list Tuesday.</t>
         </is>
       </c>
     </row>
@@ -36238,12 +36238,12 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Keyshaun Elliott</t>
+          <t>Elijah Hicks</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
@@ -36258,7 +36258,7 @@
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>The Bears activated Elliott (undisclosed) from the active/PUP list Tuesday.</t>
+          <t>The Bears activated Hicks (shin) from the active/PUP list Tuesday.</t>
         </is>
       </c>
     </row>
@@ -36270,27 +36270,27 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>Elijah Hicks</t>
+          <t>Kalif Raymond</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>The Bears activated Hicks (shin) from the active/PUP list Tuesday.</t>
+          <t>Raymond has made a strong impression in his first five months with Chicago, with Kevin Fishbain of The Athletic relaying coach Ben Johnson's praise Monday and calling him "the most selfless player I've ever been around."</t>
         </is>
       </c>
     </row>
@@ -36302,12 +36302,12 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Kalif Raymond</t>
+          <t>Cairo Santos</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
@@ -36322,7 +36322,7 @@
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>Raymond has made a strong impression in his first five months with Chicago, with Kevin Fishbain of The Athletic relaying coach Ben Johnson's praise Monday and calling him "the most selfless player I've ever been around."</t>
+          <t>Santos connected on field-goal attempts of 45, 26 and 44 yards and missed wide right from 53 yards in the Bears' 27-9 preseason loss to the Bengals on Saturday.</t>
         </is>
       </c>
     </row>
@@ -36334,12 +36334,12 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>Cairo Santos</t>
+          <t>Rome Odunze</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
@@ -36354,7 +36354,7 @@
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>Santos connected on field-goal attempts of 45, 26 and 44 yards and missed wide right from 53 yards in the Bears' 27-9 preseason loss to the Bengals on Saturday.</t>
+          <t>Odunze brought in one of two targets for 18 yards in the Bears' 27-9 preseason loss to the Bengals on Saturday.</t>
         </is>
       </c>
     </row>
@@ -36366,12 +36366,12 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Rome Odunze</t>
+          <t>Colston Loveland</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
@@ -36386,7 +36386,7 @@
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>Odunze brought in one of two targets for 18 yards in the Bears' 27-9 preseason loss to the Bengals on Saturday.</t>
+          <t>Loveland brought in one of three targets for 10 yards in the Bears' 27-9 preseason loss to the Bengals on Saturday.</t>
         </is>
       </c>
     </row>
@@ -36398,12 +36398,12 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>Colston Loveland</t>
+          <t>Caleb Williams</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
@@ -36418,7 +36418,7 @@
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>Loveland brought in one of three targets for 10 yards in the Bears' 27-9 preseason loss to the Bengals on Saturday.</t>
+          <t>Williams completed two of five passes for 28 yards with no touchdowns or interceptions in the Bears' 27-9 preseason loss to the Bengals on Saturday.</t>
         </is>
       </c>
     </row>
@@ -36430,27 +36430,27 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Caleb Williams</t>
+          <t>Tyrique Stevenson</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>Williams completed two of five passes for 28 yards with no touchdowns or interceptions in the Bears' 27-9 preseason loss to the Bengals on Saturday.</t>
+          <t>Stevenson (undisclosed) returned to practice Thursday following a week-long absence, Brad Biggs of the Chicago Tribune reports.</t>
         </is>
       </c>
     </row>
@@ -36462,12 +36462,12 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>Tyrique Stevenson</t>
+          <t>Xavier Woods</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
@@ -36482,7 +36482,7 @@
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
-          <t>Stevenson (undisclosed) returned to practice Thursday following a week-long absence, Brad Biggs of the Chicago Tribune reports.</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -36494,12 +36494,12 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>Xavier Woods</t>
+          <t>Ruben Hyppolite II</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
@@ -36526,17 +36526,17 @@
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>Ruben Hyppolite II</t>
+          <t>Nikola Kalinic</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
@@ -36546,7 +36546,7 @@
       </c>
       <c r="F148" s="5" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>ir</t>
         </is>
       </c>
     </row>
@@ -36558,27 +36558,27 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>Nikola Kalinic</t>
+          <t>Coby Bryant</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Surgery</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>ir</t>
+          <t>out</t>
         </is>
       </c>
     </row>
@@ -36590,27 +36590,27 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>Coby Bryant</t>
+          <t>Dallis Flowers</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>Out</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>Surgery</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F150" s="5" t="inlineStr">
         <is>
-          <t>out</t>
+          <t>ir</t>
         </is>
       </c>
     </row>
@@ -36622,12 +36622,12 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>Dallis Flowers</t>
+          <t>Jonathan Garvin</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
@@ -36654,29 +36654,25 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>Jonathan Garvin</t>
+          <t>Ozzy Trapilo</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>OT</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="F152" s="5" t="inlineStr">
-        <is>
-          <t>ir</t>
-        </is>
-      </c>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F152" s="5" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
@@ -36686,12 +36682,12 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Ozzy Trapilo</t>
+          <t>Dayo Odeyingbo</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>OT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
@@ -36714,25 +36710,29 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>Dayo Odeyingbo</t>
+          <t>Kyle Monangai</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="F154" s="5" t="inlineStr"/>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F154" s="5" t="inlineStr">
+        <is>
+          <t>Monangai (knee) is considered week-to-week, Adam Jahns of AllCHGO.com reports.</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
@@ -42298,7 +42298,7 @@
       </c>
       <c r="F330" s="5" t="inlineStr">
         <is>
-          <t>Allen caught his only target for 24 yards in Saturday's 25-16 preseason loss to the Lions.</t>
+          <t>Allen was arrested early Sunday morning and charged with DUI, FOX59 reports.</t>
         </is>
       </c>
     </row>
@@ -53422,27 +53422,27 @@
       </c>
       <c r="B680" s="5" t="inlineStr">
         <is>
-          <t>Deebo Samuel Sr.</t>
+          <t>George Kittle</t>
         </is>
       </c>
       <c r="C680" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D680" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E680" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Surgery</t>
         </is>
       </c>
       <c r="F680" s="5" t="inlineStr">
         <is>
-          <t>Samuel didn't play in Thursday's preseason victory against Las Vegas.</t>
+          <t>Kittle (Achilles) is expected to practice this week as he continues his push to play in the 49ers' season opener against the Rams in Australia, Adam Schefter of ESPN reports.</t>
         </is>
       </c>
     </row>
@@ -53454,12 +53454,12 @@
       </c>
       <c r="B681" s="4" t="inlineStr">
         <is>
-          <t>Brock Purdy</t>
+          <t>Deebo Samuel Sr.</t>
         </is>
       </c>
       <c r="C681" s="4" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D681" s="4" t="inlineStr">
@@ -53474,7 +53474,7 @@
       </c>
       <c r="F681" s="4" t="inlineStr">
         <is>
-          <t>Purdy sat out Thursday's exhibition win over the Raiders.</t>
+          <t>Samuel didn't play in Thursday's preseason victory against Las Vegas.</t>
         </is>
       </c>
     </row>
@@ -53486,7 +53486,7 @@
       </c>
       <c r="B682" s="5" t="inlineStr">
         <is>
-          <t>Mac Jones</t>
+          <t>Brock Purdy</t>
         </is>
       </c>
       <c r="C682" s="5" t="inlineStr">
@@ -53506,7 +53506,7 @@
       </c>
       <c r="F682" s="5" t="inlineStr">
         <is>
-          <t>Jones completed one of his five pass attempts for seven yards in Thursday night's preseason finale against the Raiders.</t>
+          <t>Purdy sat out Thursday's exhibition win over the Raiders.</t>
         </is>
       </c>
     </row>
@@ -53518,12 +53518,12 @@
       </c>
       <c r="B683" s="4" t="inlineStr">
         <is>
-          <t>Eddy Pineiro</t>
+          <t>Mac Jones</t>
         </is>
       </c>
       <c r="C683" s="4" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D683" s="4" t="inlineStr">
@@ -53538,7 +53538,7 @@
       </c>
       <c r="F683" s="4" t="inlineStr">
         <is>
-          <t>Pineiro made all six of his field-goal attempts in Thursday night's 18-12 preseason win over the Raiders.</t>
+          <t>Jones completed one of his five pass attempts for seven yards in Thursday night's preseason finale against the Raiders.</t>
         </is>
       </c>
     </row>
@@ -53550,12 +53550,12 @@
       </c>
       <c r="B684" s="5" t="inlineStr">
         <is>
-          <t>Jordan Watkins</t>
+          <t>Eddy Pineiro</t>
         </is>
       </c>
       <c r="C684" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="D684" s="5" t="inlineStr">
@@ -53570,7 +53570,7 @@
       </c>
       <c r="F684" s="5" t="inlineStr">
         <is>
-          <t>Watkins caught four of eight targets for 64 yards in Thursday night's 18-12 preseason win over the Raiders.</t>
+          <t>Pineiro made all six of his field-goal attempts in Thursday night's 18-12 preseason win over the Raiders.</t>
         </is>
       </c>
     </row>
@@ -53582,12 +53582,12 @@
       </c>
       <c r="B685" s="4" t="inlineStr">
         <is>
-          <t>Jordan James</t>
+          <t>Jordan Watkins</t>
         </is>
       </c>
       <c r="C685" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D685" s="4" t="inlineStr">
@@ -53602,7 +53602,7 @@
       </c>
       <c r="F685" s="4" t="inlineStr">
         <is>
-          <t>James (ribs) rushed eight times for 35 yards and brought in one of two targets for 20 yards in the 49ers' 18-12 preseason win over the Raiders on Thursday.</t>
+          <t>Watkins caught four of eight targets for 64 yards in Thursday night's 18-12 preseason win over the Raiders.</t>
         </is>
       </c>
     </row>
@@ -53614,7 +53614,7 @@
       </c>
       <c r="B686" s="5" t="inlineStr">
         <is>
-          <t>Kaelon Black</t>
+          <t>Jordan James</t>
         </is>
       </c>
       <c r="C686" s="5" t="inlineStr">
@@ -53634,7 +53634,7 @@
       </c>
       <c r="F686" s="5" t="inlineStr">
         <is>
-          <t>Black rushed four times for 28 yards and failed to bring in his only target in the 49ers' 18-12 preseason win over the Raiders on Thursday.</t>
+          <t>James (ribs) rushed eight times for 35 yards and brought in one of two targets for 20 yards in the 49ers' 18-12 preseason win over the Raiders on Thursday.</t>
         </is>
       </c>
     </row>
@@ -53646,27 +53646,27 @@
       </c>
       <c r="B687" s="4" t="inlineStr">
         <is>
-          <t>Brayden Willis</t>
+          <t>Kaelon Black</t>
         </is>
       </c>
       <c r="C687" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D687" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E687" s="4" t="inlineStr">
         <is>
-          <t>Concussion</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F687" s="4" t="inlineStr">
         <is>
-          <t>Willis (concussion) has been ruled out for the remainder of Thursday's preseason matchup with the Raiders, Noah Furtado of the San Francisco Chronicle reports.</t>
+          <t>Black rushed four times for 28 yards and failed to bring in his only target in the 49ers' 18-12 preseason win over the Raiders on Thursday.</t>
         </is>
       </c>
     </row>
@@ -53678,12 +53678,12 @@
       </c>
       <c r="B688" s="5" t="inlineStr">
         <is>
-          <t>Ephesians Prysock</t>
+          <t>Brayden Willis</t>
         </is>
       </c>
       <c r="C688" s="5" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D688" s="5" t="inlineStr">
@@ -53693,12 +53693,12 @@
       </c>
       <c r="E688" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Concussion</t>
         </is>
       </c>
       <c r="F688" s="5" t="inlineStr">
         <is>
-          <t>Prysock suffered a shoulder injury and will not return to Thursday's preseason matchup with the Raiders, Noah Furtado of the San Francisco Chronicle reports.</t>
+          <t>Willis (concussion) has been ruled out for the remainder of Thursday's preseason matchup with the Raiders, Noah Furtado of the San Francisco Chronicle reports.</t>
         </is>
       </c>
     </row>
@@ -53710,17 +53710,17 @@
       </c>
       <c r="B689" s="4" t="inlineStr">
         <is>
-          <t>Victor Dimukeje</t>
+          <t>Ephesians Prysock</t>
         </is>
       </c>
       <c r="C689" s="4" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D689" s="4" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E689" s="4" t="inlineStr">
@@ -53730,7 +53730,7 @@
       </c>
       <c r="F689" s="4" t="inlineStr">
         <is>
-          <t>Dimukeje (undisclosed) was placed on injured reserve by the 49ers on Thursday.</t>
+          <t>Prysock suffered a shoulder injury and will not return to Thursday's preseason matchup with the Raiders, Noah Furtado of the San Francisco Chronicle reports.</t>
         </is>
       </c>
     </row>
@@ -53742,27 +53742,27 @@
       </c>
       <c r="B690" s="5" t="inlineStr">
         <is>
-          <t>Jah Joyner</t>
+          <t>Victor Dimukeje</t>
         </is>
       </c>
       <c r="C690" s="5" t="inlineStr">
         <is>
-          <t>DL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D690" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E690" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F690" s="5" t="inlineStr">
         <is>
-          <t>Joyner signed with the 49ers on Thursday.</t>
+          <t>Dimukeje (undisclosed) was placed on injured reserve by the 49ers on Thursday.</t>
         </is>
       </c>
     </row>
@@ -53774,27 +53774,27 @@
       </c>
       <c r="B691" s="4" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Jah Joyner</t>
         </is>
       </c>
       <c r="C691" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>DL</t>
         </is>
       </c>
       <c r="D691" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E691" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F691" s="4" t="inlineStr">
         <is>
-          <t>Stribling (shoulder) won't suit up for Thursday's preseason contest at Las Vegas, David Lombardi of SFStandard.com reports.</t>
+          <t>Joyner signed with the 49ers on Thursday.</t>
         </is>
       </c>
     </row>
@@ -53806,7 +53806,7 @@
       </c>
       <c r="B692" s="5" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="C692" s="5" t="inlineStr">
@@ -53826,7 +53826,7 @@
       </c>
       <c r="F692" s="5" t="inlineStr">
         <is>
-          <t>Evans' groin injury is considered minor, and he plans to be ready for the 49ers' Week 1 regular-season opener against the Rams on Thursday, Sept. 10, Jeremy Fowler of ESPN reports.</t>
+          <t>Stribling (shoulder) won't suit up for Thursday's preseason contest at Las Vegas, David Lombardi of SFStandard.com reports.</t>
         </is>
       </c>
     </row>
@@ -53838,12 +53838,12 @@
       </c>
       <c r="B693" s="4" t="inlineStr">
         <is>
-          <t>Robert Jones</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="C693" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D693" s="4" t="inlineStr">
@@ -53858,7 +53858,7 @@
       </c>
       <c r="F693" s="4" t="inlineStr">
         <is>
-          <t>Jones (calf) did not participate at the 49ers' training camp practice Tuesday, Nick Wagoner of ESPN.com reports.</t>
+          <t>Evans' groin injury is considered minor, and he plans to be ready for the 49ers' Week 1 regular-season opener against the Rams on Thursday, Sept. 10, Jeremy Fowler of ESPN reports.</t>
         </is>
       </c>
     </row>
@@ -53870,12 +53870,12 @@
       </c>
       <c r="B694" s="5" t="inlineStr">
         <is>
-          <t>Kurtis Rourke</t>
+          <t>Robert Jones</t>
         </is>
       </c>
       <c r="C694" s="5" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D694" s="5" t="inlineStr">
@@ -53890,7 +53890,7 @@
       </c>
       <c r="F694" s="5" t="inlineStr">
         <is>
-          <t>Coach Kyle Shanahan said Tuesday that Rourke (ribs) has a chance to return to the field next week, Nick Wagoner of ESPN.com reports.</t>
+          <t>Jones (calf) did not participate at the 49ers' training camp practice Tuesday, Nick Wagoner of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -53902,12 +53902,12 @@
       </c>
       <c r="B695" s="4" t="inlineStr">
         <is>
-          <t>Upton Stout</t>
+          <t>Kurtis Rourke</t>
         </is>
       </c>
       <c r="C695" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D695" s="4" t="inlineStr">
@@ -53922,7 +53922,7 @@
       </c>
       <c r="F695" s="4" t="inlineStr">
         <is>
-          <t>Stout (hip) did not participate at the 49ers' training camp practice Tuesday, Nick Wagoner of ESPN.com reports.</t>
+          <t>Coach Kyle Shanahan said Tuesday that Rourke (ribs) has a chance to return to the field next week, Nick Wagoner of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -53934,12 +53934,12 @@
       </c>
       <c r="B696" s="5" t="inlineStr">
         <is>
-          <t>Jacob Cowing</t>
+          <t>Upton Stout</t>
         </is>
       </c>
       <c r="C696" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D696" s="5" t="inlineStr">
@@ -53954,7 +53954,7 @@
       </c>
       <c r="F696" s="5" t="inlineStr">
         <is>
-          <t>Cowing (groin) did not participate at the 49ers' training camp practice Tuesday, Nick Wagoner of ESPN.com reports.</t>
+          <t>Stout (hip) did not participate at the 49ers' training camp practice Tuesday, Nick Wagoner of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -53966,27 +53966,27 @@
       </c>
       <c r="B697" s="4" t="inlineStr">
         <is>
-          <t>Deion Jones</t>
+          <t>Jacob Cowing</t>
         </is>
       </c>
       <c r="C697" s="4" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D697" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E697" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F697" s="4" t="inlineStr">
         <is>
-          <t>Jones was traded from the Saints to the 49ers in exchange for running back Zamir White on Sunday, Adam Schefter of ESPN reports.</t>
+          <t>Cowing (groin) did not participate at the 49ers' training camp practice Tuesday, Nick Wagoner of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -53998,27 +53998,27 @@
       </c>
       <c r="B698" s="5" t="inlineStr">
         <is>
-          <t>Romello Height</t>
+          <t>Deion Jones</t>
         </is>
       </c>
       <c r="C698" s="5" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D698" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E698" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F698" s="5" t="inlineStr">
         <is>
-          <t>Height (undisclosed) did not participate in Sunday's practice, Nick Wagoner of ESPN.com reports.</t>
+          <t>Jones was traded from the Saints to the 49ers in exchange for running back Zamir White on Sunday, Adam Schefter of ESPN reports.</t>
         </is>
       </c>
     </row>
@@ -54030,12 +54030,12 @@
       </c>
       <c r="B699" s="4" t="inlineStr">
         <is>
-          <t>Christian McCaffrey</t>
+          <t>Romello Height</t>
         </is>
       </c>
       <c r="C699" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D699" s="4" t="inlineStr">
@@ -54050,7 +54050,7 @@
       </c>
       <c r="F699" s="4" t="inlineStr">
         <is>
-          <t>McCaffrey (undisclosed) said Sunday that he always planned to take a break during training camp and then "ramp back up," Vic Tafur of The Athletic reports.</t>
+          <t>Height (undisclosed) did not participate in Sunday's practice, Nick Wagoner of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -54062,27 +54062,27 @@
       </c>
       <c r="B700" s="5" t="inlineStr">
         <is>
-          <t>Deommodore Lenoir</t>
+          <t>Christian McCaffrey</t>
         </is>
       </c>
       <c r="C700" s="5" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D700" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E700" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F700" s="5" t="inlineStr">
         <is>
-          <t>Lenoir (shoulder) participated in Sunday's training camp practice, Noah Furtado of the San Francisco Chronicle reports.</t>
+          <t>McCaffrey (undisclosed) said Sunday that he always planned to take a break during training camp and then "ramp back up," Vic Tafur of The Athletic reports.</t>
         </is>
       </c>
     </row>
@@ -54094,27 +54094,27 @@
       </c>
       <c r="B701" s="4" t="inlineStr">
         <is>
-          <t>George Kittle</t>
+          <t>Deommodore Lenoir</t>
         </is>
       </c>
       <c r="C701" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D701" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E701" s="4" t="inlineStr">
         <is>
-          <t>Surgery</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F701" s="4" t="inlineStr">
         <is>
-          <t>Kittle (Achilles) was activated from the active/PUP list Sunday.</t>
+          <t>Lenoir (shoulder) participated in Sunday's training camp practice, Noah Furtado of the San Francisco Chronicle reports.</t>
         </is>
       </c>
     </row>
@@ -54222,12 +54222,12 @@
       </c>
       <c r="B705" s="4" t="inlineStr">
         <is>
-          <t>Jalen Milroe</t>
+          <t>Jason Myers</t>
         </is>
       </c>
       <c r="C705" s="4" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="D705" s="4" t="inlineStr">
@@ -54242,7 +54242,7 @@
       </c>
       <c r="F705" s="4" t="inlineStr">
         <is>
-          <t>Milroe completed 16 of 26 pass attempts for 223 yards and one touchdown without any interceptions in Friday's 9-9 preseason tie versus Kansas City.</t>
+          <t>Myers went 1-for-2 on field-goal attempts and missed his lone PAT try in Friday's 9-9 preseason tie against the Chiefs.</t>
         </is>
       </c>
     </row>
@@ -54254,27 +54254,27 @@
       </c>
       <c r="B706" s="5" t="inlineStr">
         <is>
-          <t>Terrion Arnold</t>
+          <t>Jalen Milroe</t>
         </is>
       </c>
       <c r="C706" s="5" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D706" s="5" t="inlineStr">
         <is>
-          <t>Out</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E706" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F706" s="5" t="inlineStr">
         <is>
-          <t>Arnold signed a contract with the Seahawks on Saturday.</t>
+          <t>Milroe completed 16 of 26 pass attempts for 223 yards and one touchdown without any interceptions in Friday's 9-9 preseason tie versus Kansas City.</t>
         </is>
       </c>
     </row>
@@ -54286,27 +54286,27 @@
       </c>
       <c r="B707" s="4" t="inlineStr">
         <is>
-          <t>Elijah Arroyo</t>
+          <t>Terrion Arnold</t>
         </is>
       </c>
       <c r="C707" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D707" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="E707" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F707" s="4" t="inlineStr">
         <is>
-          <t>Arroyo secured his only target for a 24-yard reception in the Seahawks' 9-9 preseason tie with the Chiefs on Friday.</t>
+          <t>Arnold signed a contract with the Seahawks on Saturday.</t>
         </is>
       </c>
     </row>
@@ -54318,12 +54318,12 @@
       </c>
       <c r="B708" s="5" t="inlineStr">
         <is>
-          <t>Emmanuel Henderson Jr.</t>
+          <t>Elijah Arroyo</t>
         </is>
       </c>
       <c r="C708" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D708" s="5" t="inlineStr">
@@ -54338,7 +54338,7 @@
       </c>
       <c r="F708" s="5" t="inlineStr">
         <is>
-          <t>Henderson secured three of four targets for 58 yards and returned two kickoffs for 41 yards in the Seahawks' 9-9 tie with the Chiefs on Friday.</t>
+          <t>Arroyo secured his only target for a 24-yard reception in the Seahawks' 9-9 preseason tie with the Chiefs on Friday.</t>
         </is>
       </c>
     </row>
@@ -54350,27 +54350,27 @@
       </c>
       <c r="B709" s="4" t="inlineStr">
         <is>
-          <t>Chris Paul Jr.</t>
+          <t>Emmanuel Henderson Jr.</t>
         </is>
       </c>
       <c r="C709" s="4" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D709" s="4" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E709" s="4" t="inlineStr">
         <is>
-          <t>Undisclosed</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F709" s="4" t="inlineStr">
         <is>
-          <t>Paul (undisclosed) reverted to the Seahawks' injured reserve list Friday, per the NFL's transaction log.</t>
+          <t>Henderson secured three of four targets for 58 yards and returned two kickoffs for 41 yards in the Seahawks' 9-9 tie with the Chiefs on Friday.</t>
         </is>
       </c>
     </row>
@@ -54382,27 +54382,27 @@
       </c>
       <c r="B710" s="5" t="inlineStr">
         <is>
-          <t>Tory Horton</t>
+          <t>Chris Paul Jr.</t>
         </is>
       </c>
       <c r="C710" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D710" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E710" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Undisclosed</t>
         </is>
       </c>
       <c r="F710" s="5" t="inlineStr">
         <is>
-          <t>Horton (undisclosed) is not dealing with a long-term injury, Corbin K. Smith of SI.com reports.</t>
+          <t>Paul (undisclosed) reverted to the Seahawks' injured reserve list Friday, per the NFL's transaction log.</t>
         </is>
       </c>
     </row>
@@ -54414,27 +54414,27 @@
       </c>
       <c r="B711" s="4" t="inlineStr">
         <is>
-          <t>Jadarian Price</t>
+          <t>Tory Horton</t>
         </is>
       </c>
       <c r="C711" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D711" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E711" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F711" s="4" t="inlineStr">
         <is>
-          <t>Price will not play in Friday's preseason finale against the Chiefs, Brady Henderson of ESPN.com reports.</t>
+          <t>Horton (undisclosed) is not dealing with a long-term injury, Corbin K. Smith of SI.com reports.</t>
         </is>
       </c>
     </row>
@@ -54446,12 +54446,12 @@
       </c>
       <c r="B712" s="5" t="inlineStr">
         <is>
-          <t>Leonard Williams</t>
+          <t>Jadarian Price</t>
         </is>
       </c>
       <c r="C712" s="5" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D712" s="5" t="inlineStr">
@@ -54466,7 +54466,7 @@
       </c>
       <c r="F712" s="5" t="inlineStr">
         <is>
-          <t>Williams has agreed to a three-year, $90 million contract extension with the Seahawks, Ian Rapoport of ESPN and NFL Network reports.</t>
+          <t>Price will not play in Friday's preseason finale against the Chiefs, Brady Henderson of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -54478,12 +54478,12 @@
       </c>
       <c r="B713" s="4" t="inlineStr">
         <is>
-          <t>Justin Jones</t>
+          <t>Leonard Williams</t>
         </is>
       </c>
       <c r="C713" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="D713" s="4" t="inlineStr">
@@ -54498,7 +54498,7 @@
       </c>
       <c r="F713" s="4" t="inlineStr">
         <is>
-          <t>The Seahawks signed Jones to a contract Wednesday, Aaron Wilson of KPRC 2 Houston reports.</t>
+          <t>Williams has agreed to a three-year, $90 million contract extension with the Seahawks, Ian Rapoport of ESPN and NFL Network reports.</t>
         </is>
       </c>
     </row>
@@ -54510,27 +54510,27 @@
       </c>
       <c r="B714" s="5" t="inlineStr">
         <is>
-          <t>Mason Richman</t>
+          <t>Justin Jones</t>
         </is>
       </c>
       <c r="C714" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D714" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E714" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F714" s="5" t="inlineStr">
         <is>
-          <t>The Seahawks placed Richman (leg) on injured reserve Tuesday, Brady Henderson of ESPN.com reports.</t>
+          <t>The Seahawks signed Jones to a contract Wednesday, Aaron Wilson of KPRC 2 Houston reports.</t>
         </is>
       </c>
     </row>
@@ -54542,12 +54542,12 @@
       </c>
       <c r="B715" s="4" t="inlineStr">
         <is>
-          <t>Bud Clark</t>
+          <t>Mason Richman</t>
         </is>
       </c>
       <c r="C715" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D715" s="4" t="inlineStr">
@@ -54557,12 +54557,12 @@
       </c>
       <c r="E715" s="4" t="inlineStr">
         <is>
-          <t>Fracture</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F715" s="4" t="inlineStr">
         <is>
-          <t>The Seahawks placed Clark (ankle) on injured reserve Tuesday, Brady Henderson of ESPN.com reports.</t>
+          <t>The Seahawks placed Richman (leg) on injured reserve Tuesday, Brady Henderson of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -54574,7 +54574,7 @@
       </c>
       <c r="B716" s="5" t="inlineStr">
         <is>
-          <t>Rodney Thomas II</t>
+          <t>Bud Clark</t>
         </is>
       </c>
       <c r="C716" s="5" t="inlineStr">
@@ -54584,17 +54584,17 @@
       </c>
       <c r="D716" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E716" s="5" t="inlineStr">
         <is>
-          <t>Surgery</t>
+          <t>Fracture</t>
         </is>
       </c>
       <c r="F716" s="5" t="inlineStr">
         <is>
-          <t>Thomas (hand) might be able to play in Seattle's preseason finale versus Kansas City on Friday, Brady Henderson of ESPN reports.</t>
+          <t>The Seahawks placed Clark (ankle) on injured reserve Tuesday, Brady Henderson of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -54606,27 +54606,27 @@
       </c>
       <c r="B717" s="4" t="inlineStr">
         <is>
-          <t>Drew Lock</t>
+          <t>Rodney Thomas II</t>
         </is>
       </c>
       <c r="C717" s="4" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D717" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E717" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Surgery</t>
         </is>
       </c>
       <c r="F717" s="4" t="inlineStr">
         <is>
-          <t>Lock completed 12 of 14 passes for 103 yards and a touchdown while rushing twice for eight yards in Sunday's 19-16 preseason loss to the Titans.</t>
+          <t>Thomas (hand) might be able to play in Seattle's preseason finale versus Kansas City on Friday, Brady Henderson of ESPN reports.</t>
         </is>
       </c>
     </row>
@@ -54638,12 +54638,12 @@
       </c>
       <c r="B718" s="5" t="inlineStr">
         <is>
-          <t>Julian Hicks</t>
+          <t>Drew Lock</t>
         </is>
       </c>
       <c r="C718" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D718" s="5" t="inlineStr">
@@ -54658,7 +54658,7 @@
       </c>
       <c r="F718" s="5" t="inlineStr">
         <is>
-          <t>The Seahawks signed Hicks to a contract Saturday, John Boyle of the team's official site reports.</t>
+          <t>Lock completed 12 of 14 passes for 103 yards and a touchdown while rushing twice for eight yards in Sunday's 19-16 preseason loss to the Titans.</t>
         </is>
       </c>
     </row>
@@ -54670,7 +54670,7 @@
       </c>
       <c r="B719" s="4" t="inlineStr">
         <is>
-          <t>Jake Bobo</t>
+          <t>Julian Hicks</t>
         </is>
       </c>
       <c r="C719" s="4" t="inlineStr">
@@ -54680,17 +54680,17 @@
       </c>
       <c r="D719" s="4" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E719" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F719" s="4" t="inlineStr">
         <is>
-          <t>The Seahawks placed Bobo (knee) on injured reserve Saturday, John Boyle of the team's official site reports.</t>
+          <t>The Seahawks signed Hicks to a contract Saturday, John Boyle of the team's official site reports.</t>
         </is>
       </c>
     </row>
@@ -54702,27 +54702,27 @@
       </c>
       <c r="B720" s="5" t="inlineStr">
         <is>
-          <t>Trevon Diggs</t>
+          <t>Jake Bobo</t>
         </is>
       </c>
       <c r="C720" s="5" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D720" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E720" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F720" s="5" t="inlineStr">
         <is>
-          <t>The Seahawks are slated to sign Diggs to a one-year deal, Adam Schefter of ESPN reports.</t>
+          <t>The Seahawks placed Bobo (knee) on injured reserve Saturday, John Boyle of the team's official site reports.</t>
         </is>
       </c>
     </row>
@@ -54734,27 +54734,27 @@
       </c>
       <c r="B721" s="4" t="inlineStr">
         <is>
-          <t>Emanuel Wilson</t>
+          <t>Trevon Diggs</t>
         </is>
       </c>
       <c r="C721" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D721" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E721" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F721" s="4" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>The Seahawks are slated to sign Diggs to a one-year deal, Adam Schefter of ESPN reports.</t>
         </is>
       </c>
     </row>
@@ -54766,17 +54766,17 @@
       </c>
       <c r="B722" s="5" t="inlineStr">
         <is>
-          <t>Robbie Ouzts</t>
+          <t>Emanuel Wilson</t>
         </is>
       </c>
       <c r="C722" s="5" t="inlineStr">
         <is>
-          <t>FB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D722" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E722" s="5" t="inlineStr">
@@ -54786,7 +54786,7 @@
       </c>
       <c r="F722" s="5" t="inlineStr">
         <is>
-          <t>ir</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -54798,27 +54798,27 @@
       </c>
       <c r="B723" s="4" t="inlineStr">
         <is>
-          <t>Nick Emmanwori</t>
+          <t>Robbie Ouzts</t>
         </is>
       </c>
       <c r="C723" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="D723" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E723" s="4" t="inlineStr">
         <is>
-          <t>Surgery</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F723" s="4" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>ir</t>
         </is>
       </c>
     </row>
@@ -54830,27 +54830,27 @@
       </c>
       <c r="B724" s="5" t="inlineStr">
         <is>
-          <t>Montorie Foster Jr.</t>
+          <t>Nick Emmanwori</t>
         </is>
       </c>
       <c r="C724" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D724" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E724" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Surgery</t>
         </is>
       </c>
       <c r="F724" s="5" t="inlineStr">
         <is>
-          <t>Foster caught five of seven targets for 36 yards and a touchdown in Saturday's 17-7 preseason loss to the Cowboys, building on what has been a strong performance in training camp, John Boyle of the Seahawks' official site reports.</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -54862,7 +54862,7 @@
       </c>
       <c r="B725" s="4" t="inlineStr">
         <is>
-          <t>Rashid Shaheed</t>
+          <t>Montorie Foster Jr.</t>
         </is>
       </c>
       <c r="C725" s="4" t="inlineStr">
@@ -54882,7 +54882,7 @@
       </c>
       <c r="F725" s="4" t="inlineStr">
         <is>
-          <t>Shaheed didn't suit up for Saturday's 17-7 preseason loss to the Cowboys.</t>
+          <t>Foster caught five of seven targets for 36 yards and a touchdown in Saturday's 17-7 preseason loss to the Cowboys, building on what has been a strong performance in training camp, John Boyle of the Seahawks' official site reports.</t>
         </is>
       </c>
     </row>
@@ -54894,12 +54894,12 @@
       </c>
       <c r="B726" s="5" t="inlineStr">
         <is>
-          <t>AJ Barner</t>
+          <t>Rashid Shaheed</t>
         </is>
       </c>
       <c r="C726" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D726" s="5" t="inlineStr">
@@ -54914,7 +54914,7 @@
       </c>
       <c r="F726" s="5" t="inlineStr">
         <is>
-          <t>Barner was rested for Seattle's 17-7 preseason loss to the Cowboys on Saturday.</t>
+          <t>Shaheed didn't suit up for Saturday's 17-7 preseason loss to the Cowboys.</t>
         </is>
       </c>
     </row>
@@ -54926,27 +54926,27 @@
       </c>
       <c r="B727" s="4" t="inlineStr">
         <is>
-          <t>Zach Charbonnet</t>
+          <t>AJ Barner</t>
         </is>
       </c>
       <c r="C727" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D727" s="4" t="inlineStr">
         <is>
-          <t>Out</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E727" s="4" t="inlineStr">
         <is>
-          <t>Surgery</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F727" s="4" t="inlineStr">
         <is>
-          <t>Charbonnet (knee) remains on the active/PUP list as the Seahawks' second preseason contest (Sunday, Aug. 23 versus the Titans) approaches.</t>
+          <t>Barner was rested for Seattle's 17-7 preseason loss to the Cowboys on Saturday.</t>
         </is>
       </c>
     </row>
@@ -54958,27 +54958,27 @@
       </c>
       <c r="B728" s="5" t="inlineStr">
         <is>
-          <t>Jason Myers</t>
+          <t>Zach Charbonnet</t>
         </is>
       </c>
       <c r="C728" s="5" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D728" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="E728" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Surgery</t>
         </is>
       </c>
       <c r="F728" s="5" t="inlineStr">
         <is>
-          <t>Myers missed his only field-goal attempt from 45 yards out and made his only extra-point try in the Seahawks' 17-7 preseason loss to the Cowboys on Saturday.</t>
+          <t>Charbonnet (knee) remains on the active/PUP list as the Seahawks' second preseason contest (Sunday, Aug. 23 versus the Titans) approaches.</t>
         </is>
       </c>
     </row>
@@ -55022,27 +55022,27 @@
       </c>
       <c r="B730" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Kamara</t>
+          <t>Jalon Daniels</t>
         </is>
       </c>
       <c r="C730" s="5" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D730" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E730" s="5" t="inlineStr">
         <is>
-          <t>Sprain</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F730" s="5" t="inlineStr">
         <is>
-          <t>Kamara (knee) will undergo an MRI on Saturday to determine the severity of his injury, Jenna Laine of ESPN.com reports.</t>
+          <t>Daniels is moving forward as Tampa Bay's backup quarterback behind Baker Mayfield after impressing throughout training camp, Ian Rapoport of NFL Network reports.</t>
         </is>
       </c>
     </row>
@@ -55054,12 +55054,12 @@
       </c>
       <c r="B731" s="4" t="inlineStr">
         <is>
-          <t>Josh Hayes</t>
+          <t>Mohamed Kamara</t>
         </is>
       </c>
       <c r="C731" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D731" s="4" t="inlineStr">
@@ -55069,12 +55069,12 @@
       </c>
       <c r="E731" s="4" t="inlineStr">
         <is>
-          <t>Surgery</t>
+          <t>Sprain</t>
         </is>
       </c>
       <c r="F731" s="4" t="inlineStr">
         <is>
-          <t>Hayes (knee) underwent a procedure Saturday that will sideline him for the start of the 2026 regular season, Greg Auman of Fox Sports reports.</t>
+          <t>Kamara (knee) will undergo an MRI on Saturday to determine the severity of his injury, Jenna Laine of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -55086,12 +55086,12 @@
       </c>
       <c r="B732" s="5" t="inlineStr">
         <is>
-          <t>Jalen McMillan</t>
+          <t>Josh Hayes</t>
         </is>
       </c>
       <c r="C732" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D732" s="5" t="inlineStr">
@@ -55101,12 +55101,12 @@
       </c>
       <c r="E732" s="5" t="inlineStr">
         <is>
-          <t>Soreness</t>
+          <t>Surgery</t>
         </is>
       </c>
       <c r="F732" s="5" t="inlineStr">
         <is>
-          <t>Head coach Todd Bowles said Saturday that he expects McMillan (knee) to be available for the Buccaneers' Week 1 clash against the Bengals on Sunday, Sept. 13, Greg Auman of Fox Sports reports.</t>
+          <t>Hayes (knee) underwent a procedure Saturday that will sideline him for the start of the 2026 regular season, Greg Auman of Fox Sports reports.</t>
         </is>
       </c>
     </row>
@@ -55118,7 +55118,7 @@
       </c>
       <c r="B733" s="4" t="inlineStr">
         <is>
-          <t>Emeka Egbuka</t>
+          <t>Jalen McMillan</t>
         </is>
       </c>
       <c r="C733" s="4" t="inlineStr">
@@ -55133,12 +55133,12 @@
       </c>
       <c r="E733" s="4" t="inlineStr">
         <is>
-          <t>Sprain</t>
+          <t>Soreness</t>
         </is>
       </c>
       <c r="F733" s="4" t="inlineStr">
         <is>
-          <t>Egbuka (toe), per head coach Todd Bowles, will "hopefully" be ready for Week 1, Greg Auman of Fox Sports reports.</t>
+          <t>Head coach Todd Bowles said Saturday that he expects McMillan (knee) to be available for the Buccaneers' Week 1 clash against the Bengals on Sunday, Sept. 13, Greg Auman of Fox Sports reports.</t>
         </is>
       </c>
     </row>
@@ -55150,7 +55150,7 @@
       </c>
       <c r="B734" s="5" t="inlineStr">
         <is>
-          <t>Tez Johnson</t>
+          <t>Emeka Egbuka</t>
         </is>
       </c>
       <c r="C734" s="5" t="inlineStr">
@@ -55160,17 +55160,17 @@
       </c>
       <c r="D734" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E734" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Sprain</t>
         </is>
       </c>
       <c r="F734" s="5" t="inlineStr">
         <is>
-          <t>Johnson secured one of three targets for nine yards in the Buccaneers' 19-0 preseason loss to the Jaguars on Friday.</t>
+          <t>Egbuka (toe), per head coach Todd Bowles, will "hopefully" be ready for Week 1, Greg Auman of Fox Sports reports.</t>
         </is>
       </c>
     </row>
@@ -55182,12 +55182,12 @@
       </c>
       <c r="B735" s="4" t="inlineStr">
         <is>
-          <t>Sean Tucker</t>
+          <t>Tez Johnson</t>
         </is>
       </c>
       <c r="C735" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D735" s="4" t="inlineStr">
@@ -55202,7 +55202,7 @@
       </c>
       <c r="F735" s="4" t="inlineStr">
         <is>
-          <t>Tucker rushed five times for 15 yards and secured his only target for minus-1 yard in the Buccaneers' 19-0 preseason loss to the Jaguars on Friday.</t>
+          <t>Johnson secured one of three targets for nine yards in the Buccaneers' 19-0 preseason loss to the Jaguars on Friday.</t>
         </is>
       </c>
     </row>
@@ -55214,12 +55214,12 @@
       </c>
       <c r="B736" s="5" t="inlineStr">
         <is>
-          <t>Jalon Daniels</t>
+          <t>Sean Tucker</t>
         </is>
       </c>
       <c r="C736" s="5" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D736" s="5" t="inlineStr">
@@ -55234,7 +55234,7 @@
       </c>
       <c r="F736" s="5" t="inlineStr">
         <is>
-          <t>Daniels completed eight of 15 passes for 57 yards with no touchdowns or interceptions and rushed four times for nine yards in the Buccaneers' 19-0 preseason loss to the Jaguars on Friday. He also lost a fumble.</t>
+          <t>Tucker rushed five times for 15 yards and secured his only target for minus-1 yard in the Buccaneers' 19-0 preseason loss to the Jaguars on Friday.</t>
         </is>
       </c>
     </row>
@@ -55786,12 +55786,12 @@
       </c>
       <c r="B754" s="5" t="inlineStr">
         <is>
-          <t>Jake Browning</t>
+          <t>Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="C754" s="5" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D754" s="5" t="inlineStr">
@@ -55806,7 +55806,7 @@
       </c>
       <c r="F754" s="5" t="inlineStr">
         <is>
-          <t>Browning (back) practiced Monday after missing Friday's preseason game against the Jets, Rick Stroud of the Tampa Bay Times reports.</t>
+          <t>Godwin didn't play in Friday's 24-16 preseason victory over the Jets.</t>
         </is>
       </c>
     </row>
@@ -57524,10 +57524,10 @@
         <v>6.9</v>
       </c>
       <c r="F5" s="17" t="n">
-        <v>8.300000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="G5" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
@@ -57565,7 +57565,7 @@
         <v>30</v>
       </c>
       <c r="G6" s="19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
@@ -57604,7 +57604,7 @@
         <v>7.4</v>
       </c>
       <c r="F7" s="17" t="n">
-        <v>9.6</v>
+        <v>13.2</v>
       </c>
       <c r="G7" s="17" t="n">
         <v>10</v>
@@ -57642,10 +57642,10 @@
         <v>5.3</v>
       </c>
       <c r="F8" s="19" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="G8" s="19" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
@@ -57680,10 +57680,10 @@
         <v>7.7</v>
       </c>
       <c r="F9" s="17" t="n">
-        <v>8.300000000000001</v>
+        <v>11.4</v>
       </c>
       <c r="G9" s="17" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
@@ -57718,10 +57718,10 @@
         <v>3.1</v>
       </c>
       <c r="F10" s="19" t="n">
-        <v>15</v>
+        <v>5.1</v>
       </c>
       <c r="G10" s="19" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
@@ -57756,10 +57756,10 @@
         <v>10.1</v>
       </c>
       <c r="F11" s="17" t="n">
-        <v>17.2</v>
+        <v>9.4</v>
       </c>
       <c r="G11" s="17" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
@@ -57794,10 +57794,10 @@
         <v>3.9</v>
       </c>
       <c r="F12" s="19" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="G12" s="19" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
@@ -57836,10 +57836,10 @@
         <v>4.3</v>
       </c>
       <c r="F13" s="17" t="n">
-        <v>5.6</v>
+        <v>6.9</v>
       </c>
       <c r="G13" s="17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
@@ -57874,10 +57874,10 @@
         <v>2.5</v>
       </c>
       <c r="F14" s="19" t="n">
-        <v>5.1</v>
+        <v>3.6</v>
       </c>
       <c r="G14" s="19" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
@@ -57915,7 +57915,7 @@
         <v>4.5</v>
       </c>
       <c r="G15" s="17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
@@ -57950,10 +57950,10 @@
         <v>8.5</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>9.6</v>
+        <v>14.5</v>
       </c>
       <c r="G16" s="19" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
@@ -57992,10 +57992,10 @@
         <v>7.4</v>
       </c>
       <c r="F17" s="17" t="n">
-        <v>8.1</v>
+        <v>12.8</v>
       </c>
       <c r="G17" s="17" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
@@ -58034,10 +58034,10 @@
         <v>10.5</v>
       </c>
       <c r="F18" s="19" t="n">
-        <v>9.199999999999999</v>
+        <v>14.8</v>
       </c>
       <c r="G18" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
@@ -58072,10 +58072,10 @@
         <v>11.6</v>
       </c>
       <c r="F19" s="17" t="n">
-        <v>11.4</v>
+        <v>20.8</v>
       </c>
       <c r="G19" s="17" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
@@ -58083,9 +58083,13 @@
         </is>
       </c>
       <c r="I19" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr"/>
+        <v>-0.8</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>Wind 12 mph (gusts 21)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -58110,10 +58114,10 @@
         <v>10.1</v>
       </c>
       <c r="F20" s="19" t="n">
-        <v>19</v>
+        <v>17.4</v>
       </c>
       <c r="G20" s="19" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
@@ -58121,11 +58125,11 @@
         </is>
       </c>
       <c r="I20" s="14" t="n">
-        <v>-1.3</v>
+        <v>-0.5</v>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>Wind 10 mph (gusts 19) · 96°F</t>
+          <t>96°F</t>
         </is>
       </c>
     </row>

--- a/NFL_Edge_Model.xlsx
+++ b/NFL_Edge_Model.xlsx
@@ -692,7 +692,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Snapshot of the live model, generated 2026-08-31T05:08:05+00:00. Read-only: the model runs in the pipeline, not in this file.</t>
+          <t>Snapshot of the live model, generated 2026-08-31T12:02:48+00:00. Read-only: the model runs in the pipeline, not in this file.</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>2026-08-31T05:08:05+00:00</t>
+          <t>2026-08-31T12:02:48+00:00</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2833,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>NO @ DET</t>
+          <t>ARI @ LAC</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -2843,23 +2843,23 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Under 49.5</t>
+          <t>Under 46.5</t>
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>0.5664</v>
+        <v>0.5616</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>0.5192</v>
+        <v>0.5122</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>0.0382</v>
+        <v>0.0394</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>0.09076545612274922</v>
+        <v>0.09650071503637747</v>
       </c>
       <c r="J9" s="10" t="n">
         <v>0.5</v>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>DEN @ KC</t>
+          <t>NO @ DET</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2884,23 +2884,23 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Under 42.5</t>
+          <t>Under 49.5</t>
         </is>
       </c>
       <c r="E10" s="12" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5679</v>
+        <v>0.5664</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5192</v>
       </c>
       <c r="H10" s="13" t="n">
-        <v>0.0366</v>
+        <v>0.0382</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>0.08410573711423441</v>
+        <v>0.09076545612274922</v>
       </c>
       <c r="J10" s="15" t="n">
         <v>0.5</v>
@@ -2915,33 +2915,33 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>ARI @ LAC</t>
+          <t>MIA @ SF</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Under 46.5</t>
+          <t>MIA +10.5</t>
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>0.5542</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.5238</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>0.0354</v>
+        <v>0.0349</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>0.08202900246656697</v>
+        <v>0.07858394820276593</v>
       </c>
       <c r="J11" s="10" t="n">
         <v>0.5</v>
@@ -2956,33 +2956,33 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>MIA @ SF</t>
+          <t>CLE @ JAX</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>MIA +10.5</t>
+          <t>CLE ML</t>
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>-110</v>
+        <v>300</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.289</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.25</v>
       </c>
       <c r="H12" s="13" t="n">
-        <v>0.0349</v>
+        <v>0.0335</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>0.07858394820276593</v>
+        <v>0.1546925628455892</v>
       </c>
       <c r="J12" s="15" t="n">
         <v>0.5</v>
@@ -2997,33 +2997,33 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>CLE @ JAX</t>
+          <t>GB @ MIN</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>CLE ML</t>
+          <t>Under 45.5</t>
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>300</v>
+        <v>-110</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>0.289</v>
+        <v>0.5605</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>0.25</v>
+        <v>0.5238</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>0.0335</v>
+        <v>0.0321</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0.1546925628455892</v>
+        <v>0.07000273724694861</v>
       </c>
       <c r="J13" s="10" t="n">
         <v>0.5</v>
@@ -3038,33 +3038,33 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>GB @ MIN</t>
+          <t>GB @ NYJ</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Under 45.5</t>
+          <t>NYJ ML</t>
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>-110</v>
+        <v>200</v>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5605</v>
+        <v>0.3658</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.3333</v>
       </c>
       <c r="H14" s="13" t="n">
-        <v>0.0321</v>
+        <v>0.0292</v>
       </c>
       <c r="I14" s="13" t="n">
-        <v>0.07000273724694861</v>
+        <v>0.09658252921335053</v>
       </c>
       <c r="J14" s="15" t="n">
         <v>0.5</v>
@@ -3079,33 +3079,33 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>GB @ NYJ</t>
+          <t>IND @ KC</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>NYJ ML</t>
+          <t>Under 47.5</t>
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>200</v>
+        <v>-110</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>0.3658</v>
+        <v>0.5555</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>0.3333</v>
+        <v>0.5238</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>0.0292</v>
+        <v>0.0286</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>0.09658252921335053</v>
+        <v>0.0605390484807935</v>
       </c>
       <c r="J15" s="10" t="n">
         <v>0.5</v>
@@ -3125,28 +3125,28 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Under 47.5</t>
+          <t>IND ML</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>-110</v>
+        <v>260</v>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5555</v>
+        <v>0.3092</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.2778</v>
       </c>
       <c r="H16" s="13" t="n">
-        <v>0.0286</v>
+        <v>0.0284</v>
       </c>
       <c r="I16" s="13" t="n">
-        <v>0.0605390484807935</v>
+        <v>0.1121746593664866</v>
       </c>
       <c r="J16" s="15" t="n">
         <v>0.5</v>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>IND @ KC</t>
+          <t>MIN @ CHI</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -3171,23 +3171,23 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>IND ML</t>
+          <t>MIN ML</t>
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>260</v>
+        <v>164</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>0.3092</v>
+        <v>0.4082</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>0.2778</v>
+        <v>0.3788</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>0.0284</v>
+        <v>0.0269</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>0.1121746593664866</v>
+        <v>0.07702420117397479</v>
       </c>
       <c r="J17" s="10" t="n">
         <v>0.5</v>
@@ -3202,33 +3202,33 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>MIN @ CHI</t>
+          <t>DET @ BUF</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>MIN ML</t>
+          <t>Under 52.5</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>164</v>
+        <v>-110</v>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.4082</v>
+        <v>0.553</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>0.3788</v>
+        <v>0.5238</v>
       </c>
       <c r="H18" s="13" t="n">
-        <v>0.0269</v>
+        <v>0.0268</v>
       </c>
       <c r="I18" s="13" t="n">
-        <v>0.07702420117397479</v>
+        <v>0.05579209699090848</v>
       </c>
       <c r="J18" s="15" t="n">
         <v>0.5</v>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>SF @ LAR</t>
+          <t>NO @ BAL</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -3253,7 +3253,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Under 48.5</t>
+          <t>Under 46.5</t>
         </is>
       </c>
       <c r="E19" s="7" t="n">
@@ -3269,7 +3269,7 @@
         <v>0.0268</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>0.05579115452263916</v>
+        <v>0.05578948952918739</v>
       </c>
       <c r="J19" s="10" t="n">
         <v>0.5</v>
@@ -3284,33 +3284,33 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>DET @ BUF</t>
+          <t>CLE @ JAX</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Under 52.5</t>
+          <t>CLE +7.5</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.553</v>
+        <v>0.5525</v>
       </c>
       <c r="G20" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H20" s="13" t="n">
-        <v>0.0268</v>
+        <v>0.0264</v>
       </c>
       <c r="I20" s="13" t="n">
-        <v>0.05579209699090848</v>
+        <v>0.05481784822078883</v>
       </c>
       <c r="J20" s="15" t="n">
         <v>0.5</v>
@@ -3325,33 +3325,33 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>NO @ BAL</t>
+          <t>SF @ LAR</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Under 46.5</t>
+          <t>SF ML</t>
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>-110</v>
+        <v>164</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>0.553</v>
+        <v>0.4068</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.3788</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>0.0268</v>
+        <v>0.0258</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>0.05578948952918739</v>
+        <v>0.07325082097221369</v>
       </c>
       <c r="J21" s="10" t="n">
         <v>0.5</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>CLE @ JAX</t>
+          <t>LV @ LAC</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -3376,23 +3376,23 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>CLE +7.5</t>
+          <t>LV +8.5</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5525</v>
+        <v>0.5503</v>
       </c>
       <c r="G22" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H22" s="13" t="n">
-        <v>0.0264</v>
+        <v>0.0246</v>
       </c>
       <c r="I22" s="13" t="n">
-        <v>0.05481784822078883</v>
+        <v>0.05055573331046148</v>
       </c>
       <c r="J22" s="15" t="n">
         <v>0.5</v>
@@ -3407,33 +3407,33 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>SF @ LAR</t>
+          <t>CHI @ CAR</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>SF ML</t>
+          <t>Under 47.5</t>
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>164</v>
+        <v>-105</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>0.4068</v>
+        <v>0.5367</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>0.3788</v>
+        <v>0.5122</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>0.0258</v>
+        <v>0.023</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>0.07325082097221369</v>
+        <v>0.04790851573937971</v>
       </c>
       <c r="J23" s="10" t="n">
         <v>0.5</v>
@@ -3448,33 +3448,33 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>LV @ LAC</t>
+          <t>WSH @ PHI</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>LV +8.5</t>
+          <t>Under 46.5</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5503</v>
+        <v>0.5593</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5349</v>
       </c>
       <c r="H24" s="13" t="n">
-        <v>0.0246</v>
+        <v>0.0229</v>
       </c>
       <c r="I24" s="13" t="n">
-        <v>0.05055573331046148</v>
+        <v>0.04567005021435533</v>
       </c>
       <c r="J24" s="15" t="n">
         <v>0.5</v>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>CHI @ CAR</t>
+          <t>MIN @ CHI</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -3499,23 +3499,23 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Under 47.5</t>
+          <t>Under 45.5</t>
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>0.5367</v>
+        <v>0.548</v>
       </c>
       <c r="G25" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.5238</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>0.023</v>
+        <v>0.0228</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>0.04790851573937971</v>
+        <v>0.04626263390290908</v>
       </c>
       <c r="J25" s="10" t="n">
         <v>0.5</v>
@@ -3530,7 +3530,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>WSH @ PHI</t>
+          <t>LV @ LAC</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -3540,23 +3540,23 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Under 46.5</t>
+          <t>Under 42.5</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5593</v>
+        <v>0.548</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.5238</v>
       </c>
       <c r="H26" s="13" t="n">
-        <v>0.0229</v>
+        <v>0.0228</v>
       </c>
       <c r="I26" s="13" t="n">
-        <v>0.04567005021435533</v>
+        <v>0.04625197982017371</v>
       </c>
       <c r="J26" s="15" t="n">
         <v>0.5</v>
@@ -3571,33 +3571,33 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>MIN @ CHI</t>
+          <t>GB @ NYJ</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Under 45.5</t>
+          <t>NYJ +5.5</t>
         </is>
       </c>
       <c r="E27" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>0.548</v>
+        <v>0.545</v>
       </c>
       <c r="G27" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H27" s="8" t="n">
-        <v>0.0228</v>
+        <v>0.0202</v>
       </c>
       <c r="I27" s="8" t="n">
-        <v>0.04626263390290908</v>
+        <v>0.04045606588307799</v>
       </c>
       <c r="J27" s="10" t="n">
         <v>0.5</v>
@@ -3612,33 +3612,33 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>LV @ LAC</t>
+          <t>NYG @ LAR</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Under 42.5</t>
+          <t>NYG +8.5</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.548</v>
+        <v>0.5444</v>
       </c>
       <c r="G28" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H28" s="13" t="n">
-        <v>0.0228</v>
+        <v>0.0197</v>
       </c>
       <c r="I28" s="13" t="n">
-        <v>0.04625197982017371</v>
+        <v>0.0393979976176152</v>
       </c>
       <c r="J28" s="15" t="n">
         <v>0.5</v>
@@ -3653,33 +3653,33 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>GB @ NYJ</t>
+          <t>PHI @ TEN</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>NYJ +5.5</t>
+          <t>TEN ML</t>
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>-110</v>
+        <v>170</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>0.545</v>
+        <v>0.3908</v>
       </c>
       <c r="G29" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.3704</v>
       </c>
       <c r="H29" s="8" t="n">
-        <v>0.0202</v>
+        <v>0.0195</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>0.04045606588307799</v>
+        <v>0.05459664495979222</v>
       </c>
       <c r="J29" s="10" t="n">
         <v>0.5</v>
@@ -3694,33 +3694,33 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>NYG @ LAR</t>
+          <t>TB @ CIN</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>NYG +8.5</t>
+          <t>Under 51.5</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>-110</v>
+        <v>-118</v>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.5444</v>
+        <v>0.5616</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5413</v>
       </c>
       <c r="H30" s="13" t="n">
-        <v>0.0197</v>
+        <v>0.0194</v>
       </c>
       <c r="I30" s="13" t="n">
-        <v>0.0393979976176152</v>
+        <v>0.03752981802182648</v>
       </c>
       <c r="J30" s="15" t="n">
         <v>0.5</v>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>PHI @ TEN</t>
+          <t>ARI @ LAC</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -3745,23 +3745,23 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>TEN ML</t>
+          <t>ARI ML</t>
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>170</v>
+        <v>425</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>0.3908</v>
+        <v>0.2101</v>
       </c>
       <c r="G31" s="8" t="n">
-        <v>0.3704</v>
+        <v>0.1905</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>0.0195</v>
+        <v>0.0189</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>0.05459664495979222</v>
+        <v>0.1024745196002579</v>
       </c>
       <c r="J31" s="10" t="n">
         <v>0.5</v>
@@ -3776,33 +3776,33 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>TB @ CIN</t>
+          <t>PHI @ TEN</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Under 51.5</t>
+          <t>TEN +4.5</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>-118</v>
+        <v>-110</v>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.5616</v>
+        <v>0.5433</v>
       </c>
       <c r="G32" s="13" t="n">
-        <v>0.5413</v>
+        <v>0.5238</v>
       </c>
       <c r="H32" s="13" t="n">
-        <v>0.0194</v>
+        <v>0.0187</v>
       </c>
       <c r="I32" s="13" t="n">
-        <v>0.03752981802182648</v>
+        <v>0.03717421966315448</v>
       </c>
       <c r="J32" s="15" t="n">
         <v>0.5</v>
@@ -3817,33 +3817,33 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>ARI @ LAC</t>
+          <t>WSH @ DAL</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>ARI ML</t>
+          <t>Under 51.5</t>
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>425</v>
+        <v>-110</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>0.2101</v>
+        <v>0.543</v>
       </c>
       <c r="G33" s="8" t="n">
-        <v>0.1905</v>
+        <v>0.5238</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>0.0189</v>
+        <v>0.0185</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>0.1024745196002579</v>
+        <v>0.03670597155556737</v>
       </c>
       <c r="J33" s="10" t="n">
         <v>0.5</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>PHI @ TEN</t>
+          <t>ARI @ LAC</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -3868,23 +3868,23 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>TEN +4.5</t>
+          <t>ARI +10.5</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.5433</v>
+        <v>0.5427</v>
       </c>
       <c r="G34" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H34" s="13" t="n">
-        <v>0.0187</v>
+        <v>0.0182</v>
       </c>
       <c r="I34" s="13" t="n">
-        <v>0.03717421966315448</v>
+        <v>0.0361373241332813</v>
       </c>
       <c r="J34" s="15" t="n">
         <v>0.5</v>
@@ -3899,33 +3899,33 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>WSH @ DAL</t>
+          <t>LV @ LAC</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Under 51.5</t>
+          <t>LV ML</t>
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>-110</v>
+        <v>295</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>0.543</v>
+        <v>0.2721</v>
       </c>
       <c r="G35" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.2532</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>0.0185</v>
+        <v>0.0182</v>
       </c>
       <c r="I35" s="8" t="n">
-        <v>0.03670597155556737</v>
+        <v>0.07412962567057657</v>
       </c>
       <c r="J35" s="10" t="n">
         <v>0.5</v>
@@ -3940,33 +3940,33 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>ARI @ LAC</t>
+          <t>DEN @ KC</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>ARI +10.5</t>
+          <t>Under 42.5</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.5427</v>
+        <v>0.5405</v>
       </c>
       <c r="G36" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H36" s="13" t="n">
-        <v>0.0182</v>
+        <v>0.0162</v>
       </c>
       <c r="I36" s="13" t="n">
-        <v>0.0361373241332813</v>
+        <v>0.03190068409202224</v>
       </c>
       <c r="J36" s="15" t="n">
         <v>0.5</v>
@@ -3981,33 +3981,33 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>LV @ LAC</t>
+          <t>GB @ NYJ</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>LV ML</t>
+          <t>Over 42.5</t>
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>295</v>
+        <v>-110</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>0.2721</v>
+        <v>0.5405</v>
       </c>
       <c r="G37" s="8" t="n">
-        <v>0.2532</v>
+        <v>0.5238</v>
       </c>
       <c r="H37" s="8" t="n">
-        <v>0.0182</v>
+        <v>0.0162</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>0.07412962567057657</v>
+        <v>0.03191823479432238</v>
       </c>
       <c r="J37" s="10" t="n">
         <v>0.5</v>
@@ -4022,33 +4022,33 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>GB @ NYJ</t>
+          <t>NYG @ LAR</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Over 42.5</t>
+          <t>NYG ML</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>-110</v>
+        <v>300</v>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.5405</v>
+        <v>0.2661</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.25</v>
       </c>
       <c r="H38" s="13" t="n">
-        <v>0.0162</v>
+        <v>0.0156</v>
       </c>
       <c r="I38" s="13" t="n">
-        <v>0.03191823479432238</v>
+        <v>0.06377533884460185</v>
       </c>
       <c r="J38" s="15" t="n">
         <v>0.5</v>
@@ -4063,33 +4063,33 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>NYG @ LAR</t>
+          <t>SF @ LAR</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>NYG ML</t>
+          <t>SF +3.5</t>
         </is>
       </c>
       <c r="E39" s="7" t="n">
-        <v>300</v>
+        <v>-108</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>0.2661</v>
+        <v>0.5341</v>
       </c>
       <c r="G39" s="8" t="n">
-        <v>0.25</v>
+        <v>0.5192</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>0.0156</v>
+        <v>0.0145</v>
       </c>
       <c r="I39" s="8" t="n">
-        <v>0.06377533884460185</v>
+        <v>0.02860021870096729</v>
       </c>
       <c r="J39" s="10" t="n">
         <v>0.5</v>
@@ -4104,33 +4104,33 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>SF @ LAR</t>
+          <t>MIA @ LV</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>SF +3.5</t>
+          <t>Over 40.5</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.5341</v>
+        <v>0.538</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>0.5192</v>
+        <v>0.5238</v>
       </c>
       <c r="H40" s="13" t="n">
-        <v>0.0145</v>
+        <v>0.0139</v>
       </c>
       <c r="I40" s="13" t="n">
-        <v>0.02860021870096729</v>
+        <v>0.02712503029680507</v>
       </c>
       <c r="J40" s="15" t="n">
         <v>0.5</v>
@@ -4145,33 +4145,33 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>MIA @ LV</t>
+          <t>MIN @ CHI</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Over 40.5</t>
+          <t>MIN +3.5</t>
         </is>
       </c>
       <c r="E41" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>0.538</v>
+        <v>0.537</v>
       </c>
       <c r="G41" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H41" s="8" t="n">
-        <v>0.0139</v>
+        <v>0.013</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>0.02712503029680507</v>
+        <v>0.0252193678819661</v>
       </c>
       <c r="J41" s="10" t="n">
         <v>0.5</v>
@@ -4186,33 +4186,33 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>MIN @ CHI</t>
+          <t>CHI @ CAR</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>MIN +3.5</t>
+          <t>CAR ML</t>
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>-110</v>
+        <v>120</v>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.537</v>
+        <v>0.4675</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.4545</v>
       </c>
       <c r="H42" s="13" t="n">
-        <v>0.013</v>
+        <v>0.0128</v>
       </c>
       <c r="I42" s="13" t="n">
-        <v>0.0252193678819661</v>
+        <v>0.02833896180555251</v>
       </c>
       <c r="J42" s="15" t="n">
         <v>0.5</v>
@@ -4232,28 +4232,28 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>CAR ML</t>
+          <t>CAR +2.5</t>
         </is>
       </c>
       <c r="E43" s="7" t="n">
-        <v>120</v>
+        <v>-102</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>0.4675</v>
+        <v>0.5175</v>
       </c>
       <c r="G43" s="8" t="n">
-        <v>0.4545</v>
+        <v>0.505</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>0.0128</v>
+        <v>0.0123</v>
       </c>
       <c r="I43" s="8" t="n">
-        <v>0.02833896180555251</v>
+        <v>0.02481499147296085</v>
       </c>
       <c r="J43" s="10" t="n">
         <v>0.5</v>
@@ -4268,33 +4268,33 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>CHI @ CAR</t>
+          <t>NE @ SEA</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>CAR +2.5</t>
+          <t>NE ML</t>
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>-102</v>
+        <v>150</v>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.5175</v>
+        <v>0.412</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>0.505</v>
+        <v>0.4</v>
       </c>
       <c r="H44" s="13" t="n">
-        <v>0.0123</v>
+        <v>0.0118</v>
       </c>
       <c r="I44" s="13" t="n">
-        <v>0.02481499147296085</v>
+        <v>0.02964597219292286</v>
       </c>
       <c r="J44" s="15" t="n">
         <v>0.5</v>
@@ -4309,33 +4309,33 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>NE @ SEA</t>
+          <t>ATL @ PIT</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>NE ML</t>
+          <t>Over 42.5</t>
         </is>
       </c>
       <c r="E45" s="7" t="n">
-        <v>150</v>
+        <v>-105</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>0.412</v>
+        <v>0.5241</v>
       </c>
       <c r="G45" s="8" t="n">
-        <v>0.4</v>
+        <v>0.5122</v>
       </c>
       <c r="H45" s="8" t="n">
         <v>0.0118</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>0.02964597219292286</v>
+        <v>0.02330691394991258</v>
       </c>
       <c r="J45" s="10" t="n">
         <v>0.5</v>
@@ -4350,33 +4350,33 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>ATL @ PIT</t>
+          <t>MIA @ LV</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Over 42.5</t>
+          <t>MIA ML</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>-105</v>
+        <v>164</v>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.5241</v>
+        <v>0.3899</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>0.5122</v>
+        <v>0.3788</v>
       </c>
       <c r="H46" s="13" t="n">
-        <v>0.0118</v>
+        <v>0.011</v>
       </c>
       <c r="I46" s="13" t="n">
-        <v>0.02330691394991258</v>
+        <v>0.02919767655888217</v>
       </c>
       <c r="J46" s="15" t="n">
         <v>0.5</v>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>MIA @ LV</t>
+          <t>PIT @ NE</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -4401,23 +4401,23 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>MIA ML</t>
+          <t>PIT ML</t>
         </is>
       </c>
       <c r="E47" s="7" t="n">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>0.3899</v>
+        <v>0.3676</v>
       </c>
       <c r="G47" s="8" t="n">
-        <v>0.3788</v>
+        <v>0.3571</v>
       </c>
       <c r="H47" s="8" t="n">
-        <v>0.011</v>
+        <v>0.0103</v>
       </c>
       <c r="I47" s="8" t="n">
-        <v>0.02919767655888217</v>
+        <v>0.02891003499198008</v>
       </c>
       <c r="J47" s="10" t="n">
         <v>0.5</v>
@@ -4432,7 +4432,7 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>PIT @ NE</t>
+          <t>NO @ BAL</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
@@ -4442,23 +4442,23 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>PIT ML</t>
+          <t>NO ML</t>
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>180</v>
+        <v>280</v>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.3676</v>
+        <v>0.273</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>0.3571</v>
+        <v>0.2632</v>
       </c>
       <c r="H48" s="13" t="n">
-        <v>0.0103</v>
+        <v>0.0097</v>
       </c>
       <c r="I48" s="13" t="n">
-        <v>0.02891003499198008</v>
+        <v>0.03713258600306735</v>
       </c>
       <c r="J48" s="15" t="n">
         <v>0.5</v>
@@ -4473,33 +4473,33 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>NO @ BAL</t>
+          <t>CLE @ JAX</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>NO ML</t>
+          <t>Over 40.5</t>
         </is>
       </c>
       <c r="E49" s="7" t="n">
-        <v>280</v>
+        <v>-110</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>0.273</v>
+        <v>0.533</v>
       </c>
       <c r="G49" s="8" t="n">
-        <v>0.2632</v>
+        <v>0.5238</v>
       </c>
       <c r="H49" s="8" t="n">
-        <v>0.0097</v>
+        <v>0.0091</v>
       </c>
       <c r="I49" s="8" t="n">
-        <v>0.03713258600306735</v>
+        <v>0.01750631230941713</v>
       </c>
       <c r="J49" s="10" t="n">
         <v>0.5</v>
@@ -4514,33 +4514,33 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>CLE @ JAX</t>
+          <t>NO @ DET</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Over 40.5</t>
+          <t>NO ML</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>-110</v>
+        <v>250</v>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.533</v>
+        <v>0.2935</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.2857</v>
       </c>
       <c r="H50" s="13" t="n">
-        <v>0.0091</v>
+        <v>0.0077</v>
       </c>
       <c r="I50" s="13" t="n">
-        <v>0.01750631230941713</v>
+        <v>0.02694594815974183</v>
       </c>
       <c r="J50" s="15" t="n">
         <v>0.5</v>
@@ -4678,33 +4678,33 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>NO @ DET</t>
+          <t>NE @ SEA</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>NO ML</t>
+          <t>Under 44.5</t>
         </is>
       </c>
       <c r="E54" s="12" t="n">
-        <v>245</v>
+        <v>-110</v>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.2948</v>
+        <v>0.5279</v>
       </c>
       <c r="G54" s="13" t="n">
-        <v>0.2899</v>
+        <v>0.5238</v>
       </c>
       <c r="H54" s="13" t="n">
-        <v>0.0049</v>
+        <v>0.0041</v>
       </c>
       <c r="I54" s="13" t="n">
-        <v>0.01678835385325272</v>
+        <v>0.007846567516078207</v>
       </c>
       <c r="J54" s="15" t="n">
         <v>0.5</v>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>BAL @ IND</t>
+          <t>SF @ LAR</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -4733,19 +4733,19 @@
         </is>
       </c>
       <c r="E55" s="7" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>0.5393</v>
+        <v>0.5279</v>
       </c>
       <c r="G55" s="8" t="n">
-        <v>0.5349</v>
+        <v>0.5238</v>
       </c>
       <c r="H55" s="8" t="n">
-        <v>0.0044</v>
+        <v>0.0041</v>
       </c>
       <c r="I55" s="8" t="n">
-        <v>0.008230624751543902</v>
+        <v>0.007850543917437502</v>
       </c>
       <c r="J55" s="10" t="n">
         <v>0.5</v>
@@ -4760,17 +4760,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>NE @ SEA</t>
+          <t>NO @ DET</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Under 44.5</t>
+          <t>NO +7</t>
         </is>
       </c>
       <c r="E56" s="12" t="n">
@@ -4786,7 +4786,7 @@
         <v>0.0041</v>
       </c>
       <c r="I56" s="13" t="n">
-        <v>0.007846567516078207</v>
+        <v>0.007327889802806964</v>
       </c>
       <c r="J56" s="15" t="n">
         <v>0.5</v>
@@ -4801,33 +4801,33 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>NO @ DET</t>
+          <t>CIN @ HOU</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>NO +7</t>
+          <t>CIN ML</t>
         </is>
       </c>
       <c r="E57" s="7" t="n">
-        <v>-110</v>
+        <v>114</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>0.5279</v>
+        <v>0.4699</v>
       </c>
       <c r="G57" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.4673</v>
       </c>
       <c r="H57" s="8" t="n">
-        <v>0.0041</v>
+        <v>0.0026</v>
       </c>
       <c r="I57" s="8" t="n">
-        <v>0.007327889802806964</v>
+        <v>0.005609880883099994</v>
       </c>
       <c r="J57" s="10" t="n">
         <v>0.5</v>
@@ -4842,33 +4842,33 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>CIN @ HOU</t>
+          <t>NE @ SEA</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>CIN ML</t>
+          <t>NE +3.5</t>
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>114</v>
+        <v>-115</v>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.4699</v>
+        <v>0.5374</v>
       </c>
       <c r="G58" s="13" t="n">
-        <v>0.4673</v>
+        <v>0.5349</v>
       </c>
       <c r="H58" s="13" t="n">
-        <v>0.0026</v>
+        <v>0.0025</v>
       </c>
       <c r="I58" s="13" t="n">
-        <v>0.005609880883099994</v>
+        <v>0.004758703379786511</v>
       </c>
       <c r="J58" s="15" t="n">
         <v>0.5</v>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>NE @ SEA</t>
+          <t>BAL @ IND</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -4893,23 +4893,23 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>NE +3.5</t>
+          <t>IND +3.5</t>
         </is>
       </c>
       <c r="E59" s="7" t="n">
-        <v>-115</v>
+        <v>-112</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>0.5374</v>
+        <v>0.53</v>
       </c>
       <c r="G59" s="8" t="n">
-        <v>0.5349</v>
+        <v>0.5283</v>
       </c>
       <c r="H59" s="8" t="n">
-        <v>0.0025</v>
+        <v>0.0017</v>
       </c>
       <c r="I59" s="8" t="n">
-        <v>0.004758703379786511</v>
+        <v>0.003169898488009193</v>
       </c>
       <c r="J59" s="10" t="n">
         <v>0.5</v>
@@ -4929,28 +4929,28 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>IND +3.5</t>
+          <t>IND ML</t>
         </is>
       </c>
       <c r="E60" s="12" t="n">
-        <v>-112</v>
+        <v>145</v>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.53</v>
+        <v>0.4093</v>
       </c>
       <c r="G60" s="13" t="n">
-        <v>0.5283</v>
+        <v>0.4082</v>
       </c>
       <c r="H60" s="13" t="n">
-        <v>0.0017</v>
+        <v>0.0011</v>
       </c>
       <c r="I60" s="13" t="n">
-        <v>0.003169898488009193</v>
+        <v>0.002699590400753182</v>
       </c>
       <c r="J60" s="15" t="n">
         <v>0.5</v>
@@ -4965,33 +4965,33 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>BAL @ IND</t>
+          <t>PIT @ NE</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>IND ML</t>
+          <t>PIT +4.5</t>
         </is>
       </c>
       <c r="E61" s="7" t="n">
-        <v>145</v>
+        <v>-110</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>0.4093</v>
+        <v>0.5243</v>
       </c>
       <c r="G61" s="8" t="n">
-        <v>0.4082</v>
+        <v>0.5238</v>
       </c>
       <c r="H61" s="8" t="n">
-        <v>0.0011</v>
+        <v>0.0005</v>
       </c>
       <c r="I61" s="8" t="n">
-        <v>0.002699590400753182</v>
+        <v>0.0009570663741733654</v>
       </c>
       <c r="J61" s="10" t="n">
         <v>0.5</v>
@@ -5006,7 +5006,7 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>PIT @ NE</t>
+          <t>TB @ CIN</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -5016,23 +5016,23 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>PIT +4.5</t>
+          <t>TB +3.5</t>
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.5243</v>
+        <v>0.5105</v>
       </c>
       <c r="G62" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5122</v>
       </c>
       <c r="H62" s="13" t="n">
-        <v>0.0005</v>
+        <v>-0.0017</v>
       </c>
       <c r="I62" s="13" t="n">
-        <v>0.0009570663741733654</v>
+        <v>-0.003303895591773687</v>
       </c>
       <c r="J62" s="15" t="n">
         <v>0.5</v>
@@ -5047,7 +5047,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>TB @ CIN</t>
+          <t>CIN @ HOU</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -5057,23 +5057,23 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>TB +3.5</t>
+          <t>CIN +2.5</t>
         </is>
       </c>
       <c r="E63" s="7" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>0.5105</v>
+        <v>0.5218</v>
       </c>
       <c r="G63" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.5238</v>
       </c>
       <c r="H63" s="8" t="n">
-        <v>-0.0017</v>
+        <v>-0.002</v>
       </c>
       <c r="I63" s="8" t="n">
-        <v>-0.003303895591773687</v>
+        <v>-0.003906352011651737</v>
       </c>
       <c r="J63" s="10" t="n">
         <v>0.5</v>
@@ -5088,33 +5088,33 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>CIN @ HOU</t>
+          <t>BAL @ IND</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>CIN +2.5</t>
+          <t>Under 48.5</t>
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.5218</v>
+        <v>0.5317</v>
       </c>
       <c r="G64" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5349</v>
       </c>
       <c r="H64" s="13" t="n">
-        <v>-0.002</v>
+        <v>-0.0032</v>
       </c>
       <c r="I64" s="13" t="n">
-        <v>-0.003906352011651737</v>
+        <v>-0.00592656807527242</v>
       </c>
       <c r="J64" s="15" t="n">
         <v>0.5</v>
@@ -5662,33 +5662,33 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>BUF @ HOU</t>
+          <t>GB @ MIN</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Over 44.5</t>
+          <t>MIN ML</t>
         </is>
       </c>
       <c r="E78" s="12" t="n">
-        <v>-110</v>
+        <v>-118</v>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.5102</v>
+        <v>0.5273</v>
       </c>
       <c r="G78" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5413</v>
       </c>
       <c r="H78" s="13" t="n">
-        <v>-0.0134</v>
+        <v>-0.0137</v>
       </c>
       <c r="I78" s="13" t="n">
-        <v>-0.02603526383612009</v>
+        <v>-0.02567696379121553</v>
       </c>
       <c r="J78" s="15" t="n">
         <v>0.5</v>
@@ -5703,33 +5703,33 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>GB @ MIN</t>
+          <t>WSH @ PHI</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>MIN ML</t>
+          <t>WSH +4.5</t>
         </is>
       </c>
       <c r="E79" s="7" t="n">
-        <v>-118</v>
+        <v>-110</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>0.5273</v>
+        <v>0.5091</v>
       </c>
       <c r="G79" s="8" t="n">
-        <v>0.5413</v>
+        <v>0.5238</v>
       </c>
       <c r="H79" s="8" t="n">
-        <v>-0.0137</v>
+        <v>-0.0143</v>
       </c>
       <c r="I79" s="8" t="n">
-        <v>-0.02567696379121553</v>
+        <v>-0.02800091373558378</v>
       </c>
       <c r="J79" s="10" t="n">
         <v>0.5</v>
@@ -5744,33 +5744,33 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>WSH @ PHI</t>
+          <t>CAR @ ATL</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>WSH +4.5</t>
+          <t>Under 44.5</t>
         </is>
       </c>
       <c r="E80" s="12" t="n">
-        <v>-110</v>
+        <v>-118</v>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.5091</v>
+        <v>0.5264</v>
       </c>
       <c r="G80" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5413</v>
       </c>
       <c r="H80" s="13" t="n">
-        <v>-0.0143</v>
+        <v>-0.0145</v>
       </c>
       <c r="I80" s="13" t="n">
-        <v>-0.02800091373558378</v>
+        <v>-0.02749691463734988</v>
       </c>
       <c r="J80" s="15" t="n">
         <v>0.5</v>
@@ -5785,33 +5785,33 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>CAR @ ATL</t>
+          <t>JAX @ DEN</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Under 44.5</t>
+          <t>DEN ML</t>
         </is>
       </c>
       <c r="E81" s="7" t="n">
-        <v>-118</v>
+        <v>-142</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>0.5264</v>
+        <v>0.5715</v>
       </c>
       <c r="G81" s="8" t="n">
-        <v>0.5413</v>
+        <v>0.5868</v>
       </c>
       <c r="H81" s="8" t="n">
-        <v>-0.0145</v>
+        <v>-0.0149</v>
       </c>
       <c r="I81" s="8" t="n">
-        <v>-0.02749691463734988</v>
+        <v>-0.02583402925899386</v>
       </c>
       <c r="J81" s="10" t="n">
         <v>0.5</v>
@@ -5831,28 +5831,28 @@
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>DEN ML</t>
+          <t>DEN -2.5</t>
         </is>
       </c>
       <c r="E82" s="12" t="n">
-        <v>-142</v>
+        <v>-115</v>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.5715</v>
+        <v>0.519</v>
       </c>
       <c r="G82" s="13" t="n">
-        <v>0.5868</v>
+        <v>0.5349</v>
       </c>
       <c r="H82" s="13" t="n">
-        <v>-0.0149</v>
+        <v>-0.0155</v>
       </c>
       <c r="I82" s="13" t="n">
-        <v>-0.02583402925899386</v>
+        <v>-0.02977111681097477</v>
       </c>
       <c r="J82" s="15" t="n">
         <v>0.5</v>
@@ -5867,33 +5867,33 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>JAX @ DEN</t>
+          <t>CIN @ HOU</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>DEN -2.5</t>
+          <t>Under 46.5</t>
         </is>
       </c>
       <c r="E83" s="7" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>0.519</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="G83" s="8" t="n">
-        <v>0.5349</v>
+        <v>0.5238</v>
       </c>
       <c r="H83" s="8" t="n">
-        <v>-0.0155</v>
+        <v>-0.0157</v>
       </c>
       <c r="I83" s="8" t="n">
-        <v>-0.02977111681097477</v>
+        <v>-0.03089189112351293</v>
       </c>
       <c r="J83" s="10" t="n">
         <v>0.5</v>
@@ -5908,7 +5908,7 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>DAL @ NYG</t>
+          <t>JAX @ DEN</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Under 48.5</t>
+          <t>Over 43.5</t>
         </is>
       </c>
       <c r="E84" s="12" t="n">
@@ -5934,7 +5934,7 @@
         <v>-0.0157</v>
       </c>
       <c r="I84" s="13" t="n">
-        <v>-0.03089102485674816</v>
+        <v>-0.030886059598909</v>
       </c>
       <c r="J84" s="15" t="n">
         <v>0.5</v>
@@ -5949,33 +5949,33 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>CIN @ HOU</t>
+          <t>DEN @ KC</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Under 46.5</t>
+          <t>KC -3</t>
         </is>
       </c>
       <c r="E85" s="7" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.4958</v>
       </c>
       <c r="G85" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5122</v>
       </c>
       <c r="H85" s="8" t="n">
-        <v>-0.0157</v>
+        <v>-0.0159</v>
       </c>
       <c r="I85" s="8" t="n">
-        <v>-0.03089189112351293</v>
+        <v>-0.02966212380928346</v>
       </c>
       <c r="J85" s="10" t="n">
         <v>0.5</v>
@@ -5990,33 +5990,33 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>JAX @ DEN</t>
+          <t>DAL @ NYG</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>Over 43.5</t>
+          <t>NYG +2.5</t>
         </is>
       </c>
       <c r="E86" s="12" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.4938</v>
       </c>
       <c r="G86" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5122</v>
       </c>
       <c r="H86" s="13" t="n">
-        <v>-0.0157</v>
+        <v>-0.0177</v>
       </c>
       <c r="I86" s="13" t="n">
-        <v>-0.030886059598909</v>
+        <v>-0.035832187864627</v>
       </c>
       <c r="J86" s="15" t="n">
         <v>0.5</v>
@@ -6031,33 +6031,33 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>DEN @ KC</t>
+          <t>ATL @ PIT</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>KC -3</t>
+          <t>ATL ML</t>
         </is>
       </c>
       <c r="E87" s="7" t="n">
-        <v>-105</v>
+        <v>145</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>0.4958</v>
+        <v>0.3897</v>
       </c>
       <c r="G87" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.4082</v>
       </c>
       <c r="H87" s="8" t="n">
-        <v>-0.0159</v>
+        <v>-0.0178</v>
       </c>
       <c r="I87" s="8" t="n">
-        <v>-0.02966212380928346</v>
+        <v>-0.04481458105109759</v>
       </c>
       <c r="J87" s="10" t="n">
         <v>0.5</v>
@@ -6072,33 +6072,33 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>DAL @ NYG</t>
+          <t>BUF @ HOU</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>NYG +2.5</t>
+          <t>Over 44.5</t>
         </is>
       </c>
       <c r="E88" s="12" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.4938</v>
+        <v>0.5051</v>
       </c>
       <c r="G88" s="13" t="n">
-        <v>0.5122</v>
+        <v>0.5238</v>
       </c>
       <c r="H88" s="13" t="n">
-        <v>-0.0177</v>
+        <v>-0.018</v>
       </c>
       <c r="I88" s="13" t="n">
-        <v>-0.035832187864627</v>
+        <v>-0.0357414669279264</v>
       </c>
       <c r="J88" s="15" t="n">
         <v>0.5</v>
@@ -6113,33 +6113,33 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>ATL @ PIT</t>
+          <t>DAL @ NYG</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>ATL ML</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="E89" s="7" t="n">
-        <v>145</v>
+        <v>-110</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>0.3897</v>
+        <v>0.5051</v>
       </c>
       <c r="G89" s="8" t="n">
-        <v>0.4082</v>
+        <v>0.5238</v>
       </c>
       <c r="H89" s="8" t="n">
-        <v>-0.0178</v>
+        <v>-0.018</v>
       </c>
       <c r="I89" s="8" t="n">
-        <v>-0.04481458105109759</v>
+        <v>-0.0357439529371551</v>
       </c>
       <c r="J89" s="10" t="n">
         <v>0.5</v>
@@ -7138,33 +7138,33 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>WSH @ DAL</t>
+          <t>BUF @ HOU</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>DAL ML</t>
+          <t>Under 44.5</t>
         </is>
       </c>
       <c r="E114" s="12" t="n">
-        <v>-205</v>
+        <v>-110</v>
       </c>
       <c r="F114" s="13" t="n">
-        <v>0.6425999999999999</v>
+        <v>0.4949</v>
       </c>
       <c r="G114" s="13" t="n">
-        <v>0.6721</v>
+        <v>0.5238</v>
       </c>
       <c r="H114" s="13" t="n">
-        <v>-0.027</v>
+        <v>-0.0265</v>
       </c>
       <c r="I114" s="13" t="n">
-        <v>-0.04361348211614119</v>
+        <v>-0.05516762398116443</v>
       </c>
       <c r="J114" s="15" t="n">
         <v>0.5</v>
@@ -7179,33 +7179,33 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>DEN @ KC</t>
+          <t>DAL @ NYG</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>DEN ML</t>
+          <t>Under 48.5</t>
         </is>
       </c>
       <c r="E115" s="7" t="n">
-        <v>124</v>
+        <v>-110</v>
       </c>
       <c r="F115" s="8" t="n">
-        <v>0.4161</v>
+        <v>0.4949</v>
       </c>
       <c r="G115" s="8" t="n">
-        <v>0.4464</v>
+        <v>0.5238</v>
       </c>
       <c r="H115" s="8" t="n">
-        <v>-0.0276</v>
+        <v>-0.0265</v>
       </c>
       <c r="I115" s="8" t="n">
-        <v>-0.06742870187302918</v>
+        <v>-0.05516513797193573</v>
       </c>
       <c r="J115" s="10" t="n">
         <v>0.5</v>
@@ -7220,33 +7220,33 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>DEN @ KC</t>
+          <t>WSH @ DAL</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>DEN +3</t>
+          <t>DAL ML</t>
         </is>
       </c>
       <c r="E116" s="12" t="n">
-        <v>-115</v>
+        <v>-205</v>
       </c>
       <c r="F116" s="13" t="n">
-        <v>0.5042</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="G116" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.6721</v>
       </c>
       <c r="H116" s="13" t="n">
-        <v>-0.0279</v>
+        <v>-0.027</v>
       </c>
       <c r="I116" s="13" t="n">
-        <v>-0.05326245823759107</v>
+        <v>-0.04361348211614119</v>
       </c>
       <c r="J116" s="15" t="n">
         <v>0.5</v>
@@ -7261,7 +7261,7 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>NYJ @ TEN</t>
+          <t>DEN @ KC</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
@@ -7271,23 +7271,23 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>NYJ ML</t>
+          <t>DEN ML</t>
         </is>
       </c>
       <c r="E117" s="7" t="n">
         <v>124</v>
       </c>
       <c r="F117" s="8" t="n">
-        <v>0.4153</v>
+        <v>0.4161</v>
       </c>
       <c r="G117" s="8" t="n">
         <v>0.4464</v>
       </c>
       <c r="H117" s="8" t="n">
-        <v>-0.0282</v>
+        <v>-0.0276</v>
       </c>
       <c r="I117" s="8" t="n">
-        <v>-0.0690906107045296</v>
+        <v>-0.06742870187302918</v>
       </c>
       <c r="J117" s="10" t="n">
         <v>0.5</v>
@@ -7302,7 +7302,7 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>JAX @ DEN</t>
+          <t>DEN @ KC</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
@@ -7312,23 +7312,23 @@
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>JAX +2.5</t>
+          <t>DEN +3</t>
         </is>
       </c>
       <c r="E118" s="12" t="n">
-        <v>-105</v>
+        <v>-115</v>
       </c>
       <c r="F118" s="13" t="n">
-        <v>0.481</v>
+        <v>0.5042</v>
       </c>
       <c r="G118" s="13" t="n">
-        <v>0.5122</v>
+        <v>0.5349</v>
       </c>
       <c r="H118" s="13" t="n">
-        <v>-0.0282</v>
+        <v>-0.0279</v>
       </c>
       <c r="I118" s="13" t="n">
-        <v>-0.06082595442663441</v>
+        <v>-0.05326245823759107</v>
       </c>
       <c r="J118" s="15" t="n">
         <v>0.5</v>
@@ -7343,33 +7343,33 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>CAR @ ATL</t>
+          <t>NYJ @ TEN</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Over 44.5</t>
+          <t>NYJ ML</t>
         </is>
       </c>
       <c r="E119" s="7" t="n">
-        <v>-102</v>
+        <v>124</v>
       </c>
       <c r="F119" s="8" t="n">
-        <v>0.4736</v>
+        <v>0.4153</v>
       </c>
       <c r="G119" s="8" t="n">
-        <v>0.505</v>
+        <v>0.4464</v>
       </c>
       <c r="H119" s="8" t="n">
-        <v>-0.0283</v>
+        <v>-0.0282</v>
       </c>
       <c r="I119" s="8" t="n">
-        <v>-0.06208776500738122</v>
+        <v>-0.0690906107045296</v>
       </c>
       <c r="J119" s="10" t="n">
         <v>0.5</v>
@@ -7384,33 +7384,33 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>DAL @ NYG</t>
+          <t>JAX @ DEN</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>JAX +2.5</t>
         </is>
       </c>
       <c r="E120" s="12" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="F120" s="13" t="n">
-        <v>0.4924</v>
+        <v>0.481</v>
       </c>
       <c r="G120" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5122</v>
       </c>
       <c r="H120" s="13" t="n">
-        <v>-0.0284</v>
+        <v>-0.0282</v>
       </c>
       <c r="I120" s="13" t="n">
-        <v>-0.06001806605234272</v>
+        <v>-0.06082595442663441</v>
       </c>
       <c r="J120" s="15" t="n">
         <v>0.5</v>
@@ -7425,7 +7425,7 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>CIN @ HOU</t>
+          <t>CAR @ ATL</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
@@ -7435,23 +7435,23 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Over 46.5</t>
+          <t>Over 44.5</t>
         </is>
       </c>
       <c r="E121" s="7" t="n">
-        <v>-110</v>
+        <v>-102</v>
       </c>
       <c r="F121" s="8" t="n">
-        <v>0.4924</v>
+        <v>0.4736</v>
       </c>
       <c r="G121" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.505</v>
       </c>
       <c r="H121" s="8" t="n">
-        <v>-0.0284</v>
+        <v>-0.0283</v>
       </c>
       <c r="I121" s="8" t="n">
-        <v>-0.0600171997855779</v>
+        <v>-0.06208776500738122</v>
       </c>
       <c r="J121" s="10" t="n">
         <v>0.5</v>
@@ -7466,7 +7466,7 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>JAX @ DEN</t>
+          <t>CIN @ HOU</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>Under 43.5</t>
+          <t>Over 46.5</t>
         </is>
       </c>
       <c r="E122" s="12" t="n">
@@ -7492,7 +7492,7 @@
         <v>-0.0284</v>
       </c>
       <c r="I122" s="13" t="n">
-        <v>-0.06002303131018183</v>
+        <v>-0.0600171997855779</v>
       </c>
       <c r="J122" s="15" t="n">
         <v>0.5</v>
@@ -7507,33 +7507,33 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>CLE @ TB</t>
+          <t>JAX @ DEN</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>TB ML</t>
+          <t>Under 43.5</t>
         </is>
       </c>
       <c r="E123" s="7" t="n">
-        <v>-238</v>
+        <v>-110</v>
       </c>
       <c r="F123" s="8" t="n">
-        <v>0.6722</v>
+        <v>0.4924</v>
       </c>
       <c r="G123" s="8" t="n">
-        <v>0.7040999999999999</v>
+        <v>0.5238</v>
       </c>
       <c r="H123" s="8" t="n">
-        <v>-0.0288</v>
+        <v>-0.0284</v>
       </c>
       <c r="I123" s="8" t="n">
-        <v>-0.04504032124547858</v>
+        <v>-0.06002303131018183</v>
       </c>
       <c r="J123" s="10" t="n">
         <v>0.5</v>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>GB @ MIN</t>
+          <t>CLE @ TB</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
@@ -7558,23 +7558,23 @@
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>GB ML</t>
+          <t>TB ML</t>
         </is>
       </c>
       <c r="E124" s="12" t="n">
-        <v>-102</v>
+        <v>-238</v>
       </c>
       <c r="F124" s="13" t="n">
-        <v>0.4727</v>
+        <v>0.6722</v>
       </c>
       <c r="G124" s="13" t="n">
-        <v>0.505</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="H124" s="13" t="n">
-        <v>-0.029</v>
+        <v>-0.0288</v>
       </c>
       <c r="I124" s="13" t="n">
-        <v>-0.063218757376162</v>
+        <v>-0.04504032124547858</v>
       </c>
       <c r="J124" s="15" t="n">
         <v>0.5</v>
@@ -7589,33 +7589,33 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>WSH @ PHI</t>
+          <t>GB @ MIN</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>PHI -4.5</t>
+          <t>GB ML</t>
         </is>
       </c>
       <c r="E125" s="7" t="n">
-        <v>-110</v>
+        <v>-102</v>
       </c>
       <c r="F125" s="8" t="n">
-        <v>0.4909</v>
+        <v>0.4727</v>
       </c>
       <c r="G125" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.505</v>
       </c>
       <c r="H125" s="8" t="n">
-        <v>-0.0295</v>
+        <v>-0.029</v>
       </c>
       <c r="I125" s="8" t="n">
-        <v>-0.06290817717350705</v>
+        <v>-0.063218757376162</v>
       </c>
       <c r="J125" s="10" t="n">
         <v>0.5</v>
@@ -7630,7 +7630,7 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>BUF @ HOU</t>
+          <t>WSH @ PHI</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
@@ -7640,23 +7640,23 @@
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>HOU +1.5</t>
+          <t>PHI -4.5</t>
         </is>
       </c>
       <c r="E126" s="12" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="F126" s="13" t="n">
-        <v>0.5009</v>
+        <v>0.4909</v>
       </c>
       <c r="G126" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.5238</v>
       </c>
       <c r="H126" s="13" t="n">
-        <v>-0.0302</v>
+        <v>-0.0295</v>
       </c>
       <c r="I126" s="13" t="n">
-        <v>-0.06355970664821076</v>
+        <v>-0.06290817717350705</v>
       </c>
       <c r="J126" s="15" t="n">
         <v>0.5</v>
@@ -7676,28 +7676,28 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Under 44.5</t>
+          <t>HOU +1.5</t>
         </is>
       </c>
       <c r="E127" s="7" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="F127" s="8" t="n">
-        <v>0.4898</v>
+        <v>0.5009</v>
       </c>
       <c r="G127" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5349</v>
       </c>
       <c r="H127" s="8" t="n">
         <v>-0.0302</v>
       </c>
       <c r="I127" s="8" t="n">
-        <v>-0.06487382707297074</v>
+        <v>-0.06355970664821076</v>
       </c>
       <c r="J127" s="10" t="n">
         <v>0.5</v>
@@ -8081,33 +8081,33 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>CIN @ HOU</t>
+          <t>BAL @ IND</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>HOU ML</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="E137" s="7" t="n">
-        <v>-135</v>
+        <v>-105</v>
       </c>
       <c r="F137" s="8" t="n">
-        <v>0.5301</v>
+        <v>0.4683</v>
       </c>
       <c r="G137" s="8" t="n">
-        <v>0.5745</v>
+        <v>0.5122</v>
       </c>
       <c r="H137" s="8" t="n">
-        <v>-0.0367</v>
+        <v>-0.0365</v>
       </c>
       <c r="I137" s="8" t="n">
-        <v>-0.07660038478634146</v>
+        <v>-0.08572674009415082</v>
       </c>
       <c r="J137" s="10" t="n">
         <v>0.5</v>
@@ -8122,33 +8122,33 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>TB @ CIN</t>
+          <t>CIN @ HOU</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>CIN -3.5</t>
+          <t>HOU ML</t>
         </is>
       </c>
       <c r="E138" s="12" t="n">
-        <v>-115</v>
+        <v>-135</v>
       </c>
       <c r="F138" s="13" t="n">
-        <v>0.4895</v>
+        <v>0.5301</v>
       </c>
       <c r="G138" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.5745</v>
       </c>
       <c r="H138" s="13" t="n">
-        <v>-0.0373</v>
+        <v>-0.0367</v>
       </c>
       <c r="I138" s="13" t="n">
-        <v>-0.08485321556800468</v>
+        <v>-0.07660038478634146</v>
       </c>
       <c r="J138" s="15" t="n">
         <v>0.5</v>
@@ -8163,33 +8163,33 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>BAL @ IND</t>
+          <t>TB @ CIN</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>BAL ML</t>
+          <t>CIN -3.5</t>
         </is>
       </c>
       <c r="E139" s="7" t="n">
-        <v>-175</v>
+        <v>-115</v>
       </c>
       <c r="F139" s="8" t="n">
-        <v>0.5907</v>
+        <v>0.4895</v>
       </c>
       <c r="G139" s="8" t="n">
-        <v>0.6364</v>
+        <v>0.5349</v>
       </c>
       <c r="H139" s="8" t="n">
-        <v>-0.0374</v>
+        <v>-0.0373</v>
       </c>
       <c r="I139" s="8" t="n">
-        <v>-0.07108657807518826</v>
+        <v>-0.08485321556800468</v>
       </c>
       <c r="J139" s="10" t="n">
         <v>0.5</v>
@@ -8204,33 +8204,33 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>CIN @ HOU</t>
+          <t>BAL @ IND</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>HOU -2.5</t>
+          <t>BAL ML</t>
         </is>
       </c>
       <c r="E140" s="12" t="n">
-        <v>-110</v>
+        <v>-175</v>
       </c>
       <c r="F140" s="13" t="n">
-        <v>0.4782</v>
+        <v>0.5907</v>
       </c>
       <c r="G140" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.6364</v>
       </c>
       <c r="H140" s="13" t="n">
         <v>-0.0374</v>
       </c>
       <c r="I140" s="13" t="n">
-        <v>-0.08700273889743909</v>
+        <v>-0.07108657807518826</v>
       </c>
       <c r="J140" s="15" t="n">
         <v>0.5</v>
@@ -8245,33 +8245,33 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>NO @ DET</t>
+          <t>CIN @ HOU</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>DET ML</t>
+          <t>HOU -2.5</t>
         </is>
       </c>
       <c r="E141" s="7" t="n">
-        <v>-305</v>
+        <v>-110</v>
       </c>
       <c r="F141" s="8" t="n">
-        <v>0.7052</v>
+        <v>0.4782</v>
       </c>
       <c r="G141" s="8" t="n">
-        <v>0.7531</v>
+        <v>0.5238</v>
       </c>
       <c r="H141" s="8" t="n">
-        <v>-0.0386</v>
+        <v>-0.0374</v>
       </c>
       <c r="I141" s="8" t="n">
-        <v>-0.06303304767056689</v>
+        <v>-0.08700273889743909</v>
       </c>
       <c r="J141" s="10" t="n">
         <v>0.5</v>
@@ -8368,33 +8368,33 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>NE @ SEA</t>
+          <t>NO @ DET</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>SEA -3.5</t>
+          <t>DET ML</t>
         </is>
       </c>
       <c r="E144" s="12" t="n">
-        <v>-105</v>
+        <v>-310</v>
       </c>
       <c r="F144" s="13" t="n">
-        <v>0.4626</v>
+        <v>0.7065</v>
       </c>
       <c r="G144" s="13" t="n">
-        <v>0.5122</v>
+        <v>0.7561</v>
       </c>
       <c r="H144" s="13" t="n">
-        <v>-0.0395</v>
+        <v>-0.0394</v>
       </c>
       <c r="I144" s="13" t="n">
-        <v>-0.09688533475873617</v>
+        <v>-0.06504615654035109</v>
       </c>
       <c r="J144" s="15" t="n">
         <v>0.5</v>
@@ -8409,33 +8409,33 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>TB @ CIN</t>
+          <t>NE @ SEA</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>CIN ML</t>
+          <t>SEA -3.5</t>
         </is>
       </c>
       <c r="E145" s="7" t="n">
-        <v>-198</v>
+        <v>-105</v>
       </c>
       <c r="F145" s="8" t="n">
-        <v>0.6145</v>
+        <v>0.4626</v>
       </c>
       <c r="G145" s="8" t="n">
-        <v>0.6644</v>
+        <v>0.5122</v>
       </c>
       <c r="H145" s="8" t="n">
-        <v>-0.0396</v>
+        <v>-0.0395</v>
       </c>
       <c r="I145" s="8" t="n">
-        <v>-0.07450287228679597</v>
+        <v>-0.09688533475873617</v>
       </c>
       <c r="J145" s="10" t="n">
         <v>0.5</v>
@@ -8450,33 +8450,33 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>BAL @ IND</t>
+          <t>TB @ CIN</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>CIN ML</t>
         </is>
       </c>
       <c r="E146" s="12" t="n">
-        <v>-105</v>
+        <v>-198</v>
       </c>
       <c r="F146" s="13" t="n">
-        <v>0.4607</v>
+        <v>0.6145</v>
       </c>
       <c r="G146" s="13" t="n">
-        <v>0.5122</v>
+        <v>0.6644</v>
       </c>
       <c r="H146" s="13" t="n">
-        <v>-0.0403</v>
+        <v>-0.0396</v>
       </c>
       <c r="I146" s="13" t="n">
-        <v>-0.1005110510971273</v>
+        <v>-0.07450287228679597</v>
       </c>
       <c r="J146" s="15" t="n">
         <v>0.5</v>
@@ -8573,33 +8573,33 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>IND @ KC</t>
+          <t>SF @ LAR</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>KC -6.5</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="E149" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F149" s="8" t="n">
-        <v>0.4711</v>
+        <v>0.4721</v>
       </c>
       <c r="G149" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H149" s="8" t="n">
-        <v>-0.0409</v>
+        <v>-0.0405</v>
       </c>
       <c r="I149" s="8" t="n">
-        <v>-0.1005383305888839</v>
+        <v>-0.09875963482652833</v>
       </c>
       <c r="J149" s="10" t="n">
         <v>0.5</v>
@@ -8614,42 +8614,38 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>NO @ BAL</t>
+          <t>IND @ KC</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>BAL ML</t>
+          <t>KC -6.5</t>
         </is>
       </c>
       <c r="E150" s="12" t="n">
-        <v>-355</v>
+        <v>-110</v>
       </c>
       <c r="F150" s="13" t="n">
-        <v>0.727</v>
+        <v>0.4711</v>
       </c>
       <c r="G150" s="13" t="n">
-        <v>0.7802</v>
+        <v>0.5238</v>
       </c>
       <c r="H150" s="13" t="n">
-        <v>-0.0411</v>
+        <v>-0.0409</v>
       </c>
       <c r="I150" s="13" t="n">
-        <v>-0.06769628093039223</v>
+        <v>-0.1005383305888839</v>
       </c>
       <c r="J150" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="K150" s="5" t="inlineStr">
-        <is>
-          <t>price -355 outside the allowed range</t>
-        </is>
-      </c>
+      <c r="K150" s="5" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
@@ -8659,7 +8655,7 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>PIT @ NE</t>
+          <t>NO @ BAL</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
@@ -8669,28 +8665,32 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>NE ML</t>
+          <t>BAL ML</t>
         </is>
       </c>
       <c r="E151" s="7" t="n">
-        <v>-218</v>
+        <v>-355</v>
       </c>
       <c r="F151" s="8" t="n">
-        <v>0.6324</v>
+        <v>0.727</v>
       </c>
       <c r="G151" s="8" t="n">
-        <v>0.6855</v>
+        <v>0.7802</v>
       </c>
       <c r="H151" s="8" t="n">
         <v>-0.0411</v>
       </c>
       <c r="I151" s="8" t="n">
-        <v>-0.07678114424026627</v>
+        <v>-0.06769628093039223</v>
       </c>
       <c r="J151" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="K151" s="4" t="inlineStr"/>
+      <c r="K151" s="4" t="inlineStr">
+        <is>
+          <t>price -355 outside the allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
@@ -8700,33 +8700,33 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>NO @ BAL</t>
+          <t>PIT @ NE</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>BAL -7.5</t>
+          <t>NE ML</t>
         </is>
       </c>
       <c r="E152" s="12" t="n">
-        <v>-110</v>
+        <v>-218</v>
       </c>
       <c r="F152" s="13" t="n">
-        <v>0.4704</v>
+        <v>0.6324</v>
       </c>
       <c r="G152" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.6855</v>
       </c>
       <c r="H152" s="13" t="n">
-        <v>-0.0412</v>
+        <v>-0.0411</v>
       </c>
       <c r="I152" s="13" t="n">
-        <v>-0.1019701015487157</v>
+        <v>-0.07678114424026627</v>
       </c>
       <c r="J152" s="15" t="n">
         <v>0.5</v>
@@ -8741,33 +8741,33 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>CHI @ CAR</t>
+          <t>NO @ BAL</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>CHI ML</t>
+          <t>BAL -7.5</t>
         </is>
       </c>
       <c r="E153" s="7" t="n">
-        <v>-142</v>
+        <v>-110</v>
       </c>
       <c r="F153" s="8" t="n">
-        <v>0.5325</v>
+        <v>0.4704</v>
       </c>
       <c r="G153" s="8" t="n">
-        <v>0.5868</v>
+        <v>0.5238</v>
       </c>
       <c r="H153" s="8" t="n">
-        <v>-0.0416</v>
+        <v>-0.0412</v>
       </c>
       <c r="I153" s="8" t="n">
-        <v>-0.09174303300906173</v>
+        <v>-0.1019701015487157</v>
       </c>
       <c r="J153" s="10" t="n">
         <v>0.5</v>
@@ -8782,7 +8782,7 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>MIA @ LV</t>
+          <t>CHI @ CAR</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
@@ -8792,23 +8792,23 @@
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>LV ML</t>
+          <t>CHI ML</t>
         </is>
       </c>
       <c r="E154" s="12" t="n">
-        <v>-198</v>
+        <v>-142</v>
       </c>
       <c r="F154" s="13" t="n">
-        <v>0.6101</v>
+        <v>0.5325</v>
       </c>
       <c r="G154" s="13" t="n">
-        <v>0.6644</v>
+        <v>0.5868</v>
       </c>
       <c r="H154" s="13" t="n">
         <v>-0.0416</v>
       </c>
       <c r="I154" s="13" t="n">
-        <v>-0.08112222648837741</v>
+        <v>-0.09174303300906173</v>
       </c>
       <c r="J154" s="15" t="n">
         <v>0.5</v>
@@ -8823,7 +8823,7 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>NE @ SEA</t>
+          <t>MIA @ LV</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
@@ -8833,23 +8833,23 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>SEA ML</t>
+          <t>LV ML</t>
         </is>
       </c>
       <c r="E155" s="7" t="n">
-        <v>-180</v>
+        <v>-198</v>
       </c>
       <c r="F155" s="8" t="n">
-        <v>0.588</v>
+        <v>0.6101</v>
       </c>
       <c r="G155" s="8" t="n">
-        <v>0.6429</v>
+        <v>0.6644</v>
       </c>
       <c r="H155" s="8" t="n">
-        <v>-0.0418</v>
+        <v>-0.0416</v>
       </c>
       <c r="I155" s="8" t="n">
-        <v>-0.08452402520706254</v>
+        <v>-0.08112222648837741</v>
       </c>
       <c r="J155" s="10" t="n">
         <v>0.5</v>
@@ -8864,33 +8864,33 @@
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>CLE @ JAX</t>
+          <t>NE @ SEA</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>Under 40.5</t>
+          <t>SEA ML</t>
         </is>
       </c>
       <c r="E156" s="12" t="n">
-        <v>-110</v>
+        <v>-180</v>
       </c>
       <c r="F156" s="13" t="n">
-        <v>0.467</v>
+        <v>0.588</v>
       </c>
       <c r="G156" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.6429</v>
       </c>
       <c r="H156" s="13" t="n">
-        <v>-0.0426</v>
+        <v>-0.0418</v>
       </c>
       <c r="I156" s="13" t="n">
-        <v>-0.108415403218508</v>
+        <v>-0.08452402520706254</v>
       </c>
       <c r="J156" s="15" t="n">
         <v>0.5</v>
@@ -8905,42 +8905,38 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>NYG @ LAR</t>
+          <t>CLE @ JAX</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>LAR ML</t>
+          <t>Under 40.5</t>
         </is>
       </c>
       <c r="E157" s="7" t="n">
-        <v>-380</v>
+        <v>-110</v>
       </c>
       <c r="F157" s="8" t="n">
-        <v>0.7339</v>
+        <v>0.467</v>
       </c>
       <c r="G157" s="8" t="n">
-        <v>0.7917</v>
+        <v>0.5238</v>
       </c>
       <c r="H157" s="8" t="n">
-        <v>-0.043</v>
+        <v>-0.0426</v>
       </c>
       <c r="I157" s="8" t="n">
-        <v>-0.07237181469160672</v>
+        <v>-0.108415403218508</v>
       </c>
       <c r="J157" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="K157" s="4" t="inlineStr">
-        <is>
-          <t>price -380 outside the allowed range</t>
-        </is>
-      </c>
+      <c r="K157" s="4" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
@@ -8950,38 +8946,42 @@
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>CHI @ CAR</t>
+          <t>NYG @ LAR</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>CHI -2.5</t>
+          <t>LAR ML</t>
         </is>
       </c>
       <c r="E158" s="12" t="n">
-        <v>-118</v>
+        <v>-380</v>
       </c>
       <c r="F158" s="13" t="n">
-        <v>0.4825</v>
+        <v>0.7339</v>
       </c>
       <c r="G158" s="13" t="n">
-        <v>0.5413</v>
+        <v>0.7917</v>
       </c>
       <c r="H158" s="13" t="n">
-        <v>-0.0434</v>
+        <v>-0.043</v>
       </c>
       <c r="I158" s="13" t="n">
-        <v>-0.1085662925991255</v>
+        <v>-0.07237181469160672</v>
       </c>
       <c r="J158" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="K158" s="5" t="inlineStr"/>
+      <c r="K158" s="5" t="inlineStr">
+        <is>
+          <t>price -380 outside the allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
@@ -8991,33 +8991,33 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>ATL @ PIT</t>
+          <t>CHI @ CAR</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>Under 42.5</t>
+          <t>CHI -2.5</t>
         </is>
       </c>
       <c r="E159" s="7" t="n">
-        <v>-115</v>
+        <v>-118</v>
       </c>
       <c r="F159" s="8" t="n">
-        <v>0.4759</v>
+        <v>0.4825</v>
       </c>
       <c r="G159" s="8" t="n">
-        <v>0.5349</v>
+        <v>0.5413</v>
       </c>
       <c r="H159" s="8" t="n">
-        <v>-0.0435</v>
+        <v>-0.0434</v>
       </c>
       <c r="I159" s="8" t="n">
-        <v>-0.1103352527007117</v>
+        <v>-0.1085662925991255</v>
       </c>
       <c r="J159" s="10" t="n">
         <v>0.5</v>
@@ -9032,33 +9032,33 @@
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>MIN @ CHI</t>
+          <t>ATL @ PIT</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>CHI -3.5</t>
+          <t>Under 42.5</t>
         </is>
       </c>
       <c r="E160" s="12" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="F160" s="13" t="n">
-        <v>0.463</v>
+        <v>0.4759</v>
       </c>
       <c r="G160" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5349</v>
       </c>
       <c r="H160" s="13" t="n">
-        <v>-0.0441</v>
+        <v>-0.0435</v>
       </c>
       <c r="I160" s="13" t="n">
-        <v>-0.1161284587910569</v>
+        <v>-0.1103352527007117</v>
       </c>
       <c r="J160" s="15" t="n">
         <v>0.5</v>
@@ -9073,42 +9073,38 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>LV @ LAC</t>
+          <t>MIN @ CHI</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>LAC ML</t>
+          <t>CHI -3.5</t>
         </is>
       </c>
       <c r="E161" s="7" t="n">
-        <v>-375</v>
+        <v>-110</v>
       </c>
       <c r="F161" s="8" t="n">
-        <v>0.7279</v>
+        <v>0.463</v>
       </c>
       <c r="G161" s="8" t="n">
-        <v>0.7895</v>
+        <v>0.5238</v>
       </c>
       <c r="H161" s="8" t="n">
-        <v>-0.0444</v>
+        <v>-0.0441</v>
       </c>
       <c r="I161" s="8" t="n">
-        <v>-0.07736481645176854</v>
+        <v>-0.1161284587910569</v>
       </c>
       <c r="J161" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="K161" s="4" t="inlineStr">
-        <is>
-          <t>price -375 outside the allowed range</t>
-        </is>
-      </c>
+      <c r="K161" s="4" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="5" t="inlineStr">
@@ -9118,7 +9114,7 @@
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>ARI @ LAC</t>
+          <t>LV @ LAC</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
@@ -9132,26 +9128,26 @@
         </is>
       </c>
       <c r="E162" s="12" t="n">
-        <v>-575</v>
+        <v>-375</v>
       </c>
       <c r="F162" s="13" t="n">
-        <v>0.7899</v>
+        <v>0.7279</v>
       </c>
       <c r="G162" s="13" t="n">
-        <v>0.8519</v>
+        <v>0.7895</v>
       </c>
       <c r="H162" s="13" t="n">
-        <v>-0.0445</v>
+        <v>-0.0444</v>
       </c>
       <c r="I162" s="13" t="n">
-        <v>-0.07226712107897987</v>
+        <v>-0.07736481645176854</v>
       </c>
       <c r="J162" s="15" t="n">
         <v>0.5</v>
       </c>
       <c r="K162" s="5" t="inlineStr">
         <is>
-          <t>price -575 outside the allowed range</t>
+          <t>price -375 outside the allowed range</t>
         </is>
       </c>
     </row>
@@ -9163,38 +9159,42 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>MIA @ LV</t>
+          <t>ARI @ LAC</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>Under 40.5</t>
+          <t>LAC ML</t>
         </is>
       </c>
       <c r="E163" s="7" t="n">
-        <v>-110</v>
+        <v>-575</v>
       </c>
       <c r="F163" s="8" t="n">
-        <v>0.462</v>
+        <v>0.7899</v>
       </c>
       <c r="G163" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.8519</v>
       </c>
       <c r="H163" s="8" t="n">
         <v>-0.0445</v>
       </c>
       <c r="I163" s="8" t="n">
-        <v>-0.1180341212058959</v>
+        <v>-0.07226712107897987</v>
       </c>
       <c r="J163" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="K163" s="4" t="inlineStr"/>
+      <c r="K163" s="4" t="inlineStr">
+        <is>
+          <t>price -575 outside the allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
@@ -9204,33 +9204,33 @@
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>SF @ LAR</t>
+          <t>MIA @ LV</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>LAR -3.5</t>
+          <t>Under 40.5</t>
         </is>
       </c>
       <c r="E164" s="12" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="F164" s="13" t="n">
-        <v>0.4659</v>
+        <v>0.462</v>
       </c>
       <c r="G164" s="13" t="n">
-        <v>0.5283</v>
+        <v>0.5238</v>
       </c>
       <c r="H164" s="13" t="n">
-        <v>-0.0447</v>
+        <v>-0.0445</v>
       </c>
       <c r="I164" s="13" t="n">
-        <v>-0.1180816709897556</v>
+        <v>-0.1180341212058959</v>
       </c>
       <c r="J164" s="15" t="n">
         <v>0.5</v>
@@ -9245,33 +9245,33 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>PHI @ TEN</t>
+          <t>SF @ LAR</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>PHI ML</t>
+          <t>LAR -3.5</t>
         </is>
       </c>
       <c r="E165" s="7" t="n">
-        <v>-205</v>
+        <v>-112</v>
       </c>
       <c r="F165" s="8" t="n">
-        <v>0.6092</v>
+        <v>0.4659</v>
       </c>
       <c r="G165" s="8" t="n">
-        <v>0.6721</v>
+        <v>0.5283</v>
       </c>
       <c r="H165" s="8" t="n">
-        <v>-0.0449</v>
+        <v>-0.0447</v>
       </c>
       <c r="I165" s="8" t="n">
-        <v>-0.09276520694518015</v>
+        <v>-0.1180816709897556</v>
       </c>
       <c r="J165" s="10" t="n">
         <v>0.5</v>
@@ -9286,33 +9286,33 @@
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>GB @ NYJ</t>
+          <t>PHI @ TEN</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>Under 42.5</t>
+          <t>PHI ML</t>
         </is>
       </c>
       <c r="E166" s="12" t="n">
-        <v>-110</v>
+        <v>-205</v>
       </c>
       <c r="F166" s="13" t="n">
-        <v>0.4595</v>
+        <v>0.6092</v>
       </c>
       <c r="G166" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.6721</v>
       </c>
       <c r="H166" s="13" t="n">
-        <v>-0.0453</v>
+        <v>-0.0449</v>
       </c>
       <c r="I166" s="13" t="n">
-        <v>-0.1228273257034132</v>
+        <v>-0.09276520694518015</v>
       </c>
       <c r="J166" s="15" t="n">
         <v>0.5</v>
@@ -9327,7 +9327,7 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>TB @ CIN</t>
+          <t>DEN @ KC</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
@@ -9337,23 +9337,23 @@
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>Over 51.5</t>
+          <t>Over 42.5</t>
         </is>
       </c>
       <c r="E167" s="7" t="n">
-        <v>-102</v>
+        <v>-110</v>
       </c>
       <c r="F167" s="8" t="n">
-        <v>0.4384</v>
+        <v>0.4595</v>
       </c>
       <c r="G167" s="8" t="n">
-        <v>0.505</v>
+        <v>0.5238</v>
       </c>
       <c r="H167" s="8" t="n">
-        <v>-0.046</v>
+        <v>-0.0453</v>
       </c>
       <c r="I167" s="8" t="n">
-        <v>-0.131793521423289</v>
+        <v>-0.1228097750011131</v>
       </c>
       <c r="J167" s="10" t="n">
         <v>0.5</v>
@@ -9368,33 +9368,33 @@
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>ARI @ LAC</t>
+          <t>GB @ NYJ</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>LAC -10.5</t>
+          <t>Under 42.5</t>
         </is>
       </c>
       <c r="E168" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F168" s="13" t="n">
-        <v>0.4573</v>
+        <v>0.4595</v>
       </c>
       <c r="G168" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H168" s="13" t="n">
-        <v>-0.046</v>
+        <v>-0.0453</v>
       </c>
       <c r="I168" s="13" t="n">
-        <v>-0.1270464150423721</v>
+        <v>-0.1228273257034132</v>
       </c>
       <c r="J168" s="15" t="n">
         <v>0.5</v>
@@ -9409,7 +9409,7 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>WSH @ DAL</t>
+          <t>TB @ CIN</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
@@ -9423,19 +9423,19 @@
         </is>
       </c>
       <c r="E169" s="7" t="n">
-        <v>-110</v>
+        <v>-102</v>
       </c>
       <c r="F169" s="8" t="n">
-        <v>0.457</v>
+        <v>0.4384</v>
       </c>
       <c r="G169" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.505</v>
       </c>
       <c r="H169" s="8" t="n">
-        <v>-0.0461</v>
+        <v>-0.046</v>
       </c>
       <c r="I169" s="8" t="n">
-        <v>-0.1276150624646581</v>
+        <v>-0.131793521423289</v>
       </c>
       <c r="J169" s="10" t="n">
         <v>0.5</v>
@@ -9450,7 +9450,7 @@
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>PHI @ TEN</t>
+          <t>ARI @ LAC</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
@@ -9460,23 +9460,23 @@
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>PHI -4.5</t>
+          <t>LAC -10.5</t>
         </is>
       </c>
       <c r="E170" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F170" s="13" t="n">
-        <v>0.4567</v>
+        <v>0.4573</v>
       </c>
       <c r="G170" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H170" s="13" t="n">
-        <v>-0.0462</v>
+        <v>-0.046</v>
       </c>
       <c r="I170" s="13" t="n">
-        <v>-0.1280833105722453</v>
+        <v>-0.1270464150423721</v>
       </c>
       <c r="J170" s="15" t="n">
         <v>0.5</v>
@@ -9491,33 +9491,33 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>NYG @ LAR</t>
+          <t>WSH @ DAL</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>LAR -8.5</t>
+          <t>Over 51.5</t>
         </is>
       </c>
       <c r="E171" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F171" s="8" t="n">
-        <v>0.4556</v>
+        <v>0.457</v>
       </c>
       <c r="G171" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H171" s="8" t="n">
-        <v>-0.0465</v>
+        <v>-0.0461</v>
       </c>
       <c r="I171" s="8" t="n">
-        <v>-0.1303070885267061</v>
+        <v>-0.1276150624646581</v>
       </c>
       <c r="J171" s="10" t="n">
         <v>0.5</v>
@@ -9532,7 +9532,7 @@
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
-          <t>GB @ NYJ</t>
+          <t>PHI @ TEN</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
@@ -9542,23 +9542,23 @@
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>GB -5.5</t>
+          <t>PHI -4.5</t>
         </is>
       </c>
       <c r="E172" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F172" s="13" t="n">
-        <v>0.455</v>
+        <v>0.4567</v>
       </c>
       <c r="G172" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H172" s="13" t="n">
-        <v>-0.0467</v>
+        <v>-0.0462</v>
       </c>
       <c r="I172" s="13" t="n">
-        <v>-0.1313651567921688</v>
+        <v>-0.1280833105722453</v>
       </c>
       <c r="J172" s="15" t="n">
         <v>0.5</v>
@@ -9573,33 +9573,33 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>SF @ LAR</t>
+          <t>NYG @ LAR</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>LAR ML</t>
+          <t>LAR -8.5</t>
         </is>
       </c>
       <c r="E173" s="7" t="n">
-        <v>-198</v>
+        <v>-110</v>
       </c>
       <c r="F173" s="8" t="n">
-        <v>0.5931999999999999</v>
+        <v>0.4556</v>
       </c>
       <c r="G173" s="8" t="n">
-        <v>0.6644</v>
+        <v>0.5238</v>
       </c>
       <c r="H173" s="8" t="n">
-        <v>-0.0473</v>
+        <v>-0.0465</v>
       </c>
       <c r="I173" s="8" t="n">
-        <v>-0.10622881330305</v>
+        <v>-0.1303070885267061</v>
       </c>
       <c r="J173" s="10" t="n">
         <v>0.5</v>
@@ -9614,33 +9614,33 @@
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>CHI @ CAR</t>
+          <t>GB @ NYJ</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>Over 47.5</t>
+          <t>GB -5.5</t>
         </is>
       </c>
       <c r="E174" s="12" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="F174" s="13" t="n">
-        <v>0.4633</v>
+        <v>0.455</v>
       </c>
       <c r="G174" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.5238</v>
       </c>
       <c r="H174" s="13" t="n">
-        <v>-0.0474</v>
+        <v>-0.0467</v>
       </c>
       <c r="I174" s="13" t="n">
-        <v>-0.1338933082848991</v>
+        <v>-0.1313651567921688</v>
       </c>
       <c r="J174" s="15" t="n">
         <v>0.5</v>
@@ -9655,33 +9655,33 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>WSH @ PHI</t>
+          <t>SF @ LAR</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>Over 46.5</t>
+          <t>LAR ML</t>
         </is>
       </c>
       <c r="E175" s="7" t="n">
-        <v>-105</v>
+        <v>-198</v>
       </c>
       <c r="F175" s="8" t="n">
-        <v>0.4407</v>
+        <v>0.5931999999999999</v>
       </c>
       <c r="G175" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.6644</v>
       </c>
       <c r="H175" s="8" t="n">
-        <v>-0.0474</v>
+        <v>-0.0473</v>
       </c>
       <c r="I175" s="8" t="n">
-        <v>-0.1396089228705838</v>
+        <v>-0.10622881330305</v>
       </c>
       <c r="J175" s="10" t="n">
         <v>0.5</v>
@@ -9696,7 +9696,7 @@
       </c>
       <c r="B176" s="5" t="inlineStr">
         <is>
-          <t>MIN @ CHI</t>
+          <t>CHI @ CAR</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
@@ -9706,23 +9706,23 @@
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
-          <t>Over 45.5</t>
+          <t>Over 47.5</t>
         </is>
       </c>
       <c r="E176" s="12" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="F176" s="13" t="n">
-        <v>0.452</v>
+        <v>0.4633</v>
       </c>
       <c r="G176" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5349</v>
       </c>
       <c r="H176" s="13" t="n">
-        <v>-0.0475</v>
+        <v>-0.0474</v>
       </c>
       <c r="I176" s="13" t="n">
-        <v>-0.1371717248119999</v>
+        <v>-0.1338933082848991</v>
       </c>
       <c r="J176" s="15" t="n">
         <v>0.5</v>
@@ -9737,7 +9737,7 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>LV @ LAC</t>
+          <t>WSH @ PHI</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
@@ -9747,23 +9747,23 @@
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>Over 42.5</t>
+          <t>Over 46.5</t>
         </is>
       </c>
       <c r="E177" s="7" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="F177" s="8" t="n">
-        <v>0.452</v>
+        <v>0.4407</v>
       </c>
       <c r="G177" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5122</v>
       </c>
       <c r="H177" s="8" t="n">
-        <v>-0.0475</v>
+        <v>-0.0474</v>
       </c>
       <c r="I177" s="8" t="n">
-        <v>-0.1371610707292645</v>
+        <v>-0.1396089228705838</v>
       </c>
       <c r="J177" s="10" t="n">
         <v>0.5</v>
@@ -9783,28 +9783,28 @@
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>CHI ML</t>
+          <t>Over 45.5</t>
         </is>
       </c>
       <c r="E178" s="12" t="n">
-        <v>-198</v>
+        <v>-110</v>
       </c>
       <c r="F178" s="13" t="n">
-        <v>0.5918</v>
+        <v>0.452</v>
       </c>
       <c r="G178" s="13" t="n">
-        <v>0.6644</v>
+        <v>0.5238</v>
       </c>
       <c r="H178" s="13" t="n">
-        <v>-0.0477</v>
+        <v>-0.0475</v>
       </c>
       <c r="I178" s="13" t="n">
-        <v>-0.1083794388993304</v>
+        <v>-0.1371717248119999</v>
       </c>
       <c r="J178" s="15" t="n">
         <v>0.5</v>
@@ -9824,28 +9824,28 @@
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>LAC -8.5</t>
+          <t>Over 42.5</t>
         </is>
       </c>
       <c r="E179" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F179" s="8" t="n">
-        <v>0.4497</v>
+        <v>0.452</v>
       </c>
       <c r="G179" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H179" s="8" t="n">
-        <v>-0.048</v>
+        <v>-0.0475</v>
       </c>
       <c r="I179" s="8" t="n">
-        <v>-0.1414648242195523</v>
+        <v>-0.1371610707292645</v>
       </c>
       <c r="J179" s="10" t="n">
         <v>0.5</v>
@@ -9860,7 +9860,7 @@
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>IND @ KC</t>
+          <t>MIN @ CHI</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
@@ -9870,23 +9870,23 @@
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>KC ML</t>
+          <t>CHI ML</t>
         </is>
       </c>
       <c r="E180" s="12" t="n">
-        <v>-325</v>
+        <v>-198</v>
       </c>
       <c r="F180" s="13" t="n">
-        <v>0.6908</v>
+        <v>0.5918</v>
       </c>
       <c r="G180" s="13" t="n">
-        <v>0.7647</v>
+        <v>0.6644</v>
       </c>
       <c r="H180" s="13" t="n">
-        <v>-0.048</v>
+        <v>-0.0477</v>
       </c>
       <c r="I180" s="13" t="n">
-        <v>-0.09584827106608132</v>
+        <v>-0.1083794388993304</v>
       </c>
       <c r="J180" s="15" t="n">
         <v>0.5</v>
@@ -9901,7 +9901,7 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>CLE @ JAX</t>
+          <t>LV @ LAC</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
@@ -9911,23 +9911,23 @@
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>JAX -7.5</t>
+          <t>LAC -8.5</t>
         </is>
       </c>
       <c r="E181" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F181" s="8" t="n">
-        <v>0.4475</v>
+        <v>0.4497</v>
       </c>
       <c r="G181" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H181" s="8" t="n">
-        <v>-0.0485</v>
+        <v>-0.048</v>
       </c>
       <c r="I181" s="8" t="n">
-        <v>-0.1457269391298796</v>
+        <v>-0.1414648242195523</v>
       </c>
       <c r="J181" s="10" t="n">
         <v>0.5</v>
@@ -9942,7 +9942,7 @@
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>GB @ NYJ</t>
+          <t>IND @ KC</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
@@ -9952,23 +9952,23 @@
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>GB ML</t>
+          <t>KC ML</t>
         </is>
       </c>
       <c r="E182" s="12" t="n">
-        <v>-245</v>
+        <v>-325</v>
       </c>
       <c r="F182" s="13" t="n">
-        <v>0.6342</v>
+        <v>0.6908</v>
       </c>
       <c r="G182" s="13" t="n">
-        <v>0.7101</v>
+        <v>0.7647</v>
       </c>
       <c r="H182" s="13" t="n">
-        <v>-0.0485</v>
+        <v>-0.048</v>
       </c>
       <c r="I182" s="13" t="n">
-        <v>-0.1060297356626327</v>
+        <v>-0.09584827106608132</v>
       </c>
       <c r="J182" s="15" t="n">
         <v>0.5</v>
@@ -9983,33 +9983,33 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>SF @ LAR</t>
+          <t>CLE @ JAX</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>JAX -7.5</t>
         </is>
       </c>
       <c r="E183" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F183" s="8" t="n">
-        <v>0.447</v>
+        <v>0.4475</v>
       </c>
       <c r="G183" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H183" s="8" t="n">
-        <v>-0.0487</v>
+        <v>-0.0485</v>
       </c>
       <c r="I183" s="8" t="n">
-        <v>-0.14670024543173</v>
+        <v>-0.1457269391298796</v>
       </c>
       <c r="J183" s="10" t="n">
         <v>0.5</v>
@@ -10024,33 +10024,33 @@
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>DET @ BUF</t>
+          <t>GB @ NYJ</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>Over 52.5</t>
+          <t>GB ML</t>
         </is>
       </c>
       <c r="E184" s="12" t="n">
-        <v>-110</v>
+        <v>-245</v>
       </c>
       <c r="F184" s="13" t="n">
-        <v>0.447</v>
+        <v>0.6342</v>
       </c>
       <c r="G184" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.7101</v>
       </c>
       <c r="H184" s="13" t="n">
-        <v>-0.0487</v>
+        <v>-0.0485</v>
       </c>
       <c r="I184" s="13" t="n">
-        <v>-0.1467011878999994</v>
+        <v>-0.1060297356626327</v>
       </c>
       <c r="J184" s="15" t="n">
         <v>0.5</v>
@@ -10065,7 +10065,7 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>NO @ BAL</t>
+          <t>DET @ BUF</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
@@ -10075,7 +10075,7 @@
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>Over 46.5</t>
+          <t>Over 52.5</t>
         </is>
       </c>
       <c r="E185" s="7" t="n">
@@ -10091,7 +10091,7 @@
         <v>-0.0487</v>
       </c>
       <c r="I185" s="8" t="n">
-        <v>-0.1466985804382782</v>
+        <v>-0.1467011878999994</v>
       </c>
       <c r="J185" s="10" t="n">
         <v>0.5</v>
@@ -10106,7 +10106,7 @@
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>IND @ KC</t>
+          <t>NO @ BAL</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
@@ -10116,23 +10116,23 @@
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>Over 47.5</t>
+          <t>Over 46.5</t>
         </is>
       </c>
       <c r="E186" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F186" s="13" t="n">
-        <v>0.4445</v>
+        <v>0.447</v>
       </c>
       <c r="G186" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H186" s="13" t="n">
-        <v>-0.0492</v>
+        <v>-0.0487</v>
       </c>
       <c r="I186" s="13" t="n">
-        <v>-0.1514481393898844</v>
+        <v>-0.1466985804382782</v>
       </c>
       <c r="J186" s="15" t="n">
         <v>0.5</v>
@@ -10147,42 +10147,38 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>CLE @ JAX</t>
+          <t>IND @ KC</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>JAX ML</t>
+          <t>Over 47.5</t>
         </is>
       </c>
       <c r="E187" s="7" t="n">
-        <v>-380</v>
+        <v>-110</v>
       </c>
       <c r="F187" s="8" t="n">
-        <v>0.711</v>
+        <v>0.4445</v>
       </c>
       <c r="G187" s="8" t="n">
-        <v>0.7917</v>
+        <v>0.5238</v>
       </c>
       <c r="H187" s="8" t="n">
-        <v>-0.0494</v>
+        <v>-0.0492</v>
       </c>
       <c r="I187" s="8" t="n">
-        <v>-0.1010603885837269</v>
+        <v>-0.1514481393898844</v>
       </c>
       <c r="J187" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="K187" s="4" t="inlineStr">
-        <is>
-          <t>price -380 outside the allowed range</t>
-        </is>
-      </c>
+      <c r="K187" s="4" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="5" t="inlineStr">
@@ -10192,38 +10188,42 @@
       </c>
       <c r="B188" s="5" t="inlineStr">
         <is>
-          <t>GB @ MIN</t>
+          <t>CLE @ JAX</t>
         </is>
       </c>
       <c r="C188" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D188" s="5" t="inlineStr">
         <is>
-          <t>Over 45.5</t>
+          <t>JAX ML</t>
         </is>
       </c>
       <c r="E188" s="12" t="n">
-        <v>-110</v>
+        <v>-380</v>
       </c>
       <c r="F188" s="13" t="n">
-        <v>0.4395</v>
+        <v>0.711</v>
       </c>
       <c r="G188" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.7917</v>
       </c>
       <c r="H188" s="13" t="n">
-        <v>-0.0501</v>
+        <v>-0.0494</v>
       </c>
       <c r="I188" s="13" t="n">
-        <v>-0.1609118281560395</v>
+        <v>-0.1010603885837269</v>
       </c>
       <c r="J188" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="K188" s="5" t="inlineStr"/>
+      <c r="K188" s="5" t="inlineStr">
+        <is>
+          <t>price -380 outside the allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
@@ -10233,33 +10233,33 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>MIA @ SF</t>
+          <t>GB @ MIN</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>SF -10.5</t>
+          <t>Over 45.5</t>
         </is>
       </c>
       <c r="E189" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F189" s="8" t="n">
-        <v>0.435</v>
+        <v>0.4395</v>
       </c>
       <c r="G189" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H189" s="8" t="n">
-        <v>-0.0508</v>
+        <v>-0.0501</v>
       </c>
       <c r="I189" s="8" t="n">
-        <v>-0.1694930391118568</v>
+        <v>-0.1609118281560395</v>
       </c>
       <c r="J189" s="10" t="n">
         <v>0.5</v>
@@ -10274,33 +10274,33 @@
       </c>
       <c r="B190" s="5" t="inlineStr">
         <is>
-          <t>ARI @ LAC</t>
+          <t>MIA @ SF</t>
         </is>
       </c>
       <c r="C190" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D190" s="5" t="inlineStr">
         <is>
-          <t>Over 46.5</t>
+          <t>SF -10.5</t>
         </is>
       </c>
       <c r="E190" s="12" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="F190" s="13" t="n">
-        <v>0.4458</v>
+        <v>0.435</v>
       </c>
       <c r="G190" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.5238</v>
       </c>
       <c r="H190" s="13" t="n">
-        <v>-0.0509</v>
+        <v>-0.0508</v>
       </c>
       <c r="I190" s="13" t="n">
-        <v>-0.1665664785019195</v>
+        <v>-0.1694930391118568</v>
       </c>
       <c r="J190" s="15" t="n">
         <v>0.5</v>
@@ -10315,38 +10315,42 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>DEN @ KC</t>
+          <t>MIA @ SF</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>Over 42.5</t>
+          <t>SF ML</t>
         </is>
       </c>
       <c r="E191" s="7" t="n">
-        <v>-110</v>
+        <v>-675</v>
       </c>
       <c r="F191" s="8" t="n">
-        <v>0.4321</v>
+        <v>0.7795</v>
       </c>
       <c r="G191" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.871</v>
       </c>
       <c r="H191" s="8" t="n">
         <v>-0.0512</v>
       </c>
       <c r="I191" s="8" t="n">
-        <v>-0.1750148280233252</v>
+        <v>-0.1042615164820876</v>
       </c>
       <c r="J191" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="K191" s="4" t="inlineStr"/>
+      <c r="K191" s="4" t="inlineStr">
+        <is>
+          <t>price -675 outside the allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="5" t="inlineStr">
@@ -10356,42 +10360,38 @@
       </c>
       <c r="B192" s="5" t="inlineStr">
         <is>
-          <t>MIA @ SF</t>
+          <t>NO @ DET</t>
         </is>
       </c>
       <c r="C192" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D192" s="5" t="inlineStr">
         <is>
-          <t>SF ML</t>
+          <t>Over 49.5</t>
         </is>
       </c>
       <c r="E192" s="12" t="n">
-        <v>-675</v>
+        <v>-112</v>
       </c>
       <c r="F192" s="13" t="n">
-        <v>0.7795</v>
+        <v>0.4336</v>
       </c>
       <c r="G192" s="13" t="n">
-        <v>0.871</v>
+        <v>0.5283</v>
       </c>
       <c r="H192" s="13" t="n">
-        <v>-0.0512</v>
+        <v>-0.0516</v>
       </c>
       <c r="I192" s="13" t="n">
-        <v>-0.1042615164820876</v>
+        <v>-0.1791795107909712</v>
       </c>
       <c r="J192" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="K192" s="5" t="inlineStr">
-        <is>
-          <t>price -675 outside the allowed range</t>
-        </is>
-      </c>
+      <c r="K192" s="5" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
@@ -10401,38 +10401,42 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>NO @ DET</t>
+          <t>SEA @ ARI</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>Over 49.5</t>
+          <t>SEA ML</t>
         </is>
       </c>
       <c r="E193" s="7" t="n">
-        <v>-112</v>
+        <v>-550</v>
       </c>
       <c r="F193" s="8" t="n">
-        <v>0.4336</v>
+        <v>0.7507</v>
       </c>
       <c r="G193" s="8" t="n">
-        <v>0.5283</v>
+        <v>0.8462</v>
       </c>
       <c r="H193" s="8" t="n">
-        <v>-0.0516</v>
+        <v>-0.0517</v>
       </c>
       <c r="I193" s="8" t="n">
-        <v>-0.1791795107909712</v>
+        <v>-0.1119734660432905</v>
       </c>
       <c r="J193" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="K193" s="4" t="inlineStr"/>
+      <c r="K193" s="4" t="inlineStr">
+        <is>
+          <t>price -550 outside the allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="5" t="inlineStr">
@@ -10442,42 +10446,38 @@
       </c>
       <c r="B194" s="5" t="inlineStr">
         <is>
-          <t>SEA @ ARI</t>
+          <t>ARI @ LAC</t>
         </is>
       </c>
       <c r="C194" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D194" s="5" t="inlineStr">
         <is>
-          <t>SEA ML</t>
+          <t>Over 46.5</t>
         </is>
       </c>
       <c r="E194" s="12" t="n">
-        <v>-550</v>
+        <v>-115</v>
       </c>
       <c r="F194" s="13" t="n">
-        <v>0.7507</v>
+        <v>0.4384</v>
       </c>
       <c r="G194" s="13" t="n">
-        <v>0.8462</v>
+        <v>0.5349</v>
       </c>
       <c r="H194" s="13" t="n">
-        <v>-0.0517</v>
+        <v>-0.0518</v>
       </c>
       <c r="I194" s="13" t="n">
-        <v>-0.1119734660432905</v>
+        <v>-0.1804243326382279</v>
       </c>
       <c r="J194" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="K194" s="5" t="inlineStr">
-        <is>
-          <t>price -550 outside the allowed range</t>
-        </is>
-      </c>
+      <c r="K194" s="5" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
@@ -11988,7 +11988,7 @@
         <v>-3</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>39.8</v>
+        <v>40.9</v>
       </c>
       <c r="G24" s="11" t="n">
         <v>42.5</v>
@@ -12022,7 +12022,7 @@
         <v>2.5</v>
       </c>
       <c r="F25" s="16" t="n">
-        <v>48.2</v>
+        <v>48.7</v>
       </c>
       <c r="G25" s="16" t="n">
         <v>48.5</v>
@@ -12056,7 +12056,7 @@
         <v>-10.5</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>44.2</v>
+        <v>43.9</v>
       </c>
       <c r="G26" s="11" t="n">
         <v>46.5</v>
@@ -12226,7 +12226,7 @@
         <v>3.5</v>
       </c>
       <c r="F31" s="16" t="n">
-        <v>47.1</v>
+        <v>47.4</v>
       </c>
       <c r="G31" s="16" t="n">
         <v>48.5</v>
@@ -12260,7 +12260,7 @@
         <v>1.5</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>44.9</v>
+        <v>44.7</v>
       </c>
       <c r="G32" s="11" t="n">
         <v>44.5</v>
@@ -12464,7 +12464,7 @@
         <v>-3.5</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>46.4</v>
+        <v>47.4</v>
       </c>
       <c r="G38" s="11" t="n">
         <v>48.5</v>
@@ -17429,10 +17429,10 @@
         <v>49.5</v>
       </c>
       <c r="I61" s="7" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="J61" s="7" t="n">
-        <v>-305</v>
+        <v>-310</v>
       </c>
       <c r="K61" s="17" t="n">
         <v>0</v>
@@ -36140,7 +36140,7 @@
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>Phillips (triceps/illness) was traded to the Bears on Sunday, Ian Rapoport of ESPN and NFL Network reports.</t>
+          <t>Phillips (triceps/illness) was traded to the Bears from the Falcons on Sunday, Ian Rapoport of ESPN and NFL Network reports.</t>
         </is>
       </c>
     </row>
@@ -40988,7 +40988,7 @@
       </c>
       <c r="F286" s="5" t="inlineStr">
         <is>
-          <t>The NFL placed Jacobs on the Commissioner's Exempt List on Sunday, Adam Schefter of ESPN reports.</t>
+          <t>The NFL placed Jacobs (groin) on the Commissioner's Exempt List on Sunday, Adam Schefter of ESPN reports.</t>
         </is>
       </c>
     </row>
@@ -57612,20 +57612,20 @@
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>72.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="E5" s="17" t="n">
-        <v>8.300000000000001</v>
+        <v>6.1</v>
       </c>
       <c r="F5" s="17" t="n">
-        <v>13.2</v>
+        <v>11</v>
       </c>
       <c r="G5" s="17" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Overcast</t>
         </is>
       </c>
       <c r="I5" s="9" t="n">
@@ -57650,30 +57650,26 @@
         </is>
       </c>
       <c r="D6" s="19" t="n">
-        <v>64.40000000000001</v>
+        <v>62</v>
       </c>
       <c r="E6" s="19" t="n">
-        <v>9.800000000000001</v>
+        <v>3</v>
       </c>
       <c r="F6" s="19" t="n">
-        <v>24.2</v>
+        <v>12.5</v>
       </c>
       <c r="G6" s="19" t="n">
         <v>8</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>Light drizzle</t>
+          <t>Partly cloudy</t>
         </is>
       </c>
       <c r="I6" s="14" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>Wind 10 mph (gusts 24)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -57692,16 +57688,16 @@
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>71.7</v>
+        <v>81.7</v>
       </c>
       <c r="E7" s="17" t="n">
-        <v>8.9</v>
+        <v>6.7</v>
       </c>
       <c r="F7" s="17" t="n">
-        <v>13.9</v>
+        <v>2.7</v>
       </c>
       <c r="G7" s="17" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
@@ -57730,30 +57726,26 @@
         </is>
       </c>
       <c r="D8" s="19" t="n">
-        <v>77.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="E8" s="19" t="n">
-        <v>11.2</v>
+        <v>9</v>
       </c>
       <c r="F8" s="19" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="G8" s="19" t="n">
         <v>19</v>
       </c>
-      <c r="G8" s="19" t="n">
-        <v>1</v>
-      </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>Mainly clear</t>
+          <t>Overcast</t>
         </is>
       </c>
       <c r="I8" s="14" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>Wind 11 mph (gusts 19) · retractable roof — effect halved</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -57772,28 +57764,28 @@
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>97.3</v>
+        <v>96.2</v>
       </c>
       <c r="E9" s="17" t="n">
-        <v>5.7</v>
+        <v>13.5</v>
       </c>
       <c r="F9" s="17" t="n">
-        <v>6.9</v>
+        <v>2.9</v>
       </c>
       <c r="G9" s="17" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Partly cloudy</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="I9" s="9" t="n">
-        <v>-0.25</v>
+        <v>-0.65</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>97°F · retractable roof — effect halved</t>
+          <t>Wind 14 mph (gusts 3) · 96°F · retractable roof — effect halved</t>
         </is>
       </c>
     </row>
@@ -57814,20 +57806,20 @@
         </is>
       </c>
       <c r="D10" s="19" t="n">
-        <v>83</v>
+        <v>72.2</v>
       </c>
       <c r="E10" s="19" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="F10" s="19" t="n">
-        <v>8.1</v>
+        <v>6</v>
       </c>
       <c r="G10" s="19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Overcast</t>
         </is>
       </c>
       <c r="I10" s="14" t="n">
@@ -57852,20 +57844,20 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>98.40000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="E11" s="17" t="n">
-        <v>4</v>
+        <v>10.3</v>
       </c>
       <c r="F11" s="17" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="G11" s="17" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Overcast</t>
         </is>
       </c>
       <c r="I11" s="9" t="n">
@@ -57873,7 +57865,7 @@
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>98°F</t>
+          <t>92°F</t>
         </is>
       </c>
     </row>
@@ -57894,20 +57886,20 @@
         </is>
       </c>
       <c r="D12" s="19" t="n">
-        <v>76.59999999999999</v>
+        <v>85</v>
       </c>
       <c r="E12" s="19" t="n">
-        <v>13.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F12" s="19" t="n">
-        <v>23.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G12" s="19" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>Mainly clear</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="I12" s="14" t="n">
@@ -57936,20 +57928,20 @@
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>82.59999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="E13" s="17" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="F13" s="17" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="G13" s="17" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Overcast</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
@@ -57974,20 +57966,20 @@
         </is>
       </c>
       <c r="D14" s="19" t="n">
-        <v>79.8</v>
+        <v>88.7</v>
       </c>
       <c r="E14" s="19" t="n">
-        <v>7.3</v>
+        <v>5.2</v>
       </c>
       <c r="F14" s="19" t="n">
-        <v>12.5</v>
+        <v>6.9</v>
       </c>
       <c r="G14" s="19" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>Mainly clear</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="I14" s="14" t="n">
@@ -58012,16 +58004,16 @@
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>81.59999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="E15" s="17" t="n">
-        <v>9</v>
+        <v>12.4</v>
       </c>
       <c r="F15" s="17" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="G15" s="17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
@@ -58029,9 +58021,13 @@
         </is>
       </c>
       <c r="I15" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr"/>
+        <v>-0.68</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>Wind 12 mph (gusts 5) · canopy — wind damped</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -58050,20 +58046,20 @@
         </is>
       </c>
       <c r="D16" s="19" t="n">
-        <v>67.90000000000001</v>
+        <v>65</v>
       </c>
       <c r="E16" s="19" t="n">
-        <v>8.300000000000001</v>
+        <v>1.6</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>10.5</v>
+        <v>34.4</v>
       </c>
       <c r="G16" s="19" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>Mainly clear</t>
+          <t>Overcast</t>
         </is>
       </c>
       <c r="I16" s="14" t="n">
@@ -58092,20 +58088,20 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>103</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="E17" s="17" t="n">
-        <v>16.8</v>
+        <v>15</v>
       </c>
       <c r="F17" s="17" t="n">
-        <v>19.9</v>
+        <v>2.5</v>
       </c>
       <c r="G17" s="17" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Mainly clear</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
@@ -58134,20 +58130,20 @@
         </is>
       </c>
       <c r="D18" s="19" t="n">
-        <v>78.09999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="E18" s="19" t="n">
-        <v>9.300000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="F18" s="19" t="n">
-        <v>13.9</v>
+        <v>14.3</v>
       </c>
       <c r="G18" s="19" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Drizzle</t>
         </is>
       </c>
       <c r="I18" s="14" t="n">
@@ -58172,30 +58168,26 @@
         </is>
       </c>
       <c r="D19" s="17" t="n">
-        <v>72.09999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="E19" s="17" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F19" s="17" t="n">
-        <v>19.7</v>
+        <v>13</v>
       </c>
       <c r="G19" s="17" t="n">
         <v>10</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Overcast</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>Wind 8 mph (gusts 20)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -58214,30 +58206,26 @@
         </is>
       </c>
       <c r="D20" s="19" t="n">
-        <v>104</v>
+        <v>68</v>
       </c>
       <c r="E20" s="19" t="n">
-        <v>15.8</v>
+        <v>7.8</v>
       </c>
       <c r="F20" s="19" t="n">
-        <v>24.8</v>
+        <v>16.6</v>
       </c>
       <c r="G20" s="19" t="n">
         <v>19</v>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>Mainly clear</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="I20" s="14" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="J20" s="5" t="inlineStr">
-        <is>
-          <t>Wind 16 mph (gusts 25) · 104°F</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">

--- a/NFL_Edge_Model.xlsx
+++ b/NFL_Edge_Model.xlsx
@@ -224,8 +224,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblBest" displayName="tblBest" ref="A4:N8" headerRowCount="1">
-  <autoFilter ref="A4:N8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblBest" displayName="tblBest" ref="A4:N9" headerRowCount="1">
+  <autoFilter ref="A4:N9"/>
   <tableColumns count="14">
     <tableColumn id="1" name="Tier"/>
     <tableColumn id="2" name="Game"/>
@@ -692,7 +692,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Snapshot of the live model, generated 2026-09-01T05:13:27+00:00. Read-only: the model runs in the pipeline, not in this file.</t>
+          <t>Snapshot of the live model, generated 2026-09-01T12:04:47+00:00. Read-only: the model runs in the pipeline, not in this file.</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01T05:13:27+00:00</t>
+          <t>2026-09-01T12:04:47+00:00</t>
         </is>
       </c>
     </row>
@@ -2289,7 +2289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2456,7 +2456,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>DEN @ KC</t>
+          <t>NO @ DET</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -2466,39 +2466,39 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Under 42.5</t>
+          <t>Under 49.5</t>
         </is>
       </c>
       <c r="E6" s="12" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5849</v>
+        <v>0.5714</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5122</v>
       </c>
       <c r="H6" s="13" t="n">
-        <v>0.0442</v>
+        <v>0.0436</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>0.0611</v>
+        <v>0.0592</v>
       </c>
       <c r="J6" s="14" t="n">
-        <v>-3.42</v>
+        <v>-3.05</v>
       </c>
       <c r="K6" s="15" t="n">
         <v>0.5</v>
       </c>
       <c r="L6" s="16" t="n">
-        <v>18.1</v>
+        <v>19.5</v>
       </c>
       <c r="M6" s="16" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="N6" s="5" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -2510,49 +2510,49 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>NO @ DET</t>
+          <t>MIA @ SF</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Under 49.5</t>
+          <t>MIA ML</t>
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>-105</v>
+        <v>470</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>0.5714</v>
+        <v>0.2336</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.1754</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>0.0436</v>
+        <v>0.0431</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>0.0592</v>
+        <v>0.0581</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>-3.05</v>
+        <v>-1.79</v>
       </c>
       <c r="K7" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="L7" s="11" t="n">
-        <v>19.5</v>
+        <v>18.4</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>27</v>
+        <v>27.1</v>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -2564,49 +2564,103 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>MIA @ SF</t>
+          <t>SF @ LAR</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>MIA ML</t>
+          <t>Under 48.5</t>
         </is>
       </c>
       <c r="E8" s="12" t="n">
-        <v>470</v>
+        <v>-110</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.2336</v>
+        <v>0.5752</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>0.1754</v>
+        <v>0.5238</v>
       </c>
       <c r="H8" s="13" t="n">
-        <v>0.0431</v>
+        <v>0.0403</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>0.0581</v>
+        <v>0.0514</v>
       </c>
       <c r="J8" s="14" t="n">
-        <v>-1.79</v>
+        <v>-3.02</v>
       </c>
       <c r="K8" s="15" t="n">
         <v>0.5</v>
       </c>
       <c r="L8" s="16" t="n">
-        <v>18.4</v>
+        <v>21</v>
       </c>
       <c r="M8" s="16" t="n">
-        <v>27.1</v>
+        <v>24.5</v>
       </c>
       <c r="N8" s="5" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>LEAN</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>NYJ @ TEN</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Over 38.5</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>-115</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>0.5863</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>0.5349</v>
+      </c>
+      <c r="H9" s="8" t="n">
+        <v>0.0403</v>
+      </c>
+      <c r="I9" s="8" t="n">
+        <v>0.0514</v>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="K9" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L9" s="11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="M9" s="11" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2814,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>DEN @ KC</t>
+          <t>NO @ DET</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -2770,23 +2824,23 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Under 42.5</t>
+          <t>Under 49.5</t>
         </is>
       </c>
       <c r="E6" s="12" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5849</v>
+        <v>0.5714</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5122</v>
       </c>
       <c r="H6" s="13" t="n">
-        <v>0.0442</v>
+        <v>0.0436</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>0.1165958889485751</v>
+        <v>0.1156289126830108</v>
       </c>
       <c r="J6" s="15" t="n">
         <v>0.5</v>
@@ -2801,33 +2855,33 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>NO @ DET</t>
+          <t>MIA @ SF</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Under 49.5</t>
+          <t>MIA ML</t>
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>-105</v>
+        <v>470</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>0.5714</v>
+        <v>0.2336</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.1754</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>0.0436</v>
+        <v>0.0431</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>0.1156289126830108</v>
+        <v>0.3288535048635309</v>
       </c>
       <c r="J7" s="10" t="n">
         <v>0.5</v>
@@ -2842,33 +2896,33 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>MIA @ SF</t>
+          <t>SF @ LAR</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>MIA ML</t>
+          <t>Under 48.5</t>
         </is>
       </c>
       <c r="E8" s="12" t="n">
-        <v>470</v>
+        <v>-110</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.2336</v>
+        <v>0.5752</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>0.1754</v>
+        <v>0.5238</v>
       </c>
       <c r="H8" s="13" t="n">
-        <v>0.0431</v>
+        <v>0.0403</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>0.3288535048635309</v>
+        <v>0.09813079684167703</v>
       </c>
       <c r="J8" s="15" t="n">
         <v>0.5</v>
@@ -2878,47 +2932,43 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>LEAN</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>SEA @ ARI</t>
+          <t>NYJ @ TEN</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>ARI ML</t>
+          <t>Over 38.5</t>
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>410</v>
+        <v>-115</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>0.2556</v>
+        <v>0.5863</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>0.1961</v>
+        <v>0.5349</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>0.0437</v>
+        <v>0.0403</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>0.3013869591776513</v>
+        <v>0.09609813123903277</v>
       </c>
       <c r="J9" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>correlated with a stronger play on the same game</t>
-        </is>
-      </c>
+      <c r="K9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -2928,33 +2978,33 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>MIA @ SF</t>
+          <t>SEA @ ARI</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>MIA +10.5</t>
+          <t>ARI ML</t>
         </is>
       </c>
       <c r="E10" s="12" t="n">
-        <v>-110</v>
+        <v>410</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5784</v>
+        <v>0.2556</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.1961</v>
       </c>
       <c r="H10" s="13" t="n">
-        <v>0.0417</v>
+        <v>0.0437</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>0.1041938633967684</v>
+        <v>0.3013869591776513</v>
       </c>
       <c r="J10" s="15" t="n">
         <v>0.5</v>
@@ -2973,38 +3023,42 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>ARI @ LAC</t>
+          <t>MIA @ SF</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Under 46.5</t>
+          <t>MIA +10.5</t>
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>0.5616</v>
+        <v>0.5784</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.5238</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>0.0394</v>
+        <v>0.0417</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>0.09650071503637747</v>
+        <v>0.1041938633967684</v>
       </c>
       <c r="J11" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="K11" s="4" t="inlineStr"/>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>correlated with a stronger play on the same game</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -3014,7 +3068,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>NYJ @ TEN</t>
+          <t>ARI @ LAC</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -3024,23 +3078,23 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Over 38.5</t>
+          <t>Under 46.5</t>
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>-115</v>
+        <v>-105</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5814</v>
+        <v>0.5616</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.5122</v>
       </c>
       <c r="H12" s="13" t="n">
-        <v>0.0379</v>
+        <v>0.0394</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>0.08704652960204162</v>
+        <v>0.09650071503637747</v>
       </c>
       <c r="J12" s="15" t="n">
         <v>0.5</v>
@@ -3564,16 +3618,16 @@
         <v>300</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>0.2796</v>
+        <v>0.2797</v>
       </c>
       <c r="G25" s="8" t="n">
         <v>0.25</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>0.027</v>
+        <v>0.0271</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>0.1172753011722295</v>
+        <v>0.1179143496855546</v>
       </c>
       <c r="J25" s="10" t="n">
         <v>0.5</v>
@@ -3711,7 +3765,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>TB @ CIN</t>
+          <t>DEN @ KC</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -3721,23 +3775,23 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Under 51.5</t>
+          <t>Under 42.5</t>
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>-118</v>
+        <v>-110</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>0.5641</v>
+        <v>0.5505</v>
       </c>
       <c r="G29" s="8" t="n">
-        <v>0.5413</v>
+        <v>0.5238</v>
       </c>
       <c r="H29" s="8" t="n">
-        <v>0.0216</v>
+        <v>0.0248</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>0.04211539969282557</v>
+        <v>0.05101886947689394</v>
       </c>
       <c r="J29" s="10" t="n">
         <v>0.5</v>
@@ -3752,33 +3806,33 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>LV @ LAC</t>
+          <t>TB @ CIN</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>LV ML</t>
+          <t>Under 51.5</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>295</v>
+        <v>-118</v>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.2754</v>
+        <v>0.5641</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>0.2532</v>
+        <v>0.5413</v>
       </c>
       <c r="H30" s="13" t="n">
-        <v>0.0211</v>
+        <v>0.0216</v>
       </c>
       <c r="I30" s="13" t="n">
-        <v>0.08718388052155757</v>
+        <v>0.04211539969282557</v>
       </c>
       <c r="J30" s="15" t="n">
         <v>0.5</v>
@@ -3793,33 +3847,33 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>NYG @ LAR</t>
+          <t>LV @ LAC</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>NYG +8.5</t>
+          <t>LV ML</t>
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>-110</v>
+        <v>295</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>0.5457</v>
+        <v>0.2754</v>
       </c>
       <c r="G31" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.2532</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>0.0208</v>
+        <v>0.0211</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>0.04184409282887513</v>
+        <v>0.08718388052155757</v>
       </c>
       <c r="J31" s="10" t="n">
         <v>0.5</v>
@@ -3875,33 +3929,33 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>NE @ SEA</t>
+          <t>NYG @ LAR</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>NE ML</t>
+          <t>NYG +8.5</t>
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>150</v>
+        <v>-110</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>0.4203</v>
+        <v>0.5454</v>
       </c>
       <c r="G33" s="8" t="n">
-        <v>0.4</v>
+        <v>0.5238</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>0.0194</v>
+        <v>0.0205</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>0.05021125444334651</v>
+        <v>0.04114550651634863</v>
       </c>
       <c r="J33" s="10" t="n">
         <v>0.5</v>
@@ -3916,7 +3970,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>PHI @ TEN</t>
+          <t>NE @ SEA</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -3926,23 +3980,23 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>TEN ML</t>
+          <t>NE ML</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.3762</v>
+        <v>0.4203</v>
       </c>
       <c r="G34" s="13" t="n">
-        <v>0.3571</v>
+        <v>0.4</v>
       </c>
       <c r="H34" s="13" t="n">
-        <v>0.0183</v>
+        <v>0.0194</v>
       </c>
       <c r="I34" s="13" t="n">
-        <v>0.05284850326466584</v>
+        <v>0.05021125444334651</v>
       </c>
       <c r="J34" s="15" t="n">
         <v>0.5</v>
@@ -3957,33 +4011,33 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>CLE @ JAX</t>
+          <t>PHI @ TEN</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>CLE +7.5</t>
+          <t>TEN ML</t>
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>-110</v>
+        <v>180</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>0.542</v>
+        <v>0.3762</v>
       </c>
       <c r="G35" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.3571</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>0.0176</v>
+        <v>0.0183</v>
       </c>
       <c r="I35" s="8" t="n">
-        <v>0.0347828407971677</v>
+        <v>0.05284850326466584</v>
       </c>
       <c r="J35" s="10" t="n">
         <v>0.5</v>
@@ -3998,33 +4052,33 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>MIA @ LV</t>
+          <t>CLE @ JAX</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>MIA ML</t>
+          <t>CLE +7.5</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>164</v>
+        <v>-110</v>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.3971</v>
+        <v>0.5422</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>0.3788</v>
+        <v>0.5238</v>
       </c>
       <c r="H36" s="13" t="n">
-        <v>0.0176</v>
+        <v>0.0177</v>
       </c>
       <c r="I36" s="13" t="n">
-        <v>0.04787514855665331</v>
+        <v>0.03512992094286965</v>
       </c>
       <c r="J36" s="15" t="n">
         <v>0.5</v>
@@ -4039,7 +4093,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>MIN @ CHI</t>
+          <t>MIA @ LV</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -4049,23 +4103,23 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>MIN ML</t>
+          <t>MIA ML</t>
         </is>
       </c>
       <c r="E37" s="7" t="n">
         <v>164</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>0.3962</v>
+        <v>0.3971</v>
       </c>
       <c r="G37" s="8" t="n">
         <v>0.3788</v>
       </c>
       <c r="H37" s="8" t="n">
-        <v>0.0168</v>
+        <v>0.0176</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>0.0455345620803117</v>
+        <v>0.04787514855665331</v>
       </c>
       <c r="J37" s="10" t="n">
         <v>0.5</v>
@@ -4080,33 +4134,33 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>IND @ KC</t>
+          <t>MIN @ CHI</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>IND +6.5</t>
+          <t>MIN ML</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>-110</v>
+        <v>164</v>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.5411</v>
+        <v>0.3962</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.3788</v>
       </c>
       <c r="H38" s="13" t="n">
         <v>0.0168</v>
       </c>
       <c r="I38" s="13" t="n">
-        <v>0.03303001835355274</v>
+        <v>0.0455345620803117</v>
       </c>
       <c r="J38" s="15" t="n">
         <v>0.5</v>
@@ -4121,33 +4175,33 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>NYG @ LAR</t>
+          <t>IND @ KC</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>NYG ML</t>
+          <t>IND +6.5</t>
         </is>
       </c>
       <c r="E39" s="7" t="n">
-        <v>300</v>
+        <v>-110</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>0.2672</v>
+        <v>0.5411</v>
       </c>
       <c r="G39" s="8" t="n">
-        <v>0.25</v>
+        <v>0.5238</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>0.0166</v>
+        <v>0.0168</v>
       </c>
       <c r="I39" s="8" t="n">
-        <v>0.0681184473903711</v>
+        <v>0.03303001835355274</v>
       </c>
       <c r="J39" s="10" t="n">
         <v>0.5</v>
@@ -4162,33 +4216,33 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>SF @ LAR</t>
+          <t>NYG @ LAR</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Under 48.5</t>
+          <t>NYG ML</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>-110</v>
+        <v>300</v>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.5405</v>
+        <v>0.2668</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.25</v>
       </c>
       <c r="H40" s="13" t="n">
-        <v>0.0162</v>
+        <v>0.0163</v>
       </c>
       <c r="I40" s="13" t="n">
-        <v>0.0319130781248223</v>
+        <v>0.06687638084325775</v>
       </c>
       <c r="J40" s="15" t="n">
         <v>0.5</v>
@@ -4203,33 +4257,33 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>CLE @ JAX</t>
+          <t>NE @ SEA</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Over 40.5</t>
+          <t>NE +3.5</t>
         </is>
       </c>
       <c r="E41" s="7" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>0.538</v>
+        <v>0.5456</v>
       </c>
       <c r="G41" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5349</v>
       </c>
       <c r="H41" s="8" t="n">
-        <v>0.0139</v>
+        <v>0.0106</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>0.02712503029680507</v>
+        <v>0.02004531325434894</v>
       </c>
       <c r="J41" s="10" t="n">
         <v>0.5</v>
@@ -4249,28 +4303,28 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>NE +3.5</t>
+          <t>Under 44.5</t>
         </is>
       </c>
       <c r="E42" s="12" t="n">
         <v>-115</v>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.5456</v>
+        <v>0.5443</v>
       </c>
       <c r="G42" s="13" t="n">
         <v>0.5349</v>
       </c>
       <c r="H42" s="13" t="n">
-        <v>0.0106</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="I42" s="13" t="n">
-        <v>0.02004531325434894</v>
+        <v>0.01763314497491086</v>
       </c>
       <c r="J42" s="15" t="n">
         <v>0.5</v>
@@ -4285,33 +4339,33 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>SF @ LAR</t>
+          <t>CAR @ ATL</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>SF ML</t>
+          <t>Under 43.5</t>
         </is>
       </c>
       <c r="E43" s="7" t="n">
-        <v>164</v>
+        <v>-102</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>0.3883</v>
+        <v>0.5142</v>
       </c>
       <c r="G43" s="8" t="n">
-        <v>0.3788</v>
+        <v>0.505</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>0.0095</v>
+        <v>0.0092</v>
       </c>
       <c r="I43" s="8" t="n">
-        <v>0.02501076933874147</v>
+        <v>0.01840603867218615</v>
       </c>
       <c r="J43" s="10" t="n">
         <v>0.5</v>
@@ -4326,33 +4380,33 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>NE @ SEA</t>
+          <t>PHI @ TEN</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Under 44.5</t>
+          <t>TEN +4.5</t>
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.5443</v>
+        <v>0.5331</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.5238</v>
       </c>
       <c r="H44" s="13" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0092</v>
       </c>
       <c r="I44" s="13" t="n">
-        <v>0.01763314497491086</v>
+        <v>0.01775328317101132</v>
       </c>
       <c r="J44" s="15" t="n">
         <v>0.5</v>
@@ -4367,33 +4421,33 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>CAR @ ATL</t>
+          <t>SF @ LAR</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Under 43.5</t>
+          <t>SF ML</t>
         </is>
       </c>
       <c r="E45" s="7" t="n">
-        <v>-102</v>
+        <v>164</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>0.5142</v>
+        <v>0.388</v>
       </c>
       <c r="G45" s="8" t="n">
-        <v>0.505</v>
+        <v>0.3788</v>
       </c>
       <c r="H45" s="8" t="n">
-        <v>0.0092</v>
+        <v>0.0091</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>0.01840603867218615</v>
+        <v>0.02408115735673189</v>
       </c>
       <c r="J45" s="10" t="n">
         <v>0.5</v>
@@ -4408,33 +4462,33 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>PHI @ TEN</t>
+          <t>ATL @ GB</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>TEN +4.5</t>
+          <t>Under 46.5</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.5331</v>
+        <v>0.533</v>
       </c>
       <c r="G46" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H46" s="13" t="n">
-        <v>0.0092</v>
+        <v>0.0091</v>
       </c>
       <c r="I46" s="13" t="n">
-        <v>0.01775328317101132</v>
+        <v>0.01749282810775288</v>
       </c>
       <c r="J46" s="15" t="n">
         <v>0.5</v>
@@ -4449,7 +4503,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>ATL @ GB</t>
+          <t>ATL @ PIT</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -4459,23 +4513,23 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Under 46.5</t>
+          <t>Over 42.5</t>
         </is>
       </c>
       <c r="E47" s="7" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>0.533</v>
+        <v>0.5191</v>
       </c>
       <c r="G47" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5122</v>
       </c>
       <c r="H47" s="8" t="n">
-        <v>0.0091</v>
+        <v>0.0068</v>
       </c>
       <c r="I47" s="8" t="n">
-        <v>0.01749282810775288</v>
+        <v>0.01342415224820337</v>
       </c>
       <c r="J47" s="10" t="n">
         <v>0.5</v>
@@ -4490,7 +4544,7 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>ATL @ PIT</t>
+          <t>CLE @ JAX</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
@@ -4500,23 +4554,23 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Over 42.5</t>
+          <t>Over 40.5</t>
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.5191</v>
+        <v>0.5305</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>0.5122</v>
+        <v>0.5238</v>
       </c>
       <c r="H48" s="13" t="n">
-        <v>0.0068</v>
+        <v>0.0066</v>
       </c>
       <c r="I48" s="13" t="n">
-        <v>0.01342415224820337</v>
+        <v>0.01268771139495323</v>
       </c>
       <c r="J48" s="15" t="n">
         <v>0.5</v>
@@ -4999,16 +5053,16 @@
         <v>-130</v>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.5667</v>
+        <v>0.5666</v>
       </c>
       <c r="G60" s="13" t="n">
         <v>0.5652</v>
       </c>
       <c r="H60" s="13" t="n">
-        <v>0.0015</v>
+        <v>0.0013</v>
       </c>
       <c r="I60" s="13" t="n">
-        <v>0.002661666039075805</v>
+        <v>0.002347016438638383</v>
       </c>
       <c r="J60" s="15" t="n">
         <v>0.5</v>
@@ -5163,16 +5217,16 @@
         <v>-115</v>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.5348000000000001</v>
+        <v>0.5347</v>
       </c>
       <c r="G64" s="13" t="n">
         <v>0.5349</v>
       </c>
       <c r="H64" s="13" t="n">
-        <v>-0</v>
+        <v>-0.0002</v>
       </c>
       <c r="I64" s="13" t="n">
-        <v>-7.207569994466256e-05</v>
+        <v>-0.000408162702336401</v>
       </c>
       <c r="J64" s="15" t="n">
         <v>0.5</v>
@@ -5351,33 +5405,33 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>SF @ LAR</t>
+          <t>BUF @ HOU</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>SF +3.5</t>
+          <t>BUF ML</t>
         </is>
       </c>
       <c r="E69" s="7" t="n">
-        <v>-108</v>
+        <v>-118</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>0.5157</v>
+        <v>0.5374</v>
       </c>
       <c r="G69" s="8" t="n">
-        <v>0.5192</v>
+        <v>0.5413</v>
       </c>
       <c r="H69" s="8" t="n">
-        <v>-0.0036</v>
+        <v>-0.0038</v>
       </c>
       <c r="I69" s="8" t="n">
-        <v>-0.006886285227016176</v>
+        <v>-0.007024902242636077</v>
       </c>
       <c r="J69" s="10" t="n">
         <v>0.5</v>
@@ -5392,33 +5446,33 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>BUF @ HOU</t>
+          <t>SF @ LAR</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>BUF ML</t>
+          <t>SF +3.5</t>
         </is>
       </c>
       <c r="E70" s="12" t="n">
-        <v>-118</v>
+        <v>-108</v>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.5374</v>
+        <v>0.5153</v>
       </c>
       <c r="G70" s="13" t="n">
-        <v>0.5413</v>
+        <v>0.5192</v>
       </c>
       <c r="H70" s="13" t="n">
-        <v>-0.0038</v>
+        <v>-0.0039</v>
       </c>
       <c r="I70" s="13" t="n">
-        <v>-0.007024902242636077</v>
+        <v>-0.00757828565733093</v>
       </c>
       <c r="J70" s="15" t="n">
         <v>0.5</v>
@@ -5450,16 +5504,16 @@
         <v>124</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>0.4421</v>
+        <v>0.442</v>
       </c>
       <c r="G71" s="8" t="n">
         <v>0.4464</v>
       </c>
       <c r="H71" s="8" t="n">
-        <v>-0.0043</v>
+        <v>-0.0045</v>
       </c>
       <c r="I71" s="8" t="n">
-        <v>-0.009524547947419304</v>
+        <v>-0.009927378901474437</v>
       </c>
       <c r="J71" s="10" t="n">
         <v>0.5</v>
@@ -5491,16 +5545,16 @@
         <v>200</v>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.3287</v>
+        <v>0.3286</v>
       </c>
       <c r="G72" s="13" t="n">
         <v>0.3333</v>
       </c>
       <c r="H72" s="13" t="n">
-        <v>-0.0046</v>
+        <v>-0.0047</v>
       </c>
       <c r="I72" s="13" t="n">
-        <v>-0.01364986484133868</v>
+        <v>-0.01414912923927325</v>
       </c>
       <c r="J72" s="15" t="n">
         <v>0.5</v>
@@ -5614,16 +5668,16 @@
         <v>-105</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>0.5058</v>
+        <v>0.5059</v>
       </c>
       <c r="G75" s="8" t="n">
         <v>0.5122</v>
       </c>
       <c r="H75" s="8" t="n">
-        <v>-0.0064</v>
+        <v>-0.0062</v>
       </c>
       <c r="I75" s="8" t="n">
-        <v>-0.01257807639092878</v>
+        <v>-0.01222345728980595</v>
       </c>
       <c r="J75" s="10" t="n">
         <v>0.5</v>
@@ -5761,33 +5815,33 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>BUF @ HOU</t>
+          <t>DET @ BUF</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Over 44.5</t>
+          <t>BUF ML</t>
         </is>
       </c>
       <c r="E79" s="7" t="n">
-        <v>-110</v>
+        <v>-155</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>0.5127</v>
+        <v>0.5962</v>
       </c>
       <c r="G79" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.6078</v>
       </c>
       <c r="H79" s="8" t="n">
-        <v>-0.0109</v>
+        <v>-0.0115</v>
       </c>
       <c r="I79" s="8" t="n">
-        <v>-0.02118472397290833</v>
+        <v>-0.01906002789140349</v>
       </c>
       <c r="J79" s="10" t="n">
         <v>0.5</v>
@@ -5802,7 +5856,7 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>DET @ BUF</t>
+          <t>WSH @ DAL</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
@@ -5812,23 +5866,23 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>BUF ML</t>
+          <t>DAL ML</t>
         </is>
       </c>
       <c r="E80" s="12" t="n">
-        <v>-155</v>
+        <v>-205</v>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.5962</v>
+        <v>0.6602</v>
       </c>
       <c r="G80" s="13" t="n">
-        <v>0.6078</v>
+        <v>0.6721</v>
       </c>
       <c r="H80" s="13" t="n">
-        <v>-0.0115</v>
+        <v>-0.0117</v>
       </c>
       <c r="I80" s="13" t="n">
-        <v>-0.01906002789140349</v>
+        <v>-0.01757170464578495</v>
       </c>
       <c r="J80" s="15" t="n">
         <v>0.5</v>
@@ -5843,33 +5897,33 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>WSH @ DAL</t>
+          <t>CAR @ ATL</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>DAL ML</t>
+          <t>ATL -1.5</t>
         </is>
       </c>
       <c r="E81" s="7" t="n">
-        <v>-205</v>
+        <v>-110</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>0.6601</v>
+        <v>0.5114</v>
       </c>
       <c r="G81" s="8" t="n">
-        <v>0.6721</v>
+        <v>0.5238</v>
       </c>
       <c r="H81" s="8" t="n">
-        <v>-0.0119</v>
+        <v>-0.0122</v>
       </c>
       <c r="I81" s="8" t="n">
-        <v>-0.01781868529128067</v>
+        <v>-0.02369008041236687</v>
       </c>
       <c r="J81" s="10" t="n">
         <v>0.5</v>
@@ -5884,7 +5938,7 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>CAR @ ATL</t>
+          <t>DET @ BUF</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
@@ -5894,23 +5948,23 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>ATL -1.5</t>
+          <t>BUF -3</t>
         </is>
       </c>
       <c r="E82" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.5114</v>
+        <v>0.5105</v>
       </c>
       <c r="G82" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H82" s="13" t="n">
-        <v>-0.0122</v>
+        <v>-0.0131</v>
       </c>
       <c r="I82" s="13" t="n">
-        <v>-0.02369008041236687</v>
+        <v>-0.02366289073816819</v>
       </c>
       <c r="J82" s="15" t="n">
         <v>0.5</v>
@@ -5925,7 +5979,7 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>DET @ BUF</t>
+          <t>DAL @ NYG</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -5935,23 +5989,23 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>BUF -3</t>
+          <t>NYG +2.5</t>
         </is>
       </c>
       <c r="E83" s="7" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>0.5105</v>
+        <v>0.4974</v>
       </c>
       <c r="G83" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5122</v>
       </c>
       <c r="H83" s="8" t="n">
-        <v>-0.0131</v>
+        <v>-0.0144</v>
       </c>
       <c r="I83" s="8" t="n">
-        <v>-0.02366289073816819</v>
+        <v>-0.02879040426669344</v>
       </c>
       <c r="J83" s="10" t="n">
         <v>0.5</v>
@@ -5966,33 +6020,33 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>DAL @ NYG</t>
+          <t>ATL @ PIT</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>NYG +2.5</t>
+          <t>ATL ML</t>
         </is>
       </c>
       <c r="E84" s="12" t="n">
-        <v>-105</v>
+        <v>145</v>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.4976</v>
+        <v>0.3922</v>
       </c>
       <c r="G84" s="13" t="n">
-        <v>0.5122</v>
+        <v>0.4082</v>
       </c>
       <c r="H84" s="13" t="n">
-        <v>-0.0142</v>
+        <v>-0.0155</v>
       </c>
       <c r="I84" s="13" t="n">
-        <v>-0.02843835042789322</v>
+        <v>-0.03881419460589064</v>
       </c>
       <c r="J84" s="15" t="n">
         <v>0.5</v>
@@ -6007,33 +6061,33 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>ATL @ PIT</t>
+          <t>BUF @ HOU</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>ATL ML</t>
+          <t>Over 44.5</t>
         </is>
       </c>
       <c r="E85" s="7" t="n">
-        <v>145</v>
+        <v>-110</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>0.3924</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="G85" s="8" t="n">
-        <v>0.4082</v>
+        <v>0.5238</v>
       </c>
       <c r="H85" s="8" t="n">
-        <v>-0.0154</v>
+        <v>-0.0157</v>
       </c>
       <c r="I85" s="8" t="n">
-        <v>-0.03838502881250883</v>
+        <v>-0.03088766692791661</v>
       </c>
       <c r="J85" s="10" t="n">
         <v>0.5</v>
@@ -6106,16 +6160,16 @@
         <v>-205</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>0.6553</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="G87" s="8" t="n">
         <v>0.6721</v>
       </c>
       <c r="H87" s="8" t="n">
-        <v>-0.0163</v>
+        <v>-0.016</v>
       </c>
       <c r="I87" s="8" t="n">
-        <v>-0.02476211020273922</v>
+        <v>-0.02426438295817168</v>
       </c>
       <c r="J87" s="10" t="n">
         <v>0.5</v>
@@ -6188,16 +6242,16 @@
         <v>-110</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>0.5062</v>
+        <v>0.5061</v>
       </c>
       <c r="G89" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H89" s="8" t="n">
-        <v>-0.017</v>
+        <v>-0.0172</v>
       </c>
       <c r="I89" s="8" t="n">
-        <v>-0.03353074385385046</v>
+        <v>-0.0338779412367774</v>
       </c>
       <c r="J89" s="10" t="n">
         <v>0.5</v>
@@ -6352,16 +6406,16 @@
         <v>-110</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>0.5044999999999999</v>
+        <v>0.5048</v>
       </c>
       <c r="G93" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H93" s="8" t="n">
-        <v>-0.0186</v>
+        <v>-0.0183</v>
       </c>
       <c r="I93" s="8" t="n">
-        <v>-0.03694058913192133</v>
+        <v>-0.03624731383348789</v>
       </c>
       <c r="J93" s="10" t="n">
         <v>0.5</v>
@@ -6417,33 +6471,33 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>ATL @ PIT</t>
+          <t>JAX @ DEN</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>ATL +3</t>
+          <t>JAX ML</t>
         </is>
       </c>
       <c r="E95" s="7" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="F95" s="8" t="n">
-        <v>0.4794</v>
+        <v>0.4339</v>
       </c>
       <c r="G95" s="8" t="n">
-        <v>0.5</v>
+        <v>0.4545</v>
       </c>
       <c r="H95" s="8" t="n">
         <v>-0.0197</v>
       </c>
       <c r="I95" s="8" t="n">
-        <v>-0.03818131037285988</v>
+        <v>-0.04497708260678568</v>
       </c>
       <c r="J95" s="10" t="n">
         <v>0.5</v>
@@ -6458,33 +6512,33 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>JAX @ DEN</t>
+          <t>ATL @ PIT</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>JAX ML</t>
+          <t>ATL +3</t>
         </is>
       </c>
       <c r="E96" s="12" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F96" s="13" t="n">
-        <v>0.4339</v>
+        <v>0.4792</v>
       </c>
       <c r="G96" s="13" t="n">
-        <v>0.4545</v>
+        <v>0.5</v>
       </c>
       <c r="H96" s="13" t="n">
-        <v>-0.0197</v>
+        <v>-0.0198</v>
       </c>
       <c r="I96" s="13" t="n">
-        <v>-0.04497708260678568</v>
+        <v>-0.03854042707833383</v>
       </c>
       <c r="J96" s="15" t="n">
         <v>0.5</v>
@@ -6926,16 +6980,16 @@
         <v>-120</v>
       </c>
       <c r="F107" s="8" t="n">
-        <v>0.5206</v>
+        <v>0.5208</v>
       </c>
       <c r="G107" s="8" t="n">
         <v>0.5455</v>
       </c>
       <c r="H107" s="8" t="n">
-        <v>-0.0233</v>
+        <v>-0.0232</v>
       </c>
       <c r="I107" s="8" t="n">
-        <v>-0.04232167579267038</v>
+        <v>-0.04199259833787239</v>
       </c>
       <c r="J107" s="10" t="n">
         <v>0.5</v>
@@ -7032,33 +7086,33 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>WSH @ PHI</t>
+          <t>JAX @ DEN</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>WSH ML</t>
+          <t>JAX +2.5</t>
         </is>
       </c>
       <c r="E110" s="12" t="n">
-        <v>170</v>
+        <v>-105</v>
       </c>
       <c r="F110" s="13" t="n">
-        <v>0.3447</v>
+        <v>0.4864</v>
       </c>
       <c r="G110" s="13" t="n">
-        <v>0.3704</v>
+        <v>0.5122</v>
       </c>
       <c r="H110" s="13" t="n">
         <v>-0.024</v>
       </c>
       <c r="I110" s="13" t="n">
-        <v>-0.06887082213294937</v>
+        <v>-0.05026802719465456</v>
       </c>
       <c r="J110" s="15" t="n">
         <v>0.5</v>
@@ -7073,33 +7127,33 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>JAX @ DEN</t>
+          <t>WSH @ PHI</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>JAX +2.5</t>
+          <t>WSH ML</t>
         </is>
       </c>
       <c r="E111" s="7" t="n">
-        <v>-105</v>
+        <v>170</v>
       </c>
       <c r="F111" s="8" t="n">
-        <v>0.4864</v>
+        <v>0.3443</v>
       </c>
       <c r="G111" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.3704</v>
       </c>
       <c r="H111" s="8" t="n">
-        <v>-0.024</v>
+        <v>-0.0243</v>
       </c>
       <c r="I111" s="8" t="n">
-        <v>-0.05026802719465456</v>
+        <v>-0.06977463081454904</v>
       </c>
       <c r="J111" s="10" t="n">
         <v>0.5</v>
@@ -7196,33 +7250,33 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>WSH @ PHI</t>
+          <t>ATL @ PIT</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>WSH +4.5</t>
+          <t>PIT ML</t>
         </is>
       </c>
       <c r="E114" s="12" t="n">
-        <v>-110</v>
+        <v>-175</v>
       </c>
       <c r="F114" s="13" t="n">
-        <v>0.4955</v>
+        <v>0.6078</v>
       </c>
       <c r="G114" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.6364</v>
       </c>
       <c r="H114" s="13" t="n">
-        <v>-0.026</v>
+        <v>-0.0262</v>
       </c>
       <c r="I114" s="13" t="n">
-        <v>-0.0539685017771695</v>
+        <v>-0.04446946701398502</v>
       </c>
       <c r="J114" s="15" t="n">
         <v>0.5</v>
@@ -7237,33 +7291,33 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>ATL @ PIT</t>
+          <t>WSH @ PHI</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>PIT ML</t>
+          <t>WSH +4.5</t>
         </is>
       </c>
       <c r="E115" s="7" t="n">
-        <v>-175</v>
+        <v>-110</v>
       </c>
       <c r="F115" s="8" t="n">
-        <v>0.6076</v>
+        <v>0.4952</v>
       </c>
       <c r="G115" s="8" t="n">
-        <v>0.6364</v>
+        <v>0.5238</v>
       </c>
       <c r="H115" s="8" t="n">
-        <v>-0.0264</v>
+        <v>-0.0263</v>
       </c>
       <c r="I115" s="8" t="n">
-        <v>-0.04474461798234386</v>
+        <v>-0.05466177707560294</v>
       </c>
       <c r="J115" s="10" t="n">
         <v>0.5</v>
@@ -7442,7 +7496,7 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>TB @ CIN</t>
+          <t>CLE @ TB</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
@@ -7452,23 +7506,23 @@
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>CIN -3.5</t>
+          <t>TB -5.5</t>
         </is>
       </c>
       <c r="E120" s="12" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="F120" s="13" t="n">
-        <v>0.5048</v>
+        <v>0.4939</v>
       </c>
       <c r="G120" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.5238</v>
       </c>
       <c r="H120" s="13" t="n">
-        <v>-0.0274</v>
+        <v>-0.0272</v>
       </c>
       <c r="I120" s="13" t="n">
-        <v>-0.05622011654448439</v>
+        <v>-0.05703114967231343</v>
       </c>
       <c r="J120" s="15" t="n">
         <v>0.5</v>
@@ -7483,7 +7537,7 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>CLE @ TB</t>
+          <t>TB @ CIN</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
@@ -7493,23 +7547,23 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>TB -5.5</t>
+          <t>CIN -3.5</t>
         </is>
       </c>
       <c r="E121" s="7" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="F121" s="8" t="n">
-        <v>0.4938</v>
+        <v>0.5048</v>
       </c>
       <c r="G121" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5349</v>
       </c>
       <c r="H121" s="8" t="n">
         <v>-0.0274</v>
       </c>
       <c r="I121" s="8" t="n">
-        <v>-0.05737834705524036</v>
+        <v>-0.05622011654448439</v>
       </c>
       <c r="J121" s="10" t="n">
         <v>0.5</v>
@@ -7541,16 +7595,16 @@
         <v>170</v>
       </c>
       <c r="F122" s="13" t="n">
-        <v>0.3399</v>
+        <v>0.3398</v>
       </c>
       <c r="G122" s="13" t="n">
         <v>0.3704</v>
       </c>
       <c r="H122" s="13" t="n">
-        <v>-0.0277</v>
+        <v>-0.0278</v>
       </c>
       <c r="I122" s="13" t="n">
-        <v>-0.08147936056166394</v>
+        <v>-0.08192785858412999</v>
       </c>
       <c r="J122" s="15" t="n">
         <v>0.5</v>
@@ -7606,7 +7660,7 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>PIT @ NE</t>
+          <t>BUF @ HOU</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
@@ -7616,7 +7670,7 @@
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>Over 43.5</t>
+          <t>Under 44.5</t>
         </is>
       </c>
       <c r="E124" s="12" t="n">
@@ -7632,7 +7686,7 @@
         <v>-0.0284</v>
       </c>
       <c r="I124" s="13" t="n">
-        <v>-0.06001309614417871</v>
+        <v>-0.06002142398117422</v>
       </c>
       <c r="J124" s="15" t="n">
         <v>0.5</v>
@@ -7647,33 +7701,33 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>DAL @ NYG</t>
+          <t>PIT @ NE</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>DAL -2.5</t>
+          <t>Over 43.5</t>
         </is>
       </c>
       <c r="E125" s="7" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="F125" s="8" t="n">
-        <v>0.5024</v>
+        <v>0.4924</v>
       </c>
       <c r="G125" s="8" t="n">
-        <v>0.5349</v>
+        <v>0.5238</v>
       </c>
       <c r="H125" s="8" t="n">
-        <v>-0.0292</v>
+        <v>-0.0284</v>
       </c>
       <c r="I125" s="8" t="n">
-        <v>-0.06078490939937703</v>
+        <v>-0.06001309614417871</v>
       </c>
       <c r="J125" s="10" t="n">
         <v>0.5</v>
@@ -7688,7 +7742,7 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>DET @ BUF</t>
+          <t>DAL @ NYG</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
@@ -7698,23 +7752,23 @@
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>DET +3</t>
+          <t>DAL -2.5</t>
         </is>
       </c>
       <c r="E126" s="12" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="F126" s="13" t="n">
-        <v>0.4895</v>
+        <v>0.5026</v>
       </c>
       <c r="G126" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5349</v>
       </c>
       <c r="H126" s="13" t="n">
-        <v>-0.0304</v>
+        <v>-0.0291</v>
       </c>
       <c r="I126" s="13" t="n">
-        <v>-0.06068621837874821</v>
+        <v>-0.06044778891535091</v>
       </c>
       <c r="J126" s="15" t="n">
         <v>0.5</v>
@@ -7729,33 +7783,33 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>TB @ CIN</t>
+          <t>DET @ BUF</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>CIN ML</t>
+          <t>DET +3</t>
         </is>
       </c>
       <c r="E127" s="7" t="n">
-        <v>-198</v>
+        <v>-110</v>
       </c>
       <c r="F127" s="8" t="n">
-        <v>0.6294</v>
+        <v>0.4895</v>
       </c>
       <c r="G127" s="8" t="n">
-        <v>0.6644</v>
+        <v>0.5238</v>
       </c>
       <c r="H127" s="8" t="n">
-        <v>-0.0309</v>
+        <v>-0.0304</v>
       </c>
       <c r="I127" s="8" t="n">
-        <v>-0.0522151050002545</v>
+        <v>-0.06068621837874821</v>
       </c>
       <c r="J127" s="10" t="n">
         <v>0.5</v>
@@ -7770,33 +7824,33 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>CAR @ ATL</t>
+          <t>TB @ CIN</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>CAR +1.5</t>
+          <t>CIN ML</t>
         </is>
       </c>
       <c r="E128" s="12" t="n">
-        <v>-110</v>
+        <v>-198</v>
       </c>
       <c r="F128" s="13" t="n">
-        <v>0.4886</v>
+        <v>0.6294</v>
       </c>
       <c r="G128" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.6644</v>
       </c>
       <c r="H128" s="13" t="n">
-        <v>-0.0311</v>
+        <v>-0.0309</v>
       </c>
       <c r="I128" s="13" t="n">
-        <v>-0.06721901049672396</v>
+        <v>-0.0522151050002545</v>
       </c>
       <c r="J128" s="15" t="n">
         <v>0.5</v>
@@ -7816,28 +7870,28 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>CAR ML</t>
+          <t>CAR +1.5</t>
         </is>
       </c>
       <c r="E129" s="7" t="n">
-        <v>102</v>
+        <v>-110</v>
       </c>
       <c r="F129" s="8" t="n">
-        <v>0.4588</v>
+        <v>0.4886</v>
       </c>
       <c r="G129" s="8" t="n">
-        <v>0.495</v>
+        <v>0.5238</v>
       </c>
       <c r="H129" s="8" t="n">
-        <v>-0.0318</v>
+        <v>-0.0311</v>
       </c>
       <c r="I129" s="8" t="n">
-        <v>-0.07262458964321516</v>
+        <v>-0.06721901049672396</v>
       </c>
       <c r="J129" s="10" t="n">
         <v>0.5</v>
@@ -7852,33 +7906,33 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>BUF @ HOU</t>
+          <t>CAR @ ATL</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>Under 44.5</t>
+          <t>CAR ML</t>
         </is>
       </c>
       <c r="E130" s="12" t="n">
-        <v>-110</v>
+        <v>102</v>
       </c>
       <c r="F130" s="13" t="n">
-        <v>0.4873</v>
+        <v>0.4588</v>
       </c>
       <c r="G130" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.495</v>
       </c>
       <c r="H130" s="13" t="n">
-        <v>-0.032</v>
+        <v>-0.0318</v>
       </c>
       <c r="I130" s="13" t="n">
-        <v>-0.0697243669361825</v>
+        <v>-0.07262458964321516</v>
       </c>
       <c r="J130" s="15" t="n">
         <v>0.5</v>
@@ -7910,16 +7964,16 @@
         <v>-148</v>
       </c>
       <c r="F131" s="8" t="n">
-        <v>0.5579</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="G131" s="8" t="n">
         <v>0.5968</v>
       </c>
       <c r="H131" s="8" t="n">
-        <v>-0.0335</v>
+        <v>-0.0334</v>
       </c>
       <c r="I131" s="8" t="n">
-        <v>-0.06462351467344279</v>
+        <v>-0.06432222647230235</v>
       </c>
       <c r="J131" s="10" t="n">
         <v>0.5</v>
@@ -7951,16 +8005,16 @@
         <v>-245</v>
       </c>
       <c r="F132" s="13" t="n">
-        <v>0.6713</v>
+        <v>0.6714</v>
       </c>
       <c r="G132" s="13" t="n">
         <v>0.7101</v>
       </c>
       <c r="H132" s="13" t="n">
-        <v>-0.0335</v>
+        <v>-0.0334</v>
       </c>
       <c r="I132" s="13" t="n">
-        <v>-0.05431562614774066</v>
+        <v>-0.05408143001598997</v>
       </c>
       <c r="J132" s="15" t="n">
         <v>0.5</v>
@@ -8074,16 +8128,16 @@
         <v>-115</v>
       </c>
       <c r="F135" s="8" t="n">
-        <v>0.4942</v>
+        <v>0.4941</v>
       </c>
       <c r="G135" s="8" t="n">
         <v>0.5349</v>
       </c>
       <c r="H135" s="8" t="n">
-        <v>-0.0346</v>
+        <v>-0.0347</v>
       </c>
       <c r="I135" s="8" t="n">
-        <v>-0.0759724252587396</v>
+        <v>-0.07631200219226442</v>
       </c>
       <c r="J135" s="10" t="n">
         <v>0.5</v>
@@ -8238,16 +8292,16 @@
         <v>110</v>
       </c>
       <c r="F139" s="8" t="n">
-        <v>0.4333</v>
+        <v>0.4334</v>
       </c>
       <c r="G139" s="8" t="n">
         <v>0.4762</v>
       </c>
       <c r="H139" s="8" t="n">
-        <v>-0.0359</v>
+        <v>-0.0358</v>
       </c>
       <c r="I139" s="8" t="n">
-        <v>-0.08935010122584919</v>
+        <v>-0.08897651782496302</v>
       </c>
       <c r="J139" s="10" t="n">
         <v>0.5</v>
@@ -8279,16 +8333,16 @@
         <v>-112</v>
       </c>
       <c r="F140" s="13" t="n">
-        <v>0.4843</v>
+        <v>0.4847</v>
       </c>
       <c r="G140" s="13" t="n">
         <v>0.5283</v>
       </c>
       <c r="H140" s="13" t="n">
-        <v>-0.0365</v>
+        <v>-0.0363</v>
       </c>
       <c r="I140" s="13" t="n">
-        <v>-0.08320448203306302</v>
+        <v>-0.0825243634782688</v>
       </c>
       <c r="J140" s="15" t="n">
         <v>0.5</v>
@@ -8525,16 +8579,16 @@
         <v>-105</v>
       </c>
       <c r="F146" s="13" t="n">
-        <v>0.4652</v>
+        <v>0.4653</v>
       </c>
       <c r="G146" s="13" t="n">
         <v>0.5122</v>
       </c>
       <c r="H146" s="13" t="n">
-        <v>-0.0382</v>
+        <v>-0.0381</v>
       </c>
       <c r="I146" s="13" t="n">
-        <v>-0.0918405676799029</v>
+        <v>-0.09148959310265437</v>
       </c>
       <c r="J146" s="15" t="n">
         <v>0.5</v>
@@ -8976,16 +9030,16 @@
         <v>-198</v>
       </c>
       <c r="F157" s="8" t="n">
-        <v>0.6117</v>
+        <v>0.612</v>
       </c>
       <c r="G157" s="8" t="n">
         <v>0.6644</v>
       </c>
       <c r="H157" s="8" t="n">
-        <v>-0.0409</v>
+        <v>-0.0408</v>
       </c>
       <c r="I157" s="8" t="n">
-        <v>-0.0787361723695737</v>
+        <v>-0.07820640387615446</v>
       </c>
       <c r="J157" s="10" t="n">
         <v>0.5</v>
@@ -9082,7 +9136,7 @@
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>MIA @ LV</t>
+          <t>CLE @ JAX</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
@@ -9123,7 +9177,7 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>CAR @ ATL</t>
+          <t>MIA @ LV</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
@@ -9133,23 +9187,23 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>Over 43.5</t>
+          <t>Under 40.5</t>
         </is>
       </c>
       <c r="E161" s="7" t="n">
-        <v>-118</v>
+        <v>-110</v>
       </c>
       <c r="F161" s="8" t="n">
-        <v>0.4858</v>
+        <v>0.4695</v>
       </c>
       <c r="G161" s="8" t="n">
-        <v>0.5413</v>
+        <v>0.5238</v>
       </c>
       <c r="H161" s="8" t="n">
-        <v>-0.0421</v>
+        <v>-0.0416</v>
       </c>
       <c r="I161" s="8" t="n">
-        <v>-0.1025875430405576</v>
+        <v>-0.1035968023040441</v>
       </c>
       <c r="J161" s="10" t="n">
         <v>0.5</v>
@@ -9164,7 +9218,7 @@
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>NE @ SEA</t>
+          <t>CAR @ ATL</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
@@ -9174,23 +9228,23 @@
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>Over 44.5</t>
+          <t>Over 43.5</t>
         </is>
       </c>
       <c r="E162" s="12" t="n">
-        <v>-105</v>
+        <v>-118</v>
       </c>
       <c r="F162" s="13" t="n">
-        <v>0.4557</v>
+        <v>0.4858</v>
       </c>
       <c r="G162" s="13" t="n">
-        <v>0.5122</v>
+        <v>0.5413</v>
       </c>
       <c r="H162" s="13" t="n">
-        <v>-0.0425</v>
+        <v>-0.0421</v>
       </c>
       <c r="I162" s="13" t="n">
-        <v>-0.1103300727700344</v>
+        <v>-0.1025875430405576</v>
       </c>
       <c r="J162" s="15" t="n">
         <v>0.5</v>
@@ -9205,7 +9259,7 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>ATL @ GB</t>
+          <t>NE @ SEA</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
@@ -9215,23 +9269,23 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>Over 46.5</t>
+          <t>Over 44.5</t>
         </is>
       </c>
       <c r="E163" s="7" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="F163" s="8" t="n">
-        <v>0.467</v>
+        <v>0.4557</v>
       </c>
       <c r="G163" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5122</v>
       </c>
       <c r="H163" s="8" t="n">
-        <v>-0.0426</v>
+        <v>-0.0425</v>
       </c>
       <c r="I163" s="8" t="n">
-        <v>-0.1084019190168437</v>
+        <v>-0.1103300727700344</v>
       </c>
       <c r="J163" s="10" t="n">
         <v>0.5</v>
@@ -9246,33 +9300,33 @@
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>PHI @ TEN</t>
+          <t>ATL @ GB</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>PHI -4.5</t>
+          <t>Over 46.5</t>
         </is>
       </c>
       <c r="E164" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F164" s="13" t="n">
-        <v>0.4669</v>
+        <v>0.467</v>
       </c>
       <c r="G164" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H164" s="13" t="n">
-        <v>-0.0427</v>
+        <v>-0.0426</v>
       </c>
       <c r="I164" s="13" t="n">
-        <v>-0.1086623740801022</v>
+        <v>-0.1084019190168437</v>
       </c>
       <c r="J164" s="15" t="n">
         <v>0.5</v>
@@ -9287,7 +9341,7 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>NE @ SEA</t>
+          <t>PHI @ TEN</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
@@ -9297,23 +9351,23 @@
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>SEA -3.5</t>
+          <t>PHI -4.5</t>
         </is>
       </c>
       <c r="E165" s="7" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="F165" s="8" t="n">
-        <v>0.4544</v>
+        <v>0.4669</v>
       </c>
       <c r="G165" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.5238</v>
       </c>
       <c r="H165" s="8" t="n">
-        <v>-0.043</v>
+        <v>-0.0427</v>
       </c>
       <c r="I165" s="8" t="n">
-        <v>-0.1128490923575317</v>
+        <v>-0.1086623740801022</v>
       </c>
       <c r="J165" s="10" t="n">
         <v>0.5</v>
@@ -9328,42 +9382,38 @@
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>NYG @ LAR</t>
+          <t>NE @ SEA</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>LAR ML</t>
+          <t>SEA -3.5</t>
         </is>
       </c>
       <c r="E166" s="12" t="n">
-        <v>-380</v>
+        <v>-105</v>
       </c>
       <c r="F166" s="13" t="n">
-        <v>0.7328</v>
+        <v>0.4544</v>
       </c>
       <c r="G166" s="13" t="n">
-        <v>0.7917</v>
+        <v>0.5122</v>
       </c>
       <c r="H166" s="13" t="n">
-        <v>-0.0434</v>
+        <v>-0.043</v>
       </c>
       <c r="I166" s="13" t="n">
-        <v>-0.07374216851612969</v>
+        <v>-0.1128490923575317</v>
       </c>
       <c r="J166" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="K166" s="5" t="inlineStr">
-        <is>
-          <t>price -380 outside the allowed range</t>
-        </is>
-      </c>
+      <c r="K166" s="5" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
@@ -9373,7 +9423,7 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>MIN @ CHI</t>
+          <t>NYG @ LAR</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
@@ -9383,28 +9433,32 @@
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>CHI ML</t>
+          <t>LAR ML</t>
         </is>
       </c>
       <c r="E167" s="7" t="n">
-        <v>-198</v>
+        <v>-380</v>
       </c>
       <c r="F167" s="8" t="n">
-        <v>0.6038</v>
+        <v>0.7332</v>
       </c>
       <c r="G167" s="8" t="n">
-        <v>0.6644</v>
+        <v>0.7917</v>
       </c>
       <c r="H167" s="8" t="n">
-        <v>-0.0441</v>
+        <v>-0.0433</v>
       </c>
       <c r="I167" s="8" t="n">
-        <v>-0.090432584438073</v>
+        <v>-0.07335026602967182</v>
       </c>
       <c r="J167" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="K167" s="4" t="inlineStr"/>
+      <c r="K167" s="4" t="inlineStr">
+        <is>
+          <t>price -380 outside the allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
@@ -9414,7 +9468,7 @@
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>MIA @ LV</t>
+          <t>MIN @ CHI</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
@@ -9424,23 +9478,23 @@
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>LV ML</t>
+          <t>CHI ML</t>
         </is>
       </c>
       <c r="E168" s="12" t="n">
         <v>-198</v>
       </c>
       <c r="F168" s="13" t="n">
-        <v>0.6029</v>
+        <v>0.6038</v>
       </c>
       <c r="G168" s="13" t="n">
         <v>0.6644</v>
       </c>
       <c r="H168" s="13" t="n">
-        <v>-0.0444</v>
+        <v>-0.0441</v>
       </c>
       <c r="I168" s="13" t="n">
-        <v>-0.09176650825332933</v>
+        <v>-0.090432584438073</v>
       </c>
       <c r="J168" s="15" t="n">
         <v>0.5</v>
@@ -9455,33 +9509,33 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>CLE @ JAX</t>
+          <t>MIA @ LV</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>Under 40.5</t>
+          <t>LV ML</t>
         </is>
       </c>
       <c r="E169" s="7" t="n">
-        <v>-110</v>
+        <v>-198</v>
       </c>
       <c r="F169" s="8" t="n">
-        <v>0.462</v>
+        <v>0.6029</v>
       </c>
       <c r="G169" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.6644</v>
       </c>
       <c r="H169" s="8" t="n">
-        <v>-0.0445</v>
+        <v>-0.0444</v>
       </c>
       <c r="I169" s="8" t="n">
-        <v>-0.1180341212058959</v>
+        <v>-0.09176650825332933</v>
       </c>
       <c r="J169" s="10" t="n">
         <v>0.5</v>
@@ -9619,38 +9673,42 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>SF @ LAR</t>
+          <t>LV @ LAC</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>LAC ML</t>
         </is>
       </c>
       <c r="E173" s="7" t="n">
-        <v>-110</v>
+        <v>-375</v>
       </c>
       <c r="F173" s="8" t="n">
-        <v>0.4595</v>
+        <v>0.7246</v>
       </c>
       <c r="G173" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.7895</v>
       </c>
       <c r="H173" s="8" t="n">
-        <v>-0.0453</v>
+        <v>-0.0455</v>
       </c>
       <c r="I173" s="8" t="n">
-        <v>-0.1228221690339132</v>
+        <v>-0.08154755880401182</v>
       </c>
       <c r="J173" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="K173" s="4" t="inlineStr"/>
+      <c r="K173" s="4" t="inlineStr">
+        <is>
+          <t>price -375 outside the allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
@@ -9660,42 +9718,38 @@
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>LV @ LAC</t>
+          <t>IND @ KC</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>LAC ML</t>
+          <t>KC -6.5</t>
         </is>
       </c>
       <c r="E174" s="12" t="n">
-        <v>-375</v>
+        <v>-110</v>
       </c>
       <c r="F174" s="13" t="n">
-        <v>0.7246</v>
+        <v>0.4589</v>
       </c>
       <c r="G174" s="13" t="n">
-        <v>0.7895</v>
+        <v>0.5238</v>
       </c>
       <c r="H174" s="13" t="n">
         <v>-0.0455</v>
       </c>
       <c r="I174" s="13" t="n">
-        <v>-0.08154755880401182</v>
+        <v>-0.1239391092626436</v>
       </c>
       <c r="J174" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="K174" s="5" t="inlineStr">
-        <is>
-          <t>price -375 outside the allowed range</t>
-        </is>
-      </c>
+      <c r="K174" s="5" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
@@ -9705,7 +9759,7 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>IND @ KC</t>
+          <t>CLE @ JAX</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
@@ -9715,23 +9769,23 @@
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>KC -6.5</t>
+          <t>JAX -7.5</t>
         </is>
       </c>
       <c r="E175" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F175" s="8" t="n">
-        <v>0.4589</v>
+        <v>0.4578</v>
       </c>
       <c r="G175" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H175" s="8" t="n">
-        <v>-0.0455</v>
+        <v>-0.0459</v>
       </c>
       <c r="I175" s="8" t="n">
-        <v>-0.1239391092626436</v>
+        <v>-0.1260390118519604</v>
       </c>
       <c r="J175" s="10" t="n">
         <v>0.5</v>
@@ -9746,33 +9800,33 @@
       </c>
       <c r="B176" s="5" t="inlineStr">
         <is>
-          <t>CLE @ JAX</t>
+          <t>TB @ CIN</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
-          <t>JAX -7.5</t>
+          <t>Over 51.5</t>
         </is>
       </c>
       <c r="E176" s="12" t="n">
-        <v>-110</v>
+        <v>-102</v>
       </c>
       <c r="F176" s="13" t="n">
-        <v>0.458</v>
+        <v>0.4359</v>
       </c>
       <c r="G176" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.505</v>
       </c>
       <c r="H176" s="13" t="n">
-        <v>-0.0458</v>
+        <v>-0.0467</v>
       </c>
       <c r="I176" s="13" t="n">
-        <v>-0.1256919317062585</v>
+        <v>-0.1367090604010699</v>
       </c>
       <c r="J176" s="15" t="n">
         <v>0.5</v>
@@ -9787,33 +9841,33 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>TB @ CIN</t>
+          <t>NYG @ LAR</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>Over 51.5</t>
+          <t>LAR -8.5</t>
         </is>
       </c>
       <c r="E177" s="7" t="n">
-        <v>-102</v>
+        <v>-110</v>
       </c>
       <c r="F177" s="8" t="n">
-        <v>0.4359</v>
+        <v>0.4546</v>
       </c>
       <c r="G177" s="8" t="n">
-        <v>0.505</v>
+        <v>0.5238</v>
       </c>
       <c r="H177" s="8" t="n">
-        <v>-0.0467</v>
+        <v>-0.0468</v>
       </c>
       <c r="I177" s="8" t="n">
-        <v>-0.1367090604010699</v>
+        <v>-0.1320545974254394</v>
       </c>
       <c r="J177" s="10" t="n">
         <v>0.5</v>
@@ -9828,38 +9882,42 @@
       </c>
       <c r="B178" s="5" t="inlineStr">
         <is>
-          <t>NYG @ LAR</t>
+          <t>ARI @ LAC</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>LAR -8.5</t>
+          <t>LAC ML</t>
         </is>
       </c>
       <c r="E178" s="12" t="n">
-        <v>-110</v>
+        <v>-575</v>
       </c>
       <c r="F178" s="13" t="n">
-        <v>0.4543</v>
+        <v>0.7819</v>
       </c>
       <c r="G178" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.8519</v>
       </c>
       <c r="H178" s="13" t="n">
-        <v>-0.0469</v>
+        <v>-0.047</v>
       </c>
       <c r="I178" s="13" t="n">
-        <v>-0.132753183737966</v>
+        <v>-0.0815270974192778</v>
       </c>
       <c r="J178" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="K178" s="5" t="inlineStr"/>
+      <c r="K178" s="5" t="inlineStr">
+        <is>
+          <t>price -575 outside the allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
@@ -9869,7 +9927,7 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>ARI @ LAC</t>
+          <t>CLE @ JAX</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
@@ -9879,30 +9937,30 @@
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>LAC ML</t>
+          <t>JAX ML</t>
         </is>
       </c>
       <c r="E179" s="7" t="n">
-        <v>-575</v>
+        <v>-380</v>
       </c>
       <c r="F179" s="8" t="n">
-        <v>0.7819</v>
+        <v>0.7203000000000001</v>
       </c>
       <c r="G179" s="8" t="n">
-        <v>0.8519</v>
+        <v>0.7917</v>
       </c>
       <c r="H179" s="8" t="n">
-        <v>-0.047</v>
+        <v>-0.0474</v>
       </c>
       <c r="I179" s="8" t="n">
-        <v>-0.0815270974192778</v>
+        <v>-0.08945465843273717</v>
       </c>
       <c r="J179" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>price -575 outside the allowed range</t>
+          <t>price -380 outside the allowed range</t>
         </is>
       </c>
     </row>
@@ -9914,42 +9972,38 @@
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>CLE @ JAX</t>
+          <t>DEN @ KC</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>JAX ML</t>
+          <t>Over 42.5</t>
         </is>
       </c>
       <c r="E180" s="12" t="n">
-        <v>-380</v>
+        <v>-110</v>
       </c>
       <c r="F180" s="13" t="n">
-        <v>0.7204</v>
+        <v>0.4495</v>
       </c>
       <c r="G180" s="13" t="n">
-        <v>0.7917</v>
+        <v>0.5238</v>
       </c>
       <c r="H180" s="13" t="n">
-        <v>-0.0473</v>
+        <v>-0.0481</v>
       </c>
       <c r="I180" s="13" t="n">
-        <v>-0.08925300638423508</v>
+        <v>-0.1419279603859848</v>
       </c>
       <c r="J180" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="K180" s="5" t="inlineStr">
-        <is>
-          <t>price -380 outside the allowed range</t>
-        </is>
-      </c>
+      <c r="K180" s="5" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
@@ -10496,7 +10550,7 @@
       </c>
       <c r="B194" s="5" t="inlineStr">
         <is>
-          <t>NYJ @ TEN</t>
+          <t>GB @ MIN</t>
         </is>
       </c>
       <c r="C194" s="5" t="inlineStr">
@@ -10506,23 +10560,23 @@
       </c>
       <c r="D194" s="5" t="inlineStr">
         <is>
-          <t>Under 38.5</t>
+          <t>Over 45.5</t>
         </is>
       </c>
       <c r="E194" s="12" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="F194" s="13" t="n">
-        <v>0.4186</v>
+        <v>0.4297</v>
       </c>
       <c r="G194" s="13" t="n">
-        <v>0.5122</v>
+        <v>0.5238</v>
       </c>
       <c r="H194" s="13" t="n">
         <v>-0.0515</v>
       </c>
       <c r="I194" s="13" t="n">
-        <v>-0.1828182474138708</v>
+        <v>-0.1797102353978136</v>
       </c>
       <c r="J194" s="15" t="n">
         <v>0.5</v>
@@ -10537,7 +10591,7 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>GB @ MIN</t>
+          <t>ARI @ LAC</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
@@ -10547,23 +10601,23 @@
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>Over 45.5</t>
+          <t>Over 46.5</t>
         </is>
       </c>
       <c r="E195" s="7" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="F195" s="8" t="n">
-        <v>0.4297</v>
+        <v>0.4384</v>
       </c>
       <c r="G195" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5349</v>
       </c>
       <c r="H195" s="8" t="n">
-        <v>-0.0515</v>
+        <v>-0.0518</v>
       </c>
       <c r="I195" s="8" t="n">
-        <v>-0.1797102353978136</v>
+        <v>-0.1804243326382279</v>
       </c>
       <c r="J195" s="10" t="n">
         <v>0.5</v>
@@ -10578,7 +10632,7 @@
       </c>
       <c r="B196" s="5" t="inlineStr">
         <is>
-          <t>ARI @ LAC</t>
+          <t>NYJ @ TEN</t>
         </is>
       </c>
       <c r="C196" s="5" t="inlineStr">
@@ -10588,23 +10642,23 @@
       </c>
       <c r="D196" s="5" t="inlineStr">
         <is>
-          <t>Over 46.5</t>
+          <t>Under 38.5</t>
         </is>
       </c>
       <c r="E196" s="12" t="n">
-        <v>-115</v>
+        <v>-105</v>
       </c>
       <c r="F196" s="13" t="n">
-        <v>0.4384</v>
+        <v>0.4137</v>
       </c>
       <c r="G196" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.5122</v>
       </c>
       <c r="H196" s="13" t="n">
-        <v>-0.0518</v>
+        <v>-0.052</v>
       </c>
       <c r="I196" s="13" t="n">
-        <v>-0.1804243326382279</v>
+        <v>-0.1922708059340066</v>
       </c>
       <c r="J196" s="15" t="n">
         <v>0.5</v>
@@ -10619,42 +10673,38 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>MIA @ SF</t>
+          <t>SF @ LAR</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>SF ML</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="E197" s="7" t="n">
-        <v>-650</v>
+        <v>-110</v>
       </c>
       <c r="F197" s="8" t="n">
-        <v>0.7664</v>
+        <v>0.4248</v>
       </c>
       <c r="G197" s="8" t="n">
-        <v>0.8667</v>
+        <v>0.5238</v>
       </c>
       <c r="H197" s="8" t="n">
-        <v>-0.0522</v>
+        <v>-0.0521</v>
       </c>
       <c r="I197" s="8" t="n">
-        <v>-0.1147913763618906</v>
+        <v>-0.1890398877507678</v>
       </c>
       <c r="J197" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="K197" s="4" t="inlineStr">
-        <is>
-          <t>price -650 outside the allowed range</t>
-        </is>
-      </c>
+      <c r="K197" s="4" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="5" t="inlineStr">
@@ -10664,7 +10714,7 @@
       </c>
       <c r="B198" s="5" t="inlineStr">
         <is>
-          <t>SEA @ ARI</t>
+          <t>MIA @ SF</t>
         </is>
       </c>
       <c r="C198" s="5" t="inlineStr">
@@ -10674,30 +10724,30 @@
       </c>
       <c r="D198" s="5" t="inlineStr">
         <is>
-          <t>SEA ML</t>
+          <t>SF ML</t>
         </is>
       </c>
       <c r="E198" s="12" t="n">
-        <v>-550</v>
+        <v>-650</v>
       </c>
       <c r="F198" s="13" t="n">
-        <v>0.7444</v>
+        <v>0.7664</v>
       </c>
       <c r="G198" s="13" t="n">
-        <v>0.8462</v>
+        <v>0.8667</v>
       </c>
       <c r="H198" s="13" t="n">
-        <v>-0.0523</v>
+        <v>-0.0522</v>
       </c>
       <c r="I198" s="13" t="n">
-        <v>-0.1193647652869892</v>
+        <v>-0.1147913763618906</v>
       </c>
       <c r="J198" s="15" t="n">
         <v>0.5</v>
       </c>
       <c r="K198" s="5" t="inlineStr">
         <is>
-          <t>price -550 outside the allowed range</t>
+          <t>price -650 outside the allowed range</t>
         </is>
       </c>
     </row>
@@ -10709,38 +10759,42 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>MIA @ SF</t>
+          <t>SEA @ ARI</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>SF -10.5</t>
+          <t>SEA ML</t>
         </is>
       </c>
       <c r="E199" s="7" t="n">
-        <v>-110</v>
+        <v>-550</v>
       </c>
       <c r="F199" s="8" t="n">
-        <v>0.4216</v>
+        <v>0.7444</v>
       </c>
       <c r="G199" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.8462</v>
       </c>
       <c r="H199" s="8" t="n">
-        <v>-0.0524</v>
+        <v>-0.0523</v>
       </c>
       <c r="I199" s="8" t="n">
-        <v>-0.1951029543058591</v>
+        <v>-0.1193647652869892</v>
       </c>
       <c r="J199" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="K199" s="4" t="inlineStr"/>
+      <c r="K199" s="4" t="inlineStr">
+        <is>
+          <t>price -550 outside the allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="5" t="inlineStr">
@@ -10750,33 +10804,33 @@
       </c>
       <c r="B200" s="5" t="inlineStr">
         <is>
-          <t>NO @ DET</t>
+          <t>MIA @ SF</t>
         </is>
       </c>
       <c r="C200" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D200" s="5" t="inlineStr">
         <is>
-          <t>Over 49.5</t>
+          <t>SF -10.5</t>
         </is>
       </c>
       <c r="E200" s="12" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="F200" s="13" t="n">
-        <v>0.4286</v>
+        <v>0.4216</v>
       </c>
       <c r="G200" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.5238</v>
       </c>
       <c r="H200" s="13" t="n">
-        <v>-0.0527</v>
+        <v>-0.0524</v>
       </c>
       <c r="I200" s="13" t="n">
-        <v>-0.1987411539265735</v>
+        <v>-0.1951029543058591</v>
       </c>
       <c r="J200" s="15" t="n">
         <v>0.5</v>
@@ -10791,7 +10845,7 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>DEN @ KC</t>
+          <t>NO @ DET</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
@@ -10801,23 +10855,23 @@
       </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>Over 42.5</t>
+          <t>Over 49.5</t>
         </is>
       </c>
       <c r="E201" s="7" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="F201" s="8" t="n">
-        <v>0.4151</v>
+        <v>0.4286</v>
       </c>
       <c r="G201" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5349</v>
       </c>
       <c r="H201" s="8" t="n">
-        <v>-0.0529</v>
+        <v>-0.0527</v>
       </c>
       <c r="I201" s="8" t="n">
-        <v>-0.2075049798576659</v>
+        <v>-0.1987411539265735</v>
       </c>
       <c r="J201" s="10" t="n">
         <v>0.5</v>
@@ -11776,7 +11830,7 @@
         </is>
       </c>
       <c r="D9" s="14" t="n">
-        <v>8.16</v>
+        <v>8.18</v>
       </c>
       <c r="E9" s="14" t="n">
         <v>-8.5</v>
@@ -11912,7 +11966,7 @@
         </is>
       </c>
       <c r="D13" s="14" t="n">
-        <v>6.16</v>
+        <v>6.17</v>
       </c>
       <c r="E13" s="14" t="n">
         <v>-4.5</v>
@@ -12082,7 +12136,7 @@
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>6.08</v>
+        <v>6.09</v>
       </c>
       <c r="E18" s="9" t="n">
         <v>-5.5</v>
@@ -12326,7 +12380,7 @@
         <v>-3</v>
       </c>
       <c r="F25" s="16" t="n">
-        <v>39.1</v>
+        <v>40.5</v>
       </c>
       <c r="G25" s="16" t="n">
         <v>42.5</v>
@@ -12354,7 +12408,7 @@
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>-1.79</v>
+        <v>-1.8</v>
       </c>
       <c r="E26" s="9" t="n">
         <v>2.5</v>
@@ -12490,7 +12544,7 @@
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>5.88</v>
+        <v>5.9</v>
       </c>
       <c r="E30" s="9" t="n">
         <v>-4.5</v>
@@ -12524,7 +12578,7 @@
         </is>
       </c>
       <c r="D31" s="14" t="n">
-        <v>3.84</v>
+        <v>3.85</v>
       </c>
       <c r="E31" s="14" t="n">
         <v>-3</v>
@@ -12598,7 +12652,7 @@
         <v>1.5</v>
       </c>
       <c r="F33" s="16" t="n">
-        <v>45</v>
+        <v>44.8</v>
       </c>
       <c r="G33" s="16" t="n">
         <v>44.5</v>
@@ -12660,13 +12714,13 @@
         </is>
       </c>
       <c r="D35" s="14" t="n">
-        <v>7.38</v>
+        <v>7.37</v>
       </c>
       <c r="E35" s="14" t="n">
         <v>-7.5</v>
       </c>
       <c r="F35" s="16" t="n">
-        <v>42</v>
+        <v>41.7</v>
       </c>
       <c r="G35" s="16" t="n">
         <v>40.5</v>
@@ -12728,13 +12782,13 @@
         </is>
       </c>
       <c r="D37" s="14" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="E37" s="14" t="n">
         <v>-1.5</v>
       </c>
       <c r="F37" s="16" t="n">
-        <v>41.6</v>
+        <v>41.8</v>
       </c>
       <c r="G37" s="16" t="n">
         <v>38.5</v>
@@ -12796,13 +12850,13 @@
         </is>
       </c>
       <c r="D39" s="14" t="n">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="E39" s="14" t="n">
         <v>-3.5</v>
       </c>
       <c r="F39" s="16" t="n">
-        <v>46.9</v>
+        <v>45.5</v>
       </c>
       <c r="G39" s="16" t="n">
         <v>48.5</v>
@@ -13895,7 +13949,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="18" t="n">
-        <v>3.76</v>
+        <v>3.8</v>
       </c>
       <c r="E5" s="18" t="n">
         <v>2.9</v>
@@ -13927,7 +13981,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="20" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="E6" s="20" t="n">
         <v>2.35</v>
@@ -14084,7 +14138,7 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" s="18" t="n">
         <v>1.93</v>
@@ -14116,7 +14170,7 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D12" s="20" t="n">
         <v>1.91</v>
@@ -14407,7 +14461,7 @@
         <v>0</v>
       </c>
       <c r="D21" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="E21" s="18" t="n">
         <v>1.87</v>
@@ -14567,7 +14621,7 @@
         <v>0</v>
       </c>
       <c r="D26" s="20" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.85</v>
       </c>
       <c r="E26" s="20" t="n">
         <v>-0.8100000000000001</v>
@@ -14727,7 +14781,7 @@
         <v>0</v>
       </c>
       <c r="D31" s="18" t="n">
-        <v>-2.66</v>
+        <v>-2.67</v>
       </c>
       <c r="E31" s="18" t="n">
         <v>-1.44</v>
@@ -14887,7 +14941,7 @@
         <v>0</v>
       </c>
       <c r="D36" s="20" t="n">
-        <v>-5.61</v>
+        <v>-5.6</v>
       </c>
       <c r="E36" s="20" t="n">
         <v>-0.88</v>
@@ -19463,10 +19517,10 @@
         <v>46.5</v>
       </c>
       <c r="I93" s="7" t="n">
-        <v>-185</v>
+        <v>-192</v>
       </c>
       <c r="J93" s="7" t="n">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="K93" s="17" t="n">
         <v>0</v>
@@ -22270,10 +22324,10 @@
         <v>50.5</v>
       </c>
       <c r="I146" s="12" t="n">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="J146" s="12" t="n">
-        <v>-245</v>
+        <v>-250</v>
       </c>
       <c r="K146" s="19" t="n">
         <v>0</v>
@@ -24119,13 +24173,13 @@
         </is>
       </c>
       <c r="G181" s="9" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="H181" s="11" t="n">
         <v>50.5</v>
       </c>
       <c r="I181" s="7" t="n">
-        <v>-218</v>
+        <v>-225</v>
       </c>
       <c r="J181" s="7" t="n">
         <v>180</v>
@@ -24284,10 +24338,10 @@
         <v>43.5</v>
       </c>
       <c r="I184" s="12" t="n">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="J184" s="12" t="n">
-        <v>-142</v>
+        <v>-135</v>
       </c>
       <c r="K184" s="19" t="n">
         <v>0</v>
@@ -24602,10 +24656,10 @@
         <v>47.5</v>
       </c>
       <c r="I190" s="12" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="J190" s="12" t="n">
-        <v>-125</v>
+        <v>-122</v>
       </c>
       <c r="K190" s="19" t="n">
         <v>0</v>
@@ -25980,10 +26034,10 @@
         <v>52.5</v>
       </c>
       <c r="I216" s="12" t="n">
-        <v>-122</v>
+        <v>-125</v>
       </c>
       <c r="J216" s="12" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="K216" s="19" t="n">
         <v>0</v>
@@ -27835,10 +27889,10 @@
         <v>44.5</v>
       </c>
       <c r="I251" s="7" t="n">
-        <v>-122</v>
+        <v>-125</v>
       </c>
       <c r="J251" s="7" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="K251" s="17" t="n">
         <v>0</v>
@@ -28577,10 +28631,10 @@
         <v>46.5</v>
       </c>
       <c r="I265" s="7" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="J265" s="7" t="n">
-        <v>-180</v>
+        <v>-185</v>
       </c>
       <c r="K265" s="17" t="n">
         <v>0</v>
@@ -28842,10 +28896,10 @@
         <v>43.5</v>
       </c>
       <c r="I270" s="12" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="J270" s="12" t="n">
-        <v>-155</v>
+        <v>-162</v>
       </c>
       <c r="K270" s="19" t="n">
         <v>0</v>
@@ -30326,10 +30380,10 @@
         <v>48.5</v>
       </c>
       <c r="I298" s="12" t="n">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="J298" s="12" t="n">
-        <v>-192</v>
+        <v>-185</v>
       </c>
       <c r="K298" s="19" t="n">
         <v>0</v>
@@ -44370,7 +44424,7 @@
       </c>
       <c r="F381" s="4" t="inlineStr">
         <is>
-          <t>Smith (undisclosed) reverted to the Chiefs' injured reserve list Monday, Matt Derrick of ChiefsDigest.com reports.</t>
+          <t>Smith (undisclosed) reverted to the Chiefs' injured-reserve list Monday, Matt Derrick of ChiefsDigest.com reports.</t>
         </is>
       </c>
     </row>
@@ -53106,7 +53160,7 @@
       </c>
       <c r="F655" s="4" t="inlineStr">
         <is>
-          <t>The Steelers placed Driscoll (undisclosed) on injured reserve Monday with a designation to return during the regular season, Teresa Varley of the team's official site reports.</t>
+          <t>The Steelers placed Driscoll (undisclosed) on injured reserve Monday with a designation to return, Teresa Varley of the team's official site reports.</t>
         </is>
       </c>
     </row>
@@ -57986,20 +58040,20 @@
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>69.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="E5" s="17" t="n">
-        <v>9.300000000000001</v>
+        <v>2.1</v>
       </c>
       <c r="F5" s="17" t="n">
-        <v>13.6</v>
+        <v>6.7</v>
       </c>
       <c r="G5" s="17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Overcast</t>
         </is>
       </c>
       <c r="I5" s="9" t="n">
@@ -58024,26 +58078,30 @@
         </is>
       </c>
       <c r="D6" s="19" t="n">
-        <v>66.40000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="E6" s="19" t="n">
-        <v>4.6</v>
+        <v>10.4</v>
       </c>
       <c r="F6" s="19" t="n">
-        <v>12.3</v>
+        <v>29.1</v>
       </c>
       <c r="G6" s="19" t="n">
         <v>7</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>Mainly clear</t>
+          <t>Light drizzle</t>
         </is>
       </c>
       <c r="I6" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5" t="inlineStr"/>
+        <v>-3</v>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Wind 10 mph (gusts 29)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -58062,20 +58120,20 @@
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>76.5</v>
+        <v>79.3</v>
       </c>
       <c r="E7" s="17" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="F7" s="17" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G7" s="17" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Drizzle</t>
+          <t>Overcast</t>
         </is>
       </c>
       <c r="I7" s="9" t="n">
@@ -58100,16 +58158,16 @@
         </is>
       </c>
       <c r="D8" s="19" t="n">
-        <v>77.59999999999999</v>
+        <v>81</v>
       </c>
       <c r="E8" s="19" t="n">
-        <v>8.800000000000001</v>
+        <v>3.3</v>
       </c>
       <c r="F8" s="19" t="n">
-        <v>14.1</v>
+        <v>8.5</v>
       </c>
       <c r="G8" s="19" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
@@ -58138,28 +58196,28 @@
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>97.09999999999999</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="E9" s="17" t="n">
-        <v>10.3</v>
+        <v>12.5</v>
       </c>
       <c r="F9" s="17" t="n">
-        <v>12.5</v>
+        <v>8.5</v>
       </c>
       <c r="G9" s="17" t="n">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Partly cloudy</t>
         </is>
       </c>
       <c r="I9" s="9" t="n">
-        <v>-0.25</v>
+        <v>-0.65</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>97°F · retractable roof — effect halved</t>
+          <t>Wind 12 mph (gusts 8) · 96°F · retractable roof — effect halved</t>
         </is>
       </c>
     </row>
@@ -58180,16 +58238,16 @@
         </is>
       </c>
       <c r="D10" s="19" t="n">
-        <v>93</v>
+        <v>95.2</v>
       </c>
       <c r="E10" s="19" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="F10" s="19" t="n">
-        <v>8.1</v>
+        <v>6.5</v>
       </c>
       <c r="G10" s="19" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
@@ -58201,7 +58259,7 @@
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>93°F</t>
+          <t>95°F</t>
         </is>
       </c>
     </row>
@@ -58222,26 +58280,30 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>91.3</v>
+        <v>101.1</v>
       </c>
       <c r="E11" s="17" t="n">
-        <v>8.800000000000001</v>
+        <v>3.5</v>
       </c>
       <c r="F11" s="17" t="n">
-        <v>6.9</v>
+        <v>12.3</v>
       </c>
       <c r="G11" s="17" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Light drizzle</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="I11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr"/>
+        <v>-0.5</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>101°F</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -58260,16 +58322,16 @@
         </is>
       </c>
       <c r="D12" s="19" t="n">
-        <v>81.3</v>
+        <v>74.2</v>
       </c>
       <c r="E12" s="19" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="F12" s="19" t="n">
-        <v>10.5</v>
+        <v>3.8</v>
       </c>
       <c r="G12" s="19" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
@@ -58302,16 +58364,16 @@
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>93.2</v>
+        <v>90.8</v>
       </c>
       <c r="E13" s="17" t="n">
-        <v>9</v>
+        <v>1.1</v>
       </c>
       <c r="F13" s="17" t="n">
-        <v>13</v>
+        <v>6.7</v>
       </c>
       <c r="G13" s="17" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
@@ -58319,13 +58381,9 @@
         </is>
       </c>
       <c r="I13" s="9" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>93°F</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -58344,20 +58402,20 @@
         </is>
       </c>
       <c r="D14" s="19" t="n">
-        <v>74.59999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="E14" s="19" t="n">
-        <v>7.2</v>
+        <v>2.5</v>
       </c>
       <c r="F14" s="19" t="n">
-        <v>17.7</v>
+        <v>4.7</v>
       </c>
       <c r="G14" s="19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>Overcast</t>
+          <t>Mainly clear</t>
         </is>
       </c>
       <c r="I14" s="14" t="n">
@@ -58382,20 +58440,20 @@
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>70.90000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="E15" s="17" t="n">
-        <v>7.2</v>
+        <v>10.7</v>
       </c>
       <c r="F15" s="17" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="G15" s="17" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Overcast</t>
+          <t>Mainly clear</t>
         </is>
       </c>
       <c r="I15" s="9" t="n">
@@ -58420,20 +58478,20 @@
         </is>
       </c>
       <c r="D16" s="19" t="n">
-        <v>84.90000000000001</v>
+        <v>74</v>
       </c>
       <c r="E16" s="19" t="n">
-        <v>12</v>
+        <v>8.1</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>24.8</v>
+        <v>2.9</v>
       </c>
       <c r="G16" s="19" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>Overcast</t>
+          <t>Light drizzle</t>
         </is>
       </c>
       <c r="I16" s="14" t="n">
@@ -58462,20 +58520,20 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>89.09999999999999</v>
+        <v>88</v>
       </c>
       <c r="E17" s="17" t="n">
-        <v>15.5</v>
+        <v>1.5</v>
       </c>
       <c r="F17" s="17" t="n">
-        <v>19.7</v>
+        <v>14.8</v>
       </c>
       <c r="G17" s="17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Overcast</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
@@ -58504,16 +58562,16 @@
         </is>
       </c>
       <c r="D18" s="19" t="n">
-        <v>78.7</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="E18" s="19" t="n">
-        <v>1.8</v>
+        <v>11</v>
       </c>
       <c r="F18" s="19" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="G18" s="19" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
@@ -58542,20 +58600,20 @@
         </is>
       </c>
       <c r="D19" s="17" t="n">
-        <v>74.8</v>
+        <v>77.5</v>
       </c>
       <c r="E19" s="17" t="n">
-        <v>4.8</v>
+        <v>10.7</v>
       </c>
       <c r="F19" s="17" t="n">
-        <v>5.4</v>
+        <v>9.6</v>
       </c>
       <c r="G19" s="17" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Overcast</t>
+          <t>Partly cloudy</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
@@ -58580,30 +58638,26 @@
         </is>
       </c>
       <c r="D20" s="19" t="n">
-        <v>98.59999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="E20" s="19" t="n">
-        <v>18.2</v>
+        <v>11.1</v>
       </c>
       <c r="F20" s="19" t="n">
-        <v>30.9</v>
+        <v>3.4</v>
       </c>
       <c r="G20" s="19" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Overcast</t>
         </is>
       </c>
       <c r="I20" s="14" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="J20" s="5" t="inlineStr">
-        <is>
-          <t>Wind 18 mph (gusts 31) · 99°F</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">

--- a/NFL_Edge_Model.xlsx
+++ b/NFL_Edge_Model.xlsx
@@ -692,7 +692,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Snapshot of the live model, generated 2026-09-02T00:22:30+00:00. Read-only: the model runs in the pipeline, not in this file.</t>
+          <t>Snapshot of the live model, generated 2026-09-02T05:13:05+00:00. Read-only: the model runs in the pipeline, not in this file.</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02T00:22:30+00:00</t>
+          <t>2026-09-02T05:13:05+00:00</t>
         </is>
       </c>
     </row>
@@ -2992,19 +2992,19 @@
         </is>
       </c>
       <c r="E10" s="12" t="n">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.258</v>
+        <v>0.2593</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>0.1961</v>
+        <v>0.2</v>
       </c>
       <c r="H10" s="13" t="n">
-        <v>0.0445</v>
+        <v>0.0436</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>0.3134779741630834</v>
+        <v>0.2943176647439902</v>
       </c>
       <c r="J10" s="15" t="n">
         <v>0.5</v>
@@ -3068,33 +3068,33 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>TB @ CIN</t>
+          <t>IND @ KC</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Under 50.5</t>
+          <t>IND ML</t>
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>-102</v>
+        <v>270</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.3171</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>0.505</v>
+        <v>0.2703</v>
       </c>
       <c r="H12" s="13" t="n">
         <v>0.0381</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>0.09302958902873293</v>
+        <v>0.1718450921457355</v>
       </c>
       <c r="J12" s="15" t="n">
         <v>0.5</v>
@@ -3109,33 +3109,33 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>IND @ KC</t>
+          <t>GB @ MIN</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>IND ML</t>
+          <t>Under 45.5</t>
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>270</v>
+        <v>-110</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>0.3171</v>
+        <v>0.5703</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>0.2703</v>
+        <v>0.5238</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>0.0381</v>
+        <v>0.0379</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0.1718450921457355</v>
+        <v>0.08880114448872278</v>
       </c>
       <c r="J13" s="10" t="n">
         <v>0.5</v>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>GB @ MIN</t>
+          <t>ARI @ LAC</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -3160,23 +3160,23 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Under 45.5</t>
+          <t>Under 46.5</t>
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5703</v>
+        <v>0.5567</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5122</v>
       </c>
       <c r="H14" s="13" t="n">
-        <v>0.0379</v>
+        <v>0.0368</v>
       </c>
       <c r="I14" s="13" t="n">
-        <v>0.08880114448872278</v>
+        <v>0.08686420603240941</v>
       </c>
       <c r="J14" s="15" t="n">
         <v>0.5</v>
@@ -3196,28 +3196,28 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Under 46.5</t>
+          <t>ARI +10.5</t>
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>0.5567</v>
+        <v>0.5673</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.5238</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>0.0368</v>
+        <v>0.0363</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>0.08686420603240941</v>
+        <v>0.08311702747853356</v>
       </c>
       <c r="J15" s="10" t="n">
         <v>0.5</v>
@@ -3273,33 +3273,33 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>ARI @ LAC</t>
+          <t>LV @ LAC</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>ARI +10.5</t>
+          <t>Under 42.5</t>
         </is>
       </c>
       <c r="E17" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>0.5657</v>
+        <v>0.5654</v>
       </c>
       <c r="G17" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>0.0353</v>
+        <v>0.0351</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>0.07998022224357693</v>
+        <v>0.07941221357333128</v>
       </c>
       <c r="J17" s="10" t="n">
         <v>0.5</v>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>LV @ LAC</t>
+          <t>TB @ CIN</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -3406,23 +3406,23 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Under 42.5</t>
+          <t>Under 50.5</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>-110</v>
+        <v>-102</v>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5629</v>
+        <v>0.542</v>
       </c>
       <c r="G20" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.505</v>
       </c>
       <c r="H20" s="13" t="n">
-        <v>0.0336</v>
+        <v>0.0323</v>
       </c>
       <c r="I20" s="13" t="n">
-        <v>0.07470691978380595</v>
+        <v>0.0733067893543442</v>
       </c>
       <c r="J20" s="15" t="n">
         <v>0.5</v>
@@ -3478,33 +3478,33 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>ATL @ GB</t>
+          <t>ARI @ LAC</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>ATL +7.5</t>
+          <t>ARI ML</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>-110</v>
+        <v>410</v>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5583</v>
+        <v>0.2313</v>
       </c>
       <c r="G22" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.1961</v>
       </c>
       <c r="H22" s="13" t="n">
-        <v>0.0306</v>
+        <v>0.0311</v>
       </c>
       <c r="I22" s="13" t="n">
-        <v>0.06578185805433401</v>
+        <v>0.1781480074782005</v>
       </c>
       <c r="J22" s="15" t="n">
         <v>0.5</v>
@@ -3519,33 +3519,33 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>NO @ BAL</t>
+          <t>ATL @ GB</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Under 46.5</t>
+          <t>ATL +7.5</t>
         </is>
       </c>
       <c r="E23" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.5583</v>
       </c>
       <c r="G23" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>0.0304</v>
+        <v>0.0306</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>0.06527646820956157</v>
+        <v>0.06578185805433401</v>
       </c>
       <c r="J23" s="10" t="n">
         <v>0.5</v>
@@ -3560,33 +3560,33 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>ARI @ LAC</t>
+          <t>NO @ BAL</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>ARI ML</t>
+          <t>Under 46.5</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>410</v>
+        <v>-110</v>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.2299</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>0.1961</v>
+        <v>0.5238</v>
       </c>
       <c r="H24" s="13" t="n">
-        <v>0.0301</v>
+        <v>0.0304</v>
       </c>
       <c r="I24" s="13" t="n">
-        <v>0.1713663058585707</v>
+        <v>0.06527646820956157</v>
       </c>
       <c r="J24" s="15" t="n">
         <v>0.5</v>
@@ -3618,16 +3618,16 @@
         <v>-110</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>0.5565</v>
+        <v>0.5574</v>
       </c>
       <c r="G25" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>0.0293</v>
+        <v>0.0299</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>0.0623388873539078</v>
+        <v>0.06406509553445949</v>
       </c>
       <c r="J25" s="10" t="n">
         <v>0.5</v>
@@ -3946,16 +3946,16 @@
         <v>-110</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>0.5494</v>
+        <v>0.5503</v>
       </c>
       <c r="G33" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>0.0239</v>
+        <v>0.0246</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>0.04881652803681086</v>
+        <v>0.05055573331046148</v>
       </c>
       <c r="J33" s="10" t="n">
         <v>0.5</v>
@@ -4028,16 +4028,16 @@
         <v>300</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>0.2703</v>
+        <v>0.2711</v>
       </c>
       <c r="G35" s="8" t="n">
         <v>0.25</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>0.0194</v>
+        <v>0.0201</v>
       </c>
       <c r="I35" s="8" t="n">
-        <v>0.08059054237450491</v>
+        <v>0.08372305641244782</v>
       </c>
       <c r="J35" s="10" t="n">
         <v>0.5</v>
@@ -4052,7 +4052,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>GB @ NYJ</t>
+          <t>LV @ LAC</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -4062,23 +4062,23 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>NYJ ML</t>
+          <t>LV ML</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>205</v>
+        <v>285</v>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.348</v>
+        <v>0.2805</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>0.3279</v>
+        <v>0.2597</v>
       </c>
       <c r="H36" s="13" t="n">
-        <v>0.0193</v>
+        <v>0.0198</v>
       </c>
       <c r="I36" s="13" t="n">
-        <v>0.06097479808193551</v>
+        <v>0.07936450655420757</v>
       </c>
       <c r="J36" s="15" t="n">
         <v>0.5</v>
@@ -4093,7 +4093,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>LV @ LAC</t>
+          <t>GB @ NYJ</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -4103,23 +4103,23 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>LV ML</t>
+          <t>NYJ ML</t>
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>285</v>
+        <v>205</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>0.2797</v>
+        <v>0.348</v>
       </c>
       <c r="G37" s="8" t="n">
-        <v>0.2597</v>
+        <v>0.3279</v>
       </c>
       <c r="H37" s="8" t="n">
-        <v>0.0191</v>
+        <v>0.0193</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>0.07630668567848609</v>
+        <v>0.06097479808193551</v>
       </c>
       <c r="J37" s="10" t="n">
         <v>0.5</v>
@@ -4274,16 +4274,16 @@
         <v>150</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>0.413</v>
+        <v>0.4127</v>
       </c>
       <c r="G41" s="8" t="n">
         <v>0.4</v>
       </c>
       <c r="H41" s="8" t="n">
-        <v>0.0128</v>
+        <v>0.0125</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>0.0323224999921764</v>
+        <v>0.03143011644167559</v>
       </c>
       <c r="J41" s="10" t="n">
         <v>0.5</v>
@@ -4438,16 +4438,16 @@
         <v>-110</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>0.5347</v>
+        <v>0.5343</v>
       </c>
       <c r="G45" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H45" s="8" t="n">
-        <v>0.0108</v>
+        <v>0.0104</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>0.02080244151609179</v>
+        <v>0.02012234820486508</v>
       </c>
       <c r="J45" s="10" t="n">
         <v>0.5</v>
@@ -5217,16 +5217,16 @@
         <v>-110</v>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5244</v>
       </c>
       <c r="G64" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H64" s="13" t="n">
-        <v>0</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="I64" s="13" t="n">
-        <v>1.891903972672804e-05</v>
+        <v>0.001064095033525336</v>
       </c>
       <c r="J64" s="15" t="n">
         <v>0.5</v>
@@ -5258,16 +5258,16 @@
         <v>124</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>0.446</v>
+        <v>0.4469</v>
       </c>
       <c r="G65" s="8" t="n">
         <v>0.4464</v>
       </c>
       <c r="H65" s="8" t="n">
-        <v>-0.0005</v>
+        <v>0.0004</v>
       </c>
       <c r="I65" s="8" t="n">
-        <v>-0.001057861630209156</v>
+        <v>0.000959947923989013</v>
       </c>
       <c r="J65" s="10" t="n">
         <v>0.5</v>
@@ -5282,33 +5282,33 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>GB @ NYJ</t>
+          <t>NO @ DET</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Over 42.5</t>
+          <t>NO ML</t>
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>-110</v>
+        <v>240</v>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.5229</v>
+        <v>0.2933</v>
       </c>
       <c r="G66" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.2941</v>
       </c>
       <c r="H66" s="13" t="n">
-        <v>-0.0009</v>
+        <v>-0.0008</v>
       </c>
       <c r="I66" s="13" t="n">
-        <v>-0.0018072101636053</v>
+        <v>-0.002773564204436085</v>
       </c>
       <c r="J66" s="15" t="n">
         <v>0.5</v>
@@ -5323,33 +5323,33 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>MIA @ LV</t>
+          <t>GB @ NYJ</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>MIA +3.5</t>
+          <t>Over 42.5</t>
         </is>
       </c>
       <c r="E67" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.5229</v>
       </c>
       <c r="G67" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H67" s="8" t="n">
-        <v>-0.0011</v>
+        <v>-0.0009</v>
       </c>
       <c r="I67" s="8" t="n">
-        <v>-0.002054425831649553</v>
+        <v>-0.0018072101636053</v>
       </c>
       <c r="J67" s="10" t="n">
         <v>0.5</v>
@@ -5364,33 +5364,33 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>NO @ DET</t>
+          <t>MIA @ LV</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>NO ML</t>
+          <t>MIA +3.5</t>
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>240</v>
+        <v>-110</v>
       </c>
       <c r="F68" s="13" t="n">
-        <v>0.2928</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="G68" s="13" t="n">
-        <v>0.2941</v>
+        <v>0.5238</v>
       </c>
       <c r="H68" s="13" t="n">
-        <v>-0.0013</v>
+        <v>-0.0011</v>
       </c>
       <c r="I68" s="13" t="n">
-        <v>-0.004399555514966624</v>
+        <v>-0.002054425831649553</v>
       </c>
       <c r="J68" s="15" t="n">
         <v>0.5</v>
@@ -5750,16 +5750,16 @@
         <v>-110</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>0.5149</v>
+        <v>0.5157</v>
       </c>
       <c r="G77" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H77" s="8" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0081</v>
       </c>
       <c r="I77" s="8" t="n">
-        <v>-0.01578031606371538</v>
+        <v>-0.01440979091609185</v>
       </c>
       <c r="J77" s="10" t="n">
         <v>0.5</v>
@@ -5791,16 +5791,16 @@
         <v>200</v>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.3241</v>
+        <v>0.3239</v>
       </c>
       <c r="G78" s="13" t="n">
         <v>0.3333</v>
       </c>
       <c r="H78" s="13" t="n">
-        <v>-0.0092</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="I78" s="13" t="n">
-        <v>-0.02757605251240169</v>
+        <v>-0.02807134898259012</v>
       </c>
       <c r="J78" s="15" t="n">
         <v>0.5</v>
@@ -5815,7 +5815,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>NO @ BAL</t>
+          <t>DAL @ NYG</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -5825,23 +5825,23 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>NO +7.5</t>
+          <t>NYG +2.5</t>
         </is>
       </c>
       <c r="E79" s="7" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>0.5139</v>
+        <v>0.5023</v>
       </c>
       <c r="G79" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5122</v>
       </c>
       <c r="H79" s="8" t="n">
         <v>-0.0098</v>
       </c>
       <c r="I79" s="8" t="n">
-        <v>-0.01887108993526976</v>
+        <v>-0.0192869873361099</v>
       </c>
       <c r="J79" s="10" t="n">
         <v>0.5</v>
@@ -5856,7 +5856,7 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>DAL @ NYG</t>
+          <t>NO @ BAL</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
@@ -5866,23 +5866,23 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>NYG +2.5</t>
+          <t>NO +7.5</t>
         </is>
       </c>
       <c r="E80" s="12" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.5014</v>
+        <v>0.5139</v>
       </c>
       <c r="G80" s="13" t="n">
-        <v>0.5122</v>
+        <v>0.5238</v>
       </c>
       <c r="H80" s="13" t="n">
-        <v>-0.0106</v>
+        <v>-0.0098</v>
       </c>
       <c r="I80" s="13" t="n">
-        <v>-0.02104650038944611</v>
+        <v>-0.01887108993526976</v>
       </c>
       <c r="J80" s="15" t="n">
         <v>0.5</v>
@@ -6037,16 +6037,16 @@
         <v>100</v>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.4866</v>
+        <v>0.4868</v>
       </c>
       <c r="G84" s="13" t="n">
         <v>0.5</v>
       </c>
       <c r="H84" s="13" t="n">
-        <v>-0.0132</v>
+        <v>-0.013</v>
       </c>
       <c r="I84" s="13" t="n">
-        <v>-0.02488865445146499</v>
+        <v>-0.02452981169788415</v>
       </c>
       <c r="J84" s="15" t="n">
         <v>0.5</v>
@@ -6061,33 +6061,33 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>TB @ CIN</t>
+          <t>DET @ BUF</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>TB +3.5</t>
+          <t>BUF ML</t>
         </is>
       </c>
       <c r="E85" s="7" t="n">
-        <v>-105</v>
+        <v>-162</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>0.4981</v>
+        <v>0.6046</v>
       </c>
       <c r="G85" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.6183</v>
       </c>
       <c r="H85" s="8" t="n">
-        <v>-0.0138</v>
+        <v>-0.0135</v>
       </c>
       <c r="I85" s="8" t="n">
-        <v>-0.0275697342050793</v>
+        <v>-0.02206534803966503</v>
       </c>
       <c r="J85" s="10" t="n">
         <v>0.5</v>
@@ -6102,33 +6102,33 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>DET @ BUF</t>
+          <t>TB @ CIN</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>BUF ML</t>
+          <t>TB +3.5</t>
         </is>
       </c>
       <c r="E86" s="12" t="n">
-        <v>-162</v>
+        <v>-105</v>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.6039</v>
+        <v>0.4981</v>
       </c>
       <c r="G86" s="13" t="n">
-        <v>0.6183</v>
+        <v>0.5122</v>
       </c>
       <c r="H86" s="13" t="n">
-        <v>-0.0141</v>
+        <v>-0.0138</v>
       </c>
       <c r="I86" s="13" t="n">
-        <v>-0.02319589236872954</v>
+        <v>-0.0275697342050793</v>
       </c>
       <c r="J86" s="15" t="n">
         <v>0.5</v>
@@ -6447,16 +6447,16 @@
         <v>-148</v>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.5774</v>
+        <v>0.5775</v>
       </c>
       <c r="G94" s="13" t="n">
         <v>0.5968</v>
       </c>
       <c r="H94" s="13" t="n">
-        <v>-0.0187</v>
+        <v>-0.0185</v>
       </c>
       <c r="I94" s="13" t="n">
-        <v>-0.03225450219495668</v>
+        <v>-0.03195665133187686</v>
       </c>
       <c r="J94" s="15" t="n">
         <v>0.5</v>
@@ -6522,23 +6522,23 @@
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>DEN ML</t>
+          <t>JAX ML</t>
         </is>
       </c>
       <c r="E96" s="12" t="n">
-        <v>-142</v>
+        <v>120</v>
       </c>
       <c r="F96" s="13" t="n">
-        <v>0.5663</v>
+        <v>0.4339</v>
       </c>
       <c r="G96" s="13" t="n">
-        <v>0.5868</v>
+        <v>0.4545</v>
       </c>
       <c r="H96" s="13" t="n">
-        <v>-0.0196</v>
+        <v>-0.0197</v>
       </c>
       <c r="I96" s="13" t="n">
-        <v>-0.03465283785547102</v>
+        <v>-0.04497708260678568</v>
       </c>
       <c r="J96" s="15" t="n">
         <v>0.5</v>
@@ -6604,23 +6604,23 @@
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>JAX ML</t>
+          <t>DEN ML</t>
         </is>
       </c>
       <c r="E98" s="12" t="n">
-        <v>120</v>
+        <v>-142</v>
       </c>
       <c r="F98" s="13" t="n">
-        <v>0.4337</v>
+        <v>0.5661</v>
       </c>
       <c r="G98" s="13" t="n">
-        <v>0.4545</v>
+        <v>0.5868</v>
       </c>
       <c r="H98" s="13" t="n">
-        <v>-0.0199</v>
+        <v>-0.0198</v>
       </c>
       <c r="I98" s="13" t="n">
-        <v>-0.04537041246747764</v>
+        <v>-0.03495745537836692</v>
       </c>
       <c r="J98" s="15" t="n">
         <v>0.5</v>
@@ -6635,33 +6635,33 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>JAX @ DEN</t>
+          <t>CLE @ TB</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>DEN -2.5</t>
+          <t>Under 42.5</t>
         </is>
       </c>
       <c r="E99" s="7" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="F99" s="8" t="n">
-        <v>0.5137</v>
+        <v>0.5024999999999999</v>
       </c>
       <c r="G99" s="8" t="n">
-        <v>0.5349</v>
+        <v>0.5238</v>
       </c>
       <c r="H99" s="8" t="n">
-        <v>-0.0202</v>
+        <v>-0.0203</v>
       </c>
       <c r="I99" s="8" t="n">
-        <v>-0.03954410308742839</v>
+        <v>-0.0406071812651127</v>
       </c>
       <c r="J99" s="10" t="n">
         <v>0.5</v>
@@ -6676,33 +6676,33 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>CLE @ TB</t>
+          <t>JAX @ DEN</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>Under 42.5</t>
+          <t>DEN -2.5</t>
         </is>
       </c>
       <c r="E100" s="12" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="F100" s="13" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="G100" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5349</v>
       </c>
       <c r="H100" s="13" t="n">
         <v>-0.0203</v>
       </c>
       <c r="I100" s="13" t="n">
-        <v>-0.0406071812651127</v>
+        <v>-0.03988119983375077</v>
       </c>
       <c r="J100" s="15" t="n">
         <v>0.5</v>
@@ -6775,16 +6775,16 @@
         <v>-110</v>
       </c>
       <c r="F102" s="13" t="n">
-        <v>0.5012</v>
+        <v>0.501</v>
       </c>
       <c r="G102" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H102" s="13" t="n">
-        <v>-0.0215</v>
+        <v>-0.0216</v>
       </c>
       <c r="I102" s="13" t="n">
-        <v>-0.04325826480315459</v>
+        <v>-0.0436058847096103</v>
       </c>
       <c r="J102" s="15" t="n">
         <v>0.5</v>
@@ -6881,33 +6881,33 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>DEN @ KC</t>
+          <t>NYG @ LAR</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>DEN ML</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="E105" s="7" t="n">
-        <v>124</v>
+        <v>-110</v>
       </c>
       <c r="F105" s="8" t="n">
-        <v>0.4226</v>
+        <v>0.5</v>
       </c>
       <c r="G105" s="8" t="n">
-        <v>0.4464</v>
+        <v>0.5238</v>
       </c>
       <c r="H105" s="8" t="n">
         <v>-0.0224</v>
       </c>
       <c r="I105" s="8" t="n">
-        <v>-0.05280529636403453</v>
+        <v>-0.04545406739379704</v>
       </c>
       <c r="J105" s="10" t="n">
         <v>0.5</v>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>Under 48.5</t>
         </is>
       </c>
       <c r="E106" s="12" t="n">
@@ -6948,7 +6948,7 @@
         <v>-0.0224</v>
       </c>
       <c r="I106" s="13" t="n">
-        <v>-0.04545406739379704</v>
+        <v>-0.04545502351529379</v>
       </c>
       <c r="J106" s="15" t="n">
         <v>0.5</v>
@@ -6963,33 +6963,33 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>NYG @ LAR</t>
+          <t>GB @ MIN</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Under 48.5</t>
+          <t>MIN ML</t>
         </is>
       </c>
       <c r="E107" s="7" t="n">
-        <v>-110</v>
+        <v>-118</v>
       </c>
       <c r="F107" s="8" t="n">
-        <v>0.5</v>
+        <v>0.5174</v>
       </c>
       <c r="G107" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5413</v>
       </c>
       <c r="H107" s="8" t="n">
-        <v>-0.0224</v>
+        <v>-0.0225</v>
       </c>
       <c r="I107" s="8" t="n">
-        <v>-0.04545502351529379</v>
+        <v>-0.04371535600107435</v>
       </c>
       <c r="J107" s="10" t="n">
         <v>0.5</v>
@@ -7004,7 +7004,7 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>GB @ MIN</t>
+          <t>DEN @ KC</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
@@ -7014,23 +7014,23 @@
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>MIN ML</t>
+          <t>DEN ML</t>
         </is>
       </c>
       <c r="E108" s="12" t="n">
-        <v>-118</v>
+        <v>124</v>
       </c>
       <c r="F108" s="13" t="n">
-        <v>0.5174</v>
+        <v>0.4225</v>
       </c>
       <c r="G108" s="13" t="n">
-        <v>0.5413</v>
+        <v>0.4464</v>
       </c>
       <c r="H108" s="13" t="n">
-        <v>-0.0225</v>
+        <v>-0.0226</v>
       </c>
       <c r="I108" s="13" t="n">
-        <v>-0.04371535600107435</v>
+        <v>-0.05320357713228918</v>
       </c>
       <c r="J108" s="15" t="n">
         <v>0.5</v>
@@ -7103,16 +7103,16 @@
         <v>-110</v>
       </c>
       <c r="F110" s="13" t="n">
-        <v>0.4988</v>
+        <v>0.499</v>
       </c>
       <c r="G110" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H110" s="13" t="n">
-        <v>-0.0234</v>
+        <v>-0.0232</v>
       </c>
       <c r="I110" s="13" t="n">
-        <v>-0.04765082610593624</v>
+        <v>-0.04730320619948047</v>
       </c>
       <c r="J110" s="15" t="n">
         <v>0.5</v>
@@ -7127,7 +7127,7 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>GB @ MIN</t>
+          <t>JAX @ DEN</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
@@ -7137,23 +7137,23 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>GB +1.5</t>
+          <t>JAX +2.5</t>
         </is>
       </c>
       <c r="E111" s="7" t="n">
-        <v>-118</v>
+        <v>-105</v>
       </c>
       <c r="F111" s="8" t="n">
-        <v>0.5153</v>
+        <v>0.4864</v>
       </c>
       <c r="G111" s="8" t="n">
-        <v>0.5413</v>
+        <v>0.5122</v>
       </c>
       <c r="H111" s="8" t="n">
-        <v>-0.0242</v>
+        <v>-0.024</v>
       </c>
       <c r="I111" s="8" t="n">
-        <v>-0.04803970643539485</v>
+        <v>-0.05026802719465456</v>
       </c>
       <c r="J111" s="10" t="n">
         <v>0.5</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>JAX @ DEN</t>
+          <t>GB @ MIN</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
@@ -7178,23 +7178,23 @@
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>JAX +2.5</t>
+          <t>GB +1.5</t>
         </is>
       </c>
       <c r="E112" s="12" t="n">
-        <v>-105</v>
+        <v>-118</v>
       </c>
       <c r="F112" s="13" t="n">
-        <v>0.4863</v>
+        <v>0.5153</v>
       </c>
       <c r="G112" s="13" t="n">
-        <v>0.5122</v>
+        <v>0.5413</v>
       </c>
       <c r="H112" s="13" t="n">
         <v>-0.0242</v>
       </c>
       <c r="I112" s="13" t="n">
-        <v>-0.05062005624424709</v>
+        <v>-0.04803970643539485</v>
       </c>
       <c r="J112" s="15" t="n">
         <v>0.5</v>
@@ -7308,16 +7308,16 @@
         <v>136</v>
       </c>
       <c r="F115" s="8" t="n">
-        <v>0.3961</v>
+        <v>0.3954</v>
       </c>
       <c r="G115" s="8" t="n">
         <v>0.4237</v>
       </c>
       <c r="H115" s="8" t="n">
-        <v>-0.0255</v>
+        <v>-0.026</v>
       </c>
       <c r="I115" s="8" t="n">
-        <v>-0.06453040950051492</v>
+        <v>-0.06618081598377579</v>
       </c>
       <c r="J115" s="10" t="n">
         <v>0.5</v>
@@ -7636,16 +7636,16 @@
         <v>-120</v>
       </c>
       <c r="F123" s="8" t="n">
-        <v>0.5134</v>
+        <v>0.5132</v>
       </c>
       <c r="G123" s="8" t="n">
         <v>0.5455</v>
       </c>
       <c r="H123" s="8" t="n">
-        <v>-0.0289</v>
+        <v>-0.029</v>
       </c>
       <c r="I123" s="8" t="n">
-        <v>-0.05450993515297092</v>
+        <v>-0.05483869624996013</v>
       </c>
       <c r="J123" s="10" t="n">
         <v>0.5</v>
@@ -7718,16 +7718,16 @@
         <v>-245</v>
       </c>
       <c r="F125" s="8" t="n">
-        <v>0.6758999999999999</v>
+        <v>0.6761</v>
       </c>
       <c r="G125" s="8" t="n">
         <v>0.7101</v>
       </c>
       <c r="H125" s="8" t="n">
-        <v>-0.0304</v>
+        <v>-0.0303</v>
       </c>
       <c r="I125" s="8" t="n">
-        <v>-0.04778319140028664</v>
+        <v>-0.04755086353455601</v>
       </c>
       <c r="J125" s="10" t="n">
         <v>0.5</v>
@@ -7824,33 +7824,33 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>DAL @ NYG</t>
+          <t>NO @ BAL</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>DAL -2.5</t>
+          <t>BAL ML</t>
         </is>
       </c>
       <c r="E128" s="12" t="n">
-        <v>-115</v>
+        <v>-345</v>
       </c>
       <c r="F128" s="13" t="n">
-        <v>0.4986</v>
+        <v>0.7388</v>
       </c>
       <c r="G128" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.7753</v>
       </c>
       <c r="H128" s="13" t="n">
-        <v>-0.0318</v>
+        <v>-0.0319</v>
       </c>
       <c r="I128" s="13" t="n">
-        <v>-0.06786321330681894</v>
+        <v>-0.04666581495910796</v>
       </c>
       <c r="J128" s="15" t="n">
         <v>0.5</v>
@@ -7865,33 +7865,33 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>NO @ BAL</t>
+          <t>CIN @ HOU</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>BAL ML</t>
+          <t>Over 46.5</t>
         </is>
       </c>
       <c r="E129" s="7" t="n">
-        <v>-345</v>
+        <v>-110</v>
       </c>
       <c r="F129" s="8" t="n">
-        <v>0.7388</v>
+        <v>0.4873</v>
       </c>
       <c r="G129" s="8" t="n">
-        <v>0.7753</v>
+        <v>0.5238</v>
       </c>
       <c r="H129" s="8" t="n">
-        <v>-0.0319</v>
+        <v>-0.032</v>
       </c>
       <c r="I129" s="8" t="n">
-        <v>-0.04666581495910796</v>
+        <v>-0.0697202361973796</v>
       </c>
       <c r="J129" s="10" t="n">
         <v>0.5</v>
@@ -7906,33 +7906,33 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>CIN @ HOU</t>
+          <t>DAL @ NYG</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>Over 46.5</t>
+          <t>DAL -2.5</t>
         </is>
       </c>
       <c r="E130" s="12" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="F130" s="13" t="n">
-        <v>0.4873</v>
+        <v>0.4977</v>
       </c>
       <c r="G130" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5349</v>
       </c>
       <c r="H130" s="13" t="n">
-        <v>-0.032</v>
+        <v>-0.0324</v>
       </c>
       <c r="I130" s="13" t="n">
-        <v>-0.0697202361973796</v>
+        <v>-0.06954809166011972</v>
       </c>
       <c r="J130" s="15" t="n">
         <v>0.5</v>
@@ -8046,16 +8046,16 @@
         <v>-110</v>
       </c>
       <c r="F133" s="8" t="n">
-        <v>0.4851</v>
+        <v>0.4843</v>
       </c>
       <c r="G133" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H133" s="8" t="n">
-        <v>-0.0334</v>
+        <v>-0.0339</v>
       </c>
       <c r="I133" s="8" t="n">
-        <v>-0.06857147393121826</v>
+        <v>-0.0699426424025904</v>
       </c>
       <c r="J133" s="10" t="n">
         <v>0.5</v>
@@ -8152,33 +8152,33 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>NO @ DET</t>
+          <t>SEA @ ARI</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>DET ML</t>
+          <t>Over 44.5</t>
         </is>
       </c>
       <c r="E136" s="12" t="n">
-        <v>-298</v>
+        <v>-110</v>
       </c>
       <c r="F136" s="13" t="n">
-        <v>0.7072000000000001</v>
+        <v>0.4822</v>
       </c>
       <c r="G136" s="13" t="n">
-        <v>0.7487</v>
+        <v>0.5238</v>
       </c>
       <c r="H136" s="13" t="n">
         <v>-0.0351</v>
       </c>
       <c r="I136" s="13" t="n">
-        <v>-0.05506860221922086</v>
+        <v>-0.07941149046730145</v>
       </c>
       <c r="J136" s="15" t="n">
         <v>0.5</v>
@@ -8193,33 +8193,33 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>SEA @ ARI</t>
+          <t>NO @ DET</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Over 44.5</t>
+          <t>DET ML</t>
         </is>
       </c>
       <c r="E137" s="7" t="n">
-        <v>-110</v>
+        <v>-298</v>
       </c>
       <c r="F137" s="8" t="n">
-        <v>0.4822</v>
+        <v>0.7067</v>
       </c>
       <c r="G137" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.7487</v>
       </c>
       <c r="H137" s="8" t="n">
-        <v>-0.0351</v>
+        <v>-0.0354</v>
       </c>
       <c r="I137" s="8" t="n">
-        <v>-0.07941149046730145</v>
+        <v>-0.05570681329196545</v>
       </c>
       <c r="J137" s="10" t="n">
         <v>0.5</v>
@@ -8251,16 +8251,16 @@
         <v>-148</v>
       </c>
       <c r="F138" s="13" t="n">
-        <v>0.554</v>
+        <v>0.5531</v>
       </c>
       <c r="G138" s="13" t="n">
         <v>0.5968</v>
       </c>
       <c r="H138" s="13" t="n">
-        <v>-0.0358</v>
+        <v>-0.0363</v>
       </c>
       <c r="I138" s="13" t="n">
-        <v>-0.07095605300959495</v>
+        <v>-0.0724652659439004</v>
       </c>
       <c r="J138" s="15" t="n">
         <v>0.5</v>
@@ -8579,16 +8579,16 @@
         <v>-110</v>
       </c>
       <c r="F146" s="13" t="n">
-        <v>0.4762</v>
+        <v>0.4756</v>
       </c>
       <c r="G146" s="13" t="n">
         <v>0.5238</v>
       </c>
       <c r="H146" s="13" t="n">
-        <v>-0.0385</v>
+        <v>-0.0388</v>
       </c>
       <c r="I146" s="13" t="n">
-        <v>-0.08592599385079452</v>
+        <v>-0.086971586113257</v>
       </c>
       <c r="J146" s="15" t="n">
         <v>0.5</v>
@@ -9194,16 +9194,16 @@
         <v>-180</v>
       </c>
       <c r="F161" s="8" t="n">
-        <v>0.587</v>
+        <v>0.5873</v>
       </c>
       <c r="G161" s="8" t="n">
         <v>0.6429</v>
       </c>
       <c r="H161" s="8" t="n">
-        <v>-0.0423</v>
+        <v>-0.0421</v>
       </c>
       <c r="I161" s="8" t="n">
-        <v>-0.08618896999467829</v>
+        <v>-0.0856338580806873</v>
       </c>
       <c r="J161" s="10" t="n">
         <v>0.5</v>
@@ -9341,33 +9341,33 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>MIA @ LV</t>
+          <t>NE @ SEA</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>LV ML</t>
+          <t>SEA -3.5</t>
         </is>
       </c>
       <c r="E165" s="7" t="n">
-        <v>-198</v>
+        <v>-110</v>
       </c>
       <c r="F165" s="8" t="n">
-        <v>0.6061</v>
+        <v>0.4657</v>
       </c>
       <c r="G165" s="8" t="n">
-        <v>0.6644</v>
+        <v>0.5238</v>
       </c>
       <c r="H165" s="8" t="n">
         <v>-0.0432</v>
       </c>
       <c r="I165" s="8" t="n">
-        <v>-0.08696881509886251</v>
+        <v>-0.1110314391139559</v>
       </c>
       <c r="J165" s="10" t="n">
         <v>0.5</v>
@@ -9382,33 +9382,33 @@
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>NE @ SEA</t>
+          <t>MIA @ LV</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>SEA -3.5</t>
+          <t>LV ML</t>
         </is>
       </c>
       <c r="E166" s="12" t="n">
-        <v>-110</v>
+        <v>-198</v>
       </c>
       <c r="F166" s="13" t="n">
-        <v>0.4653</v>
+        <v>0.6061</v>
       </c>
       <c r="G166" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.6644</v>
       </c>
       <c r="H166" s="13" t="n">
-        <v>-0.0433</v>
+        <v>-0.0432</v>
       </c>
       <c r="I166" s="13" t="n">
-        <v>-0.1117115324251826</v>
+        <v>-0.08696881509886251</v>
       </c>
       <c r="J166" s="15" t="n">
         <v>0.5</v>
@@ -9464,42 +9464,38 @@
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>NYG @ LAR</t>
+          <t>CLE @ JAX</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>LAR ML</t>
+          <t>JAX -7.5</t>
         </is>
       </c>
       <c r="E168" s="12" t="n">
-        <v>-380</v>
+        <v>-110</v>
       </c>
       <c r="F168" s="13" t="n">
-        <v>0.7297</v>
+        <v>0.4614</v>
       </c>
       <c r="G168" s="13" t="n">
-        <v>0.7917</v>
+        <v>0.5238</v>
       </c>
       <c r="H168" s="13" t="n">
-        <v>-0.0445</v>
+        <v>-0.0447</v>
       </c>
       <c r="I168" s="13" t="n">
-        <v>-0.07767746543280904</v>
+        <v>-0.1190871693327967</v>
       </c>
       <c r="J168" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="K168" s="5" t="inlineStr">
-        <is>
-          <t>price -380 outside the allowed range</t>
-        </is>
-      </c>
+      <c r="K168" s="5" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
@@ -9509,33 +9505,33 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>CLE @ JAX</t>
+          <t>GB @ NYJ</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>JAX -7.5</t>
+          <t>GB ML</t>
         </is>
       </c>
       <c r="E169" s="7" t="n">
-        <v>-110</v>
+        <v>-250</v>
       </c>
       <c r="F169" s="8" t="n">
-        <v>0.4614</v>
+        <v>0.652</v>
       </c>
       <c r="G169" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.7143</v>
       </c>
       <c r="H169" s="8" t="n">
         <v>-0.0447</v>
       </c>
       <c r="I169" s="8" t="n">
-        <v>-0.1190871693327967</v>
+        <v>-0.08650465376930194</v>
       </c>
       <c r="J169" s="10" t="n">
         <v>0.5</v>
@@ -9550,7 +9546,7 @@
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>GB @ NYJ</t>
+          <t>NYG @ LAR</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
@@ -9560,28 +9556,32 @@
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>GB ML</t>
+          <t>LAR ML</t>
         </is>
       </c>
       <c r="E170" s="12" t="n">
-        <v>-250</v>
+        <v>-380</v>
       </c>
       <c r="F170" s="13" t="n">
-        <v>0.652</v>
+        <v>0.7289</v>
       </c>
       <c r="G170" s="13" t="n">
-        <v>0.7143</v>
+        <v>0.7917</v>
       </c>
       <c r="H170" s="13" t="n">
-        <v>-0.0447</v>
+        <v>-0.0448</v>
       </c>
       <c r="I170" s="13" t="n">
-        <v>-0.08650465376930194</v>
+        <v>-0.07866587450896917</v>
       </c>
       <c r="J170" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="K170" s="5" t="inlineStr"/>
+      <c r="K170" s="5" t="inlineStr">
+        <is>
+          <t>price -380 outside the allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
@@ -9608,16 +9608,16 @@
         <v>-360</v>
       </c>
       <c r="F171" s="8" t="n">
-        <v>0.7203000000000001</v>
+        <v>0.7195</v>
       </c>
       <c r="G171" s="8" t="n">
         <v>0.7826</v>
       </c>
       <c r="H171" s="8" t="n">
-        <v>-0.0447</v>
+        <v>-0.0449</v>
       </c>
       <c r="I171" s="8" t="n">
-        <v>-0.07901652342922608</v>
+        <v>-0.08003058590442327</v>
       </c>
       <c r="J171" s="10" t="n">
         <v>0.5</v>
@@ -9862,16 +9862,16 @@
         <v>-110</v>
       </c>
       <c r="F177" s="8" t="n">
-        <v>0.4506</v>
+        <v>0.4497</v>
       </c>
       <c r="G177" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H177" s="8" t="n">
-        <v>-0.0478</v>
+        <v>-0.048</v>
       </c>
       <c r="I177" s="8" t="n">
-        <v>-0.1397256189459017</v>
+        <v>-0.1414648242195523</v>
       </c>
       <c r="J177" s="10" t="n">
         <v>0.5</v>
@@ -9944,16 +9944,16 @@
         <v>-550</v>
       </c>
       <c r="F179" s="8" t="n">
-        <v>0.7701</v>
+        <v>0.7687</v>
       </c>
       <c r="G179" s="8" t="n">
         <v>0.8462</v>
       </c>
       <c r="H179" s="8" t="n">
-        <v>-0.0485</v>
+        <v>-0.0488</v>
       </c>
       <c r="I179" s="8" t="n">
-        <v>-0.08926209098656329</v>
+        <v>-0.09083207401703816</v>
       </c>
       <c r="J179" s="10" t="n">
         <v>0.5</v>
@@ -10112,16 +10112,16 @@
         <v>-110</v>
       </c>
       <c r="F183" s="8" t="n">
-        <v>0.4435</v>
+        <v>0.4426</v>
       </c>
       <c r="G183" s="8" t="n">
         <v>0.5238</v>
       </c>
       <c r="H183" s="8" t="n">
-        <v>-0.0494</v>
+        <v>-0.0495</v>
       </c>
       <c r="I183" s="8" t="n">
-        <v>-0.1532479782629986</v>
+        <v>-0.1549741864435504</v>
       </c>
       <c r="J183" s="10" t="n">
         <v>0.5</v>
@@ -10218,7 +10218,7 @@
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>IND @ KC</t>
+          <t>TB @ CIN</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
@@ -10228,23 +10228,23 @@
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>Over 47.5</t>
+          <t>Over 50.5</t>
         </is>
       </c>
       <c r="E186" s="12" t="n">
-        <v>-110</v>
+        <v>-118</v>
       </c>
       <c r="F186" s="13" t="n">
-        <v>0.4395</v>
+        <v>0.458</v>
       </c>
       <c r="G186" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5413</v>
       </c>
       <c r="H186" s="13" t="n">
-        <v>-0.0501</v>
+        <v>-0.0499</v>
       </c>
       <c r="I186" s="13" t="n">
-        <v>-0.1609146747875762</v>
+        <v>-0.1538030612553783</v>
       </c>
       <c r="J186" s="15" t="n">
         <v>0.5</v>
@@ -10259,42 +10259,38 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>ATL @ GB</t>
+          <t>IND @ KC</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>GB ML</t>
+          <t>Over 47.5</t>
         </is>
       </c>
       <c r="E187" s="7" t="n">
-        <v>-375</v>
+        <v>-110</v>
       </c>
       <c r="F187" s="8" t="n">
-        <v>0.7047</v>
+        <v>0.4395</v>
       </c>
       <c r="G187" s="8" t="n">
-        <v>0.7895</v>
+        <v>0.5238</v>
       </c>
       <c r="H187" s="8" t="n">
-        <v>-0.0502</v>
+        <v>-0.0501</v>
       </c>
       <c r="I187" s="8" t="n">
-        <v>-0.1064489077074873</v>
+        <v>-0.1609146747875762</v>
       </c>
       <c r="J187" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="K187" s="4" t="inlineStr">
-        <is>
-          <t>price -375 outside the allowed range</t>
-        </is>
-      </c>
+      <c r="K187" s="4" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="5" t="inlineStr">
@@ -10304,38 +10300,42 @@
       </c>
       <c r="B188" s="5" t="inlineStr">
         <is>
-          <t>CHI @ CAR</t>
+          <t>ATL @ GB</t>
         </is>
       </c>
       <c r="C188" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D188" s="5" t="inlineStr">
         <is>
-          <t>Over 47.5</t>
+          <t>GB ML</t>
         </is>
       </c>
       <c r="E188" s="12" t="n">
-        <v>-115</v>
+        <v>-375</v>
       </c>
       <c r="F188" s="13" t="n">
-        <v>0.4483</v>
+        <v>0.7047</v>
       </c>
       <c r="G188" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.7895</v>
       </c>
       <c r="H188" s="13" t="n">
-        <v>-0.0505</v>
+        <v>-0.0502</v>
       </c>
       <c r="I188" s="13" t="n">
-        <v>-0.1619271419973495</v>
+        <v>-0.1064489077074873</v>
       </c>
       <c r="J188" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="K188" s="5" t="inlineStr"/>
+      <c r="K188" s="5" t="inlineStr">
+        <is>
+          <t>price -375 outside the allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
@@ -10345,7 +10345,7 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>DET @ BUF</t>
+          <t>CHI @ CAR</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
@@ -10355,23 +10355,23 @@
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>Over 52.5</t>
+          <t>Over 47.5</t>
         </is>
       </c>
       <c r="E189" s="7" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="F189" s="8" t="n">
-        <v>0.437</v>
+        <v>0.4483</v>
       </c>
       <c r="G189" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.5349</v>
       </c>
       <c r="H189" s="8" t="n">
         <v>-0.0505</v>
       </c>
       <c r="I189" s="8" t="n">
-        <v>-0.1656336429379587</v>
+        <v>-0.1619271419973495</v>
       </c>
       <c r="J189" s="10" t="n">
         <v>0.5</v>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="B190" s="5" t="inlineStr">
         <is>
-          <t>LV @ LAC</t>
+          <t>DET @ BUF</t>
         </is>
       </c>
       <c r="C190" s="5" t="inlineStr">
@@ -10396,14 +10396,14 @@
       </c>
       <c r="D190" s="5" t="inlineStr">
         <is>
-          <t>Over 42.5</t>
+          <t>Over 52.5</t>
         </is>
       </c>
       <c r="E190" s="12" t="n">
         <v>-110</v>
       </c>
       <c r="F190" s="13" t="n">
-        <v>0.4371</v>
+        <v>0.437</v>
       </c>
       <c r="G190" s="13" t="n">
         <v>0.5238</v>
@@ -10412,7 +10412,7 @@
         <v>-0.0505</v>
       </c>
       <c r="I190" s="13" t="n">
-        <v>-0.1656160106928967</v>
+        <v>-0.1656336429379587</v>
       </c>
       <c r="J190" s="15" t="n">
         <v>0.5</v>
@@ -10427,24 +10427,24 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>ARI @ LAC</t>
+          <t>LV @ LAC</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>LAC -10.5</t>
+          <t>Over 42.5</t>
         </is>
       </c>
       <c r="E191" s="7" t="n">
         <v>-110</v>
       </c>
       <c r="F191" s="8" t="n">
-        <v>0.4343</v>
+        <v>0.4346</v>
       </c>
       <c r="G191" s="8" t="n">
         <v>0.5238</v>
@@ -10453,7 +10453,7 @@
         <v>-0.0509</v>
       </c>
       <c r="I191" s="8" t="n">
-        <v>-0.1708893131526678</v>
+        <v>-0.1703213044824221</v>
       </c>
       <c r="J191" s="10" t="n">
         <v>0.5</v>
@@ -10514,28 +10514,28 @@
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>Over 46.5</t>
+          <t>LAC -10.5</t>
         </is>
       </c>
       <c r="E193" s="7" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="F193" s="8" t="n">
-        <v>0.4433</v>
+        <v>0.4327</v>
       </c>
       <c r="G193" s="8" t="n">
-        <v>0.5349</v>
+        <v>0.5238</v>
       </c>
       <c r="H193" s="8" t="n">
-        <v>-0.0512</v>
+        <v>-0.0511</v>
       </c>
       <c r="I193" s="8" t="n">
-        <v>-0.1711965832950857</v>
+        <v>-0.1740261183876243</v>
       </c>
       <c r="J193" s="10" t="n">
         <v>0.5</v>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="B194" s="5" t="inlineStr">
         <is>
-          <t>TB @ CIN</t>
+          <t>ARI @ LAC</t>
         </is>
       </c>
       <c r="C194" s="5" t="inlineStr">
@@ -10560,23 +10560,23 @@
       </c>
       <c r="D194" s="5" t="inlineStr">
         <is>
-          <t>Over 50.5</t>
+          <t>Over 46.5</t>
         </is>
       </c>
       <c r="E194" s="12" t="n">
-        <v>-118</v>
+        <v>-115</v>
       </c>
       <c r="F194" s="13" t="n">
-        <v>0.4481</v>
+        <v>0.4433</v>
       </c>
       <c r="G194" s="13" t="n">
-        <v>0.5413</v>
+        <v>0.5349</v>
       </c>
       <c r="H194" s="13" t="n">
-        <v>-0.0514</v>
+        <v>-0.0512</v>
       </c>
       <c r="I194" s="13" t="n">
-        <v>-0.1722019609684052</v>
+        <v>-0.1711965832950857</v>
       </c>
       <c r="J194" s="15" t="n">
         <v>0.5</v>
@@ -10673,38 +10673,42 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>SF @ LAR</t>
+          <t>SEA @ ARI</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>Over 48.5</t>
+          <t>SEA ML</t>
         </is>
       </c>
       <c r="E197" s="7" t="n">
-        <v>-105</v>
+        <v>-535</v>
       </c>
       <c r="F197" s="8" t="n">
-        <v>0.4089</v>
+        <v>0.7407</v>
       </c>
       <c r="G197" s="8" t="n">
-        <v>0.5122</v>
+        <v>0.8425</v>
       </c>
       <c r="H197" s="8" t="n">
-        <v>-0.0525</v>
+        <v>-0.0524</v>
       </c>
       <c r="I197" s="8" t="n">
-        <v>-0.2016493735659793</v>
+        <v>-0.1199405621712683</v>
       </c>
       <c r="J197" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="K197" s="4" t="inlineStr"/>
+      <c r="K197" s="4" t="inlineStr">
+        <is>
+          <t>price -535 outside the allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="5" t="inlineStr">
@@ -10714,42 +10718,38 @@
       </c>
       <c r="B198" s="5" t="inlineStr">
         <is>
-          <t>MIA @ SF</t>
+          <t>SF @ LAR</t>
         </is>
       </c>
       <c r="C198" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D198" s="5" t="inlineStr">
         <is>
-          <t>SF ML</t>
+          <t>Over 48.5</t>
         </is>
       </c>
       <c r="E198" s="12" t="n">
-        <v>-675</v>
+        <v>-105</v>
       </c>
       <c r="F198" s="13" t="n">
-        <v>0.7662</v>
+        <v>0.4089</v>
       </c>
       <c r="G198" s="13" t="n">
-        <v>0.871</v>
+        <v>0.5122</v>
       </c>
       <c r="H198" s="13" t="n">
-        <v>-0.0526</v>
+        <v>-0.0525</v>
       </c>
       <c r="I198" s="13" t="n">
-        <v>-0.1193978309219639</v>
+        <v>-0.2016493735659793</v>
       </c>
       <c r="J198" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="K198" s="5" t="inlineStr">
-        <is>
-          <t>price -675 outside the allowed range</t>
-        </is>
-      </c>
+      <c r="K198" s="5" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
@@ -10764,33 +10764,37 @@
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>SF -10.5</t>
+          <t>SF ML</t>
         </is>
       </c>
       <c r="E199" s="7" t="n">
-        <v>-110</v>
+        <v>-675</v>
       </c>
       <c r="F199" s="8" t="n">
-        <v>0.4191</v>
+        <v>0.7662</v>
       </c>
       <c r="G199" s="8" t="n">
-        <v>0.5238</v>
+        <v>0.871</v>
       </c>
       <c r="H199" s="8" t="n">
         <v>-0.0526</v>
       </c>
       <c r="I199" s="8" t="n">
-        <v>-0.1998928619335059</v>
+        <v>-0.1193978309219639</v>
       </c>
       <c r="J199" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="K199" s="4" t="inlineStr"/>
+      <c r="K199" s="4" t="inlineStr">
+        <is>
+          <t>price -675 outside the allowed range</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="5" t="inlineStr">
@@ -10800,42 +10804,38 @@
       </c>
       <c r="B200" s="5" t="inlineStr">
         <is>
-          <t>SEA @ ARI</t>
+          <t>MIA @ SF</t>
         </is>
       </c>
       <c r="C200" s="5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D200" s="5" t="inlineStr">
         <is>
-          <t>SEA ML</t>
+          <t>SF -10.5</t>
         </is>
       </c>
       <c r="E200" s="12" t="n">
-        <v>-550</v>
+        <v>-110</v>
       </c>
       <c r="F200" s="13" t="n">
-        <v>0.742</v>
+        <v>0.4191</v>
       </c>
       <c r="G200" s="13" t="n">
-        <v>0.8462</v>
+        <v>0.5238</v>
       </c>
       <c r="H200" s="13" t="n">
         <v>-0.0526</v>
       </c>
       <c r="I200" s="13" t="n">
-        <v>-0.122164368839268</v>
+        <v>-0.1998928619335059</v>
       </c>
       <c r="J200" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="K200" s="5" t="inlineStr">
-        <is>
-          <t>price -550 outside the allowed range</t>
-        </is>
-      </c>
+      <c r="K200" s="5" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
@@ -11830,7 +11830,7 @@
         </is>
       </c>
       <c r="D9" s="14" t="n">
-        <v>7.96</v>
+        <v>7.91</v>
       </c>
       <c r="E9" s="14" t="n">
         <v>-8.5</v>
@@ -12000,7 +12000,7 @@
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="E14" s="9" t="n">
         <v>-2.5</v>
@@ -12034,13 +12034,13 @@
         </is>
       </c>
       <c r="D15" s="14" t="n">
-        <v>7.57</v>
+        <v>7.52</v>
       </c>
       <c r="E15" s="14" t="n">
         <v>-8.5</v>
       </c>
       <c r="F15" s="16" t="n">
-        <v>40</v>
+        <v>39.9</v>
       </c>
       <c r="G15" s="16" t="n">
         <v>42.5</v>
@@ -12136,7 +12136,7 @@
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>6.36</v>
+        <v>6.37</v>
       </c>
       <c r="E18" s="9" t="n">
         <v>-5.5</v>
@@ -12340,7 +12340,7 @@
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>3.94</v>
+        <v>3.98</v>
       </c>
       <c r="E24" s="9" t="n">
         <v>-3</v>
@@ -12374,7 +12374,7 @@
         </is>
       </c>
       <c r="D25" s="14" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="E25" s="14" t="n">
         <v>-3</v>
@@ -12408,7 +12408,7 @@
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>-1.58</v>
+        <v>-1.53</v>
       </c>
       <c r="E26" s="9" t="n">
         <v>2.5</v>
@@ -12442,7 +12442,7 @@
         </is>
       </c>
       <c r="D27" s="14" t="n">
-        <v>9.41</v>
+        <v>9.32</v>
       </c>
       <c r="E27" s="14" t="n">
         <v>-10.5</v>
@@ -12748,7 +12748,7 @@
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>7.47</v>
+        <v>7.44</v>
       </c>
       <c r="E36" s="9" t="n">
         <v>-7</v>
@@ -12822,7 +12822,7 @@
         <v>-3.5</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>48.2</v>
+        <v>48.6</v>
       </c>
       <c r="G38" s="11" t="n">
         <v>50.5</v>
@@ -12884,7 +12884,7 @@
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="E40" s="9" t="n">
         <v>-3.5</v>
@@ -13949,7 +13949,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="18" t="n">
-        <v>3.81</v>
+        <v>3.82</v>
       </c>
       <c r="E5" s="18" t="n">
         <v>2.9</v>
@@ -13981,7 +13981,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="20" t="n">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
       <c r="E6" s="20" t="n">
         <v>2.35</v>
@@ -14301,7 +14301,7 @@
         <v>0</v>
       </c>
       <c r="D16" s="20" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="E16" s="20" t="n">
         <v>0.64</v>
@@ -14365,7 +14365,7 @@
         <v>0</v>
       </c>
       <c r="D18" s="20" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="E18" s="20" t="n">
         <v>-0.24</v>
@@ -14397,7 +14397,7 @@
         <v>0</v>
       </c>
       <c r="D19" s="18" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="E19" s="18" t="n">
         <v>0.71</v>
@@ -14429,7 +14429,7 @@
         <v>0</v>
       </c>
       <c r="D20" s="20" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="E20" s="20" t="n">
         <v>0.93</v>
@@ -18934,10 +18934,10 @@
         <v>44.5</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>-550</v>
+        <v>-535</v>
       </c>
       <c r="J82" s="12" t="n">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="K82" s="19" t="n">
         <v>0</v>
@@ -19517,10 +19517,10 @@
         <v>46.5</v>
       </c>
       <c r="I93" s="7" t="n">
-        <v>-192</v>
+        <v>-185</v>
       </c>
       <c r="J93" s="7" t="n">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="K93" s="17" t="n">
         <v>0</v>
@@ -19833,10 +19833,10 @@
         <v>42.5</v>
       </c>
       <c r="I99" s="7" t="n">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="J99" s="7" t="n">
-        <v>-185</v>
+        <v>-192</v>
       </c>
       <c r="K99" s="17" t="n">
         <v>0</v>
@@ -21629,7 +21629,7 @@
         </is>
       </c>
       <c r="G133" s="9" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="H133" s="11" t="n">
         <v>43.5</v>
@@ -25186,10 +25186,10 @@
         <v>43.5</v>
       </c>
       <c r="I200" s="12" t="n">
-        <v>-305</v>
+        <v>-310</v>
       </c>
       <c r="J200" s="12" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="K200" s="19" t="n">
         <v>0</v>
@@ -27995,10 +27995,10 @@
         <v>43.5</v>
       </c>
       <c r="I253" s="7" t="n">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="J253" s="7" t="n">
-        <v>-142</v>
+        <v>-135</v>
       </c>
       <c r="K253" s="17" t="n">
         <v>0</v>
@@ -28313,10 +28313,10 @@
         <v>45.5</v>
       </c>
       <c r="I259" s="7" t="n">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="J259" s="7" t="n">
-        <v>-410</v>
+        <v>-395</v>
       </c>
       <c r="K259" s="17" t="n">
         <v>0</v>
@@ -28631,10 +28631,10 @@
         <v>46.5</v>
       </c>
       <c r="I265" s="7" t="n">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="J265" s="7" t="n">
-        <v>-185</v>
+        <v>-180</v>
       </c>
       <c r="K265" s="17" t="n">
         <v>0</v>
@@ -31705,10 +31705,10 @@
         <v>44.5</v>
       </c>
       <c r="I323" s="7" t="n">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="J323" s="7" t="n">
-        <v>-162</v>
+        <v>-155</v>
       </c>
       <c r="K323" s="17" t="n">
         <v>0</v>
@@ -31758,10 +31758,10 @@
         <v>43.5</v>
       </c>
       <c r="I324" s="12" t="n">
-        <v>-122</v>
+        <v>-125</v>
       </c>
       <c r="J324" s="12" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="K324" s="19" t="n">
         <v>0</v>
@@ -32476,17 +32476,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Josh Minkins</t>
+          <t>Zachary Carter</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -32496,7 +32496,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Minkins (undisclosed) reverted to the Cardinals' injured reserve Monday, per the NFL's transaction log.</t>
+          <t>The Cardinals placed Carter (knee) on injured reserve Sunday with a designation to return, Darren Urban of the team's official site reports.</t>
         </is>
       </c>
     </row>
@@ -32508,27 +32508,27 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Zachary Carter</t>
+          <t>Will Johnson</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Lower Body</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>The Cardinals placed Carter (knee) on injured reserve Sunday with a designation to return, Darren Urban of the team's official site reports.</t>
+          <t>Head coach Mike LaFleur said Monday that Johnson is working through a lower-body injury, Bo Brack of GoPHNX.com reports.</t>
         </is>
       </c>
     </row>
@@ -32540,27 +32540,27 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Will Johnson</t>
+          <t>Carson Beck</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Lower Body</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Head coach Mike LaFleur said Monday that Johnson is working through a lower-body injury, Bo Brack of GoPHNX.com reports.</t>
+          <t>Coach Mike LaFleur said Beck (ribs) will return to practice Monday, Josh Weinfuss of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -32572,27 +32572,27 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Carson Beck</t>
+          <t>Tip Reiman</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Coach Mike LaFleur said Beck (ribs) will return to practice Monday, Josh Weinfuss of ESPN.com reports.</t>
+          <t>The Cardinals moved Reiman (ankle) from the active/PUP list to the reserve/PUP list Sunday, Darren Urban of the team's official site reports.</t>
         </is>
       </c>
     </row>
@@ -32604,17 +32604,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Tip Reiman</t>
+          <t>James Conner</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Out</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -32624,7 +32624,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>The Cardinals moved Reiman (ankle) from the active/PUP list to the reserve/PUP list Sunday, Darren Urban of the team's official site reports.</t>
+          <t>The Cardinals are placing Conner (foot) on injured reserve with a designation to return, John Gambadoro of Arizona Sports 98.7 FM Phoenix reports.</t>
         </is>
       </c>
     </row>
@@ -32636,27 +32636,27 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>James Conner</t>
+          <t>Hunter Long</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>The Cardinals are placing Conner (foot) on injured reserve with a designation to return, John Gambadoro of Arizona Sports 98.7 FM Phoenix reports.</t>
+          <t>Long has been traded from Jacksonville to the Cardinals, Ian Rapoport of NFL Network reports.</t>
         </is>
       </c>
     </row>
@@ -32668,12 +32668,12 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Hunter Long</t>
+          <t>Reggie Virgil</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -32688,7 +32688,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Long has been traded from Jacksonville to the Cardinals, Ian Rapoport of NFL Network reports.</t>
+          <t>Virgil caught three of six targets for 23 yards in a loss to Green Bay during Friday's exhibition contest.</t>
         </is>
       </c>
     </row>
@@ -32700,7 +32700,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Reggie Virgil</t>
+          <t>Jalen Brooks</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -32720,7 +32720,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Virgil caught three of six targets for 23 yards in a loss to Green Bay during Friday's exhibition contest.</t>
+          <t>Brooks caught all four of his targets for 57 yards during Friday's exhibition loss to Green Bay.</t>
         </is>
       </c>
     </row>
@@ -32732,12 +32732,12 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Jalen Brooks</t>
+          <t>Elijah Higgins</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -32752,7 +32752,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Brooks caught all four of his targets for 57 yards during Friday's exhibition loss to Green Bay.</t>
+          <t>Higgins (concussion) caught two passes on three targets for 15 yards during Friday's 42-38 preseason loss to Green Bay.</t>
         </is>
       </c>
     </row>
@@ -32764,12 +32764,12 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Elijah Higgins</t>
+          <t>Gardner Minshew II</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -32784,7 +32784,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Higgins (concussion) caught two passes on three targets for 15 yards during Friday's 42-38 preseason loss to Green Bay.</t>
+          <t>Minshew completed seven of nine passes for 126 yards and a touchdown while taking a 10-yard sack during the Cardinals' 42-38 preseason loss to the Packers on Friday.</t>
         </is>
       </c>
     </row>
@@ -32796,12 +32796,12 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Gardner Minshew II</t>
+          <t>Hjalte Froholdt</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -32816,7 +32816,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Minshew completed seven of nine passes for 126 yards and a touchdown while taking a 10-yard sack during the Cardinals' 42-38 preseason loss to the Packers on Friday.</t>
+          <t>Arizona signed Froholdt to a two-year, $20 million contract extension Tuesday, Ian Rapoport of ESPN and NFL Network reports.</t>
         </is>
       </c>
     </row>
@@ -32828,27 +32828,27 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Hjalte Froholdt</t>
+          <t>Trey Benson</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Arizona signed Froholdt to a two-year, $20 million contract extension Tuesday, Ian Rapoport of ESPN and NFL Network reports.</t>
+          <t>Benson (knee) reverted to the Cardinals' injured reserve list Tuesday, David Furones of the South Florida Sun Sentinel reports.</t>
         </is>
       </c>
     </row>
@@ -32860,27 +32860,27 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Trey Benson</t>
+          <t>Josh Sweat</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Benson (knee) reverted to the Cardinals' injured reserve list Tuesday, David Furones of the South Florida Sun Sentinel reports.</t>
+          <t>Sweat (knee) was activated from the active/PUP list Monday, Darren Urban of the Cardinals' official site reports.</t>
         </is>
       </c>
     </row>
@@ -32892,12 +32892,12 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Josh Sweat</t>
+          <t>Chad Ryland</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -32912,7 +32912,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Sweat (knee) was activated from the active/PUP list Monday, Darren Urban of the Cardinals' official site reports.</t>
+          <t>Ryland made field goals of 38 and 31 yards, missed a 62-yarder wide right and knocked through his only extra-point try in the Cardinals' 34-13 preseason loss to the Cowboys on Saturday.</t>
         </is>
       </c>
     </row>
@@ -32924,27 +32924,27 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Chad Ryland</t>
+          <t>Dadrion Taylor-Demerson</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Ryland made field goals of 38 and 31 yards, missed a 62-yarder wide right and knocked through his only extra-point try in the Cardinals' 34-13 preseason loss to the Cowboys on Saturday.</t>
+          <t>Taylor-Demerson is questionable to return to Saturday's preseason game against the Cowboys due to a rib injury.</t>
         </is>
       </c>
     </row>
@@ -32956,12 +32956,12 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Dadrion Taylor-Demerson</t>
+          <t>Blake Gillikin</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -32976,7 +32976,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Taylor-Demerson is questionable to return to Saturday's preseason game against the Cowboys due to a rib injury.</t>
+          <t>Gillikin sustained a groin injury during pregame warmups and is questionable to play in Saturday's preseason game against the Cowboys, Darren Urban of the Cardinals' official site reports.</t>
         </is>
       </c>
     </row>
@@ -32988,27 +32988,27 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Blake Gillikin</t>
+          <t>Garrett Williams</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Gillikin sustained a groin injury during pregame warmups and is questionable to play in Saturday's preseason game against the Cowboys, Darren Urban of the Cardinals' official site reports.</t>
+          <t>Williams (Achilles) was activated from the PUP list by the Cardinals on Thursday, Darren Urban of the Cardinals' official site reports.</t>
         </is>
       </c>
     </row>
@@ -33020,12 +33020,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Garrett Williams</t>
+          <t>Jacoby Brissett</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -33040,7 +33040,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Williams (Achilles) was activated from the PUP list by the Cardinals on Thursday, Darren Urban of the Cardinals' official site reports.</t>
+          <t>Coach Mike LaFleur said Thursday that Brissett won't suit up for Saturday's preseason game against the Cowboys, Josh Weinfuss of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -33052,12 +33052,12 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Jacoby Brissett</t>
+          <t>Valentin Senn</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>OT</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -33070,11 +33070,7 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>Coach Mike LaFleur said Thursday that Brissett won't suit up for Saturday's preseason game against the Cowboys, Josh Weinfuss of ESPN.com reports.</t>
-        </is>
-      </c>
+      <c r="F24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -33084,25 +33080,29 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Valentin Senn</t>
+          <t>Chase Bisontis</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>OT</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr"/>
+          <t>Surgery</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>ir</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -33112,12 +33112,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Chase Bisontis</t>
+          <t>Joey Blount</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -33127,7 +33127,7 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Surgery</t>
+          <t>Stinger</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
@@ -33144,12 +33144,12 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Joey Blount</t>
+          <t>Jameson Geers</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -33159,7 +33159,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Stinger</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -33176,27 +33176,27 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Jameson Geers</t>
+          <t>Tyler Allgeier</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>ir</t>
+          <t>Allgeier could open the regular season as the Cardinals' primary running back, as Adam Schefter of ESPN reports that Jeremiyah Love sustained a high-ankle sprain in Thursday's preseason win over the Raiders.</t>
         </is>
       </c>
     </row>
@@ -33208,12 +33208,12 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Tyler Allgeier</t>
+          <t>Trey McBride</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -33228,7 +33228,7 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Allgeier could open the regular season as the Cardinals' primary running back, as Adam Schefter of ESPN reports that Jeremiyah Love sustained a high-ankle sprain in Thursday's preseason win over the Raiders.</t>
+          <t>McBride played one snap in Thursday's 27-14 preseason win over the Raiders.</t>
         </is>
       </c>
     </row>
@@ -36416,27 +36416,27 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>Hayden Large</t>
+          <t>Jack Sanborn</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>The Bears placed Large (undisclosed) on injured reserve Tuesday.</t>
+          <t>Chicago signed Sanborn to the active roster Tuesday.</t>
         </is>
       </c>
     </row>
@@ -36448,12 +36448,12 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Coby Bryant</t>
+          <t>Hayden Large</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>Surgery</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>The Bears placed Bryant (knee) on injured reserve Tuesday.</t>
+          <t>The Bears placed Large (undisclosed) on injured reserve Tuesday.</t>
         </is>
       </c>
     </row>
@@ -36480,27 +36480,27 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>Luther Burden III</t>
+          <t>Coby Bryant</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Surgery</t>
         </is>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>Coach Ben Johnson said Burden (groin) will participate in Tuesday's practice, Zack Pearson of BearReport reports.</t>
+          <t>The Bears placed Bryant (knee) on injured reserve Tuesday.</t>
         </is>
       </c>
     </row>
@@ -36512,12 +36512,12 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Kyle Monangai</t>
+          <t>Luther Burden III</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
@@ -36532,7 +36532,7 @@
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>Coach Ben Johnson said Tuesday that Monangai is "week-to-week" due to the right knee injury that he sustained in practice back on Sunday, Aug. 16, Chris Emma of 670TheScore.com reports.</t>
+          <t>Coach Ben Johnson said Burden (groin) will participate in Tuesday's practice, Zack Pearson of BearReport reports.</t>
         </is>
       </c>
     </row>
@@ -36544,7 +36544,7 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>Kyle Monangai</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
@@ -36554,17 +36554,17 @@
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>Coach Ben Johnson believes Swift is "primed for a big year" in 2026, Dan Wiederer of The Athletic reports.</t>
+          <t>Coach Ben Johnson said Tuesday that Monangai is "week-to-week" due to the right knee injury that he sustained in practice back on Sunday, Aug. 16, Chris Emma of 670TheScore.com reports.</t>
         </is>
       </c>
     </row>
@@ -36576,27 +36576,27 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Dontae Manning</t>
+          <t>D'Andre Swift</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>Manning (undisclosed) reverted to the Bears' injured reserve Monday, per the NFL's transaction log.</t>
+          <t>Coach Ben Johnson believes Swift is "primed for a big year" in 2026, Dan Wiederer of The Athletic reports.</t>
         </is>
       </c>
     </row>
@@ -36608,12 +36608,12 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>Ruben Hyppolite II</t>
+          <t>Dontae Manning</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
@@ -36628,7 +36628,7 @@
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>Hyppolite (shoulder) reverted to Chicago's injured reserve Monday, per the NFL's transaction log.</t>
+          <t>Manning (undisclosed) reverted to the Bears' injured reserve Monday, per the NFL's transaction log.</t>
         </is>
       </c>
     </row>
@@ -36640,12 +36640,12 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Beanie Bishop Jr.</t>
+          <t>Ruben Hyppolite II</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
@@ -36660,7 +36660,7 @@
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>Bishop (suspension) reverted to the Bear's injured reserve Monday, per the NFL's transaction log.</t>
+          <t>Hyppolite (shoulder) reverted to Chicago's injured reserve Monday, per the NFL's transaction log.</t>
         </is>
       </c>
     </row>
@@ -36672,12 +36672,12 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>Tony Fields II</t>
+          <t>Beanie Bishop Jr.</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
@@ -36692,7 +36692,7 @@
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>The Bears placed Fields (undisclosed) on injured reserve Sunday with a designation to return.</t>
+          <t>Bishop (suspension) reverted to the Bear's injured reserve Monday, per the NFL's transaction log.</t>
         </is>
       </c>
     </row>
@@ -36704,7 +36704,7 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Noah Sewell</t>
+          <t>Tony Fields II</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
@@ -36714,17 +36714,17 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Out</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>Ruptured</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>Sewell (Achilles) was moved to the reserve/PUP list by the Bears on Sunday.</t>
+          <t>The Bears placed Fields (undisclosed) on injured reserve Sunday with a designation to return.</t>
         </is>
       </c>
     </row>
@@ -36736,12 +36736,12 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>Shemar Turner</t>
+          <t>Noah Sewell</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
@@ -36751,12 +36751,12 @@
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>Surgery</t>
+          <t>Ruptured</t>
         </is>
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>Turner (knee) was moved to the reserve/PUP list by the Bears on Sunday.</t>
+          <t>Sewell (Achilles) was moved to the reserve/PUP list by the Bears on Sunday.</t>
         </is>
       </c>
     </row>
@@ -36768,12 +36768,12 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Kyler Gordon</t>
+          <t>Shemar Turner</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
@@ -36783,12 +36783,12 @@
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Surgery</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>Gordon (calf) was moved to the reserve/PUP list by the Bears on Sunday.</t>
+          <t>Turner (knee) was moved to the reserve/PUP list by the Bears on Sunday.</t>
         </is>
       </c>
     </row>
@@ -36800,17 +36800,17 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>Brittain Brown</t>
+          <t>Kyler Gordon</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
@@ -36820,7 +36820,7 @@
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>Brown (undisclosed) was placed on injured reserve by the Bears on Sunday.</t>
+          <t>Gordon (calf) was moved to the reserve/PUP list by the Bears on Sunday.</t>
         </is>
       </c>
     </row>
@@ -36832,12 +36832,12 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Ray-Ray McCloud III</t>
+          <t>Brittain Brown</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
@@ -36852,7 +36852,7 @@
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>McCloud (undisclosed) was placed on injured reserve by the Bears on Sunday.</t>
+          <t>Brown (undisclosed) was placed on injured reserve by the Bears on Sunday.</t>
         </is>
       </c>
     </row>
@@ -36864,27 +36864,27 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>Clark Phillips III</t>
+          <t>Ray-Ray McCloud III</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>Phillips (triceps/illness) was traded to the Bears from the Falcons on Sunday, Ian Rapoport of ESPN and NFL Network reports.</t>
+          <t>McCloud (undisclosed) was placed on injured reserve by the Bears on Sunday.</t>
         </is>
       </c>
     </row>
@@ -36896,12 +36896,12 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Jahdae Walker</t>
+          <t>Clark Phillips III</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
@@ -36916,7 +36916,7 @@
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>Walker brought in his only target for 12 yards in the Bears' 24-15 preseason win over the Titans on Saturday.</t>
+          <t>Phillips (triceps/illness) was traded to the Bears from the Falcons on Sunday, Ian Rapoport of ESPN and NFL Network reports.</t>
         </is>
       </c>
     </row>
@@ -36928,12 +36928,12 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>Sam Roush</t>
+          <t>Jahdae Walker</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
@@ -36948,7 +36948,7 @@
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
-          <t>Roush brought in one of two targets for 19 yards in the Bears' 24-15 preseason win over the Titans on Saturday.</t>
+          <t>Walker brought in his only target for 12 yards in the Bears' 24-15 preseason win over the Titans on Saturday.</t>
         </is>
       </c>
     </row>
@@ -36960,12 +36960,12 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>Zavion Thomas</t>
+          <t>Sam Roush</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
@@ -36980,7 +36980,7 @@
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>Thomas secured all five targets for 140 yards and a touchdown, ran back one kickoff for 22 yards and returned one punt for 39 yards in the Bears' 24-15 preseason win over the Titans on Saturday.</t>
+          <t>Roush brought in one of two targets for 19 yards in the Bears' 24-15 preseason win over the Titans on Saturday.</t>
         </is>
       </c>
     </row>
@@ -36992,12 +36992,12 @@
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>Tyson Bagent</t>
+          <t>Zavion Thomas</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
@@ -37012,7 +37012,7 @@
       </c>
       <c r="F148" s="5" t="inlineStr">
         <is>
-          <t>Bagent completed 16 of 17 passes for 208 yards with two touchdowns and no interceptions and rushed twice for 21 yards in the Bears' 24-15 preseason win over the Titans on Saturday. He also lost a fumble.</t>
+          <t>Thomas secured all five targets for 140 yards and a touchdown, ran back one kickoff for 22 yards and returned one punt for 39 yards in the Bears' 24-15 preseason win over the Titans on Saturday.</t>
         </is>
       </c>
     </row>
@@ -37024,27 +37024,27 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>Jaylon Johnson</t>
+          <t>Tyson Bagent</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>Johnson is dealing with an arm injury, Patrick Finley of the Chicago Sun-Times reports.</t>
+          <t>Bagent completed 16 of 17 passes for 208 yards with two touchdowns and no interceptions and rushed twice for 21 yards in the Bears' 24-15 preseason win over the Titans on Saturday. He also lost a fumble.</t>
         </is>
       </c>
     </row>
@@ -37056,12 +37056,12 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>Austin Booker</t>
+          <t>Jaylon Johnson</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
@@ -37076,7 +37076,7 @@
       </c>
       <c r="F150" s="5" t="inlineStr">
         <is>
-          <t>Booker has a groin injury and his status is "week-to-week," Brad Biggs of the Chicago Tribune reports.</t>
+          <t>Johnson is dealing with an arm injury, Patrick Finley of the Chicago Sun-Times reports.</t>
         </is>
       </c>
     </row>
@@ -37088,27 +37088,27 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>Nephi Sewell</t>
+          <t>Austin Booker</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>Concussion</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>The Bears placed Sewell (concussion) on injured reserve Tuesday.</t>
+          <t>Booker has a groin injury and his status is "week-to-week," Brad Biggs of the Chicago Tribune reports.</t>
         </is>
       </c>
     </row>
@@ -37120,7 +37120,7 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>Keyshaun Elliott</t>
+          <t>Nephi Sewell</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
@@ -37130,17 +37130,17 @@
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Concussion</t>
         </is>
       </c>
       <c r="F152" s="5" t="inlineStr">
         <is>
-          <t>The Bears activated Elliott (undisclosed) from the active/PUP list Tuesday.</t>
+          <t>The Bears placed Sewell (concussion) on injured reserve Tuesday.</t>
         </is>
       </c>
     </row>
@@ -37152,12 +37152,12 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Elijah Hicks</t>
+          <t>Keyshaun Elliott</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
@@ -37172,7 +37172,7 @@
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>The Bears activated Hicks (shin) from the active/PUP list Tuesday.</t>
+          <t>The Bears activated Elliott (undisclosed) from the active/PUP list Tuesday.</t>
         </is>
       </c>
     </row>
@@ -37184,27 +37184,27 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>Kalif Raymond</t>
+          <t>Elijah Hicks</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F154" s="5" t="inlineStr">
         <is>
-          <t>Raymond has made a strong impression in his first five months with Chicago, with Kevin Fishbain of The Athletic relaying coach Ben Johnson's praise Monday and calling him "the most selfless player I've ever been around."</t>
+          <t>The Bears activated Hicks (shin) from the active/PUP list Tuesday.</t>
         </is>
       </c>
     </row>
@@ -39096,12 +39096,12 @@
       </c>
       <c r="B214" s="5" t="inlineStr">
         <is>
-          <t>Anthony Smith</t>
+          <t>Brandon Aubrey</t>
         </is>
       </c>
       <c r="C214" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="D214" s="5" t="inlineStr">
@@ -39116,7 +39116,7 @@
       </c>
       <c r="F214" s="5" t="inlineStr">
         <is>
-          <t>Smith caught three of his four targets for 19 yards during the Cowboys' preseason game Friday versus the Saints.</t>
+          <t>Aubrey made three of four field-goal attempts and converted his lone PAT try in Friday's 27-24 preseason loss to the Saints.</t>
         </is>
       </c>
     </row>
@@ -39128,27 +39128,27 @@
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>Brandon Aubrey</t>
+          <t>Kelvin Gilliam Jr.</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="D215" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E215" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F215" s="4" t="inlineStr">
         <is>
-          <t>Aubrey made three of four field-goal attempts and converted his lone PAT try in Friday's 27-24 preseason loss to the Saints.</t>
+          <t>Gilliam (triceps) reverted to Dallas' injured reserve Tuesday, Tommy Yarrish of the team's official site reports.</t>
         </is>
       </c>
     </row>
@@ -39160,27 +39160,27 @@
       </c>
       <c r="B216" s="5" t="inlineStr">
         <is>
-          <t>Kelvin Gilliam Jr.</t>
+          <t>Tyler Guyton</t>
         </is>
       </c>
       <c r="C216" s="5" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>OT</t>
         </is>
       </c>
       <c r="D216" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E216" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Soreness</t>
         </is>
       </c>
       <c r="F216" s="5" t="inlineStr">
         <is>
-          <t>Gilliam (triceps) reverted to Dallas' injured reserve Tuesday, Tommy Yarrish of the team's official site reports.</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -39192,12 +39192,12 @@
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>Mitch Van Vooren</t>
+          <t>Jalen Thompson</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D217" s="4" t="inlineStr">
@@ -39210,11 +39210,7 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F217" s="4" t="inlineStr">
-        <is>
-          <t>Van Vooren signed with the Cowboys on Monday, Nick Harris of the Fort Worth Star-Telegram reports.</t>
-        </is>
-      </c>
+      <c r="F217" s="4" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="5" t="inlineStr">
@@ -39224,12 +39220,12 @@
       </c>
       <c r="B218" s="5" t="inlineStr">
         <is>
-          <t>Tyler Guyton</t>
+          <t>Jonathan Bullard</t>
         </is>
       </c>
       <c r="C218" s="5" t="inlineStr">
         <is>
-          <t>OT</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="D218" s="5" t="inlineStr">
@@ -39256,25 +39252,29 @@
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>Jalen Thompson</t>
+          <t>Princeton Fant</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D219" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E219" s="4" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="F219" s="4" t="inlineStr"/>
+          <t>Surgery</t>
+        </is>
+      </c>
+      <c r="F219" s="4" t="inlineStr">
+        <is>
+          <t>ir</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="5" t="inlineStr">
@@ -39284,29 +39284,25 @@
       </c>
       <c r="B220" s="5" t="inlineStr">
         <is>
-          <t>Jonathan Bullard</t>
+          <t>Ajani Cornelius</t>
         </is>
       </c>
       <c r="C220" s="5" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>OT</t>
         </is>
       </c>
       <c r="D220" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E220" s="5" t="inlineStr">
         <is>
-          <t>Soreness</t>
-        </is>
-      </c>
-      <c r="F220" s="5" t="inlineStr">
-        <is>
-          <t>questionable</t>
-        </is>
-      </c>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F220" s="5" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="4" t="inlineStr">
@@ -39316,29 +39312,25 @@
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>Princeton Fant</t>
+          <t>P.J. Locke</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D221" s="4" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E221" s="4" t="inlineStr">
         <is>
-          <t>Surgery</t>
-        </is>
-      </c>
-      <c r="F221" s="4" t="inlineStr">
-        <is>
-          <t>ir</t>
-        </is>
-      </c>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F221" s="4" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="5" t="inlineStr">
@@ -39348,12 +39340,12 @@
       </c>
       <c r="B222" s="5" t="inlineStr">
         <is>
-          <t>Ajani Cornelius</t>
+          <t>James Houston</t>
         </is>
       </c>
       <c r="C222" s="5" t="inlineStr">
         <is>
-          <t>OT</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D222" s="5" t="inlineStr">
@@ -39376,12 +39368,12 @@
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>P.J. Locke</t>
+          <t>DeMarvion Overshown</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D223" s="4" t="inlineStr">
@@ -39394,7 +39386,11 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F223" s="4" t="inlineStr"/>
+      <c r="F223" s="4" t="inlineStr">
+        <is>
+          <t>Overshown (lower body) participated at the Cowboys' training camp practice Monday, Todd Archer of ESPN.com reports.</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="5" t="inlineStr">
@@ -39404,7 +39400,7 @@
       </c>
       <c r="B224" s="5" t="inlineStr">
         <is>
-          <t>James Houston</t>
+          <t>Jaishawn Barham</t>
         </is>
       </c>
       <c r="C224" s="5" t="inlineStr">
@@ -39422,7 +39418,11 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F224" s="5" t="inlineStr"/>
+      <c r="F224" s="5" t="inlineStr">
+        <is>
+          <t>Barham (groin) returned to practice Monday, Todd Archer of ESPN.com reports.</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="4" t="inlineStr">
@@ -39432,7 +39432,7 @@
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>DeMarvion Overshown</t>
+          <t>Von Miller</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr">
@@ -39452,7 +39452,7 @@
       </c>
       <c r="F225" s="4" t="inlineStr">
         <is>
-          <t>Overshown (lower body) participated at the Cowboys' training camp practice Monday, Todd Archer of ESPN.com reports.</t>
+          <t>Miller is not expected to practice with the Cowboys this week, Calvin Watkins of The Dallas Morning News reports.</t>
         </is>
       </c>
     </row>
@@ -39464,12 +39464,12 @@
       </c>
       <c r="B226" s="5" t="inlineStr">
         <is>
-          <t>Jaishawn Barham</t>
+          <t>Alijah Clark</t>
         </is>
       </c>
       <c r="C226" s="5" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D226" s="5" t="inlineStr">
@@ -39484,7 +39484,7 @@
       </c>
       <c r="F226" s="5" t="inlineStr">
         <is>
-          <t>Barham (groin) returned to practice Monday, Todd Archer of ESPN.com reports.</t>
+          <t>Clark (ankle) recorded one tackle in the Cowboys' 17-7 preseason win over the Seahawks on Saturday.</t>
         </is>
       </c>
     </row>
@@ -39496,12 +39496,12 @@
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>Von Miller</t>
+          <t>Ryan Flournoy</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D227" s="4" t="inlineStr">
@@ -39516,7 +39516,7 @@
       </c>
       <c r="F227" s="4" t="inlineStr">
         <is>
-          <t>Miller is not expected to practice with the Cowboys this week, Calvin Watkins of The Dallas Morning News reports.</t>
+          <t>Flournoy isn't suited up ahead of Saturday's preseason opener versus Seattle, Nick Harris of the Fort Worth Star-Telegram reports.</t>
         </is>
       </c>
     </row>
@@ -39528,12 +39528,12 @@
       </c>
       <c r="B228" s="5" t="inlineStr">
         <is>
-          <t>Alijah Clark</t>
+          <t>Jake Ferguson</t>
         </is>
       </c>
       <c r="C228" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D228" s="5" t="inlineStr">
@@ -39548,7 +39548,7 @@
       </c>
       <c r="F228" s="5" t="inlineStr">
         <is>
-          <t>Clark (ankle) recorded one tackle in the Cowboys' 17-7 preseason win over the Seahawks on Saturday.</t>
+          <t>Ferguson isn't suited up for Saturday's preseason contest against the Seahawks, Nick Harris of the Fort Worth Star-Telegram reports.</t>
         </is>
       </c>
     </row>
@@ -39560,12 +39560,12 @@
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>Ryan Flournoy</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D229" s="4" t="inlineStr">
@@ -39580,7 +39580,7 @@
       </c>
       <c r="F229" s="4" t="inlineStr">
         <is>
-          <t>Flournoy isn't suited up ahead of Saturday's preseason opener versus Seattle, Nick Harris of the Fort Worth Star-Telegram reports.</t>
+          <t>Prescott isn't slated to play in Saturday's preseason matchup versus Seattle, Nick Harris of the Fort Worth Star-Telegram reports.</t>
         </is>
       </c>
     </row>
@@ -40668,7 +40668,7 @@
       </c>
       <c r="B264" s="5" t="inlineStr">
         <is>
-          <t>Luke Altmyer</t>
+          <t>Joshua Dobbs</t>
         </is>
       </c>
       <c r="C264" s="5" t="inlineStr">
@@ -40688,7 +40688,7 @@
       </c>
       <c r="F264" s="5" t="inlineStr">
         <is>
-          <t>Altmyer completed seven of 11 passes for 55 yards and an interception in Saturday's 25-16 preseason win over the Colts. He also gained two yards on two carries and committed two fumbles, losing one.</t>
+          <t>Dobbs completed 15 of 19 passes for 128 yards and two touchdowns in Saturday's 25-16 preseason win over the Colts. He also recorded minus-1 yard on five carries.</t>
         </is>
       </c>
     </row>
@@ -40700,27 +40700,27 @@
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>Joshua Dobbs</t>
+          <t>Seth McLaughlin</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D265" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E265" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Concussion</t>
         </is>
       </c>
       <c r="F265" s="4" t="inlineStr">
         <is>
-          <t>Dobbs completed 15 of 19 passes for 128 yards and two touchdowns in Saturday's 25-16 preseason win over the Colts. He also recorded minus-1 yard on five carries.</t>
+          <t>McLaughlin has been diagnosed with a concussion and is in the league's five-step protocol, Nolan Bianchi of The Detroit News reports.</t>
         </is>
       </c>
     </row>
@@ -40732,27 +40732,27 @@
       </c>
       <c r="B266" s="5" t="inlineStr">
         <is>
-          <t>Seth McLaughlin</t>
+          <t>Sione Vaki</t>
         </is>
       </c>
       <c r="C266" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D266" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E266" s="5" t="inlineStr">
         <is>
-          <t>Concussion</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F266" s="5" t="inlineStr">
         <is>
-          <t>McLaughlin has been diagnosed with a concussion and is in the league's five-step protocol, Nolan Bianchi of The Detroit News reports.</t>
+          <t>Vaki did not play in Saturday's preseason finale against the Colts, Nolan Bianchi of The Detroit News reports.</t>
         </is>
       </c>
     </row>
@@ -40764,27 +40764,27 @@
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>Sione Vaki</t>
+          <t>Derrick Moore</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D267" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E267" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Strain</t>
         </is>
       </c>
       <c r="F267" s="4" t="inlineStr">
         <is>
-          <t>Vaki did not play in Saturday's preseason finale against the Colts, Nolan Bianchi of The Detroit News reports.</t>
+          <t>Moore (groin) might return to practice next week, Nolan Bianchi of The Detroit News reports.</t>
         </is>
       </c>
     </row>
@@ -40796,7 +40796,7 @@
       </c>
       <c r="B268" s="5" t="inlineStr">
         <is>
-          <t>Derrick Moore</t>
+          <t>Payton Turner</t>
         </is>
       </c>
       <c r="C268" s="5" t="inlineStr">
@@ -40806,17 +40806,17 @@
       </c>
       <c r="D268" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E268" s="5" t="inlineStr">
         <is>
-          <t>Strain</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F268" s="5" t="inlineStr">
         <is>
-          <t>Moore (groin) might return to practice next week, Nolan Bianchi of The Detroit News reports.</t>
+          <t>Turner (back) was placed on injured reserve by the Lions on Thursday.</t>
         </is>
       </c>
     </row>
@@ -40828,12 +40828,12 @@
       </c>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>Payton Turner</t>
+          <t>Damone Clark</t>
         </is>
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D269" s="4" t="inlineStr">
@@ -40848,7 +40848,7 @@
       </c>
       <c r="F269" s="4" t="inlineStr">
         <is>
-          <t>Turner (back) was placed on injured reserve by the Lions on Thursday.</t>
+          <t>Detroit placed Clark (undisclosed) on its injured reserve list Tuesday.</t>
         </is>
       </c>
     </row>
@@ -40860,17 +40860,17 @@
       </c>
       <c r="B270" s="5" t="inlineStr">
         <is>
-          <t>Damone Clark</t>
+          <t>Sam LaPorta</t>
         </is>
       </c>
       <c r="C270" s="5" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D270" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E270" s="5" t="inlineStr">
@@ -40880,7 +40880,7 @@
       </c>
       <c r="F270" s="5" t="inlineStr">
         <is>
-          <t>Detroit placed Clark (undisclosed) on its injured reserve list Tuesday.</t>
+          <t>LaPorta (hip) returned to practice Tuesday, Richard Silva of The Detroit News reports.</t>
         </is>
       </c>
     </row>
@@ -40892,27 +40892,27 @@
       </c>
       <c r="B271" s="4" t="inlineStr">
         <is>
-          <t>Sam LaPorta</t>
+          <t>Jacob Saylors</t>
         </is>
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D271" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E271" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F271" s="4" t="inlineStr">
         <is>
-          <t>LaPorta (hip) returned to practice Tuesday, Richard Silva of The Detroit News reports.</t>
+          <t>Saylors rushed six times for 32 yards while also giving up a fumble-six in Saturday's 17-13 preseason win over the Commanders.</t>
         </is>
       </c>
     </row>
@@ -40924,12 +40924,12 @@
       </c>
       <c r="B272" s="5" t="inlineStr">
         <is>
-          <t>Jacob Saylors</t>
+          <t>Brock Wright</t>
         </is>
       </c>
       <c r="C272" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D272" s="5" t="inlineStr">
@@ -40944,7 +40944,7 @@
       </c>
       <c r="F272" s="5" t="inlineStr">
         <is>
-          <t>Saylors rushed six times for 32 yards while also giving up a fumble-six in Saturday's 17-13 preseason win over the Commanders.</t>
+          <t>Wright caught the first target of Thursday's preseason game against the Commanders, taking his sole reception for three yards.</t>
         </is>
       </c>
     </row>
@@ -40956,27 +40956,27 @@
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>Brock Wright</t>
+          <t>Ennis Rakestraw Jr.</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D273" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E273" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F273" s="4" t="inlineStr">
         <is>
-          <t>Wright caught the first target of Thursday's preseason game against the Commanders, taking his sole reception for three yards.</t>
+          <t>Rakestraw didn't finish practice Thursday due to an apparent leg injury, Colton Pouncy of The Athletic reports.</t>
         </is>
       </c>
     </row>
@@ -40988,12 +40988,12 @@
       </c>
       <c r="B274" s="5" t="inlineStr">
         <is>
-          <t>Ennis Rakestraw Jr.</t>
+          <t>Jimmy Rolder</t>
         </is>
       </c>
       <c r="C274" s="5" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D274" s="5" t="inlineStr">
@@ -41008,7 +41008,7 @@
       </c>
       <c r="F274" s="5" t="inlineStr">
         <is>
-          <t>Rakestraw didn't finish practice Thursday due to an apparent leg injury, Colton Pouncy of The Athletic reports.</t>
+          <t>Coach Dan Campbell said this week that Rolder (hamstring) could begin practicing pretty early in the season, Nolan Bianchi of The Detroit News reports.</t>
         </is>
       </c>
     </row>
@@ -41020,27 +41020,27 @@
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>Jimmy Rolder</t>
+          <t>Jared Goff</t>
         </is>
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D275" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E275" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F275" s="4" t="inlineStr">
         <is>
-          <t>Coach Dan Campbell said this week that Rolder (hamstring) could begin practicing pretty early in the season, Nolan Bianchi of The Detroit News reports.</t>
+          <t>Goff will be rested for Saturday's preseason game against the Commanders, Tim Twentyman of the Lions' official site reports.</t>
         </is>
       </c>
     </row>
@@ -41052,12 +41052,12 @@
       </c>
       <c r="B276" s="5" t="inlineStr">
         <is>
-          <t>Jared Goff</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="C276" s="5" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D276" s="5" t="inlineStr">
@@ -41072,7 +41072,7 @@
       </c>
       <c r="F276" s="5" t="inlineStr">
         <is>
-          <t>Goff will be rested for Saturday's preseason game against the Commanders, Tim Twentyman of the Lions' official site reports.</t>
+          <t>Williams (shoulder) participated in team drills and 7-on-7s during Wednesday's practice, Tim Twentyman of the Lions' official site reports.</t>
         </is>
       </c>
     </row>
@@ -41084,27 +41084,27 @@
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>Mekhi Wingo</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="D277" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E277" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F277" s="4" t="inlineStr">
         <is>
-          <t>Williams (shoulder) participated in team drills and 7-on-7s during Wednesday's practice, Tim Twentyman of the Lions' official site reports.</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -41116,12 +41116,12 @@
       </c>
       <c r="B278" s="5" t="inlineStr">
         <is>
-          <t>Mekhi Wingo</t>
+          <t>D.J. Reed</t>
         </is>
       </c>
       <c r="C278" s="5" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D278" s="5" t="inlineStr">
@@ -41148,12 +41148,12 @@
       </c>
       <c r="B279" s="4" t="inlineStr">
         <is>
-          <t>D.J. Reed</t>
+          <t>Malcolm Rodriguez</t>
         </is>
       </c>
       <c r="C279" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D279" s="4" t="inlineStr">
@@ -41200,7 +41200,7 @@
       </c>
       <c r="F280" s="5" t="inlineStr">
         <is>
-          <t>Oliver is dealing with Achilles and calf injuries and is considered week-to-week, Weston Hodkiewicz of the Packers' official site reports.</t>
+          <t>Oliver is dealing with Achilles and calf injuries. and is considered week-to-week, Weston Hodkiewicz of the Packers' official site reports.</t>
         </is>
       </c>
     </row>
@@ -45368,12 +45368,12 @@
       </c>
       <c r="B411" s="4" t="inlineStr">
         <is>
-          <t>Dare Ogunbowale</t>
+          <t>Kirk Cousins</t>
         </is>
       </c>
       <c r="C411" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D411" s="4" t="inlineStr">
@@ -45388,7 +45388,7 @@
       </c>
       <c r="F411" s="4" t="inlineStr">
         <is>
-          <t>Ogunbowale was released by Las Vegas on Sunday, Tom Pelissero of NFL Network reports.</t>
+          <t>Cousins is expected to be named starting quarterback for the Raiders, Matt Zenitz of CBSSports.com reports.</t>
         </is>
       </c>
     </row>
@@ -45400,12 +45400,12 @@
       </c>
       <c r="B412" s="5" t="inlineStr">
         <is>
-          <t>Kirk Cousins</t>
+          <t>Jack Bech</t>
         </is>
       </c>
       <c r="C412" s="5" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D412" s="5" t="inlineStr">
@@ -45420,7 +45420,7 @@
       </c>
       <c r="F412" s="5" t="inlineStr">
         <is>
-          <t>Cousins is expected to be named starting quarterback for the Raiders, Matt Zenitz of CBSSports.com reports.</t>
+          <t>Bech caught his sole target for five yards in Thursday night's preseason finale against the 49ers.</t>
         </is>
       </c>
     </row>
@@ -45432,12 +45432,12 @@
       </c>
       <c r="B413" s="4" t="inlineStr">
         <is>
-          <t>Jack Bech</t>
+          <t>Matt Gay</t>
         </is>
       </c>
       <c r="C413" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="D413" s="4" t="inlineStr">
@@ -45452,7 +45452,7 @@
       </c>
       <c r="F413" s="4" t="inlineStr">
         <is>
-          <t>Bech caught his sole target for five yards in Thursday night's preseason finale against the 49ers.</t>
+          <t>Gay converted four of five field-goal attempts in Thursday night's 18-12 preseason loss to the 49ers.</t>
         </is>
       </c>
     </row>
@@ -45464,12 +45464,12 @@
       </c>
       <c r="B414" s="5" t="inlineStr">
         <is>
-          <t>Matt Gay</t>
+          <t>Malik Benson</t>
         </is>
       </c>
       <c r="C414" s="5" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D414" s="5" t="inlineStr">
@@ -45484,7 +45484,7 @@
       </c>
       <c r="F414" s="5" t="inlineStr">
         <is>
-          <t>Gay converted four of five field-goal attempts in Thursday night's 18-12 preseason loss to the 49ers.</t>
+          <t>Benson failed to catch his only target in Thursday night's preseason finale against the 49ers.</t>
         </is>
       </c>
     </row>
@@ -45496,12 +45496,12 @@
       </c>
       <c r="B415" s="4" t="inlineStr">
         <is>
-          <t>Malik Benson</t>
+          <t>Michael Mayer</t>
         </is>
       </c>
       <c r="C415" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D415" s="4" t="inlineStr">
@@ -45516,7 +45516,7 @@
       </c>
       <c r="F415" s="4" t="inlineStr">
         <is>
-          <t>Benson failed to catch his only target in Thursday night's preseason finale against the 49ers.</t>
+          <t>Mayer caught both of his targets for eight yards in Thursday night's 18-12 preseason loss to the 49ers.</t>
         </is>
       </c>
     </row>
@@ -45528,12 +45528,12 @@
       </c>
       <c r="B416" s="5" t="inlineStr">
         <is>
-          <t>Michael Mayer</t>
+          <t>Jalen Nailor</t>
         </is>
       </c>
       <c r="C416" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D416" s="5" t="inlineStr">
@@ -45548,7 +45548,7 @@
       </c>
       <c r="F416" s="5" t="inlineStr">
         <is>
-          <t>Mayer caught both of his targets for eight yards in Thursday night's 18-12 preseason loss to the 49ers.</t>
+          <t>Nailor brought in two of four targets for 13 yards in the Raiders' 18-12 preseason loss to the 49ers on Thursday.</t>
         </is>
       </c>
     </row>
@@ -45560,7 +45560,7 @@
       </c>
       <c r="B417" s="4" t="inlineStr">
         <is>
-          <t>Jalen Nailor</t>
+          <t>Tre Tucker</t>
         </is>
       </c>
       <c r="C417" s="4" t="inlineStr">
@@ -45580,7 +45580,7 @@
       </c>
       <c r="F417" s="4" t="inlineStr">
         <is>
-          <t>Nailor brought in two of four targets for 13 yards in the Raiders' 18-12 preseason loss to the 49ers on Thursday.</t>
+          <t>Tucker secured all three targets for 25 yards in the Raiders' 18-12 preseason loss to the 49ers on Thursday.</t>
         </is>
       </c>
     </row>
@@ -45592,12 +45592,12 @@
       </c>
       <c r="B418" s="5" t="inlineStr">
         <is>
-          <t>Tre Tucker</t>
+          <t>Fernando Mendoza</t>
         </is>
       </c>
       <c r="C418" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D418" s="5" t="inlineStr">
@@ -45612,7 +45612,7 @@
       </c>
       <c r="F418" s="5" t="inlineStr">
         <is>
-          <t>Tucker secured all three targets for 25 yards in the Raiders' 18-12 preseason loss to the 49ers on Thursday.</t>
+          <t>Mendoza remains in the mix for the Raiders' starting quarterback job along with veteran Kirk Cousins, Vinny Bonsignore of the California Post reports.</t>
         </is>
       </c>
     </row>
@@ -45624,12 +45624,12 @@
       </c>
       <c r="B419" s="4" t="inlineStr">
         <is>
-          <t>Fernando Mendoza</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C419" s="4" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D419" s="4" t="inlineStr">
@@ -45644,7 +45644,7 @@
       </c>
       <c r="F419" s="4" t="inlineStr">
         <is>
-          <t>Mendoza remains in the mix for the Raiders' starting quarterback job along with veteran Kirk Cousins, Vinny Bonsignore of the California Post reports.</t>
+          <t>Washington rushed eight times for 49 yards and failed to bring in his only target in the Raiders' 18-12 preseason loss to the 49ers on Thursday.</t>
         </is>
       </c>
     </row>
@@ -45656,12 +45656,12 @@
       </c>
       <c r="B420" s="5" t="inlineStr">
         <is>
-          <t>Mike Washington Jr.</t>
+          <t>Brock Bowers</t>
         </is>
       </c>
       <c r="C420" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D420" s="5" t="inlineStr">
@@ -45676,7 +45676,7 @@
       </c>
       <c r="F420" s="5" t="inlineStr">
         <is>
-          <t>Washington rushed eight times for 49 yards and failed to bring in his only target in the Raiders' 18-12 preseason loss to the 49ers on Thursday.</t>
+          <t>Bowers secured one of two targets for six yards in the Raiders' 18-12 preseason loss to the 49ers on Thursday.</t>
         </is>
       </c>
     </row>
@@ -45688,27 +45688,27 @@
       </c>
       <c r="B421" s="4" t="inlineStr">
         <is>
-          <t>Brock Bowers</t>
+          <t>Chigozie Anusiem</t>
         </is>
       </c>
       <c r="C421" s="4" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D421" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E421" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F421" s="4" t="inlineStr">
         <is>
-          <t>Bowers secured one of two targets for six yards in the Raiders' 18-12 preseason loss to the 49ers on Thursday.</t>
+          <t>The Raiders placed Anusiem (knee) on injured reserve Saturday, Adam Schefter of ESPN reports.</t>
         </is>
       </c>
     </row>
@@ -45720,12 +45720,12 @@
       </c>
       <c r="B422" s="5" t="inlineStr">
         <is>
-          <t>Chigozie Anusiem</t>
+          <t>Justin Pickett</t>
         </is>
       </c>
       <c r="C422" s="5" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D422" s="5" t="inlineStr">
@@ -45740,7 +45740,7 @@
       </c>
       <c r="F422" s="5" t="inlineStr">
         <is>
-          <t>The Raiders placed Anusiem (knee) on injured reserve Saturday, Adam Schefter of ESPN reports.</t>
+          <t>ir</t>
         </is>
       </c>
     </row>
@@ -45752,12 +45752,12 @@
       </c>
       <c r="B423" s="4" t="inlineStr">
         <is>
-          <t>Justin Pickett</t>
+          <t>Brennan Jackson</t>
         </is>
       </c>
       <c r="C423" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D423" s="4" t="inlineStr">
@@ -45784,29 +45784,25 @@
       </c>
       <c r="B424" s="5" t="inlineStr">
         <is>
-          <t>Brennan Jackson</t>
+          <t>Jermod McCoy</t>
         </is>
       </c>
       <c r="C424" s="5" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D424" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E424" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="F424" s="5" t="inlineStr">
-        <is>
-          <t>ir</t>
-        </is>
-      </c>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F424" s="5" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" s="4" t="inlineStr">
@@ -45816,12 +45812,12 @@
       </c>
       <c r="B425" s="4" t="inlineStr">
         <is>
-          <t>Jermod McCoy</t>
+          <t>Folorunso Fatukasi</t>
         </is>
       </c>
       <c r="C425" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="D425" s="4" t="inlineStr">
@@ -45834,7 +45830,11 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F425" s="4" t="inlineStr"/>
+      <c r="F425" s="4" t="inlineStr">
+        <is>
+          <t>The Raiders signed Fatukasi to a contract Saturday, Jeremy Fowler of ESPN.com reports.</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" s="5" t="inlineStr">
@@ -45844,12 +45844,12 @@
       </c>
       <c r="B426" s="5" t="inlineStr">
         <is>
-          <t>Folorunso Fatukasi</t>
+          <t>Caleb Rogers</t>
         </is>
       </c>
       <c r="C426" s="5" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D426" s="5" t="inlineStr">
@@ -45864,7 +45864,7 @@
       </c>
       <c r="F426" s="5" t="inlineStr">
         <is>
-          <t>The Raiders signed Fatukasi to a contract Saturday, Jeremy Fowler of ESPN.com reports.</t>
+          <t>Rogers (undisclosed) was back in uniform at the Raiders' practice Tuesday, Ryan McFadden of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -45876,27 +45876,27 @@
       </c>
       <c r="B427" s="4" t="inlineStr">
         <is>
-          <t>Caleb Rogers</t>
+          <t>Chris Collier</t>
         </is>
       </c>
       <c r="C427" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D427" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E427" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F427" s="4" t="inlineStr">
         <is>
-          <t>Rogers (undisclosed) was back in uniform at the Raiders' practice Tuesday, Ryan McFadden of ESPN.com reports.</t>
+          <t>Collier (undisclosed) reverted to injured reserve with the Raiders on Sunday, Sam Warren of The Athletic reports.</t>
         </is>
       </c>
     </row>
@@ -45908,12 +45908,12 @@
       </c>
       <c r="B428" s="5" t="inlineStr">
         <is>
-          <t>Chris Myarick</t>
+          <t>Adam Butler</t>
         </is>
       </c>
       <c r="C428" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="D428" s="5" t="inlineStr">
@@ -45926,11 +45926,7 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F428" s="5" t="inlineStr">
-        <is>
-          <t>Las Vegas signed Myarick on Wednesday.</t>
-        </is>
-      </c>
+      <c r="F428" s="5" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" s="4" t="inlineStr">
@@ -45940,27 +45936,27 @@
       </c>
       <c r="B429" s="4" t="inlineStr">
         <is>
-          <t>Chris Collier</t>
+          <t>Maxx Crosby</t>
         </is>
       </c>
       <c r="C429" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D429" s="4" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E429" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F429" s="4" t="inlineStr">
         <is>
-          <t>Collier (undisclosed) reverted to injured reserve with the Raiders on Sunday, Sam Warren of The Athletic reports.</t>
+          <t>Crosby (knee) has been cleared for the start of training camp and will practice Wednesday, Ryan McFadden of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -46708,27 +46704,27 @@
       </c>
       <c r="B453" s="4" t="inlineStr">
         <is>
-          <t>Gary Jennings</t>
+          <t>Tyler Biadasz</t>
         </is>
       </c>
       <c r="C453" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D453" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E453" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F453" s="4" t="inlineStr">
         <is>
-          <t>The Chargers signed Jennings to a contract Sunday.</t>
+          <t>The Chargers placed Biadasz (knee) on injured reserve Sunday.</t>
         </is>
       </c>
     </row>
@@ -46740,17 +46736,17 @@
       </c>
       <c r="B454" s="5" t="inlineStr">
         <is>
-          <t>Tyler Biadasz</t>
+          <t>Rashawn Slater</t>
         </is>
       </c>
       <c r="C454" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>OT</t>
         </is>
       </c>
       <c r="D454" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E454" s="5" t="inlineStr">
@@ -46760,7 +46756,7 @@
       </c>
       <c r="F454" s="5" t="inlineStr">
         <is>
-          <t>The Chargers placed Biadasz (knee) on injured reserve Sunday.</t>
+          <t>Slater (undisclosed) was a limited participant in Saturday's practice, Alex Insdorf of BoltBeat.com reports.</t>
         </is>
       </c>
     </row>
@@ -47412,7 +47408,7 @@
       </c>
       <c r="B475" s="4" t="inlineStr">
         <is>
-          <t>Alex Bachman</t>
+          <t>Davante Adams</t>
         </is>
       </c>
       <c r="C475" s="4" t="inlineStr">
@@ -47432,7 +47428,7 @@
       </c>
       <c r="F475" s="4" t="inlineStr">
         <is>
-          <t>The Rams signed Bachman on Tuesday.</t>
+          <t>Adams did not play in the Rams' 20-12 preseason win over the Chiefs on Saturday.</t>
         </is>
       </c>
     </row>
@@ -47444,12 +47440,12 @@
       </c>
       <c r="B476" s="5" t="inlineStr">
         <is>
-          <t>Davante Adams</t>
+          <t>Blake Corum</t>
         </is>
       </c>
       <c r="C476" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D476" s="5" t="inlineStr">
@@ -47464,7 +47460,7 @@
       </c>
       <c r="F476" s="5" t="inlineStr">
         <is>
-          <t>Adams did not play in the Rams' 20-12 preseason win over the Chiefs on Saturday.</t>
+          <t>Teammate Kyren Williams said last week that Corum looks "a lot leaner" and "more explosive" headed into his third season, Nate Atkins of The Athletic reports.</t>
         </is>
       </c>
     </row>
@@ -47476,27 +47472,27 @@
       </c>
       <c r="B477" s="4" t="inlineStr">
         <is>
-          <t>Blake Corum</t>
+          <t>Alaric Jackson</t>
         </is>
       </c>
       <c r="C477" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>OT</t>
         </is>
       </c>
       <c r="D477" s="4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E477" s="4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F477" s="4" t="inlineStr">
         <is>
-          <t>Teammate Kyren Williams said last week that Corum looks "a lot leaner" and "more explosive" headed into his third season, Nate Atkins of The Athletic reports.</t>
+          <t>Jackson missed practice Wednesday due to management of his blood clot issue, Stu Jackson and Zach Edwards of the Rams' official site report.</t>
         </is>
       </c>
     </row>
@@ -47508,27 +47504,27 @@
       </c>
       <c r="B478" s="5" t="inlineStr">
         <is>
-          <t>Alaric Jackson</t>
+          <t>Jordan Whittington</t>
         </is>
       </c>
       <c r="C478" s="5" t="inlineStr">
         <is>
-          <t>OT</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D478" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E478" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F478" s="5" t="inlineStr">
         <is>
-          <t>Jackson missed practice Wednesday due to management of his blood clot issue, Stu Jackson and Zach Edwards of the Rams' official site report.</t>
+          <t>Whittington looks like the early leader in the competition for the Rams' No. 3 receiver job, according to Cameron DaSilva of Rams Wire.</t>
         </is>
       </c>
     </row>
@@ -47540,12 +47536,12 @@
       </c>
       <c r="B479" s="4" t="inlineStr">
         <is>
-          <t>Jordan Whittington</t>
+          <t>Blake Hance</t>
         </is>
       </c>
       <c r="C479" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D479" s="4" t="inlineStr">
@@ -47560,7 +47556,7 @@
       </c>
       <c r="F479" s="4" t="inlineStr">
         <is>
-          <t>Whittington looks like the early leader in the competition for the Rams' No. 3 receiver job, according to Cameron DaSilva of Rams Wire.</t>
+          <t>The Rams signed Hance (shoulder) on Tuesday, per the NFL's transaction log.</t>
         </is>
       </c>
     </row>
@@ -49952,27 +49948,27 @@
       </c>
       <c r="B555" s="4" t="inlineStr">
         <is>
-          <t>Lorenzo Styles Jr.</t>
+          <t>Kendre Miller</t>
         </is>
       </c>
       <c r="C555" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D555" s="4" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E555" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Undisclosed</t>
         </is>
       </c>
       <c r="F555" s="4" t="inlineStr">
         <is>
-          <t>The Saints placed Styles (calf) on injured reserve Tuesday, John Hendrix of AthlonSports.com reports.</t>
+          <t>Miller is believed to have sustained only a minor injury at Tuesday's practice, Nick Underhill of NewOrleans.Football reports.</t>
         </is>
       </c>
     </row>
@@ -49984,27 +49980,27 @@
       </c>
       <c r="B556" s="5" t="inlineStr">
         <is>
-          <t>Kendre Miller</t>
+          <t>Lorenzo Styles Jr.</t>
         </is>
       </c>
       <c r="C556" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D556" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E556" s="5" t="inlineStr">
         <is>
-          <t>Undisclosed</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F556" s="5" t="inlineStr">
         <is>
-          <t>Miller exited Tuesday's practice alongside trainers with an apparent injury, Katherine Terrell of ESPN.com reports.</t>
+          <t>The Saints placed Styles (calf) on injured reserve Tuesday, John Hendrix of AthlonSports.com reports.</t>
         </is>
       </c>
     </row>
@@ -50752,12 +50748,12 @@
       </c>
       <c r="B580" s="5" t="inlineStr">
         <is>
-          <t>DJ James</t>
+          <t>Tyrone Tracy Jr.</t>
         </is>
       </c>
       <c r="C580" s="5" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D580" s="5" t="inlineStr">
@@ -50772,7 +50768,7 @@
       </c>
       <c r="F580" s="5" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>Tracy (neck) is present at Tuesday's practice in a non-contact jersey, Dan Duggan of The Athletic reports.</t>
         </is>
       </c>
     </row>
@@ -50784,12 +50780,12 @@
       </c>
       <c r="B581" s="4" t="inlineStr">
         <is>
-          <t>Tyrone Tracy Jr.</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="C581" s="4" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D581" s="4" t="inlineStr">
@@ -50799,12 +50795,12 @@
       </c>
       <c r="E581" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Surgery</t>
         </is>
       </c>
       <c r="F581" s="4" t="inlineStr">
         <is>
-          <t>Tracy (neck) is present at Tuesday's practice in a non-contact jersey, Dan Duggan of The Athletic reports.</t>
+          <t>Nabers (knee) was not spotted at the portion of Tuesday's practice open to the media, but he later took the field in uniform, according to Connor Hughes of SNY.tv.</t>
         </is>
       </c>
     </row>
@@ -50816,27 +50812,27 @@
       </c>
       <c r="B582" s="5" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Korie Black</t>
         </is>
       </c>
       <c r="C582" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D582" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E582" s="5" t="inlineStr">
         <is>
-          <t>Surgery</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F582" s="5" t="inlineStr">
         <is>
-          <t>Nabers (knee) was not spotted at the portion of Tuesday's practice open to the media, but he later took the field in uniform, according to Connor Hughes of SNY.tv.</t>
+          <t>Black (undisclosed) was placed on injured reserve with a designation to return by the Giants on Monday, Dan Salomone and Matt Citak of the team's official site report.</t>
         </is>
       </c>
     </row>
@@ -50848,17 +50844,17 @@
       </c>
       <c r="B583" s="4" t="inlineStr">
         <is>
-          <t>Korie Black</t>
+          <t>Theo Johnson</t>
         </is>
       </c>
       <c r="C583" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D583" s="4" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E583" s="4" t="inlineStr">
@@ -50868,7 +50864,7 @@
       </c>
       <c r="F583" s="4" t="inlineStr">
         <is>
-          <t>Black (undisclosed) was placed on injured reserve with a designation to return by the Giants on Monday, Dan Salomone and Matt Citak of the team's official site report.</t>
+          <t>Johnson (shoulder) is participating in Monday's practice in a non-contact jersey, Pat Leonard of the New York Daily News reports.</t>
         </is>
       </c>
     </row>
@@ -50880,27 +50876,27 @@
       </c>
       <c r="B584" s="5" t="inlineStr">
         <is>
-          <t>Theo Johnson</t>
+          <t>Darius Slayton</t>
         </is>
       </c>
       <c r="C584" s="5" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D584" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E584" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F584" s="5" t="inlineStr">
         <is>
-          <t>Johnson (shoulder) is participating in Monday's practice in a non-contact jersey, Pat Leonard of the New York Daily News reports.</t>
+          <t>Slayton is a member of the Giants' initial 53-man roster in 2026, Paul Schwartz of the New York Post reports.</t>
         </is>
       </c>
     </row>
@@ -50912,7 +50908,7 @@
       </c>
       <c r="B585" s="4" t="inlineStr">
         <is>
-          <t>Darius Slayton</t>
+          <t>Odell Beckham Jr.</t>
         </is>
       </c>
       <c r="C585" s="4" t="inlineStr">
@@ -50932,7 +50928,7 @@
       </c>
       <c r="F585" s="4" t="inlineStr">
         <is>
-          <t>Slayton is a member of the Giants' initial 53-man roster in 2026, Paul Schwartz of the New York Post reports.</t>
+          <t>Beckham has earned a spot on the 53-man roster for the Giants, Jordan Raanan of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -50944,12 +50940,12 @@
       </c>
       <c r="B586" s="5" t="inlineStr">
         <is>
-          <t>Odell Beckham Jr.</t>
+          <t>CJ Okoye</t>
         </is>
       </c>
       <c r="C586" s="5" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="D586" s="5" t="inlineStr">
@@ -50964,7 +50960,7 @@
       </c>
       <c r="F586" s="5" t="inlineStr">
         <is>
-          <t>Beckham has earned a spot on the 53-man roster for the Giants, Jordan Raanan of ESPN.com reports.</t>
+          <t>The Ravens traded Okoye to the Giants in exchange for a 2028 seventh-round pick Saturday, Ian Rapoport of ESPN and NFL Network reports.</t>
         </is>
       </c>
     </row>
@@ -50976,12 +50972,12 @@
       </c>
       <c r="B587" s="4" t="inlineStr">
         <is>
-          <t>CJ Okoye</t>
+          <t>Najee Harris</t>
         </is>
       </c>
       <c r="C587" s="4" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D587" s="4" t="inlineStr">
@@ -50996,7 +50992,7 @@
       </c>
       <c r="F587" s="4" t="inlineStr">
         <is>
-          <t>The Ravens traded Okoye to the Giants in exchange for a 2028 seventh-round pick Saturday, Ian Rapoport of ESPN and NFL Network reports.</t>
+          <t>Harris rushed 11 times for 39 yards and added a 20-yard reception on his lone target in Friday's 23-6 preseason win over the Jets.</t>
         </is>
       </c>
     </row>
@@ -51008,12 +51004,12 @@
       </c>
       <c r="B588" s="5" t="inlineStr">
         <is>
-          <t>Najee Harris</t>
+          <t>Dominic Zvada</t>
         </is>
       </c>
       <c r="C588" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="D588" s="5" t="inlineStr">
@@ -51028,7 +51024,7 @@
       </c>
       <c r="F588" s="5" t="inlineStr">
         <is>
-          <t>Harris rushed 11 times for 39 yards and added a 20-yard reception on his lone target in Friday's 23-6 preseason win over the Jets.</t>
+          <t>Zvada, per head coach John Harbaugh, will open the season as the Giants' kicker, Pat Leonard of the New York Daily News reports.</t>
         </is>
       </c>
     </row>
@@ -51040,12 +51036,12 @@
       </c>
       <c r="B589" s="4" t="inlineStr">
         <is>
-          <t>Dominic Zvada</t>
+          <t>Devin Singletary</t>
         </is>
       </c>
       <c r="C589" s="4" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D589" s="4" t="inlineStr">
@@ -51060,7 +51056,7 @@
       </c>
       <c r="F589" s="4" t="inlineStr">
         <is>
-          <t>Zvada, per head coach John Harbaugh, will open the season as the Giants' kicker, Pat Leonard of the New York Daily News reports.</t>
+          <t>Singletary isn't in uniform ahead of Friday's preseason contest against the Jets, Ryan Dunleavy of the New York Post reports.</t>
         </is>
       </c>
     </row>
@@ -51072,27 +51068,27 @@
       </c>
       <c r="B590" s="5" t="inlineStr">
         <is>
-          <t>Devin Singletary</t>
+          <t>Calvin Austin III</t>
         </is>
       </c>
       <c r="C590" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D590" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E590" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F590" s="5" t="inlineStr">
         <is>
-          <t>Singletary isn't in uniform ahead of Friday's preseason contest against the Jets, Ryan Dunleavy of the New York Post reports.</t>
+          <t>The Giants placed Austin (knee) on injured reserve Thursday, Patricia Traina of SI.com reports.</t>
         </is>
       </c>
     </row>
@@ -51104,7 +51100,7 @@
       </c>
       <c r="B591" s="4" t="inlineStr">
         <is>
-          <t>Calvin Austin III</t>
+          <t>Malachi Fields</t>
         </is>
       </c>
       <c r="C591" s="4" t="inlineStr">
@@ -51114,17 +51110,17 @@
       </c>
       <c r="D591" s="4" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E591" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F591" s="4" t="inlineStr">
         <is>
-          <t>The Giants placed Austin (knee) on injured reserve Thursday, Patricia Traina of SI.com reports.</t>
+          <t>Fields could be one of multiple Giants receivers who benefits from added opportunities to begin the season after Calvin Austin (knee) sustained a torn ACL during Tuesday's practice, Jordan Raanan of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -51136,7 +51132,7 @@
       </c>
       <c r="B592" s="5" t="inlineStr">
         <is>
-          <t>Malachi Fields</t>
+          <t>Darnell Mooney</t>
         </is>
       </c>
       <c r="C592" s="5" t="inlineStr">
@@ -51156,7 +51152,7 @@
       </c>
       <c r="F592" s="5" t="inlineStr">
         <is>
-          <t>Fields could be one of multiple Giants receivers who benefits from added opportunities to begin the season after Calvin Austin (knee) sustained a torn ACL during Tuesday's practice, Jordan Raanan of ESPN.com reports.</t>
+          <t>Mooney could have a chance to open the season as the Giants' No. 3 receiver after Calvin Austin (knee) sustained a torn ACL in Tuesday's practice, Jordan Ranaan of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -51168,12 +51164,12 @@
       </c>
       <c r="B593" s="4" t="inlineStr">
         <is>
-          <t>Darnell Mooney</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C593" s="4" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D593" s="4" t="inlineStr">
@@ -51188,7 +51184,7 @@
       </c>
       <c r="F593" s="4" t="inlineStr">
         <is>
-          <t>Mooney could have a chance to open the season as the Giants' No. 3 receiver after Calvin Austin (knee) sustained a torn ACL in Tuesday's practice, Jordan Ranaan of ESPN.com reports.</t>
+          <t>Skattebo is listed as the Giants' starting running back on the team's unofficial depth chart for the preseason finale versus the Jets, Jordan Raanan of ESPN.com reports.</t>
         </is>
       </c>
     </row>
@@ -51200,27 +51196,27 @@
       </c>
       <c r="B594" s="5" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Colton Hood</t>
         </is>
       </c>
       <c r="C594" s="5" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D594" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E594" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F594" s="5" t="inlineStr">
         <is>
-          <t>Skattebo is listed as the Giants' starting running back on the team's unofficial depth chart for the preseason finale versus the Jets, Jordan Raanan of ESPN.com reports.</t>
+          <t>Hood (quadriceps) is expected to return to practice this week, Paul Schwartz of New York Post reports.</t>
         </is>
       </c>
     </row>
@@ -51232,27 +51228,27 @@
       </c>
       <c r="B595" s="4" t="inlineStr">
         <is>
-          <t>Colton Hood</t>
+          <t>Jaxson Dart</t>
         </is>
       </c>
       <c r="C595" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D595" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E595" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F595" s="4" t="inlineStr">
         <is>
-          <t>Hood (quadriceps) is expected to return to practice this week, Paul Schwartz of New York Post reports.</t>
+          <t>Dart didn't suit up for Saturday's 26-3 preseason win over the Dolphins.</t>
         </is>
       </c>
     </row>
@@ -51264,27 +51260,27 @@
       </c>
       <c r="B596" s="5" t="inlineStr">
         <is>
-          <t>Jaxson Dart</t>
+          <t>Francis Mauigoa</t>
         </is>
       </c>
       <c r="C596" s="5" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>OT</t>
         </is>
       </c>
       <c r="D596" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E596" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Stinger</t>
         </is>
       </c>
       <c r="F596" s="5" t="inlineStr">
         <is>
-          <t>Dart didn't suit up for Saturday's 26-3 preseason win over the Dolphins.</t>
+          <t>Mauigoa (upper body) had to leave Thursday's joint practice with the Dolphins due to a stinger, Dan Benton of USA Today reports.</t>
         </is>
       </c>
     </row>
@@ -51296,12 +51292,12 @@
       </c>
       <c r="B597" s="4" t="inlineStr">
         <is>
-          <t>Francis Mauigoa</t>
+          <t>Greg Newsome II</t>
         </is>
       </c>
       <c r="C597" s="4" t="inlineStr">
         <is>
-          <t>OT</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D597" s="4" t="inlineStr">
@@ -51311,12 +51307,12 @@
       </c>
       <c r="E597" s="4" t="inlineStr">
         <is>
-          <t>Stinger</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F597" s="4" t="inlineStr">
         <is>
-          <t>Mauigoa (upper body) had to leave Thursday's joint practice with the Dolphins due to a stinger, Dan Benton of USA Today reports.</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -51328,7 +51324,7 @@
       </c>
       <c r="B598" s="5" t="inlineStr">
         <is>
-          <t>Greg Newsome II</t>
+          <t>Dru Phillips</t>
         </is>
       </c>
       <c r="C598" s="5" t="inlineStr">
@@ -51343,7 +51339,7 @@
       </c>
       <c r="E598" s="5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Sprain</t>
         </is>
       </c>
       <c r="F598" s="5" t="inlineStr">
@@ -51360,27 +51356,27 @@
       </c>
       <c r="B599" s="4" t="inlineStr">
         <is>
-          <t>Dru Phillips</t>
+          <t>Roy Robertson-Harris</t>
         </is>
       </c>
       <c r="C599" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="D599" s="4" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E599" s="4" t="inlineStr">
         <is>
-          <t>Sprain</t>
+          <t>Surgery</t>
         </is>
       </c>
       <c r="F599" s="4" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>ir</t>
         </is>
       </c>
     </row>
@@ -51392,27 +51388,27 @@
       </c>
       <c r="B600" s="5" t="inlineStr">
         <is>
-          <t>Roy Robertson-Harris</t>
+          <t>John Michael Schmitz Jr.</t>
         </is>
       </c>
       <c r="C600" s="5" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D600" s="5" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Questionable</t>
         </is>
       </c>
       <c r="E600" s="5" t="inlineStr">
         <is>
-          <t>Surgery</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F600" s="5" t="inlineStr">
         <is>
-          <t>ir</t>
+          <t>questionable</t>
         </is>
       </c>
     </row>
@@ -51424,12 +51420,12 @@
       </c>
       <c r="B601" s="4" t="inlineStr">
         <is>
-          <t>John Michael Schmitz Jr.</t>
+          <t>Paulson Adebo</t>
         </is>
       </c>
       <c r="C601" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D601" s="4" t="inlineStr">
@@ -51456,7 +51452,7 @@
       </c>
       <c r="B602" s="5" t="inlineStr">
         <is>
-          <t>Paulson Adebo</t>
+          <t>Jarrick Bernard-Converse</t>
         </is>
       </c>
       <c r="C602" s="5" t="inlineStr">
@@ -51466,7 +51462,7 @@
       </c>
       <c r="D602" s="5" t="inlineStr">
         <is>
-          <t>Questionable</t>
+          <t>Injured Reserve</t>
         </is>
       </c>
       <c r="E602" s="5" t="inlineStr">
@@ -51476,7 +51472,7 @@
       </c>
       <c r="F602" s="5" t="inlineStr">
         <is>
-          <t>questionable</t>
+          <t>ir</t>
         </is>
       </c>
     </row>
@@ -51488,29 +51484,25 @@
       </c>
       <c r="B603" s="4" t="inlineStr">
         <is>
-          <t>Jarrick Bernard-Converse</t>
+          <t>Jevon Holland</t>
         </is>
       </c>
       <c r="C603" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D603" s="4" t="inlineStr">
         <is>
-          <t>Injured Reserve</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="E603" s="4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="F603" s="4" t="inlineStr">
-        <is>
-          <t>ir</t>
-        </is>
-      </c>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F603" s="4" t="inlineStr"/>
     </row>
     <row r="604">
       <c r="A604" s="5" t="inlineStr">
@@ -51520,12 +51512,12 @@
       </c>
       <c r="B604" s="5" t="inlineStr">
         <is>
-          <t>Jevon Holland</t>
+          <t>Jake Haener</t>
         </is>
       </c>
       <c r="C604" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D604" s="5" t="inlineStr">
@@ -51538,7 +51530,11 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F604" s="5" t="inlineStr"/>
+      <c r="F604" s="5" t="inlineStr">
+        <is>
+          <t>The Giants signed Haener to a contract Monday, Mike Garafolo of NFL Network reports.</t>
+        </is>
+      </c>
     </row>
     <row r="605">
       <c r="A605" s="4" t="inlineStr">
@@ -58054,10 +58050,10 @@
         <v>8.5</v>
       </c>
       <c r="F5" s="17" t="n">
-        <v>8.9</v>
+        <v>10.3</v>
       </c>
       <c r="G5" s="17" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
@@ -58134,10 +58130,10 @@
         <v>6.6</v>
       </c>
       <c r="F7" s="17" t="n">
-        <v>2.2</v>
+        <v>13</v>
       </c>
       <c r="G7" s="17" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
@@ -58172,10 +58168,10 @@
         <v>6.7</v>
       </c>
       <c r="F8" s="19" t="n">
-        <v>15.2</v>
+        <v>8.9</v>
       </c>
       <c r="G8" s="19" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
@@ -58210,10 +58206,10 @@
         <v>1.6</v>
       </c>
       <c r="F9" s="17" t="n">
-        <v>17.2</v>
+        <v>3.1</v>
       </c>
       <c r="G9" s="17" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
@@ -58252,10 +58248,10 @@
         <v>3.1</v>
       </c>
       <c r="F10" s="19" t="n">
-        <v>10.1</v>
+        <v>3.8</v>
       </c>
       <c r="G10" s="19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
@@ -58290,10 +58286,10 @@
         <v>8.699999999999999</v>
       </c>
       <c r="F11" s="17" t="n">
-        <v>2.7</v>
+        <v>10.7</v>
       </c>
       <c r="G11" s="17" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
@@ -58332,10 +58328,10 @@
         <v>9.9</v>
       </c>
       <c r="F12" s="19" t="n">
-        <v>6.5</v>
+        <v>13.4</v>
       </c>
       <c r="G12" s="19" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
@@ -58374,10 +58370,10 @@
         <v>6.8</v>
       </c>
       <c r="F13" s="17" t="n">
-        <v>10.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G13" s="17" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
@@ -58412,10 +58408,10 @@
         <v>7</v>
       </c>
       <c r="F14" s="19" t="n">
-        <v>19</v>
+        <v>10.1</v>
       </c>
       <c r="G14" s="19" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
@@ -58423,13 +58419,9 @@
         </is>
       </c>
       <c r="I14" s="14" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>Wind 7 mph (gusts 19)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -58457,7 +58449,7 @@
         <v>4.5</v>
       </c>
       <c r="G15" s="17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
@@ -58492,10 +58484,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>12.3</v>
+        <v>14.5</v>
       </c>
       <c r="G16" s="19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
@@ -58534,10 +58526,10 @@
         <v>3.5</v>
       </c>
       <c r="F17" s="17" t="n">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="G17" s="17" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
@@ -58576,10 +58568,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="F18" s="19" t="n">
-        <v>10.5</v>
+        <v>15.2</v>
       </c>
       <c r="G18" s="19" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
@@ -58614,10 +58606,10 @@
         <v>5.9</v>
       </c>
       <c r="F19" s="17" t="n">
-        <v>10.5</v>
+        <v>14.3</v>
       </c>
       <c r="G19" s="17" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
@@ -58652,10 +58644,10 @@
         <v>6.5</v>
       </c>
       <c r="F20" s="19" t="n">
-        <v>5.1</v>
+        <v>6.5</v>
       </c>
       <c r="G20" s="19" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>

--- a/NFL_Edge_Model.xlsx
+++ b/NFL_Edge_Model.xlsx
@@ -224,8 +224,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblBest" displayName="tblBest" ref="A4:N9" headerRowCount="1">
-  <autoFilter ref="A4:N9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblBest" displayName="tblBest" ref="A4:N7" headerRowCount="1">
+  <autoFilter ref="A4:N7"/>
   <tableColumns count="14">
     <tableColumn id="1" name="Tier"/>
     <tableColumn id="2" name="Game"/>
@@ -692,7 +692,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Snapshot of the live model, generated 2026-09-02T05:13:05+00:00. Read-only: the model runs in the pipeline, not in this file.</t>
+          <t>Snapshot of the live model, generated 2026-09-02T12:04:47+00:00. Read-only: the model runs in the pipeline, not in this file.</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02T05:13:05+00:00</t>
+          <t>2026-09-02T12:04:47+00:00</t>
         </is>
       </c>
     </row>
@@ -2289,7 +2289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2553,114 +2553,6 @@
       <c r="N7" s="4" t="inlineStr">
         <is>
           <t>2026-09-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>SF @ LAR</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Under 48.5</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="n">
-        <v>-115</v>
-      </c>
-      <c r="F8" s="13" t="n">
-        <v>0.5911</v>
-      </c>
-      <c r="G8" s="13" t="n">
-        <v>0.5349</v>
-      </c>
-      <c r="H8" s="13" t="n">
-        <v>0.0424</v>
-      </c>
-      <c r="I8" s="13" t="n">
-        <v>0.0562</v>
-      </c>
-      <c r="J8" s="14" t="n">
-        <v>-3.53</v>
-      </c>
-      <c r="K8" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L8" s="16" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="M8" s="16" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="N8" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>NYJ @ TEN</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Over 38.5</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>-115</v>
-      </c>
-      <c r="F9" s="8" t="n">
-        <v>0.5863</v>
-      </c>
-      <c r="G9" s="8" t="n">
-        <v>0.5349</v>
-      </c>
-      <c r="H9" s="8" t="n">
-        <v>0.0403</v>
-      </c>
-      <c r="I9" s="8" t="n">
-        <v>0.0514</v>
-      </c>
-      <c r="J9" s="9" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="K9" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L9" s="11" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="M9" s="11" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="N9" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -2891,84 +2783,92 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>LEAN</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>SF @ LAR</t>
+          <t>SEA @ ARI</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Under 48.5</t>
+          <t>ARI ML</t>
         </is>
       </c>
       <c r="E8" s="12" t="n">
-        <v>-115</v>
+        <v>400</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5911</v>
+        <v>0.2593</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>0.5349</v>
+        <v>0.2</v>
       </c>
       <c r="H8" s="13" t="n">
-        <v>0.0424</v>
+        <v>0.0436</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>0.1050788805197023</v>
+        <v>0.2943176647439902</v>
       </c>
       <c r="J8" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="K8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>correlated with a stronger play on the same game</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>LEAN</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>NYJ @ TEN</t>
+          <t>MIA @ SF</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Over 38.5</t>
+          <t>MIA +10.5</t>
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>0.5863</v>
+        <v>0.5809</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>0.5349</v>
+        <v>0.5238</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>0.0403</v>
+        <v>0.0427</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>0.09609813123903277</v>
+        <v>0.108983771024415</v>
       </c>
       <c r="J9" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="K9" s="4" t="inlineStr"/>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>correlated with a stronger play on the same game</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -2978,7 +2878,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>SEA @ ARI</t>
+          <t>IND @ KC</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2988,32 +2888,28 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>ARI ML</t>
+          <t>IND ML</t>
         </is>
       </c>
       <c r="E10" s="12" t="n">
-        <v>400</v>
+        <v>270</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.2593</v>
+        <v>0.3171</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>0.2</v>
+        <v>0.2703</v>
       </c>
       <c r="H10" s="13" t="n">
-        <v>0.0436</v>
+        <v>0.0381</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>0.2943176647439902</v>
+        <v>0.1718450921457355</v>
       </c>
       <c r="J10" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>correlated with a stronger play on the same game</t>
-        </is>
-      </c>
+      <c r="K10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -3023,42 +2919,38 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
       